--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -9,25 +9,23 @@
   <sheets>
     <sheet name="Opis parametrów" sheetId="2" r:id="rId2"/>
     <sheet name="Oddziały" sheetId="3" r:id="rId3"/>
-    <sheet name="Dzienniki zajeć innych" sheetId="4" r:id="rId4"/>
-    <sheet name="Dyżury" sheetId="5" r:id="rId5"/>
+    <sheet name="Dyżury" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Oddziały!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dzienniki zajeć innych'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dyżury!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Dyżury!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="152">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 16.02.2026 (pon.) - 22.02.2026 (niedz.)</t>
+    <t>Okres: 23.02.2026 (pon.) - 01.03.2026 (niedz.)</t>
   </si>
   <si>
     <t>Dzień</t>
@@ -57,7 +55,82 @@
     <t>Forma płatności</t>
   </si>
   <si>
-    <t>16.02.2026</t>
+    <t>23.02.2026</t>
+  </si>
+  <si>
+    <t>3, 09:40-10:25</t>
+  </si>
+  <si>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>3FA</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t>prF3</t>
+  </si>
+  <si>
+    <t>Sobczak Anna</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Dodatkowo płatne</t>
+  </si>
+  <si>
+    <t>5, 11:25-12:10</t>
+  </si>
+  <si>
+    <t>3K</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Ulanowska Magdalena</t>
+  </si>
+  <si>
+    <t>6, 12:25-13:10</t>
+  </si>
+  <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>Zajęcia z wychowawcą</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Socha Dariusz</t>
+  </si>
+  <si>
+    <t>7, 13:15-14:00</t>
+  </si>
+  <si>
+    <t>2S</t>
+  </si>
+  <si>
+    <t>Leńczowska Iwona</t>
+  </si>
+  <si>
+    <t>8, 14:05-14:50</t>
+  </si>
+  <si>
+    <t>3S</t>
+  </si>
+  <si>
+    <t>Biologia</t>
+  </si>
+  <si>
+    <t>Sałdyka Karolina</t>
   </si>
   <si>
     <t>1, 08:00-08:45</t>
@@ -66,9 +139,6 @@
     <t>Stępień Krystyna</t>
   </si>
   <si>
-    <t>2CB</t>
-  </si>
-  <si>
     <t>Technika w produkcji cukierniczej</t>
   </si>
   <si>
@@ -78,18 +148,12 @@
     <t>Uczniowie przychodzą później</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
     <t>2, 08:50-09:35</t>
   </si>
   <si>
-    <t>3, 09:40-10:25</t>
-  </si>
-  <si>
     <t>1CA|JA1</t>
   </si>
   <si>
@@ -102,9 +166,6 @@
     <t>Karczmarz Aleksandra</t>
   </si>
   <si>
-    <t>Dodatkowo płatne</t>
-  </si>
-  <si>
     <t>1CA|JA2</t>
   </si>
   <si>
@@ -117,16 +178,7 @@
     <t>3CA</t>
   </si>
   <si>
-    <t>Chemia</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Hudziec Agnieszka</t>
-  </si>
-  <si>
-    <t>5, 11:25-12:10</t>
+    <t>Małecka Barbara</t>
   </si>
   <si>
     <t>30</t>
@@ -135,13 +187,58 @@
     <t>Kończyńska Małgorzata</t>
   </si>
   <si>
-    <t>6, 12:25-13:10</t>
-  </si>
-  <si>
     <t>Technologie produkcji cukierniczej</t>
   </si>
   <si>
-    <t>17.02.2026</t>
+    <t>Taszycka Magdalena</t>
+  </si>
+  <si>
+    <t>1FB|JA1</t>
+  </si>
+  <si>
+    <t>Informatyka</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>1TFB|JA1</t>
+  </si>
+  <si>
+    <t>2TFB|JA2</t>
+  </si>
+  <si>
+    <t>3TFA|JA2</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
+    <t>1TFB|JA2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Cieśla Marcin</t>
+  </si>
+  <si>
+    <t>1TH|JA2</t>
+  </si>
+  <si>
+    <t>Biznes i zarządzanie</t>
+  </si>
+  <si>
+    <t>Uczniowie zwolnieni do domu</t>
+  </si>
+  <si>
+    <t>24.02.2026</t>
   </si>
   <si>
     <t>Antoszewska Joanna</t>
@@ -156,412 +253,229 @@
     <t>sg2</t>
   </si>
   <si>
-    <t>Nestoruk Lidia</t>
-  </si>
-  <si>
-    <t>Świerzewicz Katarzyna</t>
-  </si>
-  <si>
-    <t>3K</t>
-  </si>
-  <si>
-    <t>Technologia gastronomiczna z towaroznawstwem</t>
+    <t>2WA</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3FB|DZ</t>
+  </si>
+  <si>
+    <t>sg4</t>
+  </si>
+  <si>
+    <t>3M|JN2</t>
+  </si>
+  <si>
+    <t>sg1</t>
+  </si>
+  <si>
+    <t>Okienko dla uczniów</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>3S|DZ</t>
+  </si>
+  <si>
+    <t>aq1</t>
+  </si>
+  <si>
+    <t>25.02.2026</t>
+  </si>
+  <si>
+    <t>2CA|DZ</t>
+  </si>
+  <si>
+    <t>2WA|CH</t>
+  </si>
+  <si>
+    <t>Skarupa Agnieszka</t>
+  </si>
+  <si>
+    <t>3TH|JA2</t>
+  </si>
+  <si>
+    <t>Symulacyjna firma handlowa</t>
   </si>
   <si>
     <t>37</t>
   </si>
   <si>
-    <t>Mocarski Arkadiusz</t>
-  </si>
-  <si>
-    <t>Zajęcia z wychowawcą</t>
-  </si>
-  <si>
-    <t>2WA</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Pietrycha Małgorzata</t>
-  </si>
-  <si>
-    <t>Technika w produkcji gastronomicznej</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>3FB|DZ</t>
-  </si>
-  <si>
-    <t>sg4</t>
-  </si>
-  <si>
-    <t>Dalach Sławomir</t>
-  </si>
-  <si>
-    <t>7, 13:15-14:00</t>
-  </si>
-  <si>
-    <t>8, 14:05-14:50</t>
-  </si>
-  <si>
-    <t>18.02.2026</t>
-  </si>
-  <si>
-    <t>Biezmienow Małgorzata</t>
-  </si>
-  <si>
-    <t>2K|JA2</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>2CA|DZ</t>
+    <t>Zastępstwo</t>
+  </si>
+  <si>
+    <t>Pracownia sprzedaży</t>
+  </si>
+  <si>
+    <t>1FA|JA2</t>
+  </si>
+  <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>1TH|JA1</t>
+  </si>
+  <si>
+    <t>26.02.2026</t>
   </si>
   <si>
     <t>5TF</t>
   </si>
   <si>
-    <t>Zastępstwo</t>
-  </si>
-  <si>
-    <t>lekcja przeniesiona, zajęcia z wychowawcą za lekcję 1</t>
-  </si>
-  <si>
-    <t>2FB</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
-  </si>
-  <si>
-    <t>2WA|CH</t>
-  </si>
-  <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>44</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>4TFB|dz2</t>
+  </si>
+  <si>
+    <t>Nowaczyk Agnieszka</t>
+  </si>
+  <si>
+    <t>3TH</t>
+  </si>
+  <si>
+    <t>Język angielski zawodowy</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>9, 14:55-15:40</t>
+  </si>
+  <si>
+    <t>10, 15:45-16:30</t>
+  </si>
+  <si>
+    <t>3FB</t>
+  </si>
+  <si>
+    <t>11, 16:35-17:20</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>12, 17:25-18:10</t>
+  </si>
+  <si>
+    <t>13, 18:15-19:00</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>2TFA|JA2</t>
+  </si>
+  <si>
+    <t>3TH|JA1</t>
+  </si>
+  <si>
+    <t>1CB|JA1</t>
+  </si>
+  <si>
+    <t>1TFA|JA2</t>
+  </si>
+  <si>
+    <t>1WB|JN1</t>
+  </si>
+  <si>
+    <t>27.02.2026</t>
+  </si>
+  <si>
+    <t>2TH|DZ</t>
+  </si>
+  <si>
+    <t>2TFB|DZ</t>
+  </si>
+  <si>
+    <t>1CB|JA2</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</t>
+  </si>
+  <si>
+    <t>1CA</t>
+  </si>
+  <si>
+    <t>1FB|JA2</t>
+  </si>
+  <si>
+    <t>1WA|JN1</t>
+  </si>
+  <si>
+    <t>1FA|JA1</t>
+  </si>
+  <si>
+    <t>1K|JA1</t>
+  </si>
+  <si>
+    <t>1FC|JA1</t>
+  </si>
+  <si>
+    <t>1S|JA1</t>
+  </si>
+  <si>
+    <t>Godzina</t>
+  </si>
+  <si>
+    <t>Nauczyciel</t>
+  </si>
+  <si>
+    <t>Miejsce dyżuru</t>
+  </si>
+  <si>
+    <t>10:25-10:35</t>
+  </si>
+  <si>
+    <t>piętro_1</t>
+  </si>
+  <si>
+    <t>Jastrzębska-Majtyka Agnieszka</t>
+  </si>
+  <si>
+    <t>08:45-08:50</t>
+  </si>
+  <si>
+    <t>piętro_3</t>
+  </si>
+  <si>
+    <t>Najwer Maciej</t>
+  </si>
+  <si>
+    <t>11:20-11:25</t>
   </si>
   <si>
     <t>Misiąg Anna</t>
   </si>
   <si>
-    <t>2S</t>
-  </si>
-  <si>
-    <t>Edukacja obywatelska</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Kopij Marcin</t>
-  </si>
-  <si>
-    <t>Dalach Krystyna</t>
-  </si>
-  <si>
-    <t>2CA</t>
-  </si>
-  <si>
-    <t>Język polski</t>
-  </si>
-  <si>
-    <t>Filipek Anna</t>
-  </si>
-  <si>
-    <t>3TFB|JA1</t>
-  </si>
-  <si>
-    <t>Uczniowie zwolnieni do domu</t>
-  </si>
-  <si>
-    <t>19.02.2026</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>4TFB|JA2</t>
-  </si>
-  <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
-    <t>2TFA|JA1</t>
-  </si>
-  <si>
-    <t>Informatyka</t>
-  </si>
-  <si>
-    <t>konferencja o AI dla jednostek samorządu (bez opieki nad uczniami)</t>
-  </si>
-  <si>
-    <t>1TFB|JA1</t>
-  </si>
-  <si>
-    <t>Zajęcia biblioteczne</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>Zając Ewa</t>
-  </si>
-  <si>
-    <t>1TH|JA1</t>
-  </si>
-  <si>
-    <t>3FB</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Fiodorów Małgorzata</t>
-  </si>
-  <si>
-    <t>4TFB|dz2</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Staliś Donata</t>
-  </si>
-  <si>
-    <t>3TH|JA1</t>
-  </si>
-  <si>
-    <t>2FA</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - barber</t>
-  </si>
-  <si>
-    <t>prF3</t>
-  </si>
-  <si>
-    <t>Sobczak Anna</t>
-  </si>
-  <si>
-    <t>1TFA|JA1</t>
-  </si>
-  <si>
-    <t>Wójcik Kamil</t>
-  </si>
-  <si>
-    <t>2TH</t>
-  </si>
-  <si>
-    <t>Biznes i zarządzanie</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Socha Dariusz</t>
-  </si>
-  <si>
-    <t>Smirnow-Zechman Eleonora</t>
-  </si>
-  <si>
-    <t>2TFB</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Krzemińska Beata</t>
-  </si>
-  <si>
-    <t>Pracownia sprzedaży</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>1TFB|JA2</t>
-  </si>
-  <si>
-    <t>Nowak Damiana</t>
-  </si>
-  <si>
-    <t>1TH</t>
-  </si>
-  <si>
-    <t>Danielewski Paweł</t>
-  </si>
-  <si>
-    <t>1WB|JN2</t>
-  </si>
-  <si>
-    <t>Ostrowska Ewa</t>
-  </si>
-  <si>
-    <t>2B</t>
-  </si>
-  <si>
-    <t>Matematyka</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Rada Pedagogiczna w SP4</t>
-  </si>
-  <si>
-    <t>1CB</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>Kosin Anna</t>
-  </si>
-  <si>
-    <t>9, 14:55-15:40</t>
-  </si>
-  <si>
-    <t>1FA</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
-    <t>10, 15:45-16:30</t>
-  </si>
-  <si>
-    <t>11, 16:35-17:20</t>
-  </si>
-  <si>
-    <t>12, 17:25-18:10</t>
-  </si>
-  <si>
-    <t>1S</t>
-  </si>
-  <si>
-    <t>20.02.2026</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - Zasady zdrowego żywienia</t>
-  </si>
-  <si>
-    <t>2TH|DZ</t>
-  </si>
-  <si>
-    <t>2TFB|DZ</t>
-  </si>
-  <si>
-    <t>1CA</t>
-  </si>
-  <si>
-    <t>1CB|JA2</t>
-  </si>
-  <si>
-    <t>Jastrzębska-Majtyka Agnieszka</t>
-  </si>
-  <si>
-    <t>Godzina</t>
-  </si>
-  <si>
-    <t>Nauczyciel</t>
-  </si>
-  <si>
-    <t>Dziennik zajęć innych</t>
-  </si>
-  <si>
-    <t>Opis zajęć</t>
-  </si>
-  <si>
-    <t>18:00-19:30</t>
-  </si>
-  <si>
-    <t>Zofia Nykiel  - 5 TFB - indywidualne nauczanie</t>
-  </si>
-  <si>
-    <t>język angielski 2 godziny lekcyjne</t>
-  </si>
-  <si>
-    <t>Miejsce dyżuru</t>
-  </si>
-  <si>
-    <t>08:45-08:50</t>
+    <t>13:10-13:15</t>
+  </si>
+  <si>
+    <t>Czukiewska Bożena</t>
   </si>
   <si>
     <t>boisko - dziedziniec wejściowy/boisko</t>
   </si>
   <si>
+    <t>12:10-12:25</t>
+  </si>
+  <si>
+    <t>07:55-08:00</t>
+  </si>
+  <si>
+    <t>piętro_2</t>
+  </si>
+  <si>
     <t>09:35-09:40</t>
   </si>
   <si>
-    <t>11:20-11:25</t>
-  </si>
-  <si>
-    <t>piętro_2</t>
-  </si>
-  <si>
-    <t>14:00-14:05</t>
-  </si>
-  <si>
-    <t>piętro_1</t>
-  </si>
-  <si>
-    <t>Zaleska Magdalena</t>
-  </si>
-  <si>
-    <t>Piątek-Pawłowska Bożena</t>
-  </si>
-  <si>
-    <t>13:10-13:15</t>
-  </si>
-  <si>
-    <t>Derezińska Katarzyna</t>
-  </si>
-  <si>
-    <t>17:20-17:25</t>
-  </si>
-  <si>
-    <t>parter</t>
-  </si>
-  <si>
-    <t>Nowaczyk Agnieszka</t>
-  </si>
-  <si>
-    <t>18:10-18:15</t>
-  </si>
-  <si>
-    <t>07:55-08:00</t>
-  </si>
-  <si>
-    <t>piętro_3</t>
-  </si>
-  <si>
-    <t>10:25-10:35</t>
-  </si>
-  <si>
-    <t>Małecka Barbara</t>
-  </si>
-  <si>
-    <t>12:10-12:25</t>
+    <t>14:50-14:55</t>
+  </si>
+  <si>
+    <t>16:30-16:35</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +925,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{331e98f9-cd60-41e7-b98b-cec92a849a20}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e6afb607-2b77-4305-8b6f-d89fe6610e1b}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1032,18 +946,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2107e708-ee7b-4ee1-88b1-7e18fa97ff9b}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ac7d8b98-5ced-4b7b-a4e3-dabc1831f304}">
   <dimension ref="A1:I96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="56.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="55.8571428571429" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
-    <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="61.1428571428571" customWidth="1"/>
+    <col min="7" max="7" width="27.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1116,16 +1030,16 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
@@ -1139,28 +1053,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
@@ -1168,28 +1082,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>23</v>
       </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -1197,28 +1111,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -1226,28 +1140,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -1255,2580 +1169,2580 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
       </c>
       <c r="I9" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
         <v>45</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>46</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>47</v>
       </c>
-      <c r="F10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
         <v>49</v>
-      </c>
-      <c r="H10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
         <v>39</v>
       </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" t="s">
-        <v>47</v>
-      </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G14" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H14" t="s">
         <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G15" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s">
         <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G18" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H18" t="s">
         <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F20" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="H20" t="s">
         <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H21" t="s">
         <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H22" t="s">
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E23" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="H23" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E24" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H24" t="s">
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" t="s">
         <v>75</v>
       </c>
-      <c r="E27" t="s">
-        <v>23</v>
-      </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="F29" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G29" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s">
         <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="G30" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="G31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F34" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D35" t="s">
         <v>89</v>
       </c>
       <c r="E35" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F35" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H35" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="D36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" t="s">
+        <v>75</v>
+      </c>
+      <c r="F36" t="s">
         <v>80</v>
       </c>
-      <c r="E36" t="s">
-        <v>38</v>
-      </c>
-      <c r="F36" t="s">
-        <v>55</v>
-      </c>
       <c r="G36" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D37" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F37" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="D38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E38" t="s">
         <v>92</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>93</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>94</v>
       </c>
-      <c r="G38" t="s">
-        <v>95</v>
-      </c>
       <c r="H38" t="s">
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D39" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E39" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F39" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="F40" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="E41" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="F41" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="H41" t="s">
         <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="D42" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E42" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="F42" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E43" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="F43" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B44" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="D44" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F44" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G44" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B45" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E45" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F45" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="G45" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D46" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="E46" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F46" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="G46" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D47" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="F47" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="G47" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E48" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F48" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="G48" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D49" t="s">
         <v>100</v>
       </c>
       <c r="E49" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F49" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="G49" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E50" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="F50" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G50" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E51" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F51" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="G51" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C52" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D52" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E52" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="F52" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="G52" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="H52" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="D53" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E53" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="F53" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="G53" t="s">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D54" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="E54" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="F54" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="G54" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="C55" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E55" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="F55" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="G55" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B56" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="C56" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="D56" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E56" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="F56" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G56" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>37</v>
+        <v>110</v>
       </c>
       <c r="C57" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D57" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E57" t="s">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="F57" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="G57" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E58" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F58" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="G58" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="C59" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E59" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F59" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="G59" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C60" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E60" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="F60" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="G60" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="H60" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C61" t="s">
+        <v>38</v>
+      </c>
+      <c r="D61" t="s">
         <v>114</v>
       </c>
-      <c r="D61" t="s">
-        <v>125</v>
-      </c>
       <c r="E61" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="F61" t="s">
-        <v>117</v>
+        <v>40</v>
       </c>
       <c r="G61" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="D62" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E62" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="F62" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="G62" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C63" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="D63" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="E63" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="F63" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="G63" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H63" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B64" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C64" t="s">
+        <v>38</v>
+      </c>
+      <c r="D64" t="s">
         <v>114</v>
       </c>
-      <c r="D64" t="s">
-        <v>133</v>
-      </c>
       <c r="E64" t="s">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="F64" t="s">
-        <v>134</v>
+        <v>40</v>
       </c>
       <c r="G64" t="s">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B65" t="s">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="D65" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="E65" t="s">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="F65" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="G65" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="H65" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B66" t="s">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="C66" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="D66" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="E66" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="F66" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="G66" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B67" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="C67" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="D67" t="s">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="E67" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="F67" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="G67" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="H67" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B68" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="D68" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="E68" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="F68" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="G68" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B69" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="C69" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="D69" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E69" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="F69" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="G69" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="C70" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="D70" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="E70" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="F70" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="G70" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="B71" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C71" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="D71" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="E71" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F71" t="s">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="G71" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="B72" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C72" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D72" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="E72" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="F72" t="s">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="G72" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C73" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="D73" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="E73" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="F73" t="s">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="G73" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="E74" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="F74" t="s">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="G74" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B75" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D75" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="E75" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F75" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B76" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C76" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D76" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="E76" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F76" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="G76" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B77" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C77" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D77" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="E77" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="F77" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G77" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B78" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C78" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="D78" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="E78" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F78" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="G78" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C79" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D79" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="E79" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="F79" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="G79" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B80" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C80" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D80" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="E80" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F80" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="G80" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B81" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C81" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D81" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E81" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F81" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="G81" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B82" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C82" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D82" t="s">
+        <v>123</v>
+      </c>
+      <c r="E82" t="s">
+        <v>75</v>
+      </c>
+      <c r="F82" t="s">
         <v>80</v>
       </c>
-      <c r="E82" t="s">
-        <v>81</v>
-      </c>
-      <c r="F82" t="s">
-        <v>35</v>
-      </c>
       <c r="G82" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B83" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C83" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D83" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="E83" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="F83" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="G83" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C84" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D84" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E84" t="s">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="F84" t="s">
-        <v>134</v>
+        <v>40</v>
       </c>
       <c r="G84" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B85" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C85" t="s">
+        <v>38</v>
+      </c>
+      <c r="D85" t="s">
+        <v>125</v>
+      </c>
+      <c r="E85" t="s">
+        <v>55</v>
+      </c>
+      <c r="F85" t="s">
         <v>40</v>
       </c>
-      <c r="D85" t="s">
-        <v>147</v>
-      </c>
-      <c r="E85" t="s">
-        <v>42</v>
-      </c>
-      <c r="F85" t="s">
-        <v>57</v>
-      </c>
       <c r="G85" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C86" t="s">
+        <v>38</v>
+      </c>
+      <c r="D86" t="s">
+        <v>125</v>
+      </c>
+      <c r="E86" t="s">
+        <v>55</v>
+      </c>
+      <c r="F86" t="s">
         <v>40</v>
       </c>
-      <c r="D86" t="s">
-        <v>148</v>
-      </c>
-      <c r="E86" t="s">
-        <v>42</v>
-      </c>
-      <c r="F86" t="s">
-        <v>57</v>
-      </c>
       <c r="G86" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D87" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="E87" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F87" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="G87" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B88" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C88" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D88" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E88" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F88" t="s">
-        <v>134</v>
+        <v>40</v>
       </c>
       <c r="G88" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B89" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D89" t="s">
-        <v>150</v>
+        <v>69</v>
       </c>
       <c r="E89" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F89" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G89" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B90" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C90" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D90" t="s">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="E90" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="F90" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G90" t="s">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B91" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C91" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="D91" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="E91" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F91" t="s">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="G91" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B92" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C92" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D92" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E92" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="F92" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="G92" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B93" t="s">
+        <v>30</v>
+      </c>
+      <c r="C93" t="s">
+        <v>56</v>
+      </c>
+      <c r="D93" t="s">
+        <v>128</v>
+      </c>
+      <c r="E93" t="s">
+        <v>58</v>
+      </c>
+      <c r="F93" t="s">
         <v>59</v>
       </c>
-      <c r="C93" t="s">
-        <v>40</v>
-      </c>
-      <c r="D93" t="s">
-        <v>150</v>
-      </c>
-      <c r="E93" t="s">
-        <v>42</v>
-      </c>
-      <c r="F93" t="s">
-        <v>57</v>
-      </c>
       <c r="G93" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B94" t="s">
+        <v>33</v>
+      </c>
+      <c r="C94" t="s">
+        <v>56</v>
+      </c>
+      <c r="D94" t="s">
+        <v>129</v>
+      </c>
+      <c r="E94" t="s">
+        <v>58</v>
+      </c>
+      <c r="F94" t="s">
         <v>59</v>
       </c>
-      <c r="C94" t="s">
-        <v>62</v>
-      </c>
-      <c r="D94" t="s">
-        <v>80</v>
-      </c>
-      <c r="E94" t="s">
-        <v>50</v>
-      </c>
-      <c r="F94" t="s">
-        <v>64</v>
-      </c>
       <c r="G94" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B95" t="s">
+        <v>107</v>
+      </c>
+      <c r="C95" t="s">
+        <v>56</v>
+      </c>
+      <c r="D95" t="s">
+        <v>130</v>
+      </c>
+      <c r="E95" t="s">
+        <v>58</v>
+      </c>
+      <c r="F95" t="s">
         <v>59</v>
       </c>
-      <c r="C95" t="s">
-        <v>45</v>
-      </c>
-      <c r="D95" t="s">
-        <v>121</v>
-      </c>
-      <c r="E95" t="s">
-        <v>50</v>
-      </c>
-      <c r="F95" t="s">
-        <v>134</v>
-      </c>
       <c r="G95" t="s">
-        <v>151</v>
+        <v>42</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B96" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="C96" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D96" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="E96" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F96" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G96" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3839,96 +3753,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{15630c25-5c19-4932-b180-d6a1d384d42f}">
-  <dimension ref="A1:I2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4f06a7a6-1527-414e-97f6-03851b64f663}">
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="41.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="30.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
-    <col min="7" max="7" width="11.4285714285714" customWidth="1"/>
-    <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
-    <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="56.25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15">
-      <c r="A2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{de367c59-cfed-4db7-9933-bfb70fe72043}">
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
-    <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="24.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3937,13 +3770,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -3954,19 +3787,19 @@
     </row>
     <row r="2" spans="1:6" ht="15">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -3974,19 +3807,19 @@
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -3994,19 +3827,19 @@
     </row>
     <row r="4" spans="1:6" ht="15">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -4014,19 +3847,19 @@
     </row>
     <row r="5" spans="1:6" ht="15">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -4034,19 +3867,19 @@
     </row>
     <row r="6" spans="1:6" ht="15">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
-        <v>167</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -4054,19 +3887,19 @@
     </row>
     <row r="7" spans="1:6" ht="15">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>168</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -4074,19 +3907,19 @@
     </row>
     <row r="8" spans="1:6" ht="15">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -4094,19 +3927,19 @@
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -4114,19 +3947,19 @@
     </row>
     <row r="10" spans="1:6" ht="15">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="E10" t="s">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -4134,19 +3967,19 @@
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" t="s">
         <v>143</v>
       </c>
-      <c r="B11" t="s">
-        <v>175</v>
-      </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -4154,19 +3987,19 @@
     </row>
     <row r="12" spans="1:6" ht="15">
       <c r="A12" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="B12" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -4174,19 +4007,19 @@
     </row>
     <row r="13" spans="1:6" ht="15">
       <c r="A13" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="E13" t="s">
-        <v>178</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -4194,19 +4027,19 @@
     </row>
     <row r="14" spans="1:6" ht="15">
       <c r="A14" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="B14" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -4214,21 +4047,121 @@
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="A15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" t="s">
         <v>143</v>
       </c>
-      <c r="B15" t="s">
-        <v>179</v>
-      </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15">
+      <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15">
+      <c r="A17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
+        <v>145</v>
+      </c>
+      <c r="E17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15">
+      <c r="A18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
+        <v>139</v>
+      </c>
+      <c r="E18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15">
+      <c r="A19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15">
+      <c r="A20" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" t="s">
         <v>18</v>
       </c>
     </row>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="245">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -118,7 +118,16 @@
     <t>2S</t>
   </si>
   <si>
-    <t>Leńczowska Iwona</t>
+    <t>Zajęcia biblioteczne</t>
+  </si>
+  <si>
+    <t>bib</t>
+  </si>
+  <si>
+    <t>Nowak Damiana</t>
+  </si>
+  <si>
+    <t>Bezpłatne</t>
   </si>
   <si>
     <t>8, 14:05-14:50</t>
@@ -133,6 +142,36 @@
     <t>Sałdyka Karolina</t>
   </si>
   <si>
+    <t>4, 10:35-11:20</t>
+  </si>
+  <si>
+    <t>Smirnow-Zechman Eleonora</t>
+  </si>
+  <si>
+    <t>1CA</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Rejno Julita</t>
+  </si>
+  <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>Biznes i zarządzanie</t>
+  </si>
+  <si>
+    <t>Najwer Maciej</t>
+  </si>
+  <si>
     <t>1, 08:00-08:45</t>
   </si>
   <si>
@@ -169,12 +208,6 @@
     <t>1CA|JA2</t>
   </si>
   <si>
-    <t>Bezpłatne</t>
-  </si>
-  <si>
-    <t>4, 10:35-11:20</t>
-  </si>
-  <si>
     <t>3CA</t>
   </si>
   <si>
@@ -232,9 +265,6 @@
     <t>1TH|JA2</t>
   </si>
   <si>
-    <t>Biznes i zarządzanie</t>
-  </si>
-  <si>
     <t>Uczniowie zwolnieni do domu</t>
   </si>
   <si>
@@ -253,36 +283,189 @@
     <t>sg2</t>
   </si>
   <si>
+    <t>Nestoruk Lidia</t>
+  </si>
+  <si>
     <t>2WA</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>Pietrycha Małgorzata</t>
+  </si>
+  <si>
     <t>3FB|DZ</t>
   </si>
   <si>
     <t>sg4</t>
   </si>
   <si>
+    <t>Dalach Sławomir</t>
+  </si>
+  <si>
     <t>3M|JN2</t>
   </si>
   <si>
     <t>sg1</t>
   </si>
   <si>
+    <t>Wójcik Kamil</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
     <t>Okienko dla uczniów</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>3S|DZ</t>
   </si>
   <si>
     <t>aq1</t>
   </si>
   <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>Zastępstwo</t>
+  </si>
+  <si>
+    <t>p. Rejno, zajęcia z wychowawcą za środę 25.02</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>Język niemiecki zawodowy</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>9, 14:55-15:40</t>
+  </si>
+  <si>
+    <t>10, 15:45-16:30</t>
+  </si>
+  <si>
+    <t>3WA</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Derezińska Katarzyna</t>
+  </si>
+  <si>
+    <t>11, 16:35-17:20</t>
+  </si>
+  <si>
+    <t>Bokuniewicz Sylwia</t>
+  </si>
+  <si>
+    <t>3TH|JA1</t>
+  </si>
+  <si>
+    <t>3TH|JA2</t>
+  </si>
+  <si>
+    <t>4TFB</t>
+  </si>
+  <si>
+    <t>Kosin Anna</t>
+  </si>
+  <si>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>Jastrzębska-Majtyka Agnieszka</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>1TFB</t>
+  </si>
+  <si>
+    <t>Chemia</t>
+  </si>
+  <si>
+    <t>1TH</t>
+  </si>
+  <si>
+    <t>Towar jako przedmiot handlu</t>
+  </si>
+  <si>
+    <t>Paleczny Maciej</t>
+  </si>
+  <si>
+    <t>3TFB|relu</t>
+  </si>
+  <si>
+    <t>Religia</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>3FB|relu</t>
+  </si>
+  <si>
+    <t>3CA|relu</t>
+  </si>
+  <si>
+    <t>3FA|relu</t>
+  </si>
+  <si>
+    <t>3TFA|relu</t>
+  </si>
+  <si>
+    <t>4TFB|relu</t>
+  </si>
+  <si>
+    <t>Świerzewicz Katarzyna</t>
+  </si>
+  <si>
+    <t>Technologia gastronomiczna z towaroznawstwem</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Mocarski Arkadiusz</t>
+  </si>
+  <si>
+    <t>Wakat3 edukacja zdrow.</t>
+  </si>
+  <si>
+    <t>3CA|edu</t>
+  </si>
+  <si>
+    <t>Edukacja zdrowotna</t>
+  </si>
+  <si>
+    <t>3FA|edu</t>
+  </si>
+  <si>
+    <t>3M|edu</t>
+  </si>
+  <si>
+    <t>3TFA|edu</t>
+  </si>
+  <si>
     <t>25.02.2026</t>
   </si>
   <si>
@@ -292,33 +475,78 @@
     <t>2WA|CH</t>
   </si>
   <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>2FA</t>
+  </si>
+  <si>
+    <t>2TH|relu</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>2FB|relu</t>
+  </si>
+  <si>
+    <t>2CA|relu</t>
+  </si>
+  <si>
     <t>Skarupa Agnieszka</t>
   </si>
   <si>
-    <t>3TH|JA2</t>
-  </si>
-  <si>
     <t>Symulacyjna firma handlowa</t>
   </si>
   <si>
     <t>37</t>
   </si>
   <si>
-    <t>Zastępstwo</t>
-  </si>
-  <si>
     <t>Pracownia sprzedaży</t>
   </si>
   <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>1WA</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>1FA|JA2</t>
   </si>
   <si>
-    <t>2TFA</t>
-  </si>
-  <si>
     <t>1TH|JA1</t>
   </si>
   <si>
+    <t>Wakat1 j. niemiecki</t>
+  </si>
+  <si>
+    <t>1WA|JN2</t>
+  </si>
+  <si>
+    <t>2FC|edu</t>
+  </si>
+  <si>
+    <t>2WA|edu</t>
+  </si>
+  <si>
+    <t>2S|edu</t>
+  </si>
+  <si>
+    <t>2CA|edu</t>
+  </si>
+  <si>
     <t>26.02.2026</t>
   </si>
   <si>
@@ -343,36 +571,33 @@
     <t>04</t>
   </si>
   <si>
-    <t>9, 14:55-15:40</t>
-  </si>
-  <si>
-    <t>10, 15:45-16:30</t>
-  </si>
-  <si>
     <t>3FB</t>
   </si>
   <si>
-    <t>11, 16:35-17:20</t>
-  </si>
-  <si>
-    <t>4B</t>
-  </si>
-  <si>
     <t>12, 17:25-18:10</t>
   </si>
   <si>
     <t>13, 18:15-19:00</t>
   </si>
   <si>
-    <t>2CA</t>
+    <t>2TFB</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>1CB</t>
+  </si>
+  <si>
+    <t>1FC</t>
+  </si>
+  <si>
+    <t>1S</t>
   </si>
   <si>
     <t>2TFA|JA2</t>
   </si>
   <si>
-    <t>3TH|JA1</t>
-  </si>
-  <si>
     <t>1CB|JA1</t>
   </si>
   <si>
@@ -394,21 +619,45 @@
     <t>1CB|JA2</t>
   </si>
   <si>
+    <t>1WB|relu</t>
+  </si>
+  <si>
+    <t>1TFA|relu</t>
+  </si>
+  <si>
+    <t>1TFB|relu</t>
+  </si>
+  <si>
+    <t>1S|relu</t>
+  </si>
+  <si>
+    <t>1CB|relu</t>
+  </si>
+  <si>
+    <t>1TH|relu</t>
+  </si>
+  <si>
+    <t>1WA|relu</t>
+  </si>
+  <si>
+    <t>1CA|relu</t>
+  </si>
+  <si>
+    <t>1FA|relu</t>
+  </si>
+  <si>
+    <t>1WB</t>
+  </si>
+  <si>
     <t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</t>
   </si>
   <si>
-    <t>1CA</t>
-  </si>
-  <si>
     <t>1FB|JA2</t>
   </si>
   <si>
     <t>1WA|JN1</t>
   </si>
   <si>
-    <t>1FA|JA1</t>
-  </si>
-  <si>
     <t>1K|JA1</t>
   </si>
   <si>
@@ -418,6 +667,15 @@
     <t>1S|JA1</t>
   </si>
   <si>
+    <t>Wakat2 matematyka</t>
+  </si>
+  <si>
+    <t>Matematyka</t>
+  </si>
+  <si>
+    <t>Młynarczyk Paweł</t>
+  </si>
+  <si>
     <t>Godzina</t>
   </si>
   <si>
@@ -433,18 +691,12 @@
     <t>piętro_1</t>
   </si>
   <si>
-    <t>Jastrzębska-Majtyka Agnieszka</t>
-  </si>
-  <si>
     <t>08:45-08:50</t>
   </si>
   <si>
     <t>piętro_3</t>
   </si>
   <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
     <t>11:20-11:25</t>
   </si>
   <si>
@@ -460,22 +712,49 @@
     <t>boisko - dziedziniec wejściowy/boisko</t>
   </si>
   <si>
+    <t>Jaworska Edyta</t>
+  </si>
+  <si>
     <t>12:10-12:25</t>
   </si>
   <si>
+    <t>09:35-09:40</t>
+  </si>
+  <si>
+    <t>piętro_2</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>15:40-15:45</t>
+  </si>
+  <si>
+    <t>Jarek Zbigniew</t>
+  </si>
+  <si>
+    <t>16:30-16:35</t>
+  </si>
+  <si>
+    <t>Ostrowska Ewa</t>
+  </si>
+  <si>
+    <t>14:00-14:05</t>
+  </si>
+  <si>
     <t>07:55-08:00</t>
   </si>
   <si>
-    <t>piętro_2</t>
-  </si>
-  <si>
-    <t>09:35-09:40</t>
+    <t>17:20-17:25</t>
+  </si>
+  <si>
+    <t>parter</t>
+  </si>
+  <si>
+    <t>18:10-18:15</t>
   </si>
   <si>
     <t>14:50-14:55</t>
-  </si>
-  <si>
-    <t>16:30-16:35</t>
   </si>
 </sst>
 </file>
@@ -925,7 +1204,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e6afb607-2b77-4305-8b6f-d89fe6610e1b}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{fe0b43fd-a9d3-4aac-a631-28790cdf6209}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -946,18 +1225,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ac7d8b98-5ced-4b7b-a4e3-dabc1831f304}">
-  <dimension ref="A1:I96"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{89ca7c21-d943-4075-a13a-e0d742228799}">
+  <dimension ref="A1:I169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="55.8571428571429" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
-    <col min="7" max="7" width="27.8571428571429" customWidth="1"/>
-    <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
+    <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="41.4285714285714" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1091,19 +1370,19 @@
         <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -1111,22 +1390,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
         <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
@@ -1140,28 +1419,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -1169,28 +1448,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
         <v>43</v>
       </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
@@ -1198,22 +1477,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
@@ -1227,28 +1506,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
@@ -1256,28 +1535,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1285,22 +1564,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
@@ -1314,28 +1593,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G13" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
@@ -1343,28 +1622,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
         <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1372,28 +1651,28 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G15" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
@@ -1401,28 +1680,28 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G16" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -1433,25 +1712,25 @@
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="H17" t="s">
         <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -1459,28 +1738,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="H18" t="s">
         <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1488,28 +1767,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" t="s">
         <v>69</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>70</v>
       </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
       <c r="G19" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -1517,2232 +1796,4349 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
         <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s">
         <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G22" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H22" t="s">
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F23" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G23" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s">
         <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G24" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s">
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E25" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F25" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G25" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G26" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G28" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G29" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s">
         <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" t="s">
         <v>85</v>
       </c>
-      <c r="E30" t="s">
-        <v>75</v>
-      </c>
       <c r="F30" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G30" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
+        <v>94</v>
+      </c>
+      <c r="E31" t="s">
         <v>85</v>
       </c>
-      <c r="E31" t="s">
-        <v>75</v>
-      </c>
       <c r="F31" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G31" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="E32" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="F32" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="G32" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E33" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G33" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F34" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G34" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="E35" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="F35" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="G35" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="H35" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="I35" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="E36" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="F36" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="G36" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="E37" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="F37" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="G37" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="F38" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="G38" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D39" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="F39" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="G39" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="E40" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="F40" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="G40" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="C41" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="E41" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="F41" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="G41" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="H41" t="s">
         <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="C42" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="F42" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="G42" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D43" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="E43" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="F43" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="G43" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="E44" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="G44" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E45" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F45" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G45" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="E46" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="F46" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B47" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C47" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="E47" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="F47" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="G47" t="s">
-        <v>42</v>
+        <v>121</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E48" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="F48" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B49" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="E49" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="F49" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="G49" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C50" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E50" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="F50" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="G50" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C51" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="E51" t="s">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="F51" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="G51" t="s">
-        <v>42</v>
+        <v>121</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="C52" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="D52" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="E52" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="F52" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="G52" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="C53" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="D53" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E53" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="F53" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="G53" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="D54" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="E54" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="F54" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="G54" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C55" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="D55" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="E55" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="F55" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="G55" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="D56" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="E56" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="F56" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="G56" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B57" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C57" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="D57" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="E57" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="F57" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="G57" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B58" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="D58" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E58" t="s">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="F58" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="G58" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="D59" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="E59" t="s">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="F59" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="G59" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C60" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="D60" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="E60" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="F60" t="s">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="G60" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C61" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="D61" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="E61" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="F61" t="s">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="G61" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C62" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="D62" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="E62" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="F62" t="s">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="G62" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C63" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="D63" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="E63" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="F63" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="G63" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B64" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="D64" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="E64" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="F64" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="G64" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B65" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C65" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="D65" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="E65" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="F65" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="G65" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B66" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C66" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="D66" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="E66" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="F66" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="G66" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B67" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="D67" t="s">
-        <v>66</v>
+        <v>150</v>
       </c>
       <c r="E67" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="F67" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="G67" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B68" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C68" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="D68" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="E68" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="F68" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="G68" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B69" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C69" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="E69" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="F69" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="G69" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B70" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C70" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="E70" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="F70" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="G70" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B71" t="s">
         <v>25</v>
       </c>
       <c r="C71" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="E71" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="F71" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="G71" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B72" t="s">
         <v>30</v>
       </c>
       <c r="C72" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="E72" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="F72" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="G72" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B73" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="C73" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="D73" t="s">
-        <v>98</v>
+        <v>155</v>
       </c>
       <c r="E73" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="F73" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="G73" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B74" t="s">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="C74" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="D74" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="E74" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="F74" t="s">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="G74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B75" t="s">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="C75" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="D75" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="E75" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="F75" t="s">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="G75" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B76" t="s">
         <v>50</v>
       </c>
       <c r="C76" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="D76" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E76" t="s">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="F76" t="s">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="G76" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B77" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C77" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="D77" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E77" t="s">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="F77" t="s">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="G77" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="D78" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E78" t="s">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="F78" t="s">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="G78" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C79" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="D79" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E79" t="s">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="F79" t="s">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="G79" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B80" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C80" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="D80" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E80" t="s">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="F80" t="s">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="G80" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B81" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C81" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="D81" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E81" t="s">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="F81" t="s">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="G81" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B82" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C82" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="D82" t="s">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="E82" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="F82" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="G82" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B83" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C83" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D83" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="E83" t="s">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="F83" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G83" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B84" t="s">
+        <v>36</v>
+      </c>
+      <c r="C84" t="s">
+        <v>41</v>
+      </c>
+      <c r="D84" t="s">
+        <v>165</v>
+      </c>
+      <c r="E84" t="s">
+        <v>48</v>
+      </c>
+      <c r="F84" t="s">
         <v>43</v>
       </c>
-      <c r="C84" t="s">
-        <v>38</v>
-      </c>
-      <c r="D84" t="s">
-        <v>114</v>
-      </c>
-      <c r="E84" t="s">
-        <v>124</v>
-      </c>
-      <c r="F84" t="s">
-        <v>40</v>
-      </c>
       <c r="G84" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B85" t="s">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="C85" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D85" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="E85" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F85" t="s">
-        <v>40</v>
+        <v>166</v>
       </c>
       <c r="G85" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B86" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C86" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D86" t="s">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="E86" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F86" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G86" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B87" t="s">
         <v>20</v>
       </c>
       <c r="C87" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D87" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="E87" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="F87" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G87" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B88" t="s">
         <v>25</v>
       </c>
       <c r="C88" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D88" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="E88" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F88" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G88" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B89" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C89" t="s">
-        <v>56</v>
+        <v>169</v>
       </c>
       <c r="D89" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="E89" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F89" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G89" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B90" t="s">
         <v>50</v>
       </c>
       <c r="C90" t="s">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="D90" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="E90" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F90" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="G90" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B91" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C91" t="s">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="D91" t="s">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="E91" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F91" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="G91" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B92" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C92" t="s">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="D92" t="s">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="E92" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F92" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="G92" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B93" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C93" t="s">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="D93" t="s">
-        <v>128</v>
+        <v>174</v>
       </c>
       <c r="E93" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F93" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="G93" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="B94" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C94" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="D94" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="E94" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="F94" t="s">
-        <v>59</v>
+        <v>177</v>
       </c>
       <c r="G94" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="C95" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="D95" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E95" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="F95" t="s">
-        <v>59</v>
+        <v>177</v>
       </c>
       <c r="G95" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
+        <v>83</v>
+      </c>
+      <c r="D96" t="s">
+        <v>176</v>
+      </c>
+      <c r="E96" t="s">
+        <v>85</v>
+      </c>
+      <c r="F96" t="s">
+        <v>177</v>
+      </c>
+      <c r="G96" t="s">
+        <v>55</v>
+      </c>
+      <c r="H96" t="s">
+        <v>18</v>
+      </c>
+      <c r="I96" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="15">
+      <c r="A97" t="s">
+        <v>175</v>
+      </c>
+      <c r="B97" t="s">
+        <v>40</v>
+      </c>
+      <c r="C97" t="s">
+        <v>83</v>
+      </c>
+      <c r="D97" t="s">
+        <v>178</v>
+      </c>
+      <c r="E97" t="s">
+        <v>85</v>
+      </c>
+      <c r="F97" t="s">
+        <v>177</v>
+      </c>
+      <c r="G97" t="s">
+        <v>55</v>
+      </c>
+      <c r="H97" t="s">
+        <v>18</v>
+      </c>
+      <c r="I97" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15">
+      <c r="A98" t="s">
+        <v>175</v>
+      </c>
+      <c r="B98" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98" t="s">
+        <v>83</v>
+      </c>
+      <c r="D98" t="s">
+        <v>178</v>
+      </c>
+      <c r="E98" t="s">
+        <v>85</v>
+      </c>
+      <c r="F98" t="s">
+        <v>177</v>
+      </c>
+      <c r="G98" t="s">
+        <v>55</v>
+      </c>
+      <c r="H98" t="s">
+        <v>18</v>
+      </c>
+      <c r="I98" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="15">
+      <c r="A99" t="s">
+        <v>175</v>
+      </c>
+      <c r="B99" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99" t="s">
+        <v>83</v>
+      </c>
+      <c r="D99" t="s">
+        <v>178</v>
+      </c>
+      <c r="E99" t="s">
+        <v>85</v>
+      </c>
+      <c r="F99" t="s">
+        <v>177</v>
+      </c>
+      <c r="G99" t="s">
+        <v>55</v>
+      </c>
+      <c r="H99" t="s">
+        <v>18</v>
+      </c>
+      <c r="I99" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="15">
+      <c r="A100" t="s">
+        <v>175</v>
+      </c>
+      <c r="B100" t="s">
+        <v>36</v>
+      </c>
+      <c r="C100" t="s">
+        <v>179</v>
+      </c>
+      <c r="D100" t="s">
+        <v>180</v>
+      </c>
+      <c r="E100" t="s">
+        <v>181</v>
+      </c>
+      <c r="F100" t="s">
+        <v>182</v>
+      </c>
+      <c r="G100" t="s">
+        <v>55</v>
+      </c>
+      <c r="H100" t="s">
+        <v>18</v>
+      </c>
+      <c r="I100" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="15">
+      <c r="A101" t="s">
+        <v>175</v>
+      </c>
+      <c r="B101" t="s">
+        <v>111</v>
+      </c>
+      <c r="C101" t="s">
+        <v>179</v>
+      </c>
+      <c r="D101" t="s">
+        <v>180</v>
+      </c>
+      <c r="E101" t="s">
+        <v>181</v>
+      </c>
+      <c r="F101" t="s">
+        <v>182</v>
+      </c>
+      <c r="G101" t="s">
+        <v>55</v>
+      </c>
+      <c r="H101" t="s">
+        <v>18</v>
+      </c>
+      <c r="I101" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="15">
+      <c r="A102" t="s">
+        <v>175</v>
+      </c>
+      <c r="B102" t="s">
+        <v>112</v>
+      </c>
+      <c r="C102" t="s">
+        <v>179</v>
+      </c>
+      <c r="D102" t="s">
+        <v>183</v>
+      </c>
+      <c r="E102" t="s">
+        <v>181</v>
+      </c>
+      <c r="F102" t="s">
+        <v>182</v>
+      </c>
+      <c r="G102" t="s">
+        <v>55</v>
+      </c>
+      <c r="H102" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="15">
+      <c r="A103" t="s">
+        <v>175</v>
+      </c>
+      <c r="B103" t="s">
+        <v>116</v>
+      </c>
+      <c r="C103" t="s">
+        <v>179</v>
+      </c>
+      <c r="D103" t="s">
+        <v>110</v>
+      </c>
+      <c r="E103" t="s">
+        <v>58</v>
+      </c>
+      <c r="F103" t="s">
+        <v>182</v>
+      </c>
+      <c r="G103" t="s">
+        <v>55</v>
+      </c>
+      <c r="H103" t="s">
+        <v>18</v>
+      </c>
+      <c r="I103" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15">
+      <c r="A104" t="s">
+        <v>175</v>
+      </c>
+      <c r="B104" t="s">
+        <v>184</v>
+      </c>
+      <c r="C104" t="s">
+        <v>179</v>
+      </c>
+      <c r="D104" t="s">
+        <v>110</v>
+      </c>
+      <c r="E104" t="s">
+        <v>58</v>
+      </c>
+      <c r="F104" t="s">
+        <v>182</v>
+      </c>
+      <c r="G104" t="s">
+        <v>55</v>
+      </c>
+      <c r="H104" t="s">
+        <v>18</v>
+      </c>
+      <c r="I104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="15">
+      <c r="A105" t="s">
+        <v>175</v>
+      </c>
+      <c r="B105" t="s">
+        <v>185</v>
+      </c>
+      <c r="C105" t="s">
+        <v>179</v>
+      </c>
+      <c r="D105" t="s">
+        <v>110</v>
+      </c>
+      <c r="E105" t="s">
+        <v>58</v>
+      </c>
+      <c r="F105" t="s">
+        <v>182</v>
+      </c>
+      <c r="G105" t="s">
+        <v>55</v>
+      </c>
+      <c r="H105" t="s">
+        <v>18</v>
+      </c>
+      <c r="I105" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="15">
+      <c r="A106" t="s">
+        <v>175</v>
+      </c>
+      <c r="B106" t="s">
+        <v>20</v>
+      </c>
+      <c r="C106" t="s">
+        <v>41</v>
+      </c>
+      <c r="D106" t="s">
+        <v>186</v>
+      </c>
+      <c r="E106" t="s">
+        <v>48</v>
+      </c>
+      <c r="F106" t="s">
+        <v>43</v>
+      </c>
+      <c r="G106" t="s">
+        <v>55</v>
+      </c>
+      <c r="H106" t="s">
+        <v>18</v>
+      </c>
+      <c r="I106" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="15">
+      <c r="A107" t="s">
+        <v>175</v>
+      </c>
+      <c r="B107" t="s">
+        <v>25</v>
+      </c>
+      <c r="C107" t="s">
+        <v>41</v>
+      </c>
+      <c r="D107" t="s">
+        <v>187</v>
+      </c>
+      <c r="E107" t="s">
+        <v>48</v>
+      </c>
+      <c r="F107" t="s">
+        <v>43</v>
+      </c>
+      <c r="G107" t="s">
+        <v>55</v>
+      </c>
+      <c r="H107" t="s">
+        <v>18</v>
+      </c>
+      <c r="I107" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15">
+      <c r="A108" t="s">
+        <v>175</v>
+      </c>
+      <c r="B108" t="s">
+        <v>30</v>
+      </c>
+      <c r="C108" t="s">
+        <v>41</v>
+      </c>
+      <c r="D108" t="s">
+        <v>127</v>
+      </c>
+      <c r="E108" t="s">
+        <v>48</v>
+      </c>
+      <c r="F108" t="s">
+        <v>43</v>
+      </c>
+      <c r="G108" t="s">
+        <v>55</v>
+      </c>
+      <c r="H108" t="s">
+        <v>18</v>
+      </c>
+      <c r="I108" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15">
+      <c r="A109" t="s">
+        <v>175</v>
+      </c>
+      <c r="B109" t="s">
+        <v>36</v>
+      </c>
+      <c r="C109" t="s">
+        <v>41</v>
+      </c>
+      <c r="D109" t="s">
+        <v>188</v>
+      </c>
+      <c r="E109" t="s">
+        <v>48</v>
+      </c>
+      <c r="F109" t="s">
+        <v>43</v>
+      </c>
+      <c r="G109" t="s">
+        <v>55</v>
+      </c>
+      <c r="H109" t="s">
+        <v>18</v>
+      </c>
+      <c r="I109" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="15">
+      <c r="A110" t="s">
+        <v>175</v>
+      </c>
+      <c r="B110" t="s">
+        <v>111</v>
+      </c>
+      <c r="C110" t="s">
+        <v>41</v>
+      </c>
+      <c r="D110" t="s">
+        <v>189</v>
+      </c>
+      <c r="E110" t="s">
+        <v>48</v>
+      </c>
+      <c r="F110" t="s">
+        <v>43</v>
+      </c>
+      <c r="G110" t="s">
+        <v>55</v>
+      </c>
+      <c r="H110" t="s">
+        <v>18</v>
+      </c>
+      <c r="I110" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="15">
+      <c r="A111" t="s">
+        <v>175</v>
+      </c>
+      <c r="B111" t="s">
+        <v>112</v>
+      </c>
+      <c r="C111" t="s">
+        <v>41</v>
+      </c>
+      <c r="D111" t="s">
+        <v>164</v>
+      </c>
+      <c r="E111" t="s">
+        <v>48</v>
+      </c>
+      <c r="F111" t="s">
+        <v>43</v>
+      </c>
+      <c r="G111" t="s">
+        <v>55</v>
+      </c>
+      <c r="H111" t="s">
+        <v>18</v>
+      </c>
+      <c r="I111" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="15">
+      <c r="A112" t="s">
+        <v>175</v>
+      </c>
+      <c r="B112" t="s">
+        <v>116</v>
+      </c>
+      <c r="C112" t="s">
+        <v>41</v>
+      </c>
+      <c r="D112" t="s">
+        <v>163</v>
+      </c>
+      <c r="E112" t="s">
+        <v>48</v>
+      </c>
+      <c r="F112" t="s">
+        <v>43</v>
+      </c>
+      <c r="G112" t="s">
+        <v>55</v>
+      </c>
+      <c r="H112" t="s">
+        <v>18</v>
+      </c>
+      <c r="I112" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="15">
+      <c r="A113" t="s">
+        <v>175</v>
+      </c>
+      <c r="B113" t="s">
+        <v>184</v>
+      </c>
+      <c r="C113" t="s">
+        <v>41</v>
+      </c>
+      <c r="D113" t="s">
+        <v>190</v>
+      </c>
+      <c r="E113" t="s">
+        <v>48</v>
+      </c>
+      <c r="F113" t="s">
+        <v>43</v>
+      </c>
+      <c r="G113" t="s">
+        <v>55</v>
+      </c>
+      <c r="H113" t="s">
+        <v>18</v>
+      </c>
+      <c r="I113" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="15">
+      <c r="A114" t="s">
+        <v>175</v>
+      </c>
+      <c r="B114" t="s">
+        <v>50</v>
+      </c>
+      <c r="C114" t="s">
+        <v>51</v>
+      </c>
+      <c r="D114" t="s">
+        <v>153</v>
+      </c>
+      <c r="E114" t="s">
+        <v>66</v>
+      </c>
+      <c r="F114" t="s">
+        <v>53</v>
+      </c>
+      <c r="G114" t="s">
+        <v>55</v>
+      </c>
+      <c r="H114" t="s">
+        <v>18</v>
+      </c>
+      <c r="I114" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="15">
+      <c r="A115" t="s">
+        <v>175</v>
+      </c>
+      <c r="B115" t="s">
         <v>56</v>
       </c>
-      <c r="D96" t="s">
+      <c r="C115" t="s">
+        <v>51</v>
+      </c>
+      <c r="D115" t="s">
+        <v>153</v>
+      </c>
+      <c r="E115" t="s">
+        <v>66</v>
+      </c>
+      <c r="F115" t="s">
+        <v>53</v>
+      </c>
+      <c r="G115" t="s">
+        <v>55</v>
+      </c>
+      <c r="H115" t="s">
+        <v>18</v>
+      </c>
+      <c r="I115" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="15">
+      <c r="A116" t="s">
+        <v>175</v>
+      </c>
+      <c r="B116" t="s">
+        <v>12</v>
+      </c>
+      <c r="C116" t="s">
+        <v>51</v>
+      </c>
+      <c r="D116" t="s">
+        <v>153</v>
+      </c>
+      <c r="E116" t="s">
+        <v>66</v>
+      </c>
+      <c r="F116" t="s">
+        <v>53</v>
+      </c>
+      <c r="G116" t="s">
+        <v>55</v>
+      </c>
+      <c r="H116" t="s">
+        <v>18</v>
+      </c>
+      <c r="I116" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="15">
+      <c r="A117" t="s">
+        <v>175</v>
+      </c>
+      <c r="B117" t="s">
+        <v>40</v>
+      </c>
+      <c r="C117" t="s">
+        <v>51</v>
+      </c>
+      <c r="D117" t="s">
+        <v>153</v>
+      </c>
+      <c r="E117" t="s">
+        <v>66</v>
+      </c>
+      <c r="F117" t="s">
+        <v>53</v>
+      </c>
+      <c r="G117" t="s">
+        <v>55</v>
+      </c>
+      <c r="H117" t="s">
+        <v>18</v>
+      </c>
+      <c r="I117" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="15">
+      <c r="A118" t="s">
+        <v>175</v>
+      </c>
+      <c r="B118" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118" t="s">
+        <v>51</v>
+      </c>
+      <c r="D118" t="s">
+        <v>153</v>
+      </c>
+      <c r="E118" t="s">
+        <v>52</v>
+      </c>
+      <c r="F118" t="s">
+        <v>53</v>
+      </c>
+      <c r="G118" t="s">
+        <v>55</v>
+      </c>
+      <c r="H118" t="s">
+        <v>18</v>
+      </c>
+      <c r="I118" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="15">
+      <c r="A119" t="s">
+        <v>175</v>
+      </c>
+      <c r="B119" t="s">
+        <v>25</v>
+      </c>
+      <c r="C119" t="s">
+        <v>51</v>
+      </c>
+      <c r="D119" t="s">
+        <v>153</v>
+      </c>
+      <c r="E119" t="s">
+        <v>52</v>
+      </c>
+      <c r="F119" t="s">
+        <v>53</v>
+      </c>
+      <c r="G119" t="s">
+        <v>55</v>
+      </c>
+      <c r="H119" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="15">
+      <c r="A120" t="s">
+        <v>175</v>
+      </c>
+      <c r="B120" t="s">
+        <v>50</v>
+      </c>
+      <c r="C120" t="s">
+        <v>67</v>
+      </c>
+      <c r="D120" t="s">
+        <v>191</v>
+      </c>
+      <c r="E120" t="s">
+        <v>69</v>
+      </c>
+      <c r="F120" t="s">
+        <v>70</v>
+      </c>
+      <c r="G120" t="s">
+        <v>55</v>
+      </c>
+      <c r="H120" t="s">
+        <v>18</v>
+      </c>
+      <c r="I120" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="15">
+      <c r="A121" t="s">
+        <v>175</v>
+      </c>
+      <c r="B121" t="s">
+        <v>56</v>
+      </c>
+      <c r="C121" t="s">
+        <v>67</v>
+      </c>
+      <c r="D121" t="s">
+        <v>77</v>
+      </c>
+      <c r="E121" t="s">
+        <v>69</v>
+      </c>
+      <c r="F121" t="s">
+        <v>70</v>
+      </c>
+      <c r="G121" t="s">
+        <v>55</v>
+      </c>
+      <c r="H121" t="s">
+        <v>18</v>
+      </c>
+      <c r="I121" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="15">
+      <c r="A122" t="s">
+        <v>175</v>
+      </c>
+      <c r="B122" t="s">
+        <v>12</v>
+      </c>
+      <c r="C122" t="s">
+        <v>67</v>
+      </c>
+      <c r="D122" t="s">
+        <v>118</v>
+      </c>
+      <c r="E122" t="s">
+        <v>69</v>
+      </c>
+      <c r="F122" t="s">
+        <v>70</v>
+      </c>
+      <c r="G122" t="s">
+        <v>55</v>
+      </c>
+      <c r="H122" t="s">
+        <v>18</v>
+      </c>
+      <c r="I122" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="15">
+      <c r="A123" t="s">
+        <v>175</v>
+      </c>
+      <c r="B123" t="s">
+        <v>40</v>
+      </c>
+      <c r="C123" t="s">
+        <v>67</v>
+      </c>
+      <c r="D123" t="s">
+        <v>192</v>
+      </c>
+      <c r="E123" t="s">
+        <v>69</v>
+      </c>
+      <c r="F123" t="s">
+        <v>70</v>
+      </c>
+      <c r="G123" t="s">
+        <v>55</v>
+      </c>
+      <c r="H123" t="s">
+        <v>18</v>
+      </c>
+      <c r="I123" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="15">
+      <c r="A124" t="s">
+        <v>175</v>
+      </c>
+      <c r="B124" t="s">
+        <v>20</v>
+      </c>
+      <c r="C124" t="s">
+        <v>67</v>
+      </c>
+      <c r="D124" t="s">
+        <v>193</v>
+      </c>
+      <c r="E124" t="s">
+        <v>69</v>
+      </c>
+      <c r="F124" t="s">
+        <v>70</v>
+      </c>
+      <c r="G124" t="s">
+        <v>55</v>
+      </c>
+      <c r="H124" t="s">
+        <v>18</v>
+      </c>
+      <c r="I124" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="15">
+      <c r="A125" t="s">
+        <v>175</v>
+      </c>
+      <c r="B125" t="s">
+        <v>25</v>
+      </c>
+      <c r="C125" t="s">
+        <v>67</v>
+      </c>
+      <c r="D125" t="s">
+        <v>194</v>
+      </c>
+      <c r="E125" t="s">
+        <v>69</v>
+      </c>
+      <c r="F125" t="s">
+        <v>70</v>
+      </c>
+      <c r="G125" t="s">
+        <v>55</v>
+      </c>
+      <c r="H125" t="s">
+        <v>18</v>
+      </c>
+      <c r="I125" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="15">
+      <c r="A126" t="s">
+        <v>175</v>
+      </c>
+      <c r="B126" t="s">
+        <v>30</v>
+      </c>
+      <c r="C126" t="s">
+        <v>67</v>
+      </c>
+      <c r="D126" t="s">
+        <v>71</v>
+      </c>
+      <c r="E126" t="s">
+        <v>69</v>
+      </c>
+      <c r="F126" t="s">
+        <v>70</v>
+      </c>
+      <c r="G126" t="s">
+        <v>55</v>
+      </c>
+      <c r="H126" t="s">
+        <v>18</v>
+      </c>
+      <c r="I126" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="15">
+      <c r="A127" t="s">
+        <v>175</v>
+      </c>
+      <c r="B127" t="s">
+        <v>36</v>
+      </c>
+      <c r="C127" t="s">
+        <v>67</v>
+      </c>
+      <c r="D127" t="s">
+        <v>168</v>
+      </c>
+      <c r="E127" t="s">
+        <v>69</v>
+      </c>
+      <c r="F127" t="s">
+        <v>70</v>
+      </c>
+      <c r="G127" t="s">
+        <v>55</v>
+      </c>
+      <c r="H127" t="s">
+        <v>18</v>
+      </c>
+      <c r="I127" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="15">
+      <c r="A128" t="s">
+        <v>195</v>
+      </c>
+      <c r="B128" t="s">
+        <v>12</v>
+      </c>
+      <c r="C128" t="s">
+        <v>83</v>
+      </c>
+      <c r="D128" t="s">
+        <v>196</v>
+      </c>
+      <c r="E128" t="s">
+        <v>85</v>
+      </c>
+      <c r="F128" t="s">
+        <v>92</v>
+      </c>
+      <c r="G128" t="s">
+        <v>55</v>
+      </c>
+      <c r="H128" t="s">
+        <v>18</v>
+      </c>
+      <c r="I128" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="15">
+      <c r="A129" t="s">
+        <v>195</v>
+      </c>
+      <c r="B129" t="s">
+        <v>12</v>
+      </c>
+      <c r="C129" t="s">
+        <v>83</v>
+      </c>
+      <c r="D129" t="s">
+        <v>197</v>
+      </c>
+      <c r="E129" t="s">
+        <v>85</v>
+      </c>
+      <c r="F129" t="s">
+        <v>92</v>
+      </c>
+      <c r="G129" t="s">
+        <v>55</v>
+      </c>
+      <c r="H129" t="s">
+        <v>18</v>
+      </c>
+      <c r="I129" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="15">
+      <c r="A130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B130" t="s">
+        <v>40</v>
+      </c>
+      <c r="C130" t="s">
+        <v>83</v>
+      </c>
+      <c r="D130" t="s">
+        <v>196</v>
+      </c>
+      <c r="E130" t="s">
+        <v>85</v>
+      </c>
+      <c r="F130" t="s">
+        <v>92</v>
+      </c>
+      <c r="G130" t="s">
+        <v>55</v>
+      </c>
+      <c r="H130" t="s">
+        <v>18</v>
+      </c>
+      <c r="I130" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="15">
+      <c r="A131" t="s">
+        <v>195</v>
+      </c>
+      <c r="B131" t="s">
+        <v>40</v>
+      </c>
+      <c r="C131" t="s">
+        <v>83</v>
+      </c>
+      <c r="D131" t="s">
+        <v>197</v>
+      </c>
+      <c r="E131" t="s">
+        <v>85</v>
+      </c>
+      <c r="F131" t="s">
+        <v>92</v>
+      </c>
+      <c r="G131" t="s">
+        <v>55</v>
+      </c>
+      <c r="H131" t="s">
+        <v>18</v>
+      </c>
+      <c r="I131" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="15">
+      <c r="A132" t="s">
+        <v>195</v>
+      </c>
+      <c r="B132" t="s">
+        <v>20</v>
+      </c>
+      <c r="C132" t="s">
+        <v>83</v>
+      </c>
+      <c r="D132" t="s">
+        <v>196</v>
+      </c>
+      <c r="E132" t="s">
+        <v>85</v>
+      </c>
+      <c r="F132" t="s">
+        <v>92</v>
+      </c>
+      <c r="G132" t="s">
+        <v>55</v>
+      </c>
+      <c r="H132" t="s">
+        <v>18</v>
+      </c>
+      <c r="I132" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="15">
+      <c r="A133" t="s">
+        <v>195</v>
+      </c>
+      <c r="B133" t="s">
+        <v>20</v>
+      </c>
+      <c r="C133" t="s">
+        <v>83</v>
+      </c>
+      <c r="D133" t="s">
+        <v>197</v>
+      </c>
+      <c r="E133" t="s">
+        <v>85</v>
+      </c>
+      <c r="F133" t="s">
+        <v>92</v>
+      </c>
+      <c r="G133" t="s">
+        <v>55</v>
+      </c>
+      <c r="H133" t="s">
+        <v>18</v>
+      </c>
+      <c r="I133" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="15">
+      <c r="A134" t="s">
+        <v>195</v>
+      </c>
+      <c r="B134" t="s">
+        <v>25</v>
+      </c>
+      <c r="C134" t="s">
+        <v>83</v>
+      </c>
+      <c r="D134" t="s">
+        <v>198</v>
+      </c>
+      <c r="E134" t="s">
+        <v>85</v>
+      </c>
+      <c r="F134" t="s">
+        <v>92</v>
+      </c>
+      <c r="G134" t="s">
+        <v>55</v>
+      </c>
+      <c r="H134" t="s">
+        <v>18</v>
+      </c>
+      <c r="I134" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="15">
+      <c r="A135" t="s">
+        <v>195</v>
+      </c>
+      <c r="B135" t="s">
+        <v>30</v>
+      </c>
+      <c r="C135" t="s">
+        <v>83</v>
+      </c>
+      <c r="D135" t="s">
+        <v>198</v>
+      </c>
+      <c r="E135" t="s">
+        <v>85</v>
+      </c>
+      <c r="F135" t="s">
+        <v>92</v>
+      </c>
+      <c r="G135" t="s">
+        <v>55</v>
+      </c>
+      <c r="H135" t="s">
+        <v>18</v>
+      </c>
+      <c r="I135" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="15">
+      <c r="A136" t="s">
+        <v>195</v>
+      </c>
+      <c r="B136" t="s">
+        <v>36</v>
+      </c>
+      <c r="C136" t="s">
+        <v>83</v>
+      </c>
+      <c r="D136" t="s">
+        <v>198</v>
+      </c>
+      <c r="E136" t="s">
+        <v>85</v>
+      </c>
+      <c r="F136" t="s">
+        <v>92</v>
+      </c>
+      <c r="G136" t="s">
+        <v>55</v>
+      </c>
+      <c r="H136" t="s">
+        <v>18</v>
+      </c>
+      <c r="I136" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="15">
+      <c r="A137" t="s">
+        <v>195</v>
+      </c>
+      <c r="B137" t="s">
+        <v>56</v>
+      </c>
+      <c r="C137" t="s">
+        <v>129</v>
+      </c>
+      <c r="D137" t="s">
+        <v>199</v>
+      </c>
+      <c r="E137" t="s">
         <v>131</v>
       </c>
-      <c r="E96" t="s">
-        <v>58</v>
-      </c>
-      <c r="F96" t="s">
-        <v>59</v>
-      </c>
-      <c r="G96" t="s">
+      <c r="F137" t="s">
+        <v>132</v>
+      </c>
+      <c r="G137" t="s">
+        <v>55</v>
+      </c>
+      <c r="H137" t="s">
+        <v>18</v>
+      </c>
+      <c r="I137" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="15">
+      <c r="A138" t="s">
+        <v>195</v>
+      </c>
+      <c r="B138" t="s">
+        <v>56</v>
+      </c>
+      <c r="C138" t="s">
+        <v>129</v>
+      </c>
+      <c r="D138" t="s">
+        <v>200</v>
+      </c>
+      <c r="E138" t="s">
+        <v>131</v>
+      </c>
+      <c r="F138" t="s">
+        <v>132</v>
+      </c>
+      <c r="G138" t="s">
+        <v>55</v>
+      </c>
+      <c r="H138" t="s">
+        <v>18</v>
+      </c>
+      <c r="I138" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="15">
+      <c r="A139" t="s">
+        <v>195</v>
+      </c>
+      <c r="B139" t="s">
+        <v>56</v>
+      </c>
+      <c r="C139" t="s">
+        <v>129</v>
+      </c>
+      <c r="D139" t="s">
+        <v>201</v>
+      </c>
+      <c r="E139" t="s">
+        <v>131</v>
+      </c>
+      <c r="F139" t="s">
+        <v>132</v>
+      </c>
+      <c r="G139" t="s">
+        <v>55</v>
+      </c>
+      <c r="H139" t="s">
+        <v>18</v>
+      </c>
+      <c r="I139" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="15">
+      <c r="A140" t="s">
+        <v>195</v>
+      </c>
+      <c r="B140" t="s">
+        <v>56</v>
+      </c>
+      <c r="C140" t="s">
+        <v>129</v>
+      </c>
+      <c r="D140" t="s">
+        <v>202</v>
+      </c>
+      <c r="E140" t="s">
+        <v>131</v>
+      </c>
+      <c r="F140" t="s">
+        <v>132</v>
+      </c>
+      <c r="G140" t="s">
+        <v>55</v>
+      </c>
+      <c r="H140" t="s">
+        <v>18</v>
+      </c>
+      <c r="I140" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="15">
+      <c r="A141" t="s">
+        <v>195</v>
+      </c>
+      <c r="B141" t="s">
+        <v>56</v>
+      </c>
+      <c r="C141" t="s">
+        <v>129</v>
+      </c>
+      <c r="D141" t="s">
+        <v>203</v>
+      </c>
+      <c r="E141" t="s">
+        <v>131</v>
+      </c>
+      <c r="F141" t="s">
+        <v>132</v>
+      </c>
+      <c r="G141" t="s">
+        <v>55</v>
+      </c>
+      <c r="H141" t="s">
+        <v>18</v>
+      </c>
+      <c r="I141" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="15">
+      <c r="A142" t="s">
+        <v>195</v>
+      </c>
+      <c r="B142" t="s">
+        <v>56</v>
+      </c>
+      <c r="C142" t="s">
+        <v>129</v>
+      </c>
+      <c r="D142" t="s">
+        <v>204</v>
+      </c>
+      <c r="E142" t="s">
+        <v>131</v>
+      </c>
+      <c r="F142" t="s">
+        <v>132</v>
+      </c>
+      <c r="G142" t="s">
+        <v>55</v>
+      </c>
+      <c r="H142" t="s">
+        <v>18</v>
+      </c>
+      <c r="I142" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="15">
+      <c r="A143" t="s">
+        <v>195</v>
+      </c>
+      <c r="B143" t="s">
+        <v>56</v>
+      </c>
+      <c r="C143" t="s">
+        <v>129</v>
+      </c>
+      <c r="D143" t="s">
+        <v>205</v>
+      </c>
+      <c r="E143" t="s">
+        <v>131</v>
+      </c>
+      <c r="F143" t="s">
+        <v>132</v>
+      </c>
+      <c r="G143" t="s">
+        <v>55</v>
+      </c>
+      <c r="H143" t="s">
+        <v>18</v>
+      </c>
+      <c r="I143" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="15">
+      <c r="A144" t="s">
+        <v>195</v>
+      </c>
+      <c r="B144" t="s">
+        <v>56</v>
+      </c>
+      <c r="C144" t="s">
+        <v>129</v>
+      </c>
+      <c r="D144" t="s">
+        <v>206</v>
+      </c>
+      <c r="E144" t="s">
+        <v>131</v>
+      </c>
+      <c r="F144" t="s">
+        <v>132</v>
+      </c>
+      <c r="G144" t="s">
+        <v>55</v>
+      </c>
+      <c r="H144" t="s">
+        <v>18</v>
+      </c>
+      <c r="I144" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="15">
+      <c r="A145" t="s">
+        <v>195</v>
+      </c>
+      <c r="B145" t="s">
+        <v>56</v>
+      </c>
+      <c r="C145" t="s">
+        <v>129</v>
+      </c>
+      <c r="D145" t="s">
+        <v>207</v>
+      </c>
+      <c r="E145" t="s">
+        <v>131</v>
+      </c>
+      <c r="F145" t="s">
+        <v>132</v>
+      </c>
+      <c r="G145" t="s">
+        <v>55</v>
+      </c>
+      <c r="H145" t="s">
+        <v>18</v>
+      </c>
+      <c r="I145" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="15">
+      <c r="A146" t="s">
+        <v>195</v>
+      </c>
+      <c r="B146" t="s">
+        <v>50</v>
+      </c>
+      <c r="C146" t="s">
+        <v>41</v>
+      </c>
+      <c r="D146" t="s">
+        <v>47</v>
+      </c>
+      <c r="E146" t="s">
+        <v>48</v>
+      </c>
+      <c r="F146" t="s">
+        <v>43</v>
+      </c>
+      <c r="G146" t="s">
+        <v>55</v>
+      </c>
+      <c r="H146" t="s">
+        <v>18</v>
+      </c>
+      <c r="I146" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="15">
+      <c r="A147" t="s">
+        <v>195</v>
+      </c>
+      <c r="B147" t="s">
+        <v>56</v>
+      </c>
+      <c r="C147" t="s">
+        <v>41</v>
+      </c>
+      <c r="D147" t="s">
+        <v>186</v>
+      </c>
+      <c r="E147" t="s">
+        <v>48</v>
+      </c>
+      <c r="F147" t="s">
+        <v>43</v>
+      </c>
+      <c r="G147" t="s">
+        <v>55</v>
+      </c>
+      <c r="H147" t="s">
+        <v>18</v>
+      </c>
+      <c r="I147" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="15">
+      <c r="A148" t="s">
+        <v>195</v>
+      </c>
+      <c r="B148" t="s">
+        <v>12</v>
+      </c>
+      <c r="C148" t="s">
+        <v>41</v>
+      </c>
+      <c r="D148" t="s">
+        <v>188</v>
+      </c>
+      <c r="E148" t="s">
+        <v>48</v>
+      </c>
+      <c r="F148" t="s">
+        <v>43</v>
+      </c>
+      <c r="G148" t="s">
+        <v>55</v>
+      </c>
+      <c r="H148" t="s">
+        <v>18</v>
+      </c>
+      <c r="I148" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="15">
+      <c r="A149" t="s">
+        <v>195</v>
+      </c>
+      <c r="B149" t="s">
+        <v>40</v>
+      </c>
+      <c r="C149" t="s">
+        <v>41</v>
+      </c>
+      <c r="D149" t="s">
+        <v>45</v>
+      </c>
+      <c r="E149" t="s">
+        <v>48</v>
+      </c>
+      <c r="F149" t="s">
+        <v>43</v>
+      </c>
+      <c r="G149" t="s">
+        <v>55</v>
+      </c>
+      <c r="H149" t="s">
+        <v>18</v>
+      </c>
+      <c r="I149" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="15">
+      <c r="A150" t="s">
+        <v>195</v>
+      </c>
+      <c r="B150" t="s">
+        <v>20</v>
+      </c>
+      <c r="C150" t="s">
+        <v>41</v>
+      </c>
+      <c r="D150" t="s">
+        <v>208</v>
+      </c>
+      <c r="E150" t="s">
+        <v>48</v>
+      </c>
+      <c r="F150" t="s">
+        <v>43</v>
+      </c>
+      <c r="G150" t="s">
+        <v>55</v>
+      </c>
+      <c r="H150" t="s">
+        <v>18</v>
+      </c>
+      <c r="I150" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="15">
+      <c r="A151" t="s">
+        <v>195</v>
+      </c>
+      <c r="B151" t="s">
+        <v>25</v>
+      </c>
+      <c r="C151" t="s">
+        <v>41</v>
+      </c>
+      <c r="D151" t="s">
+        <v>208</v>
+      </c>
+      <c r="E151" t="s">
+        <v>48</v>
+      </c>
+      <c r="F151" t="s">
+        <v>43</v>
+      </c>
+      <c r="G151" t="s">
+        <v>55</v>
+      </c>
+      <c r="H151" t="s">
+        <v>18</v>
+      </c>
+      <c r="I151" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="15">
+      <c r="A152" t="s">
+        <v>195</v>
+      </c>
+      <c r="B152" t="s">
+        <v>30</v>
+      </c>
+      <c r="C152" t="s">
+        <v>41</v>
+      </c>
+      <c r="D152" t="s">
+        <v>152</v>
+      </c>
+      <c r="E152" t="s">
+        <v>48</v>
+      </c>
+      <c r="F152" t="s">
+        <v>43</v>
+      </c>
+      <c r="G152" t="s">
+        <v>55</v>
+      </c>
+      <c r="H152" t="s">
+        <v>18</v>
+      </c>
+      <c r="I152" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="15">
+      <c r="A153" t="s">
+        <v>195</v>
+      </c>
+      <c r="B153" t="s">
+        <v>36</v>
+      </c>
+      <c r="C153" t="s">
+        <v>41</v>
+      </c>
+      <c r="D153" t="s">
+        <v>125</v>
+      </c>
+      <c r="E153" t="s">
+        <v>48</v>
+      </c>
+      <c r="F153" t="s">
+        <v>43</v>
+      </c>
+      <c r="G153" t="s">
+        <v>55</v>
+      </c>
+      <c r="H153" t="s">
+        <v>18</v>
+      </c>
+      <c r="I153" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="15">
+      <c r="A154" t="s">
+        <v>195</v>
+      </c>
+      <c r="B154" t="s">
+        <v>111</v>
+      </c>
+      <c r="C154" t="s">
+        <v>41</v>
+      </c>
+      <c r="D154" t="s">
+        <v>187</v>
+      </c>
+      <c r="E154" t="s">
+        <v>48</v>
+      </c>
+      <c r="F154" t="s">
+        <v>43</v>
+      </c>
+      <c r="G154" t="s">
+        <v>55</v>
+      </c>
+      <c r="H154" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="15">
+      <c r="A155" t="s">
+        <v>195</v>
+      </c>
+      <c r="B155" t="s">
+        <v>112</v>
+      </c>
+      <c r="C155" t="s">
+        <v>41</v>
+      </c>
+      <c r="D155" t="s">
         <v>42</v>
       </c>
-      <c r="H96" t="s">
-        <v>18</v>
-      </c>
-      <c r="I96" t="s">
-        <v>42</v>
+      <c r="E155" t="s">
+        <v>48</v>
+      </c>
+      <c r="F155" t="s">
+        <v>43</v>
+      </c>
+      <c r="G155" t="s">
+        <v>55</v>
+      </c>
+      <c r="H155" t="s">
+        <v>18</v>
+      </c>
+      <c r="I155" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="15">
+      <c r="A156" t="s">
+        <v>195</v>
+      </c>
+      <c r="B156" t="s">
+        <v>116</v>
+      </c>
+      <c r="C156" t="s">
+        <v>41</v>
+      </c>
+      <c r="D156" t="s">
+        <v>189</v>
+      </c>
+      <c r="E156" t="s">
+        <v>48</v>
+      </c>
+      <c r="F156" t="s">
+        <v>43</v>
+      </c>
+      <c r="G156" t="s">
+        <v>55</v>
+      </c>
+      <c r="H156" t="s">
+        <v>18</v>
+      </c>
+      <c r="I156" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="15">
+      <c r="A157" t="s">
+        <v>195</v>
+      </c>
+      <c r="B157" t="s">
+        <v>184</v>
+      </c>
+      <c r="C157" t="s">
+        <v>41</v>
+      </c>
+      <c r="D157" t="s">
+        <v>190</v>
+      </c>
+      <c r="E157" t="s">
+        <v>48</v>
+      </c>
+      <c r="F157" t="s">
+        <v>43</v>
+      </c>
+      <c r="G157" t="s">
+        <v>55</v>
+      </c>
+      <c r="H157" t="s">
+        <v>18</v>
+      </c>
+      <c r="I157" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="15">
+      <c r="A158" t="s">
+        <v>195</v>
+      </c>
+      <c r="B158" t="s">
+        <v>50</v>
+      </c>
+      <c r="C158" t="s">
+        <v>51</v>
+      </c>
+      <c r="D158" t="s">
+        <v>153</v>
+      </c>
+      <c r="E158" t="s">
+        <v>209</v>
+      </c>
+      <c r="F158" t="s">
+        <v>53</v>
+      </c>
+      <c r="G158" t="s">
+        <v>55</v>
+      </c>
+      <c r="H158" t="s">
+        <v>18</v>
+      </c>
+      <c r="I158" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="15">
+      <c r="A159" t="s">
+        <v>195</v>
+      </c>
+      <c r="B159" t="s">
+        <v>56</v>
+      </c>
+      <c r="C159" t="s">
+        <v>51</v>
+      </c>
+      <c r="D159" t="s">
+        <v>153</v>
+      </c>
+      <c r="E159" t="s">
+        <v>209</v>
+      </c>
+      <c r="F159" t="s">
+        <v>53</v>
+      </c>
+      <c r="G159" t="s">
+        <v>55</v>
+      </c>
+      <c r="H159" t="s">
+        <v>18</v>
+      </c>
+      <c r="I159" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="15">
+      <c r="A160" t="s">
+        <v>195</v>
+      </c>
+      <c r="B160" t="s">
+        <v>12</v>
+      </c>
+      <c r="C160" t="s">
+        <v>67</v>
+      </c>
+      <c r="D160" t="s">
+        <v>80</v>
+      </c>
+      <c r="E160" t="s">
+        <v>69</v>
+      </c>
+      <c r="F160" t="s">
+        <v>70</v>
+      </c>
+      <c r="G160" t="s">
+        <v>55</v>
+      </c>
+      <c r="H160" t="s">
+        <v>18</v>
+      </c>
+      <c r="I160" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="15">
+      <c r="A161" t="s">
+        <v>195</v>
+      </c>
+      <c r="B161" t="s">
+        <v>40</v>
+      </c>
+      <c r="C161" t="s">
+        <v>67</v>
+      </c>
+      <c r="D161" t="s">
+        <v>193</v>
+      </c>
+      <c r="E161" t="s">
+        <v>69</v>
+      </c>
+      <c r="F161" t="s">
+        <v>70</v>
+      </c>
+      <c r="G161" t="s">
+        <v>55</v>
+      </c>
+      <c r="H161" t="s">
+        <v>18</v>
+      </c>
+      <c r="I161" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="15">
+      <c r="A162" t="s">
+        <v>195</v>
+      </c>
+      <c r="B162" t="s">
+        <v>20</v>
+      </c>
+      <c r="C162" t="s">
+        <v>67</v>
+      </c>
+      <c r="D162" t="s">
+        <v>210</v>
+      </c>
+      <c r="E162" t="s">
+        <v>69</v>
+      </c>
+      <c r="F162" t="s">
+        <v>70</v>
+      </c>
+      <c r="G162" t="s">
+        <v>55</v>
+      </c>
+      <c r="H162" t="s">
+        <v>18</v>
+      </c>
+      <c r="I162" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="15">
+      <c r="A163" t="s">
+        <v>195</v>
+      </c>
+      <c r="B163" t="s">
+        <v>25</v>
+      </c>
+      <c r="C163" t="s">
+        <v>67</v>
+      </c>
+      <c r="D163" t="s">
+        <v>211</v>
+      </c>
+      <c r="E163" t="s">
+        <v>69</v>
+      </c>
+      <c r="F163" t="s">
+        <v>70</v>
+      </c>
+      <c r="G163" t="s">
+        <v>55</v>
+      </c>
+      <c r="H163" t="s">
+        <v>18</v>
+      </c>
+      <c r="I163" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="15">
+      <c r="A164" t="s">
+        <v>195</v>
+      </c>
+      <c r="B164" t="s">
+        <v>36</v>
+      </c>
+      <c r="C164" t="s">
+        <v>67</v>
+      </c>
+      <c r="D164" t="s">
+        <v>212</v>
+      </c>
+      <c r="E164" t="s">
+        <v>69</v>
+      </c>
+      <c r="F164" t="s">
+        <v>70</v>
+      </c>
+      <c r="G164" t="s">
+        <v>55</v>
+      </c>
+      <c r="H164" t="s">
+        <v>18</v>
+      </c>
+      <c r="I164" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="15">
+      <c r="A165" t="s">
+        <v>195</v>
+      </c>
+      <c r="B165" t="s">
+        <v>111</v>
+      </c>
+      <c r="C165" t="s">
+        <v>67</v>
+      </c>
+      <c r="D165" t="s">
+        <v>213</v>
+      </c>
+      <c r="E165" t="s">
+        <v>69</v>
+      </c>
+      <c r="F165" t="s">
+        <v>70</v>
+      </c>
+      <c r="G165" t="s">
+        <v>55</v>
+      </c>
+      <c r="H165" t="s">
+        <v>18</v>
+      </c>
+      <c r="I165" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="15">
+      <c r="A166" t="s">
+        <v>195</v>
+      </c>
+      <c r="B166" t="s">
+        <v>112</v>
+      </c>
+      <c r="C166" t="s">
+        <v>67</v>
+      </c>
+      <c r="D166" t="s">
+        <v>214</v>
+      </c>
+      <c r="E166" t="s">
+        <v>69</v>
+      </c>
+      <c r="F166" t="s">
+        <v>70</v>
+      </c>
+      <c r="G166" t="s">
+        <v>55</v>
+      </c>
+      <c r="H166" t="s">
+        <v>18</v>
+      </c>
+      <c r="I166" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="15">
+      <c r="A167" t="s">
+        <v>195</v>
+      </c>
+      <c r="B167" t="s">
+        <v>36</v>
+      </c>
+      <c r="C167" t="s">
+        <v>169</v>
+      </c>
+      <c r="D167" t="s">
+        <v>170</v>
+      </c>
+      <c r="E167" t="s">
+        <v>74</v>
+      </c>
+      <c r="F167" t="s">
+        <v>75</v>
+      </c>
+      <c r="G167" t="s">
+        <v>76</v>
+      </c>
+      <c r="H167" t="s">
+        <v>18</v>
+      </c>
+      <c r="I167" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="15">
+      <c r="A168" t="s">
+        <v>195</v>
+      </c>
+      <c r="B168" t="s">
+        <v>30</v>
+      </c>
+      <c r="C168" t="s">
+        <v>215</v>
+      </c>
+      <c r="D168" t="s">
+        <v>190</v>
+      </c>
+      <c r="E168" t="s">
+        <v>216</v>
+      </c>
+      <c r="F168" t="s">
+        <v>107</v>
+      </c>
+      <c r="G168" t="s">
+        <v>217</v>
+      </c>
+      <c r="H168" t="s">
+        <v>18</v>
+      </c>
+      <c r="I168" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="15">
+      <c r="A169" t="s">
+        <v>195</v>
+      </c>
+      <c r="B169" t="s">
+        <v>36</v>
+      </c>
+      <c r="C169" t="s">
+        <v>215</v>
+      </c>
+      <c r="D169" t="s">
+        <v>190</v>
+      </c>
+      <c r="E169" t="s">
+        <v>216</v>
+      </c>
+      <c r="F169" t="s">
+        <v>107</v>
+      </c>
+      <c r="G169" t="s">
+        <v>217</v>
+      </c>
+      <c r="H169" t="s">
+        <v>18</v>
+      </c>
+      <c r="I169" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3753,13 +6149,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4f06a7a6-1527-414e-97f6-03851b64f663}">
-  <dimension ref="A1:F20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{cc790074-4ec6-4626-b2b8-d07d99f624de}">
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
@@ -3770,13 +6166,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>132</v>
+        <v>218</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -3790,16 +6186,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="E2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -3810,16 +6206,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>223</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="E3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -3830,16 +6226,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>225</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -3850,16 +6246,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>227</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="E5" t="s">
-        <v>144</v>
+        <v>228</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -3867,19 +6263,19 @@
     </row>
     <row r="6" spans="1:6" ht="15">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>223</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>229</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>230</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -3887,19 +6283,19 @@
     </row>
     <row r="7" spans="1:6" ht="15">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>146</v>
+        <v>231</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>229</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -3907,19 +6303,19 @@
     </row>
     <row r="8" spans="1:6" ht="15">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>232</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -3927,19 +6323,19 @@
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>231</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>233</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>234</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -3947,19 +6343,19 @@
     </row>
     <row r="10" spans="1:6" ht="15">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>146</v>
+        <v>235</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>236</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -3967,19 +6363,19 @@
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>143</v>
+        <v>237</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>238</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -3987,19 +6383,19 @@
     </row>
     <row r="12" spans="1:6" ht="15">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
+        <v>223</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>238</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -4007,19 +6403,19 @@
     </row>
     <row r="13" spans="1:6" ht="15">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>149</v>
+        <v>221</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -4027,19 +6423,19 @@
     </row>
     <row r="14" spans="1:6" ht="15">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>141</v>
+        <v>239</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -4047,19 +6443,19 @@
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="A15" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B15" t="s">
-        <v>143</v>
+        <v>235</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -4067,19 +6463,19 @@
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B16" t="s">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="D16" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -4087,19 +6483,19 @@
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>223</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>233</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -4107,19 +6503,19 @@
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>231</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="D18" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -4127,19 +6523,19 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B19" t="s">
-        <v>150</v>
+        <v>227</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -4147,21 +6543,381 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>235</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15">
+      <c r="A21" t="s">
+        <v>175</v>
+      </c>
+      <c r="B21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" t="s">
+        <v>233</v>
+      </c>
+      <c r="E21" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15">
+      <c r="A22" t="s">
+        <v>175</v>
+      </c>
+      <c r="B22" t="s">
+        <v>241</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" t="s">
+        <v>242</v>
+      </c>
+      <c r="E22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15">
+      <c r="A23" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" t="s">
+        <v>243</v>
+      </c>
+      <c r="C23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" t="s">
+        <v>242</v>
+      </c>
+      <c r="E23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15">
+      <c r="A24" t="s">
+        <v>175</v>
+      </c>
+      <c r="B24" t="s">
+        <v>240</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" t="s">
+        <v>224</v>
+      </c>
+      <c r="E24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15">
+      <c r="A25" t="s">
+        <v>175</v>
+      </c>
+      <c r="B25" t="s">
+        <v>232</v>
+      </c>
+      <c r="C25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" t="s">
+        <v>224</v>
+      </c>
+      <c r="E25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15">
+      <c r="A26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" t="s">
+        <v>225</v>
+      </c>
+      <c r="C26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15">
+      <c r="A27" t="s">
+        <v>175</v>
+      </c>
+      <c r="B27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" t="s">
+        <v>224</v>
+      </c>
+      <c r="E27" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15">
+      <c r="A28" t="s">
+        <v>175</v>
+      </c>
+      <c r="B28" t="s">
+        <v>244</v>
+      </c>
+      <c r="C28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" t="s">
+        <v>224</v>
+      </c>
+      <c r="E28" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15">
+      <c r="A29" t="s">
+        <v>195</v>
+      </c>
+      <c r="B29" t="s">
+        <v>231</v>
+      </c>
+      <c r="C29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" t="s">
+        <v>229</v>
+      </c>
+      <c r="E29" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15">
+      <c r="A30" t="s">
+        <v>195</v>
+      </c>
+      <c r="B30" t="s">
+        <v>240</v>
+      </c>
+      <c r="C30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" t="s">
+        <v>242</v>
+      </c>
+      <c r="E30" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15">
+      <c r="A31" t="s">
+        <v>195</v>
+      </c>
+      <c r="B31" t="s">
+        <v>223</v>
+      </c>
+      <c r="C31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" t="s">
+        <v>222</v>
+      </c>
+      <c r="E31" t="s">
+        <v>55</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15">
+      <c r="A32" t="s">
+        <v>195</v>
+      </c>
+      <c r="B32" t="s">
+        <v>235</v>
+      </c>
+      <c r="C32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E32" t="s">
+        <v>55</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15">
+      <c r="A33" t="s">
+        <v>195</v>
+      </c>
+      <c r="B33" t="s">
+        <v>237</v>
+      </c>
+      <c r="C33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" t="s">
+        <v>242</v>
+      </c>
+      <c r="E33" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15">
+      <c r="A34" t="s">
+        <v>195</v>
+      </c>
+      <c r="B34" t="s">
+        <v>241</v>
+      </c>
+      <c r="C34" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" t="s">
+        <v>242</v>
+      </c>
+      <c r="E34" t="s">
+        <v>55</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15">
+      <c r="A35" t="s">
+        <v>195</v>
+      </c>
+      <c r="B35" t="s">
+        <v>243</v>
+      </c>
+      <c r="C35" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" t="s">
+        <v>242</v>
+      </c>
+      <c r="E35" t="s">
+        <v>55</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15">
+      <c r="A36" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" t="s">
+        <v>232</v>
+      </c>
+      <c r="C36" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E36" t="s">
+        <v>55</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15">
+      <c r="A37" t="s">
+        <v>195</v>
+      </c>
+      <c r="B37" t="s">
+        <v>244</v>
+      </c>
+      <c r="C37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" t="s">
+        <v>224</v>
+      </c>
+      <c r="E37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15">
+      <c r="A38" t="s">
+        <v>195</v>
+      </c>
+      <c r="B38" t="s">
+        <v>237</v>
+      </c>
+      <c r="C38" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" t="s">
+        <v>224</v>
+      </c>
+      <c r="E38" t="s">
+        <v>55</v>
+      </c>
+      <c r="F38" t="s">
         <v>18</v>
       </c>
     </row>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -9,18 +9,20 @@
   <sheets>
     <sheet name="Opis parametrów" sheetId="2" r:id="rId2"/>
     <sheet name="Oddziały" sheetId="3" r:id="rId3"/>
-    <sheet name="Dyżury" sheetId="4" r:id="rId4"/>
+    <sheet name="Dzienniki zajeć innych" sheetId="4" r:id="rId4"/>
+    <sheet name="Dyżury" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Oddziały!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Dyżury!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dzienniki zajeć innych'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dyżury!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="266">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -58,6 +60,48 @@
     <t>23.02.2026</t>
   </si>
   <si>
+    <t>1, 08:00-08:45</t>
+  </si>
+  <si>
+    <t>Stępień Krystyna</t>
+  </si>
+  <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>Technika w produkcji cukierniczej</t>
+  </si>
+  <si>
+    <t>prs</t>
+  </si>
+  <si>
+    <t>Uczniowie przychodzą później</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Taszycka Magdalena</t>
+  </si>
+  <si>
+    <t>1FB|JA1</t>
+  </si>
+  <si>
+    <t>Informatyka</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>2, 08:50-09:35</t>
+  </si>
+  <si>
+    <t>1TFB|JA1</t>
+  </si>
+  <si>
     <t>3, 09:40-10:25</t>
   </si>
   <si>
@@ -76,12 +120,72 @@
     <t>Sobczak Anna</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Dodatkowo płatne</t>
   </si>
   <si>
+    <t>1CA|JA1</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
+    <t>1CA|JA2</t>
+  </si>
+  <si>
+    <t>Bezpłatne</t>
+  </si>
+  <si>
+    <t>2TFB|JA2</t>
+  </si>
+  <si>
+    <t>4, 10:35-11:20</t>
+  </si>
+  <si>
+    <t>Smirnow-Zechman Eleonora</t>
+  </si>
+  <si>
+    <t>1CA</t>
+  </si>
+  <si>
+    <t>Zajęcia z wychowawcą</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Rejno Julita</t>
+  </si>
+  <si>
+    <t>3CA</t>
+  </si>
+  <si>
+    <t>Biologia</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Małecka Barbara</t>
+  </si>
+  <si>
+    <t>3TFA|JA2</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
     <t>5, 11:25-12:10</t>
   </si>
   <si>
@@ -91,27 +195,51 @@
     <t>Język polski</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>Ulanowska Magdalena</t>
   </si>
   <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Kończyńska Małgorzata</t>
+  </si>
+  <si>
+    <t>1TFB|JA2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Cieśla Marcin</t>
+  </si>
+  <si>
     <t>6, 12:25-13:10</t>
   </si>
   <si>
-    <t>2CB</t>
-  </si>
-  <si>
-    <t>Zajęcia z wychowawcą</t>
-  </si>
-  <si>
     <t>42</t>
   </si>
   <si>
     <t>Socha Dariusz</t>
   </si>
   <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>Biznes i zarządzanie</t>
+  </si>
+  <si>
+    <t>Najwer Maciej</t>
+  </si>
+  <si>
+    <t>Technologie produkcji cukierniczej</t>
+  </si>
+  <si>
     <t>7, 13:15-14:00</t>
   </si>
   <si>
@@ -127,7 +255,7 @@
     <t>Nowak Damiana</t>
   </si>
   <si>
-    <t>Bezpłatne</t>
+    <t>1TH|JA2</t>
   </si>
   <si>
     <t>8, 14:05-14:50</t>
@@ -136,141 +264,39 @@
     <t>3S</t>
   </si>
   <si>
-    <t>Biologia</t>
-  </si>
-  <si>
     <t>Sałdyka Karolina</t>
   </si>
   <si>
-    <t>4, 10:35-11:20</t>
-  </si>
-  <si>
-    <t>Smirnow-Zechman Eleonora</t>
-  </si>
-  <si>
-    <t>1CA</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Rejno Julita</t>
-  </si>
-  <si>
-    <t>1FB</t>
-  </si>
-  <si>
-    <t>Danielewski Paweł</t>
-  </si>
-  <si>
-    <t>2TFA</t>
-  </si>
-  <si>
-    <t>Biznes i zarządzanie</t>
-  </si>
-  <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
-    <t>1, 08:00-08:45</t>
-  </si>
-  <si>
-    <t>Stępień Krystyna</t>
-  </si>
-  <si>
-    <t>Technika w produkcji cukierniczej</t>
-  </si>
-  <si>
-    <t>prs</t>
-  </si>
-  <si>
-    <t>Uczniowie przychodzą później</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>2, 08:50-09:35</t>
-  </si>
-  <si>
-    <t>1CA|JA1</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Karczmarz Aleksandra</t>
-  </si>
-  <si>
-    <t>1CA|JA2</t>
-  </si>
-  <si>
-    <t>3CA</t>
-  </si>
-  <si>
-    <t>Małecka Barbara</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Kończyńska Małgorzata</t>
-  </si>
-  <si>
-    <t>Technologie produkcji cukierniczej</t>
-  </si>
-  <si>
-    <t>Taszycka Magdalena</t>
-  </si>
-  <si>
-    <t>1FB|JA1</t>
-  </si>
-  <si>
-    <t>Informatyka</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>1TFB|JA1</t>
-  </si>
-  <si>
-    <t>2TFB|JA2</t>
-  </si>
-  <si>
-    <t>3TFA|JA2</t>
-  </si>
-  <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Fiodorów Małgorzata</t>
-  </si>
-  <si>
-    <t>1TFB|JA2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Cieśla Marcin</t>
-  </si>
-  <si>
-    <t>1TH|JA2</t>
-  </si>
-  <si>
     <t>Uczniowie zwolnieni do domu</t>
   </si>
   <si>
     <t>24.02.2026</t>
   </si>
   <si>
+    <t>Wakat3 edukacja zdrow.</t>
+  </si>
+  <si>
+    <t>3CA|edu</t>
+  </si>
+  <si>
+    <t>Edukacja zdrowotna</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Mocarski Arkadiusz</t>
+  </si>
+  <si>
+    <t>3FA|edu</t>
+  </si>
+  <si>
+    <t>3M|edu</t>
+  </si>
+  <si>
+    <t>3TFA|edu</t>
+  </si>
+  <si>
     <t>Antoszewska Joanna</t>
   </si>
   <si>
@@ -286,6 +312,45 @@
     <t>Nestoruk Lidia</t>
   </si>
   <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>Zastępstwo</t>
+  </si>
+  <si>
+    <t>p. Rejno, zajęcia z wychowawcą za środę 25.02</t>
+  </si>
+  <si>
+    <t>Bokuniewicz Sylwia</t>
+  </si>
+  <si>
+    <t>Świerzewicz Katarzyna</t>
+  </si>
+  <si>
+    <t>Technologia gastronomiczna z towaroznawstwem</t>
+  </si>
+  <si>
+    <t>3TH|JA1</t>
+  </si>
+  <si>
+    <t>3TH|JA2</t>
+  </si>
+  <si>
+    <t>3M|JN2</t>
+  </si>
+  <si>
+    <t>sg1</t>
+  </si>
+  <si>
+    <t>Wójcik Kamil</t>
+  </si>
+  <si>
+    <t>4TFB</t>
+  </si>
+  <si>
+    <t>Kosin Anna</t>
+  </si>
+  <si>
     <t>2WA</t>
   </si>
   <si>
@@ -295,6 +360,24 @@
     <t>Pietrycha Małgorzata</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Okienko dla uczniów</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>Język niemiecki zawodowy</t>
+  </si>
+  <si>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>Jastrzębska-Majtyka Agnieszka</t>
+  </si>
+  <si>
     <t>3FB|DZ</t>
   </si>
   <si>
@@ -304,42 +387,12 @@
     <t>Dalach Sławomir</t>
   </si>
   <si>
-    <t>3M|JN2</t>
-  </si>
-  <si>
-    <t>sg1</t>
-  </si>
-  <si>
-    <t>Wójcik Kamil</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Okienko dla uczniów</t>
-  </si>
-  <si>
     <t>3S|DZ</t>
   </si>
   <si>
     <t>aq1</t>
   </si>
   <si>
-    <t>Filipek Anna</t>
-  </si>
-  <si>
-    <t>Zastępstwo</t>
-  </si>
-  <si>
-    <t>p. Rejno, zajęcia z wychowawcą za środę 25.02</t>
-  </si>
-  <si>
-    <t>3M</t>
-  </si>
-  <si>
-    <t>Język niemiecki zawodowy</t>
-  </si>
-  <si>
     <t>Historia</t>
   </si>
   <si>
@@ -349,15 +402,57 @@
     <t>Kopij Marcin</t>
   </si>
   <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
+    <t>1TFB</t>
+  </si>
+  <si>
+    <t>Chemia</t>
+  </si>
+  <si>
     <t>4B</t>
   </si>
   <si>
+    <t>1TH</t>
+  </si>
+  <si>
+    <t>Towar jako przedmiot handlu</t>
+  </si>
+  <si>
     <t>9, 14:55-15:40</t>
   </si>
   <si>
+    <t>Paleczny Maciej</t>
+  </si>
+  <si>
+    <t>3TFB|relu</t>
+  </si>
+  <si>
+    <t>Religia</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>3FB|relu</t>
+  </si>
+  <si>
+    <t>3CA|relu</t>
+  </si>
+  <si>
+    <t>3FA|relu</t>
+  </si>
+  <si>
+    <t>3TFA|relu</t>
+  </si>
+  <si>
+    <t>4TFB|relu</t>
+  </si>
+  <si>
     <t>10, 15:45-16:30</t>
   </si>
   <si>
@@ -373,118 +468,100 @@
     <t>11, 16:35-17:20</t>
   </si>
   <si>
-    <t>Bokuniewicz Sylwia</t>
-  </si>
-  <si>
-    <t>3TH|JA1</t>
-  </si>
-  <si>
-    <t>3TH|JA2</t>
-  </si>
-  <si>
-    <t>4TFB</t>
-  </si>
-  <si>
-    <t>Kosin Anna</t>
-  </si>
-  <si>
-    <t>4TH</t>
-  </si>
-  <si>
-    <t>Jastrzębska-Majtyka Agnieszka</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
-  </si>
-  <si>
-    <t>1TFB</t>
-  </si>
-  <si>
-    <t>Chemia</t>
-  </si>
-  <si>
-    <t>1TH</t>
-  </si>
-  <si>
-    <t>Towar jako przedmiot handlu</t>
-  </si>
-  <si>
-    <t>Paleczny Maciej</t>
-  </si>
-  <si>
-    <t>3TFB|relu</t>
-  </si>
-  <si>
-    <t>Religia</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>3FB|relu</t>
-  </si>
-  <si>
-    <t>3CA|relu</t>
-  </si>
-  <si>
-    <t>3FA|relu</t>
-  </si>
-  <si>
-    <t>3TFA|relu</t>
-  </si>
-  <si>
-    <t>4TFB|relu</t>
-  </si>
-  <si>
-    <t>Świerzewicz Katarzyna</t>
-  </si>
-  <si>
-    <t>Technologia gastronomiczna z towaroznawstwem</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>Mocarski Arkadiusz</t>
-  </si>
-  <si>
-    <t>Wakat3 edukacja zdrow.</t>
-  </si>
-  <si>
-    <t>3CA|edu</t>
-  </si>
-  <si>
-    <t>Edukacja zdrowotna</t>
-  </si>
-  <si>
-    <t>3FA|edu</t>
-  </si>
-  <si>
-    <t>3M|edu</t>
-  </si>
-  <si>
-    <t>3TFA|edu</t>
-  </si>
-  <si>
     <t>25.02.2026</t>
   </si>
   <si>
+    <t>Skarupa Agnieszka</t>
+  </si>
+  <si>
+    <t>Symulacyjna firma handlowa</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>2FC|edu</t>
+  </si>
+  <si>
+    <t>2WA|edu</t>
+  </si>
+  <si>
+    <t>2S|edu</t>
+  </si>
+  <si>
+    <t>2CA|edu</t>
+  </si>
+  <si>
     <t>2CA|DZ</t>
   </si>
   <si>
+    <t>2FA</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Biezmienow Małgorzata</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>Podstawy fryzjerstwa</t>
+  </si>
+  <si>
+    <t>Leńczowska Iwona</t>
+  </si>
+  <si>
+    <t>2FC</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>Pracownia sprzedaży</t>
+  </si>
+  <si>
+    <t>1FA|JA2</t>
+  </si>
+  <si>
     <t>2WA|CH</t>
   </si>
   <si>
-    <t>2FB</t>
-  </si>
-  <si>
-    <t>1TFA</t>
+    <t>2TFB</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>Wakat1 j. niemiecki</t>
+  </si>
+  <si>
+    <t>1WA|JN2</t>
+  </si>
+  <si>
+    <t>Krzemińska Beata</t>
   </si>
   <si>
     <t>2CA</t>
   </si>
   <si>
-    <t>2FA</t>
+    <t>Edukacja obywatelska</t>
+  </si>
+  <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>1TH|JA1</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>1WA</t>
   </si>
   <si>
     <t>2TH|relu</t>
@@ -499,54 +576,9 @@
     <t>2CA|relu</t>
   </si>
   <si>
-    <t>Skarupa Agnieszka</t>
-  </si>
-  <si>
-    <t>Symulacyjna firma handlowa</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>Pracownia sprzedaży</t>
-  </si>
-  <si>
-    <t>2TH</t>
-  </si>
-  <si>
-    <t>1FA</t>
-  </si>
-  <si>
-    <t>1WA</t>
-  </si>
-  <si>
     <t>29</t>
   </si>
   <si>
-    <t>1FA|JA2</t>
-  </si>
-  <si>
-    <t>1TH|JA1</t>
-  </si>
-  <si>
-    <t>Wakat1 j. niemiecki</t>
-  </si>
-  <si>
-    <t>1WA|JN2</t>
-  </si>
-  <si>
-    <t>2FC|edu</t>
-  </si>
-  <si>
-    <t>2WA|edu</t>
-  </si>
-  <si>
-    <t>2S|edu</t>
-  </si>
-  <si>
-    <t>2CA|edu</t>
-  </si>
-  <si>
     <t>26.02.2026</t>
   </si>
   <si>
@@ -556,108 +588,123 @@
     <t>8</t>
   </si>
   <si>
+    <t>2TFA|JA2</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
     <t>4TFB|dz2</t>
   </si>
   <si>
+    <t>1CB|JA1</t>
+  </si>
+  <si>
+    <t>1TFA|JA2</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Misiąg Anna</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>1WB|JN1</t>
+  </si>
+  <si>
     <t>Nowaczyk Agnieszka</t>
   </si>
   <si>
     <t>3TH</t>
   </si>
   <si>
+    <t>1CB</t>
+  </si>
+  <si>
+    <t>1FC</t>
+  </si>
+  <si>
+    <t>3FB</t>
+  </si>
+  <si>
     <t>Język angielski zawodowy</t>
   </si>
   <si>
     <t>04</t>
   </si>
   <si>
-    <t>3FB</t>
-  </si>
-  <si>
     <t>12, 17:25-18:10</t>
   </si>
   <si>
+    <t>1S</t>
+  </si>
+  <si>
     <t>13, 18:15-19:00</t>
   </si>
   <si>
-    <t>2TFB</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>1CB</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
-    <t>1S</t>
-  </si>
-  <si>
-    <t>2TFA|JA2</t>
-  </si>
-  <si>
-    <t>1CB|JA1</t>
-  </si>
-  <si>
-    <t>1TFA|JA2</t>
-  </si>
-  <si>
-    <t>1WB|JN1</t>
-  </si>
-  <si>
     <t>27.02.2026</t>
   </si>
   <si>
+    <t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</t>
+  </si>
+  <si>
+    <t>1WB|relu</t>
+  </si>
+  <si>
+    <t>1TFA|relu</t>
+  </si>
+  <si>
+    <t>1TFB|relu</t>
+  </si>
+  <si>
+    <t>1S|relu</t>
+  </si>
+  <si>
+    <t>1CB|relu</t>
+  </si>
+  <si>
+    <t>1TH|relu</t>
+  </si>
+  <si>
+    <t>1WA|relu</t>
+  </si>
+  <si>
+    <t>1CA|relu</t>
+  </si>
+  <si>
+    <t>1FA|relu</t>
+  </si>
+  <si>
     <t>2TH|DZ</t>
   </si>
   <si>
     <t>2TFB|DZ</t>
   </si>
   <si>
+    <t>1WB</t>
+  </si>
+  <si>
+    <t>1FB|JA2</t>
+  </si>
+  <si>
     <t>1CB|JA2</t>
   </si>
   <si>
-    <t>1WB|relu</t>
-  </si>
-  <si>
-    <t>1TFA|relu</t>
-  </si>
-  <si>
-    <t>1TFB|relu</t>
-  </si>
-  <si>
-    <t>1S|relu</t>
-  </si>
-  <si>
-    <t>1CB|relu</t>
-  </si>
-  <si>
-    <t>1TH|relu</t>
-  </si>
-  <si>
-    <t>1WA|relu</t>
-  </si>
-  <si>
-    <t>1CA|relu</t>
-  </si>
-  <si>
-    <t>1FA|relu</t>
-  </si>
-  <si>
-    <t>1WB</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</t>
-  </si>
-  <si>
-    <t>1FB|JA2</t>
-  </si>
-  <si>
     <t>1WA|JN1</t>
   </si>
   <si>
+    <t>Wakat2 matematyka</t>
+  </si>
+  <si>
+    <t>Matematyka</t>
+  </si>
+  <si>
+    <t>Młynarczyk Paweł</t>
+  </si>
+  <si>
     <t>1K|JA1</t>
   </si>
   <si>
@@ -667,42 +714,54 @@
     <t>1S|JA1</t>
   </si>
   <si>
-    <t>Wakat2 matematyka</t>
-  </si>
-  <si>
-    <t>Matematyka</t>
-  </si>
-  <si>
-    <t>Młynarczyk Paweł</t>
-  </si>
-  <si>
     <t>Godzina</t>
   </si>
   <si>
     <t>Nauczyciel</t>
   </si>
   <si>
+    <t>Dziennik zajęć innych</t>
+  </si>
+  <si>
+    <t>Opis zajęć</t>
+  </si>
+  <si>
+    <t>08:50-09:35</t>
+  </si>
+  <si>
+    <t>Katarzyna Majewska -  2S - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>08:50-10:25</t>
+  </si>
+  <si>
+    <t>Krystian Pietrowski - 3M - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>09:40-10:25</t>
+  </si>
+  <si>
+    <t>16:35-17:20</t>
+  </si>
+  <si>
     <t>Miejsce dyżuru</t>
   </si>
   <si>
+    <t>08:45-08:50</t>
+  </si>
+  <si>
+    <t>piętro_3</t>
+  </si>
+  <si>
     <t>10:25-10:35</t>
   </si>
   <si>
     <t>piętro_1</t>
   </si>
   <si>
-    <t>08:45-08:50</t>
-  </si>
-  <si>
-    <t>piętro_3</t>
-  </si>
-  <si>
     <t>11:20-11:25</t>
   </si>
   <si>
-    <t>Misiąg Anna</t>
-  </si>
-  <si>
     <t>13:10-13:15</t>
   </si>
   <si>
@@ -715,16 +774,19 @@
     <t>Jaworska Edyta</t>
   </si>
   <si>
+    <t>Ostrowska Ewa</t>
+  </si>
+  <si>
+    <t>09:35-09:40</t>
+  </si>
+  <si>
+    <t>piętro_2</t>
+  </si>
+  <si>
     <t>12:10-12:25</t>
   </si>
   <si>
-    <t>09:35-09:40</t>
-  </si>
-  <si>
-    <t>piętro_2</t>
-  </si>
-  <si>
-    <t>Wojciechowski Łukasz</t>
+    <t>14:00-14:05</t>
   </si>
   <si>
     <t>15:40-15:45</t>
@@ -736,15 +798,21 @@
     <t>16:30-16:35</t>
   </si>
   <si>
-    <t>Ostrowska Ewa</t>
-  </si>
-  <si>
-    <t>14:00-14:05</t>
-  </si>
-  <si>
     <t>07:55-08:00</t>
   </si>
   <si>
+    <t>Piątek-Pawłowska Bożena</t>
+  </si>
+  <si>
+    <t>Smereka Alicja</t>
+  </si>
+  <si>
+    <t>Nowak Magdalena</t>
+  </si>
+  <si>
+    <t>14:50-14:55</t>
+  </si>
+  <si>
     <t>17:20-17:25</t>
   </si>
   <si>
@@ -752,9 +820,6 @@
   </si>
   <si>
     <t>18:10-18:15</t>
-  </si>
-  <si>
-    <t>14:50-14:55</t>
   </si>
 </sst>
 </file>
@@ -1204,7 +1269,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{fe0b43fd-a9d3-4aac-a631-28790cdf6209}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{05bea1ee-a578-4d1f-b14a-ba8b2968c3e2}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1225,8 +1290,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{89ca7c21-d943-4075-a13a-e0d742228799}">
-  <dimension ref="A1:I169"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5b5c1647-7cd6-4a55-9464-b63be66d8daa}">
+  <dimension ref="A1:I186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1303,10 +1368,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
@@ -1318,7 +1383,7 @@
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
@@ -1332,22 +1397,22 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
@@ -1361,28 +1426,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -1390,28 +1455,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -1419,28 +1484,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -1448,28 +1513,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
@@ -1477,22 +1542,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
@@ -1506,28 +1571,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
@@ -1535,28 +1600,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1564,28 +1629,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
         <v>51</v>
       </c>
-      <c r="D12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" t="s">
-        <v>58</v>
-      </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
@@ -1593,28 +1658,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
@@ -1622,28 +1687,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H14" t="s">
         <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1651,28 +1716,28 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
@@ -1680,28 +1745,28 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
         <v>62</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" t="s">
         <v>64</v>
       </c>
-      <c r="G16" t="s">
-        <v>65</v>
-      </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -1709,28 +1774,28 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" t="s">
         <v>67</v>
       </c>
-      <c r="D17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" t="s">
-        <v>54</v>
-      </c>
       <c r="H17" t="s">
         <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -1738,28 +1803,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>69</v>
       </c>
       <c r="F18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" t="s">
         <v>70</v>
       </c>
-      <c r="G18" t="s">
-        <v>54</v>
-      </c>
       <c r="H18" t="s">
         <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1767,28 +1832,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F19" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G19" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -1796,10 +1861,10 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
         <v>73</v>
@@ -1817,7 +1882,7 @@
         <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -1825,28 +1890,28 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
         <v>20</v>
-      </c>
-      <c r="C21" t="s">
-        <v>67</v>
       </c>
       <c r="D21" t="s">
         <v>77</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="H21" t="s">
         <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
@@ -1854,28 +1919,28 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" t="s">
         <v>80</v>
       </c>
-      <c r="E22" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" t="s">
-        <v>29</v>
-      </c>
       <c r="H22" t="s">
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
@@ -1883,19 +1948,19 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E23" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="G23" t="s">
         <v>81</v>
@@ -1904,7 +1969,7 @@
         <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
@@ -1912,7 +1977,7 @@
         <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
         <v>83</v>
@@ -1933,7 +1998,7 @@
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -1947,7 +2012,7 @@
         <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
         <v>85</v>
@@ -1962,7 +2027,7 @@
         <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -1970,13 +2035,13 @@
         <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
         <v>83</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
         <v>85</v>
@@ -1991,7 +2056,7 @@
         <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
@@ -1999,28 +2064,28 @@
         <v>82</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
         <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="F27" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G27" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -2028,28 +2093,28 @@
         <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E28" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
@@ -2057,25 +2122,25 @@
         <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="E29" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="G29" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H29" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="I29" t="s">
         <v>19</v>
@@ -2086,28 +2151,28 @@
         <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="E30" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="F30" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G30" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
@@ -2115,28 +2180,28 @@
         <v>82</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="E31" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="F31" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G31" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
@@ -2144,28 +2209,28 @@
         <v>82</v>
       </c>
       <c r="B32" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="F32" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G32" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
@@ -2173,28 +2238,28 @@
         <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" t="s">
         <v>79</v>
       </c>
-      <c r="D33" t="s">
-        <v>99</v>
-      </c>
       <c r="E33" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F33" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G33" t="s">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
@@ -2202,28 +2267,28 @@
         <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E34" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="F34" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="G34" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
@@ -2231,28 +2296,28 @@
         <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="E35" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="F35" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G35" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="H35" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
@@ -2260,28 +2325,28 @@
         <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="E36" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="F36" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G36" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
@@ -2289,28 +2354,28 @@
         <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="D37" t="s">
         <v>104</v>
       </c>
       <c r="E37" t="s">
+        <v>93</v>
+      </c>
+      <c r="F37" t="s">
         <v>105</v>
       </c>
-      <c r="F37" t="s">
-        <v>64</v>
-      </c>
       <c r="G37" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
@@ -2318,19 +2383,19 @@
         <v>82</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E38" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="F38" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="G38" t="s">
         <v>108</v>
@@ -2339,7 +2404,7 @@
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
@@ -2347,28 +2412,28 @@
         <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G39" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
@@ -2376,28 +2441,28 @@
         <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="D40" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F40" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="G40" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
@@ -2405,28 +2470,28 @@
         <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D41" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E41" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="F41" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H41" t="s">
         <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
@@ -2434,28 +2499,28 @@
         <v>82</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E42" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F42" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="G42" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
@@ -2463,28 +2528,28 @@
         <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D43" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E43" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="F43" t="s">
-        <v>64</v>
+        <v>119</v>
       </c>
       <c r="G43" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
@@ -2492,22 +2557,22 @@
         <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="F44" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="G44" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
@@ -2521,28 +2586,28 @@
         <v>82</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="D45" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="E45" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="F45" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="G45" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
@@ -2550,28 +2615,28 @@
         <v>82</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="E46" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="F46" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="G46" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
@@ -2579,28 +2644,28 @@
         <v>82</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="D47" t="s">
+        <v>118</v>
+      </c>
+      <c r="E47" t="s">
+        <v>93</v>
+      </c>
+      <c r="F47" t="s">
+        <v>119</v>
+      </c>
+      <c r="G47" t="s">
         <v>120</v>
       </c>
-      <c r="E47" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" t="s">
-        <v>23</v>
-      </c>
-      <c r="G47" t="s">
-        <v>121</v>
-      </c>
       <c r="H47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
@@ -2608,22 +2673,22 @@
         <v>82</v>
       </c>
       <c r="B48" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D48" t="s">
+        <v>121</v>
+      </c>
+      <c r="E48" t="s">
+        <v>93</v>
+      </c>
+      <c r="F48" t="s">
         <v>122</v>
       </c>
-      <c r="E48" t="s">
-        <v>27</v>
-      </c>
-      <c r="F48" t="s">
-        <v>78</v>
-      </c>
       <c r="G48" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
@@ -2637,28 +2702,28 @@
         <v>82</v>
       </c>
       <c r="B49" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="D49" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E49" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F49" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="G49" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
@@ -2666,19 +2731,19 @@
         <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D50" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E50" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F50" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G50" t="s">
         <v>81</v>
@@ -2687,7 +2752,7 @@
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
@@ -2695,28 +2760,28 @@
         <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="D51" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E51" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="F51" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="G51" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
@@ -2724,28 +2789,28 @@
         <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="C52" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="D52" t="s">
         <v>130</v>
       </c>
       <c r="E52" t="s">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="F52" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="G52" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
@@ -2753,28 +2818,28 @@
         <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="C53" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="D53" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E53" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F53" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="G53" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
@@ -2782,28 +2847,28 @@
         <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C54" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="D54" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E54" t="s">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="F54" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="G54" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
@@ -2811,19 +2876,19 @@
         <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C55" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D55" t="s">
         <v>135</v>
       </c>
       <c r="E55" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F55" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G55" t="s">
         <v>81</v>
@@ -2832,7 +2897,7 @@
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
@@ -2840,19 +2905,19 @@
         <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C56" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D56" t="s">
+        <v>138</v>
+      </c>
+      <c r="E56" t="s">
         <v>136</v>
       </c>
-      <c r="E56" t="s">
-        <v>131</v>
-      </c>
       <c r="F56" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G56" t="s">
         <v>81</v>
@@ -2861,7 +2926,7 @@
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
@@ -2869,19 +2934,19 @@
         <v>82</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C57" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D57" t="s">
+        <v>139</v>
+      </c>
+      <c r="E57" t="s">
+        <v>136</v>
+      </c>
+      <c r="F57" t="s">
         <v>137</v>
-      </c>
-      <c r="E57" t="s">
-        <v>131</v>
-      </c>
-      <c r="F57" t="s">
-        <v>132</v>
       </c>
       <c r="G57" t="s">
         <v>81</v>
@@ -2890,7 +2955,7 @@
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
@@ -2898,22 +2963,22 @@
         <v>82</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D58" t="s">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="E58" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F58" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G58" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
@@ -2927,28 +2992,28 @@
         <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="C59" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D59" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E59" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F59" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G59" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
@@ -2956,28 +3021,28 @@
         <v>82</v>
       </c>
       <c r="B60" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="C60" t="s">
+        <v>134</v>
+      </c>
+      <c r="D60" t="s">
         <v>142</v>
       </c>
-      <c r="D60" t="s">
-        <v>145</v>
-      </c>
       <c r="E60" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F60" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G60" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
@@ -2985,28 +3050,28 @@
         <v>82</v>
       </c>
       <c r="B61" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="C61" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="D61" t="s">
+        <v>144</v>
+      </c>
+      <c r="E61" t="s">
+        <v>56</v>
+      </c>
+      <c r="F61" t="s">
+        <v>145</v>
+      </c>
+      <c r="G61" t="s">
         <v>146</v>
       </c>
-      <c r="E61" t="s">
-        <v>144</v>
-      </c>
-      <c r="F61" t="s">
-        <v>140</v>
-      </c>
-      <c r="G61" t="s">
-        <v>141</v>
-      </c>
       <c r="H61" t="s">
         <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
@@ -3014,28 +3079,28 @@
         <v>82</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="C62" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="D62" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E62" t="s">
-        <v>144</v>
+        <v>56</v>
       </c>
       <c r="F62" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="G62" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
@@ -3043,22 +3108,22 @@
         <v>148</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="D63" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="E63" t="s">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="F63" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="G63" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
@@ -3078,13 +3143,13 @@
         <v>83</v>
       </c>
       <c r="D64" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E64" t="s">
         <v>85</v>
       </c>
       <c r="F64" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G64" t="s">
         <v>87</v>
@@ -3093,7 +3158,7 @@
         <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
@@ -3101,19 +3166,19 @@
         <v>148</v>
       </c>
       <c r="B65" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
         <v>83</v>
       </c>
       <c r="D65" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E65" t="s">
         <v>85</v>
       </c>
       <c r="F65" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G65" t="s">
         <v>87</v>
@@ -3122,7 +3187,7 @@
         <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
@@ -3130,28 +3195,28 @@
         <v>148</v>
       </c>
       <c r="B66" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C66" t="s">
         <v>83</v>
       </c>
       <c r="D66" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E66" t="s">
         <v>85</v>
       </c>
       <c r="F66" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G66" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
@@ -3159,28 +3224,28 @@
         <v>148</v>
       </c>
       <c r="B67" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C67" t="s">
         <v>83</v>
       </c>
       <c r="D67" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E67" t="s">
         <v>85</v>
       </c>
       <c r="F67" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G67" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
@@ -3188,28 +3253,28 @@
         <v>148</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C68" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D68" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E68" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F68" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="G68" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
@@ -3217,28 +3282,28 @@
         <v>148</v>
       </c>
       <c r="B69" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C69" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="D69" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E69" t="s">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="F69" t="s">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="G69" t="s">
-        <v>55</v>
+        <v>159</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
@@ -3246,28 +3311,28 @@
         <v>148</v>
       </c>
       <c r="B70" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C70" t="s">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="D70" t="s">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="E70" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="F70" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="G70" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
@@ -3275,28 +3340,28 @@
         <v>148</v>
       </c>
       <c r="B71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="D71" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E71" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="F71" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="G71" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
@@ -3304,28 +3369,28 @@
         <v>148</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="D72" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="E72" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="F72" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="G72" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
@@ -3333,28 +3398,28 @@
         <v>148</v>
       </c>
       <c r="B73" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="D73" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E73" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="F73" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="G73" t="s">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
@@ -3362,28 +3427,28 @@
         <v>148</v>
       </c>
       <c r="B74" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="D74" t="s">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="E74" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="F74" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G74" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
@@ -3391,28 +3456,28 @@
         <v>148</v>
       </c>
       <c r="B75" t="s">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="C75" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="D75" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E75" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="F75" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="G75" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
@@ -3420,28 +3485,28 @@
         <v>148</v>
       </c>
       <c r="B76" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C76" t="s">
-        <v>159</v>
+        <v>96</v>
       </c>
       <c r="D76" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="E76" t="s">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="F76" t="s">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="G76" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
@@ -3449,28 +3514,28 @@
         <v>148</v>
       </c>
       <c r="B77" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C77" t="s">
-        <v>159</v>
+        <v>27</v>
       </c>
       <c r="D77" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="E77" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="F77" t="s">
-        <v>161</v>
+        <v>48</v>
       </c>
       <c r="G77" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
@@ -3478,28 +3543,28 @@
         <v>148</v>
       </c>
       <c r="B78" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C78" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D78" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E78" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F78" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="G78" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
@@ -3510,25 +3575,25 @@
         <v>40</v>
       </c>
       <c r="C79" t="s">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="D79" t="s">
-        <v>119</v>
+        <v>167</v>
       </c>
       <c r="E79" t="s">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="F79" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="G79" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
@@ -3536,22 +3601,22 @@
         <v>148</v>
       </c>
       <c r="B80" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C80" t="s">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="D80" t="s">
+        <v>168</v>
+      </c>
+      <c r="E80" t="s">
+        <v>93</v>
+      </c>
+      <c r="F80" t="s">
         <v>119</v>
       </c>
-      <c r="E80" t="s">
-        <v>162</v>
-      </c>
-      <c r="F80" t="s">
-        <v>161</v>
-      </c>
       <c r="G80" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
@@ -3565,28 +3630,28 @@
         <v>148</v>
       </c>
       <c r="B81" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C81" t="s">
-        <v>159</v>
+        <v>96</v>
       </c>
       <c r="D81" t="s">
-        <v>119</v>
+        <v>169</v>
       </c>
       <c r="E81" t="s">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="F81" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="G81" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
@@ -3594,28 +3659,28 @@
         <v>148</v>
       </c>
       <c r="B82" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C82" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="D82" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="E82" t="s">
-        <v>48</v>
+        <v>166</v>
       </c>
       <c r="F82" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
       <c r="G82" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
@@ -3623,28 +3688,28 @@
         <v>148</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C83" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D83" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="E83" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F83" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G83" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
@@ -3652,28 +3717,28 @@
         <v>148</v>
       </c>
       <c r="B84" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C84" t="s">
-        <v>41</v>
+        <v>171</v>
       </c>
       <c r="D84" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E84" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F84" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G84" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
@@ -3681,28 +3746,28 @@
         <v>148</v>
       </c>
       <c r="B85" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="C85" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D85" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E85" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="F85" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="G85" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
@@ -3710,28 +3775,28 @@
         <v>148</v>
       </c>
       <c r="B86" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C86" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="D86" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E86" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="F86" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="G86" t="s">
-        <v>49</v>
+        <v>173</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
@@ -3739,28 +3804,28 @@
         <v>148</v>
       </c>
       <c r="B87" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C87" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="D87" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="E87" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="F87" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="G87" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
@@ -3768,28 +3833,28 @@
         <v>148</v>
       </c>
       <c r="B88" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="C88" t="s">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="D88" t="s">
-        <v>168</v>
+        <v>103</v>
       </c>
       <c r="E88" t="s">
-        <v>69</v>
+        <v>166</v>
       </c>
       <c r="F88" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="G88" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
@@ -3797,28 +3862,28 @@
         <v>148</v>
       </c>
       <c r="B89" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C89" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="D89" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E89" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="F89" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="G89" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
@@ -3826,28 +3891,28 @@
         <v>148</v>
       </c>
       <c r="B90" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C90" t="s">
-        <v>142</v>
+        <v>20</v>
       </c>
       <c r="D90" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E90" t="s">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="F90" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="G90" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
@@ -3855,22 +3920,22 @@
         <v>148</v>
       </c>
       <c r="B91" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C91" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="D91" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E91" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="F91" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="G91" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
@@ -3884,28 +3949,28 @@
         <v>148</v>
       </c>
       <c r="B92" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C92" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="D92" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="E92" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="F92" t="s">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="G92" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
@@ -3913,2197 +3978,2197 @@
         <v>148</v>
       </c>
       <c r="B93" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C93" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="D93" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E93" t="s">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="F93" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="G93" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="B94" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C94" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D94" t="s">
-        <v>176</v>
+        <v>14</v>
       </c>
       <c r="E94" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F94" t="s">
-        <v>177</v>
+        <v>60</v>
       </c>
       <c r="G94" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="B95" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C95" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="D95" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E95" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F95" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="G95" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="C96" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="D96" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E96" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="F96" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G96" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="B97" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="C97" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="D97" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E97" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="F97" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G97" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="B98" t="s">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="C98" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="D98" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E98" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="F98" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G98" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="B99" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="C99" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="D99" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E99" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F99" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="G99" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B100" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C100" t="s">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="D100" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E100" t="s">
-        <v>181</v>
+        <v>93</v>
       </c>
       <c r="F100" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G100" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B101" t="s">
-        <v>111</v>
+        <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>179</v>
+        <v>13</v>
       </c>
       <c r="D101" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E101" t="s">
-        <v>181</v>
+        <v>71</v>
       </c>
       <c r="F101" t="s">
-        <v>182</v>
+        <v>16</v>
       </c>
       <c r="G101" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
       </c>
       <c r="I101" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B102" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="D102" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E102" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="F102" t="s">
-        <v>182</v>
+        <v>23</v>
       </c>
       <c r="G102" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B103" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C103" t="s">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="D103" t="s">
-        <v>110</v>
+        <v>186</v>
       </c>
       <c r="E103" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="F103" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G103" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B104" t="s">
-        <v>184</v>
+        <v>24</v>
       </c>
       <c r="C104" t="s">
-        <v>179</v>
+        <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>110</v>
+        <v>174</v>
       </c>
       <c r="E104" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="F104" t="s">
-        <v>182</v>
+        <v>16</v>
       </c>
       <c r="G104" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H104" t="s">
         <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B105" t="s">
-        <v>185</v>
+        <v>24</v>
       </c>
       <c r="C105" t="s">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="D105" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="E105" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="F105" t="s">
-        <v>182</v>
+        <v>23</v>
       </c>
       <c r="G105" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B106" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C106" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D106" t="s">
         <v>186</v>
       </c>
       <c r="E106" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="F106" t="s">
-        <v>43</v>
+        <v>187</v>
       </c>
       <c r="G106" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="H106" t="s">
         <v>18</v>
       </c>
       <c r="I106" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B107" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C107" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="E107" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="F107" t="s">
-        <v>43</v>
+        <v>189</v>
       </c>
       <c r="G107" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
       </c>
       <c r="I107" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B108" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C108" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D108" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="E108" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="F108" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G108" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
       </c>
       <c r="I108" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B109" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C109" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D109" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E109" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="F109" t="s">
-        <v>43</v>
+        <v>187</v>
       </c>
       <c r="G109" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
       </c>
       <c r="I109" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B110" t="s">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="C110" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="D110" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="E110" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F110" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G110" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H110" t="s">
         <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B111" t="s">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="C111" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D111" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="E111" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="F111" t="s">
-        <v>43</v>
+        <v>189</v>
       </c>
       <c r="G111" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B112" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="C112" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D112" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="E112" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="F112" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G112" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B113" t="s">
-        <v>184</v>
+        <v>54</v>
       </c>
       <c r="C113" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D113" t="s">
         <v>190</v>
       </c>
       <c r="E113" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="F113" t="s">
-        <v>43</v>
+        <v>187</v>
       </c>
       <c r="G113" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B114" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C114" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="D114" t="s">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="E114" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F114" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G114" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H114" t="s">
         <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B115" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C115" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D115" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="E115" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F115" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G115" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B116" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C116" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D116" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="E116" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="F116" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="G116" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B117" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C117" t="s">
+        <v>20</v>
+      </c>
+      <c r="D117" t="s">
+        <v>192</v>
+      </c>
+      <c r="E117" t="s">
         <v>51</v>
       </c>
-      <c r="D117" t="s">
-        <v>153</v>
-      </c>
-      <c r="E117" t="s">
-        <v>66</v>
-      </c>
       <c r="F117" t="s">
-        <v>53</v>
+        <v>193</v>
       </c>
       <c r="G117" t="s">
-        <v>55</v>
+        <v>194</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B118" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C118" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="D118" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="E118" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="F118" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="G118" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B119" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="C119" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="D119" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E119" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F119" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G119" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
       </c>
       <c r="I119" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B120" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C120" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D120" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E120" t="s">
         <v>69</v>
       </c>
       <c r="F120" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="G120" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
       </c>
       <c r="I120" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B121" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C121" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="D121" t="s">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="E121" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="F121" t="s">
-        <v>70</v>
+        <v>181</v>
       </c>
       <c r="G121" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B122" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C122" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D122" t="s">
-        <v>118</v>
+        <v>196</v>
       </c>
       <c r="E122" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F122" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G122" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B123" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="C123" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="D123" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="E123" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F123" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G123" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B124" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="C124" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D124" t="s">
-        <v>193</v>
+        <v>131</v>
       </c>
       <c r="E124" t="s">
         <v>69</v>
       </c>
       <c r="F124" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="G124" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
       </c>
       <c r="I124" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B125" t="s">
+        <v>72</v>
+      </c>
+      <c r="C125" t="s">
+        <v>20</v>
+      </c>
+      <c r="D125" t="s">
         <v>25</v>
       </c>
-      <c r="C125" t="s">
-        <v>67</v>
-      </c>
-      <c r="D125" t="s">
-        <v>194</v>
-      </c>
       <c r="E125" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F125" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="G125" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
       </c>
       <c r="I125" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B126" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="C126" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="D126" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="E126" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F126" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G126" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
       </c>
       <c r="I126" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B127" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C127" t="s">
-        <v>67</v>
+        <v>197</v>
       </c>
       <c r="D127" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="E127" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="F127" t="s">
-        <v>70</v>
+        <v>189</v>
       </c>
       <c r="G127" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B128" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="C128" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="D128" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E128" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F128" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="G128" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B129" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="C129" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="D129" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="E129" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F129" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="G129" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B130" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="C130" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D130" t="s">
-        <v>196</v>
+        <v>130</v>
       </c>
       <c r="E130" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F130" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="G130" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B131" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="C131" t="s">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="D131" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E131" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="F131" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="G131" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H131" t="s">
         <v>18</v>
       </c>
       <c r="I131" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B132" t="s">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="C132" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="D132" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E132" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F132" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="G132" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B133" t="s">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="C133" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D133" t="s">
-        <v>197</v>
+        <v>130</v>
       </c>
       <c r="E133" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F133" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="G133" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
       </c>
       <c r="I133" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B134" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="C134" t="s">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="D134" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E134" t="s">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="F134" t="s">
-        <v>92</v>
+        <v>203</v>
       </c>
       <c r="G134" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H134" t="s">
         <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B135" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="C135" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="D135" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="E135" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F135" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="G135" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H135" t="s">
         <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B136" t="s">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="C136" t="s">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="D136" t="s">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="E136" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="F136" t="s">
-        <v>92</v>
+        <v>203</v>
       </c>
       <c r="G136" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H136" t="s">
         <v>18</v>
       </c>
       <c r="I136" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B137" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="C137" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="D137" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="E137" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="F137" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G137" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
       </c>
       <c r="I137" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B138" t="s">
-        <v>56</v>
+        <v>204</v>
       </c>
       <c r="C138" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="D138" t="s">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="E138" t="s">
-        <v>131</v>
+        <v>34</v>
       </c>
       <c r="F138" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="G138" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
       </c>
       <c r="I138" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B139" t="s">
-        <v>56</v>
+        <v>204</v>
       </c>
       <c r="C139" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="D139" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E139" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="F139" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G139" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H139" t="s">
         <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B140" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="C140" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="D140" t="s">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="E140" t="s">
-        <v>131</v>
+        <v>34</v>
       </c>
       <c r="F140" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="G140" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H140" t="s">
         <v>18</v>
       </c>
       <c r="I140" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B141" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="C141" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="D141" t="s">
-        <v>203</v>
+        <v>68</v>
       </c>
       <c r="E141" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="F141" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G141" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H141" t="s">
         <v>18</v>
       </c>
       <c r="I141" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B142" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="C142" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="D142" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="E142" t="s">
-        <v>131</v>
+        <v>208</v>
       </c>
       <c r="F142" t="s">
-        <v>132</v>
+        <v>16</v>
       </c>
       <c r="G142" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H142" t="s">
         <v>18</v>
       </c>
       <c r="I142" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B143" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C143" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D143" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E143" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F143" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G143" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H143" t="s">
         <v>18</v>
       </c>
       <c r="I143" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B144" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C144" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D144" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E144" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F144" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G144" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H144" t="s">
         <v>18</v>
       </c>
       <c r="I144" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B145" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C145" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D145" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E145" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F145" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G145" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H145" t="s">
         <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B146" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="C146" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="D146" t="s">
-        <v>47</v>
+        <v>212</v>
       </c>
       <c r="E146" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="F146" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="G146" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B147" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C147" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="D147" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="E147" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="F147" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="G147" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H147" t="s">
         <v>18</v>
       </c>
       <c r="I147" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B148" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C148" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="D148" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="E148" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="F148" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="G148" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H148" t="s">
         <v>18</v>
       </c>
       <c r="I148" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B149" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C149" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="D149" t="s">
-        <v>45</v>
+        <v>215</v>
       </c>
       <c r="E149" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="F149" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="G149" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H149" t="s">
         <v>18</v>
       </c>
       <c r="I149" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B150" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C150" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="D150" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E150" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="F150" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="G150" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H150" t="s">
         <v>18</v>
       </c>
       <c r="I150" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B151" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C151" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="D151" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E151" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="F151" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="G151" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H151" t="s">
         <v>18</v>
       </c>
       <c r="I151" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B152" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C152" t="s">
         <v>41</v>
       </c>
       <c r="D152" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="E152" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="F152" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G152" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H152" t="s">
         <v>18</v>
       </c>
       <c r="I152" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B153" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C153" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D153" t="s">
-        <v>125</v>
+        <v>174</v>
       </c>
       <c r="E153" t="s">
-        <v>48</v>
+        <v>208</v>
       </c>
       <c r="F153" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="G153" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H153" t="s">
         <v>18</v>
       </c>
       <c r="I153" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B154" t="s">
+        <v>26</v>
+      </c>
+      <c r="C154" t="s">
+        <v>91</v>
+      </c>
+      <c r="D154" t="s">
+        <v>218</v>
+      </c>
+      <c r="E154" t="s">
+        <v>93</v>
+      </c>
+      <c r="F154" t="s">
+        <v>119</v>
+      </c>
+      <c r="G154" t="s">
         <v>111</v>
       </c>
-      <c r="C154" t="s">
-        <v>41</v>
-      </c>
-      <c r="D154" t="s">
-        <v>187</v>
-      </c>
-      <c r="E154" t="s">
-        <v>48</v>
-      </c>
-      <c r="F154" t="s">
-        <v>43</v>
-      </c>
-      <c r="G154" t="s">
-        <v>55</v>
-      </c>
       <c r="H154" t="s">
         <v>18</v>
       </c>
       <c r="I154" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B155" t="s">
-        <v>112</v>
+        <v>26</v>
       </c>
       <c r="C155" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D155" t="s">
-        <v>42</v>
+        <v>219</v>
       </c>
       <c r="E155" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="F155" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="G155" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="H155" t="s">
         <v>18</v>
       </c>
       <c r="I155" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B156" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="C156" t="s">
         <v>41</v>
       </c>
       <c r="D156" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E156" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="F156" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G156" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H156" t="s">
         <v>18</v>
       </c>
       <c r="I156" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B157" t="s">
-        <v>184</v>
+        <v>26</v>
       </c>
       <c r="C157" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D157" t="s">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="E157" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="F157" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G157" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H157" t="s">
         <v>18</v>
       </c>
       <c r="I157" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B158" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C158" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="D158" t="s">
-        <v>153</v>
+        <v>218</v>
       </c>
       <c r="E158" t="s">
-        <v>209</v>
+        <v>93</v>
       </c>
       <c r="F158" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="G158" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
       </c>
       <c r="I158" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B159" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C159" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="D159" t="s">
-        <v>153</v>
+        <v>219</v>
       </c>
       <c r="E159" t="s">
-        <v>209</v>
+        <v>93</v>
       </c>
       <c r="F159" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="G159" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="H159" t="s">
         <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B160" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C160" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D160" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E160" t="s">
         <v>69</v>
       </c>
       <c r="F160" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="G160" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B161" t="s">
         <v>40</v>
       </c>
       <c r="C161" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D161" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E161" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F161" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="G161" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H161" t="s">
         <v>18</v>
       </c>
       <c r="I161" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B162" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C162" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="D162" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="E162" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="F162" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="G162" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="H162" t="s">
         <v>18</v>
       </c>
       <c r="I162" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B163" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C163" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="D163" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E163" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="F163" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="G163" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="H163" t="s">
         <v>18</v>
       </c>
       <c r="I163" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B164" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C164" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="D164" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="E164" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F164" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G164" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H164" t="s">
         <v>18</v>
       </c>
       <c r="I164" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B165" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="C165" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D165" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E165" t="s">
         <v>69</v>
       </c>
       <c r="F165" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="G165" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H165" t="s">
         <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B166" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="C166" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D166" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E166" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F166" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="G166" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H166" t="s">
         <v>18</v>
       </c>
       <c r="I166" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B167" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="C167" t="s">
-        <v>169</v>
+        <v>91</v>
       </c>
       <c r="D167" t="s">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="E167" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F167" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="G167" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H167" t="s">
         <v>18</v>
       </c>
       <c r="I167" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B168" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="C168" t="s">
-        <v>215</v>
+        <v>96</v>
       </c>
       <c r="D168" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="E168" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="F168" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="G168" t="s">
-        <v>217</v>
+        <v>19</v>
       </c>
       <c r="H168" t="s">
         <v>18</v>
@@ -6114,30 +6179,523 @@
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
+        <v>207</v>
+      </c>
+      <c r="B169" t="s">
+        <v>65</v>
+      </c>
+      <c r="C169" t="s">
+        <v>41</v>
+      </c>
+      <c r="D169" t="s">
+        <v>220</v>
+      </c>
+      <c r="E169" t="s">
+        <v>69</v>
+      </c>
+      <c r="F169" t="s">
+        <v>44</v>
+      </c>
+      <c r="G169" t="s">
+        <v>19</v>
+      </c>
+      <c r="H169" t="s">
+        <v>18</v>
+      </c>
+      <c r="I169" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="15">
+      <c r="A170" t="s">
+        <v>207</v>
+      </c>
+      <c r="B170" t="s">
+        <v>65</v>
+      </c>
+      <c r="C170" t="s">
+        <v>20</v>
+      </c>
+      <c r="D170" t="s">
+        <v>223</v>
+      </c>
+      <c r="E170" t="s">
+        <v>22</v>
+      </c>
+      <c r="F170" t="s">
+        <v>23</v>
+      </c>
+      <c r="G170" t="s">
+        <v>19</v>
+      </c>
+      <c r="H170" t="s">
+        <v>18</v>
+      </c>
+      <c r="I170" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="15">
+      <c r="A171" t="s">
+        <v>207</v>
+      </c>
+      <c r="B171" t="s">
+        <v>72</v>
+      </c>
+      <c r="C171" t="s">
+        <v>91</v>
+      </c>
+      <c r="D171" t="s">
+        <v>222</v>
+      </c>
+      <c r="E171" t="s">
+        <v>93</v>
+      </c>
+      <c r="F171" t="s">
+        <v>119</v>
+      </c>
+      <c r="G171" t="s">
+        <v>111</v>
+      </c>
+      <c r="H171" t="s">
+        <v>18</v>
+      </c>
+      <c r="I171" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="15">
+      <c r="A172" t="s">
+        <v>207</v>
+      </c>
+      <c r="B172" t="s">
+        <v>72</v>
+      </c>
+      <c r="C172" t="s">
+        <v>96</v>
+      </c>
+      <c r="D172" t="s">
+        <v>130</v>
+      </c>
+      <c r="E172" t="s">
+        <v>56</v>
+      </c>
+      <c r="F172" t="s">
+        <v>60</v>
+      </c>
+      <c r="G172" t="s">
+        <v>19</v>
+      </c>
+      <c r="H172" t="s">
+        <v>18</v>
+      </c>
+      <c r="I172" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="15">
+      <c r="A173" t="s">
+        <v>207</v>
+      </c>
+      <c r="B173" t="s">
+        <v>72</v>
+      </c>
+      <c r="C173" t="s">
+        <v>41</v>
+      </c>
+      <c r="D173" t="s">
+        <v>165</v>
+      </c>
+      <c r="E173" t="s">
+        <v>69</v>
+      </c>
+      <c r="F173" t="s">
+        <v>44</v>
+      </c>
+      <c r="G173" t="s">
+        <v>19</v>
+      </c>
+      <c r="H173" t="s">
+        <v>18</v>
+      </c>
+      <c r="I173" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="15">
+      <c r="A174" t="s">
+        <v>207</v>
+      </c>
+      <c r="B174" t="s">
+        <v>72</v>
+      </c>
+      <c r="C174" t="s">
+        <v>224</v>
+      </c>
+      <c r="D174" t="s">
+        <v>205</v>
+      </c>
+      <c r="E174" t="s">
+        <v>225</v>
+      </c>
+      <c r="F174" t="s">
+        <v>124</v>
+      </c>
+      <c r="G174" t="s">
+        <v>226</v>
+      </c>
+      <c r="H174" t="s">
+        <v>18</v>
+      </c>
+      <c r="I174" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="15">
+      <c r="A175" t="s">
+        <v>207</v>
+      </c>
+      <c r="B175" t="s">
+        <v>78</v>
+      </c>
+      <c r="C175" t="s">
+        <v>91</v>
+      </c>
+      <c r="D175" t="s">
+        <v>222</v>
+      </c>
+      <c r="E175" t="s">
+        <v>93</v>
+      </c>
+      <c r="F175" t="s">
+        <v>119</v>
+      </c>
+      <c r="G175" t="s">
+        <v>111</v>
+      </c>
+      <c r="H175" t="s">
+        <v>18</v>
+      </c>
+      <c r="I175" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="15">
+      <c r="A176" t="s">
+        <v>207</v>
+      </c>
+      <c r="B176" t="s">
+        <v>78</v>
+      </c>
+      <c r="C176" t="s">
+        <v>96</v>
+      </c>
+      <c r="D176" t="s">
+        <v>130</v>
+      </c>
+      <c r="E176" t="s">
+        <v>56</v>
+      </c>
+      <c r="F176" t="s">
+        <v>60</v>
+      </c>
+      <c r="G176" t="s">
+        <v>19</v>
+      </c>
+      <c r="H176" t="s">
+        <v>18</v>
+      </c>
+      <c r="I176" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="15">
+      <c r="A177" t="s">
+        <v>207</v>
+      </c>
+      <c r="B177" t="s">
+        <v>78</v>
+      </c>
+      <c r="C177" t="s">
+        <v>41</v>
+      </c>
+      <c r="D177" t="s">
+        <v>128</v>
+      </c>
+      <c r="E177" t="s">
+        <v>69</v>
+      </c>
+      <c r="F177" t="s">
+        <v>44</v>
+      </c>
+      <c r="G177" t="s">
+        <v>19</v>
+      </c>
+      <c r="H177" t="s">
+        <v>18</v>
+      </c>
+      <c r="I177" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="15">
+      <c r="A178" t="s">
+        <v>207</v>
+      </c>
+      <c r="B178" t="s">
+        <v>78</v>
+      </c>
+      <c r="C178" t="s">
+        <v>20</v>
+      </c>
+      <c r="D178" t="s">
+        <v>227</v>
+      </c>
+      <c r="E178" t="s">
+        <v>22</v>
+      </c>
+      <c r="F178" t="s">
+        <v>23</v>
+      </c>
+      <c r="G178" t="s">
+        <v>19</v>
+      </c>
+      <c r="H178" t="s">
+        <v>18</v>
+      </c>
+      <c r="I178" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="15">
+      <c r="A179" t="s">
+        <v>207</v>
+      </c>
+      <c r="B179" t="s">
+        <v>78</v>
+      </c>
+      <c r="C179" t="s">
+        <v>171</v>
+      </c>
+      <c r="D179" t="s">
+        <v>172</v>
+      </c>
+      <c r="E179" t="s">
+        <v>51</v>
+      </c>
+      <c r="F179" t="s">
+        <v>52</v>
+      </c>
+      <c r="G179" t="s">
+        <v>53</v>
+      </c>
+      <c r="H179" t="s">
+        <v>18</v>
+      </c>
+      <c r="I179" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="15">
+      <c r="A180" t="s">
+        <v>207</v>
+      </c>
+      <c r="B180" t="s">
+        <v>78</v>
+      </c>
+      <c r="C180" t="s">
+        <v>224</v>
+      </c>
+      <c r="D180" t="s">
+        <v>205</v>
+      </c>
+      <c r="E180" t="s">
+        <v>225</v>
+      </c>
+      <c r="F180" t="s">
+        <v>124</v>
+      </c>
+      <c r="G180" t="s">
+        <v>226</v>
+      </c>
+      <c r="H180" t="s">
+        <v>18</v>
+      </c>
+      <c r="I180" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="15">
+      <c r="A181" t="s">
+        <v>207</v>
+      </c>
+      <c r="B181" t="s">
+        <v>133</v>
+      </c>
+      <c r="C181" t="s">
+        <v>41</v>
+      </c>
+      <c r="D181" t="s">
         <v>195</v>
       </c>
-      <c r="B169" t="s">
-        <v>36</v>
-      </c>
-      <c r="C169" t="s">
-        <v>215</v>
-      </c>
-      <c r="D169" t="s">
-        <v>190</v>
-      </c>
-      <c r="E169" t="s">
-        <v>216</v>
-      </c>
-      <c r="F169" t="s">
-        <v>107</v>
-      </c>
-      <c r="G169" t="s">
-        <v>217</v>
-      </c>
-      <c r="H169" t="s">
-        <v>18</v>
-      </c>
-      <c r="I169" t="s">
+      <c r="E181" t="s">
+        <v>69</v>
+      </c>
+      <c r="F181" t="s">
+        <v>44</v>
+      </c>
+      <c r="G181" t="s">
+        <v>19</v>
+      </c>
+      <c r="H181" t="s">
+        <v>18</v>
+      </c>
+      <c r="I181" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="15">
+      <c r="A182" t="s">
+        <v>207</v>
+      </c>
+      <c r="B182" t="s">
+        <v>133</v>
+      </c>
+      <c r="C182" t="s">
+        <v>20</v>
+      </c>
+      <c r="D182" t="s">
+        <v>228</v>
+      </c>
+      <c r="E182" t="s">
+        <v>22</v>
+      </c>
+      <c r="F182" t="s">
+        <v>23</v>
+      </c>
+      <c r="G182" t="s">
+        <v>19</v>
+      </c>
+      <c r="H182" t="s">
+        <v>18</v>
+      </c>
+      <c r="I182" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="15">
+      <c r="A183" t="s">
+        <v>207</v>
+      </c>
+      <c r="B183" t="s">
+        <v>143</v>
+      </c>
+      <c r="C183" t="s">
+        <v>41</v>
+      </c>
+      <c r="D183" t="s">
+        <v>42</v>
+      </c>
+      <c r="E183" t="s">
+        <v>69</v>
+      </c>
+      <c r="F183" t="s">
+        <v>44</v>
+      </c>
+      <c r="G183" t="s">
+        <v>19</v>
+      </c>
+      <c r="H183" t="s">
+        <v>18</v>
+      </c>
+      <c r="I183" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="15">
+      <c r="A184" t="s">
+        <v>207</v>
+      </c>
+      <c r="B184" t="s">
+        <v>143</v>
+      </c>
+      <c r="C184" t="s">
+        <v>20</v>
+      </c>
+      <c r="D184" t="s">
+        <v>229</v>
+      </c>
+      <c r="E184" t="s">
+        <v>22</v>
+      </c>
+      <c r="F184" t="s">
+        <v>23</v>
+      </c>
+      <c r="G184" t="s">
+        <v>19</v>
+      </c>
+      <c r="H184" t="s">
+        <v>18</v>
+      </c>
+      <c r="I184" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="15">
+      <c r="A185" t="s">
+        <v>207</v>
+      </c>
+      <c r="B185" t="s">
+        <v>147</v>
+      </c>
+      <c r="C185" t="s">
+        <v>41</v>
+      </c>
+      <c r="D185" t="s">
+        <v>200</v>
+      </c>
+      <c r="E185" t="s">
+        <v>69</v>
+      </c>
+      <c r="F185" t="s">
+        <v>44</v>
+      </c>
+      <c r="G185" t="s">
+        <v>19</v>
+      </c>
+      <c r="H185" t="s">
+        <v>18</v>
+      </c>
+      <c r="I185" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="15">
+      <c r="A186" t="s">
+        <v>207</v>
+      </c>
+      <c r="B186" t="s">
+        <v>204</v>
+      </c>
+      <c r="C186" t="s">
+        <v>41</v>
+      </c>
+      <c r="D186" t="s">
+        <v>205</v>
+      </c>
+      <c r="E186" t="s">
+        <v>69</v>
+      </c>
+      <c r="F186" t="s">
+        <v>44</v>
+      </c>
+      <c r="G186" t="s">
+        <v>19</v>
+      </c>
+      <c r="H186" t="s">
+        <v>18</v>
+      </c>
+      <c r="I186" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6149,8 +6707,176 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{cc790074-4ec6-4626-b2b8-d07d99f624de}">
-  <dimension ref="A1:F38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d64db6af-27ee-431e-ab28-5ffac21b7e1d}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="13.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="46.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="12.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
+    <col min="7" max="7" width="11.4285714285714" customWidth="1"/>
+    <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
+    <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="56.25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15">
+      <c r="A2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15">
+      <c r="A3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
+      <c r="A4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15">
+      <c r="A5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{9d6e7931-2515-4e86-8066-c8fc5612287e}">
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -6166,13 +6892,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6186,16 +6912,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -6206,16 +6932,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -6226,16 +6952,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="E4" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -6246,16 +6972,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="E5" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6266,16 +6992,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="E6" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -6286,16 +7012,16 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>250</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -6306,16 +7032,16 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -6326,16 +7052,16 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E9" t="s">
-        <v>234</v>
+        <v>70</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -6346,16 +7072,16 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E10" t="s">
-        <v>236</v>
+        <v>125</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -6366,16 +7092,16 @@
         <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="E11" t="s">
-        <v>238</v>
+        <v>170</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -6386,16 +7112,16 @@
         <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="E12" t="s">
-        <v>238</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -6406,16 +7132,16 @@
         <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>221</v>
+        <v>255</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>256</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -6426,16 +7152,16 @@
         <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -6446,16 +7172,16 @@
         <v>148</v>
       </c>
       <c r="B15" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="D15" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>247</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -6466,16 +7192,16 @@
         <v>148</v>
       </c>
       <c r="B16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C16" t="s">
-        <v>159</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>259</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -6486,16 +7212,16 @@
         <v>148</v>
       </c>
       <c r="B17" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="C17" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D17" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>260</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -6506,16 +7232,16 @@
         <v>148</v>
       </c>
       <c r="B18" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="C18" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D18" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -6526,16 +7252,16 @@
         <v>148</v>
       </c>
       <c r="B19" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="C19" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -6546,16 +7272,16 @@
         <v>148</v>
       </c>
       <c r="B20" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>261</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -6563,19 +7289,19 @@
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="D21" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>260</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -6583,19 +7309,19 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="C22" t="s">
         <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>247</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -6603,19 +7329,19 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B23" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
         <v>242</v>
       </c>
       <c r="E23" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -6623,19 +7349,19 @@
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B24" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="E24" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -6643,19 +7369,19 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B25" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="E25" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -6663,19 +7389,19 @@
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B26" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -6683,19 +7409,19 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B27" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="E27" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
@@ -6703,19 +7429,19 @@
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B28" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="E28" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
@@ -6723,19 +7449,19 @@
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B29" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -6743,19 +7469,19 @@
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="C30" t="s">
         <v>41</v>
       </c>
       <c r="D30" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="E30" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
@@ -6763,19 +7489,19 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B31" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="C31" t="s">
         <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="E31" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -6783,19 +7509,19 @@
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B32" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C32" t="s">
         <v>41</v>
       </c>
       <c r="D32" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="E32" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
@@ -6803,19 +7529,19 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B33" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D33" t="s">
         <v>242</v>
       </c>
       <c r="E33" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -6823,19 +7549,19 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
@@ -6843,19 +7569,19 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B35" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D35" t="s">
         <v>242</v>
       </c>
       <c r="E35" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
@@ -6863,19 +7589,19 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B36" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="E36" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
@@ -6883,19 +7609,19 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B37" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C37" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>224</v>
+        <v>264</v>
       </c>
       <c r="E37" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -6903,21 +7629,61 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B38" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="C38" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="E38" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15">
+      <c r="A39" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39" t="s">
+        <v>263</v>
+      </c>
+      <c r="C39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" t="s">
+        <v>264</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15">
+      <c r="A40" t="s">
+        <v>207</v>
+      </c>
+      <c r="B40" t="s">
+        <v>265</v>
+      </c>
+      <c r="C40" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" t="s">
+        <v>264</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
         <v>18</v>
       </c>
     </row>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="259">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -273,13 +273,37 @@
     <t>24.02.2026</t>
   </si>
   <si>
-    <t>Wakat3 edukacja zdrow.</t>
-  </si>
-  <si>
-    <t>3CA|edu</t>
-  </si>
-  <si>
-    <t>Edukacja zdrowotna</t>
+    <t>Antoszewska Joanna</t>
+  </si>
+  <si>
+    <t>3FA|dz1</t>
+  </si>
+  <si>
+    <t>Wychowanie fizyczne</t>
+  </si>
+  <si>
+    <t>sg2</t>
+  </si>
+  <si>
+    <t>Nestoruk Lidia</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>Zastępstwo</t>
+  </si>
+  <si>
+    <t>p. Rejno, zajęcia z wychowawcą za środę 25.02</t>
+  </si>
+  <si>
+    <t>Bokuniewicz Sylwia</t>
+  </si>
+  <si>
+    <t>Świerzewicz Katarzyna</t>
+  </si>
+  <si>
+    <t>Technologia gastronomiczna z towaroznawstwem</t>
   </si>
   <si>
     <t>34</t>
@@ -288,48 +312,6 @@
     <t>Mocarski Arkadiusz</t>
   </si>
   <si>
-    <t>3FA|edu</t>
-  </si>
-  <si>
-    <t>3M|edu</t>
-  </si>
-  <si>
-    <t>3TFA|edu</t>
-  </si>
-  <si>
-    <t>Antoszewska Joanna</t>
-  </si>
-  <si>
-    <t>3FA|dz1</t>
-  </si>
-  <si>
-    <t>Wychowanie fizyczne</t>
-  </si>
-  <si>
-    <t>sg2</t>
-  </si>
-  <si>
-    <t>Nestoruk Lidia</t>
-  </si>
-  <si>
-    <t>Filipek Anna</t>
-  </si>
-  <si>
-    <t>Zastępstwo</t>
-  </si>
-  <si>
-    <t>p. Rejno, zajęcia z wychowawcą za środę 25.02</t>
-  </si>
-  <si>
-    <t>Bokuniewicz Sylwia</t>
-  </si>
-  <si>
-    <t>Świerzewicz Katarzyna</t>
-  </si>
-  <si>
-    <t>Technologia gastronomiczna z towaroznawstwem</t>
-  </si>
-  <si>
     <t>3TH|JA1</t>
   </si>
   <si>
@@ -480,18 +462,6 @@
     <t>37</t>
   </si>
   <si>
-    <t>2FC|edu</t>
-  </si>
-  <si>
-    <t>2WA|edu</t>
-  </si>
-  <si>
-    <t>2S|edu</t>
-  </si>
-  <si>
-    <t>2CA|edu</t>
-  </si>
-  <si>
     <t>2CA|DZ</t>
   </si>
   <si>
@@ -537,12 +507,6 @@
     <t>Wojciechowski Łukasz</t>
   </si>
   <si>
-    <t>Wakat1 j. niemiecki</t>
-  </si>
-  <si>
-    <t>1WA|JN2</t>
-  </si>
-  <si>
     <t>Krzemińska Beata</t>
   </si>
   <si>
@@ -591,15 +555,36 @@
     <t>2TFA|JA2</t>
   </si>
   <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>Mikołajczak Sylwia</t>
+  </si>
+  <si>
+    <t>pogrzeb</t>
+  </si>
+  <si>
+    <t>4TFB|dz2</t>
+  </si>
+  <si>
+    <t>p. Nowak, historia za lekcję 3</t>
+  </si>
+  <si>
+    <t>3FB</t>
+  </si>
+  <si>
+    <t>Kaszak Maria</t>
+  </si>
+  <si>
+    <t>1CB|JA1</t>
+  </si>
+  <si>
+    <t>3TFB</t>
+  </si>
+  <si>
     <t>31</t>
   </si>
   <si>
-    <t>4TFB|dz2</t>
-  </si>
-  <si>
-    <t>1CB|JA1</t>
-  </si>
-  <si>
     <t>1TFA|JA2</t>
   </si>
   <si>
@@ -609,27 +594,21 @@
     <t>Misiąg Anna</t>
   </si>
   <si>
-    <t>1K</t>
-  </si>
-  <si>
     <t>1WB|JN1</t>
   </si>
   <si>
+    <t>1CB</t>
+  </si>
+  <si>
     <t>Nowaczyk Agnieszka</t>
   </si>
   <si>
     <t>3TH</t>
   </si>
   <si>
-    <t>1CB</t>
-  </si>
-  <si>
     <t>1FC</t>
   </si>
   <si>
-    <t>3FB</t>
-  </si>
-  <si>
     <t>Język angielski zawodowy</t>
   </si>
   <si>
@@ -684,7 +663,10 @@
     <t>2TFB|DZ</t>
   </si>
   <si>
-    <t>1WB</t>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>2K</t>
   </si>
   <si>
     <t>1FB|JA2</t>
@@ -696,22 +678,19 @@
     <t>1WA|JN1</t>
   </si>
   <si>
-    <t>Wakat2 matematyka</t>
+    <t>1K|JA1</t>
+  </si>
+  <si>
+    <t>1FC|JA1</t>
+  </si>
+  <si>
+    <t>1S|JA1</t>
   </si>
   <si>
     <t>Matematyka</t>
   </si>
   <si>
-    <t>Młynarczyk Paweł</t>
-  </si>
-  <si>
-    <t>1K|JA1</t>
-  </si>
-  <si>
-    <t>1FC|JA1</t>
-  </si>
-  <si>
-    <t>1S|JA1</t>
+    <t>Filipiak Wiesław</t>
   </si>
   <si>
     <t>Godzina</t>
@@ -810,13 +789,13 @@
     <t>Nowak Magdalena</t>
   </si>
   <si>
+    <t>parter</t>
+  </si>
+  <si>
     <t>14:50-14:55</t>
   </si>
   <si>
     <t>17:20-17:25</t>
-  </si>
-  <si>
-    <t>parter</t>
   </si>
   <si>
     <t>18:10-18:15</t>
@@ -1269,7 +1248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{05bea1ee-a578-4d1f-b14a-ba8b2968c3e2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b6733d39-91fb-4cc6-880a-b43ee80b3669}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1290,8 +1269,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5b5c1647-7cd6-4a55-9464-b63be66d8daa}">
-  <dimension ref="A1:I186"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{43accde4-bcd2-45b5-a22d-3ead5a3078a0}">
+  <dimension ref="A1:I187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1977,7 +1956,7 @@
         <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
         <v>83</v>
@@ -1998,7 +1977,7 @@
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -2006,28 +1985,28 @@
         <v>82</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F25" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="G25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I25" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -2035,22 +2014,22 @@
         <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="G26" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
@@ -2064,28 +2043,28 @@
         <v>82</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G27" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -2093,22 +2072,22 @@
         <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
@@ -2122,13 +2101,13 @@
         <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="E29" t="s">
         <v>56</v>
@@ -2137,10 +2116,10 @@
         <v>60</v>
       </c>
       <c r="G29" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s">
         <v>19</v>
@@ -2151,22 +2130,22 @@
         <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C30" t="s">
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="E30" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G30" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
@@ -2180,28 +2159,28 @@
         <v>82</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="E31" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="F31" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="G31" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
@@ -2209,22 +2188,22 @@
         <v>82</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E32" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F32" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G32" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s">
         <v>18</v>
@@ -2238,28 +2217,28 @@
         <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="E33" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="G33" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
@@ -2267,22 +2246,22 @@
         <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
         <v>27</v>
       </c>
       <c r="D34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E34" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" t="s">
+        <v>48</v>
+      </c>
+      <c r="G34" t="s">
         <v>102</v>
-      </c>
-      <c r="E34" t="s">
-        <v>51</v>
-      </c>
-      <c r="F34" t="s">
-        <v>52</v>
-      </c>
-      <c r="G34" t="s">
-        <v>53</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
@@ -2296,28 +2275,28 @@
         <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
         <v>103</v>
       </c>
       <c r="E35" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="G35" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="H35" t="s">
         <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
@@ -2325,28 +2304,28 @@
         <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="D36" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E36" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="F36" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="G36" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
@@ -2354,28 +2333,28 @@
         <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F37" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="G37" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
@@ -2383,22 +2362,22 @@
         <v>82</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
         <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E38" t="s">
         <v>43</v>
       </c>
       <c r="F38" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="G38" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
@@ -2412,22 +2391,22 @@
         <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E39" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="F39" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G39" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
@@ -2441,22 +2420,22 @@
         <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C40" t="s">
         <v>64</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="E40" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="F40" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G40" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
@@ -2470,22 +2449,22 @@
         <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="E41" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="G41" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="H41" t="s">
         <v>18</v>
@@ -2499,22 +2478,22 @@
         <v>82</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="E42" t="s">
         <v>43</v>
       </c>
       <c r="F42" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="G42" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
@@ -2528,22 +2507,22 @@
         <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D43" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E43" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F43" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G43" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
@@ -2557,22 +2536,22 @@
         <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C44" t="s">
         <v>64</v>
       </c>
       <c r="D44" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E44" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F44" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G44" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
@@ -2586,22 +2565,22 @@
         <v>82</v>
       </c>
       <c r="B45" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D45" t="s">
         <v>55</v>
       </c>
       <c r="E45" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="F45" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G45" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
@@ -2615,28 +2594,28 @@
         <v>82</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="E46" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="F46" t="s">
         <v>48</v>
       </c>
       <c r="G46" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
@@ -2644,22 +2623,22 @@
         <v>82</v>
       </c>
       <c r="B47" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C47" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D47" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E47" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F47" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G47" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
@@ -2673,22 +2652,22 @@
         <v>82</v>
       </c>
       <c r="B48" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C48" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="D48" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E48" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="F48" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="G48" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
@@ -2702,22 +2681,22 @@
         <v>82</v>
       </c>
       <c r="B49" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="E49" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="F49" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="G49" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
@@ -2731,22 +2710,22 @@
         <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="D50" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E50" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="F50" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G50" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
@@ -2760,28 +2739,28 @@
         <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="C51" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="D51" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="E51" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="F51" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="G51" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
@@ -2789,22 +2768,22 @@
         <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="D52" t="s">
+        <v>132</v>
+      </c>
+      <c r="E52" t="s">
         <v>130</v>
       </c>
-      <c r="E52" t="s">
-        <v>56</v>
-      </c>
       <c r="F52" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="G52" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
@@ -2818,28 +2797,28 @@
         <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="C53" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="D53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E53" t="s">
+        <v>130</v>
+      </c>
+      <c r="F53" t="s">
         <v>131</v>
       </c>
-      <c r="E53" t="s">
-        <v>132</v>
-      </c>
-      <c r="F53" t="s">
-        <v>48</v>
-      </c>
       <c r="G53" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
@@ -2847,22 +2826,22 @@
         <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C54" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="D54" t="s">
+        <v>134</v>
+      </c>
+      <c r="E54" t="s">
         <v>130</v>
       </c>
-      <c r="E54" t="s">
-        <v>56</v>
-      </c>
       <c r="F54" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="G54" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
@@ -2876,19 +2855,19 @@
         <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C55" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D55" t="s">
         <v>135</v>
       </c>
       <c r="E55" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F55" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G55" t="s">
         <v>81</v>
@@ -2905,19 +2884,19 @@
         <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C56" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D56" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E56" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F56" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G56" t="s">
         <v>81</v>
@@ -2934,28 +2913,28 @@
         <v>82</v>
       </c>
       <c r="B57" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C57" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="D57" t="s">
+        <v>138</v>
+      </c>
+      <c r="E57" t="s">
+        <v>56</v>
+      </c>
+      <c r="F57" t="s">
         <v>139</v>
       </c>
-      <c r="E57" t="s">
-        <v>136</v>
-      </c>
-      <c r="F57" t="s">
-        <v>137</v>
-      </c>
       <c r="G57" t="s">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
@@ -2963,19 +2942,19 @@
         <v>82</v>
       </c>
       <c r="B58" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C58" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="D58" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E58" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="F58" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="G58" t="s">
         <v>81</v>
@@ -2989,25 +2968,25 @@
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="B59" t="s">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D59" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="E59" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F59" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G59" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
@@ -3018,54 +2997,54 @@
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D60" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E60" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F60" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="G60" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="B61" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D61" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E61" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F61" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G61" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
@@ -3076,25 +3055,25 @@
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="B62" t="s">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="D62" t="s">
+        <v>97</v>
+      </c>
+      <c r="E62" t="s">
         <v>144</v>
       </c>
-      <c r="E62" t="s">
-        <v>56</v>
-      </c>
       <c r="F62" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="G62" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
@@ -3105,83 +3084,83 @@
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="D63" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="E63" t="s">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="F63" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="G63" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D64" t="s">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="E64" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="F64" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="G64" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B65" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C65" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="D65" t="s">
+        <v>151</v>
+      </c>
+      <c r="E65" t="s">
+        <v>152</v>
+      </c>
+      <c r="F65" t="s">
+        <v>104</v>
+      </c>
+      <c r="G65" t="s">
         <v>153</v>
-      </c>
-      <c r="E65" t="s">
-        <v>85</v>
-      </c>
-      <c r="F65" t="s">
-        <v>86</v>
-      </c>
-      <c r="G65" t="s">
-        <v>87</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
@@ -3192,51 +3171,51 @@
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D66" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="E66" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="F66" t="s">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="G66" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C67" t="s">
         <v>83</v>
       </c>
       <c r="D67" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E67" t="s">
         <v>85</v>
       </c>
       <c r="F67" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="G67" t="s">
         <v>87</v>
@@ -3245,117 +3224,117 @@
         <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C68" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D68" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E68" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="F68" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="G68" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C69" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E69" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="F69" t="s">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="G69" t="s">
-        <v>159</v>
+        <v>17</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B70" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C70" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D70" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E70" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F70" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G70" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B71" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C71" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D71" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E71" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="F71" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="G71" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
@@ -3366,54 +3345,54 @@
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C72" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D72" t="s">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="E72" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="F72" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="G72" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C73" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="D73" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E73" t="s">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="F73" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="G73" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
@@ -3424,54 +3403,54 @@
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C74" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D74" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E74" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F74" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G74" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B75" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C75" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="E75" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="F75" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="G75" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
@@ -3482,83 +3461,83 @@
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B76" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C76" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D76" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E76" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="F76" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="G76" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B77" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C77" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="D77" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E77" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="F77" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="G77" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B78" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C78" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="D78" t="s">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="E78" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F78" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="G78" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
@@ -3569,25 +3548,25 @@
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B79" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C79" t="s">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="D79" t="s">
-        <v>167</v>
+        <v>97</v>
       </c>
       <c r="E79" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="F79" t="s">
-        <v>23</v>
+        <v>145</v>
       </c>
       <c r="G79" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
@@ -3598,167 +3577,167 @@
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B80" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C80" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="D80" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="F80" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="G80" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B81" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E81" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F81" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G81" t="s">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B82" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C82" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="D82" t="s">
-        <v>103</v>
+        <v>158</v>
       </c>
       <c r="E82" t="s">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="F82" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="G82" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B83" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C83" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D83" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="E83" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="F83" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G83" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B84" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C84" t="s">
-        <v>171</v>
+        <v>41</v>
       </c>
       <c r="D84" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E84" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F84" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G84" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B85" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C85" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D85" t="s">
-        <v>168</v>
+        <v>14</v>
       </c>
       <c r="E85" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="F85" t="s">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="G85" t="s">
         <v>81</v>
@@ -3772,25 +3751,25 @@
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B86" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C86" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="D86" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E86" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="F86" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="G86" t="s">
-        <v>173</v>
+        <v>95</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
@@ -3801,109 +3780,109 @@
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B87" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="C87" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="D87" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E87" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="F87" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="G87" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B88" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="C88" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="D88" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="E88" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="F88" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="G88" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B89" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="C89" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="D89" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E89" t="s">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="F89" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
       <c r="G89" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B90" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="C90" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D90" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="E90" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="F90" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="G90" t="s">
         <v>81</v>
@@ -3917,54 +3896,54 @@
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D91" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E91" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F91" t="s">
-        <v>119</v>
+        <v>175</v>
       </c>
       <c r="G91" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B92" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D92" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E92" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="F92" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="G92" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
@@ -3975,25 +3954,25 @@
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B93" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D93" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E93" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F93" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G93" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
@@ -4004,83 +3983,83 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="C94" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D94" t="s">
-        <v>14</v>
+        <v>174</v>
       </c>
       <c r="E94" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="F94" t="s">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="G94" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B95" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="C95" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D95" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E95" t="s">
         <v>69</v>
       </c>
       <c r="F95" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G95" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B96" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="C96" t="s">
-        <v>134</v>
+        <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="E96" t="s">
-        <v>136</v>
+        <v>71</v>
       </c>
       <c r="F96" t="s">
-        <v>181</v>
+        <v>16</v>
       </c>
       <c r="G96" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
@@ -4091,115 +4070,115 @@
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B97" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="C97" t="s">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="D97" t="s">
-        <v>182</v>
+        <v>62</v>
       </c>
       <c r="E97" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="F97" t="s">
-        <v>181</v>
+        <v>23</v>
       </c>
       <c r="G97" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B98" t="s">
-        <v>133</v>
+        <v>26</v>
       </c>
       <c r="C98" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D98" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="E98" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F98" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G98" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B99" t="s">
-        <v>133</v>
+        <v>26</v>
       </c>
       <c r="C99" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D99" t="s">
-        <v>179</v>
+        <v>68</v>
       </c>
       <c r="E99" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F99" t="s">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="G99" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C100" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="D100" t="s">
-        <v>186</v>
+        <v>122</v>
       </c>
       <c r="E100" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="F100" t="s">
-        <v>187</v>
+        <v>104</v>
       </c>
       <c r="G100" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="H100" t="s">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="I100" t="s">
         <v>32</v>
@@ -4207,45 +4186,45 @@
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B101" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C101" t="s">
         <v>13</v>
       </c>
       <c r="D101" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="E101" t="s">
         <v>71</v>
       </c>
       <c r="F101" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="G101" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C102" t="s">
         <v>20</v>
       </c>
       <c r="D102" t="s">
-        <v>188</v>
+        <v>96</v>
       </c>
       <c r="E102" t="s">
         <v>22</v>
@@ -4254,68 +4233,68 @@
         <v>23</v>
       </c>
       <c r="G102" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C103" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D103" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E103" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F103" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="G103" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B104" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C104" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="D104" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="E104" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F104" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="G104" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="H104" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="I104" t="s">
         <v>19</v>
@@ -4323,57 +4302,57 @@
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C105" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D105" t="s">
-        <v>62</v>
+        <v>182</v>
       </c>
       <c r="E105" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F105" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G105" t="s">
-        <v>70</v>
+        <v>183</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B106" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C106" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="D106" t="s">
-        <v>186</v>
+        <v>122</v>
       </c>
       <c r="E106" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="F106" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="G106" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="H106" t="s">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="I106" t="s">
         <v>32</v>
@@ -4381,22 +4360,22 @@
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B107" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C107" t="s">
         <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="E107" t="s">
         <v>71</v>
       </c>
       <c r="F107" t="s">
-        <v>189</v>
+        <v>60</v>
       </c>
       <c r="G107" t="s">
         <v>61</v>
@@ -4410,16 +4389,16 @@
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B108" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C108" t="s">
         <v>20</v>
       </c>
       <c r="D108" t="s">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="E108" t="s">
         <v>22</v>
@@ -4428,36 +4407,36 @@
         <v>23</v>
       </c>
       <c r="G108" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
       </c>
       <c r="I108" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B109" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C109" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D109" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="E109" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F109" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="G109" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
@@ -4468,54 +4447,54 @@
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B110" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C110" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D110" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="E110" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F110" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G110" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H110" t="s">
         <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
+        <v>173</v>
+      </c>
+      <c r="B111" t="s">
+        <v>54</v>
+      </c>
+      <c r="C111" t="s">
+        <v>27</v>
+      </c>
+      <c r="D111" t="s">
         <v>185</v>
       </c>
-      <c r="B111" t="s">
-        <v>40</v>
-      </c>
-      <c r="C111" t="s">
-        <v>13</v>
-      </c>
-      <c r="D111" t="s">
-        <v>174</v>
-      </c>
       <c r="E111" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="F111" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G111" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
@@ -4526,141 +4505,141 @@
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B112" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C112" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D112" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="E112" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="F112" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G112" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B113" t="s">
         <v>54</v>
       </c>
       <c r="C113" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="D113" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="E113" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="F113" t="s">
-        <v>187</v>
+        <v>60</v>
       </c>
       <c r="G113" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B114" t="s">
         <v>54</v>
       </c>
       <c r="C114" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="E114" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F114" t="s">
-        <v>60</v>
+        <v>188</v>
       </c>
       <c r="G114" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="H114" t="s">
         <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B115" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C115" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="D115" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E115" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F115" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="G115" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B116" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C116" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="D116" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="E116" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F116" t="s">
-        <v>189</v>
+        <v>60</v>
       </c>
       <c r="G116" t="s">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
@@ -4671,112 +4650,112 @@
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B117" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C117" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D117" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="E117" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F117" t="s">
-        <v>193</v>
+        <v>48</v>
       </c>
       <c r="G117" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B118" t="s">
         <v>65</v>
       </c>
       <c r="C118" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="D118" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="E118" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="F118" t="s">
-        <v>187</v>
+        <v>44</v>
       </c>
       <c r="G118" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B119" t="s">
         <v>65</v>
       </c>
       <c r="C119" t="s">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="D119" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E119" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="F119" t="s">
         <v>60</v>
       </c>
       <c r="G119" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
       </c>
       <c r="I119" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B120" t="s">
         <v>65</v>
       </c>
       <c r="C120" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D120" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E120" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F120" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G120" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
@@ -4787,22 +4766,22 @@
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B121" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C121" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="D121" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="E121" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="F121" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="G121" t="s">
         <v>61</v>
@@ -4816,25 +4795,25 @@
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B122" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C122" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D122" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E122" t="s">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="F122" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G122" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
@@ -4845,25 +4824,25 @@
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B123" t="s">
         <v>72</v>
       </c>
       <c r="C123" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="D123" t="s">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="E123" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F123" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G123" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
@@ -4874,22 +4853,22 @@
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B124" t="s">
         <v>72</v>
       </c>
       <c r="C124" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D124" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E124" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F124" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G124" t="s">
         <v>81</v>
@@ -4903,25 +4882,25 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B125" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C125" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="D125" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="E125" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F125" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="G125" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
@@ -4932,54 +4911,54 @@
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B126" t="s">
         <v>78</v>
       </c>
       <c r="C126" t="s">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="D126" t="s">
-        <v>130</v>
+        <v>193</v>
       </c>
       <c r="E126" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F126" t="s">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="G126" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
       </c>
       <c r="I126" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B127" t="s">
         <v>78</v>
       </c>
       <c r="C127" t="s">
-        <v>197</v>
+        <v>41</v>
       </c>
       <c r="D127" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E127" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F127" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="G127" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
@@ -4990,170 +4969,170 @@
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B128" t="s">
         <v>78</v>
       </c>
       <c r="C128" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D128" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="E128" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F128" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G128" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B129" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="C129" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="D129" t="s">
-        <v>177</v>
+        <v>124</v>
       </c>
       <c r="E129" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F129" t="s">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="G129" t="s">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B130" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C130" t="s">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="D130" t="s">
-        <v>130</v>
+        <v>193</v>
       </c>
       <c r="E130" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F130" t="s">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G130" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B131" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C131" t="s">
-        <v>197</v>
+        <v>41</v>
       </c>
       <c r="D131" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E131" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F131" t="s">
-        <v>160</v>
+        <v>44</v>
       </c>
       <c r="G131" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H131" t="s">
         <v>18</v>
       </c>
       <c r="I131" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B132" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C132" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D132" t="s">
-        <v>200</v>
+        <v>124</v>
       </c>
       <c r="E132" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F132" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="G132" t="s">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B133" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="D133" t="s">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="E133" t="s">
-        <v>56</v>
+        <v>195</v>
       </c>
       <c r="F133" t="s">
-        <v>60</v>
+        <v>196</v>
       </c>
       <c r="G133" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
@@ -5164,22 +5143,22 @@
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B134" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C134" t="s">
-        <v>197</v>
+        <v>41</v>
       </c>
       <c r="D134" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="E134" t="s">
-        <v>202</v>
+        <v>69</v>
       </c>
       <c r="F134" t="s">
-        <v>203</v>
+        <v>44</v>
       </c>
       <c r="G134" t="s">
         <v>81</v>
@@ -5193,22 +5172,22 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B135" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C135" t="s">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="D135" t="s">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="E135" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="F135" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="G135" t="s">
         <v>81</v>
@@ -5222,22 +5201,22 @@
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B136" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C136" t="s">
-        <v>197</v>
+        <v>41</v>
       </c>
       <c r="D136" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="E136" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="F136" t="s">
-        <v>203</v>
+        <v>44</v>
       </c>
       <c r="G136" t="s">
         <v>81</v>
@@ -5251,22 +5230,22 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B137" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="C137" t="s">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="D137" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="E137" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="F137" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="G137" t="s">
         <v>81</v>
@@ -5280,22 +5259,22 @@
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B138" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C138" t="s">
-        <v>197</v>
+        <v>41</v>
       </c>
       <c r="D138" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="E138" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="F138" t="s">
-        <v>203</v>
+        <v>44</v>
       </c>
       <c r="G138" t="s">
         <v>81</v>
@@ -5309,22 +5288,22 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B139" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C139" t="s">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="D139" t="s">
-        <v>205</v>
+        <v>124</v>
       </c>
       <c r="E139" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="F139" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="G139" t="s">
         <v>81</v>
@@ -5338,25 +5317,25 @@
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="B140" t="s">
-        <v>206</v>
+        <v>12</v>
       </c>
       <c r="C140" t="s">
-        <v>197</v>
+        <v>41</v>
       </c>
       <c r="D140" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="E140" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="F140" t="s">
-        <v>203</v>
+        <v>44</v>
       </c>
       <c r="G140" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H140" t="s">
         <v>18</v>
@@ -5367,51 +5346,51 @@
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B141" t="s">
         <v>12</v>
       </c>
       <c r="C141" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D141" t="s">
-        <v>68</v>
+        <v>162</v>
       </c>
       <c r="E141" t="s">
-        <v>69</v>
+        <v>201</v>
       </c>
       <c r="F141" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="G141" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="H141" t="s">
         <v>18</v>
       </c>
       <c r="I141" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B142" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C142" t="s">
-        <v>13</v>
+        <v>128</v>
       </c>
       <c r="D142" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="E142" t="s">
-        <v>208</v>
+        <v>130</v>
       </c>
       <c r="F142" t="s">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c r="G142" t="s">
         <v>17</v>
@@ -5425,22 +5404,22 @@
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B143" t="s">
         <v>24</v>
       </c>
       <c r="C143" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D143" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E143" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F143" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G143" t="s">
         <v>17</v>
@@ -5454,22 +5433,22 @@
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B144" t="s">
         <v>24</v>
       </c>
       <c r="C144" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D144" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E144" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F144" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G144" t="s">
         <v>17</v>
@@ -5483,22 +5462,22 @@
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B145" t="s">
         <v>24</v>
       </c>
       <c r="C145" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D145" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E145" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F145" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G145" t="s">
         <v>17</v>
@@ -5512,22 +5491,22 @@
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B146" t="s">
         <v>24</v>
       </c>
       <c r="C146" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D146" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E146" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F146" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G146" t="s">
         <v>17</v>
@@ -5541,22 +5520,22 @@
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B147" t="s">
         <v>24</v>
       </c>
       <c r="C147" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D147" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E147" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F147" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G147" t="s">
         <v>17</v>
@@ -5570,22 +5549,22 @@
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B148" t="s">
         <v>24</v>
       </c>
       <c r="C148" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D148" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E148" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F148" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G148" t="s">
         <v>17</v>
@@ -5599,22 +5578,22 @@
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B149" t="s">
         <v>24</v>
       </c>
       <c r="C149" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D149" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E149" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F149" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G149" t="s">
         <v>17</v>
@@ -5628,22 +5607,22 @@
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B150" t="s">
         <v>24</v>
       </c>
       <c r="C150" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D150" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E150" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F150" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G150" t="s">
         <v>17</v>
@@ -5657,152 +5636,152 @@
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B151" t="s">
         <v>24</v>
       </c>
       <c r="C151" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="D151" t="s">
-        <v>217</v>
+        <v>159</v>
       </c>
       <c r="E151" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="F151" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="G151" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H151" t="s">
         <v>18</v>
       </c>
       <c r="I151" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B152" t="s">
         <v>24</v>
       </c>
       <c r="C152" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D152" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E152" t="s">
-        <v>69</v>
+        <v>201</v>
       </c>
       <c r="F152" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="G152" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="H152" t="s">
         <v>18</v>
       </c>
       <c r="I152" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B153" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C153" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="D153" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="E153" t="s">
-        <v>208</v>
+        <v>85</v>
       </c>
       <c r="F153" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G153" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="H153" t="s">
         <v>18</v>
       </c>
       <c r="I153" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B154" t="s">
         <v>26</v>
       </c>
       <c r="C154" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D154" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E154" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F154" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G154" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H154" t="s">
         <v>18</v>
       </c>
       <c r="I154" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B155" t="s">
         <v>26</v>
       </c>
       <c r="C155" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="D155" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E155" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F155" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="G155" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="H155" t="s">
         <v>18</v>
       </c>
       <c r="I155" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B156" t="s">
         <v>26</v>
@@ -5811,7 +5790,7 @@
         <v>41</v>
       </c>
       <c r="D156" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E156" t="s">
         <v>69</v>
@@ -5820,7 +5799,7 @@
         <v>44</v>
       </c>
       <c r="G156" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H156" t="s">
         <v>18</v>
@@ -5831,138 +5810,138 @@
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B157" t="s">
         <v>26</v>
       </c>
       <c r="C157" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D157" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="E157" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="F157" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="G157" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="H157" t="s">
         <v>18</v>
       </c>
       <c r="I157" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B158" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C158" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D158" t="s">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="E158" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="F158" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="G158" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
       </c>
       <c r="I158" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B159" t="s">
         <v>40</v>
       </c>
       <c r="C159" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D159" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E159" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F159" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G159" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H159" t="s">
         <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B160" t="s">
         <v>40</v>
       </c>
       <c r="C160" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="D160" t="s">
-        <v>58</v>
+        <v>212</v>
       </c>
       <c r="E160" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F160" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="G160" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B161" t="s">
         <v>40</v>
       </c>
       <c r="C161" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D161" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="E161" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="F161" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G161" t="s">
         <v>19</v>
@@ -5976,80 +5955,80 @@
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B162" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C162" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="D162" t="s">
-        <v>218</v>
+        <v>58</v>
       </c>
       <c r="E162" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="F162" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="G162" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="H162" t="s">
         <v>18</v>
       </c>
       <c r="I162" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B163" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C163" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="D163" t="s">
-        <v>219</v>
+        <v>42</v>
       </c>
       <c r="E163" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="F163" t="s">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="G163" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="H163" t="s">
         <v>18</v>
       </c>
       <c r="I163" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B164" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C164" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="D164" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="E164" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F164" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G164" t="s">
         <v>19</v>
@@ -6063,109 +6042,109 @@
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B165" t="s">
         <v>54</v>
       </c>
       <c r="C165" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="D165" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E165" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F165" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="G165" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="H165" t="s">
         <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B166" t="s">
         <v>54</v>
       </c>
       <c r="C166" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="D166" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E166" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="F166" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="G166" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="H166" t="s">
         <v>18</v>
       </c>
       <c r="I166" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B167" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C167" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D167" t="s">
-        <v>222</v>
+        <v>162</v>
       </c>
       <c r="E167" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="F167" t="s">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="G167" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="H167" t="s">
         <v>18</v>
       </c>
       <c r="I167" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B168" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C168" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="D168" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="E168" t="s">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="F168" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G168" t="s">
         <v>19</v>
@@ -6179,45 +6158,45 @@
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B169" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C169" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D169" t="s">
-        <v>220</v>
+        <v>42</v>
       </c>
       <c r="E169" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F169" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="G169" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="H169" t="s">
         <v>18</v>
       </c>
       <c r="I169" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B170" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C170" t="s">
         <v>20</v>
       </c>
       <c r="D170" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -6226,7 +6205,7 @@
         <v>23</v>
       </c>
       <c r="G170" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H170" t="s">
         <v>18</v>
@@ -6237,25 +6216,25 @@
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B171" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C171" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D171" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E171" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F171" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G171" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H171" t="s">
         <v>18</v>
@@ -6266,16 +6245,16 @@
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B172" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C172" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D172" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="E172" t="s">
         <v>56</v>
@@ -6295,22 +6274,22 @@
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B173" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C173" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D173" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E173" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="F173" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G173" t="s">
         <v>19</v>
@@ -6324,25 +6303,25 @@
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B174" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C174" t="s">
-        <v>224</v>
+        <v>13</v>
       </c>
       <c r="D174" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="E174" t="s">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c r="F174" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="G174" t="s">
-        <v>226</v>
+        <v>61</v>
       </c>
       <c r="H174" t="s">
         <v>18</v>
@@ -6353,80 +6332,80 @@
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B175" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C175" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D175" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E175" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="F175" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="G175" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="H175" t="s">
         <v>18</v>
       </c>
       <c r="I175" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="15">
       <c r="A176" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B176" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C176" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D176" t="s">
-        <v>130</v>
+        <v>216</v>
       </c>
       <c r="E176" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="F176" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="G176" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="H176" t="s">
         <v>18</v>
       </c>
       <c r="I176" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15">
       <c r="A177" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B177" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C177" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D177" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E177" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F177" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="G177" t="s">
         <v>19</v>
@@ -6440,22 +6419,22 @@
     </row>
     <row r="178" spans="1:9" ht="15">
       <c r="A178" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B178" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C178" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D178" t="s">
-        <v>227</v>
+        <v>42</v>
       </c>
       <c r="E178" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="F178" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G178" t="s">
         <v>19</v>
@@ -6469,74 +6448,74 @@
     </row>
     <row r="179" spans="1:9" ht="15">
       <c r="A179" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B179" t="s">
         <v>78</v>
       </c>
       <c r="C179" t="s">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="D179" t="s">
-        <v>172</v>
+        <v>216</v>
       </c>
       <c r="E179" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="F179" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="G179" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="H179" t="s">
         <v>18</v>
       </c>
       <c r="I179" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="15">
       <c r="A180" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B180" t="s">
         <v>78</v>
       </c>
       <c r="C180" t="s">
-        <v>224</v>
+        <v>88</v>
       </c>
       <c r="D180" t="s">
-        <v>205</v>
+        <v>124</v>
       </c>
       <c r="E180" t="s">
-        <v>225</v>
+        <v>56</v>
       </c>
       <c r="F180" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="G180" t="s">
-        <v>226</v>
+        <v>19</v>
       </c>
       <c r="H180" t="s">
         <v>18</v>
       </c>
       <c r="I180" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="15">
       <c r="A181" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B181" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="C181" t="s">
         <v>41</v>
       </c>
       <c r="D181" t="s">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="E181" t="s">
         <v>69</v>
@@ -6545,7 +6524,7 @@
         <v>44</v>
       </c>
       <c r="G181" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="H181" t="s">
         <v>18</v>
@@ -6556,16 +6535,16 @@
     </row>
     <row r="182" spans="1:9" ht="15">
       <c r="A182" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B182" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="C182" t="s">
         <v>20</v>
       </c>
       <c r="D182" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="E182" t="s">
         <v>22</v>
@@ -6585,22 +6564,22 @@
     </row>
     <row r="183" spans="1:9" ht="15">
       <c r="A183" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B183" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="C183" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D183" t="s">
-        <v>42</v>
+        <v>219</v>
       </c>
       <c r="E183" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F183" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G183" t="s">
         <v>19</v>
@@ -6614,25 +6593,25 @@
     </row>
     <row r="184" spans="1:9" ht="15">
       <c r="A184" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B184" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C184" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D184" t="s">
-        <v>229</v>
+        <v>42</v>
       </c>
       <c r="E184" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="F184" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G184" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="H184" t="s">
         <v>18</v>
@@ -6643,22 +6622,22 @@
     </row>
     <row r="185" spans="1:9" ht="15">
       <c r="A185" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B185" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C185" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D185" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E185" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F185" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G185" t="s">
         <v>19</v>
@@ -6672,30 +6651,59 @@
     </row>
     <row r="186" spans="1:9" ht="15">
       <c r="A186" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B186" t="s">
-        <v>204</v>
+        <v>141</v>
       </c>
       <c r="C186" t="s">
         <v>41</v>
       </c>
       <c r="D186" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="E186" t="s">
-        <v>69</v>
+        <v>221</v>
       </c>
       <c r="F186" t="s">
         <v>44</v>
       </c>
       <c r="G186" t="s">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="H186" t="s">
         <v>18</v>
       </c>
       <c r="I186" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="15">
+      <c r="A187" t="s">
+        <v>200</v>
+      </c>
+      <c r="B187" t="s">
+        <v>197</v>
+      </c>
+      <c r="C187" t="s">
+        <v>41</v>
+      </c>
+      <c r="D187" t="s">
+        <v>198</v>
+      </c>
+      <c r="E187" t="s">
+        <v>69</v>
+      </c>
+      <c r="F187" t="s">
+        <v>44</v>
+      </c>
+      <c r="G187" t="s">
+        <v>81</v>
+      </c>
+      <c r="H187" t="s">
+        <v>18</v>
+      </c>
+      <c r="I187" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6707,7 +6715,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d64db6af-27ee-431e-ab28-5ffac21b7e1d}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a41ac08b-8bbc-4a55-b3c2-f410ff95f184}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6727,16 +6735,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6753,16 +6761,16 @@
     </row>
     <row r="2" spans="1:9" ht="15">
       <c r="A2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E2" t="s">
         <v>56</v>
@@ -6782,16 +6790,16 @@
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E3" t="s">
         <v>56</v>
@@ -6811,16 +6819,16 @@
     </row>
     <row r="4" spans="1:9" ht="15">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E4" t="s">
         <v>56</v>
@@ -6840,16 +6848,16 @@
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="A5" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E5" t="s">
         <v>56</v>
@@ -6875,8 +6883,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{9d6e7931-2515-4e86-8066-c8fc5612287e}">
-  <dimension ref="A1:F40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8ca045b7-9dd9-45dd-9d89-2cfebf7ba353}">
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -6892,13 +6900,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6912,13 +6920,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E2" t="s">
         <v>70</v>
@@ -6932,16 +6940,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -6952,16 +6960,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E4" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -6972,16 +6980,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E5" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6992,16 +7000,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" t="s">
-        <v>248</v>
-      </c>
       <c r="E6" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -7012,16 +7020,16 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E7" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -7032,16 +7040,16 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E8" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -7052,13 +7060,13 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E9" t="s">
         <v>70</v>
@@ -7072,16 +7080,16 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C10" t="s">
         <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -7092,16 +7100,16 @@
         <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E11" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -7112,13 +7120,13 @@
         <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E12" t="s">
         <v>36</v>
@@ -7132,16 +7140,16 @@
         <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E13" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -7152,16 +7160,16 @@
         <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E14" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -7169,19 +7177,19 @@
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="A15" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C15" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D15" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E15" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -7189,19 +7197,19 @@
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B16" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E16" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -7209,19 +7217,19 @@
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B17" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C17" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D17" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E17" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -7229,19 +7237,19 @@
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C18" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D18" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E18" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -7249,16 +7257,16 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D19" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E19" t="s">
         <v>53</v>
@@ -7269,19 +7277,19 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s">
+        <v>247</v>
+      </c>
+      <c r="C20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" t="s">
+        <v>245</v>
+      </c>
+      <c r="E20" t="s">
         <v>254</v>
-      </c>
-      <c r="C20" t="s">
-        <v>96</v>
-      </c>
-      <c r="D20" t="s">
-        <v>252</v>
-      </c>
-      <c r="E20" t="s">
-        <v>261</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -7289,19 +7297,19 @@
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C21" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D21" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E21" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -7309,19 +7317,19 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B22" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C22" t="s">
         <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E22" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -7329,16 +7337,16 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B23" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C23" t="s">
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -7349,19 +7357,19 @@
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B24" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -7369,19 +7377,19 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B25" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C25" t="s">
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -7389,19 +7397,19 @@
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E26" t="s">
         <v>252</v>
-      </c>
-      <c r="E26" t="s">
-        <v>19</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -7409,39 +7417,39 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B27" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="D27" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="C28" t="s">
         <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
@@ -7449,19 +7457,19 @@
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B29" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="C29" t="s">
         <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -7469,19 +7477,19 @@
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B30" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="C30" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
@@ -7489,19 +7497,19 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="B31" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>143</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -7509,16 +7517,16 @@
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="C32" t="s">
         <v>41</v>
       </c>
       <c r="D32" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
@@ -7529,16 +7537,16 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="B33" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -7549,16 +7557,16 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C34" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -7569,16 +7577,16 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B35" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
@@ -7589,16 +7597,16 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B36" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C36" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
@@ -7609,16 +7617,16 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B37" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -7629,16 +7637,16 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B38" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="D38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
@@ -7649,16 +7657,16 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B39" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C39" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -7669,21 +7677,101 @@
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B40" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="C40" t="s">
         <v>41</v>
       </c>
       <c r="D40" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
       </c>
       <c r="F40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15">
+      <c r="A41" t="s">
+        <v>200</v>
+      </c>
+      <c r="B41" t="s">
+        <v>250</v>
+      </c>
+      <c r="C41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" t="s">
+        <v>255</v>
+      </c>
+      <c r="E41" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15">
+      <c r="A42" t="s">
+        <v>200</v>
+      </c>
+      <c r="B42" t="s">
+        <v>250</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" t="s">
+        <v>235</v>
+      </c>
+      <c r="E42" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15">
+      <c r="A43" t="s">
+        <v>200</v>
+      </c>
+      <c r="B43" t="s">
+        <v>257</v>
+      </c>
+      <c r="C43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" t="s">
+        <v>255</v>
+      </c>
+      <c r="E43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15">
+      <c r="A44" t="s">
+        <v>200</v>
+      </c>
+      <c r="B44" t="s">
+        <v>258</v>
+      </c>
+      <c r="C44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" t="s">
+        <v>255</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
         <v>18</v>
       </c>
     </row>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="279">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -60,15 +60,126 @@
     <t>23.02.2026</t>
   </si>
   <si>
+    <t>3, 09:40-10:25</t>
+  </si>
+  <si>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>3FA</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t>prF3</t>
+  </si>
+  <si>
+    <t>Sobczak Anna</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Dodatkowo płatne</t>
+  </si>
+  <si>
+    <t>5, 11:25-12:10</t>
+  </si>
+  <si>
+    <t>3K</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Ulanowska Magdalena</t>
+  </si>
+  <si>
+    <t>6, 12:25-13:10</t>
+  </si>
+  <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>Zajęcia z wychowawcą</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Socha Dariusz</t>
+  </si>
+  <si>
+    <t>7, 13:15-14:00</t>
+  </si>
+  <si>
+    <t>2S</t>
+  </si>
+  <si>
+    <t>Zajęcia biblioteczne</t>
+  </si>
+  <si>
+    <t>bib</t>
+  </si>
+  <si>
+    <t>Nowak Damiana</t>
+  </si>
+  <si>
+    <t>Bezpłatne</t>
+  </si>
+  <si>
+    <t>8, 14:05-14:50</t>
+  </si>
+  <si>
+    <t>3S</t>
+  </si>
+  <si>
+    <t>Biologia</t>
+  </si>
+  <si>
+    <t>Sałdyka Karolina</t>
+  </si>
+  <si>
+    <t>4, 10:35-11:20</t>
+  </si>
+  <si>
+    <t>Smirnow-Zechman Eleonora</t>
+  </si>
+  <si>
+    <t>1CA</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Rejno Julita</t>
+  </si>
+  <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>Biznes i zarządzanie</t>
+  </si>
+  <si>
+    <t>Najwer Maciej</t>
+  </si>
+  <si>
     <t>1, 08:00-08:45</t>
   </si>
   <si>
     <t>Stępień Krystyna</t>
   </si>
   <si>
-    <t>2CB</t>
-  </si>
-  <si>
     <t>Technika w produkcji cukierniczej</t>
   </si>
   <si>
@@ -78,12 +189,42 @@
     <t>Uczniowie przychodzą później</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
+    <t>2, 08:50-09:35</t>
+  </si>
+  <si>
+    <t>1CA|JA1</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
+    <t>1CA|JA2</t>
+  </si>
+  <si>
+    <t>3CA</t>
+  </si>
+  <si>
+    <t>Małecka Barbara</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Kończyńska Małgorzata</t>
+  </si>
+  <si>
+    <t>Technologie produkcji cukierniczej</t>
+  </si>
+  <si>
     <t>Taszycka Magdalena</t>
   </si>
   <si>
@@ -96,84 +237,12 @@
     <t>38</t>
   </si>
   <si>
-    <t>2, 08:50-09:35</t>
-  </si>
-  <si>
     <t>1TFB|JA1</t>
   </si>
   <si>
-    <t>3, 09:40-10:25</t>
-  </si>
-  <si>
-    <t>Hudziec Agnieszka</t>
-  </si>
-  <si>
-    <t>3FA</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t>prF3</t>
-  </si>
-  <si>
-    <t>Sobczak Anna</t>
-  </si>
-  <si>
-    <t>Dodatkowo płatne</t>
-  </si>
-  <si>
-    <t>1CA|JA1</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Karczmarz Aleksandra</t>
-  </si>
-  <si>
-    <t>1CA|JA2</t>
-  </si>
-  <si>
-    <t>Bezpłatne</t>
-  </si>
-  <si>
     <t>2TFB|JA2</t>
   </si>
   <si>
-    <t>4, 10:35-11:20</t>
-  </si>
-  <si>
-    <t>Smirnow-Zechman Eleonora</t>
-  </si>
-  <si>
-    <t>1CA</t>
-  </si>
-  <si>
-    <t>Zajęcia z wychowawcą</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Rejno Julita</t>
-  </si>
-  <si>
-    <t>3CA</t>
-  </si>
-  <si>
-    <t>Biologia</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Małecka Barbara</t>
-  </si>
-  <si>
     <t>3TFA|JA2</t>
   </si>
   <si>
@@ -186,30 +255,6 @@
     <t>Fiodorów Małgorzata</t>
   </si>
   <si>
-    <t>5, 11:25-12:10</t>
-  </si>
-  <si>
-    <t>3K</t>
-  </si>
-  <si>
-    <t>Język polski</t>
-  </si>
-  <si>
-    <t>Ulanowska Magdalena</t>
-  </si>
-  <si>
-    <t>1FB</t>
-  </si>
-  <si>
-    <t>Danielewski Paweł</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Kończyńska Małgorzata</t>
-  </si>
-  <si>
     <t>1TFB|JA2</t>
   </si>
   <si>
@@ -219,54 +264,9 @@
     <t>Cieśla Marcin</t>
   </si>
   <si>
-    <t>6, 12:25-13:10</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>Socha Dariusz</t>
-  </si>
-  <si>
-    <t>2TFA</t>
-  </si>
-  <si>
-    <t>Biznes i zarządzanie</t>
-  </si>
-  <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
-    <t>Technologie produkcji cukierniczej</t>
-  </si>
-  <si>
-    <t>7, 13:15-14:00</t>
-  </si>
-  <si>
-    <t>2S</t>
-  </si>
-  <si>
-    <t>Zajęcia biblioteczne</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>Nowak Damiana</t>
-  </si>
-  <si>
     <t>1TH|JA2</t>
   </si>
   <si>
-    <t>8, 14:05-14:50</t>
-  </si>
-  <si>
-    <t>3S</t>
-  </si>
-  <si>
-    <t>Sałdyka Karolina</t>
-  </si>
-  <si>
     <t>Uczniowie zwolnieni do domu</t>
   </si>
   <si>
@@ -288,6 +288,45 @@
     <t>Nestoruk Lidia</t>
   </si>
   <si>
+    <t>2WA</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Pietrycha Małgorzata</t>
+  </si>
+  <si>
+    <t>3FB|DZ</t>
+  </si>
+  <si>
+    <t>sg4</t>
+  </si>
+  <si>
+    <t>Dalach Sławomir</t>
+  </si>
+  <si>
+    <t>3M|JN2</t>
+  </si>
+  <si>
+    <t>sg1</t>
+  </si>
+  <si>
+    <t>Wójcik Kamil</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Okienko dla uczniów</t>
+  </si>
+  <si>
+    <t>3S|DZ</t>
+  </si>
+  <si>
+    <t>aq1</t>
+  </si>
+  <si>
     <t>Filipek Anna</t>
   </si>
   <si>
@@ -297,9 +336,108 @@
     <t>p. Rejno, zajęcia z wychowawcą za środę 25.02</t>
   </si>
   <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>Język niemiecki zawodowy</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>9, 14:55-15:40</t>
+  </si>
+  <si>
+    <t>10, 15:45-16:30</t>
+  </si>
+  <si>
+    <t>3WA</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Derezińska Katarzyna</t>
+  </si>
+  <si>
+    <t>11, 16:35-17:20</t>
+  </si>
+  <si>
     <t>Bokuniewicz Sylwia</t>
   </si>
   <si>
+    <t>3TH|JA1</t>
+  </si>
+  <si>
+    <t>3TH|JA2</t>
+  </si>
+  <si>
+    <t>4TFB</t>
+  </si>
+  <si>
+    <t>Kosin Anna</t>
+  </si>
+  <si>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>Jastrzębska-Majtyka Agnieszka</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>1TFB</t>
+  </si>
+  <si>
+    <t>Chemia</t>
+  </si>
+  <si>
+    <t>1TH</t>
+  </si>
+  <si>
+    <t>Towar jako przedmiot handlu</t>
+  </si>
+  <si>
+    <t>Paleczny Maciej</t>
+  </si>
+  <si>
+    <t>3TFB|relu</t>
+  </si>
+  <si>
+    <t>Religia</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>3FB|relu</t>
+  </si>
+  <si>
+    <t>3CA|relu</t>
+  </si>
+  <si>
+    <t>3FA|relu</t>
+  </si>
+  <si>
+    <t>3TFA|relu</t>
+  </si>
+  <si>
+    <t>4TFB|relu</t>
+  </si>
+  <si>
     <t>Świerzewicz Katarzyna</t>
   </si>
   <si>
@@ -312,147 +450,87 @@
     <t>Mocarski Arkadiusz</t>
   </si>
   <si>
-    <t>3TH|JA1</t>
-  </si>
-  <si>
-    <t>3TH|JA2</t>
-  </si>
-  <si>
-    <t>3M|JN2</t>
-  </si>
-  <si>
-    <t>sg1</t>
-  </si>
-  <si>
-    <t>Wójcik Kamil</t>
-  </si>
-  <si>
-    <t>4TFB</t>
-  </si>
-  <si>
-    <t>Kosin Anna</t>
-  </si>
-  <si>
-    <t>2WA</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Pietrycha Małgorzata</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Okienko dla uczniów</t>
-  </si>
-  <si>
-    <t>3M</t>
-  </si>
-  <si>
-    <t>Język niemiecki zawodowy</t>
-  </si>
-  <si>
-    <t>4TH</t>
-  </si>
-  <si>
-    <t>Jastrzębska-Majtyka Agnieszka</t>
-  </si>
-  <si>
-    <t>3FB|DZ</t>
-  </si>
-  <si>
-    <t>sg4</t>
-  </si>
-  <si>
-    <t>Dalach Sławomir</t>
-  </si>
-  <si>
-    <t>3S|DZ</t>
-  </si>
-  <si>
-    <t>aq1</t>
-  </si>
-  <si>
-    <t>Historia</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Kopij Marcin</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>1TFB</t>
-  </si>
-  <si>
-    <t>Chemia</t>
-  </si>
-  <si>
-    <t>4B</t>
-  </si>
-  <si>
-    <t>1TH</t>
-  </si>
-  <si>
-    <t>Towar jako przedmiot handlu</t>
-  </si>
-  <si>
-    <t>9, 14:55-15:40</t>
-  </si>
-  <si>
-    <t>Paleczny Maciej</t>
-  </si>
-  <si>
-    <t>3TFB|relu</t>
-  </si>
-  <si>
-    <t>Religia</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>3FB|relu</t>
-  </si>
-  <si>
-    <t>3CA|relu</t>
-  </si>
-  <si>
-    <t>3FA|relu</t>
-  </si>
-  <si>
-    <t>3TFA|relu</t>
-  </si>
-  <si>
-    <t>4TFB|relu</t>
-  </si>
-  <si>
-    <t>10, 15:45-16:30</t>
-  </si>
-  <si>
-    <t>3WA</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>Derezińska Katarzyna</t>
-  </si>
-  <si>
-    <t>11, 16:35-17:20</t>
+    <t>Wakat3 edukacja zdrow.</t>
+  </si>
+  <si>
+    <t>3CA|edu</t>
+  </si>
+  <si>
+    <t>Edukacja zdrowotna</t>
+  </si>
+  <si>
+    <t>3FA|edu</t>
+  </si>
+  <si>
+    <t>3M|edu</t>
+  </si>
+  <si>
+    <t>3TFA|edu</t>
   </si>
   <si>
     <t>25.02.2026</t>
   </si>
   <si>
+    <t>2CA|DZ</t>
+  </si>
+  <si>
+    <t>2WA|CH</t>
+  </si>
+  <si>
+    <t>2FA</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Biezmienow Małgorzata</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>2FC</t>
+  </si>
+  <si>
+    <t>2TFB</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>Krzemińska Beata</t>
+  </si>
+  <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>Podstawy fryzjerstwa</t>
+  </si>
+  <si>
+    <t>Leńczowska Iwona</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>Edukacja obywatelska</t>
+  </si>
+  <si>
+    <t>2TH|relu</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>2FB|relu</t>
+  </si>
+  <si>
+    <t>2CA|relu</t>
+  </si>
+  <si>
     <t>Skarupa Agnieszka</t>
   </si>
   <si>
@@ -462,85 +540,43 @@
     <t>37</t>
   </si>
   <si>
-    <t>2CA|DZ</t>
-  </si>
-  <si>
-    <t>2FA</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>Biezmienow Małgorzata</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>2FB</t>
-  </si>
-  <si>
-    <t>Podstawy fryzjerstwa</t>
-  </si>
-  <si>
-    <t>Leńczowska Iwona</t>
-  </si>
-  <si>
-    <t>2FC</t>
-  </si>
-  <si>
-    <t>1TFA</t>
-  </si>
-  <si>
     <t>Pracownia sprzedaży</t>
   </si>
   <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>1WA</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>1FA|JA2</t>
   </si>
   <si>
-    <t>2WA|CH</t>
-  </si>
-  <si>
-    <t>2TFB</t>
-  </si>
-  <si>
-    <t>Wojciechowski Łukasz</t>
-  </si>
-  <si>
-    <t>Krzemińska Beata</t>
-  </si>
-  <si>
-    <t>2CA</t>
-  </si>
-  <si>
-    <t>Edukacja obywatelska</t>
-  </si>
-  <si>
-    <t>2TH</t>
-  </si>
-  <si>
     <t>1TH|JA1</t>
   </si>
   <si>
-    <t>1FA</t>
-  </si>
-  <si>
-    <t>1WA</t>
-  </si>
-  <si>
-    <t>2TH|relu</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>2FB|relu</t>
-  </si>
-  <si>
-    <t>2CA|relu</t>
-  </si>
-  <si>
-    <t>29</t>
+    <t>Wakat1 j. niemiecki</t>
+  </si>
+  <si>
+    <t>1WA|JN2</t>
+  </si>
+  <si>
+    <t>2FC|edu</t>
+  </si>
+  <si>
+    <t>2WA|edu</t>
+  </si>
+  <si>
+    <t>2S|edu</t>
+  </si>
+  <si>
+    <t>2CA|edu</t>
   </si>
   <si>
     <t>26.02.2026</t>
@@ -552,39 +588,72 @@
     <t>8</t>
   </si>
   <si>
+    <t>4TFB|dz2</t>
+  </si>
+  <si>
+    <t>p. Nowak, historia za lekcję 3</t>
+  </si>
+  <si>
+    <t>Matematyka</t>
+  </si>
+  <si>
+    <t>Nowak Magdalena</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>3FB</t>
+  </si>
+  <si>
+    <t>Kaszak Maria</t>
+  </si>
+  <si>
+    <t>3TFB</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>1CB</t>
+  </si>
+  <si>
+    <t>Mikołajczak Sylwia</t>
+  </si>
+  <si>
+    <t>pogrzeb</t>
+  </si>
+  <si>
+    <t>Nowaczyk Agnieszka</t>
+  </si>
+  <si>
+    <t>3TH</t>
+  </si>
+  <si>
+    <t>Język angielski zawodowy</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>12, 17:25-18:10</t>
+  </si>
+  <si>
+    <t>13, 18:15-19:00</t>
+  </si>
+  <si>
+    <t>1FC</t>
+  </si>
+  <si>
+    <t>1S</t>
+  </si>
+  <si>
     <t>2TFA|JA2</t>
   </si>
   <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>Mikołajczak Sylwia</t>
-  </si>
-  <si>
-    <t>pogrzeb</t>
-  </si>
-  <si>
-    <t>4TFB|dz2</t>
-  </si>
-  <si>
-    <t>p. Nowak, historia za lekcję 3</t>
-  </si>
-  <si>
-    <t>3FB</t>
-  </si>
-  <si>
-    <t>Kaszak Maria</t>
-  </si>
-  <si>
     <t>1CB|JA1</t>
   </si>
   <si>
-    <t>3TFB</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
     <t>1TFA|JA2</t>
   </si>
   <si>
@@ -597,87 +666,78 @@
     <t>1WB|JN1</t>
   </si>
   <si>
-    <t>1CB</t>
-  </si>
-  <si>
-    <t>Nowaczyk Agnieszka</t>
-  </si>
-  <si>
-    <t>3TH</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
-    <t>Język angielski zawodowy</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>12, 17:25-18:10</t>
-  </si>
-  <si>
-    <t>1S</t>
-  </si>
-  <si>
-    <t>13, 18:15-19:00</t>
-  </si>
-  <si>
     <t>27.02.2026</t>
   </si>
   <si>
+    <t>2TH|DZ</t>
+  </si>
+  <si>
+    <t>2TFB|DZ</t>
+  </si>
+  <si>
+    <t>1CB|JA2</t>
+  </si>
+  <si>
+    <t>p. Biezmienow, za lekcję 7</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - barber</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>Kruk Marcin</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>Filipiak Wiesław</t>
+  </si>
+  <si>
+    <t>1WB|relu</t>
+  </si>
+  <si>
+    <t>1TFA|relu</t>
+  </si>
+  <si>
+    <t>1TFB|relu</t>
+  </si>
+  <si>
+    <t>1S|relu</t>
+  </si>
+  <si>
+    <t>1CB|relu</t>
+  </si>
+  <si>
+    <t>1TH|relu</t>
+  </si>
+  <si>
+    <t>1WA|relu</t>
+  </si>
+  <si>
+    <t>1CA|relu</t>
+  </si>
+  <si>
+    <t>1FA|relu</t>
+  </si>
+  <si>
+    <t>1WB</t>
+  </si>
+  <si>
     <t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</t>
   </si>
   <si>
-    <t>1WB|relu</t>
-  </si>
-  <si>
-    <t>1TFA|relu</t>
-  </si>
-  <si>
-    <t>1TFB|relu</t>
-  </si>
-  <si>
-    <t>1S|relu</t>
-  </si>
-  <si>
-    <t>1CB|relu</t>
-  </si>
-  <si>
-    <t>1TH|relu</t>
-  </si>
-  <si>
-    <t>1WA|relu</t>
-  </si>
-  <si>
-    <t>1CA|relu</t>
-  </si>
-  <si>
-    <t>1FA|relu</t>
-  </si>
-  <si>
-    <t>2TH|DZ</t>
-  </si>
-  <si>
-    <t>2TFB|DZ</t>
-  </si>
-  <si>
-    <t>3TFA</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
     <t>1FB|JA2</t>
   </si>
   <si>
-    <t>1CB|JA2</t>
-  </si>
-  <si>
     <t>1WA|JN1</t>
   </si>
   <si>
+    <t>1FA|JA1</t>
+  </si>
+  <si>
     <t>1K|JA1</t>
   </si>
   <si>
@@ -687,10 +747,10 @@
     <t>1S|JA1</t>
   </si>
   <si>
-    <t>Matematyka</t>
-  </si>
-  <si>
-    <t>Filipiak Wiesław</t>
+    <t>Wakat2 matematyka</t>
+  </si>
+  <si>
+    <t>Młynarczyk Paweł</t>
   </si>
   <si>
     <t>Godzina</t>
@@ -726,18 +786,18 @@
     <t>Miejsce dyżuru</t>
   </si>
   <si>
+    <t>10:25-10:35</t>
+  </si>
+  <si>
+    <t>piętro_1</t>
+  </si>
+  <si>
     <t>08:45-08:50</t>
   </si>
   <si>
     <t>piętro_3</t>
   </si>
   <si>
-    <t>10:25-10:35</t>
-  </si>
-  <si>
-    <t>piętro_1</t>
-  </si>
-  <si>
     <t>11:20-11:25</t>
   </si>
   <si>
@@ -753,52 +813,52 @@
     <t>Jaworska Edyta</t>
   </si>
   <si>
+    <t>12:10-12:25</t>
+  </si>
+  <si>
+    <t>09:35-09:40</t>
+  </si>
+  <si>
+    <t>piętro_2</t>
+  </si>
+  <si>
+    <t>15:40-15:45</t>
+  </si>
+  <si>
+    <t>Jarek Zbigniew</t>
+  </si>
+  <si>
+    <t>16:30-16:35</t>
+  </si>
+  <si>
     <t>Ostrowska Ewa</t>
   </si>
   <si>
-    <t>09:35-09:40</t>
-  </si>
-  <si>
-    <t>piętro_2</t>
-  </si>
-  <si>
-    <t>12:10-12:25</t>
-  </si>
-  <si>
     <t>14:00-14:05</t>
   </si>
   <si>
-    <t>15:40-15:45</t>
-  </si>
-  <si>
-    <t>Jarek Zbigniew</t>
-  </si>
-  <si>
-    <t>16:30-16:35</t>
+    <t>Piątek-Pawłowska Bożena</t>
+  </si>
+  <si>
+    <t>Smereka Alicja</t>
   </si>
   <si>
     <t>07:55-08:00</t>
   </si>
   <si>
-    <t>Piątek-Pawłowska Bożena</t>
-  </si>
-  <si>
-    <t>Smereka Alicja</t>
-  </si>
-  <si>
-    <t>Nowak Magdalena</t>
-  </si>
-  <si>
     <t>parter</t>
   </si>
   <si>
+    <t>17:20-17:25</t>
+  </si>
+  <si>
+    <t>18:10-18:15</t>
+  </si>
+  <si>
     <t>14:50-14:55</t>
   </si>
   <si>
-    <t>17:20-17:25</t>
-  </si>
-  <si>
-    <t>18:10-18:15</t>
+    <t>Biczysko Wojciech</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1308,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b6733d39-91fb-4cc6-880a-b43ee80b3669}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b98d6a08-9386-4353-91ca-0bad05989e45}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1269,8 +1329,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{43accde4-bcd2-45b5-a22d-3ead5a3078a0}">
-  <dimension ref="A1:I187"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c9eb7ab7-9834-4d52-9a31-5be0af94231b}">
+  <dimension ref="A1:I204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1347,10 +1407,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
@@ -1362,7 +1422,7 @@
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
@@ -1376,22 +1436,22 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
@@ -1405,28 +1465,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -1434,28 +1494,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -1463,28 +1523,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -1492,28 +1552,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
@@ -1521,22 +1581,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
@@ -1550,28 +1610,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
@@ -1579,28 +1639,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1608,28 +1668,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
@@ -1637,28 +1697,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
@@ -1666,28 +1726,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
         <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1695,28 +1755,28 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G15" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
@@ -1724,28 +1784,28 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
         <v>62</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -1753,28 +1813,28 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="H17" t="s">
         <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -1782,28 +1842,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
         <v>69</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="H18" t="s">
         <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1811,28 +1871,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G19" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -1840,10 +1900,10 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
         <v>73</v>
@@ -1861,7 +1921,7 @@
         <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -1869,28 +1929,28 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
         <v>77</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s">
         <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
@@ -1898,28 +1958,28 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F22" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="H22" t="s">
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
@@ -1927,19 +1987,19 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="G23" t="s">
         <v>81</v>
@@ -1948,7 +2008,7 @@
         <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
@@ -1956,7 +2016,7 @@
         <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
         <v>83</v>
@@ -1977,7 +2037,7 @@
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -1985,25 +2045,25 @@
         <v>82</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="G25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I25" t="s">
         <v>19</v>
@@ -2014,28 +2074,28 @@
         <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
@@ -2043,28 +2103,28 @@
         <v>82</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -2072,28 +2132,28 @@
         <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
         <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s">
         <v>85</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G28" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
@@ -2101,22 +2161,22 @@
         <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s">
         <v>18</v>
@@ -2130,28 +2190,28 @@
         <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E30" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="G30" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
@@ -2159,28 +2219,28 @@
         <v>82</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E31" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="G31" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
@@ -2188,28 +2248,28 @@
         <v>82</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="E32" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="F32" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="G32" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
@@ -2217,28 +2277,28 @@
         <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E33" t="s">
         <v>85</v>
       </c>
       <c r="F33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G33" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
@@ -2246,28 +2306,28 @@
         <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="F34" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="G34" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
@@ -2275,28 +2335,28 @@
         <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" t="s">
         <v>103</v>
       </c>
-      <c r="E35" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" t="s">
-        <v>104</v>
-      </c>
-      <c r="G35" t="s">
-        <v>105</v>
-      </c>
-      <c r="H35" t="s">
-        <v>18</v>
-      </c>
       <c r="I35" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
@@ -2304,28 +2364,28 @@
         <v>82</v>
       </c>
       <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" t="s">
+        <v>64</v>
+      </c>
+      <c r="G36" t="s">
         <v>54</v>
       </c>
-      <c r="C36" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" t="s">
-        <v>79</v>
-      </c>
-      <c r="E36" t="s">
-        <v>43</v>
-      </c>
-      <c r="F36" t="s">
-        <v>106</v>
-      </c>
-      <c r="G36" t="s">
-        <v>107</v>
-      </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
@@ -2333,28 +2393,28 @@
         <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E37" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G37" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
@@ -2362,28 +2422,28 @@
         <v>82</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="F38" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="G38" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
@@ -2391,28 +2451,28 @@
         <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D39" t="s">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F39" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G39" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
@@ -2420,28 +2480,28 @@
         <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="C40" t="s">
+        <v>101</v>
+      </c>
+      <c r="D40" t="s">
+        <v>110</v>
+      </c>
+      <c r="E40" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" t="s">
         <v>64</v>
       </c>
-      <c r="D40" t="s">
-        <v>115</v>
-      </c>
-      <c r="E40" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" t="s">
-        <v>116</v>
-      </c>
       <c r="G40" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
@@ -2449,28 +2509,28 @@
         <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D41" t="s">
+        <v>110</v>
+      </c>
+      <c r="E41" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" t="s">
+        <v>64</v>
+      </c>
+      <c r="G41" t="s">
+        <v>54</v>
+      </c>
+      <c r="H41" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" t="s">
         <v>55</v>
-      </c>
-      <c r="E41" t="s">
-        <v>117</v>
-      </c>
-      <c r="F41" t="s">
-        <v>118</v>
-      </c>
-      <c r="G41" t="s">
-        <v>119</v>
-      </c>
-      <c r="H41" t="s">
-        <v>18</v>
-      </c>
-      <c r="I41" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
@@ -2478,28 +2538,28 @@
         <v>82</v>
       </c>
       <c r="B42" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="D42" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="E42" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F42" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="G42" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
@@ -2507,28 +2567,28 @@
         <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="C43" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E43" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F43" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="G43" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
@@ -2536,22 +2596,22 @@
         <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="E44" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="G44" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
@@ -2565,28 +2625,28 @@
         <v>82</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="E45" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="F45" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="G45" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
@@ -2594,28 +2654,28 @@
         <v>82</v>
       </c>
       <c r="B46" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E46" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="F46" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
@@ -2623,28 +2683,28 @@
         <v>82</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="C47" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E47" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="F47" t="s">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="G47" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
@@ -2652,22 +2712,22 @@
         <v>82</v>
       </c>
       <c r="B48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" t="s">
+        <v>122</v>
+      </c>
+      <c r="E48" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48" t="s">
         <v>78</v>
       </c>
-      <c r="C48" t="s">
-        <v>88</v>
-      </c>
-      <c r="D48" t="s">
-        <v>124</v>
-      </c>
-      <c r="E48" t="s">
-        <v>56</v>
-      </c>
-      <c r="F48" t="s">
-        <v>60</v>
-      </c>
       <c r="G48" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
@@ -2681,28 +2741,28 @@
         <v>82</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
+        <v>42</v>
+      </c>
+      <c r="E49" t="s">
         <v>27</v>
       </c>
-      <c r="D49" t="s">
-        <v>125</v>
-      </c>
-      <c r="E49" t="s">
-        <v>126</v>
-      </c>
       <c r="F49" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G49" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
@@ -2710,28 +2770,28 @@
         <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>127</v>
+        <v>30</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E50" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="F50" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G50" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
@@ -2739,22 +2799,22 @@
         <v>82</v>
       </c>
       <c r="B51" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" t="s">
         <v>127</v>
       </c>
-      <c r="C51" t="s">
+      <c r="E51" t="s">
         <v>128</v>
       </c>
-      <c r="D51" t="s">
-        <v>129</v>
-      </c>
-      <c r="E51" t="s">
-        <v>130</v>
-      </c>
       <c r="F51" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="G51" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
@@ -2768,19 +2828,19 @@
         <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D52" t="s">
+        <v>130</v>
+      </c>
+      <c r="E52" t="s">
+        <v>131</v>
+      </c>
+      <c r="F52" t="s">
         <v>132</v>
-      </c>
-      <c r="E52" t="s">
-        <v>130</v>
-      </c>
-      <c r="F52" t="s">
-        <v>131</v>
       </c>
       <c r="G52" t="s">
         <v>81</v>
@@ -2789,7 +2849,7 @@
         <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
@@ -2797,19 +2857,19 @@
         <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D53" t="s">
         <v>133</v>
       </c>
       <c r="E53" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F53" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G53" t="s">
         <v>81</v>
@@ -2818,7 +2878,7 @@
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
@@ -2826,19 +2886,19 @@
         <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D54" t="s">
         <v>134</v>
       </c>
       <c r="E54" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F54" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G54" t="s">
         <v>81</v>
@@ -2847,7 +2907,7 @@
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
@@ -2855,19 +2915,19 @@
         <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C55" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D55" t="s">
         <v>135</v>
       </c>
       <c r="E55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F55" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G55" t="s">
         <v>81</v>
@@ -2876,7 +2936,7 @@
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
@@ -2884,19 +2944,19 @@
         <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D56" t="s">
         <v>136</v>
       </c>
       <c r="E56" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F56" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G56" t="s">
         <v>81</v>
@@ -2905,7 +2965,7 @@
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
@@ -2913,28 +2973,28 @@
         <v>82</v>
       </c>
       <c r="B57" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57" t="s">
+        <v>129</v>
+      </c>
+      <c r="D57" t="s">
         <v>137</v>
       </c>
-      <c r="C57" t="s">
-        <v>88</v>
-      </c>
-      <c r="D57" t="s">
-        <v>138</v>
-      </c>
       <c r="E57" t="s">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="F57" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G57" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
@@ -2942,22 +3002,22 @@
         <v>82</v>
       </c>
       <c r="B58" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" t="s">
+        <v>138</v>
+      </c>
+      <c r="D58" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58" t="s">
+        <v>139</v>
+      </c>
+      <c r="F58" t="s">
+        <v>140</v>
+      </c>
+      <c r="G58" t="s">
         <v>141</v>
-      </c>
-      <c r="C58" t="s">
-        <v>88</v>
-      </c>
-      <c r="D58" t="s">
-        <v>138</v>
-      </c>
-      <c r="E58" t="s">
-        <v>56</v>
-      </c>
-      <c r="F58" t="s">
-        <v>60</v>
-      </c>
-      <c r="G58" t="s">
-        <v>81</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
@@ -2968,138 +3028,138 @@
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" t="s">
+        <v>50</v>
+      </c>
+      <c r="C59" t="s">
         <v>142</v>
       </c>
-      <c r="B59" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>143</v>
-      </c>
-      <c r="D59" t="s">
-        <v>97</v>
       </c>
       <c r="E59" t="s">
         <v>144</v>
       </c>
       <c r="F59" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G59" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
+        <v>82</v>
+      </c>
+      <c r="B60" t="s">
+        <v>50</v>
+      </c>
+      <c r="C60" t="s">
         <v>142</v>
       </c>
-      <c r="B60" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" t="s">
-        <v>83</v>
-      </c>
       <c r="D60" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E60" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="F60" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="G60" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" t="s">
+        <v>50</v>
+      </c>
+      <c r="C61" t="s">
         <v>142</v>
       </c>
-      <c r="B61" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" t="s">
-        <v>88</v>
-      </c>
       <c r="D61" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E61" t="s">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="F61" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="G61" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" t="s">
+        <v>50</v>
+      </c>
+      <c r="C62" t="s">
         <v>142</v>
       </c>
-      <c r="B62" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" t="s">
-        <v>143</v>
-      </c>
       <c r="D62" t="s">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="E62" t="s">
         <v>144</v>
       </c>
       <c r="F62" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G62" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C63" t="s">
         <v>83</v>
       </c>
       <c r="D63" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E63" t="s">
         <v>85</v>
       </c>
       <c r="F63" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="G63" t="s">
         <v>87</v>
@@ -3108,175 +3168,175 @@
         <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D64" t="s">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="E64" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="F64" t="s">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="G64" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B65" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C65" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="D65" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E65" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="F65" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="G65" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C66" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="D66" t="s">
-        <v>97</v>
+        <v>150</v>
       </c>
       <c r="E66" t="s">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="F66" t="s">
-        <v>145</v>
+        <v>92</v>
       </c>
       <c r="G66" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B67" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C67" t="s">
         <v>83</v>
       </c>
       <c r="D67" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E67" t="s">
         <v>85</v>
       </c>
       <c r="F67" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="G67" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B68" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C68" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D68" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E68" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="F68" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="G68" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B69" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C69" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="D69" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E69" t="s">
-        <v>123</v>
+        <v>58</v>
       </c>
       <c r="F69" t="s">
-        <v>48</v>
+        <v>152</v>
       </c>
       <c r="G69" t="s">
-        <v>17</v>
+        <v>153</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
@@ -3287,83 +3347,83 @@
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B70" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C70" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="D70" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="E70" t="s">
-        <v>156</v>
+        <v>38</v>
       </c>
       <c r="F70" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="G70" t="s">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B71" t="s">
         <v>40</v>
       </c>
       <c r="C71" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="D71" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E71" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F71" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G71" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B72" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C72" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D72" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E72" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="F72" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="G72" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
@@ -3374,254 +3434,254 @@
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B73" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C73" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D73" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E73" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F73" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="G73" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B74" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C74" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="D74" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="E74" t="s">
-        <v>156</v>
+        <v>22</v>
       </c>
       <c r="F74" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="G74" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B75" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="E75" t="s">
-        <v>69</v>
+        <v>160</v>
       </c>
       <c r="F75" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="G75" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B76" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C76" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E76" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="F76" t="s">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="G76" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B77" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E77" t="s">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="F77" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="G77" t="s">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B78" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="C78" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="E78" t="s">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="F78" t="s">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="G78" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B79" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="C79" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D79" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="E79" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="F79" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="G79" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B80" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="C80" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="D80" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E80" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="F80" t="s">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="G80" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B81" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="C81" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="D81" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E81" t="s">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="F81" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
       <c r="G81" t="s">
         <v>81</v>
@@ -3630,117 +3690,117 @@
         <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B82" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C82" t="s">
-        <v>83</v>
+        <v>169</v>
       </c>
       <c r="D82" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="E82" t="s">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="F82" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
       <c r="G82" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B83" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="C83" t="s">
-        <v>27</v>
+        <v>169</v>
       </c>
       <c r="D83" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="E83" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="F83" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="G83" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B84" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>41</v>
+        <v>169</v>
       </c>
       <c r="D84" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="E84" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="F84" t="s">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="G84" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B85" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="C85" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="D85" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="E85" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="F85" t="s">
-        <v>60</v>
+        <v>171</v>
       </c>
       <c r="G85" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
@@ -3751,54 +3811,54 @@
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B86" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="C86" t="s">
-        <v>41</v>
+        <v>169</v>
       </c>
       <c r="D86" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="E86" t="s">
-        <v>69</v>
+        <v>172</v>
       </c>
       <c r="F86" t="s">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="G86" t="s">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B87" t="s">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="C87" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="D87" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="E87" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="F87" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G87" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
@@ -3809,51 +3869,51 @@
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B88" t="s">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="C88" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="D88" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E88" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="F88" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="G88" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B89" t="s">
-        <v>127</v>
+        <v>30</v>
       </c>
       <c r="C89" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="D89" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E89" t="s">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="F89" t="s">
-        <v>169</v>
+        <v>43</v>
       </c>
       <c r="G89" t="s">
         <v>81</v>
@@ -3862,30 +3922,30 @@
         <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B90" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="C90" t="s">
         <v>41</v>
       </c>
       <c r="D90" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E90" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="F90" t="s">
-        <v>172</v>
+        <v>43</v>
       </c>
       <c r="G90" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
@@ -3896,54 +3956,54 @@
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="B91" t="s">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="C91" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="D91" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E91" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="F91" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G91" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="B92" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C92" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D92" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E92" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F92" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="G92" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
@@ -3954,25 +4014,25 @@
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C93" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D93" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="E93" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="F93" t="s">
         <v>23</v>
       </c>
       <c r="G93" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
@@ -3983,268 +4043,268 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="B94" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C94" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D94" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E94" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F94" t="s">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="G94" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="B95" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C95" t="s">
-        <v>27</v>
+        <v>179</v>
       </c>
       <c r="D95" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E95" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F95" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="G95" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="B96" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C96" t="s">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="D96" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="E96" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="F96" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="G96" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="B97" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C97" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="D97" t="s">
-        <v>62</v>
+        <v>182</v>
       </c>
       <c r="E97" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="F97" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="G97" t="s">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="B98" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C98" t="s">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="D98" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E98" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="F98" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="G98" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="B99" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C99" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="D99" t="s">
-        <v>68</v>
+        <v>184</v>
       </c>
       <c r="E99" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="F99" t="s">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="G99" t="s">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B100" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C100" t="s">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="D100" t="s">
-        <v>122</v>
+        <v>186</v>
       </c>
       <c r="E100" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="F100" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="G100" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="H100" t="s">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B101" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C101" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="D101" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="E101" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F101" t="s">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c r="G101" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
       </c>
       <c r="I101" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B102" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="D102" t="s">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c r="E102" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="F102" t="s">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="G102" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B103" t="s">
         <v>40</v>
@@ -4253,161 +4313,161 @@
         <v>83</v>
       </c>
       <c r="D103" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E103" t="s">
         <v>85</v>
       </c>
       <c r="F103" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="G103" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B104" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C104" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D104" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="E104" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="F104" t="s">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c r="G104" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B105" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C105" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="D105" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E105" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="F105" t="s">
-        <v>48</v>
+        <v>187</v>
       </c>
       <c r="G105" t="s">
-        <v>183</v>
+        <v>90</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B106" t="s">
         <v>40</v>
       </c>
       <c r="C106" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="D106" t="s">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="E106" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F106" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="G106" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="H106" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I106" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B107" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C107" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="D107" t="s">
-        <v>162</v>
+        <v>31</v>
       </c>
       <c r="E107" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="F107" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="G107" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
       </c>
       <c r="I107" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B108" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C108" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="D108" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="E108" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="F108" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="G108" t="s">
-        <v>17</v>
+        <v>157</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
@@ -4418,428 +4478,428 @@
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B109" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C109" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D109" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="E109" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="F109" t="s">
-        <v>175</v>
+        <v>64</v>
       </c>
       <c r="G109" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
       </c>
       <c r="I109" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B110" t="s">
+        <v>36</v>
+      </c>
+      <c r="C110" t="s">
+        <v>101</v>
+      </c>
+      <c r="D110" t="s">
+        <v>110</v>
+      </c>
+      <c r="E110" t="s">
+        <v>22</v>
+      </c>
+      <c r="F110" t="s">
+        <v>64</v>
+      </c>
+      <c r="G110" t="s">
         <v>54</v>
       </c>
-      <c r="C110" t="s">
-        <v>88</v>
-      </c>
-      <c r="D110" t="s">
-        <v>73</v>
-      </c>
-      <c r="E110" t="s">
-        <v>43</v>
-      </c>
-      <c r="F110" t="s">
-        <v>30</v>
-      </c>
-      <c r="G110" t="s">
-        <v>31</v>
-      </c>
       <c r="H110" t="s">
         <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B111" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="C111" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="D111" t="s">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="E111" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F111" t="s">
-        <v>186</v>
+        <v>114</v>
       </c>
       <c r="G111" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B112" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="C112" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="D112" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="E112" t="s">
-        <v>69</v>
+        <v>190</v>
       </c>
       <c r="F112" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="G112" t="s">
-        <v>67</v>
+        <v>191</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B113" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C113" t="s">
         <v>13</v>
       </c>
       <c r="D113" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="E113" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F113" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G113" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B114" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D114" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="E114" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F114" t="s">
-        <v>188</v>
+        <v>33</v>
       </c>
       <c r="G114" t="s">
-        <v>189</v>
+        <v>34</v>
       </c>
       <c r="H114" t="s">
         <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B115" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C115" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="D115" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E115" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="F115" t="s">
-        <v>175</v>
+        <v>23</v>
       </c>
       <c r="G115" t="s">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B116" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="C116" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="D116" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="E116" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F116" t="s">
-        <v>60</v>
+        <v>196</v>
       </c>
       <c r="G116" t="s">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B117" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C117" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D117" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E117" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="F117" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G117" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B118" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="C118" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D118" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="E118" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="F118" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G118" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B119" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="C119" t="s">
-        <v>13</v>
+        <v>158</v>
       </c>
       <c r="D119" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="E119" t="s">
         <v>15</v>
       </c>
       <c r="F119" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="G119" t="s">
-        <v>61</v>
+        <v>198</v>
       </c>
       <c r="H119" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I119" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B120" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C120" t="s">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="D120" t="s">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="E120" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F120" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="G120" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H120" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I120" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B121" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="C121" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="D121" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="E121" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F121" t="s">
-        <v>60</v>
+        <v>196</v>
       </c>
       <c r="G121" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B122" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="C122" t="s">
-        <v>27</v>
+        <v>200</v>
       </c>
       <c r="D122" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E122" t="s">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="F122" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="G122" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B123" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="C123" t="s">
-        <v>41</v>
+        <v>200</v>
       </c>
       <c r="D123" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="E123" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="F123" t="s">
-        <v>44</v>
+        <v>203</v>
       </c>
       <c r="G123" t="s">
         <v>81</v>
@@ -4848,30 +4908,30 @@
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B124" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="C124" t="s">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D124" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="E124" t="s">
-        <v>22</v>
+        <v>190</v>
       </c>
       <c r="F124" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="G124" t="s">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
@@ -4882,112 +4942,112 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B125" t="s">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="C125" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="D125" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="E125" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F125" t="s">
-        <v>60</v>
+        <v>203</v>
       </c>
       <c r="G125" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
       </c>
       <c r="I125" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B126" t="s">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="C126" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D126" t="s">
-        <v>193</v>
+        <v>110</v>
       </c>
       <c r="E126" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="F126" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="G126" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
       </c>
       <c r="I126" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B127" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="C127" t="s">
         <v>41</v>
       </c>
       <c r="D127" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="E127" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="F127" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G127" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B128" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="C128" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D128" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="E128" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="F128" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G128" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
@@ -4998,80 +5058,80 @@
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B129" t="s">
+        <v>30</v>
+      </c>
+      <c r="C129" t="s">
+        <v>41</v>
+      </c>
+      <c r="D129" t="s">
         <v>127</v>
       </c>
-      <c r="C129" t="s">
-        <v>88</v>
-      </c>
-      <c r="D129" t="s">
-        <v>124</v>
-      </c>
       <c r="E129" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F129" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="G129" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B130" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="C130" t="s">
-        <v>192</v>
+        <v>41</v>
       </c>
       <c r="D130" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E130" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F130" t="s">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="G130" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B131" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C131" t="s">
         <v>41</v>
       </c>
       <c r="D131" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="E131" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="F131" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G131" t="s">
         <v>81</v>
@@ -5080,56 +5140,56 @@
         <v>18</v>
       </c>
       <c r="I131" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B132" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C132" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="D132" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="E132" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F132" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="G132" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
+        <v>185</v>
+      </c>
+      <c r="B133" t="s">
+        <v>116</v>
+      </c>
+      <c r="C133" t="s">
+        <v>41</v>
+      </c>
+      <c r="D133" t="s">
         <v>173</v>
       </c>
-      <c r="B133" t="s">
-        <v>137</v>
-      </c>
-      <c r="C133" t="s">
-        <v>192</v>
-      </c>
-      <c r="D133" t="s">
-        <v>182</v>
-      </c>
       <c r="E133" t="s">
-        <v>195</v>
+        <v>48</v>
       </c>
       <c r="F133" t="s">
-        <v>196</v>
+        <v>43</v>
       </c>
       <c r="G133" t="s">
         <v>81</v>
@@ -5138,27 +5198,27 @@
         <v>18</v>
       </c>
       <c r="I133" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B134" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="C134" t="s">
         <v>41</v>
       </c>
       <c r="D134" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="E134" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="F134" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G134" t="s">
         <v>81</v>
@@ -5167,88 +5227,88 @@
         <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B135" t="s">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="C135" t="s">
-        <v>192</v>
+        <v>51</v>
       </c>
       <c r="D135" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="E135" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="F135" t="s">
-        <v>196</v>
+        <v>53</v>
       </c>
       <c r="G135" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="H135" t="s">
         <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B136" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="C136" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D136" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E136" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F136" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G136" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="H136" t="s">
         <v>18</v>
       </c>
       <c r="I136" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B137" t="s">
-        <v>197</v>
+        <v>12</v>
       </c>
       <c r="C137" t="s">
-        <v>192</v>
+        <v>51</v>
       </c>
       <c r="D137" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="E137" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="F137" t="s">
-        <v>196</v>
+        <v>64</v>
       </c>
       <c r="G137" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
@@ -5259,25 +5319,25 @@
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B138" t="s">
-        <v>197</v>
+        <v>40</v>
       </c>
       <c r="C138" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D138" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="E138" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F138" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="G138" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
@@ -5288,25 +5348,25 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B139" t="s">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="C139" t="s">
-        <v>192</v>
+        <v>51</v>
       </c>
       <c r="D139" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="E139" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F139" t="s">
-        <v>196</v>
+        <v>64</v>
       </c>
       <c r="G139" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="H139" t="s">
         <v>18</v>
@@ -5317,25 +5377,25 @@
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B140" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C140" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D140" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="E140" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="F140" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="G140" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="H140" t="s">
         <v>18</v>
@@ -5346,54 +5406,54 @@
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B141" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C141" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D141" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="E141" t="s">
-        <v>201</v>
+        <v>69</v>
       </c>
       <c r="F141" t="s">
-        <v>139</v>
+        <v>70</v>
       </c>
       <c r="G141" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="H141" t="s">
         <v>18</v>
       </c>
       <c r="I141" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B142" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C142" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="D142" t="s">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="E142" t="s">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="F142" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="G142" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H142" t="s">
         <v>18</v>
@@ -5404,25 +5464,25 @@
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B143" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C143" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="D143" t="s">
-        <v>203</v>
+        <v>118</v>
       </c>
       <c r="E143" t="s">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="F143" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="G143" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H143" t="s">
         <v>18</v>
@@ -5433,83 +5493,83 @@
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B144" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C144" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="D144" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E144" t="s">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="F144" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="G144" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="H144" t="s">
         <v>18</v>
       </c>
       <c r="I144" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B145" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C145" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="D145" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E145" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="F145" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="G145" t="s">
-        <v>17</v>
+        <v>212</v>
       </c>
       <c r="H145" t="s">
         <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B146" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C146" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="D146" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="E146" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="F146" t="s">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="G146" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
@@ -5520,83 +5580,83 @@
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B147" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C147" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="D147" t="s">
-        <v>207</v>
+        <v>71</v>
       </c>
       <c r="E147" t="s">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="F147" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="G147" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H147" t="s">
         <v>18</v>
       </c>
       <c r="I147" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B148" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C148" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="D148" t="s">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="E148" t="s">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="F148" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="G148" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H148" t="s">
         <v>18</v>
       </c>
       <c r="I148" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B149" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C149" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="D149" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E149" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="F149" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="G149" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H149" t="s">
         <v>18</v>
@@ -5607,170 +5667,170 @@
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B150" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C150" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="D150" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E150" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="F150" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="G150" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H150" t="s">
         <v>18</v>
       </c>
       <c r="I150" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B151" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C151" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="D151" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="E151" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="F151" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="G151" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="H151" t="s">
         <v>18</v>
       </c>
       <c r="I151" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B152" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C152" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="D152" t="s">
-        <v>162</v>
+        <v>216</v>
       </c>
       <c r="E152" t="s">
-        <v>201</v>
+        <v>85</v>
       </c>
       <c r="F152" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="G152" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="H152" t="s">
         <v>18</v>
       </c>
       <c r="I152" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B153" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C153" t="s">
         <v>83</v>
       </c>
       <c r="D153" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E153" t="s">
         <v>85</v>
       </c>
       <c r="F153" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="G153" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="H153" t="s">
         <v>18</v>
       </c>
       <c r="I153" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B154" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C154" t="s">
         <v>83</v>
       </c>
       <c r="D154" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E154" t="s">
         <v>85</v>
       </c>
       <c r="F154" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="G154" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="H154" t="s">
         <v>18</v>
       </c>
       <c r="I154" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B155" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C155" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="D155" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E155" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="F155" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G155" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="H155" t="s">
         <v>18</v>
@@ -5781,25 +5841,25 @@
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B156" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C156" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="D156" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="E156" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F156" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="G156" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H156" t="s">
         <v>18</v>
@@ -5810,141 +5870,141 @@
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B157" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C157" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="D157" t="s">
-        <v>42</v>
+        <v>217</v>
       </c>
       <c r="E157" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F157" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="G157" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="H157" t="s">
         <v>18</v>
       </c>
       <c r="I157" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B158" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C158" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="D158" t="s">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
       </c>
       <c r="F158" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="G158" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="H158" t="s">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="I158" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B159" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C159" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D159" t="s">
-        <v>211</v>
+        <v>155</v>
       </c>
       <c r="E159" t="s">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="F159" t="s">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="G159" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="H159" t="s">
         <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B160" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C160" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D160" t="s">
-        <v>212</v>
+        <v>110</v>
       </c>
       <c r="E160" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="F160" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="G160" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B161" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C161" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="D161" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="E161" t="s">
-        <v>123</v>
+        <v>58</v>
       </c>
       <c r="F161" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G161" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="H161" t="s">
         <v>18</v>
@@ -5955,25 +6015,25 @@
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B162" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C162" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D162" t="s">
-        <v>58</v>
+        <v>220</v>
       </c>
       <c r="E162" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="F162" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G162" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="H162" t="s">
         <v>18</v>
@@ -5984,7 +6044,7 @@
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B163" t="s">
         <v>40</v>
@@ -5993,45 +6053,45 @@
         <v>13</v>
       </c>
       <c r="D163" t="s">
-        <v>42</v>
+        <v>155</v>
       </c>
       <c r="E163" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="F163" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G163" t="s">
-        <v>61</v>
+        <v>221</v>
       </c>
       <c r="H163" t="s">
         <v>18</v>
       </c>
       <c r="I163" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B164" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C164" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D164" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="E164" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="F164" t="s">
         <v>23</v>
       </c>
       <c r="G164" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="H164" t="s">
         <v>18</v>
@@ -6042,373 +6102,373 @@
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B165" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C165" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="D165" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="E165" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="F165" t="s">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="G165" t="s">
-        <v>105</v>
+        <v>223</v>
       </c>
       <c r="H165" t="s">
         <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B166" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C166" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="D166" t="s">
-        <v>212</v>
+        <v>42</v>
       </c>
       <c r="E166" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="F166" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="G166" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="H166" t="s">
         <v>18</v>
       </c>
       <c r="I166" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B167" t="s">
+        <v>56</v>
+      </c>
+      <c r="C167" t="s">
+        <v>129</v>
+      </c>
+      <c r="D167" t="s">
+        <v>224</v>
+      </c>
+      <c r="E167" t="s">
+        <v>131</v>
+      </c>
+      <c r="F167" t="s">
+        <v>132</v>
+      </c>
+      <c r="G167" t="s">
         <v>54</v>
       </c>
-      <c r="C167" t="s">
-        <v>88</v>
-      </c>
-      <c r="D167" t="s">
-        <v>162</v>
-      </c>
-      <c r="E167" t="s">
-        <v>56</v>
-      </c>
-      <c r="F167" t="s">
-        <v>60</v>
-      </c>
-      <c r="G167" t="s">
-        <v>19</v>
-      </c>
       <c r="H167" t="s">
         <v>18</v>
       </c>
       <c r="I167" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B168" t="s">
+        <v>56</v>
+      </c>
+      <c r="C168" t="s">
+        <v>129</v>
+      </c>
+      <c r="D168" t="s">
+        <v>225</v>
+      </c>
+      <c r="E168" t="s">
+        <v>131</v>
+      </c>
+      <c r="F168" t="s">
+        <v>132</v>
+      </c>
+      <c r="G168" t="s">
         <v>54</v>
       </c>
-      <c r="C168" t="s">
-        <v>27</v>
-      </c>
-      <c r="D168" t="s">
-        <v>214</v>
-      </c>
-      <c r="E168" t="s">
-        <v>123</v>
-      </c>
-      <c r="F168" t="s">
-        <v>48</v>
-      </c>
-      <c r="G168" t="s">
-        <v>19</v>
-      </c>
       <c r="H168" t="s">
         <v>18</v>
       </c>
       <c r="I168" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B169" t="s">
+        <v>56</v>
+      </c>
+      <c r="C169" t="s">
+        <v>129</v>
+      </c>
+      <c r="D169" t="s">
+        <v>226</v>
+      </c>
+      <c r="E169" t="s">
+        <v>131</v>
+      </c>
+      <c r="F169" t="s">
+        <v>132</v>
+      </c>
+      <c r="G169" t="s">
         <v>54</v>
       </c>
-      <c r="C169" t="s">
-        <v>13</v>
-      </c>
-      <c r="D169" t="s">
-        <v>42</v>
-      </c>
-      <c r="E169" t="s">
-        <v>71</v>
-      </c>
-      <c r="F169" t="s">
-        <v>60</v>
-      </c>
-      <c r="G169" t="s">
-        <v>61</v>
-      </c>
       <c r="H169" t="s">
         <v>18</v>
       </c>
       <c r="I169" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B170" t="s">
+        <v>56</v>
+      </c>
+      <c r="C170" t="s">
+        <v>129</v>
+      </c>
+      <c r="D170" t="s">
+        <v>227</v>
+      </c>
+      <c r="E170" t="s">
+        <v>131</v>
+      </c>
+      <c r="F170" t="s">
+        <v>132</v>
+      </c>
+      <c r="G170" t="s">
         <v>54</v>
       </c>
-      <c r="C170" t="s">
-        <v>20</v>
-      </c>
-      <c r="D170" t="s">
-        <v>215</v>
-      </c>
-      <c r="E170" t="s">
-        <v>22</v>
-      </c>
-      <c r="F170" t="s">
-        <v>23</v>
-      </c>
-      <c r="G170" t="s">
-        <v>17</v>
-      </c>
       <c r="H170" t="s">
         <v>18</v>
       </c>
       <c r="I170" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B171" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C171" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="D171" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E171" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="F171" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="G171" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="H171" t="s">
         <v>18</v>
       </c>
       <c r="I171" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B172" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C172" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="D172" t="s">
-        <v>154</v>
+        <v>229</v>
       </c>
       <c r="E172" t="s">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="F172" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="G172" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="H172" t="s">
         <v>18</v>
       </c>
       <c r="I172" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B173" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C173" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D173" t="s">
-        <v>164</v>
+        <v>230</v>
       </c>
       <c r="E173" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F173" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="G173" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="H173" t="s">
         <v>18</v>
       </c>
       <c r="I173" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B174" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C174" t="s">
-        <v>13</v>
+        <v>129</v>
       </c>
       <c r="D174" t="s">
-        <v>42</v>
+        <v>231</v>
       </c>
       <c r="E174" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="F174" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="G174" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="H174" t="s">
         <v>18</v>
       </c>
       <c r="I174" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B175" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C175" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="D175" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="E175" t="s">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="F175" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="G175" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="H175" t="s">
         <v>18</v>
       </c>
       <c r="I175" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="15">
       <c r="A176" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B176" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C176" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="D176" t="s">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c r="E176" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="F176" t="s">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="G176" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="H176" t="s">
         <v>18</v>
       </c>
       <c r="I176" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15">
       <c r="A177" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B177" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="C177" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="D177" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="E177" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F177" t="s">
+        <v>59</v>
+      </c>
+      <c r="G177" t="s">
         <v>60</v>
-      </c>
-      <c r="G177" t="s">
-        <v>19</v>
       </c>
       <c r="H177" t="s">
         <v>18</v>
@@ -6419,83 +6479,83 @@
     </row>
     <row r="178" spans="1:9" ht="15">
       <c r="A178" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B178" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="C178" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D178" t="s">
-        <v>42</v>
+        <v>197</v>
       </c>
       <c r="E178" t="s">
-        <v>123</v>
+        <v>48</v>
       </c>
       <c r="F178" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G178" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="H178" t="s">
         <v>18</v>
       </c>
       <c r="I178" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="15">
       <c r="A179" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B179" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="C179" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="D179" t="s">
-        <v>216</v>
+        <v>45</v>
       </c>
       <c r="E179" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="F179" t="s">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="G179" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="H179" t="s">
         <v>18</v>
       </c>
       <c r="I179" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="15">
       <c r="A180" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B180" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="C180" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="D180" t="s">
-        <v>124</v>
+        <v>233</v>
       </c>
       <c r="E180" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F180" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="G180" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="H180" t="s">
         <v>18</v>
@@ -6506,25 +6566,25 @@
     </row>
     <row r="181" spans="1:9" ht="15">
       <c r="A181" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B181" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="C181" t="s">
         <v>41</v>
       </c>
       <c r="D181" t="s">
-        <v>122</v>
+        <v>233</v>
       </c>
       <c r="E181" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F181" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G181" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="H181" t="s">
         <v>18</v>
@@ -6535,25 +6595,25 @@
     </row>
     <row r="182" spans="1:9" ht="15">
       <c r="A182" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B182" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="C182" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D182" t="s">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="E182" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F182" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G182" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="H182" t="s">
         <v>18</v>
@@ -6564,54 +6624,54 @@
     </row>
     <row r="183" spans="1:9" ht="15">
       <c r="A183" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B183" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="C183" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D183" t="s">
-        <v>219</v>
+        <v>125</v>
       </c>
       <c r="E183" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="F183" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G183" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="H183" t="s">
         <v>18</v>
       </c>
       <c r="I183" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="15">
       <c r="A184" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B184" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="C184" t="s">
         <v>41</v>
       </c>
       <c r="D184" t="s">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="E184" t="s">
-        <v>69</v>
+        <v>190</v>
       </c>
       <c r="F184" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G184" t="s">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="H184" t="s">
         <v>18</v>
@@ -6622,80 +6682,80 @@
     </row>
     <row r="185" spans="1:9" ht="15">
       <c r="A185" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B185" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C185" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D185" t="s">
-        <v>220</v>
+        <v>42</v>
       </c>
       <c r="E185" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="F185" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G185" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="H185" t="s">
         <v>18</v>
       </c>
       <c r="I185" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="15">
       <c r="A186" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B186" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C186" t="s">
         <v>41</v>
       </c>
       <c r="D186" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="E186" t="s">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="F186" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G186" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H186" t="s">
         <v>18</v>
       </c>
       <c r="I186" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="15">
       <c r="A187" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B187" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C187" t="s">
         <v>41</v>
       </c>
       <c r="D187" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="E187" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="F187" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G187" t="s">
         <v>81</v>
@@ -6704,6 +6764,499 @@
         <v>18</v>
       </c>
       <c r="I187" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="15">
+      <c r="A188" t="s">
+        <v>214</v>
+      </c>
+      <c r="B188" t="s">
+        <v>50</v>
+      </c>
+      <c r="C188" t="s">
+        <v>51</v>
+      </c>
+      <c r="D188" t="s">
+        <v>163</v>
+      </c>
+      <c r="E188" t="s">
+        <v>234</v>
+      </c>
+      <c r="F188" t="s">
+        <v>114</v>
+      </c>
+      <c r="G188" t="s">
+        <v>65</v>
+      </c>
+      <c r="H188" t="s">
+        <v>18</v>
+      </c>
+      <c r="I188" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="15">
+      <c r="A189" t="s">
+        <v>214</v>
+      </c>
+      <c r="B189" t="s">
+        <v>56</v>
+      </c>
+      <c r="C189" t="s">
+        <v>51</v>
+      </c>
+      <c r="D189" t="s">
+        <v>163</v>
+      </c>
+      <c r="E189" t="s">
+        <v>234</v>
+      </c>
+      <c r="F189" t="s">
+        <v>114</v>
+      </c>
+      <c r="G189" t="s">
+        <v>65</v>
+      </c>
+      <c r="H189" t="s">
+        <v>18</v>
+      </c>
+      <c r="I189" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="15">
+      <c r="A190" t="s">
+        <v>214</v>
+      </c>
+      <c r="B190" t="s">
+        <v>12</v>
+      </c>
+      <c r="C190" t="s">
+        <v>51</v>
+      </c>
+      <c r="D190" t="s">
+        <v>42</v>
+      </c>
+      <c r="E190" t="s">
+        <v>66</v>
+      </c>
+      <c r="F190" t="s">
+        <v>64</v>
+      </c>
+      <c r="G190" t="s">
+        <v>65</v>
+      </c>
+      <c r="H190" t="s">
+        <v>18</v>
+      </c>
+      <c r="I190" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="15">
+      <c r="A191" t="s">
+        <v>214</v>
+      </c>
+      <c r="B191" t="s">
+        <v>40</v>
+      </c>
+      <c r="C191" t="s">
+        <v>51</v>
+      </c>
+      <c r="D191" t="s">
+        <v>42</v>
+      </c>
+      <c r="E191" t="s">
+        <v>66</v>
+      </c>
+      <c r="F191" t="s">
+        <v>64</v>
+      </c>
+      <c r="G191" t="s">
+        <v>65</v>
+      </c>
+      <c r="H191" t="s">
+        <v>18</v>
+      </c>
+      <c r="I191" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="15">
+      <c r="A192" t="s">
+        <v>214</v>
+      </c>
+      <c r="B192" t="s">
+        <v>20</v>
+      </c>
+      <c r="C192" t="s">
+        <v>51</v>
+      </c>
+      <c r="D192" t="s">
+        <v>42</v>
+      </c>
+      <c r="E192" t="s">
+        <v>66</v>
+      </c>
+      <c r="F192" t="s">
+        <v>64</v>
+      </c>
+      <c r="G192" t="s">
+        <v>65</v>
+      </c>
+      <c r="H192" t="s">
+        <v>18</v>
+      </c>
+      <c r="I192" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="15">
+      <c r="A193" t="s">
+        <v>214</v>
+      </c>
+      <c r="B193" t="s">
+        <v>25</v>
+      </c>
+      <c r="C193" t="s">
+        <v>51</v>
+      </c>
+      <c r="D193" t="s">
+        <v>42</v>
+      </c>
+      <c r="E193" t="s">
+        <v>66</v>
+      </c>
+      <c r="F193" t="s">
+        <v>64</v>
+      </c>
+      <c r="G193" t="s">
+        <v>65</v>
+      </c>
+      <c r="H193" t="s">
+        <v>18</v>
+      </c>
+      <c r="I193" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="15">
+      <c r="A194" t="s">
+        <v>214</v>
+      </c>
+      <c r="B194" t="s">
+        <v>12</v>
+      </c>
+      <c r="C194" t="s">
+        <v>67</v>
+      </c>
+      <c r="D194" t="s">
+        <v>80</v>
+      </c>
+      <c r="E194" t="s">
+        <v>69</v>
+      </c>
+      <c r="F194" t="s">
+        <v>70</v>
+      </c>
+      <c r="G194" t="s">
+        <v>54</v>
+      </c>
+      <c r="H194" t="s">
+        <v>18</v>
+      </c>
+      <c r="I194" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="15">
+      <c r="A195" t="s">
+        <v>214</v>
+      </c>
+      <c r="B195" t="s">
+        <v>40</v>
+      </c>
+      <c r="C195" t="s">
+        <v>67</v>
+      </c>
+      <c r="D195" t="s">
+        <v>210</v>
+      </c>
+      <c r="E195" t="s">
+        <v>85</v>
+      </c>
+      <c r="F195" t="s">
+        <v>187</v>
+      </c>
+      <c r="G195" t="s">
+        <v>87</v>
+      </c>
+      <c r="H195" t="s">
+        <v>18</v>
+      </c>
+      <c r="I195" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="15">
+      <c r="A196" t="s">
+        <v>214</v>
+      </c>
+      <c r="B196" t="s">
+        <v>20</v>
+      </c>
+      <c r="C196" t="s">
+        <v>67</v>
+      </c>
+      <c r="D196" t="s">
+        <v>235</v>
+      </c>
+      <c r="E196" t="s">
+        <v>69</v>
+      </c>
+      <c r="F196" t="s">
+        <v>70</v>
+      </c>
+      <c r="G196" t="s">
+        <v>54</v>
+      </c>
+      <c r="H196" t="s">
+        <v>18</v>
+      </c>
+      <c r="I196" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="15">
+      <c r="A197" t="s">
+        <v>214</v>
+      </c>
+      <c r="B197" t="s">
+        <v>25</v>
+      </c>
+      <c r="C197" t="s">
+        <v>67</v>
+      </c>
+      <c r="D197" t="s">
+        <v>236</v>
+      </c>
+      <c r="E197" t="s">
+        <v>27</v>
+      </c>
+      <c r="F197" t="s">
+        <v>203</v>
+      </c>
+      <c r="G197" t="s">
+        <v>157</v>
+      </c>
+      <c r="H197" t="s">
+        <v>18</v>
+      </c>
+      <c r="I197" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="15">
+      <c r="A198" t="s">
+        <v>214</v>
+      </c>
+      <c r="B198" t="s">
+        <v>30</v>
+      </c>
+      <c r="C198" t="s">
+        <v>67</v>
+      </c>
+      <c r="D198" t="s">
+        <v>237</v>
+      </c>
+      <c r="E198" t="s">
+        <v>126</v>
+      </c>
+      <c r="F198" t="s">
+        <v>23</v>
+      </c>
+      <c r="G198" t="s">
+        <v>221</v>
+      </c>
+      <c r="H198" t="s">
+        <v>18</v>
+      </c>
+      <c r="I198" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="15">
+      <c r="A199" t="s">
+        <v>214</v>
+      </c>
+      <c r="B199" t="s">
+        <v>36</v>
+      </c>
+      <c r="C199" t="s">
+        <v>67</v>
+      </c>
+      <c r="D199" t="s">
+        <v>238</v>
+      </c>
+      <c r="E199" t="s">
+        <v>126</v>
+      </c>
+      <c r="F199" t="s">
+        <v>43</v>
+      </c>
+      <c r="G199" t="s">
+        <v>221</v>
+      </c>
+      <c r="H199" t="s">
+        <v>18</v>
+      </c>
+      <c r="I199" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="15">
+      <c r="A200" t="s">
+        <v>214</v>
+      </c>
+      <c r="B200" t="s">
+        <v>111</v>
+      </c>
+      <c r="C200" t="s">
+        <v>67</v>
+      </c>
+      <c r="D200" t="s">
+        <v>239</v>
+      </c>
+      <c r="E200" t="s">
+        <v>85</v>
+      </c>
+      <c r="F200" t="s">
+        <v>187</v>
+      </c>
+      <c r="G200" t="s">
+        <v>90</v>
+      </c>
+      <c r="H200" t="s">
+        <v>18</v>
+      </c>
+      <c r="I200" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="15">
+      <c r="A201" t="s">
+        <v>214</v>
+      </c>
+      <c r="B201" t="s">
+        <v>112</v>
+      </c>
+      <c r="C201" t="s">
+        <v>67</v>
+      </c>
+      <c r="D201" t="s">
+        <v>240</v>
+      </c>
+      <c r="E201" t="s">
+        <v>58</v>
+      </c>
+      <c r="F201" t="s">
+        <v>166</v>
+      </c>
+      <c r="G201" t="s">
+        <v>124</v>
+      </c>
+      <c r="H201" t="s">
+        <v>18</v>
+      </c>
+      <c r="I201" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="15">
+      <c r="A202" t="s">
+        <v>214</v>
+      </c>
+      <c r="B202" t="s">
+        <v>36</v>
+      </c>
+      <c r="C202" t="s">
+        <v>179</v>
+      </c>
+      <c r="D202" t="s">
+        <v>180</v>
+      </c>
+      <c r="E202" t="s">
+        <v>74</v>
+      </c>
+      <c r="F202" t="s">
+        <v>75</v>
+      </c>
+      <c r="G202" t="s">
+        <v>76</v>
+      </c>
+      <c r="H202" t="s">
+        <v>18</v>
+      </c>
+      <c r="I202" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="15">
+      <c r="A203" t="s">
+        <v>214</v>
+      </c>
+      <c r="B203" t="s">
+        <v>30</v>
+      </c>
+      <c r="C203" t="s">
+        <v>241</v>
+      </c>
+      <c r="D203" t="s">
+        <v>207</v>
+      </c>
+      <c r="E203" t="s">
+        <v>190</v>
+      </c>
+      <c r="F203" t="s">
+        <v>107</v>
+      </c>
+      <c r="G203" t="s">
+        <v>242</v>
+      </c>
+      <c r="H203" t="s">
+        <v>18</v>
+      </c>
+      <c r="I203" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="15">
+      <c r="A204" t="s">
+        <v>214</v>
+      </c>
+      <c r="B204" t="s">
+        <v>36</v>
+      </c>
+      <c r="C204" t="s">
+        <v>241</v>
+      </c>
+      <c r="D204" t="s">
+        <v>207</v>
+      </c>
+      <c r="E204" t="s">
+        <v>190</v>
+      </c>
+      <c r="F204" t="s">
+        <v>107</v>
+      </c>
+      <c r="G204" t="s">
+        <v>242</v>
+      </c>
+      <c r="H204" t="s">
+        <v>18</v>
+      </c>
+      <c r="I204" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6715,7 +7268,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a41ac08b-8bbc-4a55-b3c2-f410ff95f184}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{3a5e703d-88ed-4e32-967c-ec15b425e94a}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6735,16 +7288,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6761,118 +7314,118 @@
     </row>
     <row r="2" spans="1:9" ht="15">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
       <c r="A4" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B4" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="A5" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B5" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -6883,7 +7436,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8ca045b7-9dd9-45dd-9d89-2cfebf7ba353}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{47621752-59d7-4c10-8ab0-2bb278d4f1b9}">
   <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6900,13 +7453,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6920,16 +7473,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -6940,16 +7493,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -6960,16 +7513,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="E4" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -6980,16 +7533,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="E5" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -7000,16 +7553,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="C6" t="s">
         <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="E6" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -7020,16 +7573,16 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="E7" t="s">
-        <v>243</v>
+        <v>108</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -7040,16 +7593,16 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -7060,16 +7613,16 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -7080,16 +7633,16 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="E10" t="s">
-        <v>119</v>
+        <v>267</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -7100,16 +7653,16 @@
         <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="E11" t="s">
-        <v>160</v>
+        <v>269</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -7120,16 +7673,16 @@
         <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>269</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -7140,16 +7693,16 @@
         <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="E13" t="s">
-        <v>249</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -7160,16 +7713,16 @@
         <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="E14" t="s">
-        <v>243</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -7177,19 +7730,19 @@
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B15" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C15" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="E15" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -7197,19 +7750,19 @@
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B16" t="s">
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="E16" t="s">
-        <v>252</v>
+        <v>191</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -7217,19 +7770,19 @@
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B17" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="C17" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="E17" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -7237,19 +7790,19 @@
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B18" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="C18" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="D18" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="E18" t="s">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -7257,19 +7810,19 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B19" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="C19" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="D19" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>272</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -7277,19 +7830,19 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="D20" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E20" t="s">
-        <v>254</v>
+        <v>124</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -7297,19 +7850,19 @@
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="D21" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E21" t="s">
-        <v>253</v>
+        <v>76</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -7317,19 +7870,19 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="C22" t="s">
         <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="E22" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -7337,19 +7890,19 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B23" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -7357,19 +7910,19 @@
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B24" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="E24" t="s">
-        <v>70</v>
+        <v>271</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -7377,39 +7930,39 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B25" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="D25" t="s">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="E25" t="s">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B26" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="E26" t="s">
-        <v>252</v>
+        <v>63</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -7417,39 +7970,39 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B27" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="C27" t="s">
-        <v>161</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="E27" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="F27" t="s">
-        <v>179</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B28" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="E28" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
@@ -7457,19 +8010,19 @@
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B29" t="s">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -7477,19 +8030,19 @@
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="E30" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
@@ -7497,19 +8050,19 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D31" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="E31" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -7517,19 +8070,19 @@
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
+        <v>259</v>
+      </c>
+      <c r="C32" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" t="s">
         <v>257</v>
       </c>
-      <c r="C32" t="s">
-        <v>41</v>
-      </c>
-      <c r="D32" t="s">
-        <v>255</v>
-      </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
@@ -7537,19 +8090,19 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -7557,19 +8110,19 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B34" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="D34" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
@@ -7577,19 +8130,19 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B35" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
@@ -7597,19 +8150,19 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B36" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
@@ -7617,19 +8170,19 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B37" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>271</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -7637,19 +8190,19 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>267</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
@@ -7657,19 +8210,19 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
+        <v>214</v>
+      </c>
+      <c r="B39" t="s">
+        <v>268</v>
+      </c>
+      <c r="C39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" t="s">
+        <v>274</v>
+      </c>
+      <c r="E39" t="s">
         <v>200</v>
-      </c>
-      <c r="B39" t="s">
-        <v>256</v>
-      </c>
-      <c r="C39" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" t="s">
-        <v>235</v>
-      </c>
-      <c r="E39" t="s">
-        <v>19</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
@@ -7677,19 +8230,19 @@
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B40" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="C40" t="s">
         <v>41</v>
       </c>
       <c r="D40" t="s">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="F40" t="s">
         <v>18</v>
@@ -7697,19 +8250,19 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B41" t="s">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="C41" t="s">
         <v>41</v>
       </c>
       <c r="D41" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F41" t="s">
         <v>18</v>
@@ -7717,19 +8270,19 @@
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B42" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="C42" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D42" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="F42" t="s">
         <v>18</v>
@@ -7737,19 +8290,19 @@
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B43" t="s">
+        <v>277</v>
+      </c>
+      <c r="C43" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" t="s">
         <v>257</v>
       </c>
-      <c r="C43" t="s">
-        <v>41</v>
-      </c>
-      <c r="D43" t="s">
-        <v>255</v>
-      </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>278</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -7757,19 +8310,19 @@
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B44" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C44" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D44" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>242</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="235">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -60,6 +60,72 @@
     <t>02.03.2026</t>
   </si>
   <si>
+    <t>1, 08:00-08:45</t>
+  </si>
+  <si>
+    <t>Jarek Zbigniew</t>
+  </si>
+  <si>
+    <t>1FB|JA2</t>
+  </si>
+  <si>
+    <t>Edukacja dla bezpieczeństwa</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Uczniowie przychodzą później</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Mikołajczak Sylwia</t>
+  </si>
+  <si>
+    <t>3FA</t>
+  </si>
+  <si>
+    <t>Podstawy fryzjerstwa</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Smirnow-Zechman Eleonora</t>
+  </si>
+  <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>Biznes i zarządzanie</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Stępień Krystyna</t>
+  </si>
+  <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>Technika w produkcji cukierniczej</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Kończyńska Małgorzata</t>
+  </si>
+  <si>
+    <t>Dodatkowo płatne</t>
+  </si>
+  <si>
     <t>2, 08:50-09:35</t>
   </si>
   <si>
@@ -72,21 +138,162 @@
     <t>Matematyka</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Uczniowie przychodzą później</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>-</t>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>2S</t>
+  </si>
+  <si>
+    <t>Biologia</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Małecka Barbara</t>
+  </si>
+  <si>
+    <t>Doradztwo zawodowe</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Krzemińska Beata</t>
   </si>
   <si>
     <t>3, 09:40-10:25</t>
   </si>
   <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>prF3</t>
+  </si>
+  <si>
+    <t>Sobczak Anna</t>
+  </si>
+  <si>
+    <t>Najwer Maciej</t>
+  </si>
+  <si>
+    <t>3TH|JA2</t>
+  </si>
+  <si>
+    <t>Informatyka</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>1TFB</t>
+  </si>
+  <si>
+    <t>Socha Dariusz</t>
+  </si>
+  <si>
+    <t>1CA</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>4, 10:35-11:20</t>
+  </si>
+  <si>
+    <t>3S</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Biezmienow Małgorzata</t>
+  </si>
+  <si>
+    <t>2FA</t>
+  </si>
+  <si>
+    <t>3CA</t>
+  </si>
+  <si>
+    <t>Zajęcia z wychowawcą</t>
+  </si>
+  <si>
+    <t>Kaszak Maria</t>
+  </si>
+  <si>
+    <t>5, 11:25-12:10</t>
+  </si>
+  <si>
+    <t>Chemia</t>
+  </si>
+  <si>
+    <t>2FC</t>
+  </si>
+  <si>
+    <t>Rejno Julita</t>
+  </si>
+  <si>
+    <t>1CA|DZ</t>
+  </si>
+  <si>
+    <t>Wychowanie fizyczne</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Antoszewska Joanna</t>
+  </si>
+  <si>
+    <t>6, 12:25-13:10</t>
+  </si>
+  <si>
+    <t>3K</t>
+  </si>
+  <si>
+    <t>Sałdyka Karolina</t>
+  </si>
+  <si>
+    <t>3TFB|JA2</t>
+  </si>
+  <si>
+    <t>Zajęcia biblioteczne</t>
+  </si>
+  <si>
+    <t>bib</t>
+  </si>
+  <si>
+    <t>Nowak Damiana</t>
+  </si>
+  <si>
+    <t>Bezpłatne</t>
+  </si>
+  <si>
+    <t>2TFB</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>Derezińska Katarzyna</t>
+  </si>
+  <si>
     <t>7, 13:15-14:00</t>
   </si>
   <si>
@@ -102,82 +309,22 @@
     <t>p. Sałdyka, biologia za lekcję 1</t>
   </si>
   <si>
-    <t>Hudziec Agnieszka</t>
-  </si>
-  <si>
-    <t>2S</t>
-  </si>
-  <si>
-    <t>Biologia</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Małecka Barbara</t>
-  </si>
-  <si>
-    <t>Dodatkowo płatne</t>
-  </si>
-  <si>
-    <t>3FA</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Karczmarz Aleksandra</t>
-  </si>
-  <si>
-    <t>4, 10:35-11:20</t>
-  </si>
-  <si>
-    <t>3S</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>Biezmienow Małgorzata</t>
-  </si>
-  <si>
-    <t>5, 11:25-12:10</t>
-  </si>
-  <si>
-    <t>2FA</t>
-  </si>
-  <si>
-    <t>Chemia</t>
-  </si>
-  <si>
-    <t>6, 12:25-13:10</t>
-  </si>
-  <si>
-    <t>3K</t>
-  </si>
-  <si>
-    <t>Doradztwo zawodowe</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Krzemińska Beata</t>
-  </si>
-  <si>
-    <t>1, 08:00-08:45</t>
-  </si>
-  <si>
-    <t>Jarek Zbigniew</t>
-  </si>
-  <si>
-    <t>1FB|JA2</t>
-  </si>
-  <si>
-    <t>Edukacja dla bezpieczeństwa</t>
+    <t>3TFA|JA1</t>
+  </si>
+  <si>
+    <t>Zając Ewa</t>
+  </si>
+  <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>Uczniowie zwolnieni do domu</t>
+  </si>
+  <si>
+    <t>8, 14:05-14:50</t>
+  </si>
+  <si>
+    <t>Leńczowska Iwona</t>
   </si>
   <si>
     <t>9, 14:55-15:40</t>
@@ -189,213 +336,204 @@
     <t>40</t>
   </si>
   <si>
-    <t>Uczniowie zwolnieni do domu</t>
-  </si>
-  <si>
-    <t>Mikołajczak Sylwia</t>
-  </si>
-  <si>
-    <t>Podstawy fryzjerstwa</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1FB</t>
-  </si>
-  <si>
-    <t>prF3</t>
-  </si>
-  <si>
-    <t>Sobczak Anna</t>
-  </si>
-  <si>
-    <t>2FC</t>
-  </si>
-  <si>
-    <t>Sałdyka Karolina</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t>8, 14:05-14:50</t>
-  </si>
-  <si>
-    <t>Leńczowska Iwona</t>
-  </si>
-  <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
-    <t>3TH|JA2</t>
-  </si>
-  <si>
-    <t>Informatyka</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>3TFB|JA2</t>
-  </si>
-  <si>
-    <t>Zajęcia biblioteczne</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>Nowak Damiana</t>
-  </si>
-  <si>
-    <t>Bezpłatne</t>
-  </si>
-  <si>
-    <t>3TFA|JA1</t>
-  </si>
-  <si>
-    <t>Zając Ewa</t>
-  </si>
-  <si>
-    <t>Rejno Julita</t>
-  </si>
-  <si>
-    <t>1CA|DZ</t>
-  </si>
-  <si>
-    <t>Wychowanie fizyczne</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Antoszewska Joanna</t>
-  </si>
-  <si>
-    <t>Smirnow-Zechman Eleonora</t>
-  </si>
-  <si>
-    <t>2TFA</t>
-  </si>
-  <si>
-    <t>Biznes i zarządzanie</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>1TFB</t>
-  </si>
-  <si>
-    <t>Socha Dariusz</t>
-  </si>
-  <si>
-    <t>1CA</t>
-  </si>
-  <si>
-    <t>2TFB</t>
-  </si>
-  <si>
-    <t>Danielewski Paweł</t>
-  </si>
-  <si>
-    <t>2TH</t>
-  </si>
-  <si>
-    <t>Stępień Krystyna</t>
-  </si>
-  <si>
-    <t>2CB</t>
-  </si>
-  <si>
-    <t>Technika w produkcji cukierniczej</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>Kończyńska Małgorzata</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>3CA</t>
-  </si>
-  <si>
-    <t>Zajęcia z wychowawcą</t>
-  </si>
-  <si>
-    <t>Bokuniewicz Sylwia</t>
-  </si>
-  <si>
-    <t>Język polski</t>
+    <t>03.03.2026</t>
+  </si>
+  <si>
+    <t>1TH|JA1</t>
+  </si>
+  <si>
+    <t>Wakat3 edukacja zdrow.</t>
+  </si>
+  <si>
+    <t>3CA|edu</t>
+  </si>
+  <si>
+    <t>Edukacja zdrowotna</t>
+  </si>
+  <si>
+    <t>Mocarski Arkadiusz</t>
+  </si>
+  <si>
+    <t>3FA|edu</t>
+  </si>
+  <si>
+    <t>3M|edu</t>
+  </si>
+  <si>
+    <t>3TFA|edu</t>
+  </si>
+  <si>
+    <t>3FA|dz1</t>
+  </si>
+  <si>
+    <t>sg2</t>
+  </si>
+  <si>
+    <t>Dalach Krystyna</t>
+  </si>
+  <si>
+    <t>sg4</t>
+  </si>
+  <si>
+    <t>Nestoruk Lidia</t>
+  </si>
+  <si>
+    <t>3FB</t>
+  </si>
+  <si>
+    <t>Świerzewicz Katarzyna</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>p. Pietrycha, wf za lekcję 2</t>
+  </si>
+  <si>
+    <t>3FA|JA1</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>3FA|JA2</t>
+  </si>
+  <si>
+    <t>1WB</t>
+  </si>
+  <si>
+    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
   </si>
   <si>
     <t>33</t>
   </si>
   <si>
-    <t>Derezińska Katarzyna</t>
-  </si>
-  <si>
-    <t>03.03.2026</t>
-  </si>
-  <si>
-    <t>1TH|JA1</t>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - barber</t>
+  </si>
+  <si>
+    <t>Jaworska Edyta</t>
   </si>
   <si>
     <t>1WB|JN1</t>
   </si>
   <si>
+    <t>Płatek Krzysztof</t>
+  </si>
+  <si>
+    <t>Paleczny Maciej</t>
+  </si>
+  <si>
+    <t>3CA|relu</t>
+  </si>
+  <si>
+    <t>Religia</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>3FA|relu</t>
+  </si>
+  <si>
+    <t>3FB|relu</t>
+  </si>
+  <si>
+    <t>3TFA|relu</t>
+  </si>
+  <si>
+    <t>3TFB|relu</t>
+  </si>
+  <si>
     <t>10, 15:45-16:30</t>
   </si>
   <si>
     <t>1TFA|JA1</t>
   </si>
   <si>
-    <t>2FB</t>
-  </si>
-  <si>
-    <t>1TFA</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Paleczny Maciej</t>
-  </si>
-  <si>
-    <t>3CA|relu</t>
-  </si>
-  <si>
-    <t>Religia</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>3FA|relu</t>
-  </si>
-  <si>
-    <t>3FB|relu</t>
-  </si>
-  <si>
-    <t>3TFA|relu</t>
-  </si>
-  <si>
-    <t>3TFB|relu</t>
-  </si>
-  <si>
-    <t>sg4</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>04.03.2026</t>
   </si>
   <si>
+    <t>1FC</t>
+  </si>
+  <si>
+    <t>1S</t>
+  </si>
+  <si>
+    <t>2CA|edu</t>
+  </si>
+  <si>
+    <t>2FC|edu</t>
+  </si>
+  <si>
+    <t>2S|edu</t>
+  </si>
+  <si>
+    <t>2WA|edu</t>
+  </si>
+  <si>
+    <t>5TF</t>
+  </si>
+  <si>
+    <t>1FA|JA1</t>
+  </si>
+  <si>
+    <t>1WA</t>
+  </si>
+  <si>
+    <t>2WB</t>
+  </si>
+  <si>
+    <t>sg3</t>
+  </si>
+  <si>
+    <t>Pietrycha Małgorzata</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>2K|CH</t>
+  </si>
+  <si>
+    <t>Wakat1 j. niemiecki</t>
+  </si>
+  <si>
+    <t>1WA|JN2</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
+    <t>Fizyka</t>
+  </si>
+  <si>
+    <t>Biczysko Wojciech</t>
+  </si>
+  <si>
     <t>2CA|relu</t>
   </si>
   <si>
@@ -408,30 +546,18 @@
     <t>2TH|relu</t>
   </si>
   <si>
-    <t>1FA|JA1</t>
-  </si>
-  <si>
-    <t>sg2</t>
-  </si>
-  <si>
-    <t>2K|CH</t>
-  </si>
-  <si>
-    <t>1S</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
-    <t>1WA</t>
-  </si>
-  <si>
-    <t>1FA</t>
-  </si>
-  <si>
     <t>05.03.2026</t>
   </si>
   <si>
+    <t>2WA</t>
+  </si>
+  <si>
+    <t>2TFB|JA1</t>
+  </si>
+  <si>
+    <t>2TFA|JA1</t>
+  </si>
+  <si>
     <t>1WB|JN2</t>
   </si>
   <si>
@@ -444,15 +570,15 @@
     <t>1CB|JA2</t>
   </si>
   <si>
-    <t>2TFB|JA1</t>
-  </si>
-  <si>
-    <t>2TFA|JA1</t>
-  </si>
-  <si>
     <t>06.03.2026</t>
   </si>
   <si>
+    <t>5TH</t>
+  </si>
+  <si>
+    <t>aq1</t>
+  </si>
+  <si>
     <t>1CB|JA1</t>
   </si>
   <si>
@@ -465,7 +591,10 @@
     <t>1WA|JN1</t>
   </si>
   <si>
-    <t>1WA|JN2</t>
+    <t>Wakat2 matematyka</t>
+  </si>
+  <si>
+    <t>Młynarczyk Paweł</t>
   </si>
   <si>
     <t>1S|JA2</t>
@@ -477,12 +606,6 @@
     <t>1S|JA1</t>
   </si>
   <si>
-    <t>5TH</t>
-  </si>
-  <si>
-    <t>aq1</t>
-  </si>
-  <si>
     <t>Godzina</t>
   </si>
   <si>
@@ -495,6 +618,15 @@
     <t>Opis zajęć</t>
   </si>
   <si>
+    <t>14:55-15:40</t>
+  </si>
+  <si>
+    <t>Krzysztof Miedziński - 3TFB - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>podstawy fryzjestwa/ projektowanie fryzur</t>
+  </si>
+  <si>
     <t>16:30-17:15</t>
   </si>
   <si>
@@ -504,15 +636,6 @@
     <t>matematyka</t>
   </si>
   <si>
-    <t>14:55-15:40</t>
-  </si>
-  <si>
-    <t>Krzysztof Miedziński - 3TFB - indywidualne nauczanie</t>
-  </si>
-  <si>
-    <t>podstawy fryzjestwa/ projektowanie fryzur</t>
-  </si>
-  <si>
     <t>12:20-13:05</t>
   </si>
   <si>
@@ -534,58 +657,76 @@
     <t>10:35-12:10</t>
   </si>
   <si>
+    <t>12:25-15:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kornelia Gałązka -  klasa 4TFB - indywidualne nauczanie </t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur- cztery godziny co piatek od 20.02.2026r.</t>
+  </si>
+  <si>
     <t>Miejsce dyżuru</t>
   </si>
   <si>
+    <t>07:55-08:00</t>
+  </si>
+  <si>
+    <t>boisko - dziedziniec wejściowy/boisko</t>
+  </si>
+  <si>
+    <t>parter</t>
+  </si>
+  <si>
     <t>09:35-09:40</t>
   </si>
   <si>
     <t>piętro_2</t>
   </si>
   <si>
+    <t>bramka wejściowa</t>
+  </si>
+  <si>
+    <t>Jastrzębska-Majtyka Agnieszka</t>
+  </si>
+  <si>
     <t>11:20-11:25</t>
   </si>
   <si>
     <t>piętro_1</t>
   </si>
   <si>
+    <t>12:10-12:25</t>
+  </si>
+  <si>
     <t>13:10-13:15</t>
   </si>
   <si>
     <t>Zaleska Magdalena</t>
   </si>
   <si>
-    <t>07:55-08:00</t>
-  </si>
-  <si>
-    <t>boisko - dziedziniec wejściowy/boisko</t>
-  </si>
-  <si>
-    <t>bramka wejściowa</t>
-  </si>
-  <si>
-    <t>Jastrzębska-Majtyka Agnieszka</t>
+    <t>14:00-14:05</t>
   </si>
   <si>
     <t>14:50-14:55</t>
   </si>
   <si>
-    <t>Kopij Marcin</t>
-  </si>
-  <si>
-    <t>14:00-14:05</t>
-  </si>
-  <si>
-    <t>Nestoruk Lidia</t>
-  </si>
-  <si>
-    <t>parter</t>
-  </si>
-  <si>
-    <t>12:10-12:25</t>
-  </si>
-  <si>
-    <t>Fiodorów Małgorzata</t>
+    <t>Wójcik Kamil</t>
+  </si>
+  <si>
+    <t>08:45-08:50</t>
+  </si>
+  <si>
+    <t>piętro_3</t>
+  </si>
+  <si>
+    <t>Nowaczyk Agnieszka</t>
+  </si>
+  <si>
+    <t>10:25-10:35</t>
+  </si>
+  <si>
+    <t>15:40-15:45</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1176,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{89dc003b-9a47-4d6b-9b9d-1fd685f4c371}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8cba3292-499f-4c8c-9ab2-048f2be187cf}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1056,8 +1197,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bc509059-e6d4-434e-8e65-f5dc164c5af1}">
-  <dimension ref="A1:I92"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{81b542b6-d09b-4f94-bd1b-5908e48be505}">
+  <dimension ref="A1:I147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1134,19 +1275,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
         <v>17</v>
@@ -1163,25 +1304,25 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
         <v>19</v>
@@ -1195,25 +1336,25 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -1221,28 +1362,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -1250,28 +1391,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
         <v>33</v>
-      </c>
-      <c r="F7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -1279,28 +1420,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
@@ -1308,28 +1449,28 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
       </c>
       <c r="I9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
@@ -1337,16 +1478,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
@@ -1366,28 +1507,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" t="s">
         <v>49</v>
       </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" t="s">
-        <v>55</v>
-      </c>
       <c r="H11" t="s">
         <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1395,28 +1536,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
@@ -1424,28 +1565,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
         <v>56</v>
       </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
       <c r="G13" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
@@ -1453,28 +1594,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="G14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H14" t="s">
         <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1482,28 +1623,28 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
@@ -1511,28 +1652,28 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
         <v>62</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -1540,28 +1681,28 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
         <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -1569,28 +1710,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="F18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" t="s">
         <v>58</v>
       </c>
-      <c r="G18" t="s">
-        <v>47</v>
-      </c>
       <c r="H18" t="s">
         <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1598,28 +1739,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -1627,19 +1768,19 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="G20" t="s">
         <v>17</v>
@@ -1656,28 +1797,28 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
         <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="G21" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="H21" t="s">
         <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
@@ -1685,28 +1826,28 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" t="s">
         <v>76</v>
       </c>
-      <c r="E22" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" t="s">
-        <v>73</v>
-      </c>
-      <c r="G22" t="s">
-        <v>77</v>
-      </c>
       <c r="H22" t="s">
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
@@ -1714,28 +1855,28 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="G23" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="H23" t="s">
         <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
@@ -1743,28 +1884,28 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="G24" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="H24" t="s">
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -1772,28 +1913,28 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s">
         <v>78</v>
       </c>
-      <c r="D25" t="s">
-        <v>79</v>
-      </c>
       <c r="E25" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="G25" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -1801,28 +1942,28 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
@@ -1830,28 +1971,28 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" t="s">
         <v>83</v>
       </c>
-      <c r="D27" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27" t="s">
-        <v>86</v>
-      </c>
-      <c r="G27" t="s">
-        <v>88</v>
-      </c>
       <c r="H27" t="s">
         <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -1859,28 +2000,28 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E28" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
@@ -1888,28 +2029,28 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s">
         <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
@@ -1917,28 +2058,28 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="E30" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G30" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
@@ -1946,25 +2087,25 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" t="s">
         <v>92</v>
       </c>
-      <c r="E31" t="s">
-        <v>85</v>
-      </c>
       <c r="F31" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s">
         <v>19</v>
@@ -1975,28 +2116,28 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="E32" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F32" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="G32" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
@@ -2004,28 +2145,28 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="D33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E33" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" t="s">
         <v>96</v>
       </c>
-      <c r="G33" t="s">
-        <v>97</v>
-      </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
@@ -2033,28 +2174,28 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E34" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="F34" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
@@ -2062,28 +2203,28 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
+        <v>27</v>
+      </c>
+      <c r="G35" t="s">
         <v>98</v>
       </c>
-      <c r="G35" t="s">
-        <v>101</v>
-      </c>
       <c r="H35" t="s">
         <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
@@ -2091,28 +2232,28 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="E36" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G36" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
@@ -2120,42 +2261,42 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E37" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="F37" t="s">
         <v>103</v>
       </c>
       <c r="G37" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -2164,7 +2305,7 @@
         <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
@@ -2175,228 +2316,228 @@
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="D39" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E39" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G39" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E40" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="F40" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="G40" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" t="s">
+        <v>111</v>
+      </c>
+      <c r="E41" t="s">
         <v>108</v>
       </c>
-      <c r="C41" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="F41" t="s">
+        <v>31</v>
+      </c>
+      <c r="G41" t="s">
         <v>109</v>
       </c>
-      <c r="E41" t="s">
-        <v>51</v>
-      </c>
-      <c r="F41" t="s">
-        <v>54</v>
-      </c>
-      <c r="G41" t="s">
-        <v>19</v>
-      </c>
       <c r="H41" t="s">
         <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="F42" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G42" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D43" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="E43" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="G43" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B44" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D44" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="E44" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F44" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="G44" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C45" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" t="s">
+        <v>118</v>
+      </c>
+      <c r="E45" t="s">
         <v>67</v>
       </c>
-      <c r="D45" t="s">
-        <v>92</v>
-      </c>
-      <c r="E45" t="s">
-        <v>69</v>
-      </c>
       <c r="F45" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="D46" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E46" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="F46" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G46" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
@@ -2407,173 +2548,173 @@
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C47" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="D47" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="E47" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="F47" t="s">
         <v>116</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" t="s">
         <v>52</v>
-      </c>
-      <c r="C48" t="s">
-        <v>113</v>
       </c>
       <c r="D48" t="s">
         <v>118</v>
       </c>
       <c r="E48" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="F48" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G48" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="E49" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="F49" t="s">
         <v>116</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B50" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" t="s">
         <v>52</v>
       </c>
-      <c r="C50" t="s">
-        <v>113</v>
-      </c>
       <c r="D50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E50" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="F50" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="G50" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="D51" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="E51" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F51" t="s">
-        <v>121</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B52" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52" t="s">
         <v>20</v>
       </c>
-      <c r="C52" t="s">
-        <v>78</v>
-      </c>
       <c r="D52" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="E52" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="F52" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="I52" t="s">
         <v>19</v>
@@ -2581,83 +2722,83 @@
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B53" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="C53" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="D53" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="E53" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F53" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="D54" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="E54" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="F54" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B55" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D55" t="s">
+        <v>57</v>
+      </c>
+      <c r="E55" t="s">
         <v>22</v>
       </c>
-      <c r="E55" t="s">
-        <v>15</v>
-      </c>
       <c r="F55" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G55" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
@@ -2668,170 +2809,170 @@
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B56" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E56" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="F56" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="G56" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D57" t="s">
+        <v>128</v>
+      </c>
+      <c r="E57" t="s">
+        <v>129</v>
+      </c>
+      <c r="F57" t="s">
+        <v>130</v>
+      </c>
+      <c r="G57" t="s">
         <v>109</v>
       </c>
-      <c r="E57" t="s">
-        <v>69</v>
-      </c>
-      <c r="F57" t="s">
-        <v>112</v>
-      </c>
-      <c r="G57" t="s">
-        <v>19</v>
-      </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="C58" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E58" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="F58" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G58" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" t="s">
+        <v>52</v>
+      </c>
+      <c r="D59" t="s">
         <v>123</v>
       </c>
-      <c r="B59" t="s">
-        <v>65</v>
-      </c>
-      <c r="C59" t="s">
-        <v>113</v>
-      </c>
-      <c r="D59" t="s">
-        <v>126</v>
-      </c>
       <c r="E59" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="F59" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="G59" t="s">
-        <v>19</v>
+        <v>136</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B60" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="C60" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E60" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="F60" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="G60" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="C61" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="D61" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="E61" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="F61" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="G61" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
@@ -2842,25 +2983,25 @@
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="C62" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="E62" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="F62" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="G62" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
@@ -2871,25 +3012,25 @@
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="C63" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="D63" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E63" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="F63" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="G63" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
@@ -2900,25 +3041,25 @@
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B64" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="C64" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="D64" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="E64" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="F64" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="G64" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
@@ -2929,25 +3070,25 @@
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B65" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="C65" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="D65" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E65" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="F65" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="G65" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
@@ -2958,54 +3099,54 @@
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="C66" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="E66" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="F66" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="G66" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="B67" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D67" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="E67" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F67" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="G67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
@@ -3016,25 +3157,25 @@
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="D68" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E68" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="F68" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="G68" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
@@ -3045,25 +3186,25 @@
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="B69" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C69" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="D69" t="s">
-        <v>133</v>
+        <v>65</v>
       </c>
       <c r="E69" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="F69" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="G69" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
@@ -3074,141 +3215,141 @@
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="B70" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C70" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="D70" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="E70" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="F70" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="G70" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="B71" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="D71" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="E71" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="F71" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="G71" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="B72" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="D72" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="E72" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="F72" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="G72" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B73" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="D73" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="E73" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="F73" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G73" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B74" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C74" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D74" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="E74" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F74" t="s">
         <v>16</v>
       </c>
       <c r="G74" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
@@ -3219,25 +3360,25 @@
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B75" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C75" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="D75" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="E75" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="F75" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G75" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
@@ -3248,54 +3389,54 @@
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B76" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="C76" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D76" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="E76" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F76" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="G76" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B77" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="C77" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="D77" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E77" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="F77" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="G77" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
@@ -3306,112 +3447,112 @@
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C78" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D78" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="E78" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="F78" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="G78" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B79" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C79" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="D79" t="s">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="E79" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F79" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="G79" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="C80" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D80" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="E80" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F80" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="G80" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B81" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C81" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="D81" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="E81" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="F81" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="G81" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
@@ -3422,141 +3563,141 @@
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B82" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82" t="s">
         <v>52</v>
       </c>
-      <c r="C82" t="s">
-        <v>78</v>
-      </c>
       <c r="D82" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="E82" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F82" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="G82" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B83" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="C83" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="D83" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="E83" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F83" t="s">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="G83" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B84" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C84" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D84" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E84" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F84" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="G84" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B85" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="C85" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D85" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="E85" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F85" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="G85" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B86" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C86" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="D86" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E86" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="F86" t="s">
-        <v>144</v>
+        <v>27</v>
       </c>
       <c r="G86" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
@@ -3567,175 +3708,1770 @@
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B87" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C87" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="D87" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="E87" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F87" t="s">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="G87" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B88" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="C88" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D88" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="E88" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F88" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="G88" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B89" t="s">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="C89" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D89" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="E89" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F89" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="G89" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B90" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="C90" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="D90" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="E90" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="F90" t="s">
-        <v>152</v>
+        <v>27</v>
       </c>
       <c r="G90" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B91" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C91" t="s">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="D91" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="E91" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="F91" t="s">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="G91" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B92" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="D92" t="s">
+        <v>36</v>
+      </c>
+      <c r="E92" t="s">
+        <v>168</v>
+      </c>
+      <c r="F92" t="s">
+        <v>23</v>
+      </c>
+      <c r="G92" t="s">
+        <v>169</v>
+      </c>
+      <c r="H92" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="15">
+      <c r="A93" t="s">
+        <v>149</v>
+      </c>
+      <c r="B93" t="s">
+        <v>90</v>
+      </c>
+      <c r="C93" t="s">
+        <v>100</v>
+      </c>
+      <c r="D93" t="s">
+        <v>150</v>
+      </c>
+      <c r="E93" t="s">
+        <v>43</v>
+      </c>
+      <c r="F93" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" t="s">
+        <v>45</v>
+      </c>
+      <c r="H93" t="s">
+        <v>18</v>
+      </c>
+      <c r="I93" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="15">
+      <c r="A94" t="s">
+        <v>149</v>
+      </c>
+      <c r="B94" t="s">
+        <v>90</v>
+      </c>
+      <c r="C94" t="s">
+        <v>72</v>
+      </c>
+      <c r="D94" t="s">
+        <v>163</v>
+      </c>
+      <c r="E94" t="s">
+        <v>74</v>
+      </c>
+      <c r="F94" t="s">
+        <v>114</v>
+      </c>
+      <c r="G94" t="s">
+        <v>115</v>
+      </c>
+      <c r="H94" t="s">
+        <v>18</v>
+      </c>
+      <c r="I94" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="15">
+      <c r="A95" t="s">
+        <v>149</v>
+      </c>
+      <c r="B95" t="s">
+        <v>90</v>
+      </c>
+      <c r="C95" t="s">
+        <v>24</v>
+      </c>
+      <c r="D95" t="s">
+        <v>162</v>
+      </c>
+      <c r="E95" t="s">
+        <v>26</v>
+      </c>
+      <c r="F95" t="s">
+        <v>27</v>
+      </c>
+      <c r="G95" t="s">
+        <v>109</v>
+      </c>
+      <c r="H95" t="s">
+        <v>18</v>
+      </c>
+      <c r="I95" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="15">
+      <c r="A96" t="s">
+        <v>149</v>
+      </c>
+      <c r="B96" t="s">
+        <v>99</v>
+      </c>
+      <c r="C96" t="s">
+        <v>100</v>
+      </c>
+      <c r="D96" t="s">
+        <v>150</v>
+      </c>
+      <c r="E96" t="s">
+        <v>86</v>
+      </c>
+      <c r="F96" t="s">
+        <v>23</v>
+      </c>
+      <c r="G96" t="s">
+        <v>98</v>
+      </c>
+      <c r="H96" t="s">
+        <v>18</v>
+      </c>
+      <c r="I96" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="15">
+      <c r="A97" t="s">
+        <v>149</v>
+      </c>
+      <c r="B97" t="s">
+        <v>99</v>
+      </c>
+      <c r="C97" t="s">
+        <v>139</v>
+      </c>
+      <c r="D97" t="s">
+        <v>170</v>
+      </c>
+      <c r="E97" t="s">
+        <v>141</v>
+      </c>
+      <c r="F97" t="s">
+        <v>171</v>
+      </c>
+      <c r="G97" t="s">
+        <v>98</v>
+      </c>
+      <c r="H97" t="s">
+        <v>18</v>
+      </c>
+      <c r="I97" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15">
+      <c r="A98" t="s">
+        <v>149</v>
+      </c>
+      <c r="B98" t="s">
+        <v>99</v>
+      </c>
+      <c r="C98" t="s">
+        <v>139</v>
+      </c>
+      <c r="D98" t="s">
+        <v>172</v>
+      </c>
+      <c r="E98" t="s">
+        <v>141</v>
+      </c>
+      <c r="F98" t="s">
+        <v>171</v>
+      </c>
+      <c r="G98" t="s">
+        <v>98</v>
+      </c>
+      <c r="H98" t="s">
+        <v>18</v>
+      </c>
+      <c r="I98" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="15">
+      <c r="A99" t="s">
+        <v>149</v>
+      </c>
+      <c r="B99" t="s">
+        <v>99</v>
+      </c>
+      <c r="C99" t="s">
+        <v>139</v>
+      </c>
+      <c r="D99" t="s">
+        <v>173</v>
+      </c>
+      <c r="E99" t="s">
+        <v>141</v>
+      </c>
+      <c r="F99" t="s">
+        <v>171</v>
+      </c>
+      <c r="G99" t="s">
+        <v>98</v>
+      </c>
+      <c r="H99" t="s">
+        <v>18</v>
+      </c>
+      <c r="I99" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="15">
+      <c r="A100" t="s">
+        <v>174</v>
+      </c>
+      <c r="B100" t="s">
+        <v>12</v>
+      </c>
+      <c r="C100" t="s">
+        <v>52</v>
+      </c>
+      <c r="D100" t="s">
+        <v>175</v>
+      </c>
+      <c r="E100" t="s">
+        <v>129</v>
+      </c>
+      <c r="F100" t="s">
+        <v>51</v>
+      </c>
+      <c r="G100" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100" t="s">
+        <v>18</v>
+      </c>
+      <c r="I100" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="15">
+      <c r="A101" t="s">
+        <v>174</v>
+      </c>
+      <c r="B101" t="s">
+        <v>34</v>
+      </c>
+      <c r="C101" t="s">
+        <v>20</v>
+      </c>
+      <c r="D101" t="s">
+        <v>150</v>
+      </c>
+      <c r="E101" t="s">
+        <v>22</v>
+      </c>
+      <c r="F101" t="s">
+        <v>23</v>
+      </c>
+      <c r="G101" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" t="s">
+        <v>18</v>
+      </c>
+      <c r="I101" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="15">
+      <c r="A102" t="s">
+        <v>174</v>
+      </c>
+      <c r="B102" t="s">
+        <v>34</v>
+      </c>
+      <c r="C102" t="s">
+        <v>52</v>
+      </c>
+      <c r="D102" t="s">
+        <v>175</v>
+      </c>
+      <c r="E102" t="s">
+        <v>129</v>
+      </c>
+      <c r="F102" t="s">
+        <v>51</v>
+      </c>
+      <c r="G102" t="s">
+        <v>19</v>
+      </c>
+      <c r="H102" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="15">
+      <c r="A103" t="s">
+        <v>174</v>
+      </c>
+      <c r="B103" t="s">
+        <v>46</v>
+      </c>
+      <c r="C103" t="s">
+        <v>20</v>
+      </c>
+      <c r="D103" t="s">
+        <v>25</v>
+      </c>
+      <c r="E103" t="s">
+        <v>22</v>
+      </c>
+      <c r="F103" t="s">
+        <v>23</v>
+      </c>
+      <c r="G103" t="s">
+        <v>19</v>
+      </c>
+      <c r="H103" t="s">
+        <v>18</v>
+      </c>
+      <c r="I103" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15">
+      <c r="A104" t="s">
+        <v>174</v>
+      </c>
+      <c r="B104" t="s">
+        <v>46</v>
+      </c>
+      <c r="C104" t="s">
+        <v>53</v>
+      </c>
+      <c r="D104" t="s">
+        <v>176</v>
+      </c>
+      <c r="E104" t="s">
+        <v>55</v>
+      </c>
+      <c r="F104" t="s">
+        <v>56</v>
+      </c>
+      <c r="G104" t="s">
+        <v>19</v>
+      </c>
+      <c r="H104" t="s">
+        <v>18</v>
+      </c>
+      <c r="I104" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="15">
+      <c r="A105" t="s">
+        <v>174</v>
+      </c>
+      <c r="B105" t="s">
+        <v>46</v>
+      </c>
+      <c r="C105" t="s">
+        <v>52</v>
+      </c>
+      <c r="D105" t="s">
+        <v>162</v>
+      </c>
+      <c r="E105" t="s">
+        <v>86</v>
+      </c>
+      <c r="F105" t="s">
+        <v>51</v>
+      </c>
+      <c r="G105" t="s">
+        <v>19</v>
+      </c>
+      <c r="H105" t="s">
+        <v>18</v>
+      </c>
+      <c r="I105" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="15">
+      <c r="A106" t="s">
+        <v>174</v>
+      </c>
+      <c r="B106" t="s">
+        <v>61</v>
+      </c>
+      <c r="C106" t="s">
+        <v>20</v>
+      </c>
+      <c r="D106" t="s">
+        <v>65</v>
+      </c>
+      <c r="E106" t="s">
+        <v>22</v>
+      </c>
+      <c r="F106" t="s">
+        <v>23</v>
+      </c>
+      <c r="G106" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" t="s">
+        <v>18</v>
+      </c>
+      <c r="I106" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="15">
+      <c r="A107" t="s">
+        <v>174</v>
+      </c>
+      <c r="B107" t="s">
+        <v>61</v>
+      </c>
+      <c r="C107" t="s">
+        <v>52</v>
+      </c>
+      <c r="D107" t="s">
+        <v>162</v>
+      </c>
+      <c r="E107" t="s">
+        <v>86</v>
+      </c>
+      <c r="F107" t="s">
+        <v>51</v>
+      </c>
+      <c r="G107" t="s">
+        <v>19</v>
+      </c>
+      <c r="H107" t="s">
+        <v>18</v>
+      </c>
+      <c r="I107" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15">
+      <c r="A108" t="s">
+        <v>174</v>
+      </c>
+      <c r="B108" t="s">
+        <v>69</v>
+      </c>
+      <c r="C108" t="s">
+        <v>20</v>
+      </c>
+      <c r="D108" t="s">
+        <v>118</v>
+      </c>
+      <c r="E108" t="s">
+        <v>22</v>
+      </c>
+      <c r="F108" t="s">
+        <v>23</v>
+      </c>
+      <c r="G108" t="s">
+        <v>19</v>
+      </c>
+      <c r="H108" t="s">
+        <v>18</v>
+      </c>
+      <c r="I108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15">
+      <c r="A109" t="s">
+        <v>174</v>
+      </c>
+      <c r="B109" t="s">
+        <v>69</v>
+      </c>
+      <c r="C109" t="s">
+        <v>53</v>
+      </c>
+      <c r="D109" t="s">
+        <v>177</v>
+      </c>
+      <c r="E109" t="s">
+        <v>55</v>
+      </c>
+      <c r="F109" t="s">
+        <v>56</v>
+      </c>
+      <c r="G109" t="s">
+        <v>19</v>
+      </c>
+      <c r="H109" t="s">
+        <v>18</v>
+      </c>
+      <c r="I109" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="15">
+      <c r="A110" t="s">
+        <v>174</v>
+      </c>
+      <c r="B110" t="s">
+        <v>69</v>
+      </c>
+      <c r="C110" t="s">
+        <v>52</v>
+      </c>
+      <c r="D110" t="s">
+        <v>131</v>
+      </c>
+      <c r="E110" t="s">
+        <v>86</v>
+      </c>
+      <c r="F110" t="s">
+        <v>51</v>
+      </c>
+      <c r="G110" t="s">
+        <v>19</v>
+      </c>
+      <c r="H110" t="s">
+        <v>18</v>
+      </c>
+      <c r="I110" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="15">
+      <c r="A111" t="s">
+        <v>174</v>
+      </c>
+      <c r="B111" t="s">
+        <v>77</v>
+      </c>
+      <c r="C111" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" t="s">
+        <v>162</v>
+      </c>
+      <c r="E111" t="s">
+        <v>22</v>
+      </c>
+      <c r="F111" t="s">
+        <v>23</v>
+      </c>
+      <c r="G111" t="s">
+        <v>19</v>
+      </c>
+      <c r="H111" t="s">
+        <v>18</v>
+      </c>
+      <c r="I111" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="15">
+      <c r="A112" t="s">
+        <v>174</v>
+      </c>
+      <c r="B112" t="s">
+        <v>90</v>
+      </c>
+      <c r="C112" t="s">
+        <v>35</v>
+      </c>
+      <c r="D112" t="s">
+        <v>91</v>
+      </c>
+      <c r="E112" t="s">
+        <v>37</v>
+      </c>
+      <c r="F112" t="s">
+        <v>16</v>
+      </c>
+      <c r="G112" t="s">
+        <v>19</v>
+      </c>
+      <c r="H112" t="s">
+        <v>18</v>
+      </c>
+      <c r="I112" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="15">
+      <c r="A113" t="s">
+        <v>174</v>
+      </c>
+      <c r="B113" t="s">
+        <v>90</v>
+      </c>
+      <c r="C113" t="s">
+        <v>20</v>
+      </c>
+      <c r="D113" t="s">
+        <v>85</v>
+      </c>
+      <c r="E113" t="s">
+        <v>22</v>
+      </c>
+      <c r="F113" t="s">
+        <v>23</v>
+      </c>
+      <c r="G113" t="s">
+        <v>19</v>
+      </c>
+      <c r="H113" t="s">
+        <v>18</v>
+      </c>
+      <c r="I113" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="15">
+      <c r="A114" t="s">
+        <v>174</v>
+      </c>
+      <c r="B114" t="s">
+        <v>90</v>
+      </c>
+      <c r="C114" t="s">
+        <v>53</v>
+      </c>
+      <c r="D114" t="s">
+        <v>148</v>
+      </c>
+      <c r="E114" t="s">
+        <v>55</v>
+      </c>
+      <c r="F114" t="s">
+        <v>56</v>
+      </c>
+      <c r="G114" t="s">
+        <v>19</v>
+      </c>
+      <c r="H114" t="s">
+        <v>18</v>
+      </c>
+      <c r="I114" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="15">
+      <c r="A115" t="s">
+        <v>174</v>
+      </c>
+      <c r="B115" t="s">
+        <v>99</v>
+      </c>
+      <c r="C115" t="s">
+        <v>35</v>
+      </c>
+      <c r="D115" t="s">
+        <v>91</v>
+      </c>
+      <c r="E115" t="s">
+        <v>37</v>
+      </c>
+      <c r="F115" t="s">
+        <v>16</v>
+      </c>
+      <c r="G115" t="s">
+        <v>19</v>
+      </c>
+      <c r="H115" t="s">
+        <v>18</v>
+      </c>
+      <c r="I115" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="15">
+      <c r="A116" t="s">
+        <v>174</v>
+      </c>
+      <c r="B116" t="s">
+        <v>99</v>
+      </c>
+      <c r="C116" t="s">
+        <v>72</v>
+      </c>
+      <c r="D116" t="s">
+        <v>148</v>
+      </c>
+      <c r="E116" t="s">
+        <v>74</v>
+      </c>
+      <c r="F116" t="s">
+        <v>114</v>
+      </c>
+      <c r="G116" t="s">
+        <v>115</v>
+      </c>
+      <c r="H116" t="s">
+        <v>18</v>
+      </c>
+      <c r="I116" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="15">
+      <c r="A117" t="s">
+        <v>174</v>
+      </c>
+      <c r="B117" t="s">
+        <v>101</v>
+      </c>
+      <c r="C117" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E117" t="s">
+        <v>15</v>
+      </c>
+      <c r="F117" t="s">
+        <v>103</v>
+      </c>
+      <c r="G117" t="s">
+        <v>19</v>
+      </c>
+      <c r="H117" t="s">
+        <v>18</v>
+      </c>
+      <c r="I117" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="15">
+      <c r="A118" t="s">
+        <v>174</v>
+      </c>
+      <c r="B118" t="s">
+        <v>101</v>
+      </c>
+      <c r="C118" t="s">
+        <v>20</v>
+      </c>
+      <c r="D118" t="s">
+        <v>91</v>
+      </c>
+      <c r="E118" t="s">
+        <v>22</v>
+      </c>
+      <c r="F118" t="s">
+        <v>23</v>
+      </c>
+      <c r="G118" t="s">
+        <v>19</v>
+      </c>
+      <c r="H118" t="s">
+        <v>18</v>
+      </c>
+      <c r="I118" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="15">
+      <c r="A119" t="s">
+        <v>174</v>
+      </c>
+      <c r="B119" t="s">
+        <v>101</v>
+      </c>
+      <c r="C119" t="s">
+        <v>72</v>
+      </c>
+      <c r="D119" t="s">
+        <v>148</v>
+      </c>
+      <c r="E119" t="s">
+        <v>74</v>
+      </c>
+      <c r="F119" t="s">
+        <v>114</v>
+      </c>
+      <c r="G119" t="s">
+        <v>115</v>
+      </c>
+      <c r="H119" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="15">
+      <c r="A120" t="s">
+        <v>174</v>
+      </c>
+      <c r="B120" t="s">
+        <v>147</v>
+      </c>
+      <c r="C120" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" t="s">
+        <v>179</v>
+      </c>
+      <c r="E120" t="s">
+        <v>15</v>
+      </c>
+      <c r="F120" t="s">
+        <v>103</v>
+      </c>
+      <c r="G120" t="s">
+        <v>19</v>
+      </c>
+      <c r="H120" t="s">
+        <v>18</v>
+      </c>
+      <c r="I120" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="15">
+      <c r="A121" t="s">
+        <v>174</v>
+      </c>
+      <c r="B121" t="s">
+        <v>147</v>
+      </c>
+      <c r="C121" t="s">
+        <v>72</v>
+      </c>
+      <c r="D121" t="s">
+        <v>148</v>
+      </c>
+      <c r="E121" t="s">
+        <v>74</v>
+      </c>
+      <c r="F121" t="s">
+        <v>114</v>
+      </c>
+      <c r="G121" t="s">
+        <v>115</v>
+      </c>
+      <c r="H121" t="s">
+        <v>18</v>
+      </c>
+      <c r="I121" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="15">
+      <c r="A122" t="s">
+        <v>174</v>
+      </c>
+      <c r="B122" t="s">
+        <v>180</v>
+      </c>
+      <c r="C122" t="s">
+        <v>13</v>
+      </c>
+      <c r="D122" t="s">
+        <v>181</v>
+      </c>
+      <c r="E122" t="s">
+        <v>15</v>
+      </c>
+      <c r="F122" t="s">
+        <v>103</v>
+      </c>
+      <c r="G122" t="s">
+        <v>19</v>
+      </c>
+      <c r="H122" t="s">
+        <v>18</v>
+      </c>
+      <c r="I122" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="15">
+      <c r="A123" t="s">
+        <v>182</v>
+      </c>
+      <c r="B123" t="s">
+        <v>12</v>
+      </c>
+      <c r="C123" t="s">
+        <v>20</v>
+      </c>
+      <c r="D123" t="s">
+        <v>25</v>
+      </c>
+      <c r="E123" t="s">
+        <v>22</v>
+      </c>
+      <c r="F123" t="s">
+        <v>23</v>
+      </c>
+      <c r="G123" t="s">
+        <v>19</v>
+      </c>
+      <c r="H123" t="s">
+        <v>18</v>
+      </c>
+      <c r="I123" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="15">
+      <c r="A124" t="s">
+        <v>182</v>
+      </c>
+      <c r="B124" t="s">
+        <v>34</v>
+      </c>
+      <c r="C124" t="s">
+        <v>20</v>
+      </c>
+      <c r="D124" t="s">
+        <v>85</v>
+      </c>
+      <c r="E124" t="s">
+        <v>22</v>
+      </c>
+      <c r="F124" t="s">
+        <v>23</v>
+      </c>
+      <c r="G124" t="s">
+        <v>19</v>
+      </c>
+      <c r="H124" t="s">
+        <v>18</v>
+      </c>
+      <c r="I124" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="15">
+      <c r="A125" t="s">
+        <v>182</v>
+      </c>
+      <c r="B125" t="s">
+        <v>46</v>
+      </c>
+      <c r="C125" t="s">
+        <v>20</v>
+      </c>
+      <c r="D125" t="s">
+        <v>71</v>
+      </c>
+      <c r="E125" t="s">
+        <v>22</v>
+      </c>
+      <c r="F125" t="s">
+        <v>23</v>
+      </c>
+      <c r="G125" t="s">
+        <v>19</v>
+      </c>
+      <c r="H125" t="s">
+        <v>18</v>
+      </c>
+      <c r="I125" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="15">
+      <c r="A126" t="s">
+        <v>182</v>
+      </c>
+      <c r="B126" t="s">
+        <v>46</v>
+      </c>
+      <c r="C126" t="s">
+        <v>72</v>
+      </c>
+      <c r="D126" t="s">
+        <v>183</v>
+      </c>
+      <c r="E126" t="s">
+        <v>74</v>
+      </c>
+      <c r="F126" t="s">
+        <v>184</v>
+      </c>
+      <c r="G126" t="s">
+        <v>115</v>
+      </c>
+      <c r="H126" t="s">
+        <v>18</v>
+      </c>
+      <c r="I126" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="15">
+      <c r="A127" t="s">
+        <v>182</v>
+      </c>
+      <c r="B127" t="s">
+        <v>46</v>
+      </c>
+      <c r="C127" t="s">
+        <v>52</v>
+      </c>
+      <c r="D127" t="s">
+        <v>162</v>
+      </c>
+      <c r="E127" t="s">
+        <v>86</v>
+      </c>
+      <c r="F127" t="s">
+        <v>51</v>
+      </c>
+      <c r="G127" t="s">
+        <v>19</v>
+      </c>
+      <c r="H127" t="s">
+        <v>18</v>
+      </c>
+      <c r="I127" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="15">
+      <c r="A128" t="s">
+        <v>182</v>
+      </c>
+      <c r="B128" t="s">
+        <v>61</v>
+      </c>
+      <c r="C128" t="s">
+        <v>20</v>
+      </c>
+      <c r="D128" t="s">
+        <v>123</v>
+      </c>
+      <c r="E128" t="s">
+        <v>22</v>
+      </c>
+      <c r="F128" t="s">
+        <v>23</v>
+      </c>
+      <c r="G128" t="s">
+        <v>19</v>
+      </c>
+      <c r="H128" t="s">
+        <v>18</v>
+      </c>
+      <c r="I128" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="15">
+      <c r="A129" t="s">
+        <v>182</v>
+      </c>
+      <c r="B129" t="s">
+        <v>61</v>
+      </c>
+      <c r="C129" t="s">
+        <v>72</v>
+      </c>
+      <c r="D129" t="s">
+        <v>183</v>
+      </c>
+      <c r="E129" t="s">
+        <v>74</v>
+      </c>
+      <c r="F129" t="s">
+        <v>184</v>
+      </c>
+      <c r="G129" t="s">
+        <v>115</v>
+      </c>
+      <c r="H129" t="s">
+        <v>18</v>
+      </c>
+      <c r="I129" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="15">
+      <c r="A130" t="s">
+        <v>182</v>
+      </c>
+      <c r="B130" t="s">
+        <v>61</v>
+      </c>
+      <c r="C130" t="s">
+        <v>52</v>
+      </c>
+      <c r="D130" t="s">
+        <v>162</v>
+      </c>
+      <c r="E130" t="s">
+        <v>86</v>
+      </c>
+      <c r="F130" t="s">
+        <v>51</v>
+      </c>
+      <c r="G130" t="s">
+        <v>19</v>
+      </c>
+      <c r="H130" t="s">
+        <v>18</v>
+      </c>
+      <c r="I130" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="15">
+      <c r="A131" t="s">
+        <v>182</v>
+      </c>
+      <c r="B131" t="s">
+        <v>69</v>
+      </c>
+      <c r="C131" t="s">
+        <v>20</v>
+      </c>
+      <c r="D131" t="s">
+        <v>71</v>
+      </c>
+      <c r="E131" t="s">
+        <v>86</v>
+      </c>
+      <c r="F131" t="s">
+        <v>23</v>
+      </c>
+      <c r="G131" t="s">
+        <v>19</v>
+      </c>
+      <c r="H131" t="s">
+        <v>18</v>
+      </c>
+      <c r="I131" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="15">
+      <c r="A132" t="s">
+        <v>182</v>
+      </c>
+      <c r="B132" t="s">
+        <v>69</v>
+      </c>
+      <c r="C132" t="s">
+        <v>72</v>
+      </c>
+      <c r="D132" t="s">
+        <v>183</v>
+      </c>
+      <c r="E132" t="s">
+        <v>81</v>
+      </c>
+      <c r="F132" t="s">
+        <v>82</v>
+      </c>
+      <c r="G132" t="s">
+        <v>83</v>
+      </c>
+      <c r="H132" t="s">
+        <v>18</v>
+      </c>
+      <c r="I132" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="15">
+      <c r="A133" t="s">
+        <v>182</v>
+      </c>
+      <c r="B133" t="s">
+        <v>69</v>
+      </c>
+      <c r="C133" t="s">
+        <v>52</v>
+      </c>
+      <c r="D133" t="s">
+        <v>158</v>
+      </c>
+      <c r="E133" t="s">
+        <v>129</v>
+      </c>
+      <c r="F133" t="s">
+        <v>51</v>
+      </c>
+      <c r="G133" t="s">
+        <v>19</v>
+      </c>
+      <c r="H133" t="s">
+        <v>18</v>
+      </c>
+      <c r="I133" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="15">
+      <c r="A134" t="s">
+        <v>182</v>
+      </c>
+      <c r="B134" t="s">
+        <v>77</v>
+      </c>
+      <c r="C134" t="s">
+        <v>13</v>
+      </c>
+      <c r="D134" t="s">
+        <v>185</v>
+      </c>
+      <c r="E134" t="s">
+        <v>15</v>
+      </c>
+      <c r="F134" t="s">
+        <v>186</v>
+      </c>
+      <c r="G134" t="s">
+        <v>19</v>
+      </c>
+      <c r="H134" t="s">
+        <v>18</v>
+      </c>
+      <c r="I134" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="15">
+      <c r="A135" t="s">
+        <v>182</v>
+      </c>
+      <c r="B135" t="s">
+        <v>77</v>
+      </c>
+      <c r="C135" t="s">
+        <v>20</v>
+      </c>
+      <c r="D135" t="s">
+        <v>71</v>
+      </c>
+      <c r="E135" t="s">
+        <v>86</v>
+      </c>
+      <c r="F135" t="s">
+        <v>23</v>
+      </c>
+      <c r="G135" t="s">
+        <v>19</v>
+      </c>
+      <c r="H135" t="s">
+        <v>18</v>
+      </c>
+      <c r="I135" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="15">
+      <c r="A136" t="s">
+        <v>182</v>
+      </c>
+      <c r="B136" t="s">
+        <v>77</v>
+      </c>
+      <c r="C136" t="s">
+        <v>52</v>
+      </c>
+      <c r="D136" t="s">
+        <v>131</v>
+      </c>
+      <c r="E136" t="s">
+        <v>86</v>
+      </c>
+      <c r="F136" t="s">
+        <v>51</v>
+      </c>
+      <c r="G136" t="s">
+        <v>19</v>
+      </c>
+      <c r="H136" t="s">
+        <v>18</v>
+      </c>
+      <c r="I136" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="15">
+      <c r="A137" t="s">
+        <v>182</v>
+      </c>
+      <c r="B137" t="s">
+        <v>90</v>
+      </c>
+      <c r="C137" t="s">
+        <v>13</v>
+      </c>
+      <c r="D137" t="s">
+        <v>187</v>
+      </c>
+      <c r="E137" t="s">
+        <v>15</v>
+      </c>
+      <c r="F137" t="s">
+        <v>186</v>
+      </c>
+      <c r="G137" t="s">
+        <v>19</v>
+      </c>
+      <c r="H137" t="s">
+        <v>18</v>
+      </c>
+      <c r="I137" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="15">
+      <c r="A138" t="s">
+        <v>182</v>
+      </c>
+      <c r="B138" t="s">
+        <v>90</v>
+      </c>
+      <c r="C138" t="s">
+        <v>52</v>
+      </c>
+      <c r="D138" t="s">
+        <v>131</v>
+      </c>
+      <c r="E138" t="s">
+        <v>86</v>
+      </c>
+      <c r="F138" t="s">
+        <v>51</v>
+      </c>
+      <c r="G138" t="s">
+        <v>19</v>
+      </c>
+      <c r="H138" t="s">
+        <v>18</v>
+      </c>
+      <c r="I138" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="15">
+      <c r="A139" t="s">
+        <v>182</v>
+      </c>
+      <c r="B139" t="s">
+        <v>99</v>
+      </c>
+      <c r="C139" t="s">
+        <v>13</v>
+      </c>
+      <c r="D139" t="s">
+        <v>188</v>
+      </c>
+      <c r="E139" t="s">
+        <v>15</v>
+      </c>
+      <c r="F139" t="s">
+        <v>186</v>
+      </c>
+      <c r="G139" t="s">
+        <v>19</v>
+      </c>
+      <c r="H139" t="s">
+        <v>18</v>
+      </c>
+      <c r="I139" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="15">
+      <c r="A140" t="s">
+        <v>182</v>
+      </c>
+      <c r="B140" t="s">
+        <v>99</v>
+      </c>
+      <c r="C140" t="s">
+        <v>52</v>
+      </c>
+      <c r="D140" t="s">
+        <v>71</v>
+      </c>
+      <c r="E140" t="s">
+        <v>135</v>
+      </c>
+      <c r="F140" t="s">
+        <v>51</v>
+      </c>
+      <c r="G140" t="s">
+        <v>19</v>
+      </c>
+      <c r="H140" t="s">
+        <v>18</v>
+      </c>
+      <c r="I140" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="15">
+      <c r="A141" t="s">
+        <v>182</v>
+      </c>
+      <c r="B141" t="s">
+        <v>99</v>
+      </c>
+      <c r="C141" t="s">
+        <v>164</v>
+      </c>
+      <c r="D141" t="s">
+        <v>165</v>
+      </c>
+      <c r="E141" t="s">
+        <v>166</v>
+      </c>
+      <c r="F141" t="s">
+        <v>16</v>
+      </c>
+      <c r="G141" t="s">
+        <v>167</v>
+      </c>
+      <c r="H141" t="s">
+        <v>18</v>
+      </c>
+      <c r="I141" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="15">
+      <c r="A142" t="s">
+        <v>182</v>
+      </c>
+      <c r="B142" t="s">
+        <v>99</v>
+      </c>
+      <c r="C142" t="s">
+        <v>189</v>
+      </c>
+      <c r="D142" t="s">
         <v>151</v>
       </c>
-      <c r="E92" t="s">
-        <v>80</v>
-      </c>
-      <c r="F92" t="s">
-        <v>152</v>
-      </c>
-      <c r="G92" t="s">
-        <v>19</v>
-      </c>
-      <c r="H92" t="s">
-        <v>18</v>
-      </c>
-      <c r="I92" t="s">
+      <c r="E142" t="s">
+        <v>37</v>
+      </c>
+      <c r="F142" t="s">
+        <v>41</v>
+      </c>
+      <c r="G142" t="s">
+        <v>190</v>
+      </c>
+      <c r="H142" t="s">
+        <v>18</v>
+      </c>
+      <c r="I142" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="15">
+      <c r="A143" t="s">
+        <v>182</v>
+      </c>
+      <c r="B143" t="s">
+        <v>101</v>
+      </c>
+      <c r="C143" t="s">
+        <v>13</v>
+      </c>
+      <c r="D143" t="s">
+        <v>165</v>
+      </c>
+      <c r="E143" t="s">
+        <v>15</v>
+      </c>
+      <c r="F143" t="s">
+        <v>186</v>
+      </c>
+      <c r="G143" t="s">
+        <v>19</v>
+      </c>
+      <c r="H143" t="s">
+        <v>18</v>
+      </c>
+      <c r="I143" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="15">
+      <c r="A144" t="s">
+        <v>182</v>
+      </c>
+      <c r="B144" t="s">
+        <v>101</v>
+      </c>
+      <c r="C144" t="s">
+        <v>52</v>
+      </c>
+      <c r="D144" t="s">
+        <v>123</v>
+      </c>
+      <c r="E144" t="s">
+        <v>135</v>
+      </c>
+      <c r="F144" t="s">
+        <v>51</v>
+      </c>
+      <c r="G144" t="s">
+        <v>19</v>
+      </c>
+      <c r="H144" t="s">
+        <v>18</v>
+      </c>
+      <c r="I144" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="15">
+      <c r="A145" t="s">
+        <v>182</v>
+      </c>
+      <c r="B145" t="s">
+        <v>101</v>
+      </c>
+      <c r="C145" t="s">
+        <v>189</v>
+      </c>
+      <c r="D145" t="s">
+        <v>151</v>
+      </c>
+      <c r="E145" t="s">
+        <v>37</v>
+      </c>
+      <c r="F145" t="s">
+        <v>41</v>
+      </c>
+      <c r="G145" t="s">
+        <v>190</v>
+      </c>
+      <c r="H145" t="s">
+        <v>18</v>
+      </c>
+      <c r="I145" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="15">
+      <c r="A146" t="s">
+        <v>182</v>
+      </c>
+      <c r="B146" t="s">
+        <v>147</v>
+      </c>
+      <c r="C146" t="s">
+        <v>13</v>
+      </c>
+      <c r="D146" t="s">
+        <v>191</v>
+      </c>
+      <c r="E146" t="s">
+        <v>15</v>
+      </c>
+      <c r="F146" t="s">
+        <v>186</v>
+      </c>
+      <c r="G146" t="s">
+        <v>19</v>
+      </c>
+      <c r="H146" t="s">
+        <v>18</v>
+      </c>
+      <c r="I146" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="15">
+      <c r="A147" t="s">
+        <v>182</v>
+      </c>
+      <c r="B147" t="s">
+        <v>192</v>
+      </c>
+      <c r="C147" t="s">
+        <v>13</v>
+      </c>
+      <c r="D147" t="s">
+        <v>193</v>
+      </c>
+      <c r="E147" t="s">
+        <v>15</v>
+      </c>
+      <c r="F147" t="s">
+        <v>103</v>
+      </c>
+      <c r="G147" t="s">
+        <v>19</v>
+      </c>
+      <c r="H147" t="s">
+        <v>18</v>
+      </c>
+      <c r="I147" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3747,15 +5483,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{47625ccf-cb96-4608-8ce8-8b7bfdde0654}">
-  <dimension ref="A1:I8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{10040908-ce08-4b76-90b9-7c2f370351db}">
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="17.7142857142857" customWidth="1"/>
-    <col min="4" max="4" width="48" customWidth="1"/>
-    <col min="5" max="5" width="46.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="50.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="55.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="11.4285714285714" customWidth="1"/>
     <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
@@ -3767,16 +5503,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -3796,16 +5532,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="E2" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -3825,16 +5561,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -3851,19 +5587,19 @@
     </row>
     <row r="4" spans="1:9" ht="15">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="E4" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -3880,19 +5616,19 @@
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>199</v>
       </c>
       <c r="E5" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -3909,19 +5645,19 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="E6" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -3938,19 +5674,19 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="E7" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -3967,19 +5703,19 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="E8" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -3991,6 +5727,35 @@
         <v>18</v>
       </c>
       <c r="I8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15">
+      <c r="A9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>212</v>
+      </c>
+      <c r="E9" t="s">
+        <v>213</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4002,8 +5767,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e4600b03-f857-4b4d-9ee8-dcdb00f4f4a5}">
-  <dimension ref="A1:F12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4df6047a-ba4e-4eee-8729-5c053d7890eb}">
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -4019,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -4039,16 +5804,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>216</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -4059,16 +5824,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -4079,16 +5844,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>219</v>
       </c>
       <c r="E4" t="s">
-        <v>176</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -4099,16 +5864,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>221</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -4119,16 +5884,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -4139,16 +5904,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="E7" t="s">
-        <v>182</v>
+        <v>58</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -4159,16 +5924,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="E8" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -4179,16 +5944,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="E9" t="s">
-        <v>66</v>
+        <v>226</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -4199,16 +5964,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>171</v>
+        <v>227</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="E10" t="s">
-        <v>182</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -4219,16 +5984,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="E11" t="s">
-        <v>187</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -4239,18 +6004,278 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="F12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15">
+      <c r="A13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>217</v>
+      </c>
+      <c r="E13" t="s">
+        <v>229</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15">
+      <c r="A14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
+        <v>216</v>
+      </c>
+      <c r="E14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15">
+      <c r="A15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" t="s">
+        <v>224</v>
+      </c>
+      <c r="C15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" t="s">
+        <v>231</v>
+      </c>
+      <c r="E15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15">
+      <c r="A16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>216</v>
+      </c>
+      <c r="E16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15">
+      <c r="A17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" t="s">
+        <v>227</v>
+      </c>
+      <c r="C17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" t="s">
+        <v>216</v>
+      </c>
+      <c r="E17" t="s">
+        <v>232</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15">
+      <c r="A18" t="s">
+        <v>149</v>
+      </c>
+      <c r="B18" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>216</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15">
+      <c r="A19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15">
+      <c r="A20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" t="s">
+        <v>228</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" t="s">
+        <v>216</v>
+      </c>
+      <c r="E20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15">
+      <c r="A21" t="s">
+        <v>174</v>
+      </c>
+      <c r="B21" t="s">
+        <v>215</v>
+      </c>
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" t="s">
+        <v>216</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15">
+      <c r="A22" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>220</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15">
+      <c r="A23" t="s">
+        <v>182</v>
+      </c>
+      <c r="B23" t="s">
+        <v>218</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>216</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15">
+      <c r="A24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B24" t="s">
+        <v>233</v>
+      </c>
+      <c r="C24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" t="s">
+        <v>216</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15">
+      <c r="A25" t="s">
+        <v>182</v>
+      </c>
+      <c r="B25" t="s">
+        <v>234</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" t="s">
+        <v>216</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
         <v>18</v>
       </c>
     </row>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="247">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -384,6 +384,9 @@
     <t>Świerzewicz Katarzyna</t>
   </si>
   <si>
+    <t>1TFB|JA1</t>
+  </si>
+  <si>
     <t>38</t>
   </si>
   <si>
@@ -393,6 +396,15 @@
     <t>Granatowska Mariola</t>
   </si>
   <si>
+    <t>3TFB|JA1</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
     <t>2FB</t>
   </si>
   <si>
@@ -516,6 +528,9 @@
     <t>2K|CH</t>
   </si>
   <si>
+    <t>2FA|JA2</t>
+  </si>
+  <si>
     <t>Wakat1 j. niemiecki</t>
   </si>
   <si>
@@ -528,18 +543,21 @@
     <t>Fiodorów Małgorzata</t>
   </si>
   <si>
+    <t>2CA</t>
+  </si>
+  <si>
     <t>Fizyka</t>
   </si>
   <si>
     <t>Biczysko Wojciech</t>
   </si>
   <si>
+    <t>2K</t>
+  </si>
+  <si>
     <t>2CA|relu</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>2FB|relu</t>
   </si>
   <si>
@@ -579,12 +597,27 @@
     <t>aq1</t>
   </si>
   <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>1S|JA2</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>1FA|JA2</t>
+  </si>
+  <si>
     <t>1CB|JA1</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
+    <t>1TH</t>
+  </si>
+  <si>
     <t>1FB|JA1</t>
   </si>
   <si>
@@ -597,9 +630,6 @@
     <t>Młynarczyk Paweł</t>
   </si>
   <si>
-    <t>1S|JA2</t>
-  </si>
-  <si>
     <t>12, 17:25-18:10</t>
   </si>
   <si>
@@ -654,6 +684,12 @@
     <t>14:05-14:50</t>
   </si>
   <si>
+    <t>17:25-18:55</t>
+  </si>
+  <si>
+    <t>język angielski 2 godz lekcyjne</t>
+  </si>
+  <si>
     <t>10:35-12:10</t>
   </si>
   <si>
@@ -717,13 +753,13 @@
     <t>08:45-08:50</t>
   </si>
   <si>
+    <t>10:25-10:35</t>
+  </si>
+  <si>
     <t>piętro_3</t>
   </si>
   <si>
     <t>Nowaczyk Agnieszka</t>
-  </si>
-  <si>
-    <t>10:25-10:35</t>
   </si>
   <si>
     <t>15:40-15:45</t>
@@ -1176,7 +1212,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8cba3292-499f-4c8c-9ab2-048f2be187cf}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{94757734-feb3-4f79-8384-cdf9c8b82150}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1197,8 +1233,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{81b542b6-d09b-4f94-bd1b-5908e48be505}">
-  <dimension ref="A1:I147"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4490299c-764c-4ece-8469-274ff90b00b8}">
+  <dimension ref="A1:I163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -2525,25 +2561,25 @@
         <v>46</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="E46" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="F46" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="G46" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
@@ -2554,25 +2590,25 @@
         <v>46</v>
       </c>
       <c r="C47" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D47" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="E47" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="F47" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G47" t="s">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
@@ -2583,19 +2619,19 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D48" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="E48" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="F48" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G48" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
@@ -2609,22 +2645,22 @@
         <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D49" t="s">
-        <v>29</v>
+        <v>118</v>
       </c>
       <c r="E49" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="F49" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G49" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
@@ -2641,25 +2677,25 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D50" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E50" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F50" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G50" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
@@ -2667,22 +2703,22 @@
         <v>104</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D51" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E51" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="G51" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
@@ -2696,28 +2732,28 @@
         <v>104</v>
       </c>
       <c r="B52" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D52" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E52" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F52" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G52" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
@@ -2728,19 +2764,19 @@
         <v>69</v>
       </c>
       <c r="C53" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D53" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F53" t="s">
         <v>125</v>
       </c>
-      <c r="E53" t="s">
-        <v>74</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>126</v>
-      </c>
-      <c r="G53" t="s">
-        <v>117</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
@@ -2757,25 +2793,25 @@
         <v>69</v>
       </c>
       <c r="C54" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D54" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="E54" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="F54" t="s">
-        <v>126</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
@@ -2783,13 +2819,13 @@
         <v>104</v>
       </c>
       <c r="B55" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C55" t="s">
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="E55" t="s">
         <v>22</v>
@@ -2798,10 +2834,10 @@
         <v>23</v>
       </c>
       <c r="G55" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="I55" t="s">
         <v>19</v>
@@ -2812,19 +2848,19 @@
         <v>104</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C56" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D56" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="E56" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G56" t="s">
         <v>117</v>
@@ -2841,28 +2877,28 @@
         <v>104</v>
       </c>
       <c r="B57" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C57" t="s">
         <v>52</v>
       </c>
       <c r="D57" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E57" t="s">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="F57" t="s">
         <v>130</v>
       </c>
       <c r="G57" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
@@ -2870,28 +2906,28 @@
         <v>104</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C58" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D58" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E58" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="F58" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="G58" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
@@ -2899,28 +2935,28 @@
         <v>104</v>
       </c>
       <c r="B59" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="E59" t="s">
-        <v>135</v>
+        <v>22</v>
       </c>
       <c r="F59" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G59" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
@@ -2928,22 +2964,22 @@
         <v>104</v>
       </c>
       <c r="B60" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="D60" t="s">
-        <v>137</v>
+        <v>29</v>
       </c>
       <c r="E60" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="F60" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="G60" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
@@ -2957,28 +2993,28 @@
         <v>104</v>
       </c>
       <c r="B61" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="D61" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E61" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F61" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G61" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
@@ -2986,28 +3022,28 @@
         <v>104</v>
       </c>
       <c r="B62" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C62" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="D62" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E62" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F62" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G62" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
@@ -3015,28 +3051,28 @@
         <v>104</v>
       </c>
       <c r="B63" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C63" t="s">
+        <v>52</v>
+      </c>
+      <c r="D63" t="s">
+        <v>127</v>
+      </c>
+      <c r="E63" t="s">
         <v>139</v>
       </c>
-      <c r="D63" t="s">
-        <v>144</v>
-      </c>
-      <c r="E63" t="s">
-        <v>141</v>
-      </c>
       <c r="F63" t="s">
-        <v>142</v>
+        <v>51</v>
       </c>
       <c r="G63" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
@@ -3047,25 +3083,25 @@
         <v>101</v>
       </c>
       <c r="C64" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E64" t="s">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="F64" t="s">
+        <v>103</v>
+      </c>
+      <c r="G64" t="s">
         <v>142</v>
       </c>
-      <c r="G64" t="s">
-        <v>98</v>
-      </c>
       <c r="H64" t="s">
         <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
@@ -3076,16 +3112,16 @@
         <v>101</v>
       </c>
       <c r="C65" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D65" t="s">
+        <v>144</v>
+      </c>
+      <c r="E65" t="s">
+        <v>145</v>
+      </c>
+      <c r="F65" t="s">
         <v>146</v>
-      </c>
-      <c r="E65" t="s">
-        <v>141</v>
-      </c>
-      <c r="F65" t="s">
-        <v>142</v>
       </c>
       <c r="G65" t="s">
         <v>98</v>
@@ -3102,51 +3138,51 @@
         <v>104</v>
       </c>
       <c r="B66" t="s">
+        <v>101</v>
+      </c>
+      <c r="C66" t="s">
+        <v>143</v>
+      </c>
+      <c r="D66" t="s">
         <v>147</v>
       </c>
-      <c r="C66" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" t="s">
-        <v>148</v>
-      </c>
       <c r="E66" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="F66" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="G66" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="C67" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="D67" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E67" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="F67" t="s">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="G67" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
@@ -3157,25 +3193,25 @@
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
+        <v>104</v>
+      </c>
+      <c r="B68" t="s">
+        <v>101</v>
+      </c>
+      <c r="C68" t="s">
+        <v>143</v>
+      </c>
+      <c r="D68" t="s">
         <v>149</v>
       </c>
-      <c r="B68" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68" t="s">
-        <v>24</v>
-      </c>
-      <c r="D68" t="s">
-        <v>151</v>
-      </c>
       <c r="E68" t="s">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="F68" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="G68" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
@@ -3186,25 +3222,25 @@
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="B69" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="C69" t="s">
-        <v>52</v>
+        <v>143</v>
       </c>
       <c r="D69" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="E69" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F69" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="G69" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
@@ -3215,306 +3251,306 @@
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="B70" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C70" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="D70" t="s">
         <v>152</v>
       </c>
       <c r="E70" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="F70" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="G70" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D71" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E71" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="F71" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G71" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="D72" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E72" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="F72" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G72" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="D73" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="E73" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="F73" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G73" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B74" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="D74" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="E74" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="F74" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G74" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B75" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D75" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E75" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="F75" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G75" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B76" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="D76" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E76" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="F76" t="s">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="G76" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C77" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="D77" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="E77" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="F77" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G77" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B78" t="s">
         <v>34</v>
       </c>
       <c r="C78" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D78" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="E78" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F78" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="G78" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B79" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C79" t="s">
         <v>100</v>
       </c>
       <c r="D79" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="E79" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F79" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G79" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B80" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C80" t="s">
         <v>72</v>
       </c>
       <c r="D80" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E80" t="s">
         <v>74</v>
@@ -3534,16 +3570,16 @@
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B81" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
       </c>
       <c r="D81" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E81" t="s">
         <v>26</v>
@@ -3563,39 +3599,39 @@
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B82" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C82" t="s">
         <v>52</v>
       </c>
       <c r="D82" t="s">
-        <v>159</v>
+        <v>71</v>
       </c>
       <c r="E82" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="F82" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G82" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B83" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C83" t="s">
         <v>100</v>
@@ -3604,13 +3640,13 @@
         <v>65</v>
       </c>
       <c r="E83" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="F83" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G83" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
@@ -3621,25 +3657,25 @@
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B84" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C84" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D84" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="E84" t="s">
         <v>74</v>
       </c>
       <c r="F84" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="G84" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
@@ -3650,141 +3686,141 @@
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B85" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C85" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D85" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E85" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="F85" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="G85" t="s">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B86" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D86" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E86" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="F86" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="G86" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B87" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C87" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="D87" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E87" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F87" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G87" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B88" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C88" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D88" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="E88" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F88" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="G88" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B89" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C89" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D89" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="E89" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="F89" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="G89" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
@@ -3795,25 +3831,25 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B90" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C90" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D90" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="E90" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F90" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="G90" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
@@ -3824,74 +3860,74 @@
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B91" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C91" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
       <c r="D91" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E91" t="s">
-        <v>166</v>
+        <v>26</v>
       </c>
       <c r="F91" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G91" t="s">
-        <v>167</v>
+        <v>17</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B92" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C92" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="D92" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="E92" t="s">
-        <v>168</v>
+        <v>47</v>
       </c>
       <c r="F92" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="G92" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B93" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C93" t="s">
         <v>100</v>
       </c>
       <c r="D93" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E93" t="s">
         <v>43</v>
@@ -3911,170 +3947,170 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B94" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C94" t="s">
         <v>72</v>
       </c>
       <c r="D94" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E94" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F94" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="G94" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B95" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C95" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D95" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E95" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F95" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G95" t="s">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B96" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C96" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D96" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="E96" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="F96" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="G96" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B97" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C97" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="D97" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="E97" t="s">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="F97" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="G97" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B98" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C98" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="D98" t="s">
+        <v>170</v>
+      </c>
+      <c r="E98" t="s">
+        <v>171</v>
+      </c>
+      <c r="F98" t="s">
+        <v>16</v>
+      </c>
+      <c r="G98" t="s">
         <v>172</v>
       </c>
-      <c r="E98" t="s">
-        <v>141</v>
-      </c>
-      <c r="F98" t="s">
-        <v>171</v>
-      </c>
-      <c r="G98" t="s">
-        <v>98</v>
-      </c>
       <c r="H98" t="s">
         <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C99" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="D99" t="s">
         <v>173</v>
       </c>
       <c r="E99" t="s">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="F99" t="s">
-        <v>171</v>
+        <v>63</v>
       </c>
       <c r="G99" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
@@ -4085,138 +4121,138 @@
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
+        <v>153</v>
+      </c>
+      <c r="B100" t="s">
+        <v>90</v>
+      </c>
+      <c r="C100" t="s">
+        <v>35</v>
+      </c>
+      <c r="D100" t="s">
+        <v>36</v>
+      </c>
+      <c r="E100" t="s">
         <v>174</v>
       </c>
-      <c r="B100" t="s">
-        <v>12</v>
-      </c>
-      <c r="C100" t="s">
-        <v>52</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="F100" t="s">
+        <v>23</v>
+      </c>
+      <c r="G100" t="s">
         <v>175</v>
       </c>
-      <c r="E100" t="s">
-        <v>129</v>
-      </c>
-      <c r="F100" t="s">
-        <v>51</v>
-      </c>
-      <c r="G100" t="s">
-        <v>19</v>
-      </c>
       <c r="H100" t="s">
         <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B101" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C101" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D101" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E101" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F101" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G101" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B102" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C102" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D102" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E102" t="s">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="F102" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="G102" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B103" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="C103" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D103" t="s">
-        <v>25</v>
+        <v>166</v>
       </c>
       <c r="E103" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F103" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G103" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B104" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="C104" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D104" t="s">
         <v>176</v>
       </c>
       <c r="E104" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F104" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G104" t="s">
         <v>19</v>
@@ -4230,25 +4266,25 @@
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B105" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="C105" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="D105" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E105" t="s">
         <v>86</v>
       </c>
       <c r="F105" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G105" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
@@ -4259,25 +4295,25 @@
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B106" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="C106" t="s">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="D106" t="s">
-        <v>65</v>
+        <v>177</v>
       </c>
       <c r="E106" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="F106" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="G106" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H106" t="s">
         <v>18</v>
@@ -4288,25 +4324,25 @@
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B107" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="C107" t="s">
-        <v>52</v>
+        <v>143</v>
       </c>
       <c r="D107" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="E107" t="s">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="F107" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="G107" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
@@ -4317,25 +4353,25 @@
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B108" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="C108" t="s">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="D108" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="E108" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="F108" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="G108" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
@@ -4346,22 +4382,22 @@
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B109" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D109" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E109" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="F109" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G109" t="s">
         <v>19</v>
@@ -4375,22 +4411,22 @@
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B110" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C110" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="E110" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F110" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G110" t="s">
         <v>19</v>
@@ -4404,22 +4440,22 @@
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B111" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="C111" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D111" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="E111" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="F111" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="G111" t="s">
         <v>19</v>
@@ -4433,22 +4469,22 @@
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B112" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="C112" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D112" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="E112" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F112" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G112" t="s">
         <v>19</v>
@@ -4462,22 +4498,22 @@
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B113" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="C113" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D113" t="s">
-        <v>85</v>
+        <v>182</v>
       </c>
       <c r="E113" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F113" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="G113" t="s">
         <v>19</v>
@@ -4491,22 +4527,22 @@
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B114" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="C114" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D114" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="E114" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="F114" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G114" t="s">
         <v>19</v>
@@ -4520,22 +4556,22 @@
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B115" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="C115" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D115" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="E115" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F115" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G115" t="s">
         <v>19</v>
@@ -4549,51 +4585,51 @@
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B116" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="C116" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D116" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="E116" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F116" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="G116" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B117" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C117" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="E117" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F117" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="G117" t="s">
         <v>19</v>
@@ -4607,22 +4643,22 @@
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B118" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C118" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D118" t="s">
-        <v>91</v>
+        <v>183</v>
       </c>
       <c r="E118" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F118" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="G118" t="s">
         <v>19</v>
@@ -4636,51 +4672,51 @@
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B119" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C119" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D119" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E119" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F119" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="G119" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
       </c>
       <c r="I119" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B120" t="s">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="C120" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D120" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="E120" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F120" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="G120" t="s">
         <v>19</v>
@@ -4694,51 +4730,51 @@
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B121" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="C121" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D121" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="E121" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="F121" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="G121" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B122" t="s">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="C122" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D122" t="s">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="E122" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F122" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="G122" t="s">
         <v>19</v>
@@ -4752,22 +4788,22 @@
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B123" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="C123" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D123" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="E123" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F123" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="G123" t="s">
         <v>19</v>
@@ -4781,22 +4817,22 @@
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B124" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="C124" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D124" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E124" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F124" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G124" t="s">
         <v>19</v>
@@ -4810,80 +4846,80 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B125" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="C125" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D125" t="s">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="E125" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="F125" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="G125" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
       </c>
       <c r="I125" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B126" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="C126" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="D126" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E126" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="F126" t="s">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="G126" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
       </c>
       <c r="I126" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B127" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="C127" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D127" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="E127" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F127" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G127" t="s">
         <v>19</v>
@@ -4897,109 +4933,109 @@
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B128" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C128" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D128" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="E128" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="F128" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="G128" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B129" t="s">
-        <v>61</v>
+        <v>151</v>
       </c>
       <c r="C129" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="D129" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E129" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="F129" t="s">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="G129" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B130" t="s">
-        <v>61</v>
+        <v>151</v>
       </c>
       <c r="C130" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D130" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="E130" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F130" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="G130" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B131" t="s">
-        <v>69</v>
+        <v>186</v>
       </c>
       <c r="C131" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D131" t="s">
-        <v>71</v>
+        <v>187</v>
       </c>
       <c r="E131" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="F131" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="G131" t="s">
         <v>19</v>
@@ -5013,51 +5049,51 @@
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B132" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="C132" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D132" t="s">
-        <v>183</v>
+        <v>25</v>
       </c>
       <c r="E132" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="F132" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="G132" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B133" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C133" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D133" t="s">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="E133" t="s">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="F133" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G133" t="s">
         <v>19</v>
@@ -5071,22 +5107,22 @@
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B134" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C134" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D134" t="s">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="E134" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F134" t="s">
-        <v>186</v>
+        <v>23</v>
       </c>
       <c r="G134" t="s">
         <v>19</v>
@@ -5100,45 +5136,45 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B135" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C135" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D135" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="E135" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F135" t="s">
-        <v>23</v>
+        <v>190</v>
       </c>
       <c r="G135" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H135" t="s">
         <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B136" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C136" t="s">
         <v>52</v>
       </c>
       <c r="D136" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="E136" t="s">
         <v>86</v>
@@ -5158,25 +5194,25 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B137" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="C137" t="s">
-        <v>13</v>
+        <v>191</v>
       </c>
       <c r="D137" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E137" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F137" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G137" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
@@ -5187,22 +5223,22 @@
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B138" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="C138" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D138" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E138" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F138" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G138" t="s">
         <v>19</v>
@@ -5216,48 +5252,48 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B139" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="C139" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="D139" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E139" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="F139" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G139" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H139" t="s">
         <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B140" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="C140" t="s">
         <v>52</v>
       </c>
       <c r="D140" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="E140" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="F140" t="s">
         <v>51</v>
@@ -5274,80 +5310,80 @@
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B141" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="C141" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="D141" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="E141" t="s">
-        <v>166</v>
+        <v>47</v>
       </c>
       <c r="F141" t="s">
-        <v>16</v>
+        <v>193</v>
       </c>
       <c r="G141" t="s">
-        <v>167</v>
+        <v>93</v>
       </c>
       <c r="H141" t="s">
         <v>18</v>
       </c>
       <c r="I141" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B142" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="C142" t="s">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="D142" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E142" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="F142" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="G142" t="s">
-        <v>190</v>
+        <v>93</v>
       </c>
       <c r="H142" t="s">
         <v>18</v>
       </c>
       <c r="I142" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B143" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C143" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D143" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="E143" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="F143" t="s">
-        <v>186</v>
+        <v>23</v>
       </c>
       <c r="G143" t="s">
         <v>19</v>
@@ -5361,83 +5397,83 @@
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B144" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C144" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D144" t="s">
-        <v>123</v>
+        <v>189</v>
       </c>
       <c r="E144" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="F144" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="G144" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="H144" t="s">
         <v>18</v>
       </c>
       <c r="I144" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B145" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C145" t="s">
-        <v>189</v>
+        <v>52</v>
       </c>
       <c r="D145" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="E145" t="s">
-        <v>37</v>
+        <v>133</v>
       </c>
       <c r="F145" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G145" t="s">
-        <v>190</v>
+        <v>19</v>
       </c>
       <c r="H145" t="s">
         <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B146" t="s">
-        <v>147</v>
+        <v>69</v>
       </c>
       <c r="C146" t="s">
-        <v>13</v>
+        <v>191</v>
       </c>
       <c r="D146" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E146" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F146" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G146" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
@@ -5448,30 +5484,494 @@
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B147" t="s">
+        <v>77</v>
+      </c>
+      <c r="C147" t="s">
+        <v>89</v>
+      </c>
+      <c r="D147" t="s">
+        <v>176</v>
+      </c>
+      <c r="E147" t="s">
+        <v>67</v>
+      </c>
+      <c r="F147" t="s">
+        <v>134</v>
+      </c>
+      <c r="G147" t="s">
+        <v>93</v>
+      </c>
+      <c r="H147" t="s">
+        <v>18</v>
+      </c>
+      <c r="I147" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="15">
+      <c r="A148" t="s">
+        <v>188</v>
+      </c>
+      <c r="B148" t="s">
+        <v>77</v>
+      </c>
+      <c r="C148" t="s">
+        <v>13</v>
+      </c>
+      <c r="D148" t="s">
+        <v>195</v>
+      </c>
+      <c r="E148" t="s">
+        <v>15</v>
+      </c>
+      <c r="F148" t="s">
+        <v>196</v>
+      </c>
+      <c r="G148" t="s">
+        <v>19</v>
+      </c>
+      <c r="H148" t="s">
+        <v>18</v>
+      </c>
+      <c r="I148" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="15">
+      <c r="A149" t="s">
+        <v>188</v>
+      </c>
+      <c r="B149" t="s">
+        <v>77</v>
+      </c>
+      <c r="C149" t="s">
+        <v>20</v>
+      </c>
+      <c r="D149" t="s">
+        <v>71</v>
+      </c>
+      <c r="E149" t="s">
+        <v>86</v>
+      </c>
+      <c r="F149" t="s">
+        <v>23</v>
+      </c>
+      <c r="G149" t="s">
+        <v>19</v>
+      </c>
+      <c r="H149" t="s">
+        <v>18</v>
+      </c>
+      <c r="I149" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="15">
+      <c r="A150" t="s">
+        <v>188</v>
+      </c>
+      <c r="B150" t="s">
+        <v>77</v>
+      </c>
+      <c r="C150" t="s">
+        <v>52</v>
+      </c>
+      <c r="D150" t="s">
+        <v>135</v>
+      </c>
+      <c r="E150" t="s">
+        <v>86</v>
+      </c>
+      <c r="F150" t="s">
+        <v>51</v>
+      </c>
+      <c r="G150" t="s">
+        <v>19</v>
+      </c>
+      <c r="H150" t="s">
+        <v>18</v>
+      </c>
+      <c r="I150" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="15">
+      <c r="A151" t="s">
+        <v>188</v>
+      </c>
+      <c r="B151" t="s">
+        <v>77</v>
+      </c>
+      <c r="C151" t="s">
+        <v>191</v>
+      </c>
+      <c r="D151" t="s">
+        <v>189</v>
+      </c>
+      <c r="E151" t="s">
+        <v>47</v>
+      </c>
+      <c r="F151" t="s">
+        <v>193</v>
+      </c>
+      <c r="G151" t="s">
+        <v>93</v>
+      </c>
+      <c r="H151" t="s">
+        <v>18</v>
+      </c>
+      <c r="I151" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="15">
+      <c r="A152" t="s">
+        <v>188</v>
+      </c>
+      <c r="B152" t="s">
+        <v>90</v>
+      </c>
+      <c r="C152" t="s">
+        <v>89</v>
+      </c>
+      <c r="D152" t="s">
+        <v>197</v>
+      </c>
+      <c r="E152" t="s">
+        <v>88</v>
+      </c>
+      <c r="F152" t="s">
+        <v>134</v>
+      </c>
+      <c r="G152" t="s">
+        <v>93</v>
+      </c>
+      <c r="H152" t="s">
+        <v>18</v>
+      </c>
+      <c r="I152" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="15">
+      <c r="A153" t="s">
+        <v>188</v>
+      </c>
+      <c r="B153" t="s">
+        <v>90</v>
+      </c>
+      <c r="C153" t="s">
+        <v>13</v>
+      </c>
+      <c r="D153" t="s">
+        <v>198</v>
+      </c>
+      <c r="E153" t="s">
+        <v>15</v>
+      </c>
+      <c r="F153" t="s">
+        <v>196</v>
+      </c>
+      <c r="G153" t="s">
+        <v>19</v>
+      </c>
+      <c r="H153" t="s">
+        <v>18</v>
+      </c>
+      <c r="I153" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="15">
+      <c r="A154" t="s">
+        <v>188</v>
+      </c>
+      <c r="B154" t="s">
+        <v>90</v>
+      </c>
+      <c r="C154" t="s">
+        <v>52</v>
+      </c>
+      <c r="D154" t="s">
+        <v>135</v>
+      </c>
+      <c r="E154" t="s">
+        <v>86</v>
+      </c>
+      <c r="F154" t="s">
+        <v>51</v>
+      </c>
+      <c r="G154" t="s">
+        <v>19</v>
+      </c>
+      <c r="H154" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="15">
+      <c r="A155" t="s">
+        <v>188</v>
+      </c>
+      <c r="B155" t="s">
+        <v>99</v>
+      </c>
+      <c r="C155" t="s">
+        <v>13</v>
+      </c>
+      <c r="D155" t="s">
+        <v>199</v>
+      </c>
+      <c r="E155" t="s">
+        <v>15</v>
+      </c>
+      <c r="F155" t="s">
+        <v>196</v>
+      </c>
+      <c r="G155" t="s">
+        <v>19</v>
+      </c>
+      <c r="H155" t="s">
+        <v>18</v>
+      </c>
+      <c r="I155" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="15">
+      <c r="A156" t="s">
+        <v>188</v>
+      </c>
+      <c r="B156" t="s">
+        <v>99</v>
+      </c>
+      <c r="C156" t="s">
+        <v>52</v>
+      </c>
+      <c r="D156" t="s">
+        <v>71</v>
+      </c>
+      <c r="E156" t="s">
+        <v>139</v>
+      </c>
+      <c r="F156" t="s">
+        <v>51</v>
+      </c>
+      <c r="G156" t="s">
+        <v>19</v>
+      </c>
+      <c r="H156" t="s">
+        <v>18</v>
+      </c>
+      <c r="I156" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="15">
+      <c r="A157" t="s">
+        <v>188</v>
+      </c>
+      <c r="B157" t="s">
+        <v>99</v>
+      </c>
+      <c r="C157" t="s">
+        <v>169</v>
+      </c>
+      <c r="D157" t="s">
+        <v>170</v>
+      </c>
+      <c r="E157" t="s">
+        <v>171</v>
+      </c>
+      <c r="F157" t="s">
+        <v>16</v>
+      </c>
+      <c r="G157" t="s">
+        <v>172</v>
+      </c>
+      <c r="H157" t="s">
+        <v>18</v>
+      </c>
+      <c r="I157" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="15">
+      <c r="A158" t="s">
+        <v>188</v>
+      </c>
+      <c r="B158" t="s">
+        <v>99</v>
+      </c>
+      <c r="C158" t="s">
+        <v>200</v>
+      </c>
+      <c r="D158" t="s">
+        <v>155</v>
+      </c>
+      <c r="E158" t="s">
+        <v>37</v>
+      </c>
+      <c r="F158" t="s">
+        <v>41</v>
+      </c>
+      <c r="G158" t="s">
+        <v>201</v>
+      </c>
+      <c r="H158" t="s">
+        <v>18</v>
+      </c>
+      <c r="I158" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="15">
+      <c r="A159" t="s">
+        <v>188</v>
+      </c>
+      <c r="B159" t="s">
+        <v>101</v>
+      </c>
+      <c r="C159" t="s">
+        <v>13</v>
+      </c>
+      <c r="D159" t="s">
+        <v>170</v>
+      </c>
+      <c r="E159" t="s">
+        <v>15</v>
+      </c>
+      <c r="F159" t="s">
+        <v>196</v>
+      </c>
+      <c r="G159" t="s">
+        <v>19</v>
+      </c>
+      <c r="H159" t="s">
+        <v>18</v>
+      </c>
+      <c r="I159" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="15">
+      <c r="A160" t="s">
+        <v>188</v>
+      </c>
+      <c r="B160" t="s">
+        <v>101</v>
+      </c>
+      <c r="C160" t="s">
+        <v>52</v>
+      </c>
+      <c r="D160" t="s">
+        <v>127</v>
+      </c>
+      <c r="E160" t="s">
+        <v>139</v>
+      </c>
+      <c r="F160" t="s">
+        <v>51</v>
+      </c>
+      <c r="G160" t="s">
+        <v>19</v>
+      </c>
+      <c r="H160" t="s">
+        <v>18</v>
+      </c>
+      <c r="I160" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="15">
+      <c r="A161" t="s">
+        <v>188</v>
+      </c>
+      <c r="B161" t="s">
+        <v>101</v>
+      </c>
+      <c r="C161" t="s">
+        <v>200</v>
+      </c>
+      <c r="D161" t="s">
+        <v>155</v>
+      </c>
+      <c r="E161" t="s">
+        <v>37</v>
+      </c>
+      <c r="F161" t="s">
+        <v>41</v>
+      </c>
+      <c r="G161" t="s">
+        <v>201</v>
+      </c>
+      <c r="H161" t="s">
+        <v>18</v>
+      </c>
+      <c r="I161" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="15">
+      <c r="A162" t="s">
+        <v>188</v>
+      </c>
+      <c r="B162" t="s">
+        <v>151</v>
+      </c>
+      <c r="C162" t="s">
+        <v>13</v>
+      </c>
+      <c r="D162" t="s">
         <v>192</v>
       </c>
-      <c r="C147" t="s">
+      <c r="E162" t="s">
+        <v>15</v>
+      </c>
+      <c r="F162" t="s">
+        <v>196</v>
+      </c>
+      <c r="G162" t="s">
+        <v>19</v>
+      </c>
+      <c r="H162" t="s">
+        <v>18</v>
+      </c>
+      <c r="I162" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="15">
+      <c r="A163" t="s">
+        <v>188</v>
+      </c>
+      <c r="B163" t="s">
+        <v>202</v>
+      </c>
+      <c r="C163" t="s">
         <v>13</v>
       </c>
-      <c r="D147" t="s">
-        <v>193</v>
-      </c>
-      <c r="E147" t="s">
+      <c r="D163" t="s">
+        <v>203</v>
+      </c>
+      <c r="E163" t="s">
         <v>15</v>
       </c>
-      <c r="F147" t="s">
+      <c r="F163" t="s">
         <v>103</v>
       </c>
-      <c r="G147" t="s">
-        <v>19</v>
-      </c>
-      <c r="H147" t="s">
-        <v>18</v>
-      </c>
-      <c r="I147" t="s">
+      <c r="G163" t="s">
+        <v>19</v>
+      </c>
+      <c r="H163" t="s">
+        <v>18</v>
+      </c>
+      <c r="I163" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5483,13 +5983,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{10040908-ce08-4b76-90b9-7c2f370351db}">
-  <dimension ref="A1:I9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{17473651-90c1-4a2d-abc4-602b796c3078}">
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="17.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="50.2857142857143" customWidth="1"/>
     <col min="5" max="5" width="55.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
@@ -5503,16 +6003,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -5532,16 +6032,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E2" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -5561,16 +6061,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C3" t="s">
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="E3" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -5590,16 +6090,16 @@
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E4" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -5619,16 +6119,16 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E5" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -5645,19 +6145,19 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B6" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E6" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -5674,19 +6174,19 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C7" t="s">
         <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="E7" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -5703,19 +6203,19 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B8" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="E8" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -5732,13 +6232,13 @@
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B9" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
         <v>212</v>
@@ -5756,6 +6256,35 @@
         <v>18</v>
       </c>
       <c r="I9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15">
+      <c r="A10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5767,8 +6296,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4df6047a-ba4e-4eee-8729-5c053d7890eb}">
-  <dimension ref="A1:F25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{143c40f5-f4c7-4cea-85d6-390df1e3ff08}">
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -5784,13 +6313,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -5804,13 +6333,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -5824,13 +6353,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C3" t="s">
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="E3" t="s">
         <v>100</v>
@@ -5844,13 +6373,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C4" t="s">
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="E4" t="s">
         <v>42</v>
@@ -5864,16 +6393,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="E5" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -5884,16 +6413,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="E6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -5904,13 +6433,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="C7" t="s">
         <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="E7" t="s">
         <v>58</v>
@@ -5924,16 +6453,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="E8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -5944,16 +6473,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="E9" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -5964,13 +6493,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C10" t="s">
         <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E10" t="s">
         <v>117</v>
@@ -5984,13 +6513,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
@@ -6004,16 +6533,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -6024,16 +6553,16 @@
         <v>104</v>
       </c>
       <c r="B13" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="E13" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -6044,13 +6573,13 @@
         <v>104</v>
       </c>
       <c r="B14" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C14" t="s">
         <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E14" t="s">
         <v>100</v>
@@ -6064,16 +6593,16 @@
         <v>104</v>
       </c>
       <c r="B15" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="E15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -6084,16 +6613,16 @@
         <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="E16" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -6104,16 +6633,16 @@
         <v>104</v>
       </c>
       <c r="B17" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C17" t="s">
         <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E17" t="s">
-        <v>232</v>
+        <v>138</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -6121,19 +6650,19 @@
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="C18" t="s">
         <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -6141,16 +6670,16 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B19" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -6161,16 +6690,16 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C20" t="s">
         <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -6181,16 +6710,16 @@
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B21" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -6201,16 +6730,16 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B22" t="s">
+        <v>240</v>
+      </c>
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" t="s">
         <v>228</v>
-      </c>
-      <c r="C22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" t="s">
-        <v>220</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
@@ -6221,16 +6750,16 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B23" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -6241,16 +6770,16 @@
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B24" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
@@ -6261,21 +6790,121 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B25" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
+        <v>228</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15">
+      <c r="A26" t="s">
+        <v>188</v>
+      </c>
+      <c r="B26" t="s">
+        <v>243</v>
+      </c>
+      <c r="C26" t="s">
         <v>52</v>
       </c>
-      <c r="D25" t="s">
-        <v>216</v>
-      </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="D26" t="s">
+        <v>228</v>
+      </c>
+      <c r="E26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15">
+      <c r="A27" t="s">
+        <v>188</v>
+      </c>
+      <c r="B27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C27" t="s">
+        <v>191</v>
+      </c>
+      <c r="D27" t="s">
+        <v>232</v>
+      </c>
+      <c r="E27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15">
+      <c r="A28" t="s">
+        <v>188</v>
+      </c>
+      <c r="B28" t="s">
+        <v>236</v>
+      </c>
+      <c r="C28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" t="s">
+        <v>244</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15">
+      <c r="A29" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" t="s">
+        <v>237</v>
+      </c>
+      <c r="C29" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" t="s">
+        <v>228</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15">
+      <c r="A30" t="s">
+        <v>188</v>
+      </c>
+      <c r="B30" t="s">
+        <v>246</v>
+      </c>
+      <c r="C30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" t="s">
+        <v>228</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
         <v>18</v>
       </c>
     </row>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="264">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -390,147 +390,150 @@
     <t>38</t>
   </si>
   <si>
+    <t>3TFB|JA1</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>p. Pietrycha, wf za lekcję 2</t>
+  </si>
+  <si>
+    <t>3FA|JA1</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>3FA|JA2</t>
+  </si>
+  <si>
+    <t>1WB</t>
+  </si>
+  <si>
+    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - barber</t>
+  </si>
+  <si>
+    <t>Jaworska Edyta</t>
+  </si>
+  <si>
+    <t>1WB|JN1</t>
+  </si>
+  <si>
+    <t>Płatek Krzysztof</t>
+  </si>
+  <si>
+    <t>Paleczny Maciej</t>
+  </si>
+  <si>
+    <t>3CA|relu</t>
+  </si>
+  <si>
+    <t>Religia</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>3FA|relu</t>
+  </si>
+  <si>
+    <t>3FB|relu</t>
+  </si>
+  <si>
+    <t>3TFA|relu</t>
+  </si>
+  <si>
+    <t>3TFB|relu</t>
+  </si>
+  <si>
+    <t>10, 15:45-16:30</t>
+  </si>
+  <si>
+    <t>1TFA|JA1</t>
+  </si>
+  <si>
+    <t>04.03.2026</t>
+  </si>
+  <si>
+    <t>1FC</t>
+  </si>
+  <si>
+    <t>1S</t>
+  </si>
+  <si>
+    <t>2CA|edu</t>
+  </si>
+  <si>
+    <t>2FC|edu</t>
+  </si>
+  <si>
+    <t>2S|edu</t>
+  </si>
+  <si>
+    <t>2WA|edu</t>
+  </si>
+  <si>
+    <t>5TF</t>
+  </si>
+  <si>
+    <t>1FA|JA1</t>
+  </si>
+  <si>
+    <t>1WA</t>
+  </si>
+  <si>
+    <t>2WB</t>
+  </si>
+  <si>
+    <t>sg3</t>
+  </si>
+  <si>
+    <t>Pietrycha Małgorzata</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>2K|CH</t>
+  </si>
+  <si>
+    <t>2FA|JA2</t>
+  </si>
+  <si>
     <t>43</t>
   </si>
   <si>
     <t>Granatowska Mariola</t>
   </si>
   <si>
-    <t>3TFB|JA1</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Filipek Anna</t>
-  </si>
-  <si>
-    <t>2FB</t>
-  </si>
-  <si>
-    <t>p. Pietrycha, wf za lekcję 2</t>
-  </si>
-  <si>
-    <t>3FA|JA1</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>3FA|JA2</t>
-  </si>
-  <si>
-    <t>1WB</t>
-  </si>
-  <si>
-    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>1TFA</t>
-  </si>
-  <si>
-    <t>Historia</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Kopij Marcin</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - barber</t>
-  </si>
-  <si>
-    <t>Jaworska Edyta</t>
-  </si>
-  <si>
-    <t>1WB|JN1</t>
-  </si>
-  <si>
-    <t>Płatek Krzysztof</t>
-  </si>
-  <si>
-    <t>Paleczny Maciej</t>
-  </si>
-  <si>
-    <t>3CA|relu</t>
-  </si>
-  <si>
-    <t>Religia</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>3FA|relu</t>
-  </si>
-  <si>
-    <t>3FB|relu</t>
-  </si>
-  <si>
-    <t>3TFA|relu</t>
-  </si>
-  <si>
-    <t>3TFB|relu</t>
-  </si>
-  <si>
-    <t>10, 15:45-16:30</t>
-  </si>
-  <si>
-    <t>1TFA|JA1</t>
-  </si>
-  <si>
-    <t>04.03.2026</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
-    <t>1S</t>
-  </si>
-  <si>
-    <t>2CA|edu</t>
-  </si>
-  <si>
-    <t>2FC|edu</t>
-  </si>
-  <si>
-    <t>2S|edu</t>
-  </si>
-  <si>
-    <t>2WA|edu</t>
-  </si>
-  <si>
-    <t>5TF</t>
-  </si>
-  <si>
-    <t>1FA|JA1</t>
-  </si>
-  <si>
-    <t>1WA</t>
-  </si>
-  <si>
-    <t>2WB</t>
-  </si>
-  <si>
-    <t>sg3</t>
-  </si>
-  <si>
-    <t>Pietrycha Małgorzata</t>
-  </si>
-  <si>
-    <t>1FA</t>
-  </si>
-  <si>
-    <t>2K|CH</t>
-  </si>
-  <si>
-    <t>2FA|JA2</t>
-  </si>
-  <si>
     <t>Wakat1 j. niemiecki</t>
   </si>
   <si>
@@ -555,6 +558,9 @@
     <t>2K</t>
   </si>
   <si>
+    <t>p. Sałdyka, biologia za lekcję 9</t>
+  </si>
+  <si>
     <t>2CA|relu</t>
   </si>
   <si>
@@ -570,12 +576,24 @@
     <t>2WA</t>
   </si>
   <si>
+    <t>Smaczny Monika</t>
+  </si>
+  <si>
     <t>2TFB|JA1</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>2TFA|JA1</t>
   </si>
   <si>
+    <t>p. Danielewski, techniki fryzjerskie za lekcję 9</t>
+  </si>
+  <si>
+    <t>p. Dalach, wychowanie fizyczne za lekcję 10</t>
+  </si>
+  <si>
     <t>1WB|JN2</t>
   </si>
   <si>
@@ -597,7 +615,7 @@
     <t>aq1</t>
   </si>
   <si>
-    <t>Wojciechowski Łukasz</t>
+    <t>Kruk Marcin</t>
   </si>
   <si>
     <t>1S|JA2</t>
@@ -612,18 +630,24 @@
     <t>1CB|JA1</t>
   </si>
   <si>
+    <t>sg1</t>
+  </si>
+  <si>
+    <t>Jastrzębska-Majtyka Agnieszka</t>
+  </si>
+  <si>
+    <t>Staliś Donata</t>
+  </si>
+  <si>
+    <t>1FB|JA1</t>
+  </si>
+  <si>
+    <t>1WA|JN1</t>
+  </si>
+  <si>
     <t>19</t>
   </si>
   <si>
-    <t>1TH</t>
-  </si>
-  <si>
-    <t>1FB|JA1</t>
-  </si>
-  <si>
-    <t>1WA|JN1</t>
-  </si>
-  <si>
     <t>Wakat2 matematyka</t>
   </si>
   <si>
@@ -690,9 +714,21 @@
     <t>język angielski 2 godz lekcyjne</t>
   </si>
   <si>
+    <t>08:50-09:35</t>
+  </si>
+  <si>
     <t>10:35-12:10</t>
   </si>
   <si>
+    <t>18:00-19:30</t>
+  </si>
+  <si>
+    <t>język angielski</t>
+  </si>
+  <si>
+    <t>09:40-10:25</t>
+  </si>
+  <si>
     <t>12:25-15:40</t>
   </si>
   <si>
@@ -723,9 +759,6 @@
     <t>bramka wejściowa</t>
   </si>
   <si>
-    <t>Jastrzębska-Majtyka Agnieszka</t>
-  </si>
-  <si>
     <t>11:20-11:25</t>
   </si>
   <si>
@@ -762,7 +795,25 @@
     <t>Nowaczyk Agnieszka</t>
   </si>
   <si>
+    <t>Doliński Mirosław</t>
+  </si>
+  <si>
+    <t>Dalach Sławomir</t>
+  </si>
+  <si>
     <t>15:40-15:45</t>
+  </si>
+  <si>
+    <t>Piątek-Pawłowska Bożena</t>
+  </si>
+  <si>
+    <t>Cieśla Marcin</t>
+  </si>
+  <si>
+    <t>16:30-16:35</t>
+  </si>
+  <si>
+    <t>17:20-17:25</t>
   </si>
 </sst>
 </file>
@@ -1212,7 +1263,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{94757734-feb3-4f79-8384-cdf9c8b82150}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{83075e30-bcff-4fea-9819-1b9bea301d68}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1233,8 +1284,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4490299c-764c-4ece-8469-274ff90b00b8}">
-  <dimension ref="A1:I163"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2f8ba8ef-1469-496c-bdce-63d9e43eaaf3}">
+  <dimension ref="A1:I172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1243,8 +1294,8 @@
     <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="68.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
-    <col min="7" max="7" width="27.8571428571429" customWidth="1"/>
-    <col min="8" max="8" width="27.5714285714286" customWidth="1"/>
+    <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="41.4285714285714" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2654,13 +2705,13 @@
         <v>118</v>
       </c>
       <c r="E49" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F49" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="G49" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
@@ -2680,7 +2731,7 @@
         <v>64</v>
       </c>
       <c r="D50" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E50" t="s">
         <v>47</v>
@@ -2773,10 +2824,10 @@
         <v>88</v>
       </c>
       <c r="F53" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
@@ -2825,7 +2876,7 @@
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E55" t="s">
         <v>22</v>
@@ -2837,7 +2888,7 @@
         <v>93</v>
       </c>
       <c r="H55" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I55" t="s">
         <v>19</v>
@@ -2854,13 +2905,13 @@
         <v>52</v>
       </c>
       <c r="D56" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E56" t="s">
         <v>74</v>
       </c>
       <c r="F56" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G56" t="s">
         <v>117</v>
@@ -2883,13 +2934,13 @@
         <v>52</v>
       </c>
       <c r="D57" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E57" t="s">
         <v>74</v>
       </c>
       <c r="F57" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G57" t="s">
         <v>117</v>
@@ -2912,7 +2963,7 @@
         <v>64</v>
       </c>
       <c r="D58" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E58" t="s">
         <v>81</v>
@@ -2976,7 +3027,7 @@
         <v>67</v>
       </c>
       <c r="F60" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G60" t="s">
         <v>117</v>
@@ -2999,13 +3050,13 @@
         <v>52</v>
       </c>
       <c r="D61" t="s">
+        <v>130</v>
+      </c>
+      <c r="E61" t="s">
+        <v>131</v>
+      </c>
+      <c r="F61" t="s">
         <v>132</v>
-      </c>
-      <c r="E61" t="s">
-        <v>133</v>
-      </c>
-      <c r="F61" t="s">
-        <v>134</v>
       </c>
       <c r="G61" t="s">
         <v>109</v>
@@ -3028,16 +3079,16 @@
         <v>20</v>
       </c>
       <c r="D62" t="s">
+        <v>133</v>
+      </c>
+      <c r="E62" t="s">
+        <v>134</v>
+      </c>
+      <c r="F62" t="s">
         <v>135</v>
       </c>
-      <c r="E62" t="s">
+      <c r="G62" t="s">
         <v>136</v>
-      </c>
-      <c r="F62" t="s">
-        <v>137</v>
-      </c>
-      <c r="G62" t="s">
-        <v>138</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
@@ -3057,16 +3108,16 @@
         <v>52</v>
       </c>
       <c r="D63" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E63" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F63" t="s">
         <v>51</v>
       </c>
       <c r="G63" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
@@ -3086,7 +3137,7 @@
         <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -3095,7 +3146,7 @@
         <v>103</v>
       </c>
       <c r="G64" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
@@ -3112,16 +3163,16 @@
         <v>101</v>
       </c>
       <c r="C65" t="s">
+        <v>141</v>
+      </c>
+      <c r="D65" t="s">
+        <v>142</v>
+      </c>
+      <c r="E65" t="s">
         <v>143</v>
       </c>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
         <v>144</v>
-      </c>
-      <c r="E65" t="s">
-        <v>145</v>
-      </c>
-      <c r="F65" t="s">
-        <v>146</v>
       </c>
       <c r="G65" t="s">
         <v>98</v>
@@ -3141,16 +3192,16 @@
         <v>101</v>
       </c>
       <c r="C66" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" t="s">
+        <v>145</v>
+      </c>
+      <c r="E66" t="s">
         <v>143</v>
       </c>
-      <c r="D66" t="s">
-        <v>147</v>
-      </c>
-      <c r="E66" t="s">
-        <v>145</v>
-      </c>
       <c r="F66" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G66" t="s">
         <v>98</v>
@@ -3170,16 +3221,16 @@
         <v>101</v>
       </c>
       <c r="C67" t="s">
+        <v>141</v>
+      </c>
+      <c r="D67" t="s">
+        <v>146</v>
+      </c>
+      <c r="E67" t="s">
         <v>143</v>
       </c>
-      <c r="D67" t="s">
-        <v>148</v>
-      </c>
-      <c r="E67" t="s">
-        <v>145</v>
-      </c>
       <c r="F67" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G67" t="s">
         <v>98</v>
@@ -3199,16 +3250,16 @@
         <v>101</v>
       </c>
       <c r="C68" t="s">
+        <v>141</v>
+      </c>
+      <c r="D68" t="s">
+        <v>147</v>
+      </c>
+      <c r="E68" t="s">
         <v>143</v>
       </c>
-      <c r="D68" t="s">
-        <v>149</v>
-      </c>
-      <c r="E68" t="s">
-        <v>145</v>
-      </c>
       <c r="F68" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G68" t="s">
         <v>98</v>
@@ -3228,16 +3279,16 @@
         <v>101</v>
       </c>
       <c r="C69" t="s">
+        <v>141</v>
+      </c>
+      <c r="D69" t="s">
+        <v>148</v>
+      </c>
+      <c r="E69" t="s">
         <v>143</v>
       </c>
-      <c r="D69" t="s">
-        <v>150</v>
-      </c>
-      <c r="E69" t="s">
-        <v>145</v>
-      </c>
       <c r="F69" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G69" t="s">
         <v>98</v>
@@ -3254,13 +3305,13 @@
         <v>104</v>
       </c>
       <c r="B70" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C70" t="s">
         <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
@@ -3280,7 +3331,7 @@
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
@@ -3289,7 +3340,7 @@
         <v>100</v>
       </c>
       <c r="D71" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E71" t="s">
         <v>67</v>
@@ -3309,7 +3360,7 @@
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
@@ -3318,7 +3369,7 @@
         <v>24</v>
       </c>
       <c r="D72" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E72" t="s">
         <v>26</v>
@@ -3338,7 +3389,7 @@
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
@@ -3350,7 +3401,7 @@
         <v>65</v>
       </c>
       <c r="E73" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F73" t="s">
         <v>51</v>
@@ -3367,7 +3418,7 @@
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
@@ -3376,7 +3427,7 @@
         <v>106</v>
       </c>
       <c r="D74" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E74" t="s">
         <v>108</v>
@@ -3396,7 +3447,7 @@
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
@@ -3405,7 +3456,7 @@
         <v>106</v>
       </c>
       <c r="D75" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E75" t="s">
         <v>108</v>
@@ -3425,7 +3476,7 @@
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
@@ -3434,7 +3485,7 @@
         <v>106</v>
       </c>
       <c r="D76" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E76" t="s">
         <v>108</v>
@@ -3454,7 +3505,7 @@
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B77" t="s">
         <v>12</v>
@@ -3463,7 +3514,7 @@
         <v>106</v>
       </c>
       <c r="D77" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E77" t="s">
         <v>108</v>
@@ -3483,7 +3534,7 @@
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B78" t="s">
         <v>34</v>
@@ -3512,7 +3563,7 @@
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B79" t="s">
         <v>34</v>
@@ -3521,27 +3572,27 @@
         <v>100</v>
       </c>
       <c r="D79" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E79" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F79" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="G79" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B80" t="s">
         <v>34</v>
@@ -3550,7 +3601,7 @@
         <v>72</v>
       </c>
       <c r="D80" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E80" t="s">
         <v>74</v>
@@ -3570,7 +3621,7 @@
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B81" t="s">
         <v>34</v>
@@ -3579,7 +3630,7 @@
         <v>24</v>
       </c>
       <c r="D81" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E81" t="s">
         <v>26</v>
@@ -3599,7 +3650,7 @@
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B82" t="s">
         <v>34</v>
@@ -3628,7 +3679,7 @@
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B83" t="s">
         <v>46</v>
@@ -3657,7 +3708,7 @@
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B84" t="s">
         <v>46</v>
@@ -3666,7 +3717,7 @@
         <v>72</v>
       </c>
       <c r="D84" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E84" t="s">
         <v>74</v>
@@ -3686,7 +3737,7 @@
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B85" t="s">
         <v>46</v>
@@ -3695,7 +3746,7 @@
         <v>24</v>
       </c>
       <c r="D85" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E85" t="s">
         <v>26</v>
@@ -3715,7 +3766,7 @@
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B86" t="s">
         <v>46</v>
@@ -3724,7 +3775,7 @@
         <v>52</v>
       </c>
       <c r="D86" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E86" t="s">
         <v>81</v>
@@ -3744,7 +3795,7 @@
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B87" t="s">
         <v>61</v>
@@ -3753,27 +3804,27 @@
         <v>64</v>
       </c>
       <c r="D87" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E87" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="F87" t="s">
         <v>63</v>
       </c>
       <c r="G87" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B88" t="s">
         <v>61</v>
@@ -3802,7 +3853,7 @@
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B89" t="s">
         <v>61</v>
@@ -3811,16 +3862,16 @@
         <v>53</v>
       </c>
       <c r="D89" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E89" t="s">
         <v>74</v>
       </c>
       <c r="F89" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G89" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
@@ -3831,7 +3882,7 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B90" t="s">
         <v>61</v>
@@ -3840,7 +3891,7 @@
         <v>72</v>
       </c>
       <c r="D90" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E90" t="s">
         <v>74</v>
@@ -3860,7 +3911,7 @@
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B91" t="s">
         <v>61</v>
@@ -3869,7 +3920,7 @@
         <v>24</v>
       </c>
       <c r="D91" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E91" t="s">
         <v>26</v>
@@ -3889,7 +3940,7 @@
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B92" t="s">
         <v>69</v>
@@ -3898,7 +3949,7 @@
         <v>64</v>
       </c>
       <c r="D92" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E92" t="s">
         <v>47</v>
@@ -3907,18 +3958,18 @@
         <v>63</v>
       </c>
       <c r="G92" t="s">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B93" t="s">
         <v>69</v>
@@ -3927,7 +3978,7 @@
         <v>100</v>
       </c>
       <c r="D93" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E93" t="s">
         <v>43</v>
@@ -3947,7 +3998,7 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B94" t="s">
         <v>69</v>
@@ -3956,7 +4007,7 @@
         <v>72</v>
       </c>
       <c r="D94" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E94" t="s">
         <v>81</v>
@@ -3976,7 +4027,7 @@
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B95" t="s">
         <v>77</v>
@@ -3985,27 +4036,27 @@
         <v>64</v>
       </c>
       <c r="D95" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E95" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="F95" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="G95" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B96" t="s">
         <v>77</v>
@@ -4014,16 +4065,16 @@
         <v>72</v>
       </c>
       <c r="D96" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E96" t="s">
         <v>47</v>
       </c>
       <c r="F96" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="G96" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
@@ -4034,7 +4085,7 @@
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B97" t="s">
         <v>77</v>
@@ -4043,13 +4094,13 @@
         <v>24</v>
       </c>
       <c r="D97" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E97" t="s">
         <v>26</v>
       </c>
       <c r="F97" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="G97" t="s">
         <v>109</v>
@@ -4063,25 +4114,25 @@
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B98" t="s">
         <v>77</v>
       </c>
       <c r="C98" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D98" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E98" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F98" t="s">
         <v>16</v>
       </c>
       <c r="G98" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
@@ -4092,7 +4143,7 @@
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B99" t="s">
         <v>90</v>
@@ -4101,7 +4152,7 @@
         <v>64</v>
       </c>
       <c r="D99" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E99" t="s">
         <v>47</v>
@@ -4110,7 +4161,7 @@
         <v>63</v>
       </c>
       <c r="G99" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
@@ -4121,7 +4172,7 @@
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B100" t="s">
         <v>90</v>
@@ -4133,13 +4184,13 @@
         <v>36</v>
       </c>
       <c r="E100" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F100" t="s">
         <v>23</v>
       </c>
       <c r="G100" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
@@ -4150,7 +4201,7 @@
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B101" t="s">
         <v>90</v>
@@ -4159,7 +4210,7 @@
         <v>100</v>
       </c>
       <c r="D101" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E101" t="s">
         <v>43</v>
@@ -4179,7 +4230,7 @@
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B102" t="s">
         <v>90</v>
@@ -4188,7 +4239,7 @@
         <v>72</v>
       </c>
       <c r="D102" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E102" t="s">
         <v>74</v>
@@ -4208,7 +4259,7 @@
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B103" t="s">
         <v>90</v>
@@ -4217,13 +4268,13 @@
         <v>24</v>
       </c>
       <c r="D103" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E103" t="s">
         <v>26</v>
       </c>
       <c r="F103" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G103" t="s">
         <v>109</v>
@@ -4237,7 +4288,7 @@
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B104" t="s">
         <v>99</v>
@@ -4246,7 +4297,7 @@
         <v>64</v>
       </c>
       <c r="D104" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E104" t="s">
         <v>47</v>
@@ -4255,10 +4306,10 @@
         <v>63</v>
       </c>
       <c r="G104" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="H104" t="s">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="I104" t="s">
         <v>19</v>
@@ -4266,7 +4317,7 @@
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B105" t="s">
         <v>99</v>
@@ -4275,7 +4326,7 @@
         <v>100</v>
       </c>
       <c r="D105" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E105" t="s">
         <v>86</v>
@@ -4295,22 +4346,22 @@
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B106" t="s">
         <v>99</v>
       </c>
       <c r="C106" t="s">
+        <v>141</v>
+      </c>
+      <c r="D106" t="s">
+        <v>179</v>
+      </c>
+      <c r="E106" t="s">
         <v>143</v>
       </c>
-      <c r="D106" t="s">
-        <v>177</v>
-      </c>
-      <c r="E106" t="s">
-        <v>145</v>
-      </c>
       <c r="F106" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G106" t="s">
         <v>98</v>
@@ -4324,22 +4375,22 @@
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B107" t="s">
         <v>99</v>
       </c>
       <c r="C107" t="s">
+        <v>141</v>
+      </c>
+      <c r="D107" t="s">
+        <v>180</v>
+      </c>
+      <c r="E107" t="s">
         <v>143</v>
       </c>
-      <c r="D107" t="s">
-        <v>178</v>
-      </c>
-      <c r="E107" t="s">
-        <v>145</v>
-      </c>
       <c r="F107" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G107" t="s">
         <v>98</v>
@@ -4353,22 +4404,22 @@
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B108" t="s">
         <v>99</v>
       </c>
       <c r="C108" t="s">
+        <v>141</v>
+      </c>
+      <c r="D108" t="s">
+        <v>181</v>
+      </c>
+      <c r="E108" t="s">
         <v>143</v>
       </c>
-      <c r="D108" t="s">
-        <v>179</v>
-      </c>
-      <c r="E108" t="s">
-        <v>145</v>
-      </c>
       <c r="F108" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G108" t="s">
         <v>98</v>
@@ -4382,25 +4433,25 @@
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B109" t="s">
         <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D109" t="s">
-        <v>181</v>
+        <v>39</v>
       </c>
       <c r="E109" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="F109" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G109" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
@@ -4411,25 +4462,25 @@
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B110" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D110" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="E110" t="s">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="F110" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="G110" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H110" t="s">
         <v>18</v>
@@ -4440,54 +4491,54 @@
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B111" t="s">
         <v>34</v>
       </c>
       <c r="C111" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D111" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="E111" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="F111" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G111" t="s">
-        <v>19</v>
+        <v>184</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B112" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C112" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D112" t="s">
-        <v>25</v>
+        <v>183</v>
       </c>
       <c r="E112" t="s">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="F112" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="G112" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
@@ -4498,25 +4549,25 @@
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B113" t="s">
         <v>46</v>
       </c>
       <c r="C113" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D113" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="E113" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F113" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G113" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
@@ -4527,344 +4578,344 @@
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B114" t="s">
         <v>46</v>
       </c>
       <c r="C114" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>166</v>
+        <v>25</v>
       </c>
       <c r="E114" t="s">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="F114" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G114" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="H114" t="s">
         <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B115" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C115" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D115" t="s">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="E115" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="F115" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="G115" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B116" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C116" t="s">
         <v>52</v>
       </c>
       <c r="D116" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E116" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="F116" t="s">
-        <v>51</v>
+        <v>186</v>
       </c>
       <c r="G116" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B117" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C117" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D117" t="s">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="E117" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="F117" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="G117" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B118" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C118" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D118" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="E118" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F118" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="G118" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B119" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C119" t="s">
         <v>52</v>
       </c>
       <c r="D119" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="E119" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="F119" t="s">
-        <v>51</v>
+        <v>186</v>
       </c>
       <c r="G119" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
       </c>
       <c r="I119" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B120" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C120" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D120" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E120" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="F120" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="G120" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
       </c>
       <c r="I120" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B121" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C121" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D121" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="E121" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F121" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="G121" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B122" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C122" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D122" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="E122" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="F122" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="G122" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B123" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C123" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D123" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="E123" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F123" t="s">
-        <v>56</v>
+        <v>186</v>
       </c>
       <c r="G123" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B124" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C124" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="D124" t="s">
-        <v>91</v>
+        <v>167</v>
       </c>
       <c r="E124" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="F124" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="G124" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
       </c>
       <c r="I124" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B125" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C125" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D125" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E125" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="F125" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="G125" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
@@ -4875,25 +4926,25 @@
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B126" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C126" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D126" t="s">
-        <v>184</v>
+        <v>91</v>
       </c>
       <c r="E126" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F126" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="G126" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
@@ -4904,16 +4955,16 @@
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B127" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C127" t="s">
         <v>20</v>
       </c>
       <c r="D127" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E127" t="s">
         <v>22</v>
@@ -4922,10 +4973,10 @@
         <v>23</v>
       </c>
       <c r="G127" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="H127" t="s">
-        <v>18</v>
+        <v>188</v>
       </c>
       <c r="I127" t="s">
         <v>19</v>
@@ -4933,141 +4984,141 @@
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B128" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C128" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D128" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E128" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="F128" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="G128" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="H128" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="I128" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B129" t="s">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="C129" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="D129" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="E129" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="F129" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G129" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B130" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="C130" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D130" t="s">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="E130" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="F130" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="G130" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B131" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="C131" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="D131" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="E131" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="F131" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G131" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H131" t="s">
         <v>18</v>
       </c>
       <c r="I131" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B132" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="C132" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D132" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
       <c r="E132" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F132" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="G132" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
@@ -5078,16 +5129,16 @@
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B133" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="C133" t="s">
         <v>20</v>
       </c>
       <c r="D133" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E133" t="s">
         <v>22</v>
@@ -5096,7 +5147,7 @@
         <v>23</v>
       </c>
       <c r="G133" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
@@ -5107,83 +5158,83 @@
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B134" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="C134" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D134" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="E134" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="F134" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="G134" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H134" t="s">
         <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B135" t="s">
-        <v>46</v>
+        <v>149</v>
       </c>
       <c r="C135" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="D135" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E135" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="F135" t="s">
-        <v>190</v>
+        <v>103</v>
       </c>
       <c r="G135" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="H135" t="s">
         <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B136" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="C136" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D136" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="E136" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="F136" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="G136" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H136" t="s">
         <v>18</v>
@@ -5194,25 +5245,25 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B137" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C137" t="s">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="D137" t="s">
-        <v>192</v>
+        <v>25</v>
       </c>
       <c r="E137" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F137" t="s">
-        <v>193</v>
+        <v>23</v>
       </c>
       <c r="G137" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
@@ -5223,16 +5274,16 @@
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B138" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C138" t="s">
         <v>20</v>
       </c>
       <c r="D138" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E138" t="s">
         <v>22</v>
@@ -5241,7 +5292,7 @@
         <v>23</v>
       </c>
       <c r="G138" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
@@ -5252,112 +5303,112 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B139" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C139" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D139" t="s">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="E139" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="F139" t="s">
-        <v>190</v>
+        <v>23</v>
       </c>
       <c r="G139" t="s">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="H139" t="s">
         <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B140" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C140" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D140" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="E140" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F140" t="s">
-        <v>51</v>
+        <v>196</v>
       </c>
       <c r="G140" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H140" t="s">
         <v>18</v>
       </c>
       <c r="I140" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B141" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C141" t="s">
-        <v>191</v>
+        <v>52</v>
       </c>
       <c r="D141" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="E141" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="F141" t="s">
-        <v>193</v>
+        <v>23</v>
       </c>
       <c r="G141" t="s">
-        <v>93</v>
+        <v>197</v>
       </c>
       <c r="H141" t="s">
         <v>18</v>
       </c>
       <c r="I141" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B142" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C142" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="D142" t="s">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="E142" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="F142" t="s">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="G142" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="H142" t="s">
         <v>18</v>
@@ -5368,141 +5419,141 @@
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B143" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C143" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D143" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="E143" t="s">
         <v>86</v>
       </c>
       <c r="F143" t="s">
-        <v>23</v>
+        <v>186</v>
       </c>
       <c r="G143" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H143" t="s">
         <v>18</v>
       </c>
       <c r="I143" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B144" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C144" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D144" t="s">
-        <v>189</v>
+        <v>125</v>
       </c>
       <c r="E144" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="F144" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="G144" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="H144" t="s">
         <v>18</v>
       </c>
       <c r="I144" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B145" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C145" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D145" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="E145" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="F145" t="s">
-        <v>51</v>
+        <v>196</v>
       </c>
       <c r="G145" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H145" t="s">
         <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B146" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C146" t="s">
-        <v>191</v>
+        <v>52</v>
       </c>
       <c r="D146" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="E146" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="F146" t="s">
-        <v>193</v>
+        <v>23</v>
       </c>
       <c r="G146" t="s">
-        <v>93</v>
+        <v>197</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B147" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C147" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="D147" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="E147" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="F147" t="s">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="G147" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="H147" t="s">
         <v>18</v>
@@ -5513,25 +5564,25 @@
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B148" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C148" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="D148" t="s">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="E148" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="F148" t="s">
-        <v>196</v>
+        <v>132</v>
       </c>
       <c r="G148" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H148" t="s">
         <v>18</v>
@@ -5542,10 +5593,10 @@
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B149" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C149" t="s">
         <v>20</v>
@@ -5554,216 +5605,216 @@
         <v>71</v>
       </c>
       <c r="E149" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="F149" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G149" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H149" t="s">
         <v>18</v>
       </c>
       <c r="I149" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B150" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C150" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D150" t="s">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="E150" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F150" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="G150" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="H150" t="s">
         <v>18</v>
       </c>
       <c r="I150" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B151" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C151" t="s">
-        <v>191</v>
+        <v>52</v>
       </c>
       <c r="D151" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="E151" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F151" t="s">
-        <v>193</v>
+        <v>23</v>
       </c>
       <c r="G151" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="H151" t="s">
         <v>18</v>
       </c>
       <c r="I151" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B152" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C152" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="D152" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E152" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F152" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="G152" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H152" t="s">
         <v>18</v>
       </c>
       <c r="I152" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B153" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C153" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D153" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="E153" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="F153" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="G153" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="H153" t="s">
         <v>18</v>
       </c>
       <c r="I153" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B154" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C154" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D154" t="s">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="E154" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F154" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="G154" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H154" t="s">
         <v>18</v>
       </c>
       <c r="I154" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B155" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C155" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D155" t="s">
-        <v>199</v>
+        <v>71</v>
       </c>
       <c r="E155" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="F155" t="s">
-        <v>196</v>
+        <v>23</v>
       </c>
       <c r="G155" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="H155" t="s">
         <v>18</v>
       </c>
       <c r="I155" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B156" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C156" t="s">
         <v>52</v>
       </c>
       <c r="D156" t="s">
-        <v>71</v>
+        <v>133</v>
       </c>
       <c r="E156" t="s">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="F156" t="s">
         <v>51</v>
       </c>
       <c r="G156" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H156" t="s">
         <v>18</v>
@@ -5774,54 +5825,54 @@
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B157" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C157" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D157" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="E157" t="s">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="F157" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="G157" t="s">
-        <v>172</v>
+        <v>96</v>
       </c>
       <c r="H157" t="s">
         <v>18</v>
       </c>
       <c r="I157" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B158" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C158" t="s">
-        <v>200</v>
+        <v>64</v>
       </c>
       <c r="D158" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="E158" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="F158" t="s">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="G158" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
@@ -5832,83 +5883,83 @@
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B159" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C159" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="D159" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="E159" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F159" t="s">
-        <v>196</v>
+        <v>48</v>
       </c>
       <c r="G159" t="s">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="H159" t="s">
         <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B160" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C160" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="D160" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="E160" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="F160" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G160" t="s">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B161" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C161" t="s">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="D161" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="E161" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="F161" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G161" t="s">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="H161" t="s">
         <v>18</v>
@@ -5919,25 +5970,25 @@
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B162" t="s">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="C162" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D162" t="s">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="E162" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="F162" t="s">
-        <v>196</v>
+        <v>51</v>
       </c>
       <c r="G162" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H162" t="s">
         <v>18</v>
@@ -5948,30 +5999,291 @@
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B163" t="s">
-        <v>202</v>
+        <v>99</v>
       </c>
       <c r="C163" t="s">
+        <v>64</v>
+      </c>
+      <c r="D163" t="s">
+        <v>125</v>
+      </c>
+      <c r="E163" t="s">
+        <v>47</v>
+      </c>
+      <c r="F163" t="s">
+        <v>144</v>
+      </c>
+      <c r="G163" t="s">
+        <v>79</v>
+      </c>
+      <c r="H163" t="s">
+        <v>18</v>
+      </c>
+      <c r="I163" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="15">
+      <c r="A164" t="s">
+        <v>194</v>
+      </c>
+      <c r="B164" t="s">
+        <v>99</v>
+      </c>
+      <c r="C164" t="s">
         <v>13</v>
       </c>
-      <c r="D163" t="s">
-        <v>203</v>
-      </c>
-      <c r="E163" t="s">
+      <c r="D164" t="s">
+        <v>206</v>
+      </c>
+      <c r="E164" t="s">
         <v>15</v>
       </c>
-      <c r="F163" t="s">
+      <c r="F164" t="s">
+        <v>207</v>
+      </c>
+      <c r="G164" t="s">
+        <v>98</v>
+      </c>
+      <c r="H164" t="s">
+        <v>18</v>
+      </c>
+      <c r="I164" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="15">
+      <c r="A165" t="s">
+        <v>194</v>
+      </c>
+      <c r="B165" t="s">
+        <v>99</v>
+      </c>
+      <c r="C165" t="s">
+        <v>52</v>
+      </c>
+      <c r="D165" t="s">
+        <v>71</v>
+      </c>
+      <c r="E165" t="s">
+        <v>86</v>
+      </c>
+      <c r="F165" t="s">
+        <v>44</v>
+      </c>
+      <c r="G165" t="s">
+        <v>45</v>
+      </c>
+      <c r="H165" t="s">
+        <v>18</v>
+      </c>
+      <c r="I165" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="15">
+      <c r="A166" t="s">
+        <v>194</v>
+      </c>
+      <c r="B166" t="s">
+        <v>99</v>
+      </c>
+      <c r="C166" t="s">
+        <v>170</v>
+      </c>
+      <c r="D166" t="s">
+        <v>171</v>
+      </c>
+      <c r="E166" t="s">
+        <v>172</v>
+      </c>
+      <c r="F166" t="s">
+        <v>16</v>
+      </c>
+      <c r="G166" t="s">
+        <v>173</v>
+      </c>
+      <c r="H166" t="s">
+        <v>18</v>
+      </c>
+      <c r="I166" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="15">
+      <c r="A167" t="s">
+        <v>194</v>
+      </c>
+      <c r="B167" t="s">
+        <v>99</v>
+      </c>
+      <c r="C167" t="s">
+        <v>208</v>
+      </c>
+      <c r="D167" t="s">
+        <v>153</v>
+      </c>
+      <c r="E167" t="s">
+        <v>37</v>
+      </c>
+      <c r="F167" t="s">
+        <v>41</v>
+      </c>
+      <c r="G167" t="s">
+        <v>209</v>
+      </c>
+      <c r="H167" t="s">
+        <v>18</v>
+      </c>
+      <c r="I167" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="15">
+      <c r="A168" t="s">
+        <v>194</v>
+      </c>
+      <c r="B168" t="s">
+        <v>101</v>
+      </c>
+      <c r="C168" t="s">
+        <v>13</v>
+      </c>
+      <c r="D168" t="s">
+        <v>171</v>
+      </c>
+      <c r="E168" t="s">
+        <v>15</v>
+      </c>
+      <c r="F168" t="s">
+        <v>207</v>
+      </c>
+      <c r="G168" t="s">
+        <v>98</v>
+      </c>
+      <c r="H168" t="s">
+        <v>18</v>
+      </c>
+      <c r="I168" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="15">
+      <c r="A169" t="s">
+        <v>194</v>
+      </c>
+      <c r="B169" t="s">
+        <v>101</v>
+      </c>
+      <c r="C169" t="s">
+        <v>52</v>
+      </c>
+      <c r="D169" t="s">
+        <v>125</v>
+      </c>
+      <c r="E169" t="s">
+        <v>86</v>
+      </c>
+      <c r="F169" t="s">
+        <v>44</v>
+      </c>
+      <c r="G169" t="s">
+        <v>45</v>
+      </c>
+      <c r="H169" t="s">
+        <v>18</v>
+      </c>
+      <c r="I169" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="15">
+      <c r="A170" t="s">
+        <v>194</v>
+      </c>
+      <c r="B170" t="s">
+        <v>101</v>
+      </c>
+      <c r="C170" t="s">
+        <v>208</v>
+      </c>
+      <c r="D170" t="s">
+        <v>153</v>
+      </c>
+      <c r="E170" t="s">
+        <v>37</v>
+      </c>
+      <c r="F170" t="s">
+        <v>41</v>
+      </c>
+      <c r="G170" t="s">
+        <v>209</v>
+      </c>
+      <c r="H170" t="s">
+        <v>18</v>
+      </c>
+      <c r="I170" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="15">
+      <c r="A171" t="s">
+        <v>194</v>
+      </c>
+      <c r="B171" t="s">
+        <v>149</v>
+      </c>
+      <c r="C171" t="s">
+        <v>13</v>
+      </c>
+      <c r="D171" t="s">
+        <v>198</v>
+      </c>
+      <c r="E171" t="s">
+        <v>81</v>
+      </c>
+      <c r="F171" t="s">
+        <v>82</v>
+      </c>
+      <c r="G171" t="s">
+        <v>96</v>
+      </c>
+      <c r="H171" t="s">
+        <v>18</v>
+      </c>
+      <c r="I171" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="15">
+      <c r="A172" t="s">
+        <v>194</v>
+      </c>
+      <c r="B172" t="s">
+        <v>210</v>
+      </c>
+      <c r="C172" t="s">
+        <v>13</v>
+      </c>
+      <c r="D172" t="s">
+        <v>211</v>
+      </c>
+      <c r="E172" t="s">
+        <v>15</v>
+      </c>
+      <c r="F172" t="s">
         <v>103</v>
       </c>
-      <c r="G163" t="s">
-        <v>19</v>
-      </c>
-      <c r="H163" t="s">
-        <v>18</v>
-      </c>
-      <c r="I163" t="s">
+      <c r="G172" t="s">
+        <v>98</v>
+      </c>
+      <c r="H172" t="s">
+        <v>18</v>
+      </c>
+      <c r="I172" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5983,8 +6295,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{17473651-90c1-4a2d-abc4-602b796c3078}">
-  <dimension ref="A1:I10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6518aacf-1d49-416c-a6e6-00234ebe9448}">
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -6003,16 +6315,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6032,16 +6344,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -6061,16 +6373,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C3" t="s">
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -6090,16 +6402,16 @@
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E4" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -6119,16 +6431,16 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6145,19 +6457,19 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E6" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -6174,19 +6486,19 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B7" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C7" t="s">
         <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E7" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -6203,19 +6515,19 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C8" t="s">
         <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E8" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -6232,19 +6544,19 @@
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B9" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="E9" t="s">
-        <v>213</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -6261,30 +6573,117 @@
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>220</v>
+      </c>
+      <c r="E10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15">
+      <c r="A11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" t="s">
+        <v>232</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E11" t="s">
+        <v>233</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15">
+      <c r="A12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
         <v>223</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E12" t="s">
+        <v>233</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15">
+      <c r="A13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C13" t="s">
         <v>20</v>
       </c>
-      <c r="D10" t="s">
-        <v>224</v>
-      </c>
-      <c r="E10" t="s">
-        <v>225</v>
-      </c>
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="D13" t="s">
+        <v>236</v>
+      </c>
+      <c r="E13" t="s">
+        <v>237</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6296,8 +6695,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{143c40f5-f4c7-4cea-85d6-390df1e3ff08}">
-  <dimension ref="A1:F30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{07637b1d-028d-4563-8ef2-550fb007b2a4}">
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -6313,13 +6712,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6333,13 +6732,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -6353,13 +6752,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C3" t="s">
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E3" t="s">
         <v>100</v>
@@ -6373,13 +6772,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C4" t="s">
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E4" t="s">
         <v>42</v>
@@ -6393,16 +6792,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="E5" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6413,16 +6812,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -6433,13 +6832,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C7" t="s">
         <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E7" t="s">
         <v>58</v>
@@ -6453,16 +6852,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -6473,16 +6872,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E9" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -6493,13 +6892,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C10" t="s">
         <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E10" t="s">
         <v>117</v>
@@ -6513,13 +6912,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
@@ -6533,16 +6932,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -6553,16 +6952,16 @@
         <v>104</v>
       </c>
       <c r="B13" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -6573,13 +6972,13 @@
         <v>104</v>
       </c>
       <c r="B14" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="C14" t="s">
         <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E14" t="s">
         <v>100</v>
@@ -6593,13 +6992,13 @@
         <v>104</v>
       </c>
       <c r="B15" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C15" t="s">
         <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="E15" t="s">
         <v>119</v>
@@ -6613,13 +7012,13 @@
         <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="C16" t="s">
         <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="E16" t="s">
         <v>117</v>
@@ -6633,16 +7032,16 @@
         <v>104</v>
       </c>
       <c r="B17" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C17" t="s">
         <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -6653,16 +7052,16 @@
         <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C18" t="s">
         <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E18" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -6670,19 +7069,19 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>153</v>
+        <v>104</v>
       </c>
       <c r="B19" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>163</v>
       </c>
       <c r="D19" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>256</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -6690,19 +7089,19 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B20" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -6710,19 +7109,19 @@
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -6730,19 +7129,19 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B22" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -6750,19 +7149,19 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -6770,19 +7169,19 @@
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s">
+        <v>251</v>
+      </c>
+      <c r="C24" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" t="s">
         <v>240</v>
       </c>
-      <c r="C24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" t="s">
-        <v>232</v>
-      </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>258</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -6790,19 +7189,19 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="D25" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -6810,16 +7209,16 @@
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B26" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
@@ -6830,19 +7229,19 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B27" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C27" t="s">
-        <v>191</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
@@ -6850,19 +7249,19 @@
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B28" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
@@ -6870,19 +7269,19 @@
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="C29" t="s">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -6890,21 +7289,201 @@
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B30" t="s">
+        <v>251</v>
+      </c>
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" t="s">
+        <v>244</v>
+      </c>
+      <c r="E30" t="s">
+        <v>261</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15">
+      <c r="A31" t="s">
+        <v>182</v>
+      </c>
+      <c r="B31" t="s">
+        <v>262</v>
+      </c>
+      <c r="C31" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" t="s">
+        <v>240</v>
+      </c>
+      <c r="E31" t="s">
+        <v>197</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15">
+      <c r="A32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" t="s">
+        <v>263</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s">
+        <v>243</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15">
+      <c r="A33" t="s">
+        <v>194</v>
+      </c>
+      <c r="B33" t="s">
+        <v>242</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" t="s">
+        <v>240</v>
+      </c>
+      <c r="E33" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15">
+      <c r="A34" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" t="s">
+        <v>254</v>
+      </c>
+      <c r="C34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" t="s">
         <v>246</v>
       </c>
-      <c r="C30" t="s">
+      <c r="E34" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15">
+      <c r="A35" t="s">
+        <v>194</v>
+      </c>
+      <c r="B35" t="s">
+        <v>254</v>
+      </c>
+      <c r="C35" t="s">
         <v>52</v>
       </c>
-      <c r="D30" t="s">
-        <v>228</v>
-      </c>
-      <c r="E30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="D35" t="s">
+        <v>240</v>
+      </c>
+      <c r="E35" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15">
+      <c r="A36" t="s">
+        <v>194</v>
+      </c>
+      <c r="B36" t="s">
+        <v>254</v>
+      </c>
+      <c r="C36" t="s">
+        <v>164</v>
+      </c>
+      <c r="D36" t="s">
+        <v>244</v>
+      </c>
+      <c r="E36" t="s">
+        <v>197</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15">
+      <c r="A37" t="s">
+        <v>194</v>
+      </c>
+      <c r="B37" t="s">
+        <v>247</v>
+      </c>
+      <c r="C37" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" t="s">
+        <v>255</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15">
+      <c r="A38" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" t="s">
+        <v>248</v>
+      </c>
+      <c r="C38" t="s">
+        <v>164</v>
+      </c>
+      <c r="D38" t="s">
+        <v>240</v>
+      </c>
+      <c r="E38" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15">
+      <c r="A39" t="s">
+        <v>194</v>
+      </c>
+      <c r="B39" t="s">
+        <v>259</v>
+      </c>
+      <c r="C39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" t="s">
+        <v>240</v>
+      </c>
+      <c r="E39" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" t="s">
         <v>18</v>
       </c>
     </row>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="268">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -525,6 +525,9 @@
     <t>2K|CH</t>
   </si>
   <si>
+    <t>Biczysko Wojciech</t>
+  </si>
+  <si>
     <t>2FA|JA2</t>
   </si>
   <si>
@@ -552,9 +555,6 @@
     <t>Fizyka</t>
   </si>
   <si>
-    <t>Biczysko Wojciech</t>
-  </si>
-  <si>
     <t>2K</t>
   </si>
   <si>
@@ -576,6 +576,9 @@
     <t>2WA</t>
   </si>
   <si>
+    <t>Technologie produkcji cukierniczej</t>
+  </si>
+  <si>
     <t>Smaczny Monika</t>
   </si>
   <si>
@@ -585,6 +588,9 @@
     <t>3</t>
   </si>
   <si>
+    <t>42</t>
+  </si>
+  <si>
     <t>2TFA|JA1</t>
   </si>
   <si>
@@ -609,6 +615,9 @@
     <t>06.03.2026</t>
   </si>
   <si>
+    <t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</t>
+  </si>
+  <si>
     <t>5TH</t>
   </si>
   <si>
@@ -616,6 +625,9 @@
   </si>
   <si>
     <t>Kruk Marcin</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>1S|JA2</t>
@@ -1263,7 +1275,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{83075e30-bcff-4fea-9819-1b9bea301d68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f250e64f-3b79-4d43-b2b5-c7353b7db14a}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1284,8 +1296,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2f8ba8ef-1469-496c-bdce-63d9e43eaaf3}">
-  <dimension ref="A1:I172"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f9c2e81e-3084-4240-b0e2-924124e9e296}">
+  <dimension ref="A1:I186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -4033,19 +4045,19 @@
         <v>77</v>
       </c>
       <c r="C95" t="s">
-        <v>64</v>
+        <v>167</v>
       </c>
       <c r="D95" t="s">
-        <v>167</v>
+        <v>36</v>
       </c>
       <c r="E95" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="F95" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G95" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
@@ -4062,19 +4074,19 @@
         <v>77</v>
       </c>
       <c r="C96" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D96" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E96" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="F96" t="s">
-        <v>168</v>
+        <v>44</v>
       </c>
       <c r="G96" t="s">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
@@ -4091,19 +4103,19 @@
         <v>77</v>
       </c>
       <c r="C97" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D97" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="E97" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F97" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="G97" t="s">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
@@ -4120,19 +4132,19 @@
         <v>77</v>
       </c>
       <c r="C98" t="s">
-        <v>170</v>
+        <v>24</v>
       </c>
       <c r="D98" t="s">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="E98" t="s">
-        <v>172</v>
+        <v>26</v>
       </c>
       <c r="F98" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="G98" t="s">
-        <v>173</v>
+        <v>109</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
@@ -4146,28 +4158,28 @@
         <v>151</v>
       </c>
       <c r="B99" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C99" t="s">
-        <v>64</v>
+        <v>171</v>
       </c>
       <c r="D99" t="s">
+        <v>172</v>
+      </c>
+      <c r="E99" t="s">
+        <v>173</v>
+      </c>
+      <c r="F99" t="s">
+        <v>16</v>
+      </c>
+      <c r="G99" t="s">
         <v>174</v>
       </c>
-      <c r="E99" t="s">
-        <v>47</v>
-      </c>
-      <c r="F99" t="s">
-        <v>63</v>
-      </c>
-      <c r="G99" t="s">
-        <v>98</v>
-      </c>
       <c r="H99" t="s">
         <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
@@ -4178,25 +4190,25 @@
         <v>90</v>
       </c>
       <c r="C100" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="D100" t="s">
-        <v>36</v>
+        <v>175</v>
       </c>
       <c r="E100" t="s">
-        <v>175</v>
+        <v>47</v>
       </c>
       <c r="F100" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="G100" t="s">
-        <v>176</v>
+        <v>98</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
@@ -4207,25 +4219,25 @@
         <v>90</v>
       </c>
       <c r="C101" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="D101" t="s">
-        <v>152</v>
+        <v>36</v>
       </c>
       <c r="E101" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="F101" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="G101" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
       </c>
       <c r="I101" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15">
@@ -4236,19 +4248,19 @@
         <v>90</v>
       </c>
       <c r="C102" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D102" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="E102" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="F102" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="G102" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
@@ -4265,19 +4277,19 @@
         <v>90</v>
       </c>
       <c r="C103" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D103" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E103" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F103" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="G103" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
@@ -4291,28 +4303,28 @@
         <v>151</v>
       </c>
       <c r="B104" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C104" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D104" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="E104" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F104" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="G104" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="H104" t="s">
-        <v>178</v>
+        <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
@@ -4323,16 +4335,16 @@
         <v>99</v>
       </c>
       <c r="C105" t="s">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="D105" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="E105" t="s">
-        <v>86</v>
+        <v>176</v>
       </c>
       <c r="F105" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="G105" t="s">
         <v>98</v>
@@ -4352,22 +4364,22 @@
         <v>99</v>
       </c>
       <c r="C106" t="s">
-        <v>141</v>
+        <v>64</v>
       </c>
       <c r="D106" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E106" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="F106" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="G106" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H106" t="s">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="I106" t="s">
         <v>19</v>
@@ -4381,16 +4393,16 @@
         <v>99</v>
       </c>
       <c r="C107" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="D107" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="E107" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="F107" t="s">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="G107" t="s">
         <v>98</v>
@@ -4413,7 +4425,7 @@
         <v>141</v>
       </c>
       <c r="D108" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E108" t="s">
         <v>143</v>
@@ -4433,25 +4445,25 @@
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B109" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="C109" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="D109" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="E109" t="s">
-        <v>47</v>
+        <v>143</v>
       </c>
       <c r="F109" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="G109" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
@@ -4462,25 +4474,25 @@
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B110" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="C110" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="D110" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E110" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="F110" t="s">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="G110" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="H110" t="s">
         <v>18</v>
@@ -4494,28 +4506,28 @@
         <v>182</v>
       </c>
       <c r="B111" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C111" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D111" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="E111" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="F111" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="G111" t="s">
-        <v>184</v>
+        <v>17</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15">
@@ -4523,7 +4535,7 @@
         <v>182</v>
       </c>
       <c r="B112" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C112" t="s">
         <v>52</v>
@@ -4552,28 +4564,28 @@
         <v>182</v>
       </c>
       <c r="B113" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D113" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="E113" t="s">
-        <v>47</v>
+        <v>184</v>
       </c>
       <c r="F113" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="G113" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
@@ -4581,28 +4593,28 @@
         <v>182</v>
       </c>
       <c r="B114" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C114" t="s">
         <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="E114" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="F114" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G114" t="s">
-        <v>58</v>
+        <v>185</v>
       </c>
       <c r="H114" t="s">
         <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
@@ -4610,28 +4622,28 @@
         <v>182</v>
       </c>
       <c r="B115" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C115" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D115" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E115" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F115" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G115" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
@@ -4639,22 +4651,22 @@
         <v>182</v>
       </c>
       <c r="B116" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C116" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D116" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E116" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="F116" t="s">
-        <v>186</v>
+        <v>123</v>
       </c>
       <c r="G116" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
@@ -4668,28 +4680,28 @@
         <v>182</v>
       </c>
       <c r="B117" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C117" t="s">
         <v>64</v>
       </c>
       <c r="D117" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="E117" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="F117" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="G117" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
@@ -4697,22 +4709,22 @@
         <v>182</v>
       </c>
       <c r="B118" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C118" t="s">
         <v>20</v>
       </c>
       <c r="D118" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="E118" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F118" t="s">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="G118" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
@@ -4726,28 +4738,28 @@
         <v>182</v>
       </c>
       <c r="B119" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C119" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D119" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="E119" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="F119" t="s">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="G119" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
       </c>
       <c r="I119" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
@@ -4755,22 +4767,22 @@
         <v>182</v>
       </c>
       <c r="B120" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C120" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D120" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="E120" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="F120" t="s">
-        <v>114</v>
+        <v>187</v>
       </c>
       <c r="G120" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
@@ -4784,22 +4796,22 @@
         <v>182</v>
       </c>
       <c r="B121" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C121" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D121" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="E121" t="s">
-        <v>40</v>
+        <v>184</v>
       </c>
       <c r="F121" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="G121" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
@@ -4813,28 +4825,28 @@
         <v>182</v>
       </c>
       <c r="B122" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C122" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D122" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="E122" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F122" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="G122" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
@@ -4842,22 +4854,22 @@
         <v>182</v>
       </c>
       <c r="B123" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C123" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D123" t="s">
-        <v>133</v>
+        <v>65</v>
       </c>
       <c r="E123" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F123" t="s">
-        <v>186</v>
+        <v>144</v>
       </c>
       <c r="G123" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
@@ -4871,28 +4883,28 @@
         <v>182</v>
       </c>
       <c r="B124" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C124" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D124" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E124" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="F124" t="s">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="G124" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
       </c>
       <c r="I124" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15">
@@ -4900,22 +4912,22 @@
         <v>182</v>
       </c>
       <c r="B125" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C125" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D125" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E125" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="F125" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="G125" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
@@ -4929,28 +4941,28 @@
         <v>182</v>
       </c>
       <c r="B126" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C126" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="D126" t="s">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="E126" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="F126" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="G126" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
       </c>
       <c r="I126" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
@@ -4958,28 +4970,28 @@
         <v>182</v>
       </c>
       <c r="B127" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C127" t="s">
         <v>20</v>
       </c>
       <c r="D127" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="E127" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F127" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="G127" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="H127" t="s">
-        <v>188</v>
+        <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
@@ -4987,28 +4999,28 @@
         <v>182</v>
       </c>
       <c r="B128" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C128" t="s">
         <v>53</v>
       </c>
       <c r="D128" t="s">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="E128" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="F128" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="G128" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H128" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
@@ -5016,22 +5028,22 @@
         <v>182</v>
       </c>
       <c r="B129" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C129" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D129" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="E129" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="F129" t="s">
-        <v>114</v>
+        <v>187</v>
       </c>
       <c r="G129" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
@@ -5045,28 +5057,28 @@
         <v>182</v>
       </c>
       <c r="B130" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="C130" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D130" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="E130" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F130" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="G130" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
@@ -5074,28 +5086,28 @@
         <v>182</v>
       </c>
       <c r="B131" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C131" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D131" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="E131" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F131" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="G131" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="H131" t="s">
         <v>18</v>
       </c>
       <c r="I131" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
@@ -5103,28 +5115,28 @@
         <v>182</v>
       </c>
       <c r="B132" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C132" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D132" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="E132" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="F132" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="G132" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
@@ -5132,28 +5144,28 @@
         <v>182</v>
       </c>
       <c r="B133" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C133" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D133" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="E133" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F133" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="G133" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
       </c>
       <c r="I133" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
@@ -5161,28 +5173,28 @@
         <v>182</v>
       </c>
       <c r="B134" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C134" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D134" t="s">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="E134" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="F134" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="G134" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="H134" t="s">
         <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
@@ -5190,25 +5202,25 @@
         <v>182</v>
       </c>
       <c r="B135" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="C135" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D135" t="s">
-        <v>191</v>
+        <v>85</v>
       </c>
       <c r="E135" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F135" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="G135" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H135" t="s">
-        <v>18</v>
+        <v>190</v>
       </c>
       <c r="I135" t="s">
         <v>19</v>
@@ -5219,25 +5231,25 @@
         <v>182</v>
       </c>
       <c r="B136" t="s">
-        <v>192</v>
+        <v>90</v>
       </c>
       <c r="C136" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="D136" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="E136" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="F136" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="G136" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H136" t="s">
-        <v>18</v>
+        <v>191</v>
       </c>
       <c r="I136" t="s">
         <v>19</v>
@@ -5245,54 +5257,54 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B137" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="C137" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D137" t="s">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="E137" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="F137" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="G137" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
       </c>
       <c r="I137" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B138" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="C138" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D138" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E138" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F138" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G138" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
@@ -5303,170 +5315,170 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B139" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="C139" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D139" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="E139" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="F139" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="G139" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="H139" t="s">
         <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B140" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="C140" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="D140" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E140" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="F140" t="s">
-        <v>196</v>
+        <v>103</v>
       </c>
       <c r="G140" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="H140" t="s">
         <v>18</v>
       </c>
       <c r="I140" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B141" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="C141" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D141" t="s">
-        <v>165</v>
+        <v>91</v>
       </c>
       <c r="E141" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F141" t="s">
         <v>23</v>
       </c>
       <c r="G141" t="s">
-        <v>197</v>
+        <v>98</v>
       </c>
       <c r="H141" t="s">
         <v>18</v>
       </c>
       <c r="I141" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B142" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="C142" t="s">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="D142" t="s">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c r="E142" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="F142" t="s">
-        <v>199</v>
+        <v>114</v>
       </c>
       <c r="G142" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="H142" t="s">
         <v>18</v>
       </c>
       <c r="I142" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B143" t="s">
-        <v>61</v>
+        <v>149</v>
       </c>
       <c r="C143" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D143" t="s">
-        <v>120</v>
+        <v>193</v>
       </c>
       <c r="E143" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="F143" t="s">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="G143" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="H143" t="s">
         <v>18</v>
       </c>
       <c r="I143" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
+        <v>182</v>
+      </c>
+      <c r="B144" t="s">
         <v>194</v>
       </c>
-      <c r="B144" t="s">
-        <v>61</v>
-      </c>
       <c r="C144" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D144" t="s">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="E144" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F144" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="G144" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="H144" t="s">
         <v>18</v>
@@ -5477,80 +5489,80 @@
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B145" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="C145" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D145" t="s">
-        <v>195</v>
+        <v>25</v>
       </c>
       <c r="E145" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="F145" t="s">
-        <v>196</v>
+        <v>23</v>
       </c>
       <c r="G145" t="s">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="H145" t="s">
         <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B146" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="C146" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D146" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E146" t="s">
-        <v>86</v>
+        <v>197</v>
       </c>
       <c r="F146" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="G146" t="s">
-        <v>197</v>
+        <v>17</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B147" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C147" t="s">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="D147" t="s">
-        <v>198</v>
+        <v>85</v>
       </c>
       <c r="E147" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F147" t="s">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="G147" t="s">
         <v>17</v>
@@ -5564,22 +5576,22 @@
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B148" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C148" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="D148" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="E148" t="s">
-        <v>88</v>
+        <v>197</v>
       </c>
       <c r="F148" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G148" t="s">
         <v>17</v>
@@ -5593,10 +5605,10 @@
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B149" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C149" t="s">
         <v>20</v>
@@ -5605,71 +5617,71 @@
         <v>71</v>
       </c>
       <c r="E149" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F149" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G149" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H149" t="s">
         <v>18</v>
       </c>
       <c r="I149" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B150" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C150" t="s">
         <v>72</v>
       </c>
       <c r="D150" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E150" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F150" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="G150" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="H150" t="s">
         <v>18</v>
       </c>
       <c r="I150" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B151" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C151" t="s">
         <v>52</v>
       </c>
       <c r="D151" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E151" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="F151" t="s">
         <v>23</v>
       </c>
       <c r="G151" t="s">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="H151" t="s">
         <v>18</v>
@@ -5680,83 +5692,83 @@
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B152" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C152" t="s">
-        <v>164</v>
+        <v>28</v>
       </c>
       <c r="D152" t="s">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="E152" t="s">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="F152" t="s">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="G152" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="H152" t="s">
         <v>18</v>
       </c>
       <c r="I152" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B153" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C153" t="s">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="D153" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="E153" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="F153" t="s">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="G153" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="H153" t="s">
         <v>18</v>
       </c>
       <c r="I153" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B154" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C154" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D154" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="E154" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F154" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="G154" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="H154" t="s">
         <v>18</v>
@@ -5767,112 +5779,112 @@
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B155" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C155" t="s">
         <v>20</v>
       </c>
       <c r="D155" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="E155" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F155" t="s">
         <v>23</v>
       </c>
       <c r="G155" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H155" t="s">
         <v>18</v>
       </c>
       <c r="I155" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B156" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C156" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D156" t="s">
-        <v>133</v>
+        <v>198</v>
       </c>
       <c r="E156" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F156" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="G156" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="H156" t="s">
         <v>18</v>
       </c>
       <c r="I156" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B157" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C157" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="D157" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="E157" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F157" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="G157" t="s">
-        <v>96</v>
+        <v>200</v>
       </c>
       <c r="H157" t="s">
         <v>18</v>
       </c>
       <c r="I157" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B158" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="C158" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D158" t="s">
-        <v>174</v>
+        <v>59</v>
       </c>
       <c r="E158" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F158" t="s">
-        <v>186</v>
+        <v>41</v>
       </c>
       <c r="G158" t="s">
-        <v>203</v>
+        <v>38</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
@@ -5883,83 +5895,83 @@
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B159" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="C159" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="D159" t="s">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="E159" t="s">
         <v>47</v>
       </c>
       <c r="F159" t="s">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="G159" t="s">
-        <v>204</v>
+        <v>17</v>
       </c>
       <c r="H159" t="s">
         <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B160" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C160" t="s">
         <v>89</v>
       </c>
       <c r="D160" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="E160" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="F160" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="G160" t="s">
-        <v>204</v>
+        <v>17</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B161" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C161" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D161" t="s">
-        <v>205</v>
+        <v>71</v>
       </c>
       <c r="E161" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="F161" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G161" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="H161" t="s">
         <v>18</v>
@@ -5970,54 +5982,54 @@
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B162" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C162" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D162" t="s">
-        <v>133</v>
+        <v>198</v>
       </c>
       <c r="E162" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F162" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="G162" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="H162" t="s">
         <v>18</v>
       </c>
       <c r="I162" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B163" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="C163" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D163" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="E163" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F163" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="G163" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="H163" t="s">
         <v>18</v>
@@ -6028,83 +6040,83 @@
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B164" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="C164" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D164" t="s">
-        <v>206</v>
+        <v>59</v>
       </c>
       <c r="E164" t="s">
-        <v>15</v>
+        <v>184</v>
       </c>
       <c r="F164" t="s">
-        <v>207</v>
+        <v>132</v>
       </c>
       <c r="G164" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="H164" t="s">
         <v>18</v>
       </c>
       <c r="I164" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B165" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="C165" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="D165" t="s">
-        <v>71</v>
+        <v>204</v>
       </c>
       <c r="E165" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F165" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="G165" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="H165" t="s">
         <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B166" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C166" t="s">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="D166" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E166" t="s">
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="F166" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G166" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="H166" t="s">
         <v>18</v>
@@ -6115,25 +6127,25 @@
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B167" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C167" t="s">
-        <v>208</v>
+        <v>13</v>
       </c>
       <c r="D167" t="s">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="E167" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="F167" t="s">
-        <v>41</v>
+        <v>206</v>
       </c>
       <c r="G167" t="s">
-        <v>209</v>
+        <v>76</v>
       </c>
       <c r="H167" t="s">
         <v>18</v>
@@ -6144,83 +6156,83 @@
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B168" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C168" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D168" t="s">
-        <v>171</v>
+        <v>71</v>
       </c>
       <c r="E168" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="F168" t="s">
-        <v>207</v>
+        <v>23</v>
       </c>
       <c r="G168" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H168" t="s">
         <v>18</v>
       </c>
       <c r="I168" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B169" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C169" t="s">
         <v>52</v>
       </c>
       <c r="D169" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E169" t="s">
         <v>86</v>
       </c>
       <c r="F169" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G169" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="H169" t="s">
         <v>18</v>
       </c>
       <c r="I169" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B170" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C170" t="s">
-        <v>208</v>
+        <v>28</v>
       </c>
       <c r="D170" t="s">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="E170" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="F170" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="G170" t="s">
-        <v>209</v>
+        <v>32</v>
       </c>
       <c r="H170" t="s">
         <v>18</v>
@@ -6231,13 +6243,13 @@
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B171" t="s">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="C171" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="D171" t="s">
         <v>198</v>
@@ -6260,30 +6272,436 @@
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B172" t="s">
+        <v>90</v>
+      </c>
+      <c r="C172" t="s">
+        <v>64</v>
+      </c>
+      <c r="D172" t="s">
+        <v>175</v>
+      </c>
+      <c r="E172" t="s">
+        <v>67</v>
+      </c>
+      <c r="F172" t="s">
+        <v>187</v>
+      </c>
+      <c r="G172" t="s">
+        <v>207</v>
+      </c>
+      <c r="H172" t="s">
+        <v>18</v>
+      </c>
+      <c r="I172" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="15">
+      <c r="A173" t="s">
+        <v>196</v>
+      </c>
+      <c r="B173" t="s">
+        <v>90</v>
+      </c>
+      <c r="C173" t="s">
+        <v>89</v>
+      </c>
+      <c r="D173" t="s">
+        <v>105</v>
+      </c>
+      <c r="E173" t="s">
+        <v>47</v>
+      </c>
+      <c r="F173" t="s">
+        <v>48</v>
+      </c>
+      <c r="G173" t="s">
+        <v>208</v>
+      </c>
+      <c r="H173" t="s">
+        <v>18</v>
+      </c>
+      <c r="I173" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="15">
+      <c r="A174" t="s">
+        <v>196</v>
+      </c>
+      <c r="B174" t="s">
+        <v>90</v>
+      </c>
+      <c r="C174" t="s">
+        <v>89</v>
+      </c>
+      <c r="D174" t="s">
+        <v>102</v>
+      </c>
+      <c r="E174" t="s">
+        <v>47</v>
+      </c>
+      <c r="F174" t="s">
+        <v>48</v>
+      </c>
+      <c r="G174" t="s">
+        <v>208</v>
+      </c>
+      <c r="H174" t="s">
+        <v>18</v>
+      </c>
+      <c r="I174" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="15">
+      <c r="A175" t="s">
+        <v>196</v>
+      </c>
+      <c r="B175" t="s">
+        <v>90</v>
+      </c>
+      <c r="C175" t="s">
+        <v>13</v>
+      </c>
+      <c r="D175" t="s">
+        <v>209</v>
+      </c>
+      <c r="E175" t="s">
+        <v>86</v>
+      </c>
+      <c r="F175" t="s">
+        <v>51</v>
+      </c>
+      <c r="G175" t="s">
+        <v>100</v>
+      </c>
+      <c r="H175" t="s">
+        <v>18</v>
+      </c>
+      <c r="I175" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="15">
+      <c r="A176" t="s">
+        <v>196</v>
+      </c>
+      <c r="B176" t="s">
+        <v>90</v>
+      </c>
+      <c r="C176" t="s">
+        <v>52</v>
+      </c>
+      <c r="D176" t="s">
+        <v>133</v>
+      </c>
+      <c r="E176" t="s">
+        <v>86</v>
+      </c>
+      <c r="F176" t="s">
+        <v>51</v>
+      </c>
+      <c r="G176" t="s">
+        <v>98</v>
+      </c>
+      <c r="H176" t="s">
+        <v>18</v>
+      </c>
+      <c r="I176" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="15">
+      <c r="A177" t="s">
+        <v>196</v>
+      </c>
+      <c r="B177" t="s">
+        <v>99</v>
+      </c>
+      <c r="C177" t="s">
+        <v>64</v>
+      </c>
+      <c r="D177" t="s">
+        <v>125</v>
+      </c>
+      <c r="E177" t="s">
+        <v>47</v>
+      </c>
+      <c r="F177" t="s">
+        <v>144</v>
+      </c>
+      <c r="G177" t="s">
+        <v>79</v>
+      </c>
+      <c r="H177" t="s">
+        <v>18</v>
+      </c>
+      <c r="I177" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="15">
+      <c r="A178" t="s">
+        <v>196</v>
+      </c>
+      <c r="B178" t="s">
+        <v>99</v>
+      </c>
+      <c r="C178" t="s">
+        <v>13</v>
+      </c>
+      <c r="D178" t="s">
         <v>210</v>
       </c>
-      <c r="C172" t="s">
+      <c r="E178" t="s">
+        <v>15</v>
+      </c>
+      <c r="F178" t="s">
+        <v>211</v>
+      </c>
+      <c r="G178" t="s">
+        <v>98</v>
+      </c>
+      <c r="H178" t="s">
+        <v>18</v>
+      </c>
+      <c r="I178" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="15">
+      <c r="A179" t="s">
+        <v>196</v>
+      </c>
+      <c r="B179" t="s">
+        <v>99</v>
+      </c>
+      <c r="C179" t="s">
+        <v>52</v>
+      </c>
+      <c r="D179" t="s">
+        <v>71</v>
+      </c>
+      <c r="E179" t="s">
+        <v>86</v>
+      </c>
+      <c r="F179" t="s">
+        <v>44</v>
+      </c>
+      <c r="G179" t="s">
+        <v>45</v>
+      </c>
+      <c r="H179" t="s">
+        <v>18</v>
+      </c>
+      <c r="I179" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="15">
+      <c r="A180" t="s">
+        <v>196</v>
+      </c>
+      <c r="B180" t="s">
+        <v>99</v>
+      </c>
+      <c r="C180" t="s">
+        <v>171</v>
+      </c>
+      <c r="D180" t="s">
+        <v>172</v>
+      </c>
+      <c r="E180" t="s">
+        <v>173</v>
+      </c>
+      <c r="F180" t="s">
+        <v>16</v>
+      </c>
+      <c r="G180" t="s">
+        <v>174</v>
+      </c>
+      <c r="H180" t="s">
+        <v>18</v>
+      </c>
+      <c r="I180" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="15">
+      <c r="A181" t="s">
+        <v>196</v>
+      </c>
+      <c r="B181" t="s">
+        <v>99</v>
+      </c>
+      <c r="C181" t="s">
+        <v>212</v>
+      </c>
+      <c r="D181" t="s">
+        <v>153</v>
+      </c>
+      <c r="E181" t="s">
+        <v>37</v>
+      </c>
+      <c r="F181" t="s">
+        <v>41</v>
+      </c>
+      <c r="G181" t="s">
+        <v>213</v>
+      </c>
+      <c r="H181" t="s">
+        <v>18</v>
+      </c>
+      <c r="I181" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="15">
+      <c r="A182" t="s">
+        <v>196</v>
+      </c>
+      <c r="B182" t="s">
+        <v>101</v>
+      </c>
+      <c r="C182" t="s">
         <v>13</v>
       </c>
-      <c r="D172" t="s">
+      <c r="D182" t="s">
+        <v>172</v>
+      </c>
+      <c r="E182" t="s">
+        <v>15</v>
+      </c>
+      <c r="F182" t="s">
         <v>211</v>
       </c>
-      <c r="E172" t="s">
+      <c r="G182" t="s">
+        <v>98</v>
+      </c>
+      <c r="H182" t="s">
+        <v>18</v>
+      </c>
+      <c r="I182" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="15">
+      <c r="A183" t="s">
+        <v>196</v>
+      </c>
+      <c r="B183" t="s">
+        <v>101</v>
+      </c>
+      <c r="C183" t="s">
+        <v>52</v>
+      </c>
+      <c r="D183" t="s">
+        <v>125</v>
+      </c>
+      <c r="E183" t="s">
+        <v>86</v>
+      </c>
+      <c r="F183" t="s">
+        <v>44</v>
+      </c>
+      <c r="G183" t="s">
+        <v>45</v>
+      </c>
+      <c r="H183" t="s">
+        <v>18</v>
+      </c>
+      <c r="I183" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="15">
+      <c r="A184" t="s">
+        <v>196</v>
+      </c>
+      <c r="B184" t="s">
+        <v>101</v>
+      </c>
+      <c r="C184" t="s">
+        <v>212</v>
+      </c>
+      <c r="D184" t="s">
+        <v>153</v>
+      </c>
+      <c r="E184" t="s">
+        <v>37</v>
+      </c>
+      <c r="F184" t="s">
+        <v>41</v>
+      </c>
+      <c r="G184" t="s">
+        <v>213</v>
+      </c>
+      <c r="H184" t="s">
+        <v>18</v>
+      </c>
+      <c r="I184" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="15">
+      <c r="A185" t="s">
+        <v>196</v>
+      </c>
+      <c r="B185" t="s">
+        <v>149</v>
+      </c>
+      <c r="C185" t="s">
+        <v>13</v>
+      </c>
+      <c r="D185" t="s">
+        <v>202</v>
+      </c>
+      <c r="E185" t="s">
+        <v>81</v>
+      </c>
+      <c r="F185" t="s">
+        <v>82</v>
+      </c>
+      <c r="G185" t="s">
+        <v>96</v>
+      </c>
+      <c r="H185" t="s">
+        <v>18</v>
+      </c>
+      <c r="I185" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="15">
+      <c r="A186" t="s">
+        <v>196</v>
+      </c>
+      <c r="B186" t="s">
+        <v>214</v>
+      </c>
+      <c r="C186" t="s">
+        <v>13</v>
+      </c>
+      <c r="D186" t="s">
+        <v>215</v>
+      </c>
+      <c r="E186" t="s">
         <v>15</v>
       </c>
-      <c r="F172" t="s">
+      <c r="F186" t="s">
         <v>103</v>
       </c>
-      <c r="G172" t="s">
+      <c r="G186" t="s">
         <v>98</v>
       </c>
-      <c r="H172" t="s">
-        <v>18</v>
-      </c>
-      <c r="I172" t="s">
+      <c r="H186" t="s">
+        <v>18</v>
+      </c>
+      <c r="I186" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6295,7 +6713,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6518aacf-1d49-416c-a6e6-00234ebe9448}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{818a551d-e776-4dac-9ba6-6fed0e695c81}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6315,16 +6733,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6344,16 +6762,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -6373,16 +6791,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C3" t="s">
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -6402,16 +6820,16 @@
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -6431,16 +6849,16 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6460,16 +6878,16 @@
         <v>151</v>
       </c>
       <c r="B6" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E6" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -6489,16 +6907,16 @@
         <v>151</v>
       </c>
       <c r="B7" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C7" t="s">
         <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -6518,16 +6936,16 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C8" t="s">
         <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E8" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -6547,13 +6965,13 @@
         <v>182</v>
       </c>
       <c r="B9" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C9" t="s">
         <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E9" t="s">
         <v>47</v>
@@ -6576,16 +6994,16 @@
         <v>182</v>
       </c>
       <c r="B10" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C10" t="s">
         <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E10" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -6605,16 +7023,16 @@
         <v>182</v>
       </c>
       <c r="B11" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C11" t="s">
         <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E11" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -6631,19 +7049,19 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B12" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C12" t="s">
         <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E12" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -6660,19 +7078,19 @@
     </row>
     <row r="13" spans="1:9" ht="15">
       <c r="A13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B13" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E13" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -6695,8 +7113,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{07637b1d-028d-4563-8ef2-550fb007b2a4}">
-  <dimension ref="A1:F39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ad145dd3-0022-4241-8ffb-512ac439cf68}">
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -6712,13 +7130,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6732,13 +7150,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -6752,13 +7170,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C3" t="s">
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E3" t="s">
         <v>100</v>
@@ -6772,13 +7190,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C4" t="s">
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E4" t="s">
         <v>42</v>
@@ -6792,16 +7210,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6812,13 +7230,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E6" t="s">
         <v>136</v>
@@ -6832,13 +7250,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C7" t="s">
         <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E7" t="s">
         <v>58</v>
@@ -6852,16 +7270,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -6872,16 +7290,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E9" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -6892,13 +7310,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C10" t="s">
         <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E10" t="s">
         <v>117</v>
@@ -6912,13 +7330,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
@@ -6932,13 +7350,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E12" t="s">
         <v>136</v>
@@ -6952,16 +7370,16 @@
         <v>104</v>
       </c>
       <c r="B13" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E13" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -6972,13 +7390,13 @@
         <v>104</v>
       </c>
       <c r="B14" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C14" t="s">
         <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E14" t="s">
         <v>100</v>
@@ -6992,13 +7410,13 @@
         <v>104</v>
       </c>
       <c r="B15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C15" t="s">
         <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E15" t="s">
         <v>119</v>
@@ -7012,13 +7430,13 @@
         <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C16" t="s">
         <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E16" t="s">
         <v>117</v>
@@ -7032,13 +7450,13 @@
         <v>104</v>
       </c>
       <c r="B17" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C17" t="s">
         <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E17" t="s">
         <v>136</v>
@@ -7052,16 +7470,16 @@
         <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C18" t="s">
         <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E18" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -7072,16 +7490,16 @@
         <v>104</v>
       </c>
       <c r="B19" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C19" t="s">
         <v>163</v>
       </c>
       <c r="D19" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E19" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -7092,16 +7510,16 @@
         <v>151</v>
       </c>
       <c r="B20" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C20" t="s">
         <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E20" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -7112,13 +7530,13 @@
         <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C21" t="s">
         <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E21" t="s">
         <v>87</v>
@@ -7132,16 +7550,16 @@
         <v>151</v>
       </c>
       <c r="B22" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C22" t="s">
         <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E22" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -7152,16 +7570,16 @@
         <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="D23" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -7172,16 +7590,16 @@
         <v>151</v>
       </c>
       <c r="B24" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E24" t="s">
-        <v>258</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -7192,16 +7610,16 @@
         <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="D25" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E25" t="s">
-        <v>249</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -7212,16 +7630,16 @@
         <v>151</v>
       </c>
       <c r="B26" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>262</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -7229,19 +7647,19 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B27" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="D27" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E27" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
@@ -7249,19 +7667,19 @@
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B28" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E28" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
@@ -7272,16 +7690,16 @@
         <v>182</v>
       </c>
       <c r="B29" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>264</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -7292,16 +7710,16 @@
         <v>182</v>
       </c>
       <c r="B30" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D30" t="s">
         <v>244</v>
       </c>
       <c r="E30" t="s">
-        <v>261</v>
+        <v>76</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
@@ -7312,16 +7730,16 @@
         <v>182</v>
       </c>
       <c r="B31" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E31" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -7332,16 +7750,16 @@
         <v>182</v>
       </c>
       <c r="B32" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
@@ -7349,19 +7767,19 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B33" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E33" t="s">
-        <v>87</v>
+        <v>200</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -7369,19 +7787,19 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B34" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E34" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
@@ -7389,19 +7807,19 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B35" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E35" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
@@ -7409,19 +7827,19 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B36" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C36" t="s">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="D36" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E36" t="s">
-        <v>197</v>
+        <v>24</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
@@ -7429,19 +7847,19 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B37" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D37" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>207</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -7449,19 +7867,19 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B38" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C38" t="s">
         <v>164</v>
       </c>
       <c r="D38" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E38" t="s">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
@@ -7469,21 +7887,61 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s">
+        <v>251</v>
+      </c>
+      <c r="C39" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" t="s">
         <v>259</v>
       </c>
-      <c r="C39" t="s">
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15">
+      <c r="A40" t="s">
+        <v>196</v>
+      </c>
+      <c r="B40" t="s">
+        <v>252</v>
+      </c>
+      <c r="C40" t="s">
+        <v>164</v>
+      </c>
+      <c r="D40" t="s">
+        <v>244</v>
+      </c>
+      <c r="E40" t="s">
+        <v>45</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15">
+      <c r="A41" t="s">
+        <v>196</v>
+      </c>
+      <c r="B41" t="s">
+        <v>263</v>
+      </c>
+      <c r="C41" t="s">
         <v>52</v>
       </c>
-      <c r="D39" t="s">
-        <v>240</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="D41" t="s">
+        <v>244</v>
+      </c>
+      <c r="E41" t="s">
         <v>76</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F41" t="s">
         <v>18</v>
       </c>
     </row>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="271">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -585,19 +585,28 @@
     <t>2TFB|JA1</t>
   </si>
   <si>
+    <t>1K</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
+    <t>2TFA|JA1</t>
+  </si>
+  <si>
     <t>42</t>
   </si>
   <si>
-    <t>2TFA|JA1</t>
+    <t>1TH</t>
   </si>
   <si>
     <t>p. Danielewski, techniki fryzjerskie za lekcję 9</t>
   </si>
   <si>
     <t>p. Dalach, wychowanie fizyczne za lekcję 10</t>
+  </si>
+  <si>
+    <t>1CB</t>
   </si>
   <si>
     <t>1WB|JN2</t>
@@ -1275,7 +1284,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f250e64f-3b79-4d43-b2b5-c7353b7db14a}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{82538555-36f2-4d89-b876-5be66e274ee3}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1296,8 +1305,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f9c2e81e-3084-4240-b0e2-924124e9e296}">
-  <dimension ref="A1:I186"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{142affac-beb8-4b61-ac0a-737e3ddc5add}">
+  <dimension ref="A1:I201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -4576,7 +4585,7 @@
         <v>184</v>
       </c>
       <c r="F113" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="G113" t="s">
         <v>32</v>
@@ -4625,16 +4634,16 @@
         <v>34</v>
       </c>
       <c r="C115" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D115" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="E115" t="s">
-        <v>131</v>
+        <v>26</v>
       </c>
       <c r="F115" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="G115" t="s">
         <v>17</v>
@@ -4654,25 +4663,25 @@
         <v>34</v>
       </c>
       <c r="C116" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D116" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="E116" t="s">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="F116" t="s">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="G116" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
@@ -4680,28 +4689,28 @@
         <v>182</v>
       </c>
       <c r="B117" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C117" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D117" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="E117" t="s">
-        <v>47</v>
+        <v>184</v>
       </c>
       <c r="F117" t="s">
-        <v>63</v>
+        <v>144</v>
       </c>
       <c r="G117" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
@@ -4712,25 +4721,25 @@
         <v>46</v>
       </c>
       <c r="C118" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D118" t="s">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="E118" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F118" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G118" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
@@ -4741,25 +4750,25 @@
         <v>46</v>
       </c>
       <c r="C119" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D119" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="E119" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="F119" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="G119" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
       </c>
       <c r="I119" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
@@ -4770,25 +4779,25 @@
         <v>46</v>
       </c>
       <c r="C120" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D120" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="E120" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F120" t="s">
-        <v>187</v>
+        <v>56</v>
       </c>
       <c r="G120" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
       </c>
       <c r="I120" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15">
@@ -4799,19 +4808,19 @@
         <v>46</v>
       </c>
       <c r="C121" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D121" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="E121" t="s">
-        <v>184</v>
+        <v>40</v>
       </c>
       <c r="F121" t="s">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="G121" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
@@ -4825,22 +4834,22 @@
         <v>182</v>
       </c>
       <c r="B122" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C122" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D122" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="E122" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="F122" t="s">
-        <v>116</v>
+        <v>188</v>
       </c>
       <c r="G122" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
@@ -4854,22 +4863,22 @@
         <v>182</v>
       </c>
       <c r="B123" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C123" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D123" t="s">
-        <v>65</v>
+        <v>175</v>
       </c>
       <c r="E123" t="s">
-        <v>40</v>
+        <v>184</v>
       </c>
       <c r="F123" t="s">
         <v>144</v>
       </c>
       <c r="G123" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
@@ -4886,25 +4895,25 @@
         <v>61</v>
       </c>
       <c r="C124" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D124" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E124" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F124" t="s">
-        <v>187</v>
+        <v>63</v>
       </c>
       <c r="G124" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
       </c>
       <c r="I124" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15">
@@ -4915,19 +4924,19 @@
         <v>61</v>
       </c>
       <c r="C125" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D125" t="s">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c r="E125" t="s">
-        <v>184</v>
+        <v>40</v>
       </c>
       <c r="F125" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="G125" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
@@ -4941,28 +4950,28 @@
         <v>182</v>
       </c>
       <c r="B126" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C126" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D126" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E126" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F126" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="G126" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
       </c>
       <c r="I126" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
@@ -4970,22 +4979,22 @@
         <v>182</v>
       </c>
       <c r="B127" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C127" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D127" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="E127" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F127" t="s">
-        <v>63</v>
+        <v>188</v>
       </c>
       <c r="G127" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
@@ -4999,28 +5008,28 @@
         <v>182</v>
       </c>
       <c r="B128" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C128" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="D128" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E128" t="s">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="F128" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="G128" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
@@ -5031,25 +5040,25 @@
         <v>69</v>
       </c>
       <c r="C129" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D129" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="E129" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F129" t="s">
-        <v>187</v>
+        <v>63</v>
       </c>
       <c r="G129" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
@@ -5060,19 +5069,19 @@
         <v>69</v>
       </c>
       <c r="C130" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D130" t="s">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="E130" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F130" t="s">
-        <v>188</v>
+        <v>63</v>
       </c>
       <c r="G130" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
@@ -5086,13 +5095,13 @@
         <v>182</v>
       </c>
       <c r="B131" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C131" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D131" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="E131" t="s">
         <v>81</v>
@@ -5101,7 +5110,7 @@
         <v>82</v>
       </c>
       <c r="G131" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H131" t="s">
         <v>18</v>
@@ -5115,22 +5124,22 @@
         <v>182</v>
       </c>
       <c r="B132" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C132" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D132" t="s">
-        <v>165</v>
+        <v>97</v>
       </c>
       <c r="E132" t="s">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="F132" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="G132" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
@@ -5144,22 +5153,22 @@
         <v>182</v>
       </c>
       <c r="B133" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C133" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D133" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="E133" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F133" t="s">
-        <v>103</v>
+        <v>188</v>
       </c>
       <c r="G133" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
@@ -5173,28 +5182,28 @@
         <v>182</v>
       </c>
       <c r="B134" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C134" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D134" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="E134" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F134" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="G134" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="H134" t="s">
         <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
@@ -5202,28 +5211,28 @@
         <v>182</v>
       </c>
       <c r="B135" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C135" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D135" t="s">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="E135" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="F135" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="G135" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H135" t="s">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
@@ -5231,28 +5240,28 @@
         <v>182</v>
       </c>
       <c r="B136" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C136" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D136" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="E136" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="F136" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="G136" t="s">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="H136" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="I136" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15">
@@ -5260,22 +5269,22 @@
         <v>182</v>
       </c>
       <c r="B137" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C137" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D137" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="E137" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="F137" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="G137" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
@@ -5289,28 +5298,28 @@
         <v>182</v>
       </c>
       <c r="B138" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C138" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D138" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="E138" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F138" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="G138" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
       </c>
       <c r="I138" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15">
@@ -5318,28 +5327,28 @@
         <v>182</v>
       </c>
       <c r="B139" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C139" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D139" t="s">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="E139" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="F139" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="G139" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="H139" t="s">
         <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
@@ -5347,25 +5356,25 @@
         <v>182</v>
       </c>
       <c r="B140" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C140" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D140" t="s">
+        <v>85</v>
+      </c>
+      <c r="E140" t="s">
+        <v>22</v>
+      </c>
+      <c r="F140" t="s">
+        <v>23</v>
+      </c>
+      <c r="G140" t="s">
+        <v>93</v>
+      </c>
+      <c r="H140" t="s">
         <v>192</v>
-      </c>
-      <c r="E140" t="s">
-        <v>15</v>
-      </c>
-      <c r="F140" t="s">
-        <v>103</v>
-      </c>
-      <c r="G140" t="s">
-        <v>98</v>
-      </c>
-      <c r="H140" t="s">
-        <v>18</v>
       </c>
       <c r="I140" t="s">
         <v>19</v>
@@ -5376,25 +5385,25 @@
         <v>182</v>
       </c>
       <c r="B141" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C141" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D141" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="E141" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F141" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="G141" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H141" t="s">
-        <v>18</v>
+        <v>193</v>
       </c>
       <c r="I141" t="s">
         <v>19</v>
@@ -5405,7 +5414,7 @@
         <v>182</v>
       </c>
       <c r="B142" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C142" t="s">
         <v>72</v>
@@ -5434,28 +5443,28 @@
         <v>182</v>
       </c>
       <c r="B143" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="C143" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D143" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="E143" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F143" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="G143" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="H143" t="s">
         <v>18</v>
       </c>
       <c r="I143" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15">
@@ -5463,19 +5472,19 @@
         <v>182</v>
       </c>
       <c r="B144" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="C144" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D144" t="s">
-        <v>195</v>
+        <v>91</v>
       </c>
       <c r="E144" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F144" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="G144" t="s">
         <v>98</v>
@@ -5489,83 +5498,83 @@
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B145" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="C145" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D145" t="s">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="E145" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="F145" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="G145" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="H145" t="s">
         <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B146" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="C146" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D146" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E146" t="s">
-        <v>197</v>
+        <v>26</v>
       </c>
       <c r="F146" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="G146" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B147" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="C147" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D147" t="s">
-        <v>85</v>
+        <v>195</v>
       </c>
       <c r="E147" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F147" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="G147" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="H147" t="s">
         <v>18</v>
@@ -5576,25 +5585,25 @@
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B148" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="C148" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D148" t="s">
-        <v>175</v>
+        <v>91</v>
       </c>
       <c r="E148" t="s">
-        <v>197</v>
+        <v>22</v>
       </c>
       <c r="F148" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="G148" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="H148" t="s">
         <v>18</v>
@@ -5605,138 +5614,138 @@
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B149" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="C149" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D149" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="E149" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="F149" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="G149" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="H149" t="s">
         <v>18</v>
       </c>
       <c r="I149" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
+        <v>182</v>
+      </c>
+      <c r="B150" t="s">
+        <v>149</v>
+      </c>
+      <c r="C150" t="s">
+        <v>13</v>
+      </c>
+      <c r="D150" t="s">
         <v>196</v>
       </c>
-      <c r="B150" t="s">
-        <v>46</v>
-      </c>
-      <c r="C150" t="s">
-        <v>72</v>
-      </c>
-      <c r="D150" t="s">
-        <v>198</v>
-      </c>
       <c r="E150" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="F150" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="G150" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="H150" t="s">
         <v>18</v>
       </c>
       <c r="I150" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B151" t="s">
-        <v>46</v>
+        <v>197</v>
       </c>
       <c r="C151" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D151" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="E151" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="F151" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="G151" t="s">
-        <v>200</v>
+        <v>98</v>
       </c>
       <c r="H151" t="s">
         <v>18</v>
       </c>
       <c r="I151" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B152" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C152" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D152" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="E152" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="F152" t="s">
-        <v>201</v>
+        <v>23</v>
       </c>
       <c r="G152" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="H152" t="s">
         <v>18</v>
       </c>
       <c r="I152" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B153" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C153" t="s">
-        <v>164</v>
+        <v>28</v>
       </c>
       <c r="D153" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="E153" t="s">
-        <v>47</v>
+        <v>200</v>
       </c>
       <c r="F153" t="s">
-        <v>203</v>
+        <v>135</v>
       </c>
       <c r="G153" t="s">
         <v>17</v>
@@ -5750,51 +5759,51 @@
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B154" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C154" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D154" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E154" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F154" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="G154" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H154" t="s">
         <v>18</v>
       </c>
       <c r="I154" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B155" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C155" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D155" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="E155" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F155" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G155" t="s">
         <v>17</v>
@@ -5808,83 +5817,83 @@
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B156" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C156" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="D156" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="E156" t="s">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="F156" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="G156" t="s">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="H156" t="s">
         <v>18</v>
       </c>
       <c r="I156" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B157" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C157" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D157" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="E157" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F157" t="s">
         <v>23</v>
       </c>
       <c r="G157" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="H157" t="s">
         <v>18</v>
       </c>
       <c r="I157" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B158" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C158" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="D158" t="s">
-        <v>59</v>
+        <v>201</v>
       </c>
       <c r="E158" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F158" t="s">
-        <v>41</v>
+        <v>202</v>
       </c>
       <c r="G158" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
@@ -5895,138 +5904,138 @@
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B159" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C159" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
       <c r="D159" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E159" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F159" t="s">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="G159" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="H159" t="s">
         <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B160" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C160" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D160" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E160" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F160" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="G160" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B161" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C161" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D161" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E161" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="F161" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="G161" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="H161" t="s">
         <v>18</v>
       </c>
       <c r="I161" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B162" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C162" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="D162" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="E162" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="F162" t="s">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="G162" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="H162" t="s">
         <v>18</v>
       </c>
       <c r="I162" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B163" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C163" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D163" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="E163" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="F163" t="s">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="G163" t="s">
         <v>45</v>
@@ -6040,83 +6049,83 @@
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B164" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C164" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D164" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="E164" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="F164" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="G164" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H164" t="s">
         <v>18</v>
       </c>
       <c r="I164" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B165" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C165" t="s">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="D165" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E165" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F165" t="s">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="G165" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="H165" t="s">
         <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B166" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C166" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D166" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="E166" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="F166" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="G166" t="s">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="H166" t="s">
         <v>18</v>
@@ -6127,25 +6136,25 @@
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B167" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C167" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D167" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="E167" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F167" t="s">
-        <v>206</v>
+        <v>23</v>
       </c>
       <c r="G167" t="s">
-        <v>76</v>
+        <v>203</v>
       </c>
       <c r="H167" t="s">
         <v>18</v>
@@ -6156,54 +6165,54 @@
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B168" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C168" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D168" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E168" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="F168" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G168" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="H168" t="s">
         <v>18</v>
       </c>
       <c r="I168" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B169" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C169" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="D169" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="E169" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="F169" t="s">
-        <v>51</v>
+        <v>206</v>
       </c>
       <c r="G169" t="s">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="H169" t="s">
         <v>18</v>
@@ -6214,112 +6223,112 @@
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B170" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C170" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="D170" t="s">
-        <v>59</v>
+        <v>152</v>
       </c>
       <c r="E170" t="s">
-        <v>184</v>
+        <v>88</v>
       </c>
       <c r="F170" t="s">
         <v>132</v>
       </c>
       <c r="G170" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H170" t="s">
         <v>18</v>
       </c>
       <c r="I170" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B171" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C171" t="s">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="D171" t="s">
-        <v>198</v>
+        <v>71</v>
       </c>
       <c r="E171" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F171" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="G171" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="H171" t="s">
         <v>18</v>
       </c>
       <c r="I171" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B172" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C172" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D172" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="E172" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F172" t="s">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="G172" t="s">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="H172" t="s">
         <v>18</v>
       </c>
       <c r="I172" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B173" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C173" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="D173" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="E173" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F173" t="s">
-        <v>48</v>
+        <v>204</v>
       </c>
       <c r="G173" t="s">
-        <v>208</v>
+        <v>53</v>
       </c>
       <c r="H173" t="s">
         <v>18</v>
@@ -6330,54 +6339,54 @@
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B174" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C174" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D174" t="s">
-        <v>102</v>
+        <v>160</v>
       </c>
       <c r="E174" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F174" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G174" t="s">
-        <v>208</v>
+        <v>45</v>
       </c>
       <c r="H174" t="s">
         <v>18</v>
       </c>
       <c r="I174" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B175" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C175" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D175" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="E175" t="s">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="F175" t="s">
-        <v>51</v>
+        <v>132</v>
       </c>
       <c r="G175" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="H175" t="s">
         <v>18</v>
@@ -6388,54 +6397,54 @@
     </row>
     <row r="176" spans="1:9" ht="15">
       <c r="A176" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B176" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C176" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="D176" t="s">
-        <v>133</v>
+        <v>207</v>
       </c>
       <c r="E176" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F176" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="G176" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="H176" t="s">
         <v>18</v>
       </c>
       <c r="I176" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15">
       <c r="A177" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B177" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C177" t="s">
         <v>64</v>
       </c>
       <c r="D177" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="E177" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="F177" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="G177" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="H177" t="s">
         <v>18</v>
@@ -6446,42 +6455,42 @@
     </row>
     <row r="178" spans="1:9" ht="15">
       <c r="A178" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B178" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C178" t="s">
         <v>13</v>
       </c>
       <c r="D178" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E178" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="F178" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G178" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="H178" t="s">
         <v>18</v>
       </c>
       <c r="I178" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="15">
       <c r="A179" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B179" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C179" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D179" t="s">
         <v>71</v>
@@ -6490,10 +6499,10 @@
         <v>86</v>
       </c>
       <c r="F179" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G179" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="H179" t="s">
         <v>18</v>
@@ -6504,141 +6513,141 @@
     </row>
     <row r="180" spans="1:9" ht="15">
       <c r="A180" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B180" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C180" t="s">
-        <v>171</v>
+        <v>24</v>
       </c>
       <c r="D180" t="s">
-        <v>172</v>
+        <v>50</v>
       </c>
       <c r="E180" t="s">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="F180" t="s">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="G180" t="s">
-        <v>174</v>
+        <v>42</v>
       </c>
       <c r="H180" t="s">
         <v>18</v>
       </c>
       <c r="I180" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="15">
       <c r="A181" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B181" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C181" t="s">
-        <v>212</v>
+        <v>52</v>
       </c>
       <c r="D181" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="E181" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="F181" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G181" t="s">
-        <v>213</v>
+        <v>98</v>
       </c>
       <c r="H181" t="s">
         <v>18</v>
       </c>
       <c r="I181" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="15">
       <c r="A182" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B182" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C182" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D182" t="s">
-        <v>172</v>
+        <v>59</v>
       </c>
       <c r="E182" t="s">
-        <v>15</v>
+        <v>184</v>
       </c>
       <c r="F182" t="s">
-        <v>211</v>
+        <v>132</v>
       </c>
       <c r="G182" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="H182" t="s">
         <v>18</v>
       </c>
       <c r="I182" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="15">
       <c r="A183" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B183" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C183" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="D183" t="s">
-        <v>125</v>
+        <v>201</v>
       </c>
       <c r="E183" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F183" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="G183" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="H183" t="s">
         <v>18</v>
       </c>
       <c r="I183" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="15">
       <c r="A184" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B184" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C184" t="s">
-        <v>212</v>
+        <v>64</v>
       </c>
       <c r="D184" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="E184" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="F184" t="s">
-        <v>41</v>
+        <v>188</v>
       </c>
       <c r="G184" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H184" t="s">
         <v>18</v>
@@ -6649,59 +6658,494 @@
     </row>
     <row r="185" spans="1:9" ht="15">
       <c r="A185" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B185" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="C185" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="D185" t="s">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="E185" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="F185" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G185" t="s">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="H185" t="s">
         <v>18</v>
       </c>
       <c r="I185" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="15">
       <c r="A186" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B186" t="s">
+        <v>90</v>
+      </c>
+      <c r="C186" t="s">
+        <v>89</v>
+      </c>
+      <c r="D186" t="s">
+        <v>102</v>
+      </c>
+      <c r="E186" t="s">
+        <v>47</v>
+      </c>
+      <c r="F186" t="s">
+        <v>48</v>
+      </c>
+      <c r="G186" t="s">
+        <v>211</v>
+      </c>
+      <c r="H186" t="s">
+        <v>18</v>
+      </c>
+      <c r="I186" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="15">
+      <c r="A187" t="s">
+        <v>199</v>
+      </c>
+      <c r="B187" t="s">
+        <v>90</v>
+      </c>
+      <c r="C187" t="s">
+        <v>13</v>
+      </c>
+      <c r="D187" t="s">
+        <v>212</v>
+      </c>
+      <c r="E187" t="s">
+        <v>86</v>
+      </c>
+      <c r="F187" t="s">
+        <v>51</v>
+      </c>
+      <c r="G187" t="s">
+        <v>100</v>
+      </c>
+      <c r="H187" t="s">
+        <v>18</v>
+      </c>
+      <c r="I187" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="15">
+      <c r="A188" t="s">
+        <v>199</v>
+      </c>
+      <c r="B188" t="s">
+        <v>90</v>
+      </c>
+      <c r="C188" t="s">
+        <v>24</v>
+      </c>
+      <c r="D188" t="s">
+        <v>153</v>
+      </c>
+      <c r="E188" t="s">
+        <v>26</v>
+      </c>
+      <c r="F188" t="s">
+        <v>204</v>
+      </c>
+      <c r="G188" t="s">
+        <v>32</v>
+      </c>
+      <c r="H188" t="s">
+        <v>18</v>
+      </c>
+      <c r="I188" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="15">
+      <c r="A189" t="s">
+        <v>199</v>
+      </c>
+      <c r="B189" t="s">
+        <v>90</v>
+      </c>
+      <c r="C189" t="s">
+        <v>52</v>
+      </c>
+      <c r="D189" t="s">
+        <v>133</v>
+      </c>
+      <c r="E189" t="s">
+        <v>86</v>
+      </c>
+      <c r="F189" t="s">
+        <v>51</v>
+      </c>
+      <c r="G189" t="s">
+        <v>98</v>
+      </c>
+      <c r="H189" t="s">
+        <v>18</v>
+      </c>
+      <c r="I189" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="15">
+      <c r="A190" t="s">
+        <v>199</v>
+      </c>
+      <c r="B190" t="s">
+        <v>99</v>
+      </c>
+      <c r="C190" t="s">
+        <v>64</v>
+      </c>
+      <c r="D190" t="s">
+        <v>125</v>
+      </c>
+      <c r="E190" t="s">
+        <v>47</v>
+      </c>
+      <c r="F190" t="s">
+        <v>144</v>
+      </c>
+      <c r="G190" t="s">
+        <v>79</v>
+      </c>
+      <c r="H190" t="s">
+        <v>18</v>
+      </c>
+      <c r="I190" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="15">
+      <c r="A191" t="s">
+        <v>199</v>
+      </c>
+      <c r="B191" t="s">
+        <v>99</v>
+      </c>
+      <c r="C191" t="s">
+        <v>13</v>
+      </c>
+      <c r="D191" t="s">
+        <v>213</v>
+      </c>
+      <c r="E191" t="s">
+        <v>15</v>
+      </c>
+      <c r="F191" t="s">
         <v>214</v>
       </c>
-      <c r="C186" t="s">
+      <c r="G191" t="s">
+        <v>98</v>
+      </c>
+      <c r="H191" t="s">
+        <v>18</v>
+      </c>
+      <c r="I191" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="15">
+      <c r="A192" t="s">
+        <v>199</v>
+      </c>
+      <c r="B192" t="s">
+        <v>99</v>
+      </c>
+      <c r="C192" t="s">
+        <v>24</v>
+      </c>
+      <c r="D192" t="s">
+        <v>187</v>
+      </c>
+      <c r="E192" t="s">
+        <v>26</v>
+      </c>
+      <c r="F192" t="s">
+        <v>27</v>
+      </c>
+      <c r="G192" t="s">
+        <v>203</v>
+      </c>
+      <c r="H192" t="s">
+        <v>18</v>
+      </c>
+      <c r="I192" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="15">
+      <c r="A193" t="s">
+        <v>199</v>
+      </c>
+      <c r="B193" t="s">
+        <v>99</v>
+      </c>
+      <c r="C193" t="s">
+        <v>52</v>
+      </c>
+      <c r="D193" t="s">
+        <v>71</v>
+      </c>
+      <c r="E193" t="s">
+        <v>86</v>
+      </c>
+      <c r="F193" t="s">
+        <v>44</v>
+      </c>
+      <c r="G193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H193" t="s">
+        <v>18</v>
+      </c>
+      <c r="I193" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="15">
+      <c r="A194" t="s">
+        <v>199</v>
+      </c>
+      <c r="B194" t="s">
+        <v>99</v>
+      </c>
+      <c r="C194" t="s">
+        <v>171</v>
+      </c>
+      <c r="D194" t="s">
+        <v>172</v>
+      </c>
+      <c r="E194" t="s">
+        <v>173</v>
+      </c>
+      <c r="F194" t="s">
+        <v>16</v>
+      </c>
+      <c r="G194" t="s">
+        <v>174</v>
+      </c>
+      <c r="H194" t="s">
+        <v>18</v>
+      </c>
+      <c r="I194" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="15">
+      <c r="A195" t="s">
+        <v>199</v>
+      </c>
+      <c r="B195" t="s">
+        <v>99</v>
+      </c>
+      <c r="C195" t="s">
+        <v>215</v>
+      </c>
+      <c r="D195" t="s">
+        <v>153</v>
+      </c>
+      <c r="E195" t="s">
+        <v>37</v>
+      </c>
+      <c r="F195" t="s">
+        <v>41</v>
+      </c>
+      <c r="G195" t="s">
+        <v>216</v>
+      </c>
+      <c r="H195" t="s">
+        <v>18</v>
+      </c>
+      <c r="I195" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="15">
+      <c r="A196" t="s">
+        <v>199</v>
+      </c>
+      <c r="B196" t="s">
+        <v>101</v>
+      </c>
+      <c r="C196" t="s">
         <v>13</v>
       </c>
-      <c r="D186" t="s">
+      <c r="D196" t="s">
+        <v>172</v>
+      </c>
+      <c r="E196" t="s">
+        <v>15</v>
+      </c>
+      <c r="F196" t="s">
+        <v>214</v>
+      </c>
+      <c r="G196" t="s">
+        <v>98</v>
+      </c>
+      <c r="H196" t="s">
+        <v>18</v>
+      </c>
+      <c r="I196" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="15">
+      <c r="A197" t="s">
+        <v>199</v>
+      </c>
+      <c r="B197" t="s">
+        <v>101</v>
+      </c>
+      <c r="C197" t="s">
+        <v>24</v>
+      </c>
+      <c r="D197" t="s">
+        <v>59</v>
+      </c>
+      <c r="E197" t="s">
+        <v>26</v>
+      </c>
+      <c r="F197" t="s">
+        <v>27</v>
+      </c>
+      <c r="G197" t="s">
+        <v>98</v>
+      </c>
+      <c r="H197" t="s">
+        <v>18</v>
+      </c>
+      <c r="I197" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="15">
+      <c r="A198" t="s">
+        <v>199</v>
+      </c>
+      <c r="B198" t="s">
+        <v>101</v>
+      </c>
+      <c r="C198" t="s">
+        <v>52</v>
+      </c>
+      <c r="D198" t="s">
+        <v>125</v>
+      </c>
+      <c r="E198" t="s">
+        <v>86</v>
+      </c>
+      <c r="F198" t="s">
+        <v>44</v>
+      </c>
+      <c r="G198" t="s">
+        <v>45</v>
+      </c>
+      <c r="H198" t="s">
+        <v>18</v>
+      </c>
+      <c r="I198" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="15">
+      <c r="A199" t="s">
+        <v>199</v>
+      </c>
+      <c r="B199" t="s">
+        <v>101</v>
+      </c>
+      <c r="C199" t="s">
         <v>215</v>
       </c>
-      <c r="E186" t="s">
+      <c r="D199" t="s">
+        <v>153</v>
+      </c>
+      <c r="E199" t="s">
+        <v>37</v>
+      </c>
+      <c r="F199" t="s">
+        <v>41</v>
+      </c>
+      <c r="G199" t="s">
+        <v>216</v>
+      </c>
+      <c r="H199" t="s">
+        <v>18</v>
+      </c>
+      <c r="I199" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="15">
+      <c r="A200" t="s">
+        <v>199</v>
+      </c>
+      <c r="B200" t="s">
+        <v>149</v>
+      </c>
+      <c r="C200" t="s">
+        <v>13</v>
+      </c>
+      <c r="D200" t="s">
+        <v>205</v>
+      </c>
+      <c r="E200" t="s">
+        <v>81</v>
+      </c>
+      <c r="F200" t="s">
+        <v>82</v>
+      </c>
+      <c r="G200" t="s">
+        <v>96</v>
+      </c>
+      <c r="H200" t="s">
+        <v>18</v>
+      </c>
+      <c r="I200" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="15">
+      <c r="A201" t="s">
+        <v>199</v>
+      </c>
+      <c r="B201" t="s">
+        <v>217</v>
+      </c>
+      <c r="C201" t="s">
+        <v>13</v>
+      </c>
+      <c r="D201" t="s">
+        <v>218</v>
+      </c>
+      <c r="E201" t="s">
         <v>15</v>
       </c>
-      <c r="F186" t="s">
+      <c r="F201" t="s">
         <v>103</v>
       </c>
-      <c r="G186" t="s">
+      <c r="G201" t="s">
         <v>98</v>
       </c>
-      <c r="H186" t="s">
-        <v>18</v>
-      </c>
-      <c r="I186" t="s">
+      <c r="H201" t="s">
+        <v>18</v>
+      </c>
+      <c r="I201" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6713,7 +7157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{818a551d-e776-4dac-9ba6-6fed0e695c81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e1b4d51a-6675-43b2-a2a8-379d41fa8f24}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6733,16 +7177,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6762,16 +7206,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -6791,16 +7235,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C3" t="s">
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -6820,16 +7264,16 @@
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -6849,16 +7293,16 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6878,16 +7322,16 @@
         <v>151</v>
       </c>
       <c r="B6" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E6" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -6907,16 +7351,16 @@
         <v>151</v>
       </c>
       <c r="B7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C7" t="s">
         <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -6936,16 +7380,16 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C8" t="s">
         <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E8" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -6965,13 +7409,13 @@
         <v>182</v>
       </c>
       <c r="B9" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C9" t="s">
         <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E9" t="s">
         <v>47</v>
@@ -6994,16 +7438,16 @@
         <v>182</v>
       </c>
       <c r="B10" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C10" t="s">
         <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E10" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -7023,16 +7467,16 @@
         <v>182</v>
       </c>
       <c r="B11" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C11" t="s">
         <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E11" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -7049,19 +7493,19 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C12" t="s">
         <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -7078,19 +7522,19 @@
     </row>
     <row r="13" spans="1:9" ht="15">
       <c r="A13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B13" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -7113,8 +7557,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ad145dd3-0022-4241-8ffb-512ac439cf68}">
-  <dimension ref="A1:F41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{9dfd6a7f-5b25-4931-87e3-fab61c111aac}">
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -7130,13 +7574,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -7150,13 +7594,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -7170,13 +7614,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C3" t="s">
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E3" t="s">
         <v>100</v>
@@ -7190,13 +7634,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C4" t="s">
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E4" t="s">
         <v>42</v>
@@ -7210,16 +7654,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -7230,13 +7674,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E6" t="s">
         <v>136</v>
@@ -7250,13 +7694,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C7" t="s">
         <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E7" t="s">
         <v>58</v>
@@ -7270,13 +7714,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E8" t="s">
         <v>174</v>
@@ -7290,16 +7734,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E9" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -7310,13 +7754,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C10" t="s">
         <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E10" t="s">
         <v>117</v>
@@ -7330,13 +7774,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
@@ -7350,13 +7794,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E12" t="s">
         <v>136</v>
@@ -7370,16 +7814,16 @@
         <v>104</v>
       </c>
       <c r="B13" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E13" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -7390,13 +7834,13 @@
         <v>104</v>
       </c>
       <c r="B14" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C14" t="s">
         <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E14" t="s">
         <v>100</v>
@@ -7410,13 +7854,13 @@
         <v>104</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C15" t="s">
         <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E15" t="s">
         <v>119</v>
@@ -7430,13 +7874,13 @@
         <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C16" t="s">
         <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E16" t="s">
         <v>117</v>
@@ -7450,13 +7894,13 @@
         <v>104</v>
       </c>
       <c r="B17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C17" t="s">
         <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E17" t="s">
         <v>136</v>
@@ -7470,16 +7914,16 @@
         <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C18" t="s">
         <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E18" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -7490,16 +7934,16 @@
         <v>104</v>
       </c>
       <c r="B19" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C19" t="s">
         <v>163</v>
       </c>
       <c r="D19" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E19" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -7510,16 +7954,16 @@
         <v>151</v>
       </c>
       <c r="B20" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C20" t="s">
         <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E20" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -7530,13 +7974,13 @@
         <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C21" t="s">
         <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E21" t="s">
         <v>87</v>
@@ -7550,16 +7994,16 @@
         <v>151</v>
       </c>
       <c r="B22" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C22" t="s">
         <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E22" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -7570,13 +8014,13 @@
         <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C23" t="s">
         <v>167</v>
       </c>
       <c r="D23" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E23" t="s">
         <v>115</v>
@@ -7590,13 +8034,13 @@
         <v>151</v>
       </c>
       <c r="B24" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C24" t="s">
         <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
@@ -7610,13 +8054,13 @@
         <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C25" t="s">
         <v>167</v>
       </c>
       <c r="D25" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E25" t="s">
         <v>42</v>
@@ -7630,16 +8074,16 @@
         <v>151</v>
       </c>
       <c r="B26" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C26" t="s">
         <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E26" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -7650,16 +8094,16 @@
         <v>151</v>
       </c>
       <c r="B27" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C27" t="s">
         <v>141</v>
       </c>
       <c r="D27" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E27" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
@@ -7670,13 +8114,13 @@
         <v>151</v>
       </c>
       <c r="B28" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C28" t="s">
         <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
@@ -7690,16 +8134,16 @@
         <v>182</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C29" t="s">
         <v>64</v>
       </c>
       <c r="D29" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E29" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -7710,13 +8154,13 @@
         <v>182</v>
       </c>
       <c r="B30" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C30" t="s">
         <v>52</v>
       </c>
       <c r="D30" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E30" t="s">
         <v>76</v>
@@ -7730,13 +8174,13 @@
         <v>182</v>
       </c>
       <c r="B31" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
@@ -7750,7 +8194,7 @@
         <v>182</v>
       </c>
       <c r="B32" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C32" t="s">
         <v>20</v>
@@ -7759,7 +8203,7 @@
         <v>248</v>
       </c>
       <c r="E32" t="s">
-        <v>265</v>
+        <v>45</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
@@ -7770,16 +8214,16 @@
         <v>182</v>
       </c>
       <c r="B33" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E33" t="s">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -7790,16 +8234,16 @@
         <v>182</v>
       </c>
       <c r="B34" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>268</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
@@ -7807,19 +8251,19 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B35" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E35" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
@@ -7827,19 +8271,19 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B36" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E36" t="s">
-        <v>24</v>
+        <v>203</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
@@ -7847,19 +8291,19 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B37" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E37" t="s">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -7867,19 +8311,19 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B38" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C38" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
       <c r="D38" t="s">
         <v>248</v>
       </c>
       <c r="E38" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
@@ -7887,19 +8331,19 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
@@ -7907,19 +8351,19 @@
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B40" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="D40" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="E40" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="F40" t="s">
         <v>18</v>
@@ -7927,21 +8371,161 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C41" t="s">
         <v>52</v>
       </c>
       <c r="D41" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E41" t="s">
+        <v>210</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15">
+      <c r="A42" t="s">
+        <v>199</v>
+      </c>
+      <c r="B42" t="s">
+        <v>261</v>
+      </c>
+      <c r="C42" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" t="s">
+        <v>251</v>
+      </c>
+      <c r="E42" t="s">
+        <v>203</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15">
+      <c r="A43" t="s">
+        <v>199</v>
+      </c>
+      <c r="B43" t="s">
+        <v>252</v>
+      </c>
+      <c r="C43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" t="s">
+        <v>248</v>
+      </c>
+      <c r="E43" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15">
+      <c r="A44" t="s">
+        <v>199</v>
+      </c>
+      <c r="B44" t="s">
+        <v>254</v>
+      </c>
+      <c r="C44" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" t="s">
+        <v>262</v>
+      </c>
+      <c r="E44" t="s">
+        <v>170</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15">
+      <c r="A45" t="s">
+        <v>199</v>
+      </c>
+      <c r="B45" t="s">
+        <v>255</v>
+      </c>
+      <c r="C45" t="s">
+        <v>164</v>
+      </c>
+      <c r="D45" t="s">
+        <v>247</v>
+      </c>
+      <c r="E45" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15">
+      <c r="A46" t="s">
+        <v>199</v>
+      </c>
+      <c r="B46" t="s">
+        <v>257</v>
+      </c>
+      <c r="C46" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" t="s">
+        <v>248</v>
+      </c>
+      <c r="E46" t="s">
+        <v>203</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15">
+      <c r="A47" t="s">
+        <v>199</v>
+      </c>
+      <c r="B47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" t="s">
+        <v>248</v>
+      </c>
+      <c r="E47" t="s">
+        <v>263</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15">
+      <c r="A48" t="s">
+        <v>199</v>
+      </c>
+      <c r="B48" t="s">
+        <v>266</v>
+      </c>
+      <c r="C48" t="s">
+        <v>52</v>
+      </c>
+      <c r="D48" t="s">
+        <v>247</v>
+      </c>
+      <c r="E48" t="s">
         <v>76</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F48" t="s">
         <v>18</v>
       </c>
     </row>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="285">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -594,6 +594,12 @@
     <t>2TFA|JA1</t>
   </si>
   <si>
+    <t>1CB</t>
+  </si>
+  <si>
+    <t>Wójcik Kamil</t>
+  </si>
+  <si>
     <t>42</t>
   </si>
   <si>
@@ -606,12 +612,27 @@
     <t>p. Dalach, wychowanie fizyczne za lekcję 10</t>
   </si>
   <si>
-    <t>1CB</t>
+    <t>Kruk Marcin</t>
   </si>
   <si>
     <t>1WB|JN2</t>
   </si>
   <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>Zajęcia praktyczne - projektowanie i wykonywanie fryzur</t>
+  </si>
+  <si>
+    <t>Nowaczyk Agnieszka</t>
+  </si>
+  <si>
+    <t>Język angielski zawodowy</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
     <t>1TFA|JA2</t>
   </si>
   <si>
@@ -621,6 +642,12 @@
     <t>1CB|JA2</t>
   </si>
   <si>
+    <t>12, 17:25-18:10</t>
+  </si>
+  <si>
+    <t>13, 18:15-19:00</t>
+  </si>
+  <si>
     <t>06.03.2026</t>
   </si>
   <si>
@@ -633,51 +660,51 @@
     <t>aq1</t>
   </si>
   <si>
-    <t>Kruk Marcin</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
     <t>1S|JA2</t>
   </si>
   <si>
-    <t>04</t>
-  </si>
-  <si>
     <t>1FA|JA2</t>
   </si>
   <si>
+    <t>Filipiak Wiesław</t>
+  </si>
+  <si>
     <t>1CB|JA1</t>
   </si>
   <si>
     <t>sg1</t>
   </si>
   <si>
+    <t>Staliś Donata</t>
+  </si>
+  <si>
+    <t>1FB|JA1</t>
+  </si>
+  <si>
     <t>Jastrzębska-Majtyka Agnieszka</t>
   </si>
   <si>
-    <t>Staliś Donata</t>
-  </si>
-  <si>
-    <t>1FB|JA1</t>
-  </si>
-  <si>
     <t>1WA|JN1</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>3TFA|JA2</t>
+  </si>
+  <si>
     <t>Wakat2 matematyka</t>
   </si>
   <si>
     <t>Młynarczyk Paweł</t>
   </si>
   <si>
-    <t>12, 17:25-18:10</t>
-  </si>
-  <si>
     <t>1S|JA1</t>
   </si>
   <si>
@@ -735,21 +762,42 @@
     <t>język angielski 2 godz lekcyjne</t>
   </si>
   <si>
+    <t>08:00-08:45</t>
+  </si>
+  <si>
+    <t>wiedza o społeczeństwie</t>
+  </si>
+  <si>
     <t>08:50-09:35</t>
   </si>
   <si>
     <t>10:35-12:10</t>
   </si>
   <si>
+    <t>11:30-17:30</t>
+  </si>
+  <si>
+    <t>dziennik - plan dyżurów - biblioteka</t>
+  </si>
+  <si>
+    <t>(6 godz.)</t>
+  </si>
+  <si>
     <t>18:00-19:30</t>
   </si>
   <si>
     <t>język angielski</t>
   </si>
   <si>
+    <t>07:30-13:30</t>
+  </si>
+  <si>
     <t>09:40-10:25</t>
   </si>
   <si>
+    <t>09:50-10:35</t>
+  </si>
+  <si>
     <t>12:25-15:40</t>
   </si>
   <si>
@@ -801,9 +849,6 @@
     <t>14:50-14:55</t>
   </si>
   <si>
-    <t>Wójcik Kamil</t>
-  </si>
-  <si>
     <t>08:45-08:50</t>
   </si>
   <si>
@@ -811,9 +856,6 @@
   </si>
   <si>
     <t>piętro_3</t>
-  </si>
-  <si>
-    <t>Nowaczyk Agnieszka</t>
   </si>
   <si>
     <t>Doliński Mirosław</t>
@@ -1284,7 +1326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{82538555-36f2-4d89-b876-5be66e274ee3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{87add713-074c-447f-b61c-0bb4fb6c74c0}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1305,8 +1347,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{142affac-beb8-4b61-ac0a-737e3ddc5add}">
-  <dimension ref="A1:I201"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{04c12098-1ed0-470a-b32b-6f6cd2e9909b}">
+  <dimension ref="A1:I217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -4953,16 +4995,16 @@
         <v>61</v>
       </c>
       <c r="C126" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="D126" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="E126" t="s">
         <v>81</v>
       </c>
       <c r="F126" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="G126" t="s">
         <v>96</v>
@@ -4982,25 +5024,25 @@
         <v>61</v>
       </c>
       <c r="C127" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D127" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="E127" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="F127" t="s">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="G127" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
@@ -5011,19 +5053,19 @@
         <v>61</v>
       </c>
       <c r="C128" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D128" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E128" t="s">
-        <v>184</v>
+        <v>43</v>
       </c>
       <c r="F128" t="s">
-        <v>63</v>
+        <v>188</v>
       </c>
       <c r="G128" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
@@ -5037,28 +5079,28 @@
         <v>182</v>
       </c>
       <c r="B129" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C129" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D129" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="E129" t="s">
-        <v>47</v>
+        <v>184</v>
       </c>
       <c r="F129" t="s">
         <v>63</v>
       </c>
       <c r="G129" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
@@ -5069,25 +5111,25 @@
         <v>69</v>
       </c>
       <c r="C130" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D130" t="s">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="E130" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F130" t="s">
         <v>63</v>
       </c>
       <c r="G130" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
@@ -5098,25 +5140,25 @@
         <v>69</v>
       </c>
       <c r="C131" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D131" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="E131" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="F131" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="G131" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="H131" t="s">
         <v>18</v>
       </c>
       <c r="I131" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
@@ -5127,25 +5169,25 @@
         <v>69</v>
       </c>
       <c r="C132" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D132" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="E132" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="F132" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="G132" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
@@ -5156,19 +5198,19 @@
         <v>69</v>
       </c>
       <c r="C133" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="D133" t="s">
-        <v>133</v>
+        <v>190</v>
       </c>
       <c r="E133" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="F133" t="s">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="G133" t="s">
-        <v>45</v>
+        <v>191</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
@@ -5185,19 +5227,19 @@
         <v>69</v>
       </c>
       <c r="C134" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D134" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="E134" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F134" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="G134" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="H134" t="s">
         <v>18</v>
@@ -5211,28 +5253,28 @@
         <v>182</v>
       </c>
       <c r="B135" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C135" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D135" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="E135" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="F135" t="s">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="G135" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="H135" t="s">
         <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
@@ -5240,22 +5282,22 @@
         <v>182</v>
       </c>
       <c r="B136" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C136" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D136" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E136" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="F136" t="s">
-        <v>135</v>
+        <v>192</v>
       </c>
       <c r="G136" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="H136" t="s">
         <v>18</v>
@@ -5272,19 +5314,19 @@
         <v>77</v>
       </c>
       <c r="C137" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D137" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="E137" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="F137" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="G137" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
@@ -5301,19 +5343,19 @@
         <v>77</v>
       </c>
       <c r="C138" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D138" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E138" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="F138" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="G138" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
@@ -5327,28 +5369,28 @@
         <v>182</v>
       </c>
       <c r="B139" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C139" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D139" t="s">
-        <v>91</v>
+        <v>193</v>
       </c>
       <c r="E139" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F139" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G139" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="H139" t="s">
         <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
@@ -5356,28 +5398,28 @@
         <v>182</v>
       </c>
       <c r="B140" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C140" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D140" t="s">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="E140" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F140" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="G140" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="H140" t="s">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="I140" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
@@ -5388,22 +5430,22 @@
         <v>90</v>
       </c>
       <c r="C141" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D141" t="s">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="E141" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="F141" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="G141" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H141" t="s">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="I141" t="s">
         <v>19</v>
@@ -5417,25 +5459,25 @@
         <v>90</v>
       </c>
       <c r="C142" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D142" t="s">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="E142" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="F142" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="G142" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="H142" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="I142" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
@@ -5446,25 +5488,25 @@
         <v>90</v>
       </c>
       <c r="C143" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D143" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E143" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="F143" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="G143" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="H143" t="s">
-        <v>18</v>
+        <v>195</v>
       </c>
       <c r="I143" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15">
@@ -5472,28 +5514,28 @@
         <v>182</v>
       </c>
       <c r="B144" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C144" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D144" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="E144" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="F144" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="G144" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="H144" t="s">
         <v>18</v>
       </c>
       <c r="I144" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15">
@@ -5501,22 +5543,22 @@
         <v>182</v>
       </c>
       <c r="B145" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C145" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D145" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="E145" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="F145" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="G145" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="H145" t="s">
         <v>18</v>
@@ -5533,25 +5575,25 @@
         <v>99</v>
       </c>
       <c r="C146" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D146" t="s">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="E146" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F146" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G146" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
@@ -5559,19 +5601,19 @@
         <v>182</v>
       </c>
       <c r="B147" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C147" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="D147" t="s">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="E147" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="F147" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="G147" t="s">
         <v>98</v>
@@ -5588,28 +5630,28 @@
         <v>182</v>
       </c>
       <c r="B148" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C148" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D148" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="E148" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="F148" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="G148" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="H148" t="s">
         <v>18</v>
       </c>
       <c r="I148" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15">
@@ -5617,22 +5659,22 @@
         <v>182</v>
       </c>
       <c r="B149" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C149" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D149" t="s">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="E149" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="F149" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="G149" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="H149" t="s">
         <v>18</v>
@@ -5646,13 +5688,13 @@
         <v>182</v>
       </c>
       <c r="B150" t="s">
-        <v>149</v>
+        <v>101</v>
       </c>
       <c r="C150" t="s">
         <v>13</v>
       </c>
       <c r="D150" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E150" t="s">
         <v>15</v>
@@ -5675,42 +5717,42 @@
         <v>182</v>
       </c>
       <c r="B151" t="s">
-        <v>197</v>
+        <v>101</v>
       </c>
       <c r="C151" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="D151" t="s">
         <v>198</v>
       </c>
       <c r="E151" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
       <c r="F151" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="G151" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="H151" t="s">
         <v>18</v>
       </c>
       <c r="I151" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B152" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="C152" t="s">
         <v>20</v>
       </c>
       <c r="D152" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -5719,7 +5761,7 @@
         <v>23</v>
       </c>
       <c r="G152" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="H152" t="s">
         <v>18</v>
@@ -5730,25 +5772,25 @@
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B153" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="C153" t="s">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="D153" t="s">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="E153" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F153" t="s">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="G153" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="H153" t="s">
         <v>18</v>
@@ -5759,54 +5801,54 @@
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B154" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="C154" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D154" t="s">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="E154" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="F154" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="G154" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="H154" t="s">
         <v>18</v>
       </c>
       <c r="I154" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B155" t="s">
-        <v>34</v>
+        <v>149</v>
       </c>
       <c r="C155" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D155" t="s">
-        <v>25</v>
+        <v>203</v>
       </c>
       <c r="E155" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F155" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="G155" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="H155" t="s">
         <v>18</v>
@@ -5817,54 +5859,54 @@
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
+        <v>182</v>
+      </c>
+      <c r="B156" t="s">
+        <v>149</v>
+      </c>
+      <c r="C156" t="s">
+        <v>196</v>
+      </c>
+      <c r="D156" t="s">
+        <v>198</v>
+      </c>
+      <c r="E156" t="s">
         <v>199</v>
-      </c>
-      <c r="B156" t="s">
-        <v>34</v>
-      </c>
-      <c r="C156" t="s">
-        <v>28</v>
-      </c>
-      <c r="D156" t="s">
-        <v>175</v>
-      </c>
-      <c r="E156" t="s">
-        <v>200</v>
       </c>
       <c r="F156" t="s">
         <v>135</v>
       </c>
       <c r="G156" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H156" t="s">
         <v>18</v>
       </c>
       <c r="I156" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B157" t="s">
-        <v>46</v>
+        <v>204</v>
       </c>
       <c r="C157" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D157" t="s">
-        <v>71</v>
+        <v>205</v>
       </c>
       <c r="E157" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F157" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="G157" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="H157" t="s">
         <v>18</v>
@@ -5875,25 +5917,25 @@
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
+        <v>182</v>
+      </c>
+      <c r="B158" t="s">
+        <v>204</v>
+      </c>
+      <c r="C158" t="s">
+        <v>196</v>
+      </c>
+      <c r="D158" t="s">
+        <v>198</v>
+      </c>
+      <c r="E158" t="s">
         <v>199</v>
       </c>
-      <c r="B158" t="s">
-        <v>46</v>
-      </c>
-      <c r="C158" t="s">
-        <v>72</v>
-      </c>
-      <c r="D158" t="s">
-        <v>201</v>
-      </c>
-      <c r="E158" t="s">
-        <v>74</v>
-      </c>
       <c r="F158" t="s">
-        <v>202</v>
+        <v>135</v>
       </c>
       <c r="G158" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
@@ -5904,54 +5946,54 @@
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
+        <v>182</v>
+      </c>
+      <c r="B159" t="s">
+        <v>206</v>
+      </c>
+      <c r="C159" t="s">
+        <v>196</v>
+      </c>
+      <c r="D159" t="s">
+        <v>198</v>
+      </c>
+      <c r="E159" t="s">
         <v>199</v>
       </c>
-      <c r="B159" t="s">
-        <v>46</v>
-      </c>
-      <c r="C159" t="s">
-        <v>24</v>
-      </c>
-      <c r="D159" t="s">
-        <v>194</v>
-      </c>
-      <c r="E159" t="s">
-        <v>81</v>
-      </c>
       <c r="F159" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="G159" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="H159" t="s">
         <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
+        <v>182</v>
+      </c>
+      <c r="B160" t="s">
+        <v>207</v>
+      </c>
+      <c r="C160" t="s">
+        <v>196</v>
+      </c>
+      <c r="D160" t="s">
+        <v>198</v>
+      </c>
+      <c r="E160" t="s">
         <v>199</v>
       </c>
-      <c r="B160" t="s">
-        <v>46</v>
-      </c>
-      <c r="C160" t="s">
-        <v>52</v>
-      </c>
-      <c r="D160" t="s">
-        <v>165</v>
-      </c>
-      <c r="E160" t="s">
-        <v>86</v>
-      </c>
       <c r="F160" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="G160" t="s">
-        <v>203</v>
+        <v>45</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
@@ -5962,51 +6004,51 @@
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B161" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C161" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D161" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="E161" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="F161" t="s">
-        <v>204</v>
+        <v>23</v>
       </c>
       <c r="G161" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="H161" t="s">
         <v>18</v>
       </c>
       <c r="I161" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B162" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C162" t="s">
-        <v>164</v>
+        <v>28</v>
       </c>
       <c r="D162" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="E162" t="s">
-        <v>47</v>
+        <v>209</v>
       </c>
       <c r="F162" t="s">
-        <v>206</v>
+        <v>135</v>
       </c>
       <c r="G162" t="s">
         <v>17</v>
@@ -6020,51 +6062,51 @@
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B163" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C163" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D163" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E163" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F163" t="s">
-        <v>188</v>
+        <v>23</v>
       </c>
       <c r="G163" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H163" t="s">
         <v>18</v>
       </c>
       <c r="I163" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B164" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C164" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D164" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="E164" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F164" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G164" t="s">
         <v>17</v>
@@ -6078,83 +6120,83 @@
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B165" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C165" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="D165" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="E165" t="s">
-        <v>74</v>
+        <v>209</v>
       </c>
       <c r="F165" t="s">
-        <v>202</v>
+        <v>135</v>
       </c>
       <c r="G165" t="s">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="H165" t="s">
         <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B166" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C166" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D166" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="E166" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F166" t="s">
-        <v>204</v>
+        <v>23</v>
       </c>
       <c r="G166" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H166" t="s">
         <v>18</v>
       </c>
       <c r="I166" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B167" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C167" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D167" t="s">
-        <v>165</v>
+        <v>210</v>
       </c>
       <c r="E167" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F167" t="s">
-        <v>23</v>
+        <v>211</v>
       </c>
       <c r="G167" t="s">
-        <v>203</v>
+        <v>115</v>
       </c>
       <c r="H167" t="s">
         <v>18</v>
@@ -6165,199 +6207,199 @@
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B168" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C168" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D168" t="s">
-        <v>59</v>
+        <v>190</v>
       </c>
       <c r="E168" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F168" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G168" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="H168" t="s">
         <v>18</v>
       </c>
       <c r="I168" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B169" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C169" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="D169" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="E169" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F169" t="s">
-        <v>206</v>
+        <v>27</v>
       </c>
       <c r="G169" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H169" t="s">
         <v>18</v>
       </c>
       <c r="I169" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B170" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C170" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="D170" t="s">
-        <v>152</v>
+        <v>59</v>
       </c>
       <c r="E170" t="s">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="F170" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="G170" t="s">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="H170" t="s">
         <v>18</v>
       </c>
       <c r="I170" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B171" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C171" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="D171" t="s">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="E171" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="F171" t="s">
-        <v>41</v>
+        <v>202</v>
       </c>
       <c r="G171" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H171" t="s">
         <v>18</v>
       </c>
       <c r="I171" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B172" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C172" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D172" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="E172" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F172" t="s">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="G172" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="H172" t="s">
         <v>18</v>
       </c>
       <c r="I172" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B173" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C173" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D173" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E173" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F173" t="s">
-        <v>204</v>
+        <v>23</v>
       </c>
       <c r="G173" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="H173" t="s">
         <v>18</v>
       </c>
       <c r="I173" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B174" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C174" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D174" t="s">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="E174" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="F174" t="s">
-        <v>23</v>
+        <v>211</v>
       </c>
       <c r="G174" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="H174" t="s">
         <v>18</v>
@@ -6368,19 +6410,19 @@
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B175" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C175" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D175" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="E175" t="s">
-        <v>184</v>
+        <v>26</v>
       </c>
       <c r="F175" t="s">
         <v>132</v>
@@ -6397,25 +6439,25 @@
     </row>
     <row r="176" spans="1:9" ht="15">
       <c r="A176" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B176" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C176" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="D176" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="E176" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F176" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G176" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="H176" t="s">
         <v>18</v>
@@ -6426,25 +6468,25 @@
     </row>
     <row r="177" spans="1:9" ht="15">
       <c r="A177" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B177" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C177" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D177" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="E177" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F177" t="s">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="G177" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="H177" t="s">
         <v>18</v>
@@ -6455,112 +6497,112 @@
     </row>
     <row r="178" spans="1:9" ht="15">
       <c r="A178" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B178" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C178" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D178" t="s">
-        <v>208</v>
+        <v>59</v>
       </c>
       <c r="E178" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F178" t="s">
-        <v>209</v>
+        <v>41</v>
       </c>
       <c r="G178" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="H178" t="s">
         <v>18</v>
       </c>
       <c r="I178" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="15">
       <c r="A179" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B179" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C179" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="D179" t="s">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="E179" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="F179" t="s">
-        <v>23</v>
+        <v>202</v>
       </c>
       <c r="G179" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H179" t="s">
         <v>18</v>
       </c>
       <c r="I179" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="15">
       <c r="A180" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B180" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C180" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="D180" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="E180" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="F180" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="G180" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H180" t="s">
         <v>18</v>
       </c>
       <c r="I180" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="15">
       <c r="A181" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B181" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C181" t="s">
-        <v>52</v>
+        <v>196</v>
       </c>
       <c r="D181" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="E181" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="F181" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="G181" t="s">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="H181" t="s">
         <v>18</v>
@@ -6571,25 +6613,25 @@
     </row>
     <row r="182" spans="1:9" ht="15">
       <c r="A182" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B182" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C182" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D182" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E182" t="s">
-        <v>184</v>
+        <v>70</v>
       </c>
       <c r="F182" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="G182" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H182" t="s">
         <v>18</v>
@@ -6600,54 +6642,54 @@
     </row>
     <row r="183" spans="1:9" ht="15">
       <c r="A183" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B183" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C183" t="s">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="D183" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="E183" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="F183" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="G183" t="s">
-        <v>96</v>
+        <v>215</v>
       </c>
       <c r="H183" t="s">
         <v>18</v>
       </c>
       <c r="I183" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="15">
       <c r="A184" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B184" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C184" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D184" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="E184" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="F184" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="G184" t="s">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="H184" t="s">
         <v>18</v>
@@ -6658,25 +6700,25 @@
     </row>
     <row r="185" spans="1:9" ht="15">
       <c r="A185" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B185" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C185" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D185" t="s">
-        <v>105</v>
+        <v>160</v>
       </c>
       <c r="E185" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F185" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G185" t="s">
-        <v>211</v>
+        <v>45</v>
       </c>
       <c r="H185" t="s">
         <v>18</v>
@@ -6687,51 +6729,51 @@
     </row>
     <row r="186" spans="1:9" ht="15">
       <c r="A186" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B186" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C186" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="D186" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="E186" t="s">
-        <v>47</v>
+        <v>184</v>
       </c>
       <c r="F186" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="G186" t="s">
-        <v>211</v>
+        <v>32</v>
       </c>
       <c r="H186" t="s">
         <v>18</v>
       </c>
       <c r="I186" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="15">
       <c r="A187" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B187" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C187" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="D187" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E187" t="s">
         <v>86</v>
       </c>
       <c r="F187" t="s">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="G187" t="s">
         <v>100</v>
@@ -6745,25 +6787,25 @@
     </row>
     <row r="188" spans="1:9" ht="15">
       <c r="A188" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B188" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C188" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D188" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="E188" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="F188" t="s">
-        <v>204</v>
+        <v>123</v>
       </c>
       <c r="G188" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="H188" t="s">
         <v>18</v>
@@ -6774,51 +6816,51 @@
     </row>
     <row r="189" spans="1:9" ht="15">
       <c r="A189" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B189" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C189" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D189" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="E189" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F189" t="s">
-        <v>51</v>
+        <v>217</v>
       </c>
       <c r="G189" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="H189" t="s">
         <v>18</v>
       </c>
       <c r="I189" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="15">
       <c r="A190" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B190" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C190" t="s">
-        <v>64</v>
+        <v>196</v>
       </c>
       <c r="D190" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="E190" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F190" t="s">
-        <v>144</v>
+        <v>16</v>
       </c>
       <c r="G190" t="s">
         <v>79</v>
@@ -6832,54 +6874,54 @@
     </row>
     <row r="191" spans="1:9" ht="15">
       <c r="A191" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B191" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C191" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D191" t="s">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="E191" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="F191" t="s">
-        <v>214</v>
+        <v>23</v>
       </c>
       <c r="G191" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H191" t="s">
         <v>18</v>
       </c>
       <c r="I191" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="15">
       <c r="A192" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B192" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C192" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="D192" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="E192" t="s">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="F192" t="s">
-        <v>27</v>
+        <v>188</v>
       </c>
       <c r="G192" t="s">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="H192" t="s">
         <v>18</v>
@@ -6890,83 +6932,83 @@
     </row>
     <row r="193" spans="1:9" ht="15">
       <c r="A193" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B193" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C193" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D193" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="E193" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="F193" t="s">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="G193" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H193" t="s">
         <v>18</v>
       </c>
       <c r="I193" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="15">
       <c r="A194" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B194" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C194" t="s">
-        <v>171</v>
+        <v>52</v>
       </c>
       <c r="D194" t="s">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="E194" t="s">
-        <v>173</v>
+        <v>86</v>
       </c>
       <c r="F194" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="G194" t="s">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="H194" t="s">
         <v>18</v>
       </c>
       <c r="I194" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="15">
       <c r="A195" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B195" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C195" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D195" t="s">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="E195" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F195" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G195" t="s">
-        <v>216</v>
+        <v>49</v>
       </c>
       <c r="H195" t="s">
         <v>18</v>
@@ -6977,112 +7019,112 @@
     </row>
     <row r="196" spans="1:9" ht="15">
       <c r="A196" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B196" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C196" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D196" t="s">
-        <v>172</v>
+        <v>59</v>
       </c>
       <c r="E196" t="s">
-        <v>15</v>
+        <v>184</v>
       </c>
       <c r="F196" t="s">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="G196" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="H196" t="s">
         <v>18</v>
       </c>
       <c r="I196" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="15">
       <c r="A197" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B197" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C197" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="D197" t="s">
-        <v>59</v>
+        <v>210</v>
       </c>
       <c r="E197" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="F197" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="G197" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H197" t="s">
         <v>18</v>
       </c>
       <c r="I197" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="15">
       <c r="A198" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B198" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C198" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D198" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="E198" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F198" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G198" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="H198" t="s">
         <v>18</v>
       </c>
       <c r="I198" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="15">
       <c r="A199" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B199" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C199" t="s">
-        <v>215</v>
+        <v>89</v>
       </c>
       <c r="D199" t="s">
-        <v>153</v>
+        <v>193</v>
       </c>
       <c r="E199" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F199" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="G199" t="s">
-        <v>216</v>
+        <v>42</v>
       </c>
       <c r="H199" t="s">
         <v>18</v>
@@ -7093,59 +7135,523 @@
     </row>
     <row r="200" spans="1:9" ht="15">
       <c r="A200" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B200" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="C200" t="s">
         <v>13</v>
       </c>
       <c r="D200" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="E200" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F200" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G200" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H200" t="s">
         <v>18</v>
       </c>
       <c r="I200" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="15">
       <c r="A201" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B201" t="s">
-        <v>217</v>
+        <v>90</v>
       </c>
       <c r="C201" t="s">
+        <v>196</v>
+      </c>
+      <c r="D201" t="s">
+        <v>165</v>
+      </c>
+      <c r="E201" t="s">
+        <v>22</v>
+      </c>
+      <c r="F201" t="s">
+        <v>188</v>
+      </c>
+      <c r="G201" t="s">
+        <v>220</v>
+      </c>
+      <c r="H201" t="s">
+        <v>18</v>
+      </c>
+      <c r="I201" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="15">
+      <c r="A202" t="s">
+        <v>208</v>
+      </c>
+      <c r="B202" t="s">
+        <v>90</v>
+      </c>
+      <c r="C202" t="s">
+        <v>24</v>
+      </c>
+      <c r="D202" t="s">
+        <v>153</v>
+      </c>
+      <c r="E202" t="s">
+        <v>26</v>
+      </c>
+      <c r="F202" t="s">
+        <v>48</v>
+      </c>
+      <c r="G202" t="s">
+        <v>32</v>
+      </c>
+      <c r="H202" t="s">
+        <v>18</v>
+      </c>
+      <c r="I202" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="15">
+      <c r="A203" t="s">
+        <v>208</v>
+      </c>
+      <c r="B203" t="s">
+        <v>90</v>
+      </c>
+      <c r="C203" t="s">
+        <v>52</v>
+      </c>
+      <c r="D203" t="s">
+        <v>133</v>
+      </c>
+      <c r="E203" t="s">
+        <v>86</v>
+      </c>
+      <c r="F203" t="s">
+        <v>51</v>
+      </c>
+      <c r="G203" t="s">
+        <v>98</v>
+      </c>
+      <c r="H203" t="s">
+        <v>18</v>
+      </c>
+      <c r="I203" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="15">
+      <c r="A204" t="s">
+        <v>208</v>
+      </c>
+      <c r="B204" t="s">
+        <v>99</v>
+      </c>
+      <c r="C204" t="s">
+        <v>64</v>
+      </c>
+      <c r="D204" t="s">
+        <v>125</v>
+      </c>
+      <c r="E204" t="s">
+        <v>47</v>
+      </c>
+      <c r="F204" t="s">
+        <v>144</v>
+      </c>
+      <c r="G204" t="s">
+        <v>79</v>
+      </c>
+      <c r="H204" t="s">
+        <v>18</v>
+      </c>
+      <c r="I204" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" ht="15">
+      <c r="A205" t="s">
+        <v>208</v>
+      </c>
+      <c r="B205" t="s">
+        <v>99</v>
+      </c>
+      <c r="C205" t="s">
         <v>13</v>
       </c>
-      <c r="D201" t="s">
+      <c r="D205" t="s">
+        <v>221</v>
+      </c>
+      <c r="E205" t="s">
+        <v>15</v>
+      </c>
+      <c r="F205" t="s">
+        <v>222</v>
+      </c>
+      <c r="G205" t="s">
+        <v>98</v>
+      </c>
+      <c r="H205" t="s">
+        <v>18</v>
+      </c>
+      <c r="I205" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" ht="15">
+      <c r="A206" t="s">
+        <v>208</v>
+      </c>
+      <c r="B206" t="s">
+        <v>99</v>
+      </c>
+      <c r="C206" t="s">
+        <v>83</v>
+      </c>
+      <c r="D206" t="s">
+        <v>175</v>
+      </c>
+      <c r="E206" t="s">
+        <v>134</v>
+      </c>
+      <c r="F206" t="s">
+        <v>223</v>
+      </c>
+      <c r="G206" t="s">
+        <v>98</v>
+      </c>
+      <c r="H206" t="s">
+        <v>18</v>
+      </c>
+      <c r="I206" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" ht="15">
+      <c r="A207" t="s">
+        <v>208</v>
+      </c>
+      <c r="B207" t="s">
+        <v>99</v>
+      </c>
+      <c r="C207" t="s">
+        <v>24</v>
+      </c>
+      <c r="D207" t="s">
+        <v>187</v>
+      </c>
+      <c r="E207" t="s">
+        <v>81</v>
+      </c>
+      <c r="F207" t="s">
+        <v>82</v>
+      </c>
+      <c r="G207" t="s">
+        <v>96</v>
+      </c>
+      <c r="H207" t="s">
+        <v>18</v>
+      </c>
+      <c r="I207" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" ht="15">
+      <c r="A208" t="s">
+        <v>208</v>
+      </c>
+      <c r="B208" t="s">
+        <v>99</v>
+      </c>
+      <c r="C208" t="s">
+        <v>52</v>
+      </c>
+      <c r="D208" t="s">
+        <v>71</v>
+      </c>
+      <c r="E208" t="s">
+        <v>86</v>
+      </c>
+      <c r="F208" t="s">
+        <v>44</v>
+      </c>
+      <c r="G208" t="s">
+        <v>45</v>
+      </c>
+      <c r="H208" t="s">
+        <v>18</v>
+      </c>
+      <c r="I208" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" ht="15">
+      <c r="A209" t="s">
+        <v>208</v>
+      </c>
+      <c r="B209" t="s">
+        <v>99</v>
+      </c>
+      <c r="C209" t="s">
         <v>218</v>
       </c>
-      <c r="E201" t="s">
+      <c r="D209" t="s">
+        <v>224</v>
+      </c>
+      <c r="E209" t="s">
+        <v>47</v>
+      </c>
+      <c r="F209" t="s">
+        <v>48</v>
+      </c>
+      <c r="G209" t="s">
+        <v>98</v>
+      </c>
+      <c r="H209" t="s">
+        <v>18</v>
+      </c>
+      <c r="I209" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" ht="15">
+      <c r="A210" t="s">
+        <v>208</v>
+      </c>
+      <c r="B210" t="s">
+        <v>99</v>
+      </c>
+      <c r="C210" t="s">
+        <v>171</v>
+      </c>
+      <c r="D210" t="s">
+        <v>172</v>
+      </c>
+      <c r="E210" t="s">
+        <v>173</v>
+      </c>
+      <c r="F210" t="s">
+        <v>16</v>
+      </c>
+      <c r="G210" t="s">
+        <v>174</v>
+      </c>
+      <c r="H210" t="s">
+        <v>18</v>
+      </c>
+      <c r="I210" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" ht="15">
+      <c r="A211" t="s">
+        <v>208</v>
+      </c>
+      <c r="B211" t="s">
+        <v>99</v>
+      </c>
+      <c r="C211" t="s">
+        <v>225</v>
+      </c>
+      <c r="D211" t="s">
+        <v>153</v>
+      </c>
+      <c r="E211" t="s">
+        <v>37</v>
+      </c>
+      <c r="F211" t="s">
+        <v>41</v>
+      </c>
+      <c r="G211" t="s">
+        <v>226</v>
+      </c>
+      <c r="H211" t="s">
+        <v>18</v>
+      </c>
+      <c r="I211" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" ht="15">
+      <c r="A212" t="s">
+        <v>208</v>
+      </c>
+      <c r="B212" t="s">
+        <v>101</v>
+      </c>
+      <c r="C212" t="s">
+        <v>13</v>
+      </c>
+      <c r="D212" t="s">
+        <v>172</v>
+      </c>
+      <c r="E212" t="s">
         <v>15</v>
       </c>
-      <c r="F201" t="s">
+      <c r="F212" t="s">
+        <v>222</v>
+      </c>
+      <c r="G212" t="s">
+        <v>98</v>
+      </c>
+      <c r="H212" t="s">
+        <v>18</v>
+      </c>
+      <c r="I212" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" ht="15">
+      <c r="A213" t="s">
+        <v>208</v>
+      </c>
+      <c r="B213" t="s">
+        <v>101</v>
+      </c>
+      <c r="C213" t="s">
+        <v>24</v>
+      </c>
+      <c r="D213" t="s">
+        <v>59</v>
+      </c>
+      <c r="E213" t="s">
+        <v>26</v>
+      </c>
+      <c r="F213" t="s">
+        <v>27</v>
+      </c>
+      <c r="G213" t="s">
+        <v>98</v>
+      </c>
+      <c r="H213" t="s">
+        <v>18</v>
+      </c>
+      <c r="I213" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" ht="15">
+      <c r="A214" t="s">
+        <v>208</v>
+      </c>
+      <c r="B214" t="s">
+        <v>101</v>
+      </c>
+      <c r="C214" t="s">
+        <v>52</v>
+      </c>
+      <c r="D214" t="s">
+        <v>125</v>
+      </c>
+      <c r="E214" t="s">
+        <v>86</v>
+      </c>
+      <c r="F214" t="s">
+        <v>44</v>
+      </c>
+      <c r="G214" t="s">
+        <v>45</v>
+      </c>
+      <c r="H214" t="s">
+        <v>18</v>
+      </c>
+      <c r="I214" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" ht="15">
+      <c r="A215" t="s">
+        <v>208</v>
+      </c>
+      <c r="B215" t="s">
+        <v>101</v>
+      </c>
+      <c r="C215" t="s">
+        <v>225</v>
+      </c>
+      <c r="D215" t="s">
+        <v>153</v>
+      </c>
+      <c r="E215" t="s">
+        <v>37</v>
+      </c>
+      <c r="F215" t="s">
+        <v>41</v>
+      </c>
+      <c r="G215" t="s">
+        <v>226</v>
+      </c>
+      <c r="H215" t="s">
+        <v>18</v>
+      </c>
+      <c r="I215" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="15">
+      <c r="A216" t="s">
+        <v>208</v>
+      </c>
+      <c r="B216" t="s">
+        <v>149</v>
+      </c>
+      <c r="C216" t="s">
+        <v>13</v>
+      </c>
+      <c r="D216" t="s">
+        <v>213</v>
+      </c>
+      <c r="E216" t="s">
+        <v>81</v>
+      </c>
+      <c r="F216" t="s">
+        <v>82</v>
+      </c>
+      <c r="G216" t="s">
+        <v>96</v>
+      </c>
+      <c r="H216" t="s">
+        <v>18</v>
+      </c>
+      <c r="I216" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" ht="15">
+      <c r="A217" t="s">
+        <v>208</v>
+      </c>
+      <c r="B217" t="s">
+        <v>206</v>
+      </c>
+      <c r="C217" t="s">
+        <v>13</v>
+      </c>
+      <c r="D217" t="s">
+        <v>227</v>
+      </c>
+      <c r="E217" t="s">
+        <v>15</v>
+      </c>
+      <c r="F217" t="s">
         <v>103</v>
       </c>
-      <c r="G201" t="s">
+      <c r="G217" t="s">
         <v>98</v>
       </c>
-      <c r="H201" t="s">
-        <v>18</v>
-      </c>
-      <c r="I201" t="s">
+      <c r="H217" t="s">
+        <v>18</v>
+      </c>
+      <c r="I217" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7157,8 +7663,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e1b4d51a-6675-43b2-a2a8-379d41fa8f24}">
-  <dimension ref="A1:I13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d67be520-e5e9-4c9d-b962-cd2ae09f8f15}">
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -7177,16 +7683,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -7206,16 +7712,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -7235,16 +7741,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C3" t="s">
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="E3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -7264,16 +7770,16 @@
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E4" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -7293,16 +7799,16 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E5" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -7322,16 +7828,16 @@
         <v>151</v>
       </c>
       <c r="B6" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E6" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -7351,16 +7857,16 @@
         <v>151</v>
       </c>
       <c r="B7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C7" t="s">
         <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="E7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -7380,16 +7886,16 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C8" t="s">
         <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E8" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -7409,16 +7915,16 @@
         <v>182</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>247</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -7438,16 +7944,16 @@
         <v>182</v>
       </c>
       <c r="B10" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="E10" t="s">
-        <v>228</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -7467,16 +7973,16 @@
         <v>182</v>
       </c>
       <c r="B11" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="E11" t="s">
-        <v>240</v>
+        <v>134</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -7493,19 +7999,19 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B12" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E12" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -7522,30 +8028,175 @@
     </row>
     <row r="13" spans="1:9" ht="15">
       <c r="A13" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B13" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" t="s">
+        <v>251</v>
+      </c>
+      <c r="E13" t="s">
+        <v>252</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15">
+      <c r="A14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" t="s">
+        <v>254</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15">
+      <c r="A15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B15" t="s">
+        <v>255</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>251</v>
+      </c>
+      <c r="E15" t="s">
+        <v>252</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15">
+      <c r="A16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>239</v>
+      </c>
+      <c r="E16" t="s">
+        <v>254</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15">
+      <c r="A17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B17" t="s">
+        <v>257</v>
+      </c>
+      <c r="C17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" t="s">
+        <v>236</v>
+      </c>
+      <c r="E17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15">
+      <c r="A18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B18" t="s">
+        <v>258</v>
+      </c>
+      <c r="C18" t="s">
         <v>20</v>
       </c>
-      <c r="D13" t="s">
-        <v>243</v>
-      </c>
-      <c r="E13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="D18" t="s">
+        <v>259</v>
+      </c>
+      <c r="E18" t="s">
+        <v>260</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7557,8 +8208,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{9dfd6a7f-5b25-4931-87e3-fab61c111aac}">
-  <dimension ref="A1:F48"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b23d7ac3-c614-4191-8146-ae653f875802}">
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -7574,13 +8225,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -7594,13 +8245,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -7614,13 +8265,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="C3" t="s">
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="E3" t="s">
         <v>100</v>
@@ -7634,13 +8285,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="C4" t="s">
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="E4" t="s">
         <v>42</v>
@@ -7654,16 +8305,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="E5" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -7674,13 +8325,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="E6" t="s">
         <v>136</v>
@@ -7694,13 +8345,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="C7" t="s">
         <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="E7" t="s">
         <v>58</v>
@@ -7714,13 +8365,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="E8" t="s">
         <v>174</v>
@@ -7734,16 +8385,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="E9" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -7754,13 +8405,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="C10" t="s">
         <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E10" t="s">
         <v>117</v>
@@ -7774,13 +8425,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
@@ -7794,13 +8445,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E12" t="s">
         <v>136</v>
@@ -7814,16 +8465,16 @@
         <v>104</v>
       </c>
       <c r="B13" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="E13" t="s">
-        <v>259</v>
+        <v>191</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -7834,13 +8485,13 @@
         <v>104</v>
       </c>
       <c r="B14" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="C14" t="s">
         <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E14" t="s">
         <v>100</v>
@@ -7854,13 +8505,13 @@
         <v>104</v>
       </c>
       <c r="B15" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C15" t="s">
         <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="E15" t="s">
         <v>119</v>
@@ -7874,13 +8525,13 @@
         <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="C16" t="s">
         <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="E16" t="s">
         <v>117</v>
@@ -7894,13 +8545,13 @@
         <v>104</v>
       </c>
       <c r="B17" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="C17" t="s">
         <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E17" t="s">
         <v>136</v>
@@ -7914,16 +8565,16 @@
         <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="C18" t="s">
         <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E18" t="s">
-        <v>263</v>
+        <v>200</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -7934,16 +8585,16 @@
         <v>104</v>
       </c>
       <c r="B19" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C19" t="s">
         <v>163</v>
       </c>
       <c r="D19" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E19" t="s">
-        <v>263</v>
+        <v>200</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -7954,16 +8605,16 @@
         <v>151</v>
       </c>
       <c r="B20" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="C20" t="s">
         <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E20" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -7974,13 +8625,13 @@
         <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="C21" t="s">
         <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="E21" t="s">
         <v>87</v>
@@ -7994,16 +8645,16 @@
         <v>151</v>
       </c>
       <c r="B22" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C22" t="s">
         <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="E22" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -8014,13 +8665,13 @@
         <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="C23" t="s">
         <v>167</v>
       </c>
       <c r="D23" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="E23" t="s">
         <v>115</v>
@@ -8034,13 +8685,13 @@
         <v>151</v>
       </c>
       <c r="B24" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="C24" t="s">
         <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
@@ -8054,13 +8705,13 @@
         <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C25" t="s">
         <v>167</v>
       </c>
       <c r="D25" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="E25" t="s">
         <v>42</v>
@@ -8074,16 +8725,16 @@
         <v>151</v>
       </c>
       <c r="B26" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C26" t="s">
         <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E26" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -8094,16 +8745,16 @@
         <v>151</v>
       </c>
       <c r="B27" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C27" t="s">
         <v>141</v>
       </c>
       <c r="D27" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="E27" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
@@ -8114,13 +8765,13 @@
         <v>151</v>
       </c>
       <c r="B28" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="C28" t="s">
         <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
@@ -8134,16 +8785,16 @@
         <v>182</v>
       </c>
       <c r="B29" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="C29" t="s">
         <v>64</v>
       </c>
       <c r="D29" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="E29" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -8154,13 +8805,13 @@
         <v>182</v>
       </c>
       <c r="B30" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="C30" t="s">
         <v>52</v>
       </c>
       <c r="D30" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E30" t="s">
         <v>76</v>
@@ -8174,13 +8825,13 @@
         <v>182</v>
       </c>
       <c r="B31" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="C31" t="s">
         <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
@@ -8194,13 +8845,13 @@
         <v>182</v>
       </c>
       <c r="B32" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C32" t="s">
         <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="E32" t="s">
         <v>45</v>
@@ -8214,16 +8865,16 @@
         <v>182</v>
       </c>
       <c r="B33" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="D33" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="E33" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -8234,16 +8885,16 @@
         <v>182</v>
       </c>
       <c r="B34" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="E34" t="s">
-        <v>268</v>
+        <v>136</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
@@ -8254,16 +8905,16 @@
         <v>182</v>
       </c>
       <c r="B35" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C35" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="E35" t="s">
-        <v>203</v>
+        <v>282</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
@@ -8274,16 +8925,16 @@
         <v>182</v>
       </c>
       <c r="B36" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D36" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="E36" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
@@ -8294,16 +8945,16 @@
         <v>182</v>
       </c>
       <c r="B37" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="D37" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>196</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -8311,19 +8962,19 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B38" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="E38" t="s">
-        <v>210</v>
+        <v>19</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
@@ -8331,19 +8982,19 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B39" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D39" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="E39" t="s">
-        <v>87</v>
+        <v>220</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
@@ -8351,19 +9002,19 @@
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B40" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="E40" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="F40" t="s">
         <v>18</v>
@@ -8371,19 +9022,19 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B41" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C41" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D41" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="E41" t="s">
-        <v>210</v>
+        <v>119</v>
       </c>
       <c r="F41" t="s">
         <v>18</v>
@@ -8391,19 +9042,19 @@
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B42" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C42" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="D42" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E42" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="F42" t="s">
         <v>18</v>
@@ -8411,19 +9062,19 @@
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B43" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="D43" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="E43" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -8431,19 +9082,19 @@
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B44" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="C44" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="D44" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E44" t="s">
-        <v>170</v>
+        <v>87</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>
@@ -8451,19 +9102,19 @@
     </row>
     <row r="45" spans="1:6" ht="15">
       <c r="A45" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="C45" t="s">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="D45" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="E45" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
@@ -8471,19 +9122,19 @@
     </row>
     <row r="46" spans="1:6" ht="15">
       <c r="A46" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B46" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="D46" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="E46" t="s">
-        <v>203</v>
+        <v>45</v>
       </c>
       <c r="F46" t="s">
         <v>18</v>
@@ -8491,19 +9142,19 @@
     </row>
     <row r="47" spans="1:6" ht="15">
       <c r="A47" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B47" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C47" t="s">
         <v>24</v>
       </c>
       <c r="D47" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="E47" t="s">
-        <v>263</v>
+        <v>87</v>
       </c>
       <c r="F47" t="s">
         <v>18</v>
@@ -8511,21 +9162,41 @@
     </row>
     <row r="48" spans="1:6" ht="15">
       <c r="A48" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B48" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="C48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" t="s">
+        <v>264</v>
+      </c>
+      <c r="E48" t="s">
+        <v>200</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15">
+      <c r="A49" t="s">
+        <v>208</v>
+      </c>
+      <c r="B49" t="s">
+        <v>280</v>
+      </c>
+      <c r="C49" t="s">
         <v>52</v>
       </c>
-      <c r="D48" t="s">
-        <v>247</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="D49" t="s">
+        <v>263</v>
+      </c>
+      <c r="E49" t="s">
         <v>76</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F49" t="s">
         <v>18</v>
       </c>
     </row>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -10,17 +10,19 @@
     <sheet name="Opis parametrów" sheetId="2" r:id="rId2"/>
     <sheet name="Oddziały" sheetId="3" r:id="rId3"/>
     <sheet name="Dzienniki zajeć innych" sheetId="4" r:id="rId4"/>
+    <sheet name="Dyżury" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Oddziały!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dzienniki zajeć innych'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dyżury!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="188">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -82,6 +84,30 @@
     <t>-</t>
   </si>
   <si>
+    <t>Mikołajczak Sylwia</t>
+  </si>
+  <si>
+    <t>3FA</t>
+  </si>
+  <si>
+    <t>Podstawy fryzjerstwa</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Stępień Krystyna</t>
+  </si>
+  <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>Technika w produkcji cukierniczej</t>
+  </si>
+  <si>
+    <t>prs</t>
+  </si>
+  <si>
     <t>Wakat4 doradztwo zaw.</t>
   </si>
   <si>
@@ -112,6 +138,9 @@
     <t>Matematyka</t>
   </si>
   <si>
+    <t>Zajęcia z wychowawcą</t>
+  </si>
+  <si>
     <t>Nestoruk Lidia</t>
   </si>
   <si>
@@ -130,9 +159,39 @@
     <t>3, 09:40-10:25</t>
   </si>
   <si>
+    <t>1FB|JA1</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
+    <t>Bezpłatne</t>
+  </si>
+  <si>
+    <t>1CA</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Mocarski Arkadiusz</t>
+  </si>
+  <si>
     <t>4, 10:35-11:20</t>
   </si>
   <si>
+    <t>2FA</t>
+  </si>
+  <si>
     <t>Sobczak Anna</t>
   </si>
   <si>
@@ -145,12 +204,30 @@
     <t>prF3</t>
   </si>
   <si>
+    <t>Bokuniewicz Sylwia</t>
+  </si>
+  <si>
     <t>5, 11:25-12:10</t>
   </si>
   <si>
+    <t>2FC</t>
+  </si>
+  <si>
+    <t>Zajęcia biblioteczne</t>
+  </si>
+  <si>
+    <t>bib</t>
+  </si>
+  <si>
+    <t>Nowak Damiana</t>
+  </si>
+  <si>
     <t>Antoszewska Joanna</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>3M</t>
   </si>
   <si>
@@ -160,9 +237,6 @@
     <t>Kończyńska Małgorzata</t>
   </si>
   <si>
-    <t>2CB</t>
-  </si>
-  <si>
     <t>Język polski</t>
   </si>
   <si>
@@ -172,15 +246,18 @@
     <t>Derezińska Katarzyna</t>
   </si>
   <si>
-    <t>2FA</t>
-  </si>
-  <si>
     <t>Biologia</t>
   </si>
   <si>
     <t>Sałdyka Karolina</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Filipiak Wiesław</t>
+  </si>
+  <si>
     <t>7, 13:15-14:00</t>
   </si>
   <si>
@@ -199,15 +276,9 @@
     <t>Technologie produkcji cukierniczej</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
     <t>Zastępstwo</t>
   </si>
   <si>
-    <t>3FA</t>
-  </si>
-  <si>
     <t>Techniki fryzjerskie</t>
   </si>
   <si>
@@ -220,6 +291,9 @@
     <t>Uczniowie zwolnieni do domu</t>
   </si>
   <si>
+    <t>Leńczowska Iwona</t>
+  </si>
+  <si>
     <t>9, 14:55-15:40</t>
   </si>
   <si>
@@ -244,12 +318,6 @@
     <t>34</t>
   </si>
   <si>
-    <t>Mocarski Arkadiusz</t>
-  </si>
-  <si>
-    <t>Bezpłatne</t>
-  </si>
-  <si>
     <t>3FA|edu</t>
   </si>
   <si>
@@ -265,7 +333,7 @@
     <t>3FB</t>
   </si>
   <si>
-    <t>Zajęcia z wychowawcą</t>
+    <t>Dalach Krystyna</t>
   </si>
   <si>
     <t>29</t>
@@ -277,162 +345,153 @@
     <t>1WB</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>1TH</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>2FB</t>
   </si>
   <si>
+    <t>Edukacja obywatelska</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
+    <t>1WB|JN1</t>
+  </si>
+  <si>
+    <t>Kruk Marcin</t>
+  </si>
+  <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>Jastrzębska-Majtyka Agnieszka</t>
+  </si>
+  <si>
+    <t>10, 15:45-16:30</t>
+  </si>
+  <si>
+    <t>1TFA|JA1</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur</t>
+  </si>
+  <si>
+    <t>11, 16:35-17:20</t>
+  </si>
+  <si>
+    <t>12, 17:25-18:10</t>
+  </si>
+  <si>
+    <t>13, 18:15-19:00</t>
+  </si>
+  <si>
+    <t>11.03.2026</t>
+  </si>
+  <si>
     <t>Rozwój kompetencji zawodowych - barber</t>
   </si>
   <si>
-    <t>1WB|JN1</t>
-  </si>
-  <si>
-    <t>Kruk Marcin</t>
-  </si>
-  <si>
-    <t>1FB</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Jastrzębska-Majtyka Agnieszka</t>
-  </si>
-  <si>
-    <t>10, 15:45-16:30</t>
-  </si>
-  <si>
-    <t>1TFA|JA1</t>
-  </si>
-  <si>
-    <t>2B</t>
-  </si>
-  <si>
-    <t>Projektowanie fryzur</t>
+    <t>2CA|edu</t>
+  </si>
+  <si>
+    <t>2FC|edu</t>
+  </si>
+  <si>
+    <t>2S|edu</t>
+  </si>
+  <si>
+    <t>2WA|edu</t>
+  </si>
+  <si>
+    <t>1FA|JA1</t>
+  </si>
+  <si>
+    <t>sg2</t>
+  </si>
+  <si>
+    <t>2K|CH</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>Pietrycha Małgorzata</t>
+  </si>
+  <si>
+    <t>Wakat1 j. niemiecki</t>
+  </si>
+  <si>
+    <t>1WA|JN2</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
+    <t>12.03.2026</t>
+  </si>
+  <si>
+    <t>2WA</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>Wójcik Kamil</t>
+  </si>
+  <si>
+    <t>1WA|CH</t>
+  </si>
+  <si>
+    <t>Brak</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>1WA</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>1FC</t>
+  </si>
+  <si>
+    <t>Chemia</t>
+  </si>
+  <si>
+    <t>2B|JA1</t>
+  </si>
+  <si>
+    <t>2B|JA2</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Zajęcia praktyczne - projektowanie i wykonywanie fryzur</t>
   </si>
   <si>
     <t>Danielewski Paweł</t>
   </si>
   <si>
-    <t>11, 16:35-17:20</t>
-  </si>
-  <si>
-    <t>12, 17:25-18:10</t>
-  </si>
-  <si>
-    <t>13, 18:15-19:00</t>
-  </si>
-  <si>
-    <t>11.03.2026</t>
-  </si>
-  <si>
-    <t>2CA|edu</t>
-  </si>
-  <si>
-    <t>2FC|edu</t>
-  </si>
-  <si>
-    <t>2S|edu</t>
-  </si>
-  <si>
-    <t>2WA|edu</t>
-  </si>
-  <si>
-    <t>1FA|JA1</t>
-  </si>
-  <si>
-    <t>sg2</t>
-  </si>
-  <si>
-    <t>2FC</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Karczmarz Aleksandra</t>
-  </si>
-  <si>
-    <t>2K|CH</t>
-  </si>
-  <si>
-    <t>Wojciechowski Łukasz</t>
-  </si>
-  <si>
-    <t>Pietrycha Małgorzata</t>
-  </si>
-  <si>
-    <t>Wakat1 j. niemiecki</t>
-  </si>
-  <si>
-    <t>1WA|JN2</t>
-  </si>
-  <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>Fiodorów Małgorzata</t>
-  </si>
-  <si>
-    <t>Dalach Krystyna</t>
-  </si>
-  <si>
-    <t>12.03.2026</t>
-  </si>
-  <si>
-    <t>2WA</t>
-  </si>
-  <si>
-    <t>Wójcik Kamil</t>
-  </si>
-  <si>
-    <t>1WA|CH</t>
-  </si>
-  <si>
-    <t>Brak</t>
-  </si>
-  <si>
-    <t>1FA</t>
-  </si>
-  <si>
-    <t>1TFA</t>
-  </si>
-  <si>
-    <t>1WA</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
-    <t>Chemia</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
-  </si>
-  <si>
-    <t>2TH</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>Zajęcia praktyczne - projektowanie i wykonywanie fryzur</t>
-  </si>
-  <si>
     <t>1CB|JA1</t>
   </si>
   <si>
@@ -445,9 +504,6 @@
     <t>aq1</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>Płatek Krzysztof</t>
   </si>
   <si>
@@ -463,15 +519,9 @@
     <t>p. Piątek-Pawłowska, j. polski za lekcję 1</t>
   </si>
   <si>
-    <t>Filipiak Wiesław</t>
-  </si>
-  <si>
     <t>1S</t>
   </si>
   <si>
-    <t>Podstawy fryzjerstwa</t>
-  </si>
-  <si>
     <t>28</t>
   </si>
   <si>
@@ -493,6 +543,15 @@
     <t>Opis zajęć</t>
   </si>
   <si>
+    <t>15:45-16:30</t>
+  </si>
+  <si>
+    <t>Krzysztof Miedziński - 3TFB - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>podstawy fryzjestwa/ projektowanie fryzur</t>
+  </si>
+  <si>
     <t>16:30-17:15</t>
   </si>
   <si>
@@ -500,6 +559,33 @@
   </si>
   <si>
     <t>matematyka</t>
+  </si>
+  <si>
+    <t>Miejsce dyżuru</t>
+  </si>
+  <si>
+    <t>07:55-08:00</t>
+  </si>
+  <si>
+    <t>boisko - dziedziniec wejściowy/boisko</t>
+  </si>
+  <si>
+    <t>09:35-09:40</t>
+  </si>
+  <si>
+    <t>bramka wejściowa</t>
+  </si>
+  <si>
+    <t>10:25-10:35</t>
+  </si>
+  <si>
+    <t>Nowak Magdalena</t>
+  </si>
+  <si>
+    <t>14:50-14:55</t>
+  </si>
+  <si>
+    <t>Cieśla Marcin</t>
   </si>
 </sst>
 </file>
@@ -949,7 +1035,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{75ccf1ec-a924-4a5e-ad9e-efa6e35b1e1f}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2202cc6c-42e8-4ad5-abd5-4b49e5f5fee0}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -970,8 +1056,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f0c94913-e60b-43d7-b98c-aa1cab3f0d91}">
-  <dimension ref="A1:I97"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d84e4575-df5c-4400-ac4c-f114c974903c}">
+  <dimension ref="A1:I124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1063,13 +1149,13 @@
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
@@ -1077,19 +1163,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
@@ -1106,28 +1192,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -1135,28 +1221,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -1164,19 +1250,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
@@ -1193,19 +1279,19 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
@@ -1222,19 +1308,19 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
@@ -1251,28 +1337,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
@@ -1280,28 +1366,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1309,28 +1395,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="G12" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
@@ -1341,25 +1427,25 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s">
         <v>46</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>47</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>48</v>
       </c>
-      <c r="G13" t="s">
-        <v>49</v>
-      </c>
       <c r="H13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
@@ -1370,25 +1456,25 @@
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
         <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1399,7 +1485,7 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
         <v>50</v>
@@ -1408,16 +1494,16 @@
         <v>51</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="G15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
@@ -1425,28 +1511,28 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -1454,22 +1540,22 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="G17" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
         <v>18</v>
@@ -1483,28 +1569,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="G18" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H18" t="s">
         <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1512,28 +1598,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G19" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -1541,19 +1627,19 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" t="s">
         <v>64</v>
-      </c>
-      <c r="C20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
       </c>
       <c r="G20" t="s">
         <v>65</v>
@@ -1562,7 +1648,7 @@
         <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -1570,689 +1656,689 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" t="s">
         <v>66</v>
       </c>
-      <c r="C21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21" t="s">
-        <v>65</v>
-      </c>
       <c r="H21" t="s">
         <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="E22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H22" t="s">
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
         <v>68</v>
       </c>
-      <c r="B23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" t="s">
-        <v>71</v>
-      </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G23" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="H23" t="s">
         <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
         <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" t="s">
         <v>72</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>73</v>
       </c>
-      <c r="G24" t="s">
-        <v>74</v>
-      </c>
       <c r="H24" t="s">
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="F25" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G25" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="F26" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" t="s">
         <v>37</v>
       </c>
-      <c r="D28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E28" t="s">
-        <v>22</v>
-      </c>
       <c r="F28" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
         <v>35</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>79</v>
       </c>
-      <c r="D29" t="s">
-        <v>46</v>
-      </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="F29" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s">
         <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F30" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G30" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E32" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G32" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
       <c r="A33" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="G33" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F34" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="G34" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="E35" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="F35" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="G35" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s">
         <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E36" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F36" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="B37" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E37" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F37" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E38" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="F38" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="G38" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D39" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E39" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F39" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G39" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="D40" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" t="s">
         <v>96</v>
       </c>
-      <c r="E40" t="s">
-        <v>15</v>
-      </c>
       <c r="F40" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="G40" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D41" t="s">
+        <v>100</v>
+      </c>
+      <c r="E41" t="s">
+        <v>96</v>
+      </c>
+      <c r="F41" t="s">
         <v>97</v>
       </c>
-      <c r="E41" t="s">
-        <v>98</v>
-      </c>
-      <c r="F41" t="s">
-        <v>93</v>
-      </c>
       <c r="G41" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="H41" t="s">
         <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D42" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="E42" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="F42" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="G42" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="B43" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="D43" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E43" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F43" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="G43" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="B44" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C44" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="E44" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="F44" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="G44" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
@@ -2263,22 +2349,22 @@
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="E45" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F45" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="G45" t="s">
         <v>17</v>
@@ -2292,379 +2378,379 @@
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="F46" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="G46" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F47" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G47" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" t="s">
+        <v>38</v>
+      </c>
+      <c r="F48" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" t="s">
         <v>103</v>
       </c>
-      <c r="B48" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D48" t="s">
-        <v>106</v>
-      </c>
-      <c r="E48" t="s">
-        <v>72</v>
-      </c>
-      <c r="F48" t="s">
-        <v>73</v>
-      </c>
-      <c r="G48" t="s">
-        <v>74</v>
-      </c>
       <c r="H48" t="s">
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D49" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="E49" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F49" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="G49" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C50" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="D50" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E50" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="F50" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="G50" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D51" t="s">
+        <v>107</v>
+      </c>
+      <c r="E51" t="s">
+        <v>108</v>
+      </c>
+      <c r="F51" t="s">
+        <v>109</v>
+      </c>
+      <c r="G51" t="s">
         <v>110</v>
       </c>
-      <c r="E51" t="s">
-        <v>111</v>
-      </c>
-      <c r="F51" t="s">
-        <v>112</v>
-      </c>
-      <c r="G51" t="s">
-        <v>113</v>
-      </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E52" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F52" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="C53" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="D53" t="s">
+        <v>113</v>
+      </c>
+      <c r="E53" t="s">
         <v>38</v>
       </c>
-      <c r="E53" t="s">
-        <v>29</v>
-      </c>
       <c r="F53" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="G53" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B54" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="C54" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E54" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F54" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B55" t="s">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="C55" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="D55" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E55" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F55" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="G55" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="C56" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="D56" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E56" t="s">
+        <v>118</v>
+      </c>
+      <c r="F56" t="s">
+        <v>31</v>
+      </c>
+      <c r="G56" t="s">
         <v>32</v>
       </c>
-      <c r="F56" t="s">
-        <v>109</v>
-      </c>
-      <c r="G56" t="s">
-        <v>116</v>
-      </c>
       <c r="H56" t="s">
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B57" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
         <v>117</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>118</v>
       </c>
-      <c r="E57" t="s">
-        <v>119</v>
-      </c>
       <c r="F57" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G57" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="D58" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E58" t="s">
+        <v>118</v>
+      </c>
+      <c r="F58" t="s">
+        <v>31</v>
+      </c>
+      <c r="G58" t="s">
         <v>32</v>
       </c>
-      <c r="F58" t="s">
-        <v>109</v>
-      </c>
-      <c r="G58" t="s">
-        <v>121</v>
-      </c>
       <c r="H58" t="s">
         <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
@@ -2675,16 +2761,16 @@
         <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D59" t="s">
+        <v>55</v>
+      </c>
+      <c r="E59" t="s">
         <v>123</v>
       </c>
-      <c r="E59" t="s">
-        <v>39</v>
-      </c>
       <c r="F59" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="G59" t="s">
         <v>17</v>
@@ -2701,28 +2787,28 @@
         <v>122</v>
       </c>
       <c r="B60" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="D60" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E60" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="F60" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="G60" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
@@ -2730,28 +2816,28 @@
         <v>122</v>
       </c>
       <c r="B61" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="D61" t="s">
         <v>125</v>
       </c>
       <c r="E61" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="F61" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G61" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
@@ -2759,28 +2845,28 @@
         <v>122</v>
       </c>
       <c r="B62" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="D62" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E62" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="F62" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G62" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
@@ -2788,28 +2874,28 @@
         <v>122</v>
       </c>
       <c r="B63" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="D63" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E63" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="F63" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G63" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
@@ -2817,28 +2903,28 @@
         <v>122</v>
       </c>
       <c r="B64" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C64" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="D64" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E64" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F64" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="G64" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
@@ -2846,28 +2932,28 @@
         <v>122</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>56</v>
       </c>
       <c r="D65" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="E65" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F65" t="s">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="G65" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
@@ -2875,28 +2961,28 @@
         <v>122</v>
       </c>
       <c r="B66" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C66" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="D66" t="s">
         <v>128</v>
       </c>
       <c r="E66" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F66" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="G66" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
@@ -2907,25 +2993,25 @@
         <v>44</v>
       </c>
       <c r="C67" t="s">
-        <v>124</v>
+        <v>56</v>
       </c>
       <c r="D67" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="E67" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="F67" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="G67" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
@@ -2933,28 +3019,28 @@
         <v>122</v>
       </c>
       <c r="B68" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C68" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D68" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E68" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="F68" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="G68" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
@@ -2962,28 +3048,28 @@
         <v>122</v>
       </c>
       <c r="B69" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C69" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="D69" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="E69" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F69" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="G69" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
@@ -2991,28 +3077,28 @@
         <v>122</v>
       </c>
       <c r="B70" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C70" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D70" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="E70" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="F70" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="G70" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
@@ -3020,28 +3106,28 @@
         <v>122</v>
       </c>
       <c r="B71" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="D71" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="E71" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="F71" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="G71" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
@@ -3049,109 +3135,109 @@
         <v>122</v>
       </c>
       <c r="B72" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="D72" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E72" t="s">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="F72" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="G72" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B73" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="D73" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="E73" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="F73" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="G73" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B74" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D74" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="E74" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="F74" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="G74" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B75" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="C75" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="D75" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E75" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="F75" t="s">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="G75" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
@@ -3162,138 +3248,138 @@
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B76" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="C76" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="D76" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="E76" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="F76" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="G76" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B77" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="C77" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="D77" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="E77" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="F77" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="G77" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B78" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C78" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="D78" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="E78" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F78" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="G78" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B79" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C79" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D79" t="s">
         <v>139</v>
       </c>
       <c r="E79" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="F79" t="s">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="G79" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B80" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C80" t="s">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="D80" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="E80" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F80" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="G80" t="s">
         <v>142</v>
@@ -3302,149 +3388,149 @@
         <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B81" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="C81" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D81" t="s">
         <v>143</v>
       </c>
       <c r="E81" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="F81" t="s">
-        <v>141</v>
+        <v>86</v>
       </c>
       <c r="G81" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B82" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C82" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D82" t="s">
         <v>139</v>
       </c>
       <c r="E82" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="F82" t="s">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="G82" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B83" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C83" t="s">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="D83" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E83" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F83" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="G83" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B84" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C84" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="D84" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="E84" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="F84" t="s">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="G84" t="s">
-        <v>145</v>
+        <v>32</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B85" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C85" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D85" t="s">
         <v>139</v>
       </c>
       <c r="E85" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F85" t="s">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="G85" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="H85" t="s">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="I85" t="s">
         <v>19</v>
@@ -3452,83 +3538,83 @@
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B86" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C86" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D86" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E86" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F86" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G86" t="s">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B87" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="C87" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="D87" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E87" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F87" t="s">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="G87" t="s">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B88" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C88" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="D88" t="s">
+        <v>147</v>
+      </c>
+      <c r="E88" t="s">
+        <v>148</v>
+      </c>
+      <c r="F88" t="s">
+        <v>109</v>
+      </c>
+      <c r="G88" t="s">
         <v>88</v>
-      </c>
-      <c r="E88" t="s">
-        <v>62</v>
-      </c>
-      <c r="F88" t="s">
-        <v>23</v>
-      </c>
-      <c r="G88" t="s">
-        <v>126</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
@@ -3539,263 +3625,1046 @@
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B89" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="D89" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E89" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F89" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="G89" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B90" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C90" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="D90" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="E90" t="s">
-        <v>149</v>
+        <v>46</v>
       </c>
       <c r="F90" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="G90" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B91" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C91" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="D91" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="E91" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F91" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="G91" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B92" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="D92" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E92" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F92" t="s">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="G92" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B93" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="C93" t="s">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="D93" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="E93" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F93" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G93" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B94" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="C94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
         <v>117</v>
       </c>
-      <c r="D94" t="s">
-        <v>118</v>
-      </c>
       <c r="E94" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="F94" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="G94" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B95" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="C95" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="D95" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="E95" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F95" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="G95" t="s">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B96" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="D96" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="E96" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="F96" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="G96" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B97" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="C97" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="D97" t="s">
+        <v>117</v>
+      </c>
+      <c r="E97" t="s">
+        <v>154</v>
+      </c>
+      <c r="F97" t="s">
+        <v>109</v>
+      </c>
+      <c r="G97" t="s">
+        <v>155</v>
+      </c>
+      <c r="H97" t="s">
+        <v>18</v>
+      </c>
+      <c r="I97" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15">
+      <c r="A98" t="s">
+        <v>137</v>
+      </c>
+      <c r="B98" t="s">
+        <v>120</v>
+      </c>
+      <c r="C98" t="s">
+        <v>112</v>
+      </c>
+      <c r="D98" t="s">
+        <v>117</v>
+      </c>
+      <c r="E98" t="s">
+        <v>154</v>
+      </c>
+      <c r="F98" t="s">
+        <v>109</v>
+      </c>
+      <c r="G98" t="s">
+        <v>155</v>
+      </c>
+      <c r="H98" t="s">
+        <v>18</v>
+      </c>
+      <c r="I98" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="15">
+      <c r="A99" t="s">
+        <v>137</v>
+      </c>
+      <c r="B99" t="s">
+        <v>121</v>
+      </c>
+      <c r="C99" t="s">
+        <v>112</v>
+      </c>
+      <c r="D99" t="s">
+        <v>117</v>
+      </c>
+      <c r="E99" t="s">
+        <v>154</v>
+      </c>
+      <c r="F99" t="s">
+        <v>109</v>
+      </c>
+      <c r="G99" t="s">
+        <v>155</v>
+      </c>
+      <c r="H99" t="s">
+        <v>18</v>
+      </c>
+      <c r="I99" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="15">
+      <c r="A100" t="s">
+        <v>157</v>
+      </c>
+      <c r="B100" t="s">
+        <v>12</v>
+      </c>
+      <c r="C100" t="s">
+        <v>24</v>
+      </c>
+      <c r="D100" t="s">
+        <v>139</v>
+      </c>
+      <c r="E100" t="s">
+        <v>51</v>
+      </c>
+      <c r="F100" t="s">
+        <v>109</v>
+      </c>
+      <c r="G100" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100" t="s">
+        <v>18</v>
+      </c>
+      <c r="I100" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="15">
+      <c r="A101" t="s">
+        <v>157</v>
+      </c>
+      <c r="B101" t="s">
+        <v>34</v>
+      </c>
+      <c r="C101" t="s">
+        <v>24</v>
+      </c>
+      <c r="D101" t="s">
+        <v>139</v>
+      </c>
+      <c r="E101" t="s">
+        <v>51</v>
+      </c>
+      <c r="F101" t="s">
+        <v>109</v>
+      </c>
+      <c r="G101" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" t="s">
+        <v>18</v>
+      </c>
+      <c r="I101" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="15">
+      <c r="A102" t="s">
+        <v>157</v>
+      </c>
+      <c r="B102" t="s">
+        <v>44</v>
+      </c>
+      <c r="C102" t="s">
+        <v>101</v>
+      </c>
+      <c r="D102" t="s">
+        <v>158</v>
+      </c>
+      <c r="E102" t="s">
+        <v>41</v>
+      </c>
+      <c r="F102" t="s">
+        <v>159</v>
+      </c>
+      <c r="G102" t="s">
+        <v>103</v>
+      </c>
+      <c r="H102" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="15">
+      <c r="A103" t="s">
+        <v>157</v>
+      </c>
+      <c r="B103" t="s">
+        <v>44</v>
+      </c>
+      <c r="C103" t="s">
+        <v>56</v>
+      </c>
+      <c r="D103" t="s">
+        <v>128</v>
+      </c>
+      <c r="E103" t="s">
+        <v>15</v>
+      </c>
+      <c r="F103" t="s">
+        <v>67</v>
+      </c>
+      <c r="G103" t="s">
+        <v>160</v>
+      </c>
+      <c r="H103" t="s">
+        <v>18</v>
+      </c>
+      <c r="I103" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15">
+      <c r="A104" t="s">
+        <v>157</v>
+      </c>
+      <c r="B104" t="s">
+        <v>44</v>
+      </c>
+      <c r="C104" t="s">
+        <v>56</v>
+      </c>
+      <c r="D104" t="s">
+        <v>161</v>
+      </c>
+      <c r="E104" t="s">
+        <v>15</v>
+      </c>
+      <c r="F104" t="s">
+        <v>67</v>
+      </c>
+      <c r="G104" t="s">
+        <v>160</v>
+      </c>
+      <c r="H104" t="s">
+        <v>18</v>
+      </c>
+      <c r="I104" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="15">
+      <c r="A105" t="s">
+        <v>157</v>
+      </c>
+      <c r="B105" t="s">
+        <v>44</v>
+      </c>
+      <c r="C105" t="s">
+        <v>24</v>
+      </c>
+      <c r="D105" t="s">
+        <v>50</v>
+      </c>
+      <c r="E105" t="s">
+        <v>83</v>
+      </c>
+      <c r="F105" t="s">
+        <v>27</v>
+      </c>
+      <c r="G105" t="s">
+        <v>19</v>
+      </c>
+      <c r="H105" t="s">
+        <v>18</v>
+      </c>
+      <c r="I105" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="15">
+      <c r="A106" t="s">
+        <v>157</v>
+      </c>
+      <c r="B106" t="s">
+        <v>54</v>
+      </c>
+      <c r="C106" t="s">
+        <v>101</v>
+      </c>
+      <c r="D106" t="s">
+        <v>158</v>
+      </c>
+      <c r="E106" t="s">
+        <v>41</v>
+      </c>
+      <c r="F106" t="s">
+        <v>159</v>
+      </c>
+      <c r="G106" t="s">
+        <v>103</v>
+      </c>
+      <c r="H106" t="s">
+        <v>18</v>
+      </c>
+      <c r="I106" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="15">
+      <c r="A107" t="s">
+        <v>157</v>
+      </c>
+      <c r="B107" t="s">
+        <v>54</v>
+      </c>
+      <c r="C107" t="s">
+        <v>56</v>
+      </c>
+      <c r="D107" t="s">
+        <v>143</v>
+      </c>
+      <c r="E107" t="s">
+        <v>85</v>
+      </c>
+      <c r="F107" t="s">
+        <v>109</v>
+      </c>
+      <c r="G107" t="s">
+        <v>32</v>
+      </c>
+      <c r="H107" t="s">
+        <v>18</v>
+      </c>
+      <c r="I107" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15">
+      <c r="A108" t="s">
+        <v>157</v>
+      </c>
+      <c r="B108" t="s">
+        <v>54</v>
+      </c>
+      <c r="C108" t="s">
+        <v>24</v>
+      </c>
+      <c r="D108" t="s">
+        <v>50</v>
+      </c>
+      <c r="E108" t="s">
+        <v>83</v>
+      </c>
+      <c r="F108" t="s">
+        <v>27</v>
+      </c>
+      <c r="G108" t="s">
+        <v>19</v>
+      </c>
+      <c r="H108" t="s">
+        <v>18</v>
+      </c>
+      <c r="I108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15">
+      <c r="A109" t="s">
+        <v>157</v>
+      </c>
+      <c r="B109" t="s">
+        <v>61</v>
+      </c>
+      <c r="C109" t="s">
+        <v>112</v>
+      </c>
+      <c r="D109" t="s">
+        <v>113</v>
+      </c>
+      <c r="E109" t="s">
         <v>148</v>
       </c>
-      <c r="E97" t="s">
-        <v>29</v>
-      </c>
-      <c r="F97" t="s">
+      <c r="F109" t="s">
+        <v>162</v>
+      </c>
+      <c r="G109" t="s">
+        <v>163</v>
+      </c>
+      <c r="H109" t="s">
+        <v>18</v>
+      </c>
+      <c r="I109" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="15">
+      <c r="A110" t="s">
+        <v>157</v>
+      </c>
+      <c r="B110" t="s">
+        <v>61</v>
+      </c>
+      <c r="C110" t="s">
+        <v>101</v>
+      </c>
+      <c r="D110" t="s">
+        <v>158</v>
+      </c>
+      <c r="E110" t="s">
+        <v>41</v>
+      </c>
+      <c r="F110" t="s">
+        <v>159</v>
+      </c>
+      <c r="G110" t="s">
+        <v>84</v>
+      </c>
+      <c r="H110" t="s">
+        <v>164</v>
+      </c>
+      <c r="I110" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="15">
+      <c r="A111" t="s">
+        <v>157</v>
+      </c>
+      <c r="B111" t="s">
+        <v>61</v>
+      </c>
+      <c r="C111" t="s">
+        <v>56</v>
+      </c>
+      <c r="D111" t="s">
+        <v>145</v>
+      </c>
+      <c r="E111" t="s">
+        <v>37</v>
+      </c>
+      <c r="F111" t="s">
+        <v>16</v>
+      </c>
+      <c r="G111" t="s">
+        <v>77</v>
+      </c>
+      <c r="H111" t="s">
+        <v>18</v>
+      </c>
+      <c r="I111" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="15">
+      <c r="A112" t="s">
+        <v>157</v>
+      </c>
+      <c r="B112" t="s">
+        <v>61</v>
+      </c>
+      <c r="C112" t="s">
+        <v>24</v>
+      </c>
+      <c r="D112" t="s">
+        <v>50</v>
+      </c>
+      <c r="E112" t="s">
+        <v>83</v>
+      </c>
+      <c r="F112" t="s">
+        <v>27</v>
+      </c>
+      <c r="G112" t="s">
+        <v>19</v>
+      </c>
+      <c r="H112" t="s">
+        <v>18</v>
+      </c>
+      <c r="I112" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="15">
+      <c r="A113" t="s">
+        <v>157</v>
+      </c>
+      <c r="B113" t="s">
+        <v>69</v>
+      </c>
+      <c r="C113" t="s">
+        <v>112</v>
+      </c>
+      <c r="D113" t="s">
+        <v>165</v>
+      </c>
+      <c r="E113" t="s">
+        <v>74</v>
+      </c>
+      <c r="F113" t="s">
+        <v>31</v>
+      </c>
+      <c r="G113" t="s">
+        <v>75</v>
+      </c>
+      <c r="H113" t="s">
+        <v>18</v>
+      </c>
+      <c r="I113" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="15">
+      <c r="A114" t="s">
+        <v>157</v>
+      </c>
+      <c r="B114" t="s">
+        <v>69</v>
+      </c>
+      <c r="C114" t="s">
+        <v>32</v>
+      </c>
+      <c r="D114" t="s">
+        <v>107</v>
+      </c>
+      <c r="E114" t="s">
+        <v>85</v>
+      </c>
+      <c r="F114" t="s">
+        <v>31</v>
+      </c>
+      <c r="G114" t="s">
+        <v>142</v>
+      </c>
+      <c r="H114" t="s">
+        <v>18</v>
+      </c>
+      <c r="I114" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="15">
+      <c r="A115" t="s">
+        <v>157</v>
+      </c>
+      <c r="B115" t="s">
+        <v>69</v>
+      </c>
+      <c r="C115" t="s">
+        <v>56</v>
+      </c>
+      <c r="D115" t="s">
         <v>144</v>
       </c>
-      <c r="G97" t="s">
-        <v>152</v>
-      </c>
-      <c r="H97" t="s">
-        <v>18</v>
-      </c>
-      <c r="I97" t="s">
-        <v>25</v>
+      <c r="E115" t="s">
+        <v>85</v>
+      </c>
+      <c r="F115" t="s">
+        <v>86</v>
+      </c>
+      <c r="G115" t="s">
+        <v>155</v>
+      </c>
+      <c r="H115" t="s">
+        <v>18</v>
+      </c>
+      <c r="I115" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="15">
+      <c r="A116" t="s">
+        <v>157</v>
+      </c>
+      <c r="B116" t="s">
+        <v>69</v>
+      </c>
+      <c r="C116" t="s">
+        <v>24</v>
+      </c>
+      <c r="D116" t="s">
+        <v>50</v>
+      </c>
+      <c r="E116" t="s">
+        <v>83</v>
+      </c>
+      <c r="F116" t="s">
+        <v>27</v>
+      </c>
+      <c r="G116" t="s">
+        <v>19</v>
+      </c>
+      <c r="H116" t="s">
+        <v>18</v>
+      </c>
+      <c r="I116" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="15">
+      <c r="A117" t="s">
+        <v>157</v>
+      </c>
+      <c r="B117" t="s">
+        <v>78</v>
+      </c>
+      <c r="C117" t="s">
+        <v>112</v>
+      </c>
+      <c r="D117" t="s">
+        <v>143</v>
+      </c>
+      <c r="E117" t="s">
+        <v>22</v>
+      </c>
+      <c r="F117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G117" t="s">
+        <v>114</v>
+      </c>
+      <c r="H117" t="s">
+        <v>18</v>
+      </c>
+      <c r="I117" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="15">
+      <c r="A118" t="s">
+        <v>157</v>
+      </c>
+      <c r="B118" t="s">
+        <v>78</v>
+      </c>
+      <c r="C118" t="s">
+        <v>32</v>
+      </c>
+      <c r="D118" t="s">
+        <v>107</v>
+      </c>
+      <c r="E118" t="s">
+        <v>85</v>
+      </c>
+      <c r="F118" t="s">
+        <v>31</v>
+      </c>
+      <c r="G118" t="s">
+        <v>142</v>
+      </c>
+      <c r="H118" t="s">
+        <v>18</v>
+      </c>
+      <c r="I118" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="15">
+      <c r="A119" t="s">
+        <v>157</v>
+      </c>
+      <c r="B119" t="s">
+        <v>78</v>
+      </c>
+      <c r="C119" t="s">
+        <v>56</v>
+      </c>
+      <c r="D119" t="s">
+        <v>144</v>
+      </c>
+      <c r="E119" t="s">
+        <v>85</v>
+      </c>
+      <c r="F119" t="s">
+        <v>59</v>
+      </c>
+      <c r="G119" t="s">
+        <v>88</v>
+      </c>
+      <c r="H119" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="15">
+      <c r="A120" t="s">
+        <v>157</v>
+      </c>
+      <c r="B120" t="s">
+        <v>87</v>
+      </c>
+      <c r="C120" t="s">
+        <v>56</v>
+      </c>
+      <c r="D120" t="s">
+        <v>62</v>
+      </c>
+      <c r="E120" t="s">
+        <v>74</v>
+      </c>
+      <c r="F120" t="s">
+        <v>166</v>
+      </c>
+      <c r="G120" t="s">
+        <v>75</v>
+      </c>
+      <c r="H120" t="s">
+        <v>18</v>
+      </c>
+      <c r="I120" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="15">
+      <c r="A121" t="s">
+        <v>157</v>
+      </c>
+      <c r="B121" t="s">
+        <v>87</v>
+      </c>
+      <c r="C121" t="s">
+        <v>133</v>
+      </c>
+      <c r="D121" t="s">
+        <v>134</v>
+      </c>
+      <c r="E121" t="s">
+        <v>135</v>
+      </c>
+      <c r="F121" t="s">
+        <v>16</v>
+      </c>
+      <c r="G121" t="s">
+        <v>136</v>
+      </c>
+      <c r="H121" t="s">
+        <v>18</v>
+      </c>
+      <c r="I121" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="15">
+      <c r="A122" t="s">
+        <v>157</v>
+      </c>
+      <c r="B122" t="s">
+        <v>87</v>
+      </c>
+      <c r="C122" t="s">
+        <v>167</v>
+      </c>
+      <c r="D122" t="s">
+        <v>165</v>
+      </c>
+      <c r="E122" t="s">
+        <v>37</v>
+      </c>
+      <c r="F122" t="s">
+        <v>162</v>
+      </c>
+      <c r="G122" t="s">
+        <v>168</v>
+      </c>
+      <c r="H122" t="s">
+        <v>18</v>
+      </c>
+      <c r="I122" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="15">
+      <c r="A123" t="s">
+        <v>157</v>
+      </c>
+      <c r="B123" t="s">
+        <v>90</v>
+      </c>
+      <c r="C123" t="s">
+        <v>56</v>
+      </c>
+      <c r="D123" t="s">
+        <v>107</v>
+      </c>
+      <c r="E123" t="s">
+        <v>123</v>
+      </c>
+      <c r="F123" t="s">
+        <v>109</v>
+      </c>
+      <c r="G123" t="s">
+        <v>155</v>
+      </c>
+      <c r="H123" t="s">
+        <v>18</v>
+      </c>
+      <c r="I123" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="15">
+      <c r="A124" t="s">
+        <v>157</v>
+      </c>
+      <c r="B124" t="s">
+        <v>90</v>
+      </c>
+      <c r="C124" t="s">
+        <v>167</v>
+      </c>
+      <c r="D124" t="s">
+        <v>165</v>
+      </c>
+      <c r="E124" t="s">
+        <v>37</v>
+      </c>
+      <c r="F124" t="s">
+        <v>162</v>
+      </c>
+      <c r="G124" t="s">
+        <v>168</v>
+      </c>
+      <c r="H124" t="s">
+        <v>18</v>
+      </c>
+      <c r="I124" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -3806,15 +4675,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{432383d8-600b-4d77-b2c3-fb369b96a4a1}">
-  <dimension ref="A1:I2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1e37f954-a39a-4406-ac35-ef1584479636}">
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="14.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="41.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="12.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="17.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="48" customWidth="1"/>
+    <col min="5" max="5" width="39.2857142857143" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="11.4285714285714" customWidth="1"/>
     <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
@@ -3826,16 +4695,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -3855,16 +4724,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -3876,6 +4745,35 @@
         <v>18</v>
       </c>
       <c r="I2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3884,4 +4782,124 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2e361ee8-034d-417b-98cc-64181eaece0e}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="17.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="56.25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" t="s">
+        <v>187</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
 </file>
--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="209">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -189,6 +189,18 @@
     <t>4, 10:35-11:20</t>
   </si>
   <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
+    <t>1TFB|JA1</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Biezmienow Małgorzata</t>
+  </si>
+  <si>
     <t>2FA</t>
   </si>
   <si>
@@ -210,6 +222,18 @@
     <t>5, 11:25-12:10</t>
   </si>
   <si>
+    <t>3TFA|JA1</t>
+  </si>
+  <si>
+    <t>Informatyka</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Najwer Maciej</t>
+  </si>
+  <si>
     <t>2FC</t>
   </si>
   <si>
@@ -273,6 +297,18 @@
     <t>Socha Dariusz</t>
   </si>
   <si>
+    <t>3WA|JN1</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Misiąg Anna</t>
+  </si>
+  <si>
     <t>Technologie produkcji cukierniczej</t>
   </si>
   <si>
@@ -297,6 +333,9 @@
     <t>9, 14:55-15:40</t>
   </si>
   <si>
+    <t>3TH|JA2</t>
+  </si>
+  <si>
     <t>1TH|JA2</t>
   </si>
   <si>
@@ -339,9 +378,6 @@
     <t>29</t>
   </si>
   <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
     <t>1WB</t>
   </si>
   <si>
@@ -429,12 +465,6 @@
     <t>1WA|JN2</t>
   </si>
   <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>Fiodorów Małgorzata</t>
-  </si>
-  <si>
     <t>12.03.2026</t>
   </si>
   <si>
@@ -543,6 +573,15 @@
     <t>Opis zajęć</t>
   </si>
   <si>
+    <t>12:25-13:10</t>
+  </si>
+  <si>
+    <t>Krystian Pietrowski - 3M - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>j. niemiecki</t>
+  </si>
+  <si>
     <t>15:45-16:30</t>
   </si>
   <si>
@@ -561,6 +600,18 @@
     <t>matematyka</t>
   </si>
   <si>
+    <t>18:10-18:55</t>
+  </si>
+  <si>
+    <t>Karolina Tymon - 5TH - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>19:00-19:45</t>
+  </si>
+  <si>
+    <t>19:45-20:30</t>
+  </si>
+  <si>
     <t>Miejsce dyżuru</t>
   </si>
   <si>
@@ -582,10 +633,22 @@
     <t>Nowak Magdalena</t>
   </si>
   <si>
+    <t>11:20-11:25</t>
+  </si>
+  <si>
+    <t>parter</t>
+  </si>
+  <si>
     <t>14:50-14:55</t>
   </si>
   <si>
     <t>Cieśla Marcin</t>
+  </si>
+  <si>
+    <t>15:40-15:45</t>
+  </si>
+  <si>
+    <t>Nowaczyk Agnieszka</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1098,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2202cc6c-42e8-4ad5-abd5-4b49e5f5fee0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ab05081f-2d18-478c-a392-b58f0952ae30}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1056,8 +1119,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d84e4575-df5c-4400-ac4c-f114c974903c}">
-  <dimension ref="A1:I124"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f7970a09-1b40-4050-aed5-53266657f16b}">
+  <dimension ref="A1:I129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1514,25 +1577,25 @@
         <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -1543,16 +1606,16 @@
         <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G17" t="s">
         <v>17</v>
@@ -1572,16 +1635,16 @@
         <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="G18" t="s">
         <v>17</v>
@@ -1601,25 +1664,25 @@
         <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G19" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -1627,28 +1690,28 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="E20" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" t="s">
         <v>64</v>
       </c>
-      <c r="G20" t="s">
-        <v>65</v>
-      </c>
       <c r="H20" t="s">
         <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -1656,22 +1719,22 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H21" t="s">
         <v>18</v>
@@ -1685,28 +1748,28 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G22" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="H22" t="s">
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
@@ -1714,22 +1777,22 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="s">
         <v>61</v>
       </c>
-      <c r="C23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" t="s">
-        <v>68</v>
-      </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="H23" t="s">
         <v>18</v>
@@ -1743,22 +1806,22 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H24" t="s">
         <v>18</v>
@@ -1772,16 +1835,16 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="E25" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s">
         <v>31</v>
@@ -1801,22 +1864,22 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="F26" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
@@ -1830,22 +1893,22 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
@@ -1859,22 +1922,22 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F28" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
@@ -1888,22 +1951,22 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="E29" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F29" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s">
         <v>18</v>
@@ -1917,28 +1980,28 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E30" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
@@ -1946,22 +2009,22 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="F31" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
@@ -1975,28 +2038,28 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="E32" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="F32" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
@@ -2004,28 +2067,28 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" t="s">
         <v>78</v>
       </c>
-      <c r="C33" t="s">
-        <v>56</v>
-      </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="G33" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
@@ -2033,28 +2096,28 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" t="s">
         <v>70</v>
       </c>
-      <c r="D34" t="s">
-        <v>25</v>
-      </c>
       <c r="E34" t="s">
+        <v>82</v>
+      </c>
+      <c r="F34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" t="s">
         <v>83</v>
       </c>
-      <c r="F34" t="s">
-        <v>52</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
-      </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
@@ -2062,22 +2125,22 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E35" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="H35" t="s">
         <v>18</v>
@@ -2091,193 +2154,193 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="F36" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="D37" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="E37" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F37" t="s">
         <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
         <v>95</v>
       </c>
-      <c r="E38" t="s">
-        <v>96</v>
-      </c>
       <c r="F38" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="G38" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="E39" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F39" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="G39" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" t="s">
         <v>92</v>
       </c>
-      <c r="B40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" t="s">
-        <v>94</v>
-      </c>
-      <c r="D40" t="s">
-        <v>99</v>
-      </c>
-      <c r="E40" t="s">
-        <v>96</v>
-      </c>
       <c r="F40" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="D41" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" t="s">
+        <v>89</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
       </c>
-      <c r="E41" t="s">
-        <v>96</v>
-      </c>
-      <c r="F41" t="s">
-        <v>97</v>
-      </c>
-      <c r="G41" t="s">
-        <v>53</v>
-      </c>
       <c r="H41" t="s">
         <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="E42" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F42" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="G42" t="s">
         <v>17</v>
@@ -2291,138 +2354,138 @@
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="D43" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E43" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="F43" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D44" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="E44" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="F44" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="G44" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="D45" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E45" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="F45" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="G45" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D46" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="E46" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="F46" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="G46" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C47" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="E47" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="F47" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="G47" t="s">
         <v>17</v>
@@ -2436,141 +2499,141 @@
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D48" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="E48" t="s">
         <v>38</v>
       </c>
       <c r="F48" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="G48" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B49" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D49" t="s">
         <v>25</v>
       </c>
       <c r="E49" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F49" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="G49" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="C50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D50" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E50" t="s">
+        <v>97</v>
+      </c>
+      <c r="F50" t="s">
         <v>63</v>
       </c>
-      <c r="F50" t="s">
-        <v>64</v>
-      </c>
       <c r="G50" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B51" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="D51" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="E51" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="F51" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="G51" t="s">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D52" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E52" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="F52" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="G52" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
@@ -2581,25 +2644,25 @@
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B53" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="C53" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D53" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="E53" t="s">
         <v>38</v>
       </c>
       <c r="F53" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="G53" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
@@ -2610,83 +2673,83 @@
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="D54" t="s">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="E54" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F54" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="G54" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D55" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E55" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="F55" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="G55" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B56" t="s">
+        <v>99</v>
+      </c>
+      <c r="C56" t="s">
+        <v>60</v>
+      </c>
+      <c r="D56" t="s">
         <v>119</v>
       </c>
-      <c r="C56" t="s">
-        <v>112</v>
-      </c>
-      <c r="D56" t="s">
-        <v>117</v>
-      </c>
       <c r="E56" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F56" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="G56" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
@@ -2697,54 +2760,54 @@
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E57" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="F57" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="G57" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B58" t="s">
+        <v>102</v>
+      </c>
+      <c r="C58" t="s">
+        <v>124</v>
+      </c>
+      <c r="D58" t="s">
+        <v>125</v>
+      </c>
+      <c r="E58" t="s">
+        <v>38</v>
+      </c>
+      <c r="F58" t="s">
         <v>121</v>
       </c>
-      <c r="C58" t="s">
-        <v>112</v>
-      </c>
-      <c r="D58" t="s">
-        <v>117</v>
-      </c>
-      <c r="E58" t="s">
-        <v>118</v>
-      </c>
-      <c r="F58" t="s">
-        <v>31</v>
-      </c>
       <c r="G58" t="s">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
@@ -2755,25 +2818,25 @@
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="C59" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="E59" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F59" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G59" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
@@ -2784,112 +2847,112 @@
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="D60" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E60" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="F60" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="G60" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="C61" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="D61" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E61" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="F61" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="G61" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="C62" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="D62" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E62" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="F62" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="G62" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="C63" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="D63" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E63" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="F63" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="G63" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
@@ -2900,141 +2963,141 @@
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="D64" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="E64" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="F64" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="G64" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="D65" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="E65" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="F65" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="G65" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B66" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D66" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E66" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="F66" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="G66" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="D67" t="s">
-        <v>57</v>
+        <v>138</v>
       </c>
       <c r="E67" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F67" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="G67" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B68" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D68" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E68" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="F68" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="G68" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
@@ -3045,25 +3108,25 @@
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B69" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C69" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D69" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E69" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F69" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="G69" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
@@ -3074,25 +3137,25 @@
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C70" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="D70" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="E70" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F70" t="s">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="G70" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
@@ -3103,25 +3166,25 @@
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B71" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="C71" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D71" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E71" t="s">
-        <v>135</v>
+        <v>41</v>
       </c>
       <c r="F71" t="s">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="G71" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
@@ -3132,25 +3195,25 @@
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B72" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C72" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="D72" t="s">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="E72" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F72" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="G72" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
@@ -3161,193 +3224,193 @@
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C73" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="D73" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E73" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F73" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="G73" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B74" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C74" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="D74" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E74" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="F74" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G74" t="s">
-        <v>19</v>
+        <v>143</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B75" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C75" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E75" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F75" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="G75" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B76" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D76" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E76" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F76" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G76" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B77" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="C77" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="D77" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E77" t="s">
         <v>41</v>
       </c>
       <c r="F77" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="G77" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D78" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E78" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="F78" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="G78" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B79" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
       </c>
       <c r="D79" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E79" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F79" t="s">
         <v>27</v>
@@ -3364,25 +3427,25 @@
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B80" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C80" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="D80" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E80" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="F80" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="G80" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
@@ -3393,54 +3456,54 @@
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B81" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C81" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D81" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E81" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F81" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="G81" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B82" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="D82" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E82" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="F82" t="s">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="G82" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
@@ -3451,83 +3514,83 @@
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B83" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C83" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="D83" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="E83" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="F83" t="s">
-        <v>129</v>
+        <v>31</v>
       </c>
       <c r="G83" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B84" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C84" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D84" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E84" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F84" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="G84" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B85" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C85" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="D85" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E85" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F85" t="s">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="G85" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
@@ -3538,54 +3601,54 @@
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B86" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D86" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E86" t="s">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="F86" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="G86" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B87" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C87" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="D87" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E87" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="F87" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="G87" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
@@ -3596,25 +3659,25 @@
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="C88" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="D88" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E88" t="s">
-        <v>148</v>
+        <v>41</v>
       </c>
       <c r="F88" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="G88" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
@@ -3625,25 +3688,25 @@
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C89" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="D89" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="E89" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="F89" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="G89" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
@@ -3654,112 +3717,112 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="C90" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="D90" t="s">
         <v>149</v>
       </c>
       <c r="E90" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F90" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="G90" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C91" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="D91" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E91" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F91" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="G91" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B92" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C92" t="s">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="D92" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="E92" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F92" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="G92" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B93" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C93" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="D93" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E93" t="s">
-        <v>46</v>
+        <v>158</v>
       </c>
       <c r="F93" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="G93" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
@@ -3770,25 +3833,25 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B94" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D94" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E94" t="s">
-        <v>154</v>
+        <v>41</v>
       </c>
       <c r="F94" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="G94" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
@@ -3799,83 +3862,83 @@
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B95" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C95" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="D95" t="s">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="E95" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F95" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="G95" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B96" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="C96" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="D96" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E96" t="s">
         <v>46</v>
       </c>
       <c r="F96" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="G96" t="s">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B97" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="C97" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D97" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E97" t="s">
-        <v>154</v>
+        <v>41</v>
       </c>
       <c r="F97" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="G97" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
@@ -3886,54 +3949,54 @@
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B98" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C98" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="D98" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="E98" t="s">
-        <v>154</v>
+        <v>46</v>
       </c>
       <c r="F98" t="s">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="G98" t="s">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B99" t="s">
+        <v>127</v>
+      </c>
+      <c r="C99" t="s">
+        <v>124</v>
+      </c>
+      <c r="D99" t="s">
+        <v>129</v>
+      </c>
+      <c r="E99" t="s">
+        <v>164</v>
+      </c>
+      <c r="F99" t="s">
         <v>121</v>
       </c>
-      <c r="C99" t="s">
-        <v>112</v>
-      </c>
-      <c r="D99" t="s">
-        <v>117</v>
-      </c>
-      <c r="E99" t="s">
-        <v>154</v>
-      </c>
-      <c r="F99" t="s">
-        <v>109</v>
-      </c>
       <c r="G99" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
@@ -3944,54 +4007,54 @@
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="C100" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E100" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F100" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="G100" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B101" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="C101" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="D101" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="E101" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F101" t="s">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="G101" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
@@ -4002,25 +4065,25 @@
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B102" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="C102" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="D102" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="E102" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="F102" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="G102" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
@@ -4031,25 +4094,25 @@
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B103" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="C103" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="D103" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E103" t="s">
-        <v>15</v>
+        <v>164</v>
       </c>
       <c r="F103" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="G103" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
@@ -4060,51 +4123,51 @@
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B104" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="C104" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="D104" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="E104" t="s">
-        <v>15</v>
+        <v>164</v>
       </c>
       <c r="F104" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="G104" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H104" t="s">
         <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B105" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
       </c>
       <c r="D105" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="E105" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="F105" t="s">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="G105" t="s">
         <v>19</v>
@@ -4118,54 +4181,54 @@
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B106" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C106" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="D106" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E106" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F106" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="G106" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="H106" t="s">
         <v>18</v>
       </c>
       <c r="I106" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B107" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C107" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="E107" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="F107" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="G107" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
@@ -4176,86 +4239,86 @@
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B108" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C108" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D108" t="s">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="E108" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="F108" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="G108" t="s">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
       </c>
       <c r="I108" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B109" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C109" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D109" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
       <c r="E109" t="s">
-        <v>148</v>
+        <v>15</v>
       </c>
       <c r="F109" t="s">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="G109" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
       </c>
       <c r="I109" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B110" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C110" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="D110" t="s">
-        <v>158</v>
+        <v>50</v>
       </c>
       <c r="E110" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="F110" t="s">
-        <v>159</v>
+        <v>27</v>
       </c>
       <c r="G110" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="H110" t="s">
-        <v>164</v>
+        <v>18</v>
       </c>
       <c r="I110" t="s">
         <v>19</v>
@@ -4263,25 +4326,25 @@
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B111" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C111" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="D111" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="E111" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F111" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
       <c r="G111" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
@@ -4292,228 +4355,228 @@
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B112" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C112" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D112" t="s">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="E112" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="F112" t="s">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="G112" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B113" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C113" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="D113" t="s">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="E113" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="F113" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G113" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B114" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C114" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="D114" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="E114" t="s">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="F114" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="G114" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="H114" t="s">
         <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B115" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C115" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="E115" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="F115" t="s">
-        <v>86</v>
+        <v>169</v>
       </c>
       <c r="G115" t="s">
-        <v>155</v>
+        <v>96</v>
       </c>
       <c r="H115" t="s">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="I115" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B116" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C116" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D116" t="s">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="E116" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="F116" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G116" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B117" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C117" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="D117" t="s">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="E117" t="s">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="F117" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="G117" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B118" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C118" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="D118" t="s">
-        <v>107</v>
+        <v>175</v>
       </c>
       <c r="E118" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F118" t="s">
         <v>31</v>
       </c>
       <c r="G118" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B119" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C119" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D119" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="E119" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F119" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="G119" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
@@ -4524,25 +4587,25 @@
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B120" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C120" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D120" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="E120" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="F120" t="s">
-        <v>166</v>
+        <v>98</v>
       </c>
       <c r="G120" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
@@ -4553,54 +4616,54 @@
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B121" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C121" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="D121" t="s">
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="E121" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="F121" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G121" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B122" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C122" t="s">
-        <v>167</v>
+        <v>124</v>
       </c>
       <c r="D122" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E122" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F122" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="G122" t="s">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
@@ -4611,59 +4674,204 @@
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B123" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C123" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D123" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E123" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="F123" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="G123" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B124" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C124" t="s">
+        <v>60</v>
+      </c>
+      <c r="D124" t="s">
+        <v>154</v>
+      </c>
+      <c r="E124" t="s">
+        <v>97</v>
+      </c>
+      <c r="F124" t="s">
+        <v>63</v>
+      </c>
+      <c r="G124" t="s">
+        <v>100</v>
+      </c>
+      <c r="H124" t="s">
+        <v>18</v>
+      </c>
+      <c r="I124" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="15">
+      <c r="A125" t="s">
         <v>167</v>
       </c>
-      <c r="D124" t="s">
+      <c r="B125" t="s">
+        <v>99</v>
+      </c>
+      <c r="C125" t="s">
+        <v>60</v>
+      </c>
+      <c r="D125" t="s">
+        <v>70</v>
+      </c>
+      <c r="E125" t="s">
+        <v>82</v>
+      </c>
+      <c r="F125" t="s">
+        <v>176</v>
+      </c>
+      <c r="G125" t="s">
+        <v>83</v>
+      </c>
+      <c r="H125" t="s">
+        <v>18</v>
+      </c>
+      <c r="I125" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="15">
+      <c r="A126" t="s">
+        <v>167</v>
+      </c>
+      <c r="B126" t="s">
+        <v>99</v>
+      </c>
+      <c r="C126" t="s">
+        <v>145</v>
+      </c>
+      <c r="D126" t="s">
+        <v>146</v>
+      </c>
+      <c r="E126" t="s">
+        <v>92</v>
+      </c>
+      <c r="F126" t="s">
+        <v>16</v>
+      </c>
+      <c r="G126" t="s">
+        <v>55</v>
+      </c>
+      <c r="H126" t="s">
+        <v>18</v>
+      </c>
+      <c r="I126" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="15">
+      <c r="A127" t="s">
+        <v>167</v>
+      </c>
+      <c r="B127" t="s">
+        <v>99</v>
+      </c>
+      <c r="C127" t="s">
+        <v>177</v>
+      </c>
+      <c r="D127" t="s">
+        <v>175</v>
+      </c>
+      <c r="E127" t="s">
+        <v>37</v>
+      </c>
+      <c r="F127" t="s">
+        <v>172</v>
+      </c>
+      <c r="G127" t="s">
+        <v>178</v>
+      </c>
+      <c r="H127" t="s">
+        <v>18</v>
+      </c>
+      <c r="I127" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="15">
+      <c r="A128" t="s">
+        <v>167</v>
+      </c>
+      <c r="B128" t="s">
+        <v>102</v>
+      </c>
+      <c r="C128" t="s">
+        <v>60</v>
+      </c>
+      <c r="D128" t="s">
+        <v>119</v>
+      </c>
+      <c r="E128" t="s">
+        <v>135</v>
+      </c>
+      <c r="F128" t="s">
+        <v>121</v>
+      </c>
+      <c r="G128" t="s">
         <v>165</v>
       </c>
-      <c r="E124" t="s">
+      <c r="H128" t="s">
+        <v>18</v>
+      </c>
+      <c r="I128" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="15">
+      <c r="A129" t="s">
+        <v>167</v>
+      </c>
+      <c r="B129" t="s">
+        <v>102</v>
+      </c>
+      <c r="C129" t="s">
+        <v>177</v>
+      </c>
+      <c r="D129" t="s">
+        <v>175</v>
+      </c>
+      <c r="E129" t="s">
         <v>37</v>
       </c>
-      <c r="F124" t="s">
-        <v>162</v>
-      </c>
-      <c r="G124" t="s">
-        <v>168</v>
-      </c>
-      <c r="H124" t="s">
-        <v>18</v>
-      </c>
-      <c r="I124" t="s">
+      <c r="F129" t="s">
+        <v>172</v>
+      </c>
+      <c r="G129" t="s">
+        <v>178</v>
+      </c>
+      <c r="H129" t="s">
+        <v>18</v>
+      </c>
+      <c r="I129" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4675,13 +4883,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1e37f954-a39a-4406-ac35-ef1584479636}">
-  <dimension ref="A1:I3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{36702926-9152-4f76-a399-d19776b18095}">
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="17.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="19.8571428571429" customWidth="1"/>
     <col min="4" max="4" width="48" customWidth="1"/>
     <col min="5" max="5" width="39.2857142857143" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
@@ -4695,16 +4903,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -4724,16 +4932,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="E2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -4753,27 +4961,143 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" t="s">
         <v>35</v>
       </c>
-      <c r="D3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="D4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4785,13 +5109,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2e361ee8-034d-417b-98cc-64181eaece0e}">
-  <dimension ref="A1:F5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ec179b83-01b8-4521-9935-3e0b80d71950}">
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="17.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="19.8571428571429" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
@@ -4802,13 +5126,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -4822,16 +5146,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -4842,16 +5166,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -4862,16 +5186,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -4882,18 +5206,58 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" t="s">
-        <v>187</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="D6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E7" t="s">
+        <v>208</v>
+      </c>
+      <c r="F7" t="s">
         <v>18</v>
       </c>
     </row>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2033" uniqueCount="247">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -243,136 +243,193 @@
     <t>bib</t>
   </si>
   <si>
+    <t>Zając Ewa</t>
+  </si>
+  <si>
+    <t>Antoszewska Joanna</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>6, 12:25-13:10</t>
+  </si>
+  <si>
+    <t>Dalach Krystyna</t>
+  </si>
+  <si>
+    <t>1TFB|DZ</t>
+  </si>
+  <si>
+    <t>Kończyńska Małgorzata</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Derezińska Katarzyna</t>
+  </si>
+  <si>
+    <t>Biologia</t>
+  </si>
+  <si>
+    <t>Sałdyka Karolina</t>
+  </si>
+  <si>
+    <t>Filipiak Wiesław</t>
+  </si>
+  <si>
+    <t>7, 13:15-14:00</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>3TFB</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - matematyka w działalności gospodarczej</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Socha Dariusz</t>
+  </si>
+  <si>
+    <t>3WA|JN1</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Misiąg Anna</t>
+  </si>
+  <si>
+    <t>Technologie produkcji cukierniczej</t>
+  </si>
+  <si>
+    <t>Zastępstwo</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>8, 14:05-14:50</t>
+  </si>
+  <si>
+    <t>aq1</t>
+  </si>
+  <si>
+    <t>Uczniowie zwolnieni do domu</t>
+  </si>
+  <si>
+    <t>Leńczowska Iwona</t>
+  </si>
+  <si>
+    <t>9, 14:55-15:40</t>
+  </si>
+  <si>
+    <t>3TH|JA2</t>
+  </si>
+  <si>
+    <t>1TH|JA2</t>
+  </si>
+  <si>
+    <t>10.03.2026</t>
+  </si>
+  <si>
+    <t>1TH|JA1</t>
+  </si>
+  <si>
+    <t>Jaworska Edyta</t>
+  </si>
+  <si>
+    <t>2TFB</t>
+  </si>
+  <si>
+    <t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Jastrzębska-Majtyka Agnieszka</t>
+  </si>
+  <si>
+    <t>Wakat3 edukacja zdrow.</t>
+  </si>
+  <si>
+    <t>3CA|edu</t>
+  </si>
+  <si>
+    <t>Edukacja zdrowotna</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>3FA|edu</t>
+  </si>
+  <si>
+    <t>3M|edu</t>
+  </si>
+  <si>
+    <t>3TFA|edu</t>
+  </si>
+  <si>
+    <t>3FA|dz2</t>
+  </si>
+  <si>
+    <t>sg2</t>
+  </si>
+  <si>
+    <t>Rejno Julita</t>
+  </si>
+  <si>
+    <t>3FB</t>
+  </si>
+  <si>
+    <t>3M|JN1</t>
+  </si>
+  <si>
     <t>Nowak Damiana</t>
   </si>
   <si>
-    <t>Antoszewska Joanna</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>3M</t>
-  </si>
-  <si>
-    <t>6, 12:25-13:10</t>
-  </si>
-  <si>
-    <t>Kończyńska Małgorzata</t>
-  </si>
-  <si>
-    <t>Język polski</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>Derezińska Katarzyna</t>
-  </si>
-  <si>
-    <t>Biologia</t>
-  </si>
-  <si>
-    <t>Sałdyka Karolina</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Filipiak Wiesław</t>
-  </si>
-  <si>
-    <t>7, 13:15-14:00</t>
-  </si>
-  <si>
-    <t>3TFB</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - matematyka w działalności gospodarczej</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Socha Dariusz</t>
-  </si>
-  <si>
-    <t>3WA|JN1</t>
-  </si>
-  <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>Misiąg Anna</t>
-  </si>
-  <si>
-    <t>Technologie produkcji cukierniczej</t>
-  </si>
-  <si>
-    <t>Zastępstwo</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>8, 14:05-14:50</t>
-  </si>
-  <si>
-    <t>Uczniowie zwolnieni do domu</t>
-  </si>
-  <si>
-    <t>Leńczowska Iwona</t>
-  </si>
-  <si>
-    <t>9, 14:55-15:40</t>
-  </si>
-  <si>
-    <t>3TH|JA2</t>
-  </si>
-  <si>
-    <t>1TH|JA2</t>
-  </si>
-  <si>
-    <t>10.03.2026</t>
-  </si>
-  <si>
-    <t>1TH|JA1</t>
-  </si>
-  <si>
-    <t>Wakat3 edukacja zdrow.</t>
-  </si>
-  <si>
-    <t>3CA|edu</t>
-  </si>
-  <si>
-    <t>Edukacja zdrowotna</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>3FA|edu</t>
-  </si>
-  <si>
-    <t>3M|edu</t>
-  </si>
-  <si>
-    <t>3TFA|edu</t>
-  </si>
-  <si>
-    <t>Rejno Julita</t>
-  </si>
-  <si>
-    <t>3FB</t>
-  </si>
-  <si>
-    <t>Dalach Krystyna</t>
+    <t>3TFB|JA2</t>
+  </si>
+  <si>
+    <t>Doliński Mirosław</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>Pietrycha Małgorzata</t>
+  </si>
+  <si>
+    <t>1TFB</t>
   </si>
   <si>
     <t>29</t>
@@ -381,7 +438,10 @@
     <t>1WB</t>
   </si>
   <si>
-    <t>2FB</t>
+    <t>1WB|JN1</t>
+  </si>
+  <si>
+    <t>1TFA</t>
   </si>
   <si>
     <t>Edukacja obywatelska</t>
@@ -393,7 +453,19 @@
     <t>Kopij Marcin</t>
   </si>
   <si>
-    <t>1WB|JN1</t>
+    <t>Dalach Sławomir</t>
+  </si>
+  <si>
+    <t>2FB|CH</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Zaleska Magdalena</t>
   </si>
   <si>
     <t>Kruk Marcin</t>
@@ -402,12 +474,12 @@
     <t>1FB</t>
   </si>
   <si>
-    <t>Jastrzębska-Majtyka Agnieszka</t>
-  </si>
-  <si>
     <t>10, 15:45-16:30</t>
   </si>
   <si>
+    <t>1TFA|JA2</t>
+  </si>
+  <si>
     <t>1TFA|JA1</t>
   </si>
   <si>
@@ -429,6 +501,9 @@
     <t>11.03.2026</t>
   </si>
   <si>
+    <t>prf2</t>
+  </si>
+  <si>
     <t>Rozwój kompetencji zawodowych - barber</t>
   </si>
   <si>
@@ -447,7 +522,7 @@
     <t>1FA|JA1</t>
   </si>
   <si>
-    <t>sg2</t>
+    <t>2WA|JN2</t>
   </si>
   <si>
     <t>2K|CH</t>
@@ -456,7 +531,10 @@
     <t>Wojciechowski Łukasz</t>
   </si>
   <si>
-    <t>Pietrycha Małgorzata</t>
+    <t>Skarupa Agnieszka</t>
+  </si>
+  <si>
+    <t>Pracownia sprzedaży</t>
   </si>
   <si>
     <t>Wakat1 j. niemiecki</t>
@@ -465,15 +543,24 @@
     <t>1WA|JN2</t>
   </si>
   <si>
+    <t>1WA|JN1</t>
+  </si>
+  <si>
     <t>12.03.2026</t>
   </si>
   <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
     <t>2WA</t>
   </si>
   <si>
     <t>2CA</t>
   </si>
   <si>
+    <t>1FC</t>
+  </si>
+  <si>
     <t>Wójcik Kamil</t>
   </si>
   <si>
@@ -483,21 +570,18 @@
     <t>Brak</t>
   </si>
   <si>
+    <t>2TFA</t>
+  </si>
+  <si>
     <t>1FA</t>
   </si>
   <si>
-    <t>1TFA</t>
+    <t>42</t>
   </si>
   <si>
     <t>1WA</t>
   </si>
   <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
     <t>Chemia</t>
   </si>
   <si>
@@ -519,21 +603,18 @@
     <t>Zajęcia praktyczne - projektowanie i wykonywanie fryzur</t>
   </si>
   <si>
-    <t>Danielewski Paweł</t>
-  </si>
-  <si>
     <t>1CB|JA1</t>
   </si>
   <si>
     <t>13.03.2026</t>
   </si>
   <si>
+    <t>3TFB|JA1</t>
+  </si>
+  <si>
     <t>5TH</t>
   </si>
   <si>
-    <t>aq1</t>
-  </si>
-  <si>
     <t>Płatek Krzysztof</t>
   </si>
   <si>
@@ -612,6 +693,21 @@
     <t>19:45-20:30</t>
   </si>
   <si>
+    <t>j. niemiecki zawodowy</t>
+  </si>
+  <si>
+    <t>19:00-20:30</t>
+  </si>
+  <si>
+    <t>12:25-15:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kornelia Gałązka -  klasa 4TFB - indywidualne nauczanie </t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur- cztery godziny co piatek od 20.02.2026r.</t>
+  </si>
+  <si>
     <t>Miejsce dyżuru</t>
   </si>
   <si>
@@ -639,6 +735,9 @@
     <t>parter</t>
   </si>
   <si>
+    <t>12:10-12:25</t>
+  </si>
+  <si>
     <t>14:50-14:55</t>
   </si>
   <si>
@@ -649,6 +748,21 @@
   </si>
   <si>
     <t>Nowaczyk Agnieszka</t>
+  </si>
+  <si>
+    <t>08:45-08:50</t>
+  </si>
+  <si>
+    <t>13:10-13:15</t>
+  </si>
+  <si>
+    <t>14:00-14:05</t>
+  </si>
+  <si>
+    <t>16:30-16:35</t>
+  </si>
+  <si>
+    <t>17:20-17:25</t>
   </si>
 </sst>
 </file>
@@ -1098,7 +1212,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ab05081f-2d18-478c-a392-b58f0952ae30}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bde1abec-610f-491f-acbf-cf4967f4f789}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1119,8 +1233,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f7970a09-1b40-4050-aed5-53266657f16b}">
-  <dimension ref="A1:I129"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5621122c-3426-4648-adec-47fe50f46ad4}">
+  <dimension ref="A1:I196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1870,22 +1984,22 @@
         <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="E26" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F26" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G26" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
@@ -1896,19 +2010,19 @@
         <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="F27" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
@@ -1925,19 +2039,19 @@
         <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="E28" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F28" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G28" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
@@ -1954,19 +2068,19 @@
         <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G29" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H29" t="s">
         <v>18</v>
@@ -1983,16 +2097,16 @@
         <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="G30" t="s">
         <v>85</v>
@@ -2009,22 +2123,22 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" t="s">
         <v>86</v>
-      </c>
-      <c r="C31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" t="s">
-        <v>87</v>
-      </c>
-      <c r="E31" t="s">
-        <v>88</v>
-      </c>
-      <c r="F31" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" t="s">
-        <v>90</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
@@ -2038,28 +2152,28 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>86</v>
       </c>
-      <c r="C32" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" t="s">
-        <v>91</v>
-      </c>
-      <c r="E32" t="s">
-        <v>92</v>
-      </c>
-      <c r="F32" t="s">
-        <v>93</v>
-      </c>
-      <c r="G32" t="s">
-        <v>94</v>
-      </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
@@ -2067,28 +2181,28 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="E33" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
@@ -2096,28 +2210,28 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="G34" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
@@ -2125,28 +2239,28 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E35" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="F35" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G35" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="H35" t="s">
         <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
@@ -2154,22 +2268,22 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E36" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="F36" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
@@ -2183,22 +2297,22 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D37" t="s">
         <v>61</v>
       </c>
       <c r="E37" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G37" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
@@ -2212,28 +2326,28 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" t="s">
         <v>99</v>
       </c>
-      <c r="C38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" t="s">
-        <v>95</v>
-      </c>
       <c r="F38" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
@@ -2241,22 +2355,22 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E39" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
@@ -2270,28 +2384,28 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
         <v>55</v>
       </c>
       <c r="D40" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="E40" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="F40" t="s">
         <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
@@ -2299,22 +2413,22 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="D41" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="E41" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="F41" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H41" t="s">
         <v>18</v>
@@ -2325,402 +2439,402 @@
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D42" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="E42" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G42" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
         <v>105</v>
       </c>
-      <c r="B43" t="s">
-        <v>12</v>
-      </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E43" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F43" t="s">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
         <v>105</v>
       </c>
-      <c r="B44" t="s">
-        <v>12</v>
-      </c>
       <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
         <v>107</v>
       </c>
-      <c r="D44" t="s">
-        <v>111</v>
-      </c>
       <c r="E44" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="F44" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E45" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="F45" t="s">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D46" t="s">
+        <v>111</v>
+      </c>
+      <c r="E46" t="s">
+        <v>112</v>
+      </c>
+      <c r="F46" t="s">
         <v>113</v>
       </c>
-      <c r="E46" t="s">
-        <v>109</v>
-      </c>
-      <c r="F46" t="s">
-        <v>110</v>
-      </c>
       <c r="G46" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="F47" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="G47" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B48" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="D48" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E48" t="s">
-        <v>38</v>
+        <v>117</v>
       </c>
       <c r="F48" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="G48" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="E49" t="s">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="F49" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="G49" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="D50" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E50" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="F50" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="G50" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C51" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="D51" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="E51" t="s">
         <v>41</v>
       </c>
       <c r="F51" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="G51" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D52" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E52" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="F52" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="G52" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B53" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C53" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="D53" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E53" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F53" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G53" t="s">
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B54" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="C54" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="D54" t="s">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="E54" t="s">
         <v>38</v>
       </c>
       <c r="F54" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="G54" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B55" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C55" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D55" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E55" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="F55" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="G55" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
@@ -2731,112 +2845,112 @@
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="C56" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D56" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E56" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="F56" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="G56" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B57" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="D57" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E57" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="F57" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G57" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B58" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C58" t="s">
         <v>124</v>
       </c>
       <c r="D58" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="E58" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F58" t="s">
-        <v>121</v>
+        <v>42</v>
       </c>
       <c r="G58" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B59" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D59" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E59" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="F59" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="G59" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
@@ -2847,83 +2961,83 @@
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B60" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="D60" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E60" t="s">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="F60" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="G60" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B61" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="C61" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="D61" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E61" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="F61" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="G61" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B62" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="C62" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D62" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="E62" t="s">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="F62" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
@@ -2934,25 +3048,25 @@
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B63" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="C63" t="s">
         <v>124</v>
       </c>
       <c r="D63" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" t="s">
+        <v>41</v>
+      </c>
+      <c r="F63" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" t="s">
         <v>129</v>
-      </c>
-      <c r="E63" t="s">
-        <v>130</v>
-      </c>
-      <c r="F63" t="s">
-        <v>31</v>
-      </c>
-      <c r="G63" t="s">
-        <v>32</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
@@ -2963,19 +3077,19 @@
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C64" t="s">
         <v>60</v>
       </c>
       <c r="D64" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="E64" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="F64" t="s">
         <v>63</v>
@@ -2992,112 +3106,112 @@
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B65" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C65" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="D65" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E65" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="F65" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="G65" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B66" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C66" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D66" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="E66" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="F66" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="G66" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="D67" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E67" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="F67" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="G67" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
+        <v>108</v>
+      </c>
+      <c r="B68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C68" t="s">
+        <v>60</v>
+      </c>
+      <c r="D68" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" t="s">
+        <v>38</v>
+      </c>
+      <c r="F68" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68" t="s">
         <v>134</v>
-      </c>
-      <c r="B68" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68" t="s">
-        <v>107</v>
-      </c>
-      <c r="D68" t="s">
-        <v>139</v>
-      </c>
-      <c r="E68" t="s">
-        <v>109</v>
-      </c>
-      <c r="F68" t="s">
-        <v>110</v>
-      </c>
-      <c r="G68" t="s">
-        <v>53</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
@@ -3108,112 +3222,112 @@
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B69" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="D69" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="E69" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="F69" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B70" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C70" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D70" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="E70" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="F70" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="G70" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B71" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C71" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="D71" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E71" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F71" t="s">
-        <v>141</v>
+        <v>23</v>
       </c>
       <c r="G71" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B72" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="D72" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E72" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F72" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="G72" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
@@ -3224,25 +3338,25 @@
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B73" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="D73" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E73" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="F73" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="G73" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
@@ -3253,112 +3367,112 @@
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B74" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C74" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="D74" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E74" t="s">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="F74" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="G74" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B75" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C75" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D75" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="E75" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="F75" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="G75" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C76" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="D76" t="s">
-        <v>146</v>
+        <v>66</v>
       </c>
       <c r="E76" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="F76" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="G76" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B77" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C77" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="D77" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E77" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F77" t="s">
-        <v>141</v>
+        <v>23</v>
       </c>
       <c r="G77" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
@@ -3369,54 +3483,54 @@
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="B78" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="C78" t="s">
         <v>60</v>
       </c>
       <c r="D78" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="E78" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="F78" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="G78" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="B79" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="C79" t="s">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="D79" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E79" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="F79" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="G79" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
@@ -3427,54 +3541,54 @@
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
+        <v>108</v>
+      </c>
+      <c r="B80" t="s">
+        <v>105</v>
+      </c>
+      <c r="C80" t="s">
+        <v>55</v>
+      </c>
+      <c r="D80" t="s">
+        <v>76</v>
+      </c>
+      <c r="E80" t="s">
+        <v>145</v>
+      </c>
+      <c r="F80" t="s">
+        <v>146</v>
+      </c>
+      <c r="G80" t="s">
         <v>147</v>
       </c>
-      <c r="B80" t="s">
-        <v>34</v>
-      </c>
-      <c r="C80" t="s">
-        <v>60</v>
-      </c>
-      <c r="D80" t="s">
-        <v>148</v>
-      </c>
-      <c r="E80" t="s">
-        <v>62</v>
-      </c>
-      <c r="F80" t="s">
-        <v>63</v>
-      </c>
-      <c r="G80" t="s">
-        <v>17</v>
-      </c>
       <c r="H80" t="s">
         <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E81" t="s">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="F81" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="G81" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
@@ -3485,83 +3599,83 @@
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="B82" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D82" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E82" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F82" t="s">
         <v>141</v>
       </c>
       <c r="G82" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="B83" t="s">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="C83" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E83" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="F83" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="G83" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="B84" t="s">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="C84" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="D84" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F84" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
@@ -3572,25 +3686,25 @@
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="B85" t="s">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="C85" t="s">
-        <v>150</v>
+        <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E85" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F85" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="G85" t="s">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
@@ -3601,22 +3715,22 @@
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="B86" t="s">
-        <v>54</v>
+        <v>150</v>
       </c>
       <c r="C86" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="D86" t="s">
         <v>153</v>
       </c>
       <c r="E86" t="s">
-        <v>97</v>
+        <v>154</v>
       </c>
       <c r="F86" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="G86" t="s">
         <v>32</v>
@@ -3630,25 +3744,25 @@
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="B87" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="D87" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E87" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="F87" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="G87" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
@@ -3659,51 +3773,51 @@
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="B88" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="C88" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D88" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E88" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="F88" t="s">
-        <v>141</v>
+        <v>31</v>
       </c>
       <c r="G88" t="s">
-        <v>152</v>
+        <v>32</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="B89" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="C89" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="D89" t="s">
+        <v>153</v>
+      </c>
+      <c r="E89" t="s">
         <v>154</v>
       </c>
-      <c r="E89" t="s">
-        <v>97</v>
-      </c>
       <c r="F89" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="G89" t="s">
         <v>32</v>
@@ -3717,83 +3831,83 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="B90" t="s">
-        <v>65</v>
+        <v>157</v>
       </c>
       <c r="C90" t="s">
-        <v>24</v>
+        <v>148</v>
       </c>
       <c r="D90" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E90" t="s">
-        <v>26</v>
+        <v>154</v>
       </c>
       <c r="F90" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G90" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B91" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="D91" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="E91" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="F91" t="s">
-        <v>27</v>
+        <v>159</v>
       </c>
       <c r="G91" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B92" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="D92" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="E92" t="s">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="F92" t="s">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="G92" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
@@ -3804,83 +3918,83 @@
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B93" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D93" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E93" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="F93" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G93" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B94" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D94" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="E94" t="s">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="F94" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="G94" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B95" t="s">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D95" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E95" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="F95" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G95" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
@@ -3891,25 +4005,25 @@
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B96" t="s">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D96" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E96" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="F96" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G96" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
@@ -3920,25 +4034,25 @@
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B97" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="C97" t="s">
+        <v>110</v>
+      </c>
+      <c r="D97" t="s">
+        <v>56</v>
+      </c>
+      <c r="E97" t="s">
+        <v>112</v>
+      </c>
+      <c r="F97" t="s">
+        <v>159</v>
+      </c>
+      <c r="G97" t="s">
         <v>114</v>
-      </c>
-      <c r="D97" t="s">
-        <v>128</v>
-      </c>
-      <c r="E97" t="s">
-        <v>41</v>
-      </c>
-      <c r="F97" t="s">
-        <v>141</v>
-      </c>
-      <c r="G97" t="s">
-        <v>116</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
@@ -3949,54 +4063,54 @@
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B98" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="C98" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="D98" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E98" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F98" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="G98" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="C99" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="D99" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="E99" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="F99" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="G99" t="s">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
@@ -4007,83 +4121,83 @@
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B100" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="C100" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="D100" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="E100" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="F100" t="s">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="G100" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B101" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="C101" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D101" t="s">
-        <v>166</v>
+        <v>56</v>
       </c>
       <c r="E101" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="F101" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G101" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B102" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="C102" t="s">
         <v>124</v>
       </c>
       <c r="D102" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="E102" t="s">
-        <v>164</v>
+        <v>41</v>
       </c>
       <c r="F102" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G102" t="s">
-        <v>165</v>
+        <v>39</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
@@ -4094,25 +4208,25 @@
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B103" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="C103" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="D103" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="E103" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="F103" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="G103" t="s">
-        <v>165</v>
+        <v>35</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
@@ -4123,141 +4237,141 @@
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B104" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="C104" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="D104" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="E104" t="s">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="F104" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="G104" t="s">
-        <v>165</v>
+        <v>96</v>
       </c>
       <c r="H104" t="s">
         <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B105" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C105" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="D105" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="E105" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="F105" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="G105" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B106" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C106" t="s">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="D106" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="E106" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F106" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G106" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H106" t="s">
         <v>18</v>
       </c>
       <c r="I106" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B107" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C107" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="D107" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="E107" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="F107" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="G107" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
       </c>
       <c r="I107" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B108" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C108" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D108" t="s">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="E108" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="F108" t="s">
-        <v>75</v>
+        <v>159</v>
       </c>
       <c r="G108" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
@@ -4268,83 +4382,83 @@
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
+        <v>158</v>
+      </c>
+      <c r="B109" t="s">
+        <v>65</v>
+      </c>
+      <c r="C109" t="s">
+        <v>124</v>
+      </c>
+      <c r="D109" t="s">
         <v>167</v>
       </c>
-      <c r="B109" t="s">
-        <v>44</v>
-      </c>
-      <c r="C109" t="s">
-        <v>60</v>
-      </c>
-      <c r="D109" t="s">
-        <v>171</v>
-      </c>
       <c r="E109" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F109" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="G109" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
       </c>
       <c r="I109" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B110" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C110" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="D110" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E110" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="F110" t="s">
-        <v>27</v>
+        <v>159</v>
       </c>
       <c r="G110" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="H110" t="s">
         <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
+        <v>158</v>
+      </c>
+      <c r="B111" t="s">
+        <v>77</v>
+      </c>
+      <c r="C111" t="s">
+        <v>124</v>
+      </c>
+      <c r="D111" t="s">
         <v>167</v>
-      </c>
-      <c r="B111" t="s">
-        <v>54</v>
-      </c>
-      <c r="C111" t="s">
-        <v>114</v>
-      </c>
-      <c r="D111" t="s">
-        <v>168</v>
       </c>
       <c r="E111" t="s">
         <v>41</v>
       </c>
       <c r="F111" t="s">
-        <v>169</v>
+        <v>123</v>
       </c>
       <c r="G111" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
@@ -4355,141 +4469,141 @@
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B112" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C112" t="s">
-        <v>60</v>
+        <v>169</v>
       </c>
       <c r="D112" t="s">
-        <v>153</v>
+        <v>106</v>
       </c>
       <c r="E112" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="F112" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="G112" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B113" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C113" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="D113" t="s">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="E113" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="F113" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="G113" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B114" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C114" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="D114" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="E114" t="s">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c r="F114" t="s">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="G114" t="s">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="H114" t="s">
         <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B115" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C115" t="s">
+        <v>110</v>
+      </c>
+      <c r="D115" t="s">
+        <v>56</v>
+      </c>
+      <c r="E115" t="s">
+        <v>112</v>
+      </c>
+      <c r="F115" t="s">
+        <v>159</v>
+      </c>
+      <c r="G115" t="s">
         <v>114</v>
       </c>
-      <c r="D115" t="s">
-        <v>168</v>
-      </c>
-      <c r="E115" t="s">
-        <v>41</v>
-      </c>
-      <c r="F115" t="s">
-        <v>169</v>
-      </c>
-      <c r="G115" t="s">
-        <v>96</v>
-      </c>
       <c r="H115" t="s">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
+        <v>158</v>
+      </c>
+      <c r="B116" t="s">
+        <v>87</v>
+      </c>
+      <c r="C116" t="s">
+        <v>124</v>
+      </c>
+      <c r="D116" t="s">
         <v>167</v>
       </c>
-      <c r="B116" t="s">
-        <v>65</v>
-      </c>
-      <c r="C116" t="s">
-        <v>60</v>
-      </c>
-      <c r="D116" t="s">
-        <v>155</v>
-      </c>
       <c r="E116" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F116" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G116" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
@@ -4500,25 +4614,25 @@
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B117" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C117" t="s">
-        <v>24</v>
+        <v>169</v>
       </c>
       <c r="D117" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="E117" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="F117" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="G117" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
@@ -4529,54 +4643,54 @@
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B118" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C118" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="D118" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E118" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F118" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G118" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B119" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C119" t="s">
-        <v>32</v>
+        <v>169</v>
       </c>
       <c r="D119" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="E119" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="F119" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="G119" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
@@ -4587,54 +4701,54 @@
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B120" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="C120" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D120" t="s">
-        <v>154</v>
+        <v>66</v>
       </c>
       <c r="E120" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="F120" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="G120" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
       </c>
       <c r="I120" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B121" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D121" t="s">
-        <v>50</v>
+        <v>176</v>
       </c>
       <c r="E121" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="F121" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G121" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
@@ -4645,25 +4759,25 @@
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B122" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="C122" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="D122" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="E122" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="F122" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="G122" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
@@ -4674,112 +4788,112 @@
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B123" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="C123" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="D123" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="E123" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="F123" t="s">
-        <v>31</v>
+        <v>159</v>
       </c>
       <c r="G123" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B124" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="C124" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D124" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="E124" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="F124" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="G124" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
       </c>
       <c r="I124" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B125" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="C125" t="s">
         <v>60</v>
       </c>
       <c r="D125" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="E125" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F125" t="s">
-        <v>176</v>
+        <v>63</v>
       </c>
       <c r="G125" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
       </c>
       <c r="I125" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B126" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="C126" t="s">
-        <v>145</v>
+        <v>24</v>
       </c>
       <c r="D126" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="E126" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F126" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="G126" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
@@ -4790,88 +4904,2031 @@
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B127" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="C127" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D127" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E127" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F127" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="G127" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B128" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C128" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D128" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="E128" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="F128" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="G128" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B129" t="s">
+        <v>44</v>
+      </c>
+      <c r="C129" t="s">
+        <v>20</v>
+      </c>
+      <c r="D129" t="s">
+        <v>182</v>
+      </c>
+      <c r="E129" t="s">
+        <v>22</v>
+      </c>
+      <c r="F129" t="s">
+        <v>23</v>
+      </c>
+      <c r="G129" t="s">
+        <v>104</v>
+      </c>
+      <c r="H129" t="s">
+        <v>18</v>
+      </c>
+      <c r="I129" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="15">
+      <c r="A130" t="s">
+        <v>174</v>
+      </c>
+      <c r="B130" t="s">
+        <v>44</v>
+      </c>
+      <c r="C130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D130" t="s">
+        <v>183</v>
+      </c>
+      <c r="E130" t="s">
+        <v>99</v>
+      </c>
+      <c r="F130" t="s">
+        <v>31</v>
+      </c>
+      <c r="G130" t="s">
+        <v>32</v>
+      </c>
+      <c r="H130" t="s">
+        <v>18</v>
+      </c>
+      <c r="I130" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="15">
+      <c r="A131" t="s">
+        <v>174</v>
+      </c>
+      <c r="B131" t="s">
+        <v>44</v>
+      </c>
+      <c r="C131" t="s">
+        <v>24</v>
+      </c>
+      <c r="D131" t="s">
+        <v>177</v>
+      </c>
+      <c r="E131" t="s">
+        <v>97</v>
+      </c>
+      <c r="F131" t="s">
+        <v>184</v>
+      </c>
+      <c r="G131" t="s">
+        <v>80</v>
+      </c>
+      <c r="H131" t="s">
+        <v>18</v>
+      </c>
+      <c r="I131" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="15">
+      <c r="A132" t="s">
+        <v>174</v>
+      </c>
+      <c r="B132" t="s">
+        <v>44</v>
+      </c>
+      <c r="C132" t="s">
+        <v>179</v>
+      </c>
+      <c r="D132" t="s">
+        <v>180</v>
+      </c>
+      <c r="E132" t="s">
+        <v>41</v>
+      </c>
+      <c r="F132" t="s">
+        <v>123</v>
+      </c>
+      <c r="G132" t="s">
+        <v>181</v>
+      </c>
+      <c r="H132" t="s">
+        <v>18</v>
+      </c>
+      <c r="I132" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="15">
+      <c r="A133" t="s">
+        <v>174</v>
+      </c>
+      <c r="B133" t="s">
+        <v>54</v>
+      </c>
+      <c r="C133" t="s">
+        <v>110</v>
+      </c>
+      <c r="D133" t="s">
+        <v>66</v>
+      </c>
+      <c r="E133" t="s">
+        <v>112</v>
+      </c>
+      <c r="F133" t="s">
+        <v>159</v>
+      </c>
+      <c r="G133" t="s">
+        <v>175</v>
+      </c>
+      <c r="H133" t="s">
+        <v>18</v>
+      </c>
+      <c r="I133" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="15">
+      <c r="A134" t="s">
+        <v>174</v>
+      </c>
+      <c r="B134" t="s">
+        <v>54</v>
+      </c>
+      <c r="C134" t="s">
+        <v>20</v>
+      </c>
+      <c r="D134" t="s">
+        <v>59</v>
+      </c>
+      <c r="E134" t="s">
+        <v>22</v>
+      </c>
+      <c r="F134" t="s">
+        <v>23</v>
+      </c>
+      <c r="G134" t="s">
+        <v>104</v>
+      </c>
+      <c r="H134" t="s">
+        <v>18</v>
+      </c>
+      <c r="I134" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="15">
+      <c r="A135" t="s">
+        <v>174</v>
+      </c>
+      <c r="B135" t="s">
+        <v>54</v>
+      </c>
+      <c r="C135" t="s">
+        <v>60</v>
+      </c>
+      <c r="D135" t="s">
+        <v>183</v>
+      </c>
+      <c r="E135" t="s">
+        <v>99</v>
+      </c>
+      <c r="F135" t="s">
+        <v>100</v>
+      </c>
+      <c r="G135" t="s">
+        <v>32</v>
+      </c>
+      <c r="H135" t="s">
+        <v>18</v>
+      </c>
+      <c r="I135" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="15">
+      <c r="A136" t="s">
+        <v>174</v>
+      </c>
+      <c r="B136" t="s">
+        <v>54</v>
+      </c>
+      <c r="C136" t="s">
+        <v>24</v>
+      </c>
+      <c r="D136" t="s">
+        <v>177</v>
+      </c>
+      <c r="E136" t="s">
+        <v>97</v>
+      </c>
+      <c r="F136" t="s">
+        <v>184</v>
+      </c>
+      <c r="G136" t="s">
+        <v>80</v>
+      </c>
+      <c r="H136" t="s">
+        <v>18</v>
+      </c>
+      <c r="I136" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="15">
+      <c r="A137" t="s">
+        <v>174</v>
+      </c>
+      <c r="B137" t="s">
+        <v>54</v>
+      </c>
+      <c r="C137" t="s">
+        <v>179</v>
+      </c>
+      <c r="D137" t="s">
+        <v>180</v>
+      </c>
+      <c r="E137" t="s">
+        <v>41</v>
+      </c>
+      <c r="F137" t="s">
+        <v>123</v>
+      </c>
+      <c r="G137" t="s">
+        <v>181</v>
+      </c>
+      <c r="H137" t="s">
+        <v>18</v>
+      </c>
+      <c r="I137" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="15">
+      <c r="A138" t="s">
+        <v>174</v>
+      </c>
+      <c r="B138" t="s">
+        <v>65</v>
+      </c>
+      <c r="C138" t="s">
+        <v>110</v>
+      </c>
+      <c r="D138" t="s">
+        <v>66</v>
+      </c>
+      <c r="E138" t="s">
+        <v>112</v>
+      </c>
+      <c r="F138" t="s">
+        <v>159</v>
+      </c>
+      <c r="G138" t="s">
+        <v>175</v>
+      </c>
+      <c r="H138" t="s">
+        <v>18</v>
+      </c>
+      <c r="I138" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="15">
+      <c r="A139" t="s">
+        <v>174</v>
+      </c>
+      <c r="B139" t="s">
+        <v>65</v>
+      </c>
+      <c r="C139" t="s">
+        <v>20</v>
+      </c>
+      <c r="D139" t="s">
+        <v>125</v>
+      </c>
+      <c r="E139" t="s">
+        <v>22</v>
+      </c>
+      <c r="F139" t="s">
+        <v>23</v>
+      </c>
+      <c r="G139" t="s">
+        <v>104</v>
+      </c>
+      <c r="H139" t="s">
+        <v>18</v>
+      </c>
+      <c r="I139" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="15">
+      <c r="A140" t="s">
+        <v>174</v>
+      </c>
+      <c r="B140" t="s">
+        <v>65</v>
+      </c>
+      <c r="C140" t="s">
+        <v>60</v>
+      </c>
+      <c r="D140" t="s">
+        <v>139</v>
+      </c>
+      <c r="E140" t="s">
+        <v>99</v>
+      </c>
+      <c r="F140" t="s">
+        <v>100</v>
+      </c>
+      <c r="G140" t="s">
+        <v>32</v>
+      </c>
+      <c r="H140" t="s">
+        <v>18</v>
+      </c>
+      <c r="I140" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="15">
+      <c r="A141" t="s">
+        <v>174</v>
+      </c>
+      <c r="B141" t="s">
+        <v>65</v>
+      </c>
+      <c r="C141" t="s">
+        <v>24</v>
+      </c>
+      <c r="D141" t="s">
+        <v>177</v>
+      </c>
+      <c r="E141" t="s">
+        <v>26</v>
+      </c>
+      <c r="F141" t="s">
+        <v>184</v>
+      </c>
+      <c r="G141" t="s">
+        <v>80</v>
+      </c>
+      <c r="H141" t="s">
+        <v>18</v>
+      </c>
+      <c r="I141" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="15">
+      <c r="A142" t="s">
+        <v>174</v>
+      </c>
+      <c r="B142" t="s">
+        <v>77</v>
+      </c>
+      <c r="C142" t="s">
+        <v>110</v>
+      </c>
+      <c r="D142" t="s">
+        <v>66</v>
+      </c>
+      <c r="E142" t="s">
+        <v>112</v>
+      </c>
+      <c r="F142" t="s">
+        <v>159</v>
+      </c>
+      <c r="G142" t="s">
+        <v>175</v>
+      </c>
+      <c r="H142" t="s">
+        <v>18</v>
+      </c>
+      <c r="I142" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="15">
+      <c r="A143" t="s">
+        <v>174</v>
+      </c>
+      <c r="B143" t="s">
+        <v>77</v>
+      </c>
+      <c r="C143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D143" t="s">
+        <v>183</v>
+      </c>
+      <c r="E143" t="s">
+        <v>22</v>
+      </c>
+      <c r="F143" t="s">
+        <v>23</v>
+      </c>
+      <c r="G143" t="s">
+        <v>104</v>
+      </c>
+      <c r="H143" t="s">
+        <v>18</v>
+      </c>
+      <c r="I143" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="15">
+      <c r="A144" t="s">
+        <v>174</v>
+      </c>
+      <c r="B144" t="s">
+        <v>77</v>
+      </c>
+      <c r="C144" t="s">
+        <v>24</v>
+      </c>
+      <c r="D144" t="s">
+        <v>177</v>
+      </c>
+      <c r="E144" t="s">
+        <v>26</v>
+      </c>
+      <c r="F144" t="s">
+        <v>184</v>
+      </c>
+      <c r="G144" t="s">
+        <v>80</v>
+      </c>
+      <c r="H144" t="s">
+        <v>18</v>
+      </c>
+      <c r="I144" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="15">
+      <c r="A145" t="s">
+        <v>174</v>
+      </c>
+      <c r="B145" t="s">
+        <v>77</v>
+      </c>
+      <c r="C145" t="s">
+        <v>179</v>
+      </c>
+      <c r="D145" t="s">
+        <v>185</v>
+      </c>
+      <c r="E145" t="s">
+        <v>38</v>
+      </c>
+      <c r="F145" t="s">
+        <v>184</v>
+      </c>
+      <c r="G145" t="s">
+        <v>181</v>
+      </c>
+      <c r="H145" t="s">
+        <v>18</v>
+      </c>
+      <c r="I145" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="15">
+      <c r="A146" t="s">
+        <v>174</v>
+      </c>
+      <c r="B146" t="s">
+        <v>87</v>
+      </c>
+      <c r="C146" t="s">
+        <v>20</v>
+      </c>
+      <c r="D146" t="s">
+        <v>111</v>
+      </c>
+      <c r="E146" t="s">
+        <v>22</v>
+      </c>
+      <c r="F146" t="s">
+        <v>23</v>
+      </c>
+      <c r="G146" t="s">
+        <v>104</v>
+      </c>
+      <c r="H146" t="s">
+        <v>18</v>
+      </c>
+      <c r="I146" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="15">
+      <c r="A147" t="s">
+        <v>174</v>
+      </c>
+      <c r="B147" t="s">
+        <v>101</v>
+      </c>
+      <c r="C147" t="s">
+        <v>148</v>
+      </c>
+      <c r="D147" t="s">
+        <v>178</v>
+      </c>
+      <c r="E147" t="s">
+        <v>186</v>
+      </c>
+      <c r="F147" t="s">
+        <v>141</v>
+      </c>
+      <c r="G147" t="s">
+        <v>103</v>
+      </c>
+      <c r="H147" t="s">
+        <v>18</v>
+      </c>
+      <c r="I147" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="15">
+      <c r="A148" t="s">
+        <v>174</v>
+      </c>
+      <c r="B148" t="s">
+        <v>101</v>
+      </c>
+      <c r="C148" t="s">
+        <v>124</v>
+      </c>
+      <c r="D148" t="s">
+        <v>152</v>
+      </c>
+      <c r="E148" t="s">
+        <v>41</v>
+      </c>
+      <c r="F148" t="s">
+        <v>123</v>
+      </c>
+      <c r="G148" t="s">
+        <v>78</v>
+      </c>
+      <c r="H148" t="s">
+        <v>18</v>
+      </c>
+      <c r="I148" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="15">
+      <c r="A149" t="s">
+        <v>174</v>
+      </c>
+      <c r="B149" t="s">
+        <v>105</v>
+      </c>
+      <c r="C149" t="s">
+        <v>148</v>
+      </c>
+      <c r="D149" t="s">
+        <v>187</v>
+      </c>
+      <c r="E149" t="s">
+        <v>46</v>
+      </c>
+      <c r="F149" t="s">
+        <v>141</v>
+      </c>
+      <c r="G149" t="s">
+        <v>168</v>
+      </c>
+      <c r="H149" t="s">
+        <v>18</v>
+      </c>
+      <c r="I149" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="15">
+      <c r="A150" t="s">
+        <v>174</v>
+      </c>
+      <c r="B150" t="s">
+        <v>105</v>
+      </c>
+      <c r="C150" t="s">
+        <v>148</v>
+      </c>
+      <c r="D150" t="s">
+        <v>188</v>
+      </c>
+      <c r="E150" t="s">
+        <v>46</v>
+      </c>
+      <c r="F150" t="s">
+        <v>141</v>
+      </c>
+      <c r="G150" t="s">
+        <v>168</v>
+      </c>
+      <c r="H150" t="s">
+        <v>18</v>
+      </c>
+      <c r="I150" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="15">
+      <c r="A151" t="s">
+        <v>174</v>
+      </c>
+      <c r="B151" t="s">
+        <v>105</v>
+      </c>
+      <c r="C151" t="s">
+        <v>20</v>
+      </c>
+      <c r="D151" t="s">
+        <v>89</v>
+      </c>
+      <c r="E151" t="s">
+        <v>22</v>
+      </c>
+      <c r="F151" t="s">
+        <v>23</v>
+      </c>
+      <c r="G151" t="s">
+        <v>104</v>
+      </c>
+      <c r="H151" t="s">
+        <v>18</v>
+      </c>
+      <c r="I151" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="15">
+      <c r="A152" t="s">
+        <v>174</v>
+      </c>
+      <c r="B152" t="s">
+        <v>105</v>
+      </c>
+      <c r="C152" t="s">
+        <v>124</v>
+      </c>
+      <c r="D152" t="s">
+        <v>152</v>
+      </c>
+      <c r="E152" t="s">
+        <v>41</v>
+      </c>
+      <c r="F152" t="s">
+        <v>123</v>
+      </c>
+      <c r="G152" t="s">
+        <v>78</v>
+      </c>
+      <c r="H152" t="s">
+        <v>18</v>
+      </c>
+      <c r="I152" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="15">
+      <c r="A153" t="s">
+        <v>174</v>
+      </c>
+      <c r="B153" t="s">
+        <v>150</v>
+      </c>
+      <c r="C153" t="s">
+        <v>189</v>
+      </c>
+      <c r="D153" t="s">
+        <v>190</v>
+      </c>
+      <c r="E153" t="s">
+        <v>46</v>
+      </c>
+      <c r="F153" t="s">
+        <v>191</v>
+      </c>
+      <c r="G153" t="s">
+        <v>103</v>
+      </c>
+      <c r="H153" t="s">
+        <v>18</v>
+      </c>
+      <c r="I153" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="15">
+      <c r="A154" t="s">
+        <v>174</v>
+      </c>
+      <c r="B154" t="s">
+        <v>150</v>
+      </c>
+      <c r="C154" t="s">
+        <v>148</v>
+      </c>
+      <c r="D154" t="s">
+        <v>153</v>
+      </c>
+      <c r="E154" t="s">
+        <v>192</v>
+      </c>
+      <c r="F154" t="s">
+        <v>141</v>
+      </c>
+      <c r="G154" t="s">
+        <v>175</v>
+      </c>
+      <c r="H154" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="15">
+      <c r="A155" t="s">
+        <v>174</v>
+      </c>
+      <c r="B155" t="s">
+        <v>150</v>
+      </c>
+      <c r="C155" t="s">
+        <v>124</v>
+      </c>
+      <c r="D155" t="s">
+        <v>152</v>
+      </c>
+      <c r="E155" t="s">
+        <v>41</v>
+      </c>
+      <c r="F155" t="s">
+        <v>123</v>
+      </c>
+      <c r="G155" t="s">
+        <v>78</v>
+      </c>
+      <c r="H155" t="s">
+        <v>18</v>
+      </c>
+      <c r="I155" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="15">
+      <c r="A156" t="s">
+        <v>174</v>
+      </c>
+      <c r="B156" t="s">
+        <v>155</v>
+      </c>
+      <c r="C156" t="s">
+        <v>189</v>
+      </c>
+      <c r="D156" t="s">
+        <v>193</v>
+      </c>
+      <c r="E156" t="s">
+        <v>46</v>
+      </c>
+      <c r="F156" t="s">
+        <v>191</v>
+      </c>
+      <c r="G156" t="s">
+        <v>98</v>
+      </c>
+      <c r="H156" t="s">
+        <v>18</v>
+      </c>
+      <c r="I156" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="15">
+      <c r="A157" t="s">
+        <v>174</v>
+      </c>
+      <c r="B157" t="s">
+        <v>155</v>
+      </c>
+      <c r="C157" t="s">
+        <v>148</v>
+      </c>
+      <c r="D157" t="s">
+        <v>153</v>
+      </c>
+      <c r="E157" t="s">
+        <v>192</v>
+      </c>
+      <c r="F157" t="s">
+        <v>141</v>
+      </c>
+      <c r="G157" t="s">
+        <v>175</v>
+      </c>
+      <c r="H157" t="s">
+        <v>18</v>
+      </c>
+      <c r="I157" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="15">
+      <c r="A158" t="s">
+        <v>174</v>
+      </c>
+      <c r="B158" t="s">
+        <v>156</v>
+      </c>
+      <c r="C158" t="s">
+        <v>148</v>
+      </c>
+      <c r="D158" t="s">
+        <v>153</v>
+      </c>
+      <c r="E158" t="s">
+        <v>192</v>
+      </c>
+      <c r="F158" t="s">
+        <v>141</v>
+      </c>
+      <c r="G158" t="s">
+        <v>175</v>
+      </c>
+      <c r="H158" t="s">
+        <v>18</v>
+      </c>
+      <c r="I158" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="15">
+      <c r="A159" t="s">
+        <v>174</v>
+      </c>
+      <c r="B159" t="s">
+        <v>157</v>
+      </c>
+      <c r="C159" t="s">
+        <v>148</v>
+      </c>
+      <c r="D159" t="s">
+        <v>153</v>
+      </c>
+      <c r="E159" t="s">
+        <v>192</v>
+      </c>
+      <c r="F159" t="s">
+        <v>141</v>
+      </c>
+      <c r="G159" t="s">
+        <v>175</v>
+      </c>
+      <c r="H159" t="s">
+        <v>18</v>
+      </c>
+      <c r="I159" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="15">
+      <c r="A160" t="s">
+        <v>194</v>
+      </c>
+      <c r="B160" t="s">
+        <v>12</v>
+      </c>
+      <c r="C160" t="s">
+        <v>110</v>
+      </c>
+      <c r="D160" t="s">
+        <v>195</v>
+      </c>
+      <c r="E160" t="s">
+        <v>112</v>
+      </c>
+      <c r="F160" t="s">
+        <v>113</v>
+      </c>
+      <c r="G160" t="s">
+        <v>114</v>
+      </c>
+      <c r="H160" t="s">
+        <v>18</v>
+      </c>
+      <c r="I160" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="15">
+      <c r="A161" t="s">
+        <v>194</v>
+      </c>
+      <c r="B161" t="s">
+        <v>12</v>
+      </c>
+      <c r="C161" t="s">
+        <v>20</v>
+      </c>
+      <c r="D161" t="s">
+        <v>182</v>
+      </c>
+      <c r="E161" t="s">
+        <v>22</v>
+      </c>
+      <c r="F161" t="s">
+        <v>23</v>
+      </c>
+      <c r="G161" t="s">
+        <v>104</v>
+      </c>
+      <c r="H161" t="s">
+        <v>18</v>
+      </c>
+      <c r="I161" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="15">
+      <c r="A162" t="s">
+        <v>194</v>
+      </c>
+      <c r="B162" t="s">
+        <v>12</v>
+      </c>
+      <c r="C162" t="s">
+        <v>24</v>
+      </c>
+      <c r="D162" t="s">
+        <v>177</v>
+      </c>
+      <c r="E162" t="s">
+        <v>51</v>
+      </c>
+      <c r="F162" t="s">
+        <v>118</v>
+      </c>
+      <c r="G162" t="s">
+        <v>80</v>
+      </c>
+      <c r="H162" t="s">
+        <v>18</v>
+      </c>
+      <c r="I162" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="15">
+      <c r="A163" t="s">
+        <v>194</v>
+      </c>
+      <c r="B163" t="s">
+        <v>34</v>
+      </c>
+      <c r="C163" t="s">
+        <v>110</v>
+      </c>
+      <c r="D163" t="s">
+        <v>195</v>
+      </c>
+      <c r="E163" t="s">
+        <v>112</v>
+      </c>
+      <c r="F163" t="s">
+        <v>113</v>
+      </c>
+      <c r="G163" t="s">
+        <v>114</v>
+      </c>
+      <c r="H163" t="s">
+        <v>18</v>
+      </c>
+      <c r="I163" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="15">
+      <c r="A164" t="s">
+        <v>194</v>
+      </c>
+      <c r="B164" t="s">
+        <v>34</v>
+      </c>
+      <c r="C164" t="s">
+        <v>20</v>
+      </c>
+      <c r="D164" t="s">
+        <v>111</v>
+      </c>
+      <c r="E164" t="s">
+        <v>22</v>
+      </c>
+      <c r="F164" t="s">
+        <v>23</v>
+      </c>
+      <c r="G164" t="s">
+        <v>104</v>
+      </c>
+      <c r="H164" t="s">
+        <v>18</v>
+      </c>
+      <c r="I164" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="15">
+      <c r="A165" t="s">
+        <v>194</v>
+      </c>
+      <c r="B165" t="s">
+        <v>34</v>
+      </c>
+      <c r="C165" t="s">
+        <v>24</v>
+      </c>
+      <c r="D165" t="s">
+        <v>177</v>
+      </c>
+      <c r="E165" t="s">
+        <v>51</v>
+      </c>
+      <c r="F165" t="s">
+        <v>118</v>
+      </c>
+      <c r="G165" t="s">
+        <v>80</v>
+      </c>
+      <c r="H165" t="s">
+        <v>18</v>
+      </c>
+      <c r="I165" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="15">
+      <c r="A166" t="s">
+        <v>194</v>
+      </c>
+      <c r="B166" t="s">
+        <v>44</v>
+      </c>
+      <c r="C166" t="s">
+        <v>110</v>
+      </c>
+      <c r="D166" t="s">
+        <v>195</v>
+      </c>
+      <c r="E166" t="s">
+        <v>112</v>
+      </c>
+      <c r="F166" t="s">
+        <v>113</v>
+      </c>
+      <c r="G166" t="s">
+        <v>114</v>
+      </c>
+      <c r="H166" t="s">
+        <v>18</v>
+      </c>
+      <c r="I166" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="15">
+      <c r="A167" t="s">
+        <v>194</v>
+      </c>
+      <c r="B167" t="s">
+        <v>44</v>
+      </c>
+      <c r="C167" t="s">
+        <v>20</v>
+      </c>
+      <c r="D167" t="s">
+        <v>70</v>
+      </c>
+      <c r="E167" t="s">
+        <v>22</v>
+      </c>
+      <c r="F167" t="s">
+        <v>23</v>
+      </c>
+      <c r="G167" t="s">
+        <v>104</v>
+      </c>
+      <c r="H167" t="s">
+        <v>18</v>
+      </c>
+      <c r="I167" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="15">
+      <c r="A168" t="s">
+        <v>194</v>
+      </c>
+      <c r="B168" t="s">
+        <v>44</v>
+      </c>
+      <c r="C168" t="s">
+        <v>124</v>
+      </c>
+      <c r="D168" t="s">
+        <v>196</v>
+      </c>
+      <c r="E168" t="s">
+        <v>41</v>
+      </c>
+      <c r="F168" t="s">
         <v>102</v>
       </c>
-      <c r="C129" t="s">
-        <v>177</v>
-      </c>
-      <c r="D129" t="s">
+      <c r="G168" t="s">
+        <v>78</v>
+      </c>
+      <c r="H168" t="s">
+        <v>18</v>
+      </c>
+      <c r="I168" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="15">
+      <c r="A169" t="s">
+        <v>194</v>
+      </c>
+      <c r="B169" t="s">
+        <v>44</v>
+      </c>
+      <c r="C169" t="s">
+        <v>60</v>
+      </c>
+      <c r="D169" t="s">
+        <v>165</v>
+      </c>
+      <c r="E169" t="s">
+        <v>15</v>
+      </c>
+      <c r="F169" t="s">
+        <v>75</v>
+      </c>
+      <c r="G169" t="s">
+        <v>197</v>
+      </c>
+      <c r="H169" t="s">
+        <v>18</v>
+      </c>
+      <c r="I169" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="15">
+      <c r="A170" t="s">
+        <v>194</v>
+      </c>
+      <c r="B170" t="s">
+        <v>44</v>
+      </c>
+      <c r="C170" t="s">
+        <v>60</v>
+      </c>
+      <c r="D170" t="s">
+        <v>198</v>
+      </c>
+      <c r="E170" t="s">
+        <v>15</v>
+      </c>
+      <c r="F170" t="s">
+        <v>75</v>
+      </c>
+      <c r="G170" t="s">
+        <v>197</v>
+      </c>
+      <c r="H170" t="s">
+        <v>18</v>
+      </c>
+      <c r="I170" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="15">
+      <c r="A171" t="s">
+        <v>194</v>
+      </c>
+      <c r="B171" t="s">
+        <v>44</v>
+      </c>
+      <c r="C171" t="s">
+        <v>24</v>
+      </c>
+      <c r="D171" t="s">
+        <v>50</v>
+      </c>
+      <c r="E171" t="s">
+        <v>97</v>
+      </c>
+      <c r="F171" t="s">
+        <v>118</v>
+      </c>
+      <c r="G171" t="s">
+        <v>80</v>
+      </c>
+      <c r="H171" t="s">
+        <v>18</v>
+      </c>
+      <c r="I171" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="15">
+      <c r="A172" t="s">
+        <v>194</v>
+      </c>
+      <c r="B172" t="s">
+        <v>54</v>
+      </c>
+      <c r="C172" t="s">
+        <v>110</v>
+      </c>
+      <c r="D172" t="s">
+        <v>195</v>
+      </c>
+      <c r="E172" t="s">
+        <v>112</v>
+      </c>
+      <c r="F172" t="s">
+        <v>113</v>
+      </c>
+      <c r="G172" t="s">
+        <v>114</v>
+      </c>
+      <c r="H172" t="s">
+        <v>18</v>
+      </c>
+      <c r="I172" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="15">
+      <c r="A173" t="s">
+        <v>194</v>
+      </c>
+      <c r="B173" t="s">
+        <v>54</v>
+      </c>
+      <c r="C173" t="s">
+        <v>20</v>
+      </c>
+      <c r="D173" t="s">
+        <v>132</v>
+      </c>
+      <c r="E173" t="s">
+        <v>22</v>
+      </c>
+      <c r="F173" t="s">
+        <v>23</v>
+      </c>
+      <c r="G173" t="s">
+        <v>104</v>
+      </c>
+      <c r="H173" t="s">
+        <v>18</v>
+      </c>
+      <c r="I173" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="15">
+      <c r="A174" t="s">
+        <v>194</v>
+      </c>
+      <c r="B174" t="s">
+        <v>54</v>
+      </c>
+      <c r="C174" t="s">
+        <v>124</v>
+      </c>
+      <c r="D174" t="s">
+        <v>196</v>
+      </c>
+      <c r="E174" t="s">
+        <v>41</v>
+      </c>
+      <c r="F174" t="s">
+        <v>102</v>
+      </c>
+      <c r="G174" t="s">
+        <v>78</v>
+      </c>
+      <c r="H174" t="s">
+        <v>18</v>
+      </c>
+      <c r="I174" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="15">
+      <c r="A175" t="s">
+        <v>194</v>
+      </c>
+      <c r="B175" t="s">
+        <v>54</v>
+      </c>
+      <c r="C175" t="s">
+        <v>60</v>
+      </c>
+      <c r="D175" t="s">
+        <v>183</v>
+      </c>
+      <c r="E175" t="s">
+        <v>99</v>
+      </c>
+      <c r="F175" t="s">
+        <v>141</v>
+      </c>
+      <c r="G175" t="s">
+        <v>32</v>
+      </c>
+      <c r="H175" t="s">
+        <v>18</v>
+      </c>
+      <c r="I175" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="15">
+      <c r="A176" t="s">
+        <v>194</v>
+      </c>
+      <c r="B176" t="s">
+        <v>54</v>
+      </c>
+      <c r="C176" t="s">
+        <v>24</v>
+      </c>
+      <c r="D176" t="s">
+        <v>50</v>
+      </c>
+      <c r="E176" t="s">
+        <v>97</v>
+      </c>
+      <c r="F176" t="s">
+        <v>136</v>
+      </c>
+      <c r="G176" t="s">
+        <v>80</v>
+      </c>
+      <c r="H176" t="s">
+        <v>18</v>
+      </c>
+      <c r="I176" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="15">
+      <c r="A177" t="s">
+        <v>194</v>
+      </c>
+      <c r="B177" t="s">
+        <v>65</v>
+      </c>
+      <c r="C177" t="s">
+        <v>110</v>
+      </c>
+      <c r="D177" t="s">
+        <v>195</v>
+      </c>
+      <c r="E177" t="s">
+        <v>112</v>
+      </c>
+      <c r="F177" t="s">
+        <v>113</v>
+      </c>
+      <c r="G177" t="s">
+        <v>114</v>
+      </c>
+      <c r="H177" t="s">
+        <v>18</v>
+      </c>
+      <c r="I177" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="15">
+      <c r="A178" t="s">
+        <v>194</v>
+      </c>
+      <c r="B178" t="s">
+        <v>65</v>
+      </c>
+      <c r="C178" t="s">
+        <v>148</v>
+      </c>
+      <c r="D178" t="s">
+        <v>149</v>
+      </c>
+      <c r="E178" t="s">
+        <v>186</v>
+      </c>
+      <c r="F178" t="s">
+        <v>199</v>
+      </c>
+      <c r="G178" t="s">
+        <v>200</v>
+      </c>
+      <c r="H178" t="s">
+        <v>18</v>
+      </c>
+      <c r="I178" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="15">
+      <c r="A179" t="s">
+        <v>194</v>
+      </c>
+      <c r="B179" t="s">
+        <v>65</v>
+      </c>
+      <c r="C179" t="s">
+        <v>20</v>
+      </c>
+      <c r="D179" t="s">
+        <v>70</v>
+      </c>
+      <c r="E179" t="s">
+        <v>99</v>
+      </c>
+      <c r="F179" t="s">
+        <v>23</v>
+      </c>
+      <c r="G179" t="s">
+        <v>104</v>
+      </c>
+      <c r="H179" t="s">
+        <v>18</v>
+      </c>
+      <c r="I179" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="15">
+      <c r="A180" t="s">
+        <v>194</v>
+      </c>
+      <c r="B180" t="s">
+        <v>65</v>
+      </c>
+      <c r="C180" t="s">
+        <v>124</v>
+      </c>
+      <c r="D180" t="s">
+        <v>196</v>
+      </c>
+      <c r="E180" t="s">
+        <v>41</v>
+      </c>
+      <c r="F180" t="s">
+        <v>102</v>
+      </c>
+      <c r="G180" t="s">
+        <v>98</v>
+      </c>
+      <c r="H180" t="s">
+        <v>201</v>
+      </c>
+      <c r="I180" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="15">
+      <c r="A181" t="s">
+        <v>194</v>
+      </c>
+      <c r="B181" t="s">
+        <v>65</v>
+      </c>
+      <c r="C181" t="s">
+        <v>60</v>
+      </c>
+      <c r="D181" t="s">
+        <v>185</v>
+      </c>
+      <c r="E181" t="s">
+        <v>37</v>
+      </c>
+      <c r="F181" t="s">
+        <v>16</v>
+      </c>
+      <c r="G181" t="s">
+        <v>86</v>
+      </c>
+      <c r="H181" t="s">
+        <v>18</v>
+      </c>
+      <c r="I181" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="15">
+      <c r="A182" t="s">
+        <v>194</v>
+      </c>
+      <c r="B182" t="s">
+        <v>65</v>
+      </c>
+      <c r="C182" t="s">
+        <v>24</v>
+      </c>
+      <c r="D182" t="s">
+        <v>50</v>
+      </c>
+      <c r="E182" t="s">
+        <v>97</v>
+      </c>
+      <c r="F182" t="s">
+        <v>136</v>
+      </c>
+      <c r="G182" t="s">
+        <v>80</v>
+      </c>
+      <c r="H182" t="s">
+        <v>18</v>
+      </c>
+      <c r="I182" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="15">
+      <c r="A183" t="s">
+        <v>194</v>
+      </c>
+      <c r="B183" t="s">
+        <v>77</v>
+      </c>
+      <c r="C183" t="s">
+        <v>110</v>
+      </c>
+      <c r="D183" t="s">
+        <v>195</v>
+      </c>
+      <c r="E183" t="s">
+        <v>112</v>
+      </c>
+      <c r="F183" t="s">
+        <v>113</v>
+      </c>
+      <c r="G183" t="s">
+        <v>114</v>
+      </c>
+      <c r="H183" t="s">
+        <v>18</v>
+      </c>
+      <c r="I183" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="15">
+      <c r="A184" t="s">
+        <v>194</v>
+      </c>
+      <c r="B184" t="s">
+        <v>77</v>
+      </c>
+      <c r="C184" t="s">
+        <v>148</v>
+      </c>
+      <c r="D184" t="s">
+        <v>202</v>
+      </c>
+      <c r="E184" t="s">
+        <v>84</v>
+      </c>
+      <c r="F184" t="s">
+        <v>31</v>
+      </c>
+      <c r="G184" t="s">
+        <v>85</v>
+      </c>
+      <c r="H184" t="s">
+        <v>18</v>
+      </c>
+      <c r="I184" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="15">
+      <c r="A185" t="s">
+        <v>194</v>
+      </c>
+      <c r="B185" t="s">
+        <v>77</v>
+      </c>
+      <c r="C185" t="s">
+        <v>32</v>
+      </c>
+      <c r="D185" t="s">
+        <v>132</v>
+      </c>
+      <c r="E185" t="s">
+        <v>99</v>
+      </c>
+      <c r="F185" t="s">
+        <v>31</v>
+      </c>
+      <c r="G185" t="s">
+        <v>181</v>
+      </c>
+      <c r="H185" t="s">
+        <v>18</v>
+      </c>
+      <c r="I185" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="15">
+      <c r="A186" t="s">
+        <v>194</v>
+      </c>
+      <c r="B186" t="s">
+        <v>77</v>
+      </c>
+      <c r="C186" t="s">
+        <v>20</v>
+      </c>
+      <c r="D186" t="s">
+        <v>70</v>
+      </c>
+      <c r="E186" t="s">
+        <v>99</v>
+      </c>
+      <c r="F186" t="s">
+        <v>23</v>
+      </c>
+      <c r="G186" t="s">
+        <v>104</v>
+      </c>
+      <c r="H186" t="s">
+        <v>18</v>
+      </c>
+      <c r="I186" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="15">
+      <c r="A187" t="s">
+        <v>194</v>
+      </c>
+      <c r="B187" t="s">
+        <v>77</v>
+      </c>
+      <c r="C187" t="s">
+        <v>60</v>
+      </c>
+      <c r="D187" t="s">
+        <v>139</v>
+      </c>
+      <c r="E187" t="s">
+        <v>99</v>
+      </c>
+      <c r="F187" t="s">
+        <v>100</v>
+      </c>
+      <c r="G187" t="s">
         <v>175</v>
       </c>
-      <c r="E129" t="s">
+      <c r="H187" t="s">
+        <v>18</v>
+      </c>
+      <c r="I187" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="15">
+      <c r="A188" t="s">
+        <v>194</v>
+      </c>
+      <c r="B188" t="s">
+        <v>77</v>
+      </c>
+      <c r="C188" t="s">
+        <v>24</v>
+      </c>
+      <c r="D188" t="s">
+        <v>50</v>
+      </c>
+      <c r="E188" t="s">
+        <v>97</v>
+      </c>
+      <c r="F188" t="s">
+        <v>75</v>
+      </c>
+      <c r="G188" t="s">
+        <v>80</v>
+      </c>
+      <c r="H188" t="s">
+        <v>18</v>
+      </c>
+      <c r="I188" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="15">
+      <c r="A189" t="s">
+        <v>194</v>
+      </c>
+      <c r="B189" t="s">
+        <v>87</v>
+      </c>
+      <c r="C189" t="s">
+        <v>148</v>
+      </c>
+      <c r="D189" t="s">
+        <v>183</v>
+      </c>
+      <c r="E189" t="s">
+        <v>22</v>
+      </c>
+      <c r="F189" t="s">
+        <v>100</v>
+      </c>
+      <c r="G189" t="s">
+        <v>114</v>
+      </c>
+      <c r="H189" t="s">
+        <v>18</v>
+      </c>
+      <c r="I189" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="15">
+      <c r="A190" t="s">
+        <v>194</v>
+      </c>
+      <c r="B190" t="s">
+        <v>87</v>
+      </c>
+      <c r="C190" t="s">
+        <v>32</v>
+      </c>
+      <c r="D190" t="s">
+        <v>132</v>
+      </c>
+      <c r="E190" t="s">
+        <v>99</v>
+      </c>
+      <c r="F190" t="s">
+        <v>31</v>
+      </c>
+      <c r="G190" t="s">
+        <v>181</v>
+      </c>
+      <c r="H190" t="s">
+        <v>18</v>
+      </c>
+      <c r="I190" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="15">
+      <c r="A191" t="s">
+        <v>194</v>
+      </c>
+      <c r="B191" t="s">
+        <v>87</v>
+      </c>
+      <c r="C191" t="s">
+        <v>60</v>
+      </c>
+      <c r="D191" t="s">
+        <v>139</v>
+      </c>
+      <c r="E191" t="s">
+        <v>99</v>
+      </c>
+      <c r="F191" t="s">
+        <v>63</v>
+      </c>
+      <c r="G191" t="s">
+        <v>103</v>
+      </c>
+      <c r="H191" t="s">
+        <v>18</v>
+      </c>
+      <c r="I191" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="15">
+      <c r="A192" t="s">
+        <v>194</v>
+      </c>
+      <c r="B192" t="s">
+        <v>101</v>
+      </c>
+      <c r="C192" t="s">
+        <v>60</v>
+      </c>
+      <c r="D192" t="s">
+        <v>70</v>
+      </c>
+      <c r="E192" t="s">
+        <v>84</v>
+      </c>
+      <c r="F192" t="s">
+        <v>203</v>
+      </c>
+      <c r="G192" t="s">
+        <v>85</v>
+      </c>
+      <c r="H192" t="s">
+        <v>18</v>
+      </c>
+      <c r="I192" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="15">
+      <c r="A193" t="s">
+        <v>194</v>
+      </c>
+      <c r="B193" t="s">
+        <v>101</v>
+      </c>
+      <c r="C193" t="s">
+        <v>171</v>
+      </c>
+      <c r="D193" t="s">
+        <v>172</v>
+      </c>
+      <c r="E193" t="s">
+        <v>94</v>
+      </c>
+      <c r="F193" t="s">
+        <v>16</v>
+      </c>
+      <c r="G193" t="s">
+        <v>55</v>
+      </c>
+      <c r="H193" t="s">
+        <v>18</v>
+      </c>
+      <c r="I193" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="15">
+      <c r="A194" t="s">
+        <v>194</v>
+      </c>
+      <c r="B194" t="s">
+        <v>101</v>
+      </c>
+      <c r="C194" t="s">
+        <v>204</v>
+      </c>
+      <c r="D194" t="s">
+        <v>202</v>
+      </c>
+      <c r="E194" t="s">
         <v>37</v>
       </c>
-      <c r="F129" t="s">
-        <v>172</v>
-      </c>
-      <c r="G129" t="s">
-        <v>178</v>
-      </c>
-      <c r="H129" t="s">
-        <v>18</v>
-      </c>
-      <c r="I129" t="s">
+      <c r="F194" t="s">
+        <v>199</v>
+      </c>
+      <c r="G194" t="s">
+        <v>205</v>
+      </c>
+      <c r="H194" t="s">
+        <v>18</v>
+      </c>
+      <c r="I194" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="15">
+      <c r="A195" t="s">
+        <v>194</v>
+      </c>
+      <c r="B195" t="s">
+        <v>105</v>
+      </c>
+      <c r="C195" t="s">
+        <v>60</v>
+      </c>
+      <c r="D195" t="s">
+        <v>132</v>
+      </c>
+      <c r="E195" t="s">
+        <v>160</v>
+      </c>
+      <c r="F195" t="s">
+        <v>141</v>
+      </c>
+      <c r="G195" t="s">
+        <v>175</v>
+      </c>
+      <c r="H195" t="s">
+        <v>18</v>
+      </c>
+      <c r="I195" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="15">
+      <c r="A196" t="s">
+        <v>194</v>
+      </c>
+      <c r="B196" t="s">
+        <v>105</v>
+      </c>
+      <c r="C196" t="s">
+        <v>204</v>
+      </c>
+      <c r="D196" t="s">
+        <v>202</v>
+      </c>
+      <c r="E196" t="s">
+        <v>37</v>
+      </c>
+      <c r="F196" t="s">
+        <v>199</v>
+      </c>
+      <c r="G196" t="s">
+        <v>205</v>
+      </c>
+      <c r="H196" t="s">
+        <v>18</v>
+      </c>
+      <c r="I196" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4883,15 +6940,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{36702926-9152-4f76-a399-d19776b18095}">
-  <dimension ref="A1:I7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{9d6baf38-db5d-4bb5-bd15-58a1dd8fee29}">
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="19.8571428571429" customWidth="1"/>
-    <col min="4" max="4" width="48" customWidth="1"/>
-    <col min="5" max="5" width="39.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="50.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="55.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="11.4285714285714" customWidth="1"/>
     <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
@@ -4903,16 +6960,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -4932,16 +6989,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="C2" t="s">
         <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -4961,16 +7018,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="E3" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -4990,16 +7047,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="E4" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -5019,16 +7076,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="E5" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -5048,16 +7105,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="C6" t="s">
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -5077,16 +7134,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="C7" t="s">
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="E7" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -5098,6 +7155,122 @@
         <v>18</v>
       </c>
       <c r="I7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15">
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" t="s">
+        <v>211</v>
+      </c>
+      <c r="E8" t="s">
+        <v>223</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E9" t="s">
+        <v>223</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15">
+      <c r="A10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>217</v>
+      </c>
+      <c r="E10" t="s">
+        <v>223</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15">
+      <c r="A11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" t="s">
+        <v>225</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5109,8 +7282,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ec179b83-01b8-4521-9935-3e0b80d71950}">
-  <dimension ref="A1:F7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{22b2566a-3828-433f-8333-974abe91cdc2}">
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -5126,13 +7299,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -5146,16 +7319,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -5166,16 +7339,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -5186,16 +7359,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="C4" t="s">
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="E4" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -5206,13 +7379,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="E5" t="s">
         <v>32</v>
@@ -5226,16 +7399,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E6" t="s">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -5246,18 +7419,438 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" t="s">
         <v>55</v>
       </c>
-      <c r="D7" t="s">
-        <v>204</v>
-      </c>
-      <c r="E7" t="s">
-        <v>208</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="D8" t="s">
+        <v>236</v>
+      </c>
+      <c r="E8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>236</v>
+      </c>
+      <c r="E9" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15">
+      <c r="A10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" t="s">
+        <v>236</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15">
+      <c r="A11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E11" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15">
+      <c r="A12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15">
+      <c r="A13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>236</v>
+      </c>
+      <c r="E13" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15">
+      <c r="A14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15">
+      <c r="A15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" t="s">
+        <v>243</v>
+      </c>
+      <c r="C15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" t="s">
+        <v>232</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15">
+      <c r="A16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" t="s">
+        <v>232</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15">
+      <c r="A17" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" t="s">
+        <v>240</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" t="s">
+        <v>236</v>
+      </c>
+      <c r="E17" t="s">
+        <v>241</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15">
+      <c r="A18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" t="s">
+        <v>245</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" t="s">
+        <v>236</v>
+      </c>
+      <c r="E18" t="s">
+        <v>241</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15">
+      <c r="A19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C19" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" t="s">
+        <v>230</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15">
+      <c r="A20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B20" t="s">
+        <v>235</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>236</v>
+      </c>
+      <c r="E20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15">
+      <c r="A21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B21" t="s">
+        <v>238</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>236</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15">
+      <c r="A22" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" t="s">
+        <v>233</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>236</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15">
+      <c r="A23" t="s">
+        <v>174</v>
+      </c>
+      <c r="B23" t="s">
+        <v>238</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>232</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15">
+      <c r="A24" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" t="s">
+        <v>229</v>
+      </c>
+      <c r="C24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" t="s">
+        <v>230</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15">
+      <c r="A25" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" t="s">
+        <v>231</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" t="s">
+        <v>232</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15">
+      <c r="A26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B26" t="s">
+        <v>231</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15">
+      <c r="A27" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" t="s">
+        <v>232</v>
+      </c>
+      <c r="E27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15">
+      <c r="A28" t="s">
+        <v>194</v>
+      </c>
+      <c r="B28" t="s">
+        <v>243</v>
+      </c>
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>232</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
         <v>18</v>
       </c>
     </row>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2033" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2501" uniqueCount="266">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -432,97 +432,121 @@
     <t>1TFB</t>
   </si>
   <si>
+    <t>1WB</t>
+  </si>
+  <si>
+    <t>1WB|JN1</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>Edukacja obywatelska</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
+    <t>Dalach Sławomir</t>
+  </si>
+  <si>
+    <t>2FB|CH</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Zaleska Magdalena</t>
+  </si>
+  <si>
+    <t>Kruk Marcin</t>
+  </si>
+  <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>10, 15:45-16:30</t>
+  </si>
+  <si>
+    <t>1TFA|JA2</t>
+  </si>
+  <si>
+    <t>1TFA|JA1</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur</t>
+  </si>
+  <si>
+    <t>11, 16:35-17:20</t>
+  </si>
+  <si>
+    <t>12, 17:25-18:10</t>
+  </si>
+  <si>
+    <t>13, 18:15-19:00</t>
+  </si>
+  <si>
+    <t>11.03.2026</t>
+  </si>
+  <si>
+    <t>1FA|JA2</t>
+  </si>
+  <si>
+    <t>prf2</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - barber</t>
+  </si>
+  <si>
+    <t>2CA|edu</t>
+  </si>
+  <si>
+    <t>2FC|edu</t>
+  </si>
+  <si>
+    <t>2S|edu</t>
+  </si>
+  <si>
+    <t>2WA|edu</t>
+  </si>
+  <si>
+    <t>Bujanowska Iwona</t>
+  </si>
+  <si>
+    <t>2WA</t>
+  </si>
+  <si>
+    <t>1FA|JA1</t>
+  </si>
+  <si>
+    <t>Chemia</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>2WA|JN2</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
     <t>29</t>
   </si>
   <si>
-    <t>1WB</t>
-  </si>
-  <si>
-    <t>1WB|JN1</t>
-  </si>
-  <si>
-    <t>1TFA</t>
-  </si>
-  <si>
-    <t>Edukacja obywatelska</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Kopij Marcin</t>
-  </si>
-  <si>
-    <t>Dalach Sławomir</t>
-  </si>
-  <si>
-    <t>2FB|CH</t>
-  </si>
-  <si>
-    <t>Historia</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Zaleska Magdalena</t>
-  </si>
-  <si>
-    <t>Kruk Marcin</t>
-  </si>
-  <si>
-    <t>1FB</t>
-  </si>
-  <si>
-    <t>10, 15:45-16:30</t>
-  </si>
-  <si>
-    <t>1TFA|JA2</t>
-  </si>
-  <si>
-    <t>1TFA|JA1</t>
-  </si>
-  <si>
-    <t>2B</t>
-  </si>
-  <si>
-    <t>Projektowanie fryzur</t>
-  </si>
-  <si>
-    <t>11, 16:35-17:20</t>
-  </si>
-  <si>
-    <t>12, 17:25-18:10</t>
-  </si>
-  <si>
-    <t>13, 18:15-19:00</t>
-  </si>
-  <si>
-    <t>11.03.2026</t>
-  </si>
-  <si>
-    <t>prf2</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - barber</t>
-  </si>
-  <si>
-    <t>2CA|edu</t>
-  </si>
-  <si>
-    <t>2FC|edu</t>
-  </si>
-  <si>
-    <t>2S|edu</t>
-  </si>
-  <si>
-    <t>2WA|edu</t>
-  </si>
-  <si>
-    <t>1FA|JA1</t>
-  </si>
-  <si>
-    <t>2WA|JN2</t>
+    <t>1FC|JA1</t>
   </si>
   <si>
     <t>2K|CH</t>
@@ -531,6 +555,9 @@
     <t>Wojciechowski Łukasz</t>
   </si>
   <si>
+    <t>2S|CH</t>
+  </si>
+  <si>
     <t>Skarupa Agnieszka</t>
   </si>
   <si>
@@ -549,18 +576,30 @@
     <t>12.03.2026</t>
   </si>
   <si>
+    <t>2FA|JA1</t>
+  </si>
+  <si>
+    <t>sg1</t>
+  </si>
+  <si>
     <t>Danielewski Paweł</t>
   </si>
   <si>
-    <t>2WA</t>
-  </si>
-  <si>
     <t>2CA</t>
   </si>
   <si>
     <t>1FC</t>
   </si>
   <si>
+    <t>Smirnow-Zechman Eleonora</t>
+  </si>
+  <si>
+    <t>Biznes i zarządzanie</t>
+  </si>
+  <si>
+    <t>Kariera z klasą - inspiracja, matura biznes. Bez uczniów</t>
+  </si>
+  <si>
     <t>Wójcik Kamil</t>
   </si>
   <si>
@@ -573,16 +612,28 @@
     <t>2TFA</t>
   </si>
   <si>
+    <t>1K</t>
+  </si>
+  <si>
     <t>1FA</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
+    <t>3TFB|DZ</t>
+  </si>
+  <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>1TH</t>
+  </si>
+  <si>
     <t>1WA</t>
   </si>
   <si>
-    <t>Chemia</t>
+    <t>1CB</t>
   </si>
   <si>
     <t>2B|JA1</t>
@@ -594,9 +645,6 @@
     <t>Granatowska Mariola</t>
   </si>
   <si>
-    <t>2TH</t>
-  </si>
-  <si>
     <t>43</t>
   </si>
   <si>
@@ -618,13 +666,10 @@
     <t>Płatek Krzysztof</t>
   </si>
   <si>
-    <t>1FA|JA2</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Hudziec Agnieszka</t>
+    <t>3TFA|JA2</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>p. Piątek-Pawłowska, j. polski za lekcję 1</t>
@@ -633,6 +678,9 @@
     <t>1S</t>
   </si>
   <si>
+    <t>Staliś Donata</t>
+  </si>
+  <si>
     <t>28</t>
   </si>
   <si>
@@ -763,6 +811,15 @@
   </si>
   <si>
     <t>17:20-17:25</t>
+  </si>
+  <si>
+    <t>piętro_1</t>
+  </si>
+  <si>
+    <t>piętro_2</t>
+  </si>
+  <si>
+    <t>piętro_3</t>
   </si>
 </sst>
 </file>
@@ -1212,7 +1269,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bde1abec-610f-491f-acbf-cf4967f4f789}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{39c6e93d-debd-4fe5-bde7-6429f26e12fa}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1233,18 +1290,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5621122c-3426-4648-adec-47fe50f46ad4}">
-  <dimension ref="A1:I196"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e98c8f7c-4105-4d91-821d-8405622da9b4}">
+  <dimension ref="A1:I238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="22.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="68.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="36.7142857142857" customWidth="1"/>
+    <col min="8" max="8" width="49" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3324,7 +3381,7 @@
         <v>38</v>
       </c>
       <c r="F72" t="s">
-        <v>136</v>
+        <v>16</v>
       </c>
       <c r="G72" t="s">
         <v>69</v>
@@ -3347,7 +3404,7 @@
         <v>60</v>
       </c>
       <c r="D73" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E73" t="s">
         <v>62</v>
@@ -3376,7 +3433,7 @@
         <v>55</v>
       </c>
       <c r="D74" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E74" t="s">
         <v>94</v>
@@ -3463,7 +3520,7 @@
         <v>20</v>
       </c>
       <c r="D77" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E77" t="s">
         <v>22</v>
@@ -3495,13 +3552,13 @@
         <v>132</v>
       </c>
       <c r="E78" t="s">
+        <v>139</v>
+      </c>
+      <c r="F78" t="s">
         <v>140</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>141</v>
-      </c>
-      <c r="G78" t="s">
-        <v>142</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
@@ -3518,10 +3575,10 @@
         <v>105</v>
       </c>
       <c r="C79" t="s">
+        <v>142</v>
+      </c>
+      <c r="D79" t="s">
         <v>143</v>
-      </c>
-      <c r="D79" t="s">
-        <v>144</v>
       </c>
       <c r="E79" t="s">
         <v>41</v>
@@ -3553,13 +3610,13 @@
         <v>76</v>
       </c>
       <c r="E80" t="s">
+        <v>144</v>
+      </c>
+      <c r="F80" t="s">
         <v>145</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>146</v>
-      </c>
-      <c r="G80" t="s">
-        <v>147</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
@@ -3579,7 +3636,7 @@
         <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E81" t="s">
         <v>15</v>
@@ -3605,16 +3662,16 @@
         <v>105</v>
       </c>
       <c r="C82" t="s">
+        <v>147</v>
+      </c>
+      <c r="D82" t="s">
         <v>148</v>
-      </c>
-      <c r="D82" t="s">
-        <v>149</v>
       </c>
       <c r="E82" t="s">
         <v>38</v>
       </c>
       <c r="F82" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G82" t="s">
         <v>114</v>
@@ -3631,13 +3688,13 @@
         <v>108</v>
       </c>
       <c r="B83" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C83" t="s">
+        <v>142</v>
+      </c>
+      <c r="D83" t="s">
         <v>143</v>
-      </c>
-      <c r="D83" t="s">
-        <v>144</v>
       </c>
       <c r="E83" t="s">
         <v>41</v>
@@ -3660,13 +3717,13 @@
         <v>108</v>
       </c>
       <c r="B84" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C84" t="s">
         <v>55</v>
       </c>
       <c r="D84" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E84" t="s">
         <v>94</v>
@@ -3689,13 +3746,13 @@
         <v>108</v>
       </c>
       <c r="B85" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C85" t="s">
         <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E85" t="s">
         <v>15</v>
@@ -3718,16 +3775,16 @@
         <v>108</v>
       </c>
       <c r="B86" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C86" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D86" t="s">
+        <v>152</v>
+      </c>
+      <c r="E86" t="s">
         <v>153</v>
-      </c>
-      <c r="E86" t="s">
-        <v>154</v>
       </c>
       <c r="F86" t="s">
         <v>31</v>
@@ -3747,13 +3804,13 @@
         <v>108</v>
       </c>
       <c r="B87" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C87" t="s">
+        <v>142</v>
+      </c>
+      <c r="D87" t="s">
         <v>143</v>
-      </c>
-      <c r="D87" t="s">
-        <v>144</v>
       </c>
       <c r="E87" t="s">
         <v>41</v>
@@ -3776,16 +3833,16 @@
         <v>108</v>
       </c>
       <c r="B88" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C88" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D88" t="s">
+        <v>152</v>
+      </c>
+      <c r="E88" t="s">
         <v>153</v>
-      </c>
-      <c r="E88" t="s">
-        <v>154</v>
       </c>
       <c r="F88" t="s">
         <v>31</v>
@@ -3805,16 +3862,16 @@
         <v>108</v>
       </c>
       <c r="B89" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C89" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D89" t="s">
+        <v>152</v>
+      </c>
+      <c r="E89" t="s">
         <v>153</v>
-      </c>
-      <c r="E89" t="s">
-        <v>154</v>
       </c>
       <c r="F89" t="s">
         <v>31</v>
@@ -3834,16 +3891,16 @@
         <v>108</v>
       </c>
       <c r="B90" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C90" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D90" t="s">
+        <v>152</v>
+      </c>
+      <c r="E90" t="s">
         <v>153</v>
-      </c>
-      <c r="E90" t="s">
-        <v>154</v>
       </c>
       <c r="F90" t="s">
         <v>31</v>
@@ -3860,94 +3917,94 @@
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B91" t="s">
         <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="E91" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F91" t="s">
-        <v>159</v>
+        <v>42</v>
       </c>
       <c r="G91" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B92" t="s">
         <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D92" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E92" t="s">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="F92" t="s">
-        <v>63</v>
+        <v>159</v>
       </c>
       <c r="G92" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B93" t="s">
         <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="D93" t="s">
-        <v>161</v>
+        <v>59</v>
       </c>
       <c r="E93" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F93" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="G93" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B94" t="s">
         <v>12</v>
@@ -3956,7 +4013,7 @@
         <v>115</v>
       </c>
       <c r="D94" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E94" t="s">
         <v>117</v>
@@ -3976,7 +4033,7 @@
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B95" t="s">
         <v>12</v>
@@ -3985,7 +4042,7 @@
         <v>115</v>
       </c>
       <c r="D95" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E95" t="s">
         <v>117</v>
@@ -4005,7 +4062,7 @@
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B96" t="s">
         <v>12</v>
@@ -4014,7 +4071,7 @@
         <v>115</v>
       </c>
       <c r="D96" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E96" t="s">
         <v>117</v>
@@ -4029,30 +4086,30 @@
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B97" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D97" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
       <c r="E97" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F97" t="s">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="G97" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
@@ -4063,25 +4120,25 @@
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B98" t="s">
         <v>34</v>
       </c>
       <c r="C98" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="D98" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E98" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="F98" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G98" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
@@ -4092,83 +4149,83 @@
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B99" t="s">
         <v>34</v>
       </c>
       <c r="C99" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D99" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="E99" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F99" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G99" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B100" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C100" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="D100" t="s">
-        <v>166</v>
+        <v>56</v>
       </c>
       <c r="E100" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="F100" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="G100" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B101" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C101" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D101" t="s">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="E101" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F101" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="G101" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
@@ -4179,25 +4236,25 @@
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B102" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C102" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="D102" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="E102" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F102" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="G102" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
@@ -4208,25 +4265,25 @@
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B103" t="s">
         <v>44</v>
       </c>
       <c r="C103" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="D103" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="E103" t="s">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="F103" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="G103" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
@@ -4237,83 +4294,83 @@
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
+        <v>157</v>
+      </c>
+      <c r="B104" t="s">
+        <v>44</v>
+      </c>
+      <c r="C104" t="s">
+        <v>78</v>
+      </c>
+      <c r="D104" t="s">
         <v>158</v>
       </c>
-      <c r="B104" t="s">
-        <v>54</v>
-      </c>
-      <c r="C104" t="s">
-        <v>55</v>
-      </c>
-      <c r="D104" t="s">
-        <v>166</v>
-      </c>
       <c r="E104" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="F104" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="G104" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="H104" t="s">
         <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B105" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C105" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="D105" t="s">
-        <v>56</v>
+        <v>171</v>
       </c>
       <c r="E105" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F105" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="G105" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B106" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C106" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D106" t="s">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="E106" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="F106" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="G106" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="H106" t="s">
         <v>18</v>
@@ -4324,54 +4381,54 @@
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B107" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C107" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="D107" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="E107" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="F107" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="G107" t="s">
-        <v>127</v>
+        <v>39</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
       </c>
       <c r="I107" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B108" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C108" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D108" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E108" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="F108" t="s">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="G108" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
@@ -4382,25 +4439,25 @@
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B109" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C109" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="D109" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E109" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F109" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="G109" t="s">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
@@ -4411,373 +4468,373 @@
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B110" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C110" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D110" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="E110" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F110" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="G110" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="H110" t="s">
         <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B111" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C111" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="D111" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E111" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="F111" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="G111" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B112" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C112" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="D112" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="E112" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="F112" t="s">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="G112" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B113" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C113" t="s">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="D113" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E113" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="F113" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="G113" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B114" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C114" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="D114" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E114" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="F114" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="G114" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="H114" t="s">
         <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B115" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C115" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D115" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="E115" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F115" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="G115" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B116" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C116" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="D116" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="E116" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="F116" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="G116" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B117" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C117" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="D117" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="E117" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="F117" t="s">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="G117" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B118" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="C118" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="D118" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E118" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="F118" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G118" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B119" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C119" t="s">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="D119" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="E119" t="s">
-        <v>170</v>
+        <v>41</v>
       </c>
       <c r="F119" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="G119" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
       </c>
       <c r="I119" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B120" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C120" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="D120" t="s">
-        <v>66</v>
+        <v>177</v>
       </c>
       <c r="E120" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F120" t="s">
-        <v>159</v>
+        <v>42</v>
       </c>
       <c r="G120" t="s">
-        <v>175</v>
+        <v>103</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
       </c>
       <c r="I120" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B121" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C121" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D121" t="s">
-        <v>176</v>
+        <v>56</v>
       </c>
       <c r="E121" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="F121" t="s">
-        <v>63</v>
+        <v>159</v>
       </c>
       <c r="G121" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B122" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C122" t="s">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="D122" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E122" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="F122" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G122" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
@@ -4788,83 +4845,83 @@
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B123" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C123" t="s">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="D123" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="E123" t="s">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="F123" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="G123" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B124" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C124" t="s">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="D124" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E124" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="F124" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="G124" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
       </c>
       <c r="I124" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B125" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="C125" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="D125" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E125" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F125" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="G125" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
@@ -4875,199 +4932,199 @@
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B126" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="C126" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="D126" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="E126" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="F126" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="G126" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
       </c>
       <c r="I126" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B127" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="C127" t="s">
-        <v>179</v>
+        <v>110</v>
       </c>
       <c r="D127" t="s">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="E127" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="F127" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="G127" t="s">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B128" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C128" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D128" t="s">
-        <v>66</v>
+        <v>175</v>
       </c>
       <c r="E128" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F128" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="G128" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B129" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C129" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="D129" t="s">
-        <v>182</v>
+        <v>106</v>
       </c>
       <c r="E129" t="s">
-        <v>22</v>
+        <v>179</v>
       </c>
       <c r="F129" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="G129" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B130" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="C130" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="D130" t="s">
-        <v>183</v>
+        <v>59</v>
       </c>
       <c r="E130" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="F130" t="s">
-        <v>31</v>
+        <v>173</v>
       </c>
       <c r="G130" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B131" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="C131" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="D131" t="s">
         <v>177</v>
       </c>
       <c r="E131" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="F131" t="s">
-        <v>184</v>
+        <v>42</v>
       </c>
       <c r="G131" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="H131" t="s">
         <v>18</v>
       </c>
       <c r="I131" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B132" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="C132" t="s">
-        <v>179</v>
+        <v>55</v>
       </c>
       <c r="D132" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E132" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="F132" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G132" t="s">
-        <v>181</v>
+        <v>103</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
@@ -5078,228 +5135,228 @@
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B133" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C133" t="s">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="D133" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="E133" t="s">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="F133" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="G133" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
       </c>
       <c r="I133" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B134" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C134" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D134" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="E134" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F134" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="G134" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="H134" t="s">
         <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B135" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C135" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D135" t="s">
-        <v>183</v>
+        <v>66</v>
       </c>
       <c r="E135" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F135" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="G135" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="H135" t="s">
         <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B136" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C136" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D136" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="E136" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F136" t="s">
-        <v>184</v>
+        <v>63</v>
       </c>
       <c r="G136" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="H136" t="s">
         <v>18</v>
       </c>
       <c r="I136" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B137" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C137" t="s">
-        <v>179</v>
+        <v>24</v>
       </c>
       <c r="D137" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="E137" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="F137" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G137" t="s">
-        <v>181</v>
+        <v>80</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
       </c>
       <c r="I137" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B138" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C138" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D138" t="s">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="E138" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F138" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="G138" t="s">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
       </c>
       <c r="I138" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B139" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C139" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D139" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="E139" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="F139" t="s">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="G139" t="s">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="H139" t="s">
         <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B140" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C140" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D140" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="E140" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="F140" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="G140" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="H140" t="s">
         <v>18</v>
@@ -5310,83 +5367,83 @@
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B141" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C141" t="s">
-        <v>24</v>
+        <v>189</v>
       </c>
       <c r="D141" t="s">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="E141" t="s">
-        <v>26</v>
+        <v>190</v>
       </c>
       <c r="F141" t="s">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="G141" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="H141" t="s">
-        <v>18</v>
+        <v>191</v>
       </c>
       <c r="I141" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B142" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="C142" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D142" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="E142" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="F142" t="s">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="G142" t="s">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="H142" t="s">
         <v>18</v>
       </c>
       <c r="I142" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B143" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="C143" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D143" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E143" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="F143" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="G143" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="H143" t="s">
         <v>18</v>
@@ -5397,54 +5454,54 @@
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B144" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="C144" t="s">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D144" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="E144" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F144" t="s">
-        <v>184</v>
+        <v>123</v>
       </c>
       <c r="G144" t="s">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="H144" t="s">
         <v>18</v>
       </c>
       <c r="I144" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B145" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C145" t="s">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="D145" t="s">
+        <v>184</v>
+      </c>
+      <c r="E145" t="s">
+        <v>41</v>
+      </c>
+      <c r="F145" t="s">
         <v>185</v>
       </c>
-      <c r="E145" t="s">
-        <v>38</v>
-      </c>
-      <c r="F145" t="s">
-        <v>184</v>
-      </c>
       <c r="G145" t="s">
-        <v>181</v>
+        <v>17</v>
       </c>
       <c r="H145" t="s">
         <v>18</v>
@@ -5455,141 +5512,141 @@
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B146" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="C146" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D146" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="E146" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="F146" t="s">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="G146" t="s">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B147" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="C147" t="s">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="D147" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="E147" t="s">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="F147" t="s">
-        <v>141</v>
+        <v>23</v>
       </c>
       <c r="G147" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H147" t="s">
         <v>18</v>
       </c>
       <c r="I147" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B148" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="C148" t="s">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="D148" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="E148" t="s">
-        <v>41</v>
+        <v>190</v>
       </c>
       <c r="F148" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G148" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="H148" t="s">
-        <v>18</v>
+        <v>191</v>
       </c>
       <c r="I148" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B149" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="C149" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="D149" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="E149" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="F149" t="s">
-        <v>141</v>
+        <v>31</v>
       </c>
       <c r="G149" t="s">
-        <v>168</v>
+        <v>32</v>
       </c>
       <c r="H149" t="s">
         <v>18</v>
       </c>
       <c r="I149" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B150" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="C150" t="s">
-        <v>148</v>
+        <v>24</v>
       </c>
       <c r="D150" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E150" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="F150" t="s">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="G150" t="s">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="H150" t="s">
         <v>18</v>
@@ -5600,54 +5657,54 @@
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B151" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="C151" t="s">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="D151" t="s">
-        <v>89</v>
+        <v>193</v>
       </c>
       <c r="E151" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F151" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="G151" t="s">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="H151" t="s">
         <v>18</v>
       </c>
       <c r="I151" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B152" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="C152" t="s">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="D152" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="E152" t="s">
         <v>41</v>
       </c>
       <c r="F152" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="G152" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="H152" t="s">
         <v>18</v>
@@ -5658,54 +5715,54 @@
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B153" t="s">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="C153" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="D153" t="s">
-        <v>190</v>
+        <v>66</v>
       </c>
       <c r="E153" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="F153" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="G153" t="s">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="H153" t="s">
         <v>18</v>
       </c>
       <c r="I153" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B154" t="s">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="C154" t="s">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="D154" t="s">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="E154" t="s">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="F154" t="s">
-        <v>141</v>
+        <v>23</v>
       </c>
       <c r="G154" t="s">
-        <v>175</v>
+        <v>104</v>
       </c>
       <c r="H154" t="s">
         <v>18</v>
@@ -5716,83 +5773,83 @@
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B155" t="s">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="C155" t="s">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="D155" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="E155" t="s">
-        <v>41</v>
+        <v>190</v>
       </c>
       <c r="F155" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G155" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="H155" t="s">
-        <v>18</v>
+        <v>191</v>
       </c>
       <c r="I155" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B156" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="C156" t="s">
-        <v>189</v>
+        <v>60</v>
       </c>
       <c r="D156" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E156" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="F156" t="s">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="G156" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="H156" t="s">
         <v>18</v>
       </c>
       <c r="I156" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B157" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="C157" t="s">
-        <v>148</v>
+        <v>24</v>
       </c>
       <c r="D157" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="E157" t="s">
-        <v>192</v>
+        <v>97</v>
       </c>
       <c r="F157" t="s">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="G157" t="s">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="H157" t="s">
         <v>18</v>
@@ -5803,54 +5860,54 @@
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B158" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="C158" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="D158" t="s">
-        <v>153</v>
+        <v>193</v>
       </c>
       <c r="E158" t="s">
-        <v>192</v>
+        <v>41</v>
       </c>
       <c r="F158" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G158" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
       </c>
       <c r="I158" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B159" t="s">
-        <v>157</v>
+        <v>65</v>
       </c>
       <c r="C159" t="s">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="D159" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="E159" t="s">
-        <v>192</v>
+        <v>41</v>
       </c>
       <c r="F159" t="s">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="G159" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="H159" t="s">
         <v>18</v>
@@ -5861,25 +5918,25 @@
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B160" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C160" t="s">
         <v>110</v>
       </c>
       <c r="D160" t="s">
-        <v>195</v>
+        <v>66</v>
       </c>
       <c r="E160" t="s">
         <v>112</v>
       </c>
       <c r="F160" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="G160" t="s">
-        <v>114</v>
+        <v>186</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
@@ -5890,16 +5947,16 @@
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B161" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C161" t="s">
         <v>20</v>
       </c>
       <c r="D161" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -5919,83 +5976,83 @@
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B162" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C162" t="s">
-        <v>24</v>
+        <v>189</v>
       </c>
       <c r="D162" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="E162" t="s">
-        <v>51</v>
+        <v>190</v>
       </c>
       <c r="F162" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="G162" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="H162" t="s">
-        <v>18</v>
+        <v>191</v>
       </c>
       <c r="I162" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B163" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C163" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D163" t="s">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="E163" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="F163" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="G163" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="H163" t="s">
         <v>18</v>
       </c>
       <c r="I163" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B164" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C164" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D164" t="s">
-        <v>111</v>
+        <v>187</v>
       </c>
       <c r="E164" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F164" t="s">
-        <v>23</v>
+        <v>198</v>
       </c>
       <c r="G164" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="H164" t="s">
         <v>18</v>
@@ -6006,25 +6063,25 @@
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B165" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C165" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="D165" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E165" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F165" t="s">
-        <v>118</v>
+        <v>185</v>
       </c>
       <c r="G165" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H165" t="s">
         <v>18</v>
@@ -6035,25 +6092,25 @@
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B166" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C166" t="s">
         <v>110</v>
       </c>
       <c r="D166" t="s">
-        <v>195</v>
+        <v>66</v>
       </c>
       <c r="E166" t="s">
         <v>112</v>
       </c>
       <c r="F166" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="G166" t="s">
-        <v>114</v>
+        <v>186</v>
       </c>
       <c r="H166" t="s">
         <v>18</v>
@@ -6064,16 +6121,16 @@
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B167" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C167" t="s">
         <v>20</v>
       </c>
       <c r="D167" t="s">
-        <v>70</v>
+        <v>197</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -6093,54 +6150,54 @@
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B168" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C168" t="s">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="D168" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E168" t="s">
-        <v>41</v>
+        <v>190</v>
       </c>
       <c r="F168" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="G168" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="H168" t="s">
-        <v>18</v>
+        <v>191</v>
       </c>
       <c r="I168" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B169" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C169" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D169" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="E169" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F169" t="s">
-        <v>75</v>
+        <v>198</v>
       </c>
       <c r="G169" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="H169" t="s">
         <v>18</v>
@@ -6151,54 +6208,54 @@
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
+        <v>183</v>
+      </c>
+      <c r="B170" t="s">
+        <v>77</v>
+      </c>
+      <c r="C170" t="s">
+        <v>192</v>
+      </c>
+      <c r="D170" t="s">
+        <v>202</v>
+      </c>
+      <c r="E170" t="s">
+        <v>38</v>
+      </c>
+      <c r="F170" t="s">
+        <v>198</v>
+      </c>
+      <c r="G170" t="s">
         <v>194</v>
       </c>
-      <c r="B170" t="s">
-        <v>44</v>
-      </c>
-      <c r="C170" t="s">
-        <v>60</v>
-      </c>
-      <c r="D170" t="s">
-        <v>198</v>
-      </c>
-      <c r="E170" t="s">
-        <v>15</v>
-      </c>
-      <c r="F170" t="s">
-        <v>75</v>
-      </c>
-      <c r="G170" t="s">
-        <v>197</v>
-      </c>
       <c r="H170" t="s">
         <v>18</v>
       </c>
       <c r="I170" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B171" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C171" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D171" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="E171" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="F171" t="s">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="G171" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="H171" t="s">
         <v>18</v>
@@ -6209,83 +6266,83 @@
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B172" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C172" t="s">
-        <v>110</v>
+        <v>189</v>
       </c>
       <c r="D172" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E172" t="s">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="F172" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="G172" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="H172" t="s">
-        <v>18</v>
+        <v>191</v>
       </c>
       <c r="I172" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B173" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C173" t="s">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="D173" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="E173" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F173" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="G173" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H173" t="s">
         <v>18</v>
       </c>
       <c r="I173" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B174" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C174" t="s">
         <v>124</v>
       </c>
       <c r="D174" t="s">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="E174" t="s">
         <v>41</v>
       </c>
       <c r="F174" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="G174" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="H174" t="s">
         <v>18</v>
@@ -6296,112 +6353,112 @@
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B175" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C175" t="s">
-        <v>60</v>
+        <v>189</v>
       </c>
       <c r="D175" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="E175" t="s">
-        <v>99</v>
+        <v>190</v>
       </c>
       <c r="F175" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="G175" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H175" t="s">
-        <v>18</v>
+        <v>191</v>
       </c>
       <c r="I175" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="15">
       <c r="A176" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B176" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C176" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="D176" t="s">
-        <v>50</v>
+        <v>204</v>
       </c>
       <c r="E176" t="s">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="F176" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G176" t="s">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="H176" t="s">
         <v>18</v>
       </c>
       <c r="I176" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15">
       <c r="A177" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B177" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="C177" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="D177" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E177" t="s">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="F177" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="G177" t="s">
-        <v>114</v>
+        <v>176</v>
       </c>
       <c r="H177" t="s">
         <v>18</v>
       </c>
       <c r="I177" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="15">
       <c r="A178" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B178" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="C178" t="s">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="D178" t="s">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="E178" t="s">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="F178" t="s">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="G178" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="H178" t="s">
         <v>18</v>
@@ -6412,25 +6469,25 @@
     </row>
     <row r="179" spans="1:9" ht="15">
       <c r="A179" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B179" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="C179" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="D179" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="E179" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="F179" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="G179" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="H179" t="s">
         <v>18</v>
@@ -6441,28 +6498,28 @@
     </row>
     <row r="180" spans="1:9" ht="15">
       <c r="A180" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B180" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="C180" t="s">
-        <v>124</v>
+        <v>206</v>
       </c>
       <c r="D180" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E180" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F180" t="s">
-        <v>102</v>
+        <v>207</v>
       </c>
       <c r="G180" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H180" t="s">
-        <v>201</v>
+        <v>18</v>
       </c>
       <c r="I180" t="s">
         <v>19</v>
@@ -6470,25 +6527,25 @@
     </row>
     <row r="181" spans="1:9" ht="15">
       <c r="A181" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B181" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="C181" t="s">
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="D181" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="E181" t="s">
-        <v>37</v>
+        <v>208</v>
       </c>
       <c r="F181" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="G181" t="s">
-        <v>86</v>
+        <v>186</v>
       </c>
       <c r="H181" t="s">
         <v>18</v>
@@ -6499,25 +6556,25 @@
     </row>
     <row r="182" spans="1:9" ht="15">
       <c r="A182" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B182" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="C182" t="s">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="D182" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="E182" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="F182" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="G182" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H182" t="s">
         <v>18</v>
@@ -6528,54 +6585,54 @@
     </row>
     <row r="183" spans="1:9" ht="15">
       <c r="A183" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B183" t="s">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="C183" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="D183" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="E183" t="s">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="F183" t="s">
-        <v>113</v>
+        <v>207</v>
       </c>
       <c r="G183" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="H183" t="s">
         <v>18</v>
       </c>
       <c r="I183" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="15">
       <c r="A184" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="C184" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D184" t="s">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="E184" t="s">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="F184" t="s">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="G184" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="H184" t="s">
         <v>18</v>
@@ -6586,54 +6643,54 @@
     </row>
     <row r="185" spans="1:9" ht="15">
       <c r="A185" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="C185" t="s">
-        <v>32</v>
+        <v>147</v>
       </c>
       <c r="D185" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="E185" t="s">
-        <v>99</v>
+        <v>208</v>
       </c>
       <c r="F185" t="s">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="G185" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H185" t="s">
         <v>18</v>
       </c>
       <c r="I185" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="15">
       <c r="A186" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B186" t="s">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="C186" t="s">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="D186" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="E186" t="s">
-        <v>99</v>
+        <v>208</v>
       </c>
       <c r="F186" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="G186" t="s">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="H186" t="s">
         <v>18</v>
@@ -6644,54 +6701,54 @@
     </row>
     <row r="187" spans="1:9" ht="15">
       <c r="A187" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B187" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="C187" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D187" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="E187" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F187" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="G187" t="s">
-        <v>175</v>
+        <v>114</v>
       </c>
       <c r="H187" t="s">
         <v>18</v>
       </c>
       <c r="I187" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="15">
       <c r="A188" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B188" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="C188" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D188" t="s">
-        <v>50</v>
+        <v>195</v>
       </c>
       <c r="E188" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="F188" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="G188" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="H188" t="s">
         <v>18</v>
@@ -6702,25 +6759,25 @@
     </row>
     <row r="189" spans="1:9" ht="15">
       <c r="A189" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B189" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="C189" t="s">
-        <v>148</v>
+        <v>24</v>
       </c>
       <c r="D189" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E189" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="F189" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="G189" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H189" t="s">
         <v>18</v>
@@ -6731,112 +6788,112 @@
     </row>
     <row r="190" spans="1:9" ht="15">
       <c r="A190" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B190" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="C190" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="D190" t="s">
-        <v>132</v>
+        <v>211</v>
       </c>
       <c r="E190" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F190" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="G190" t="s">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="H190" t="s">
         <v>18</v>
       </c>
       <c r="I190" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="15">
       <c r="A191" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B191" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="C191" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D191" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="E191" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="F191" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="G191" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H191" t="s">
         <v>18</v>
       </c>
       <c r="I191" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="15">
       <c r="A192" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B192" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="C192" t="s">
-        <v>60</v>
+        <v>189</v>
       </c>
       <c r="D192" t="s">
-        <v>70</v>
+        <v>195</v>
       </c>
       <c r="E192" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="F192" t="s">
-        <v>203</v>
+        <v>131</v>
       </c>
       <c r="G192" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="H192" t="s">
-        <v>18</v>
+        <v>191</v>
       </c>
       <c r="I192" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="15">
       <c r="A193" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B193" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="C193" t="s">
-        <v>171</v>
+        <v>24</v>
       </c>
       <c r="D193" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="E193" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="F193" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="G193" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H193" t="s">
         <v>18</v>
@@ -6847,54 +6904,54 @@
     </row>
     <row r="194" spans="1:9" ht="15">
       <c r="A194" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B194" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="C194" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="D194" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E194" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="F194" t="s">
-        <v>199</v>
+        <v>113</v>
       </c>
       <c r="G194" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="H194" t="s">
         <v>18</v>
       </c>
       <c r="I194" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="15">
       <c r="A195" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B195" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="C195" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D195" t="s">
-        <v>132</v>
+        <v>70</v>
       </c>
       <c r="E195" t="s">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="F195" t="s">
-        <v>141</v>
+        <v>23</v>
       </c>
       <c r="G195" t="s">
-        <v>175</v>
+        <v>104</v>
       </c>
       <c r="H195" t="s">
         <v>18</v>
@@ -6905,30 +6962,1248 @@
     </row>
     <row r="196" spans="1:9" ht="15">
       <c r="A196" t="s">
+        <v>210</v>
+      </c>
+      <c r="B196" t="s">
+        <v>44</v>
+      </c>
+      <c r="C196" t="s">
+        <v>124</v>
+      </c>
+      <c r="D196" t="s">
+        <v>212</v>
+      </c>
+      <c r="E196" t="s">
+        <v>41</v>
+      </c>
+      <c r="F196" t="s">
+        <v>102</v>
+      </c>
+      <c r="G196" t="s">
+        <v>134</v>
+      </c>
+      <c r="H196" t="s">
+        <v>18</v>
+      </c>
+      <c r="I196" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="15">
+      <c r="A197" t="s">
+        <v>210</v>
+      </c>
+      <c r="B197" t="s">
+        <v>44</v>
+      </c>
+      <c r="C197" t="s">
+        <v>189</v>
+      </c>
+      <c r="D197" t="s">
+        <v>203</v>
+      </c>
+      <c r="E197" t="s">
+        <v>190</v>
+      </c>
+      <c r="F197" t="s">
+        <v>131</v>
+      </c>
+      <c r="G197" t="s">
+        <v>19</v>
+      </c>
+      <c r="H197" t="s">
+        <v>191</v>
+      </c>
+      <c r="I197" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="15">
+      <c r="A198" t="s">
+        <v>210</v>
+      </c>
+      <c r="B198" t="s">
+        <v>44</v>
+      </c>
+      <c r="C198" t="s">
+        <v>60</v>
+      </c>
+      <c r="D198" t="s">
+        <v>167</v>
+      </c>
+      <c r="E198" t="s">
+        <v>15</v>
+      </c>
+      <c r="F198" t="s">
+        <v>75</v>
+      </c>
+      <c r="G198" t="s">
+        <v>213</v>
+      </c>
+      <c r="H198" t="s">
+        <v>18</v>
+      </c>
+      <c r="I198" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="15">
+      <c r="A199" t="s">
+        <v>210</v>
+      </c>
+      <c r="B199" t="s">
+        <v>44</v>
+      </c>
+      <c r="C199" t="s">
+        <v>60</v>
+      </c>
+      <c r="D199" t="s">
+        <v>158</v>
+      </c>
+      <c r="E199" t="s">
+        <v>15</v>
+      </c>
+      <c r="F199" t="s">
+        <v>75</v>
+      </c>
+      <c r="G199" t="s">
+        <v>213</v>
+      </c>
+      <c r="H199" t="s">
+        <v>18</v>
+      </c>
+      <c r="I199" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="15">
+      <c r="A200" t="s">
+        <v>210</v>
+      </c>
+      <c r="B200" t="s">
+        <v>44</v>
+      </c>
+      <c r="C200" t="s">
+        <v>24</v>
+      </c>
+      <c r="D200" t="s">
+        <v>50</v>
+      </c>
+      <c r="E200" t="s">
+        <v>97</v>
+      </c>
+      <c r="F200" t="s">
+        <v>118</v>
+      </c>
+      <c r="G200" t="s">
+        <v>80</v>
+      </c>
+      <c r="H200" t="s">
+        <v>18</v>
+      </c>
+      <c r="I200" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="15">
+      <c r="A201" t="s">
+        <v>210</v>
+      </c>
+      <c r="B201" t="s">
+        <v>54</v>
+      </c>
+      <c r="C201" t="s">
+        <v>110</v>
+      </c>
+      <c r="D201" t="s">
+        <v>211</v>
+      </c>
+      <c r="E201" t="s">
+        <v>112</v>
+      </c>
+      <c r="F201" t="s">
+        <v>113</v>
+      </c>
+      <c r="G201" t="s">
+        <v>114</v>
+      </c>
+      <c r="H201" t="s">
+        <v>18</v>
+      </c>
+      <c r="I201" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="15">
+      <c r="A202" t="s">
+        <v>210</v>
+      </c>
+      <c r="B202" t="s">
+        <v>54</v>
+      </c>
+      <c r="C202" t="s">
+        <v>20</v>
+      </c>
+      <c r="D202" t="s">
+        <v>132</v>
+      </c>
+      <c r="E202" t="s">
+        <v>22</v>
+      </c>
+      <c r="F202" t="s">
+        <v>23</v>
+      </c>
+      <c r="G202" t="s">
+        <v>104</v>
+      </c>
+      <c r="H202" t="s">
+        <v>18</v>
+      </c>
+      <c r="I202" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="15">
+      <c r="A203" t="s">
+        <v>210</v>
+      </c>
+      <c r="B203" t="s">
+        <v>54</v>
+      </c>
+      <c r="C203" t="s">
+        <v>124</v>
+      </c>
+      <c r="D203" t="s">
+        <v>212</v>
+      </c>
+      <c r="E203" t="s">
+        <v>41</v>
+      </c>
+      <c r="F203" t="s">
+        <v>102</v>
+      </c>
+      <c r="G203" t="s">
+        <v>134</v>
+      </c>
+      <c r="H203" t="s">
+        <v>18</v>
+      </c>
+      <c r="I203" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="15">
+      <c r="A204" t="s">
+        <v>210</v>
+      </c>
+      <c r="B204" t="s">
+        <v>54</v>
+      </c>
+      <c r="C204" t="s">
+        <v>189</v>
+      </c>
+      <c r="D204" t="s">
+        <v>136</v>
+      </c>
+      <c r="E204" t="s">
+        <v>190</v>
+      </c>
+      <c r="F204" t="s">
+        <v>88</v>
+      </c>
+      <c r="G204" t="s">
+        <v>19</v>
+      </c>
+      <c r="H204" t="s">
+        <v>191</v>
+      </c>
+      <c r="I204" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" ht="15">
+      <c r="A205" t="s">
+        <v>210</v>
+      </c>
+      <c r="B205" t="s">
+        <v>54</v>
+      </c>
+      <c r="C205" t="s">
+        <v>60</v>
+      </c>
+      <c r="D205" t="s">
+        <v>197</v>
+      </c>
+      <c r="E205" t="s">
+        <v>99</v>
+      </c>
+      <c r="F205" t="s">
+        <v>140</v>
+      </c>
+      <c r="G205" t="s">
+        <v>32</v>
+      </c>
+      <c r="H205" t="s">
+        <v>18</v>
+      </c>
+      <c r="I205" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" ht="15">
+      <c r="A206" t="s">
+        <v>210</v>
+      </c>
+      <c r="B206" t="s">
+        <v>54</v>
+      </c>
+      <c r="C206" t="s">
+        <v>24</v>
+      </c>
+      <c r="D206" t="s">
+        <v>50</v>
+      </c>
+      <c r="E206" t="s">
+        <v>97</v>
+      </c>
+      <c r="F206" t="s">
+        <v>173</v>
+      </c>
+      <c r="G206" t="s">
+        <v>80</v>
+      </c>
+      <c r="H206" t="s">
+        <v>18</v>
+      </c>
+      <c r="I206" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" ht="15">
+      <c r="A207" t="s">
+        <v>210</v>
+      </c>
+      <c r="B207" t="s">
+        <v>65</v>
+      </c>
+      <c r="C207" t="s">
+        <v>78</v>
+      </c>
+      <c r="D207" t="s">
+        <v>214</v>
+      </c>
+      <c r="E207" t="s">
+        <v>41</v>
+      </c>
+      <c r="F207" t="s">
+        <v>215</v>
+      </c>
+      <c r="G207" t="s">
+        <v>134</v>
+      </c>
+      <c r="H207" t="s">
+        <v>18</v>
+      </c>
+      <c r="I207" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" ht="15">
+      <c r="A208" t="s">
+        <v>210</v>
+      </c>
+      <c r="B208" t="s">
+        <v>65</v>
+      </c>
+      <c r="C208" t="s">
+        <v>110</v>
+      </c>
+      <c r="D208" t="s">
+        <v>211</v>
+      </c>
+      <c r="E208" t="s">
+        <v>112</v>
+      </c>
+      <c r="F208" t="s">
+        <v>113</v>
+      </c>
+      <c r="G208" t="s">
+        <v>114</v>
+      </c>
+      <c r="H208" t="s">
+        <v>18</v>
+      </c>
+      <c r="I208" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" ht="15">
+      <c r="A209" t="s">
+        <v>210</v>
+      </c>
+      <c r="B209" t="s">
+        <v>65</v>
+      </c>
+      <c r="C209" t="s">
+        <v>147</v>
+      </c>
+      <c r="D209" t="s">
+        <v>148</v>
+      </c>
+      <c r="E209" t="s">
+        <v>168</v>
+      </c>
+      <c r="F209" t="s">
+        <v>169</v>
+      </c>
+      <c r="G209" t="s">
+        <v>170</v>
+      </c>
+      <c r="H209" t="s">
+        <v>18</v>
+      </c>
+      <c r="I209" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" ht="15">
+      <c r="A210" t="s">
+        <v>210</v>
+      </c>
+      <c r="B210" t="s">
+        <v>65</v>
+      </c>
+      <c r="C210" t="s">
+        <v>20</v>
+      </c>
+      <c r="D210" t="s">
+        <v>70</v>
+      </c>
+      <c r="E210" t="s">
+        <v>99</v>
+      </c>
+      <c r="F210" t="s">
+        <v>23</v>
+      </c>
+      <c r="G210" t="s">
+        <v>104</v>
+      </c>
+      <c r="H210" t="s">
+        <v>18</v>
+      </c>
+      <c r="I210" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" ht="15">
+      <c r="A211" t="s">
+        <v>210</v>
+      </c>
+      <c r="B211" t="s">
+        <v>65</v>
+      </c>
+      <c r="C211" t="s">
+        <v>124</v>
+      </c>
+      <c r="D211" t="s">
+        <v>212</v>
+      </c>
+      <c r="E211" t="s">
+        <v>41</v>
+      </c>
+      <c r="F211" t="s">
+        <v>102</v>
+      </c>
+      <c r="G211" t="s">
+        <v>98</v>
+      </c>
+      <c r="H211" t="s">
+        <v>216</v>
+      </c>
+      <c r="I211" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" ht="15">
+      <c r="A212" t="s">
+        <v>210</v>
+      </c>
+      <c r="B212" t="s">
+        <v>65</v>
+      </c>
+      <c r="C212" t="s">
+        <v>189</v>
+      </c>
+      <c r="D212" t="s">
+        <v>136</v>
+      </c>
+      <c r="E212" t="s">
+        <v>190</v>
+      </c>
+      <c r="F212" t="s">
+        <v>88</v>
+      </c>
+      <c r="G212" t="s">
+        <v>19</v>
+      </c>
+      <c r="H212" t="s">
+        <v>191</v>
+      </c>
+      <c r="I212" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" ht="15">
+      <c r="A213" t="s">
+        <v>210</v>
+      </c>
+      <c r="B213" t="s">
+        <v>65</v>
+      </c>
+      <c r="C213" t="s">
+        <v>60</v>
+      </c>
+      <c r="D213" t="s">
+        <v>202</v>
+      </c>
+      <c r="E213" t="s">
+        <v>37</v>
+      </c>
+      <c r="F213" t="s">
+        <v>16</v>
+      </c>
+      <c r="G213" t="s">
+        <v>86</v>
+      </c>
+      <c r="H213" t="s">
+        <v>18</v>
+      </c>
+      <c r="I213" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" ht="15">
+      <c r="A214" t="s">
+        <v>210</v>
+      </c>
+      <c r="B214" t="s">
+        <v>65</v>
+      </c>
+      <c r="C214" t="s">
+        <v>24</v>
+      </c>
+      <c r="D214" t="s">
+        <v>50</v>
+      </c>
+      <c r="E214" t="s">
+        <v>97</v>
+      </c>
+      <c r="F214" t="s">
+        <v>173</v>
+      </c>
+      <c r="G214" t="s">
+        <v>80</v>
+      </c>
+      <c r="H214" t="s">
+        <v>18</v>
+      </c>
+      <c r="I214" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" ht="15">
+      <c r="A215" t="s">
+        <v>210</v>
+      </c>
+      <c r="B215" t="s">
+        <v>77</v>
+      </c>
+      <c r="C215" t="s">
+        <v>78</v>
+      </c>
+      <c r="D215" t="s">
+        <v>214</v>
+      </c>
+      <c r="E215" t="s">
+        <v>41</v>
+      </c>
+      <c r="F215" t="s">
+        <v>215</v>
+      </c>
+      <c r="G215" t="s">
+        <v>134</v>
+      </c>
+      <c r="H215" t="s">
+        <v>18</v>
+      </c>
+      <c r="I215" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="15">
+      <c r="A216" t="s">
+        <v>210</v>
+      </c>
+      <c r="B216" t="s">
+        <v>77</v>
+      </c>
+      <c r="C216" t="s">
+        <v>110</v>
+      </c>
+      <c r="D216" t="s">
+        <v>211</v>
+      </c>
+      <c r="E216" t="s">
+        <v>112</v>
+      </c>
+      <c r="F216" t="s">
+        <v>113</v>
+      </c>
+      <c r="G216" t="s">
+        <v>114</v>
+      </c>
+      <c r="H216" t="s">
+        <v>18</v>
+      </c>
+      <c r="I216" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" ht="15">
+      <c r="A217" t="s">
+        <v>210</v>
+      </c>
+      <c r="B217" t="s">
+        <v>77</v>
+      </c>
+      <c r="C217" t="s">
+        <v>147</v>
+      </c>
+      <c r="D217" t="s">
+        <v>217</v>
+      </c>
+      <c r="E217" t="s">
+        <v>84</v>
+      </c>
+      <c r="F217" t="s">
+        <v>31</v>
+      </c>
+      <c r="G217" t="s">
+        <v>85</v>
+      </c>
+      <c r="H217" t="s">
+        <v>18</v>
+      </c>
+      <c r="I217" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" ht="15">
+      <c r="A218" t="s">
+        <v>210</v>
+      </c>
+      <c r="B218" t="s">
+        <v>77</v>
+      </c>
+      <c r="C218" t="s">
+        <v>32</v>
+      </c>
+      <c r="D218" t="s">
+        <v>132</v>
+      </c>
+      <c r="E218" t="s">
+        <v>99</v>
+      </c>
+      <c r="F218" t="s">
+        <v>31</v>
+      </c>
+      <c r="G218" t="s">
         <v>194</v>
       </c>
-      <c r="B196" t="s">
+      <c r="H218" t="s">
+        <v>18</v>
+      </c>
+      <c r="I218" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" ht="15">
+      <c r="A219" t="s">
+        <v>210</v>
+      </c>
+      <c r="B219" t="s">
+        <v>77</v>
+      </c>
+      <c r="C219" t="s">
+        <v>20</v>
+      </c>
+      <c r="D219" t="s">
+        <v>70</v>
+      </c>
+      <c r="E219" t="s">
+        <v>99</v>
+      </c>
+      <c r="F219" t="s">
+        <v>23</v>
+      </c>
+      <c r="G219" t="s">
+        <v>104</v>
+      </c>
+      <c r="H219" t="s">
+        <v>18</v>
+      </c>
+      <c r="I219" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" ht="15">
+      <c r="A220" t="s">
+        <v>210</v>
+      </c>
+      <c r="B220" t="s">
+        <v>77</v>
+      </c>
+      <c r="C220" t="s">
+        <v>189</v>
+      </c>
+      <c r="D220" t="s">
+        <v>148</v>
+      </c>
+      <c r="E220" t="s">
+        <v>190</v>
+      </c>
+      <c r="F220" t="s">
+        <v>88</v>
+      </c>
+      <c r="G220" t="s">
+        <v>19</v>
+      </c>
+      <c r="H220" t="s">
+        <v>191</v>
+      </c>
+      <c r="I220" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" ht="15">
+      <c r="A221" t="s">
+        <v>210</v>
+      </c>
+      <c r="B221" t="s">
+        <v>77</v>
+      </c>
+      <c r="C221" t="s">
+        <v>60</v>
+      </c>
+      <c r="D221" t="s">
+        <v>138</v>
+      </c>
+      <c r="E221" t="s">
+        <v>99</v>
+      </c>
+      <c r="F221" t="s">
+        <v>100</v>
+      </c>
+      <c r="G221" t="s">
+        <v>186</v>
+      </c>
+      <c r="H221" t="s">
+        <v>18</v>
+      </c>
+      <c r="I221" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" ht="15">
+      <c r="A222" t="s">
+        <v>210</v>
+      </c>
+      <c r="B222" t="s">
+        <v>77</v>
+      </c>
+      <c r="C222" t="s">
+        <v>24</v>
+      </c>
+      <c r="D222" t="s">
+        <v>50</v>
+      </c>
+      <c r="E222" t="s">
+        <v>97</v>
+      </c>
+      <c r="F222" t="s">
+        <v>75</v>
+      </c>
+      <c r="G222" t="s">
+        <v>80</v>
+      </c>
+      <c r="H222" t="s">
+        <v>18</v>
+      </c>
+      <c r="I222" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" ht="15">
+      <c r="A223" t="s">
+        <v>210</v>
+      </c>
+      <c r="B223" t="s">
+        <v>87</v>
+      </c>
+      <c r="C223" t="s">
+        <v>78</v>
+      </c>
+      <c r="D223" t="s">
+        <v>214</v>
+      </c>
+      <c r="E223" t="s">
+        <v>41</v>
+      </c>
+      <c r="F223" t="s">
+        <v>215</v>
+      </c>
+      <c r="G223" t="s">
+        <v>134</v>
+      </c>
+      <c r="H223" t="s">
+        <v>18</v>
+      </c>
+      <c r="I223" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" ht="15">
+      <c r="A224" t="s">
+        <v>210</v>
+      </c>
+      <c r="B224" t="s">
+        <v>87</v>
+      </c>
+      <c r="C224" t="s">
+        <v>142</v>
+      </c>
+      <c r="D224" t="s">
+        <v>209</v>
+      </c>
+      <c r="E224" t="s">
+        <v>46</v>
+      </c>
+      <c r="F224" t="s">
+        <v>47</v>
+      </c>
+      <c r="G224" t="s">
+        <v>218</v>
+      </c>
+      <c r="H224" t="s">
+        <v>18</v>
+      </c>
+      <c r="I224" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" ht="15">
+      <c r="A225" t="s">
+        <v>210</v>
+      </c>
+      <c r="B225" t="s">
+        <v>87</v>
+      </c>
+      <c r="C225" t="s">
+        <v>147</v>
+      </c>
+      <c r="D225" t="s">
+        <v>197</v>
+      </c>
+      <c r="E225" t="s">
+        <v>22</v>
+      </c>
+      <c r="F225" t="s">
+        <v>100</v>
+      </c>
+      <c r="G225" t="s">
+        <v>114</v>
+      </c>
+      <c r="H225" t="s">
+        <v>18</v>
+      </c>
+      <c r="I225" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" ht="15">
+      <c r="A226" t="s">
+        <v>210</v>
+      </c>
+      <c r="B226" t="s">
+        <v>87</v>
+      </c>
+      <c r="C226" t="s">
+        <v>32</v>
+      </c>
+      <c r="D226" t="s">
+        <v>132</v>
+      </c>
+      <c r="E226" t="s">
+        <v>99</v>
+      </c>
+      <c r="F226" t="s">
+        <v>31</v>
+      </c>
+      <c r="G226" t="s">
+        <v>194</v>
+      </c>
+      <c r="H226" t="s">
+        <v>18</v>
+      </c>
+      <c r="I226" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" ht="15">
+      <c r="A227" t="s">
+        <v>210</v>
+      </c>
+      <c r="B227" t="s">
+        <v>87</v>
+      </c>
+      <c r="C227" t="s">
+        <v>189</v>
+      </c>
+      <c r="D227" t="s">
+        <v>217</v>
+      </c>
+      <c r="E227" t="s">
+        <v>190</v>
+      </c>
+      <c r="F227" t="s">
+        <v>88</v>
+      </c>
+      <c r="G227" t="s">
+        <v>19</v>
+      </c>
+      <c r="H227" t="s">
+        <v>191</v>
+      </c>
+      <c r="I227" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" ht="15">
+      <c r="A228" t="s">
+        <v>210</v>
+      </c>
+      <c r="B228" t="s">
+        <v>87</v>
+      </c>
+      <c r="C228" t="s">
+        <v>60</v>
+      </c>
+      <c r="D228" t="s">
+        <v>138</v>
+      </c>
+      <c r="E228" t="s">
+        <v>99</v>
+      </c>
+      <c r="F228" t="s">
+        <v>63</v>
+      </c>
+      <c r="G228" t="s">
+        <v>103</v>
+      </c>
+      <c r="H228" t="s">
+        <v>18</v>
+      </c>
+      <c r="I228" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" ht="15">
+      <c r="A229" t="s">
+        <v>210</v>
+      </c>
+      <c r="B229" t="s">
+        <v>101</v>
+      </c>
+      <c r="C229" t="s">
+        <v>78</v>
+      </c>
+      <c r="D229" t="s">
+        <v>197</v>
+      </c>
+      <c r="E229" t="s">
+        <v>38</v>
+      </c>
+      <c r="F229" t="s">
+        <v>198</v>
+      </c>
+      <c r="G229" t="s">
+        <v>134</v>
+      </c>
+      <c r="H229" t="s">
+        <v>18</v>
+      </c>
+      <c r="I229" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" ht="15">
+      <c r="A230" t="s">
+        <v>210</v>
+      </c>
+      <c r="B230" t="s">
+        <v>101</v>
+      </c>
+      <c r="C230" t="s">
+        <v>142</v>
+      </c>
+      <c r="D230" t="s">
+        <v>209</v>
+      </c>
+      <c r="E230" t="s">
+        <v>41</v>
+      </c>
+      <c r="F230" t="s">
+        <v>102</v>
+      </c>
+      <c r="G230" t="s">
+        <v>39</v>
+      </c>
+      <c r="H230" t="s">
+        <v>18</v>
+      </c>
+      <c r="I230" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" ht="15">
+      <c r="A231" t="s">
+        <v>210</v>
+      </c>
+      <c r="B231" t="s">
+        <v>101</v>
+      </c>
+      <c r="C231" t="s">
+        <v>189</v>
+      </c>
+      <c r="D231" t="s">
+        <v>196</v>
+      </c>
+      <c r="E231" t="s">
+        <v>190</v>
+      </c>
+      <c r="F231" t="s">
+        <v>131</v>
+      </c>
+      <c r="G231" t="s">
+        <v>19</v>
+      </c>
+      <c r="H231" t="s">
+        <v>191</v>
+      </c>
+      <c r="I231" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" ht="15">
+      <c r="A232" t="s">
+        <v>210</v>
+      </c>
+      <c r="B232" t="s">
+        <v>101</v>
+      </c>
+      <c r="C232" t="s">
+        <v>60</v>
+      </c>
+      <c r="D232" t="s">
+        <v>70</v>
+      </c>
+      <c r="E232" t="s">
+        <v>84</v>
+      </c>
+      <c r="F232" t="s">
+        <v>219</v>
+      </c>
+      <c r="G232" t="s">
+        <v>85</v>
+      </c>
+      <c r="H232" t="s">
+        <v>18</v>
+      </c>
+      <c r="I232" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" ht="15">
+      <c r="A233" t="s">
+        <v>210</v>
+      </c>
+      <c r="B233" t="s">
+        <v>101</v>
+      </c>
+      <c r="C233" t="s">
+        <v>180</v>
+      </c>
+      <c r="D233" t="s">
+        <v>181</v>
+      </c>
+      <c r="E233" t="s">
+        <v>94</v>
+      </c>
+      <c r="F233" t="s">
+        <v>16</v>
+      </c>
+      <c r="G233" t="s">
+        <v>55</v>
+      </c>
+      <c r="H233" t="s">
+        <v>18</v>
+      </c>
+      <c r="I233" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="15">
+      <c r="A234" t="s">
+        <v>210</v>
+      </c>
+      <c r="B234" t="s">
+        <v>101</v>
+      </c>
+      <c r="C234" t="s">
+        <v>220</v>
+      </c>
+      <c r="D234" t="s">
+        <v>217</v>
+      </c>
+      <c r="E234" t="s">
+        <v>37</v>
+      </c>
+      <c r="F234" t="s">
+        <v>169</v>
+      </c>
+      <c r="G234" t="s">
+        <v>221</v>
+      </c>
+      <c r="H234" t="s">
+        <v>18</v>
+      </c>
+      <c r="I234" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" ht="15">
+      <c r="A235" t="s">
+        <v>210</v>
+      </c>
+      <c r="B235" t="s">
         <v>105</v>
       </c>
-      <c r="C196" t="s">
-        <v>204</v>
-      </c>
-      <c r="D196" t="s">
-        <v>202</v>
-      </c>
-      <c r="E196" t="s">
+      <c r="C235" t="s">
+        <v>142</v>
+      </c>
+      <c r="D235" t="s">
+        <v>209</v>
+      </c>
+      <c r="E235" t="s">
+        <v>41</v>
+      </c>
+      <c r="F235" t="s">
+        <v>102</v>
+      </c>
+      <c r="G235" t="s">
+        <v>39</v>
+      </c>
+      <c r="H235" t="s">
+        <v>18</v>
+      </c>
+      <c r="I235" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" ht="15">
+      <c r="A236" t="s">
+        <v>210</v>
+      </c>
+      <c r="B236" t="s">
+        <v>105</v>
+      </c>
+      <c r="C236" t="s">
+        <v>189</v>
+      </c>
+      <c r="D236" t="s">
+        <v>50</v>
+      </c>
+      <c r="E236" t="s">
+        <v>190</v>
+      </c>
+      <c r="F236" t="s">
+        <v>131</v>
+      </c>
+      <c r="G236" t="s">
+        <v>19</v>
+      </c>
+      <c r="H236" t="s">
+        <v>191</v>
+      </c>
+      <c r="I236" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" ht="15">
+      <c r="A237" t="s">
+        <v>210</v>
+      </c>
+      <c r="B237" t="s">
+        <v>105</v>
+      </c>
+      <c r="C237" t="s">
+        <v>60</v>
+      </c>
+      <c r="D237" t="s">
+        <v>132</v>
+      </c>
+      <c r="E237" t="s">
+        <v>160</v>
+      </c>
+      <c r="F237" t="s">
+        <v>140</v>
+      </c>
+      <c r="G237" t="s">
+        <v>186</v>
+      </c>
+      <c r="H237" t="s">
+        <v>18</v>
+      </c>
+      <c r="I237" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" ht="15">
+      <c r="A238" t="s">
+        <v>210</v>
+      </c>
+      <c r="B238" t="s">
+        <v>105</v>
+      </c>
+      <c r="C238" t="s">
+        <v>220</v>
+      </c>
+      <c r="D238" t="s">
+        <v>217</v>
+      </c>
+      <c r="E238" t="s">
         <v>37</v>
       </c>
-      <c r="F196" t="s">
-        <v>199</v>
-      </c>
-      <c r="G196" t="s">
-        <v>205</v>
-      </c>
-      <c r="H196" t="s">
-        <v>18</v>
-      </c>
-      <c r="I196" t="s">
+      <c r="F238" t="s">
+        <v>169</v>
+      </c>
+      <c r="G238" t="s">
+        <v>221</v>
+      </c>
+      <c r="H238" t="s">
+        <v>18</v>
+      </c>
+      <c r="I238" t="s">
         <v>33</v>
       </c>
     </row>
@@ -6940,7 +8215,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{9d6baf38-db5d-4bb5-bd15-58a1dd8fee29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{caa65e29-8aa9-4f2a-9acb-f86055e209bf}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6960,16 +8235,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6989,16 +8264,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
         <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="E2" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -7018,16 +8293,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="E3" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -7047,16 +8322,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -7076,16 +8351,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="E5" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -7105,16 +8380,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="C6" t="s">
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E6" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -7134,16 +8409,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="C7" t="s">
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="E7" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -7163,16 +8438,16 @@
         <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="C8" t="s">
         <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="E8" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -7192,16 +8467,16 @@
         <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="C9" t="s">
         <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="E9" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -7221,16 +8496,16 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="C10" t="s">
         <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E10" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -7247,19 +8522,19 @@
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B11" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="E11" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -7282,16 +8557,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{22b2566a-3828-433f-8333-974abe91cdc2}">
-  <dimension ref="A1:F28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{367f1a54-3a01-42b0-ae0c-0b574d75d4f3}">
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="19.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
+    <col min="6" max="6" width="49" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="56.25" customHeight="1">
@@ -7299,13 +8574,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -7319,13 +8594,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="E2" t="s">
         <v>104</v>
@@ -7339,13 +8614,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="E3" t="s">
         <v>114</v>
@@ -7359,16 +8634,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="C4" t="s">
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="E4" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -7379,13 +8654,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E5" t="s">
         <v>32</v>
@@ -7399,13 +8674,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C6" t="s">
         <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
@@ -7419,16 +8694,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="E7" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -7439,16 +8714,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="C8" t="s">
         <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E8" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -7459,16 +8734,16 @@
         <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -7479,13 +8754,13 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="C10" t="s">
         <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
@@ -7499,16 +8774,16 @@
         <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="C11" t="s">
         <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -7519,13 +8794,13 @@
         <v>108</v>
       </c>
       <c r="B12" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="C12" t="s">
         <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -7539,13 +8814,13 @@
         <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="C13" t="s">
         <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E13" t="s">
         <v>129</v>
@@ -7559,13 +8834,13 @@
         <v>108</v>
       </c>
       <c r="B14" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="C14" t="s">
         <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -7579,13 +8854,13 @@
         <v>108</v>
       </c>
       <c r="B15" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="C15" t="s">
         <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -7599,13 +8874,13 @@
         <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="C16" t="s">
         <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
@@ -7619,16 +8894,16 @@
         <v>108</v>
       </c>
       <c r="B17" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="C17" t="s">
         <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E17" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -7639,16 +8914,16 @@
         <v>108</v>
       </c>
       <c r="B18" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="C18" t="s">
         <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E18" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -7659,13 +8934,13 @@
         <v>108</v>
       </c>
       <c r="B19" t="s">
+        <v>262</v>
+      </c>
+      <c r="C19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" t="s">
         <v>246</v>
-      </c>
-      <c r="C19" t="s">
-        <v>143</v>
-      </c>
-      <c r="D19" t="s">
-        <v>230</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -7676,19 +8951,19 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B20" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="D20" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -7696,19 +8971,19 @@
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B21" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -7716,19 +8991,19 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B22" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>186</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -7736,19 +9011,19 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="D23" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>133</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -7756,19 +9031,19 @@
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="B24" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="D24" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -7776,19 +9051,19 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="D25" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -7796,19 +9071,19 @@
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="B26" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -7816,16 +9091,16 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B27" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
@@ -7836,22 +9111,322 @@
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B28" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C28" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" t="s">
+        <v>252</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15">
+      <c r="A29" t="s">
+        <v>183</v>
+      </c>
+      <c r="B29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" t="s">
+        <v>252</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15">
+      <c r="A30" t="s">
+        <v>183</v>
+      </c>
+      <c r="B30" t="s">
+        <v>259</v>
+      </c>
+      <c r="C30" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" t="s">
+        <v>252</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15">
+      <c r="A31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B31" t="s">
+        <v>254</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s">
+        <v>248</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15">
+      <c r="A32" t="s">
+        <v>183</v>
+      </c>
+      <c r="B32" t="s">
+        <v>254</v>
+      </c>
+      <c r="C32" t="s">
+        <v>189</v>
+      </c>
+      <c r="D32" t="s">
+        <v>252</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15">
+      <c r="A33" t="s">
+        <v>210</v>
+      </c>
+      <c r="B33" t="s">
+        <v>245</v>
+      </c>
+      <c r="C33" t="s">
         <v>110</v>
       </c>
-      <c r="D28" t="s">
-        <v>232</v>
-      </c>
-      <c r="E28" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" t="s">
-        <v>18</v>
+      <c r="D33" t="s">
+        <v>246</v>
+      </c>
+      <c r="E33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15">
+      <c r="A34" t="s">
+        <v>210</v>
+      </c>
+      <c r="B34" t="s">
+        <v>258</v>
+      </c>
+      <c r="C34" t="s">
+        <v>189</v>
+      </c>
+      <c r="D34" t="s">
+        <v>252</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15">
+      <c r="A35" t="s">
+        <v>210</v>
+      </c>
+      <c r="B35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C35" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" t="s">
+        <v>248</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15">
+      <c r="A36" t="s">
+        <v>210</v>
+      </c>
+      <c r="B36" t="s">
+        <v>247</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" t="s">
+        <v>246</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15">
+      <c r="A37" t="s">
+        <v>210</v>
+      </c>
+      <c r="B37" t="s">
+        <v>251</v>
+      </c>
+      <c r="C37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" t="s">
+        <v>246</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15">
+      <c r="A38" t="s">
+        <v>210</v>
+      </c>
+      <c r="B38" t="s">
+        <v>251</v>
+      </c>
+      <c r="C38" t="s">
+        <v>110</v>
+      </c>
+      <c r="D38" t="s">
+        <v>248</v>
+      </c>
+      <c r="E38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15">
+      <c r="A39" t="s">
+        <v>210</v>
+      </c>
+      <c r="B39" t="s">
+        <v>251</v>
+      </c>
+      <c r="C39" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" t="s">
+        <v>252</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15">
+      <c r="A40" t="s">
+        <v>210</v>
+      </c>
+      <c r="B40" t="s">
+        <v>259</v>
+      </c>
+      <c r="C40" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40" t="s">
+        <v>248</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15">
+      <c r="A41" t="s">
+        <v>210</v>
+      </c>
+      <c r="B41" t="s">
+        <v>260</v>
+      </c>
+      <c r="C41" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41" t="s">
+        <v>252</v>
+      </c>
+      <c r="E41" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15">
+      <c r="A42" t="s">
+        <v>210</v>
+      </c>
+      <c r="B42" t="s">
+        <v>254</v>
+      </c>
+      <c r="C42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" t="s">
+        <v>265</v>
+      </c>
+      <c r="E42" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15">
+      <c r="A43" t="s">
+        <v>210</v>
+      </c>
+      <c r="B43" t="s">
+        <v>256</v>
+      </c>
+      <c r="C43" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" t="s">
+        <v>252</v>
+      </c>
+      <c r="E43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2501" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2702" uniqueCount="274">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -504,6 +504,12 @@
     <t>prf2</t>
   </si>
   <si>
+    <t>Smereka Alicja</t>
+  </si>
+  <si>
+    <t>Geografia</t>
+  </si>
+  <si>
     <t>Rozwój kompetencji zawodowych - barber</t>
   </si>
   <si>
@@ -540,6 +546,9 @@
     <t>2WA|JN2</t>
   </si>
   <si>
+    <t>p. Małecka, biologia za lekcję 8</t>
+  </si>
+  <si>
     <t>2K</t>
   </si>
   <si>
@@ -549,12 +558,18 @@
     <t>1FC|JA1</t>
   </si>
   <si>
+    <t>2TFA</t>
+  </si>
+  <si>
     <t>2K|CH</t>
   </si>
   <si>
     <t>Wojciechowski Łukasz</t>
   </si>
   <si>
+    <t>5TH|t.hand.</t>
+  </si>
+  <si>
     <t>2S|CH</t>
   </si>
   <si>
@@ -570,9 +585,18 @@
     <t>1WA|JN2</t>
   </si>
   <si>
+    <t>Fizyka</t>
+  </si>
+  <si>
+    <t>Biczysko Wojciech</t>
+  </si>
+  <si>
     <t>1WA|JN1</t>
   </si>
   <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>12.03.2026</t>
   </si>
   <si>
@@ -609,9 +633,6 @@
     <t>Brak</t>
   </si>
   <si>
-    <t>2TFA</t>
-  </si>
-  <si>
     <t>1K</t>
   </si>
   <si>
@@ -642,6 +663,9 @@
     <t>2B|JA2</t>
   </si>
   <si>
+    <t>3TH</t>
+  </si>
+  <si>
     <t>Granatowska Mariola</t>
   </si>
   <si>
@@ -681,9 +705,6 @@
     <t>Staliś Donata</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>Wakat2 matematyka</t>
   </si>
   <si>
@@ -820,6 +841,9 @@
   </si>
   <si>
     <t>piętro_3</t>
+  </si>
+  <si>
+    <t>Taszycka Magdalena</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1293,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{39c6e93d-debd-4fe5-bde7-6429f26e12fa}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{59a7aeed-91c6-4faa-b04a-20e763783371}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1290,14 +1314,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e98c8f7c-4105-4d91-821d-8405622da9b4}">
-  <dimension ref="A1:I238"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{45745967-a593-4b1e-850c-481e71f29bba}">
+  <dimension ref="A1:I257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
-    <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="11.8571428571429" customWidth="1"/>
     <col min="5" max="5" width="68.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
@@ -3981,16 +4005,16 @@
         <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="D93" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="E93" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F93" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G93" t="s">
         <v>17</v>
@@ -4010,25 +4034,25 @@
         <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="D94" t="s">
-        <v>161</v>
+        <v>59</v>
       </c>
       <c r="E94" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="F94" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="G94" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
@@ -4042,7 +4066,7 @@
         <v>115</v>
       </c>
       <c r="D95" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E95" t="s">
         <v>117</v>
@@ -4071,7 +4095,7 @@
         <v>115</v>
       </c>
       <c r="D96" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E96" t="s">
         <v>117</v>
@@ -4100,7 +4124,7 @@
         <v>115</v>
       </c>
       <c r="D97" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E97" t="s">
         <v>117</v>
@@ -4115,7 +4139,7 @@
         <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15">
@@ -4123,16 +4147,16 @@
         <v>157</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C98" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="D98" t="s">
         <v>166</v>
       </c>
       <c r="E98" t="s">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="F98" t="s">
         <v>118</v>
@@ -4155,25 +4179,25 @@
         <v>34</v>
       </c>
       <c r="C99" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="D99" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="E99" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="F99" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="G99" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
@@ -4184,25 +4208,25 @@
         <v>34</v>
       </c>
       <c r="C100" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D100" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="E100" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F100" t="s">
-        <v>159</v>
+        <v>42</v>
       </c>
       <c r="G100" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
@@ -4213,19 +4237,19 @@
         <v>34</v>
       </c>
       <c r="C101" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D101" t="s">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="E101" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="F101" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="G101" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
@@ -4242,19 +4266,19 @@
         <v>34</v>
       </c>
       <c r="C102" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="D102" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="E102" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F102" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="G102" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
@@ -4268,22 +4292,22 @@
         <v>157</v>
       </c>
       <c r="B103" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C103" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D103" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="E103" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F103" t="s">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="G103" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
@@ -4297,28 +4321,28 @@
         <v>157</v>
       </c>
       <c r="B104" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C104" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D104" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="E104" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F104" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G104" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="H104" t="s">
         <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
@@ -4329,25 +4353,25 @@
         <v>44</v>
       </c>
       <c r="C105" t="s">
-        <v>55</v>
+        <v>167</v>
       </c>
       <c r="D105" t="s">
+        <v>111</v>
+      </c>
+      <c r="E105" t="s">
+        <v>170</v>
+      </c>
+      <c r="F105" t="s">
         <v>171</v>
       </c>
-      <c r="E105" t="s">
-        <v>94</v>
-      </c>
-      <c r="F105" t="s">
-        <v>95</v>
-      </c>
       <c r="G105" t="s">
-        <v>96</v>
+        <v>172</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
@@ -4358,25 +4382,25 @@
         <v>44</v>
       </c>
       <c r="C106" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D106" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="E106" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F106" t="s">
-        <v>159</v>
+        <v>42</v>
       </c>
       <c r="G106" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="H106" t="s">
         <v>18</v>
       </c>
       <c r="I106" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15">
@@ -4387,25 +4411,25 @@
         <v>44</v>
       </c>
       <c r="C107" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="D107" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E107" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="F107" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="G107" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
       </c>
       <c r="I107" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15">
@@ -4416,19 +4440,19 @@
         <v>44</v>
       </c>
       <c r="C108" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D108" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E108" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="F108" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="G108" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
@@ -4442,22 +4466,22 @@
         <v>157</v>
       </c>
       <c r="B109" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C109" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="D109" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E109" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F109" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="G109" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
@@ -4471,28 +4495,28 @@
         <v>157</v>
       </c>
       <c r="B110" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C110" t="s">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="D110" t="s">
+        <v>36</v>
+      </c>
+      <c r="E110" t="s">
+        <v>161</v>
+      </c>
+      <c r="F110" t="s">
+        <v>52</v>
+      </c>
+      <c r="G110" t="s">
+        <v>98</v>
+      </c>
+      <c r="H110" t="s">
         <v>174</v>
       </c>
-      <c r="E110" t="s">
-        <v>41</v>
-      </c>
-      <c r="F110" t="s">
-        <v>102</v>
-      </c>
-      <c r="G110" t="s">
-        <v>129</v>
-      </c>
-      <c r="H110" t="s">
-        <v>18</v>
-      </c>
       <c r="I110" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
@@ -4500,28 +4524,28 @@
         <v>157</v>
       </c>
       <c r="B111" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C111" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D111" t="s">
-        <v>171</v>
+        <v>61</v>
       </c>
       <c r="E111" t="s">
-        <v>94</v>
+        <v>37</v>
       </c>
       <c r="F111" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G111" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15">
@@ -4532,19 +4556,19 @@
         <v>54</v>
       </c>
       <c r="C112" t="s">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="D112" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="E112" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="F112" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="G112" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
@@ -4561,25 +4585,25 @@
         <v>54</v>
       </c>
       <c r="C113" t="s">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="D113" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E113" t="s">
         <v>41</v>
       </c>
       <c r="F113" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="G113" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
@@ -4587,28 +4611,28 @@
         <v>157</v>
       </c>
       <c r="B114" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C114" t="s">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="D114" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="E114" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F114" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="G114" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="H114" t="s">
         <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
@@ -4616,28 +4640,28 @@
         <v>157</v>
       </c>
       <c r="B115" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C115" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="D115" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="E115" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="F115" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="G115" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
@@ -4645,28 +4669,28 @@
         <v>157</v>
       </c>
       <c r="B116" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C116" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="D116" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="E116" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="F116" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="G116" t="s">
-        <v>127</v>
+        <v>39</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
@@ -4674,22 +4698,22 @@
         <v>157</v>
       </c>
       <c r="B117" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C117" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="D117" t="s">
-        <v>56</v>
+        <v>178</v>
       </c>
       <c r="E117" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="F117" t="s">
-        <v>159</v>
+        <v>31</v>
       </c>
       <c r="G117" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
@@ -4706,19 +4730,19 @@
         <v>65</v>
       </c>
       <c r="C118" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="D118" t="s">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="E118" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="F118" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G118" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
@@ -4732,13 +4756,13 @@
         <v>157</v>
       </c>
       <c r="B119" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C119" t="s">
         <v>78</v>
       </c>
       <c r="D119" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E119" t="s">
         <v>41</v>
@@ -4761,28 +4785,28 @@
         <v>157</v>
       </c>
       <c r="B120" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C120" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="D120" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="E120" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="F120" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="G120" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
       </c>
       <c r="I120" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15">
@@ -4790,7 +4814,7 @@
         <v>157</v>
       </c>
       <c r="B121" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C121" t="s">
         <v>110</v>
@@ -4819,22 +4843,22 @@
         <v>157</v>
       </c>
       <c r="B122" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C122" t="s">
         <v>124</v>
       </c>
       <c r="D122" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E122" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F122" t="s">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="G122" t="s">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
@@ -4848,22 +4872,22 @@
         <v>157</v>
       </c>
       <c r="B123" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C123" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="D123" t="s">
-        <v>106</v>
+        <v>181</v>
       </c>
       <c r="E123" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="F123" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G123" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
@@ -4880,19 +4904,19 @@
         <v>77</v>
       </c>
       <c r="C124" t="s">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="D124" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E124" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="F124" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="G124" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
@@ -4906,13 +4930,13 @@
         <v>157</v>
       </c>
       <c r="B125" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C125" t="s">
         <v>142</v>
       </c>
       <c r="D125" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E125" t="s">
         <v>41</v>
@@ -4935,28 +4959,28 @@
         <v>157</v>
       </c>
       <c r="B126" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C126" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="D126" t="s">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="E126" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="F126" t="s">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="G126" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
       </c>
       <c r="I126" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
@@ -4964,22 +4988,22 @@
         <v>157</v>
       </c>
       <c r="B127" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C127" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D127" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
       <c r="E127" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F127" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="G127" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
@@ -4993,28 +5017,28 @@
         <v>157</v>
       </c>
       <c r="B128" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C128" t="s">
-        <v>124</v>
+        <v>183</v>
       </c>
       <c r="D128" t="s">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="E128" t="s">
-        <v>41</v>
+        <v>184</v>
       </c>
       <c r="F128" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="G128" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
@@ -5022,22 +5046,22 @@
         <v>157</v>
       </c>
       <c r="B129" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C129" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="D129" t="s">
-        <v>106</v>
+        <v>181</v>
       </c>
       <c r="E129" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="F129" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G129" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
@@ -5051,28 +5075,28 @@
         <v>157</v>
       </c>
       <c r="B130" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C130" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="D130" t="s">
-        <v>59</v>
+        <v>186</v>
       </c>
       <c r="E130" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="F130" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="G130" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
@@ -5080,13 +5104,13 @@
         <v>157</v>
       </c>
       <c r="B131" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C131" t="s">
         <v>142</v>
       </c>
       <c r="D131" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E131" t="s">
         <v>41</v>
@@ -5109,28 +5133,28 @@
         <v>157</v>
       </c>
       <c r="B132" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C132" t="s">
         <v>55</v>
       </c>
       <c r="D132" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="E132" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="F132" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="G132" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
@@ -5138,167 +5162,167 @@
         <v>157</v>
       </c>
       <c r="B133" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C133" t="s">
-        <v>178</v>
+        <v>110</v>
       </c>
       <c r="D133" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="E133" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="F133" t="s">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="G133" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
       </c>
       <c r="I133" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="B134" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="D134" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E134" t="s">
         <v>41</v>
       </c>
       <c r="F134" t="s">
-        <v>185</v>
+        <v>123</v>
       </c>
       <c r="G134" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="H134" t="s">
         <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
+        <v>157</v>
+      </c>
+      <c r="B135" t="s">
+        <v>87</v>
+      </c>
+      <c r="C135" t="s">
         <v>183</v>
       </c>
-      <c r="B135" t="s">
-        <v>12</v>
-      </c>
-      <c r="C135" t="s">
-        <v>110</v>
-      </c>
       <c r="D135" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="E135" t="s">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="F135" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="G135" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="H135" t="s">
         <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="B136" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="C136" t="s">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="D136" t="s">
-        <v>166</v>
+        <v>89</v>
       </c>
       <c r="E136" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="F136" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="G136" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="H136" t="s">
         <v>18</v>
       </c>
       <c r="I136" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="B137" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="C137" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="D137" t="s">
-        <v>187</v>
+        <v>59</v>
       </c>
       <c r="E137" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="F137" t="s">
-        <v>118</v>
+        <v>176</v>
       </c>
       <c r="G137" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
       </c>
       <c r="I137" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="B138" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="C138" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="D138" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E138" t="s">
         <v>41</v>
       </c>
       <c r="F138" t="s">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="G138" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
@@ -5309,109 +5333,109 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="B139" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="C139" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="D139" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="E139" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F139" t="s">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="G139" t="s">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="H139" t="s">
         <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
+        <v>157</v>
+      </c>
+      <c r="B140" t="s">
+        <v>101</v>
+      </c>
+      <c r="C140" t="s">
         <v>183</v>
       </c>
-      <c r="B140" t="s">
-        <v>34</v>
-      </c>
-      <c r="C140" t="s">
-        <v>20</v>
-      </c>
       <c r="D140" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="E140" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="F140" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="G140" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H140" t="s">
         <v>18</v>
       </c>
       <c r="I140" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="B141" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="C141" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D141" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="E141" t="s">
+        <v>84</v>
+      </c>
+      <c r="F141" t="s">
         <v>190</v>
       </c>
-      <c r="F141" t="s">
-        <v>131</v>
-      </c>
       <c r="G141" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="H141" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="I141" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B142" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C142" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D142" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="E142" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F142" t="s">
-        <v>63</v>
+        <v>193</v>
       </c>
       <c r="G142" t="s">
         <v>17</v>
@@ -5425,54 +5449,54 @@
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B143" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C143" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="D143" t="s">
-        <v>187</v>
+        <v>66</v>
       </c>
       <c r="E143" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="F143" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="G143" t="s">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="H143" t="s">
         <v>18</v>
       </c>
       <c r="I143" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B144" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C144" t="s">
-        <v>192</v>
+        <v>60</v>
       </c>
       <c r="D144" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="E144" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="F144" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="G144" t="s">
-        <v>194</v>
+        <v>17</v>
       </c>
       <c r="H144" t="s">
         <v>18</v>
@@ -5483,373 +5507,373 @@
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B145" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C145" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="D145" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E145" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="F145" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="G145" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="H145" t="s">
         <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B146" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C146" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D146" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="E146" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F146" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="G146" t="s">
-        <v>186</v>
+        <v>17</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B147" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C147" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D147" t="s">
-        <v>195</v>
+        <v>66</v>
       </c>
       <c r="E147" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="F147" t="s">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="G147" t="s">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="H147" t="s">
         <v>18</v>
       </c>
       <c r="I147" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B148" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C148" t="s">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="D148" t="s">
         <v>196</v>
       </c>
       <c r="E148" t="s">
-        <v>190</v>
+        <v>22</v>
       </c>
       <c r="F148" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="G148" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="H148" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="I148" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B149" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C149" t="s">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="D149" t="s">
-        <v>197</v>
+        <v>111</v>
       </c>
       <c r="E149" t="s">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="F149" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="G149" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H149" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I149" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B150" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C150" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D150" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="E150" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F150" t="s">
-        <v>198</v>
+        <v>63</v>
       </c>
       <c r="G150" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="H150" t="s">
         <v>18</v>
       </c>
       <c r="I150" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B151" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C151" t="s">
-        <v>192</v>
+        <v>24</v>
       </c>
       <c r="D151" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E151" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="F151" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G151" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="H151" t="s">
         <v>18</v>
       </c>
       <c r="I151" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B152" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C152" t="s">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="D152" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E152" t="s">
         <v>41</v>
       </c>
       <c r="F152" t="s">
-        <v>185</v>
+        <v>123</v>
       </c>
       <c r="G152" t="s">
-        <v>134</v>
+        <v>202</v>
       </c>
       <c r="H152" t="s">
         <v>18</v>
       </c>
       <c r="I152" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B153" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C153" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D153" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="E153" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F153" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="G153" t="s">
-        <v>186</v>
+        <v>17</v>
       </c>
       <c r="H153" t="s">
         <v>18</v>
       </c>
       <c r="I153" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B154" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C154" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D154" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E154" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="F154" t="s">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="G154" t="s">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="H154" t="s">
         <v>18</v>
       </c>
       <c r="I154" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B155" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C155" t="s">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="D155" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E155" t="s">
-        <v>190</v>
+        <v>22</v>
       </c>
       <c r="F155" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="G155" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="H155" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="I155" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B156" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C156" t="s">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="D156" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E156" t="s">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="F156" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="G156" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H156" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I156" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B157" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C157" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D157" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="E157" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F157" t="s">
-        <v>198</v>
+        <v>31</v>
       </c>
       <c r="G157" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="H157" t="s">
         <v>18</v>
@@ -5860,199 +5884,199 @@
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B158" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C158" t="s">
-        <v>192</v>
+        <v>24</v>
       </c>
       <c r="D158" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E158" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="F158" t="s">
-        <v>123</v>
+        <v>205</v>
       </c>
       <c r="G158" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
       </c>
       <c r="I158" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B159" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C159" t="s">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="D159" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E159" t="s">
         <v>41</v>
       </c>
       <c r="F159" t="s">
-        <v>185</v>
+        <v>123</v>
       </c>
       <c r="G159" t="s">
-        <v>134</v>
+        <v>202</v>
       </c>
       <c r="H159" t="s">
         <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B160" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C160" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D160" t="s">
-        <v>66</v>
+        <v>206</v>
       </c>
       <c r="E160" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F160" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="G160" t="s">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B161" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C161" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D161" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="E161" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="F161" t="s">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="G161" t="s">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="H161" t="s">
         <v>18</v>
       </c>
       <c r="I161" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B162" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C162" t="s">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="D162" t="s">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="E162" t="s">
-        <v>190</v>
+        <v>22</v>
       </c>
       <c r="F162" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="G162" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="H162" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="I162" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B163" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C163" t="s">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="D163" t="s">
-        <v>138</v>
+        <v>196</v>
       </c>
       <c r="E163" t="s">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="F163" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="G163" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H163" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I163" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B164" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C164" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D164" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="E164" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="F164" t="s">
-        <v>198</v>
+        <v>100</v>
       </c>
       <c r="G164" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="H164" t="s">
         <v>18</v>
@@ -6063,25 +6087,25 @@
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B165" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C165" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="D165" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E165" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="F165" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="G165" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="H165" t="s">
         <v>18</v>
@@ -6092,54 +6116,54 @@
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B166" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C166" t="s">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="D166" t="s">
-        <v>66</v>
+        <v>201</v>
       </c>
       <c r="E166" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F166" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="G166" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="H166" t="s">
         <v>18</v>
       </c>
       <c r="I166" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B167" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C167" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D167" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="E167" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F167" t="s">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="G167" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="H167" t="s">
         <v>18</v>
@@ -6150,54 +6174,54 @@
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B168" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C168" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="D168" t="s">
-        <v>201</v>
+        <v>66</v>
       </c>
       <c r="E168" t="s">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="F168" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="G168" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="H168" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="I168" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B169" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C169" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D169" t="s">
-        <v>187</v>
+        <v>125</v>
       </c>
       <c r="E169" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F169" t="s">
-        <v>198</v>
+        <v>23</v>
       </c>
       <c r="G169" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="H169" t="s">
         <v>18</v>
@@ -6208,28 +6232,28 @@
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B170" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C170" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D170" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E170" t="s">
-        <v>38</v>
+        <v>198</v>
       </c>
       <c r="F170" t="s">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="G170" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="H170" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I170" t="s">
         <v>19</v>
@@ -6237,25 +6261,25 @@
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B171" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C171" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D171" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="E171" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="F171" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="G171" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="H171" t="s">
         <v>18</v>
@@ -6266,170 +6290,170 @@
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B172" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C172" t="s">
-        <v>189</v>
+        <v>24</v>
       </c>
       <c r="D172" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E172" t="s">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="F172" t="s">
-        <v>131</v>
+        <v>205</v>
       </c>
       <c r="G172" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="H172" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="I172" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B173" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C173" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="D173" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="E173" t="s">
-        <v>168</v>
+        <v>41</v>
       </c>
       <c r="F173" t="s">
-        <v>140</v>
+        <v>193</v>
       </c>
       <c r="G173" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="H173" t="s">
         <v>18</v>
       </c>
       <c r="I173" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B174" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C174" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D174" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="E174" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="F174" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="G174" t="s">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="H174" t="s">
         <v>18</v>
       </c>
       <c r="I174" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B175" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C175" t="s">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="D175" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E175" t="s">
-        <v>190</v>
+        <v>22</v>
       </c>
       <c r="F175" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="G175" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="H175" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="I175" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="15">
       <c r="A176" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B176" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="C176" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="D176" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E176" t="s">
-        <v>46</v>
+        <v>198</v>
       </c>
       <c r="F176" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="G176" t="s">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="H176" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I176" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15">
       <c r="A177" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B177" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="C177" t="s">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="D177" t="s">
+        <v>195</v>
+      </c>
+      <c r="E177" t="s">
+        <v>26</v>
+      </c>
+      <c r="F177" t="s">
         <v>205</v>
       </c>
-      <c r="E177" t="s">
-        <v>46</v>
-      </c>
-      <c r="F177" t="s">
-        <v>140</v>
-      </c>
       <c r="G177" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="H177" t="s">
         <v>18</v>
@@ -6440,54 +6464,54 @@
     </row>
     <row r="178" spans="1:9" ht="15">
       <c r="A178" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B178" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="C178" t="s">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D178" t="s">
-        <v>89</v>
+        <v>209</v>
       </c>
       <c r="E178" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F178" t="s">
-        <v>23</v>
+        <v>205</v>
       </c>
       <c r="G178" t="s">
-        <v>104</v>
+        <v>202</v>
       </c>
       <c r="H178" t="s">
         <v>18</v>
       </c>
       <c r="I178" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="15">
       <c r="A179" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B179" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C179" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="D179" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="E179" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F179" t="s">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="G179" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="H179" t="s">
         <v>18</v>
@@ -6498,28 +6522,28 @@
     </row>
     <row r="180" spans="1:9" ht="15">
       <c r="A180" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B180" t="s">
-        <v>149</v>
+        <v>87</v>
       </c>
       <c r="C180" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="D180" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E180" t="s">
-        <v>46</v>
+        <v>198</v>
       </c>
       <c r="F180" t="s">
-        <v>207</v>
+        <v>131</v>
       </c>
       <c r="G180" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="H180" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I180" t="s">
         <v>19</v>
@@ -6527,39 +6551,39 @@
     </row>
     <row r="181" spans="1:9" ht="15">
       <c r="A181" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B181" t="s">
-        <v>149</v>
+        <v>101</v>
       </c>
       <c r="C181" t="s">
         <v>147</v>
       </c>
       <c r="D181" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="E181" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="F181" t="s">
         <v>140</v>
       </c>
       <c r="G181" t="s">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="H181" t="s">
         <v>18</v>
       </c>
       <c r="I181" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="15">
       <c r="A182" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B182" t="s">
-        <v>149</v>
+        <v>101</v>
       </c>
       <c r="C182" t="s">
         <v>124</v>
@@ -6585,28 +6609,28 @@
     </row>
     <row r="183" spans="1:9" ht="15">
       <c r="A183" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B183" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="C183" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="D183" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E183" t="s">
-        <v>46</v>
+        <v>198</v>
       </c>
       <c r="F183" t="s">
-        <v>207</v>
+        <v>131</v>
       </c>
       <c r="G183" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="H183" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I183" t="s">
         <v>19</v>
@@ -6614,54 +6638,54 @@
     </row>
     <row r="184" spans="1:9" ht="15">
       <c r="A184" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B184" t="s">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="C184" t="s">
         <v>147</v>
       </c>
       <c r="D184" t="s">
-        <v>152</v>
+        <v>211</v>
       </c>
       <c r="E184" t="s">
-        <v>208</v>
+        <v>46</v>
       </c>
       <c r="F184" t="s">
         <v>140</v>
       </c>
       <c r="G184" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H184" t="s">
         <v>18</v>
       </c>
       <c r="I184" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="15">
       <c r="A185" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B185" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="C185" t="s">
         <v>147</v>
       </c>
       <c r="D185" t="s">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="E185" t="s">
-        <v>208</v>
+        <v>46</v>
       </c>
       <c r="F185" t="s">
         <v>140</v>
       </c>
       <c r="G185" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H185" t="s">
         <v>18</v>
@@ -6672,25 +6696,25 @@
     </row>
     <row r="186" spans="1:9" ht="15">
       <c r="A186" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B186" t="s">
-        <v>156</v>
+        <v>105</v>
       </c>
       <c r="C186" t="s">
-        <v>147</v>
+        <v>20</v>
       </c>
       <c r="D186" t="s">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="E186" t="s">
-        <v>208</v>
+        <v>22</v>
       </c>
       <c r="F186" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="G186" t="s">
-        <v>186</v>
+        <v>104</v>
       </c>
       <c r="H186" t="s">
         <v>18</v>
@@ -6701,141 +6725,141 @@
     </row>
     <row r="187" spans="1:9" ht="15">
       <c r="A187" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B187" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="C187" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D187" t="s">
-        <v>211</v>
+        <v>151</v>
       </c>
       <c r="E187" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F187" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="G187" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="H187" t="s">
         <v>18</v>
       </c>
       <c r="I187" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="15">
       <c r="A188" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B188" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="C188" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="D188" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="E188" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="F188" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G188" t="s">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c r="H188" t="s">
         <v>18</v>
       </c>
       <c r="I188" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="15">
       <c r="A189" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B189" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="C189" t="s">
-        <v>24</v>
+        <v>214</v>
       </c>
       <c r="D189" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="E189" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F189" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="G189" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="H189" t="s">
         <v>18</v>
       </c>
       <c r="I189" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="15">
       <c r="A190" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B190" t="s">
-        <v>34</v>
+        <v>149</v>
       </c>
       <c r="C190" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="D190" t="s">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="E190" t="s">
-        <v>112</v>
+        <v>216</v>
       </c>
       <c r="F190" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="G190" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="H190" t="s">
         <v>18</v>
       </c>
       <c r="I190" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="15">
       <c r="A191" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B191" t="s">
-        <v>34</v>
+        <v>149</v>
       </c>
       <c r="C191" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="D191" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="E191" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F191" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="G191" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="H191" t="s">
         <v>18</v>
@@ -6846,28 +6870,28 @@
     </row>
     <row r="192" spans="1:9" ht="15">
       <c r="A192" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>34</v>
+        <v>149</v>
       </c>
       <c r="C192" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D192" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="E192" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="F192" t="s">
-        <v>131</v>
+        <v>52</v>
       </c>
       <c r="G192" t="s">
         <v>19</v>
       </c>
       <c r="H192" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="I192" t="s">
         <v>19</v>
@@ -6875,83 +6899,83 @@
     </row>
     <row r="193" spans="1:9" ht="15">
       <c r="A193" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>34</v>
+        <v>154</v>
       </c>
       <c r="C193" t="s">
-        <v>24</v>
+        <v>214</v>
       </c>
       <c r="D193" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="E193" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F193" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="G193" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="H193" t="s">
         <v>18</v>
       </c>
       <c r="I193" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="15">
       <c r="A194" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B194" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="C194" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="D194" t="s">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="E194" t="s">
-        <v>112</v>
+        <v>216</v>
       </c>
       <c r="F194" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="G194" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="H194" t="s">
         <v>18</v>
       </c>
       <c r="I194" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="15">
       <c r="A195" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B195" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="C195" t="s">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="D195" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="E195" t="s">
-        <v>22</v>
+        <v>216</v>
       </c>
       <c r="F195" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="G195" t="s">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="H195" t="s">
         <v>18</v>
@@ -6962,25 +6986,25 @@
     </row>
     <row r="196" spans="1:9" ht="15">
       <c r="A196" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B196" t="s">
-        <v>44</v>
+        <v>156</v>
       </c>
       <c r="C196" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="D196" t="s">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="E196" t="s">
-        <v>41</v>
+        <v>216</v>
       </c>
       <c r="F196" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="G196" t="s">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="H196" t="s">
         <v>18</v>
@@ -6991,54 +7015,54 @@
     </row>
     <row r="197" spans="1:9" ht="15">
       <c r="A197" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B197" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C197" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="D197" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="E197" t="s">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="F197" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="G197" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="H197" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="I197" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="15">
       <c r="A198" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B198" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C198" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D198" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="E198" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F198" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="G198" t="s">
-        <v>213</v>
+        <v>104</v>
       </c>
       <c r="H198" t="s">
         <v>18</v>
@@ -7049,48 +7073,48 @@
     </row>
     <row r="199" spans="1:9" ht="15">
       <c r="A199" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B199" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C199" t="s">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="D199" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="E199" t="s">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="F199" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="G199" t="s">
-        <v>213</v>
+        <v>19</v>
       </c>
       <c r="H199" t="s">
         <v>18</v>
       </c>
       <c r="I199" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="15">
       <c r="A200" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B200" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
       </c>
       <c r="D200" t="s">
-        <v>50</v>
+        <v>195</v>
       </c>
       <c r="E200" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="F200" t="s">
         <v>118</v>
@@ -7107,16 +7131,16 @@
     </row>
     <row r="201" spans="1:9" ht="15">
       <c r="A201" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B201" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C201" t="s">
         <v>110</v>
       </c>
       <c r="D201" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E201" t="s">
         <v>112</v>
@@ -7136,16 +7160,16 @@
     </row>
     <row r="202" spans="1:9" ht="15">
       <c r="A202" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B202" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C202" t="s">
         <v>20</v>
       </c>
       <c r="D202" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E202" t="s">
         <v>22</v>
@@ -7165,57 +7189,57 @@
     </row>
     <row r="203" spans="1:9" ht="15">
       <c r="A203" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B203" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C203" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="D203" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="E203" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
       <c r="F203" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="G203" t="s">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="H203" t="s">
         <v>18</v>
       </c>
       <c r="I203" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="204" spans="1:9" ht="15">
       <c r="A204" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B204" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C204" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D204" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="E204" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F204" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="G204" t="s">
         <v>19</v>
       </c>
       <c r="H204" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I204" t="s">
         <v>19</v>
@@ -7223,25 +7247,25 @@
     </row>
     <row r="205" spans="1:9" ht="15">
       <c r="A205" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B205" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C205" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D205" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E205" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="F205" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="G205" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="H205" t="s">
         <v>18</v>
@@ -7252,54 +7276,54 @@
     </row>
     <row r="206" spans="1:9" ht="15">
       <c r="A206" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B206" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C206" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="D206" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="E206" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="F206" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="G206" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H206" t="s">
         <v>18</v>
       </c>
       <c r="I206" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="207" spans="1:9" ht="15">
       <c r="A207" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B207" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C207" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D207" t="s">
-        <v>214</v>
+        <v>70</v>
       </c>
       <c r="E207" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F207" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="G207" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="H207" t="s">
         <v>18</v>
@@ -7310,170 +7334,170 @@
     </row>
     <row r="208" spans="1:9" ht="15">
       <c r="A208" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B208" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C208" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D208" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="E208" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F208" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="G208" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="H208" t="s">
         <v>18</v>
       </c>
       <c r="I208" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="209" spans="1:9" ht="15">
       <c r="A209" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B209" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C209" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D209" t="s">
-        <v>148</v>
+        <v>209</v>
       </c>
       <c r="E209" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F209" t="s">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="G209" t="s">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="H209" t="s">
         <v>18</v>
       </c>
       <c r="I209" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="210" spans="1:9" ht="15">
       <c r="A210" t="s">
+        <v>218</v>
+      </c>
+      <c r="B210" t="s">
+        <v>44</v>
+      </c>
+      <c r="C210" t="s">
+        <v>197</v>
+      </c>
+      <c r="D210" t="s">
         <v>210</v>
       </c>
-      <c r="B210" t="s">
-        <v>65</v>
-      </c>
-      <c r="C210" t="s">
-        <v>20</v>
-      </c>
-      <c r="D210" t="s">
-        <v>70</v>
-      </c>
       <c r="E210" t="s">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="F210" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="G210" t="s">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c r="H210" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I210" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="211" spans="1:9" ht="15">
       <c r="A211" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B211" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C211" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="D211" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="E211" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F211" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="G211" t="s">
-        <v>98</v>
+        <v>221</v>
       </c>
       <c r="H211" t="s">
-        <v>216</v>
+        <v>18</v>
       </c>
       <c r="I211" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="212" spans="1:9" ht="15">
       <c r="A212" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B212" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C212" t="s">
-        <v>189</v>
+        <v>60</v>
       </c>
       <c r="D212" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="E212" t="s">
-        <v>190</v>
+        <v>15</v>
       </c>
       <c r="F212" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G212" t="s">
-        <v>19</v>
+        <v>221</v>
       </c>
       <c r="H212" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="I212" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="213" spans="1:9" ht="15">
       <c r="A213" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B213" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C213" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D213" t="s">
-        <v>202</v>
+        <v>50</v>
       </c>
       <c r="E213" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="F213" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="G213" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H213" t="s">
         <v>18</v>
@@ -7484,54 +7508,54 @@
     </row>
     <row r="214" spans="1:9" ht="15">
       <c r="A214" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B214" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C214" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="D214" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="E214" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="F214" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="G214" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H214" t="s">
         <v>18</v>
       </c>
       <c r="I214" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="215" spans="1:9" ht="15">
       <c r="A215" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B215" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C215" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D215" t="s">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="E215" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F215" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="G215" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="H215" t="s">
         <v>18</v>
@@ -7542,86 +7566,86 @@
     </row>
     <row r="216" spans="1:9" ht="15">
       <c r="A216" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B216" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C216" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D216" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="E216" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F216" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="G216" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="H216" t="s">
         <v>18</v>
       </c>
       <c r="I216" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="217" spans="1:9" ht="15">
       <c r="A217" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B217" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C217" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D217" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E217" t="s">
-        <v>84</v>
+        <v>161</v>
       </c>
       <c r="F217" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G217" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="H217" t="s">
         <v>18</v>
       </c>
       <c r="I217" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="218" spans="1:9" ht="15">
       <c r="A218" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B218" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C218" t="s">
-        <v>32</v>
+        <v>197</v>
       </c>
       <c r="D218" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E218" t="s">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="F218" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="G218" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="H218" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I218" t="s">
         <v>19</v>
@@ -7629,25 +7653,25 @@
     </row>
     <row r="219" spans="1:9" ht="15">
       <c r="A219" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C219" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D219" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
       <c r="E219" t="s">
         <v>99</v>
       </c>
       <c r="F219" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="G219" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="H219" t="s">
         <v>18</v>
@@ -7658,54 +7682,54 @@
     </row>
     <row r="220" spans="1:9" ht="15">
       <c r="A220" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C220" t="s">
-        <v>189</v>
+        <v>24</v>
       </c>
       <c r="D220" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E220" t="s">
-        <v>190</v>
+        <v>97</v>
       </c>
       <c r="F220" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="G220" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="H220" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="I220" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="221" spans="1:9" ht="15">
       <c r="A221" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B221" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C221" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D221" t="s">
-        <v>138</v>
+        <v>222</v>
       </c>
       <c r="E221" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="F221" t="s">
-        <v>100</v>
+        <v>223</v>
       </c>
       <c r="G221" t="s">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="H221" t="s">
         <v>18</v>
@@ -7716,54 +7740,54 @@
     </row>
     <row r="222" spans="1:9" ht="15">
       <c r="A222" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B222" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C222" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="D222" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="E222" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="F222" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="G222" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H222" t="s">
         <v>18</v>
       </c>
       <c r="I222" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="223" spans="1:9" ht="15">
       <c r="A223" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B223" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C223" t="s">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="D223" t="s">
-        <v>214</v>
+        <v>148</v>
       </c>
       <c r="E223" t="s">
-        <v>41</v>
+        <v>170</v>
       </c>
       <c r="F223" t="s">
-        <v>215</v>
+        <v>171</v>
       </c>
       <c r="G223" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="H223" t="s">
         <v>18</v>
@@ -7774,25 +7798,25 @@
     </row>
     <row r="224" spans="1:9" ht="15">
       <c r="A224" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B224" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C224" t="s">
-        <v>142</v>
+        <v>20</v>
       </c>
       <c r="D224" t="s">
-        <v>209</v>
+        <v>70</v>
       </c>
       <c r="E224" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="F224" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="G224" t="s">
-        <v>218</v>
+        <v>104</v>
       </c>
       <c r="H224" t="s">
         <v>18</v>
@@ -7803,54 +7827,54 @@
     </row>
     <row r="225" spans="1:9" ht="15">
       <c r="A225" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B225" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C225" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D225" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="E225" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F225" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G225" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="H225" t="s">
-        <v>18</v>
+        <v>224</v>
       </c>
       <c r="I225" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="226" spans="1:9" ht="15">
       <c r="A226" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B226" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C226" t="s">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="D226" t="s">
-        <v>132</v>
+        <v>213</v>
       </c>
       <c r="E226" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="F226" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G226" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="H226" t="s">
         <v>18</v>
@@ -7861,19 +7885,19 @@
     </row>
     <row r="227" spans="1:9" ht="15">
       <c r="A227" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B227" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C227" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D227" t="s">
-        <v>217</v>
+        <v>136</v>
       </c>
       <c r="E227" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F227" t="s">
         <v>88</v>
@@ -7882,7 +7906,7 @@
         <v>19</v>
       </c>
       <c r="H227" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I227" t="s">
         <v>19</v>
@@ -7890,54 +7914,54 @@
     </row>
     <row r="228" spans="1:9" ht="15">
       <c r="A228" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B228" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C228" t="s">
         <v>60</v>
       </c>
       <c r="D228" t="s">
-        <v>138</v>
+        <v>209</v>
       </c>
       <c r="E228" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="F228" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="G228" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="H228" t="s">
         <v>18</v>
       </c>
       <c r="I228" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="229" spans="1:9" ht="15">
       <c r="A229" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B229" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="C229" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="D229" t="s">
-        <v>197</v>
+        <v>50</v>
       </c>
       <c r="E229" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="F229" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="G229" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="H229" t="s">
         <v>18</v>
@@ -7948,25 +7972,25 @@
     </row>
     <row r="230" spans="1:9" ht="15">
       <c r="A230" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B230" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C230" t="s">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="D230" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="E230" t="s">
         <v>41</v>
       </c>
       <c r="F230" t="s">
-        <v>102</v>
+        <v>223</v>
       </c>
       <c r="G230" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="H230" t="s">
         <v>18</v>
@@ -7977,51 +8001,51 @@
     </row>
     <row r="231" spans="1:9" ht="15">
       <c r="A231" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B231" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C231" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="D231" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="E231" t="s">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="F231" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="G231" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="H231" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="I231" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="232" spans="1:9" ht="15">
       <c r="A232" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B232" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C232" t="s">
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="D232" t="s">
-        <v>70</v>
+        <v>225</v>
       </c>
       <c r="E232" t="s">
         <v>84</v>
       </c>
       <c r="F232" t="s">
-        <v>219</v>
+        <v>31</v>
       </c>
       <c r="G232" t="s">
         <v>85</v>
@@ -8035,54 +8059,54 @@
     </row>
     <row r="233" spans="1:9" ht="15">
       <c r="A233" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B233" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C233" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="D233" t="s">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="E233" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F233" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G233" t="s">
-        <v>55</v>
+        <v>202</v>
       </c>
       <c r="H233" t="s">
         <v>18</v>
       </c>
       <c r="I233" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="234" spans="1:9" ht="15">
       <c r="A234" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B234" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C234" t="s">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="D234" t="s">
-        <v>217</v>
+        <v>70</v>
       </c>
       <c r="E234" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="F234" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
       <c r="G234" t="s">
-        <v>221</v>
+        <v>104</v>
       </c>
       <c r="H234" t="s">
         <v>18</v>
@@ -8093,57 +8117,57 @@
     </row>
     <row r="235" spans="1:9" ht="15">
       <c r="A235" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B235" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="C235" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="D235" t="s">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="E235" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
       <c r="F235" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="G235" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H235" t="s">
         <v>18</v>
       </c>
       <c r="I235" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="236" spans="1:9" ht="15">
       <c r="A236" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B236" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="C236" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D236" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E236" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F236" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="G236" t="s">
         <v>19</v>
       </c>
       <c r="H236" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I236" t="s">
         <v>19</v>
@@ -8151,25 +8175,25 @@
     </row>
     <row r="237" spans="1:9" ht="15">
       <c r="A237" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B237" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="C237" t="s">
         <v>60</v>
       </c>
       <c r="D237" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E237" t="s">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="F237" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="G237" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H237" t="s">
         <v>18</v>
@@ -8180,30 +8204,581 @@
     </row>
     <row r="238" spans="1:9" ht="15">
       <c r="A238" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B238" t="s">
+        <v>77</v>
+      </c>
+      <c r="C238" t="s">
+        <v>24</v>
+      </c>
+      <c r="D238" t="s">
+        <v>50</v>
+      </c>
+      <c r="E238" t="s">
+        <v>97</v>
+      </c>
+      <c r="F238" t="s">
+        <v>75</v>
+      </c>
+      <c r="G238" t="s">
+        <v>80</v>
+      </c>
+      <c r="H238" t="s">
+        <v>18</v>
+      </c>
+      <c r="I238" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" ht="15">
+      <c r="A239" t="s">
+        <v>218</v>
+      </c>
+      <c r="B239" t="s">
+        <v>87</v>
+      </c>
+      <c r="C239" t="s">
+        <v>78</v>
+      </c>
+      <c r="D239" t="s">
+        <v>222</v>
+      </c>
+      <c r="E239" t="s">
+        <v>41</v>
+      </c>
+      <c r="F239" t="s">
+        <v>223</v>
+      </c>
+      <c r="G239" t="s">
+        <v>134</v>
+      </c>
+      <c r="H239" t="s">
+        <v>18</v>
+      </c>
+      <c r="I239" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" ht="15">
+      <c r="A240" t="s">
+        <v>218</v>
+      </c>
+      <c r="B240" t="s">
+        <v>87</v>
+      </c>
+      <c r="C240" t="s">
+        <v>142</v>
+      </c>
+      <c r="D240" t="s">
+        <v>217</v>
+      </c>
+      <c r="E240" t="s">
+        <v>46</v>
+      </c>
+      <c r="F240" t="s">
+        <v>47</v>
+      </c>
+      <c r="G240" t="s">
+        <v>226</v>
+      </c>
+      <c r="H240" t="s">
+        <v>18</v>
+      </c>
+      <c r="I240" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" ht="15">
+      <c r="A241" t="s">
+        <v>218</v>
+      </c>
+      <c r="B241" t="s">
+        <v>87</v>
+      </c>
+      <c r="C241" t="s">
+        <v>147</v>
+      </c>
+      <c r="D241" t="s">
+        <v>204</v>
+      </c>
+      <c r="E241" t="s">
+        <v>22</v>
+      </c>
+      <c r="F241" t="s">
+        <v>100</v>
+      </c>
+      <c r="G241" t="s">
+        <v>114</v>
+      </c>
+      <c r="H241" t="s">
+        <v>18</v>
+      </c>
+      <c r="I241" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" ht="15">
+      <c r="A242" t="s">
+        <v>218</v>
+      </c>
+      <c r="B242" t="s">
+        <v>87</v>
+      </c>
+      <c r="C242" t="s">
+        <v>32</v>
+      </c>
+      <c r="D242" t="s">
+        <v>132</v>
+      </c>
+      <c r="E242" t="s">
+        <v>99</v>
+      </c>
+      <c r="F242" t="s">
+        <v>31</v>
+      </c>
+      <c r="G242" t="s">
+        <v>202</v>
+      </c>
+      <c r="H242" t="s">
+        <v>18</v>
+      </c>
+      <c r="I242" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" ht="15">
+      <c r="A243" t="s">
+        <v>218</v>
+      </c>
+      <c r="B243" t="s">
+        <v>87</v>
+      </c>
+      <c r="C243" t="s">
+        <v>160</v>
+      </c>
+      <c r="D243" t="s">
+        <v>136</v>
+      </c>
+      <c r="E243" t="s">
+        <v>161</v>
+      </c>
+      <c r="F243" t="s">
+        <v>52</v>
+      </c>
+      <c r="G243" t="s">
+        <v>19</v>
+      </c>
+      <c r="H243" t="s">
+        <v>18</v>
+      </c>
+      <c r="I243" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" ht="15">
+      <c r="A244" t="s">
+        <v>218</v>
+      </c>
+      <c r="B244" t="s">
+        <v>87</v>
+      </c>
+      <c r="C244" t="s">
+        <v>197</v>
+      </c>
+      <c r="D244" t="s">
+        <v>225</v>
+      </c>
+      <c r="E244" t="s">
+        <v>198</v>
+      </c>
+      <c r="F244" t="s">
+        <v>88</v>
+      </c>
+      <c r="G244" t="s">
+        <v>19</v>
+      </c>
+      <c r="H244" t="s">
+        <v>199</v>
+      </c>
+      <c r="I244" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" ht="15">
+      <c r="A245" t="s">
+        <v>218</v>
+      </c>
+      <c r="B245" t="s">
+        <v>87</v>
+      </c>
+      <c r="C245" t="s">
+        <v>60</v>
+      </c>
+      <c r="D245" t="s">
+        <v>138</v>
+      </c>
+      <c r="E245" t="s">
+        <v>99</v>
+      </c>
+      <c r="F245" t="s">
+        <v>63</v>
+      </c>
+      <c r="G245" t="s">
+        <v>103</v>
+      </c>
+      <c r="H245" t="s">
+        <v>18</v>
+      </c>
+      <c r="I245" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" ht="15">
+      <c r="A246" t="s">
+        <v>218</v>
+      </c>
+      <c r="B246" t="s">
+        <v>101</v>
+      </c>
+      <c r="C246" t="s">
+        <v>78</v>
+      </c>
+      <c r="D246" t="s">
+        <v>204</v>
+      </c>
+      <c r="E246" t="s">
+        <v>38</v>
+      </c>
+      <c r="F246" t="s">
+        <v>205</v>
+      </c>
+      <c r="G246" t="s">
+        <v>134</v>
+      </c>
+      <c r="H246" t="s">
+        <v>18</v>
+      </c>
+      <c r="I246" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" ht="15">
+      <c r="A247" t="s">
+        <v>218</v>
+      </c>
+      <c r="B247" t="s">
+        <v>101</v>
+      </c>
+      <c r="C247" t="s">
+        <v>142</v>
+      </c>
+      <c r="D247" t="s">
+        <v>217</v>
+      </c>
+      <c r="E247" t="s">
+        <v>41</v>
+      </c>
+      <c r="F247" t="s">
+        <v>102</v>
+      </c>
+      <c r="G247" t="s">
+        <v>39</v>
+      </c>
+      <c r="H247" t="s">
+        <v>18</v>
+      </c>
+      <c r="I247" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" ht="15">
+      <c r="A248" t="s">
+        <v>218</v>
+      </c>
+      <c r="B248" t="s">
+        <v>101</v>
+      </c>
+      <c r="C248" t="s">
+        <v>160</v>
+      </c>
+      <c r="D248" t="s">
+        <v>208</v>
+      </c>
+      <c r="E248" t="s">
+        <v>161</v>
+      </c>
+      <c r="F248" t="s">
+        <v>52</v>
+      </c>
+      <c r="G248" t="s">
+        <v>19</v>
+      </c>
+      <c r="H248" t="s">
+        <v>18</v>
+      </c>
+      <c r="I248" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" ht="15">
+      <c r="A249" t="s">
+        <v>218</v>
+      </c>
+      <c r="B249" t="s">
+        <v>101</v>
+      </c>
+      <c r="C249" t="s">
+        <v>197</v>
+      </c>
+      <c r="D249" t="s">
+        <v>203</v>
+      </c>
+      <c r="E249" t="s">
+        <v>198</v>
+      </c>
+      <c r="F249" t="s">
+        <v>131</v>
+      </c>
+      <c r="G249" t="s">
+        <v>19</v>
+      </c>
+      <c r="H249" t="s">
+        <v>199</v>
+      </c>
+      <c r="I249" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" ht="15">
+      <c r="A250" t="s">
+        <v>218</v>
+      </c>
+      <c r="B250" t="s">
+        <v>101</v>
+      </c>
+      <c r="C250" t="s">
+        <v>60</v>
+      </c>
+      <c r="D250" t="s">
+        <v>70</v>
+      </c>
+      <c r="E250" t="s">
+        <v>84</v>
+      </c>
+      <c r="F250" t="s">
+        <v>190</v>
+      </c>
+      <c r="G250" t="s">
+        <v>85</v>
+      </c>
+      <c r="H250" t="s">
+        <v>18</v>
+      </c>
+      <c r="I250" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" ht="15">
+      <c r="A251" t="s">
+        <v>218</v>
+      </c>
+      <c r="B251" t="s">
+        <v>101</v>
+      </c>
+      <c r="C251" t="s">
+        <v>185</v>
+      </c>
+      <c r="D251" t="s">
+        <v>186</v>
+      </c>
+      <c r="E251" t="s">
+        <v>94</v>
+      </c>
+      <c r="F251" t="s">
+        <v>16</v>
+      </c>
+      <c r="G251" t="s">
+        <v>55</v>
+      </c>
+      <c r="H251" t="s">
+        <v>18</v>
+      </c>
+      <c r="I251" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" ht="15">
+      <c r="A252" t="s">
+        <v>218</v>
+      </c>
+      <c r="B252" t="s">
+        <v>101</v>
+      </c>
+      <c r="C252" t="s">
+        <v>227</v>
+      </c>
+      <c r="D252" t="s">
+        <v>225</v>
+      </c>
+      <c r="E252" t="s">
+        <v>37</v>
+      </c>
+      <c r="F252" t="s">
+        <v>171</v>
+      </c>
+      <c r="G252" t="s">
+        <v>228</v>
+      </c>
+      <c r="H252" t="s">
+        <v>18</v>
+      </c>
+      <c r="I252" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" ht="15">
+      <c r="A253" t="s">
+        <v>218</v>
+      </c>
+      <c r="B253" t="s">
         <v>105</v>
       </c>
-      <c r="C238" t="s">
-        <v>220</v>
-      </c>
-      <c r="D238" t="s">
+      <c r="C253" t="s">
+        <v>142</v>
+      </c>
+      <c r="D253" t="s">
         <v>217</v>
       </c>
-      <c r="E238" t="s">
+      <c r="E253" t="s">
+        <v>41</v>
+      </c>
+      <c r="F253" t="s">
+        <v>102</v>
+      </c>
+      <c r="G253" t="s">
+        <v>39</v>
+      </c>
+      <c r="H253" t="s">
+        <v>18</v>
+      </c>
+      <c r="I253" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" ht="15">
+      <c r="A254" t="s">
+        <v>218</v>
+      </c>
+      <c r="B254" t="s">
+        <v>105</v>
+      </c>
+      <c r="C254" t="s">
+        <v>160</v>
+      </c>
+      <c r="D254" t="s">
+        <v>208</v>
+      </c>
+      <c r="E254" t="s">
+        <v>161</v>
+      </c>
+      <c r="F254" t="s">
+        <v>52</v>
+      </c>
+      <c r="G254" t="s">
+        <v>19</v>
+      </c>
+      <c r="H254" t="s">
+        <v>18</v>
+      </c>
+      <c r="I254" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" ht="15">
+      <c r="A255" t="s">
+        <v>218</v>
+      </c>
+      <c r="B255" t="s">
+        <v>105</v>
+      </c>
+      <c r="C255" t="s">
+        <v>197</v>
+      </c>
+      <c r="D255" t="s">
+        <v>50</v>
+      </c>
+      <c r="E255" t="s">
+        <v>198</v>
+      </c>
+      <c r="F255" t="s">
+        <v>131</v>
+      </c>
+      <c r="G255" t="s">
+        <v>19</v>
+      </c>
+      <c r="H255" t="s">
+        <v>199</v>
+      </c>
+      <c r="I255" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" ht="15">
+      <c r="A256" t="s">
+        <v>218</v>
+      </c>
+      <c r="B256" t="s">
+        <v>105</v>
+      </c>
+      <c r="C256" t="s">
+        <v>60</v>
+      </c>
+      <c r="D256" t="s">
+        <v>132</v>
+      </c>
+      <c r="E256" t="s">
+        <v>162</v>
+      </c>
+      <c r="F256" t="s">
+        <v>140</v>
+      </c>
+      <c r="G256" t="s">
+        <v>194</v>
+      </c>
+      <c r="H256" t="s">
+        <v>18</v>
+      </c>
+      <c r="I256" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" ht="15">
+      <c r="A257" t="s">
+        <v>218</v>
+      </c>
+      <c r="B257" t="s">
+        <v>105</v>
+      </c>
+      <c r="C257" t="s">
+        <v>227</v>
+      </c>
+      <c r="D257" t="s">
+        <v>225</v>
+      </c>
+      <c r="E257" t="s">
         <v>37</v>
       </c>
-      <c r="F238" t="s">
-        <v>169</v>
-      </c>
-      <c r="G238" t="s">
-        <v>221</v>
-      </c>
-      <c r="H238" t="s">
-        <v>18</v>
-      </c>
-      <c r="I238" t="s">
+      <c r="F257" t="s">
+        <v>171</v>
+      </c>
+      <c r="G257" t="s">
+        <v>228</v>
+      </c>
+      <c r="H257" t="s">
+        <v>18</v>
+      </c>
+      <c r="I257" t="s">
         <v>33</v>
       </c>
     </row>
@@ -8215,7 +8790,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{caa65e29-8aa9-4f2a-9acb-f86055e209bf}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{38d88559-cad2-493a-a4cb-a4ade609e552}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8235,16 +8810,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -8264,16 +8839,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C2" t="s">
         <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -8293,16 +8868,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="E3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -8322,16 +8897,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E4" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -8351,16 +8926,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -8380,16 +8955,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C6" t="s">
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E6" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -8409,16 +8984,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C7" t="s">
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E7" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -8438,16 +9013,16 @@
         <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C8" t="s">
         <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E8" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -8467,16 +9042,16 @@
         <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C9" t="s">
         <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E9" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -8496,16 +9071,16 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C10" t="s">
         <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E10" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -8522,19 +9097,19 @@
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B11" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="E11" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -8557,8 +9132,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{367f1a54-3a01-42b0-ae0c-0b574d75d4f3}">
-  <dimension ref="A1:F43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{66ba4e44-228a-42e6-aa3f-383979f072d2}">
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -8574,13 +9149,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -8594,13 +9169,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E2" t="s">
         <v>104</v>
@@ -8614,13 +9189,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E3" t="s">
         <v>114</v>
@@ -8634,16 +9209,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C4" t="s">
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E4" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -8654,13 +9229,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E5" t="s">
         <v>32</v>
@@ -8674,13 +9249,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C6" t="s">
         <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
@@ -8694,16 +9269,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E7" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -8714,16 +9289,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C8" t="s">
         <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E8" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -8734,16 +9309,16 @@
         <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E9" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -8754,13 +9329,13 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C10" t="s">
         <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
@@ -8774,13 +9349,13 @@
         <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C11" t="s">
         <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E11" t="s">
         <v>141</v>
@@ -8794,13 +9369,13 @@
         <v>108</v>
       </c>
       <c r="B12" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C12" t="s">
         <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -8814,13 +9389,13 @@
         <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C13" t="s">
         <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E13" t="s">
         <v>129</v>
@@ -8834,13 +9409,13 @@
         <v>108</v>
       </c>
       <c r="B14" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C14" t="s">
         <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -8854,13 +9429,13 @@
         <v>108</v>
       </c>
       <c r="B15" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C15" t="s">
         <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -8874,13 +9449,13 @@
         <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C16" t="s">
         <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
@@ -8894,16 +9469,16 @@
         <v>108</v>
       </c>
       <c r="B17" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C17" t="s">
         <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E17" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -8914,16 +9489,16 @@
         <v>108</v>
       </c>
       <c r="B18" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C18" t="s">
         <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E18" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -8934,13 +9509,13 @@
         <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C19" t="s">
         <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -8954,16 +9529,16 @@
         <v>157</v>
       </c>
       <c r="B20" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C20" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D20" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E20" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -8974,13 +9549,13 @@
         <v>157</v>
       </c>
       <c r="B21" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C21" t="s">
         <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E21" t="s">
         <v>69</v>
@@ -8994,16 +9569,16 @@
         <v>157</v>
       </c>
       <c r="B22" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C22" t="s">
         <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E22" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -9014,13 +9589,13 @@
         <v>157</v>
       </c>
       <c r="B23" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C23" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D23" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E23" t="s">
         <v>133</v>
@@ -9034,13 +9609,13 @@
         <v>157</v>
       </c>
       <c r="B24" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C24" t="s">
         <v>142</v>
       </c>
       <c r="D24" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E24" t="s">
         <v>69</v>
@@ -9057,13 +9632,13 @@
         <v>260</v>
       </c>
       <c r="C25" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D25" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="E25" t="s">
-        <v>146</v>
+        <v>273</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -9074,13 +9649,13 @@
         <v>157</v>
       </c>
       <c r="B26" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>167</v>
       </c>
       <c r="D26" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="E26" t="s">
         <v>146</v>
@@ -9091,19 +9666,19 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="B27" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
@@ -9111,116 +9686,116 @@
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B28" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C28" t="s">
-        <v>189</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B29" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="D29" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B30" t="s">
+        <v>256</v>
+      </c>
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" t="s">
         <v>259</v>
       </c>
-      <c r="C30" t="s">
-        <v>189</v>
-      </c>
-      <c r="D30" t="s">
-        <v>252</v>
-      </c>
       <c r="E30" t="s">
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B31" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="D31" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B32" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C32" t="s">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B33" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="D33" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -9231,36 +9806,36 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C34" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D34" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="D35" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
@@ -9271,16 +9846,16 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B36" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
@@ -9291,16 +9866,16 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B37" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="D37" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -9311,56 +9886,56 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B38" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="D38" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B39" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C39" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B40" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
@@ -9371,36 +9946,36 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B41" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C41" t="s">
-        <v>189</v>
+        <v>78</v>
       </c>
       <c r="D41" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B42" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="D42" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
@@ -9411,22 +9986,122 @@
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B43" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C43" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D43" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>191</v>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15">
+      <c r="A44" t="s">
+        <v>218</v>
+      </c>
+      <c r="B44" t="s">
+        <v>266</v>
+      </c>
+      <c r="C44" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" t="s">
+        <v>255</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15">
+      <c r="A45" t="s">
+        <v>218</v>
+      </c>
+      <c r="B45" t="s">
+        <v>267</v>
+      </c>
+      <c r="C45" t="s">
+        <v>197</v>
+      </c>
+      <c r="D45" t="s">
+        <v>259</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15">
+      <c r="A46" t="s">
+        <v>218</v>
+      </c>
+      <c r="B46" t="s">
+        <v>261</v>
+      </c>
+      <c r="C46" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" t="s">
+        <v>272</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15">
+      <c r="A47" t="s">
+        <v>218</v>
+      </c>
+      <c r="B47" t="s">
+        <v>263</v>
+      </c>
+      <c r="C47" t="s">
+        <v>160</v>
+      </c>
+      <c r="D47" t="s">
+        <v>272</v>
+      </c>
+      <c r="E47" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15">
+      <c r="A48" t="s">
+        <v>218</v>
+      </c>
+      <c r="B48" t="s">
+        <v>263</v>
+      </c>
+      <c r="C48" t="s">
+        <v>197</v>
+      </c>
+      <c r="D48" t="s">
+        <v>259</v>
+      </c>
+      <c r="E48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/zastepstwa.xlsx
+++ b/zastepstwa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="219">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -72,312 +72,342 @@
     <t>Technika w produkcji cukierniczej</t>
   </si>
   <si>
+    <t>prs</t>
+  </si>
+  <si>
+    <t>Uczniowie przychodzą później</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Ulanowska Magdalena</t>
+  </si>
+  <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>Zajęcia z wychowawcą</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Vacat DoradztwoZawodowe</t>
+  </si>
+  <si>
+    <t>3K</t>
+  </si>
+  <si>
+    <t>Doradztwo zawodowe</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Krzemińska Beata</t>
+  </si>
+  <si>
+    <t>Dodatkowo płatne</t>
+  </si>
+  <si>
+    <t>2, 08:50-09:35</t>
+  </si>
+  <si>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>2S</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - E-commerce</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Smirnow-Zechman Eleonora</t>
+  </si>
+  <si>
+    <t>Nestoruk Lidia</t>
+  </si>
+  <si>
+    <t>3WA|ch1</t>
+  </si>
+  <si>
+    <t>Wychowanie fizyczne</t>
+  </si>
+  <si>
+    <t>sg4</t>
+  </si>
+  <si>
+    <t>Dalach Krystyna</t>
+  </si>
+  <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>3, 09:40-10:25</t>
+  </si>
+  <si>
+    <t>3FA</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t>prF3</t>
+  </si>
+  <si>
+    <t>Sobczak Anna</t>
+  </si>
+  <si>
+    <t>1CA|JA1</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
+    <t>1CA|JA2</t>
+  </si>
+  <si>
+    <t>Bezpłatne</t>
+  </si>
+  <si>
+    <t>Obsługa klientów</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Skarupa Agnieszka</t>
+  </si>
+  <si>
+    <t>4, 10:35-11:20</t>
+  </si>
+  <si>
+    <t>3S</t>
+  </si>
+  <si>
+    <t>Zajęcia biblioteczne</t>
+  </si>
+  <si>
+    <t>bib</t>
+  </si>
+  <si>
+    <t>Nowak Damiana</t>
+  </si>
+  <si>
+    <t>3CA</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Bokuniewicz Sylwia</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Biezmienow Małgorzata</t>
+  </si>
+  <si>
+    <t>5, 11:25-12:10</t>
+  </si>
+  <si>
+    <t>Bujanowska Iwona</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>p. Krzemińska, doradztwo zawodowe na lekcji 5</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>Matematyka</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Zastępstwo</t>
+  </si>
+  <si>
+    <t>p. Mocarski, technologia za lekcję 10</t>
+  </si>
+  <si>
+    <t>2FA</t>
+  </si>
+  <si>
+    <t>2WB</t>
+  </si>
+  <si>
+    <t>Rejno Julita</t>
+  </si>
+  <si>
+    <t>1CA|DZ</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Antoszewska Joanna</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Kończyńska Małgorzata</t>
+  </si>
+  <si>
+    <t>6, 12:25-13:10</t>
+  </si>
+  <si>
+    <t>3WA</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Filipiak Wiesław</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
     <t>34</t>
   </si>
   <si>
-    <t>Kończyńska Małgorzata</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Dodatkowo płatne</t>
-  </si>
-  <si>
-    <t>Ulanowska Magdalena</t>
-  </si>
-  <si>
-    <t>2TH</t>
-  </si>
-  <si>
-    <t>Zajęcia z wychowawcą</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Uczniowie przychodzą później</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Vacat DoradztwoZawodowe</t>
-  </si>
-  <si>
-    <t>3K</t>
-  </si>
-  <si>
-    <t>Doradztwo zawodowe</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Krzemińska Beata</t>
-  </si>
-  <si>
-    <t>2, 08:50-09:35</t>
-  </si>
-  <si>
-    <t>Hudziec Agnieszka</t>
-  </si>
-  <si>
-    <t>2S</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - E-commerce</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Smirnow-Zechman Eleonora</t>
-  </si>
-  <si>
-    <t>Nestoruk Lidia</t>
-  </si>
-  <si>
-    <t>3WA|ch1</t>
-  </si>
-  <si>
-    <t>Wychowanie fizyczne</t>
-  </si>
-  <si>
-    <t>sg4</t>
-  </si>
-  <si>
-    <t>Dalach Krystyna</t>
-  </si>
-  <si>
-    <t>1FB</t>
-  </si>
-  <si>
-    <t>3, 09:40-10:25</t>
-  </si>
-  <si>
-    <t>3FA</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t>prF3</t>
-  </si>
-  <si>
-    <t>Sobczak Anna</t>
-  </si>
-  <si>
-    <t>1CA|JA1</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Karczmarz Aleksandra</t>
-  </si>
-  <si>
-    <t>1CA|JA2</t>
-  </si>
-  <si>
-    <t>Bezpłatne</t>
-  </si>
-  <si>
-    <t>Obsługa klientów</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Skarupa Agnieszka</t>
-  </si>
-  <si>
-    <t>4, 10:35-11:20</t>
-  </si>
-  <si>
-    <t>3S</t>
-  </si>
-  <si>
-    <t>Zajęcia biblioteczne</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>Nowak Damiana</t>
-  </si>
-  <si>
-    <t>3CA</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>Bokuniewicz Sylwia</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>Biezmienow Małgorzata</t>
-  </si>
-  <si>
-    <t>5, 11:25-12:10</t>
-  </si>
-  <si>
-    <t>Bujanowska Iwona</t>
-  </si>
-  <si>
-    <t>3M</t>
-  </si>
-  <si>
-    <t>p. Krzemińska, doradztwo zawodowe na lekcji 5</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>Matematyka</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Zastępstwo</t>
-  </si>
-  <si>
-    <t>p. Mocarski, technologia za lekcję 10</t>
-  </si>
-  <si>
-    <t>2FA</t>
-  </si>
-  <si>
-    <t>2WB</t>
-  </si>
-  <si>
-    <t>Rejno Julita</t>
-  </si>
-  <si>
-    <t>1CA|DZ</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Antoszewska Joanna</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>6, 12:25-13:10</t>
-  </si>
-  <si>
-    <t>3WA</t>
-  </si>
-  <si>
-    <t>26</t>
+    <t>Derezińska Katarzyna</t>
+  </si>
+  <si>
+    <t>7, 13:15-14:00</t>
+  </si>
+  <si>
+    <t>1TH</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>p. Derezińska, za środę 18.03</t>
+  </si>
+  <si>
+    <t>8, 14:05-14:50</t>
+  </si>
+  <si>
+    <t>p. Leńczowska, techniki fryzjerskie za lekcję 10</t>
+  </si>
+  <si>
+    <t>9, 14:55-15:40</t>
+  </si>
+  <si>
+    <t>1TFB</t>
+  </si>
+  <si>
+    <t>Uczniowie zwolnieni do domu</t>
+  </si>
+  <si>
+    <t>10, 15:45-16:30</t>
+  </si>
+  <si>
+    <t>2TFB</t>
+  </si>
+  <si>
+    <t>17.03.2026</t>
+  </si>
+  <si>
+    <t>3TH</t>
+  </si>
+  <si>
+    <t>Wakat3 edukacja zdrow.</t>
+  </si>
+  <si>
+    <t>3CA|edu</t>
+  </si>
+  <si>
+    <t>Edukacja zdrowotna</t>
+  </si>
+  <si>
+    <t>Mocarski Arkadiusz</t>
+  </si>
+  <si>
+    <t>3FA|edu</t>
+  </si>
+  <si>
+    <t>3M|edu</t>
+  </si>
+  <si>
+    <t>3TFA|edu</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>Chemia</t>
   </si>
   <si>
     <t>Nowak Magdalena</t>
   </si>
   <si>
-    <t>Język polski</t>
+    <t>5TF</t>
+  </si>
+  <si>
+    <t>1CA</t>
+  </si>
+  <si>
+    <t>1TFA</t>
   </si>
   <si>
     <t>33</t>
   </si>
   <si>
-    <t>Derezińska Katarzyna</t>
-  </si>
-  <si>
-    <t>7, 13:15-14:00</t>
-  </si>
-  <si>
-    <t>1TH</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>p. Derezińska, za środę 18.03</t>
-  </si>
-  <si>
-    <t>8, 14:05-14:50</t>
-  </si>
-  <si>
-    <t>p. Leńczowska, techniki fryzjerskie za lekcję 10</t>
-  </si>
-  <si>
-    <t>9, 14:55-15:40</t>
-  </si>
-  <si>
-    <t>1TFB</t>
-  </si>
-  <si>
-    <t>Uczniowie zwolnieni do domu</t>
-  </si>
-  <si>
-    <t>10, 15:45-16:30</t>
-  </si>
-  <si>
-    <t>2TFB</t>
-  </si>
-  <si>
-    <t>17.03.2026</t>
-  </si>
-  <si>
-    <t>3TH</t>
-  </si>
-  <si>
-    <t>Wakat3 edukacja zdrow.</t>
-  </si>
-  <si>
-    <t>3CA|edu</t>
-  </si>
-  <si>
-    <t>Edukacja zdrowotna</t>
-  </si>
-  <si>
-    <t>Mocarski Arkadiusz</t>
-  </si>
-  <si>
-    <t>3FA|edu</t>
-  </si>
-  <si>
-    <t>3M|edu</t>
-  </si>
-  <si>
-    <t>3TFA|edu</t>
-  </si>
-  <si>
-    <t>3TFA</t>
-  </si>
-  <si>
-    <t>Chemia</t>
-  </si>
-  <si>
-    <t>1CA</t>
-  </si>
-  <si>
-    <t>1TFA</t>
-  </si>
-  <si>
     <t>1K</t>
   </si>
   <si>
+    <t>Filusz Marzena</t>
+  </si>
+  <si>
+    <t>Podstawy fryzjerstwa</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Mikołajczak Sylwia</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
     <t>1WB</t>
   </si>
   <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
     <t>Kruk Marcin</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>2B</t>
   </si>
   <si>
@@ -411,6 +441,12 @@
     <t>2WA|edu</t>
   </si>
   <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
     <t>1FA|JA1</t>
   </si>
   <si>
@@ -420,27 +456,57 @@
     <t>p. Karczmarz, j. angielski za lekcję 1</t>
   </si>
   <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>p. Krzemińska, sala nr 5 za lekcję 1</t>
+  </si>
+  <si>
+    <t>5TH</t>
+  </si>
+  <si>
+    <t>Wójcik Kamil</t>
   </si>
   <si>
     <t>1S</t>
   </si>
   <si>
+    <t>Technologie produkcji cukierniczej</t>
+  </si>
+  <si>
+    <t>Obsługa klienta</t>
+  </si>
+  <si>
+    <t>Socha Dariusz</t>
+  </si>
+  <si>
     <t>2K|CH</t>
   </si>
   <si>
     <t>1WA</t>
   </si>
   <si>
+    <t>p. Smirnow-Zechman, BiZ za lekcję 3</t>
+  </si>
+  <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Leńczowska Iwona</t>
+  </si>
+  <si>
     <t>2S|DZ</t>
   </si>
   <si>
     <t>aq1</t>
   </si>
   <si>
+    <t>Pietrycha Małgorzata</t>
+  </si>
+  <si>
     <t>Wakat1 j. niemiecki</t>
   </si>
   <si>
@@ -462,19 +528,22 @@
     <t>2FA|JA2</t>
   </si>
   <si>
+    <t>3TFB</t>
+  </si>
+  <si>
+    <t>3FB</t>
+  </si>
+  <si>
     <t>3TFB|CH</t>
   </si>
   <si>
     <t>Zaleska Magdalena</t>
   </si>
   <si>
-    <t>Historia</t>
-  </si>
-  <si>
     <t>19</t>
   </si>
   <si>
-    <t>3FB</t>
+    <t>1CB</t>
   </si>
   <si>
     <t>1TFA|JA2</t>
@@ -492,12 +561,15 @@
     <t>20.03.2026</t>
   </si>
   <si>
-    <t>5TH</t>
+    <t>2CA</t>
   </si>
   <si>
     <t>3TFA|JA1</t>
   </si>
   <si>
+    <t>2FC</t>
+  </si>
+  <si>
     <t>1FA</t>
   </si>
   <si>
@@ -582,9 +654,6 @@
     <t>15:40-15:45</t>
   </si>
   <si>
-    <t>Leńczowska Iwona</t>
-  </si>
-  <si>
     <t>17:20-17:25</t>
   </si>
   <si>
@@ -594,7 +663,19 @@
     <t>08:45-08:50</t>
   </si>
   <si>
+    <t>Ostrowska Ewa</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
     <t>12:10-12:25</t>
+  </si>
+  <si>
+    <t>Piątek-Pawłowska Bożena</t>
+  </si>
+  <si>
+    <t>Dalach Sławomir</t>
   </si>
   <si>
     <t>piętro_3</t>
@@ -1047,7 +1128,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{97223821-4863-4d41-90a9-dbb63373630f}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7f191393-d419-46d3-9876-13d8e3e0ad19}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1068,8 +1149,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{49a28097-69f0-4eff-9ac6-a84960d98c76}">
-  <dimension ref="A1:I115"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{3630292e-a9b3-4232-97fe-b926b8fa48f3}">
+  <dimension ref="A1:I142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1161,13 +1242,13 @@
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
@@ -1178,25 +1259,25 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>27</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>28</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
         <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
@@ -1204,28 +1285,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>33</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>34</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>35</v>
       </c>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -1233,28 +1314,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>38</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>39</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>40</v>
       </c>
-      <c r="G6" t="s">
-        <v>41</v>
-      </c>
       <c r="H6" t="s">
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -1262,7 +1343,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -1291,28 +1372,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
         <v>28</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
         <v>29</v>
-      </c>
-      <c r="G8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
@@ -1320,28 +1401,28 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
         <v>43</v>
       </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>44</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>45</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>46</v>
       </c>
-      <c r="G9" t="s">
-        <v>47</v>
-      </c>
       <c r="H9" t="s">
         <v>18</v>
       </c>
       <c r="I9" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
@@ -1349,28 +1430,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
         <v>37</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>38</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>39</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>40</v>
       </c>
-      <c r="G10" t="s">
-        <v>41</v>
-      </c>
       <c r="H10" t="s">
         <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
@@ -1378,28 +1459,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" t="s">
         <v>48</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>49</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>50</v>
       </c>
-      <c r="G11" t="s">
-        <v>51</v>
-      </c>
       <c r="H11" t="s">
         <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1407,28 +1488,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" t="s">
         <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
@@ -1436,7 +1517,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
@@ -1445,19 +1526,19 @@
         <v>21</v>
       </c>
       <c r="E13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" t="s">
         <v>54</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>55</v>
       </c>
-      <c r="G13" t="s">
-        <v>56</v>
-      </c>
       <c r="H13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
@@ -1465,28 +1546,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
         <v>57</v>
       </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>58</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>59</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>60</v>
       </c>
-      <c r="G14" t="s">
-        <v>61</v>
-      </c>
       <c r="H14" t="s">
         <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1494,28 +1575,28 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
         <v>37</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>38</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>39</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>40</v>
       </c>
-      <c r="G15" t="s">
-        <v>41</v>
-      </c>
       <c r="H15" t="s">
         <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
@@ -1523,28 +1604,28 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
       </c>
       <c r="F16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" t="s">
         <v>63</v>
       </c>
-      <c r="G16" t="s">
-        <v>64</v>
-      </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -1552,7 +1633,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
@@ -1561,19 +1642,19 @@
         <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" t="s">
         <v>65</v>
       </c>
-      <c r="G17" t="s">
-        <v>66</v>
-      </c>
       <c r="H17" t="s">
         <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -1581,28 +1662,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
         <v>67</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>68</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" t="s">
         <v>69</v>
       </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="I18" t="s">
         <v>29</v>
-      </c>
-      <c r="G18" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" t="s">
-        <v>70</v>
-      </c>
-      <c r="I18" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1610,28 +1691,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
         <v>67</v>
       </c>
-      <c r="C19" t="s">
-        <v>68</v>
-      </c>
       <c r="D19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" t="s">
         <v>71</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>72</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>73</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>74</v>
       </c>
-      <c r="H19" t="s">
-        <v>75</v>
-      </c>
       <c r="I19" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -1639,28 +1720,28 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" t="s">
         <v>59</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>60</v>
       </c>
-      <c r="G20" t="s">
-        <v>61</v>
-      </c>
       <c r="H20" t="s">
         <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -1668,28 +1749,28 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" t="s">
         <v>39</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>40</v>
       </c>
-      <c r="G21" t="s">
-        <v>41</v>
-      </c>
       <c r="H21" t="s">
         <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
@@ -1697,28 +1778,28 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" t="s">
         <v>78</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" t="s">
         <v>79</v>
       </c>
-      <c r="E22" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>80</v>
       </c>
-      <c r="G22" t="s">
-        <v>81</v>
-      </c>
       <c r="H22" t="s">
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
@@ -1726,28 +1807,28 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
       </c>
       <c r="F23" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" t="s">
         <v>82</v>
       </c>
-      <c r="G23" t="s">
-        <v>17</v>
-      </c>
       <c r="H23" t="s">
         <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
@@ -1755,28 +1836,28 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s">
         <v>20</v>
       </c>
       <c r="D24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" t="s">
         <v>44</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>45</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>46</v>
       </c>
-      <c r="G24" t="s">
-        <v>47</v>
-      </c>
       <c r="H24" t="s">
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -1787,25 +1868,25 @@
         <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
         <v>84</v>
       </c>
       <c r="E25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" t="s">
         <v>28</v>
       </c>
-      <c r="F25" t="s">
+      <c r="H25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" t="s">
         <v>29</v>
-      </c>
-      <c r="G25" t="s">
-        <v>30</v>
-      </c>
-      <c r="H25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -1816,13 +1897,13 @@
         <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F26" t="s">
         <v>85</v>
@@ -1834,7 +1915,7 @@
         <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
@@ -1845,10 +1926,10 @@
         <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E27" t="s">
         <v>87</v>
@@ -1863,7 +1944,7 @@
         <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -1874,25 +1955,25 @@
         <v>83</v>
       </c>
       <c r="C28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" t="s">
         <v>78</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" t="s">
         <v>79</v>
       </c>
-      <c r="E28" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>80</v>
       </c>
-      <c r="G28" t="s">
-        <v>81</v>
-      </c>
       <c r="H28" t="s">
         <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
@@ -1906,22 +1987,22 @@
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" t="s">
         <v>59</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>60</v>
       </c>
-      <c r="G29" t="s">
-        <v>61</v>
-      </c>
       <c r="H29" t="s">
         <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
@@ -1932,25 +2013,25 @@
         <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
         <v>91</v>
       </c>
       <c r="E30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F30" t="s">
         <v>92</v>
       </c>
       <c r="G30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
@@ -1961,25 +2042,25 @@
         <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E31" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" t="s">
         <v>39</v>
       </c>
-      <c r="F31" t="s">
-        <v>40</v>
-      </c>
       <c r="G31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H31" t="s">
         <v>93</v>
       </c>
       <c r="I31" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
@@ -1990,25 +2071,25 @@
         <v>90</v>
       </c>
       <c r="C32" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" t="s">
         <v>78</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" t="s">
         <v>79</v>
       </c>
-      <c r="E32" t="s">
-        <v>39</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>80</v>
       </c>
-      <c r="G32" t="s">
-        <v>81</v>
-      </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
@@ -2019,25 +2100,25 @@
         <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E33" t="s">
+        <v>71</v>
+      </c>
+      <c r="F33" t="s">
         <v>72</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>73</v>
-      </c>
-      <c r="G33" t="s">
-        <v>74</v>
       </c>
       <c r="H33" t="s">
         <v>95</v>
       </c>
       <c r="I33" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
@@ -2048,16 +2129,16 @@
         <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D34" t="s">
         <v>97</v>
       </c>
       <c r="E34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" t="s">
         <v>72</v>
-      </c>
-      <c r="F34" t="s">
-        <v>73</v>
       </c>
       <c r="G34" t="s">
         <v>98</v>
@@ -2066,7 +2147,7 @@
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
@@ -2077,16 +2158,16 @@
         <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D35" t="s">
         <v>100</v>
       </c>
       <c r="E35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" t="s">
         <v>72</v>
-      </c>
-      <c r="F35" t="s">
-        <v>73</v>
       </c>
       <c r="G35" t="s">
         <v>98</v>
@@ -2095,7 +2176,7 @@
         <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
@@ -2118,13 +2199,13 @@
         <v>23</v>
       </c>
       <c r="G36" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
@@ -2144,7 +2225,7 @@
         <v>105</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s">
         <v>106</v>
@@ -2153,7 +2234,7 @@
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
@@ -2173,7 +2254,7 @@
         <v>105</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s">
         <v>106</v>
@@ -2182,7 +2263,7 @@
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
@@ -2202,7 +2283,7 @@
         <v>105</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s">
         <v>106</v>
@@ -2211,7 +2292,7 @@
         <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
@@ -2231,7 +2312,7 @@
         <v>105</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s">
         <v>106</v>
@@ -2240,7 +2321,7 @@
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
@@ -2248,10 +2329,10 @@
         <v>101</v>
       </c>
       <c r="B41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" t="s">
         <v>31</v>
-      </c>
-      <c r="C41" t="s">
-        <v>32</v>
       </c>
       <c r="D41" t="s">
         <v>110</v>
@@ -2263,13 +2344,13 @@
         <v>85</v>
       </c>
       <c r="G41" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="H41" t="s">
         <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
@@ -2277,22 +2358,22 @@
         <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D42" t="s">
         <v>14</v>
       </c>
       <c r="E42" t="s">
+        <v>38</v>
+      </c>
+      <c r="F42" t="s">
         <v>39</v>
       </c>
-      <c r="F42" t="s">
-        <v>40</v>
-      </c>
       <c r="G42" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
@@ -2306,7 +2387,7 @@
         <v>101</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C43" t="s">
         <v>20</v>
@@ -2321,13 +2402,13 @@
         <v>23</v>
       </c>
       <c r="G43" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
@@ -2335,28 +2416,28 @@
         <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E44" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="F44" t="s">
         <v>85</v>
       </c>
       <c r="G44" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
@@ -2364,22 +2445,22 @@
         <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F45" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
@@ -2393,28 +2474,28 @@
         <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C46" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="E46" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="F46" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="G46" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
@@ -2422,28 +2503,28 @@
         <v>101</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="E47" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="F47" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="G47" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
@@ -2451,28 +2532,28 @@
         <v>101</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="D48" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F48" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="G48" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
@@ -2480,28 +2561,28 @@
         <v>101</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="D49" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E49" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="F49" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G49" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
@@ -2509,28 +2590,28 @@
         <v>101</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="E50" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="F50" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="G50" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
@@ -2538,13 +2619,13 @@
         <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E51" t="s">
         <v>111</v>
@@ -2553,13 +2634,13 @@
         <v>85</v>
       </c>
       <c r="G51" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
@@ -2567,22 +2648,22 @@
         <v>101</v>
       </c>
       <c r="B52" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D52" t="s">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="E52" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="F52" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="G52" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
@@ -2596,13 +2677,13 @@
         <v>101</v>
       </c>
       <c r="B53" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C53" t="s">
         <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E53" t="s">
         <v>87</v>
@@ -2611,13 +2692,13 @@
         <v>23</v>
       </c>
       <c r="G53" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
@@ -2625,13 +2706,13 @@
         <v>101</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D54" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="E54" t="s">
         <v>111</v>
@@ -2640,13 +2721,13 @@
         <v>85</v>
       </c>
       <c r="G54" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
@@ -2654,28 +2735,28 @@
         <v>101</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C55" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E55" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="F55" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="G55" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
@@ -2683,28 +2764,28 @@
         <v>101</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C56" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D56" t="s">
-        <v>115</v>
+        <v>14</v>
       </c>
       <c r="E56" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="F56" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="G56" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
@@ -2712,28 +2793,28 @@
         <v>101</v>
       </c>
       <c r="B57" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C57" t="s">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="E57" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="F57" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="G57" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
@@ -2741,28 +2822,28 @@
         <v>101</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C58" t="s">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F58" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="G58" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
@@ -2770,28 +2851,28 @@
         <v>101</v>
       </c>
       <c r="B59" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="C59" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" t="s">
+        <v>71</v>
+      </c>
+      <c r="F59" t="s">
+        <v>88</v>
+      </c>
+      <c r="G59" t="s">
         <v>118</v>
       </c>
-      <c r="E59" t="s">
-        <v>121</v>
-      </c>
-      <c r="F59" t="s">
-        <v>117</v>
-      </c>
-      <c r="G59" t="s">
-        <v>25</v>
-      </c>
       <c r="H59" t="s">
         <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
@@ -2799,28 +2880,28 @@
         <v>101</v>
       </c>
       <c r="B60" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="C60" t="s">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="E60" t="s">
+        <v>119</v>
+      </c>
+      <c r="F60" t="s">
+        <v>120</v>
+      </c>
+      <c r="G60" t="s">
         <v>121</v>
       </c>
-      <c r="F60" t="s">
-        <v>117</v>
-      </c>
-      <c r="G60" t="s">
-        <v>25</v>
-      </c>
       <c r="H60" t="s">
         <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
@@ -2828,254 +2909,254 @@
         <v>101</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="C61" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D61" t="s">
+        <v>122</v>
+      </c>
+      <c r="E61" t="s">
+        <v>71</v>
+      </c>
+      <c r="F61" t="s">
+        <v>88</v>
+      </c>
+      <c r="G61" t="s">
         <v>118</v>
       </c>
-      <c r="E61" t="s">
-        <v>121</v>
-      </c>
-      <c r="F61" t="s">
-        <v>117</v>
-      </c>
-      <c r="G61" t="s">
-        <v>25</v>
-      </c>
       <c r="H61" t="s">
         <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="C62" t="s">
         <v>20</v>
       </c>
       <c r="D62" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="E62" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="F62" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="G62" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="D63" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="E63" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="F63" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G63" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E64" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="F64" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="G64" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B65" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="D65" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E65" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="F65" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G65" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="D66" t="s">
         <v>128</v>
       </c>
       <c r="E66" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="F66" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G66" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B67" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="C67" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="D67" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E67" t="s">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="F67" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="G67" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="H67" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B68" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E68" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="F68" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G68" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B69" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C69" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D69" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="E69" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F69" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="G69" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
@@ -3086,1272 +3167,1272 @@
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B70" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C70" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="E70" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="F70" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="G70" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="D71" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E71" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="F71" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="G71" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B72" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="D72" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E72" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="F72" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="G72" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B73" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="D73" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="E73" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="F73" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="G73" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B74" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="C74" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="D74" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="E74" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F74" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G74" t="s">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B75" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="C75" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D75" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E75" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="F75" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G75" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="H75" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="I75" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="C76" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D76" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="E76" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="F76" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="G76" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="C77" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D77" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="E77" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F77" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="G77" t="s">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="C78" t="s">
+        <v>77</v>
+      </c>
+      <c r="D78" t="s">
+        <v>141</v>
+      </c>
+      <c r="E78" t="s">
+        <v>48</v>
+      </c>
+      <c r="F78" t="s">
         <v>139</v>
       </c>
-      <c r="D78" t="s">
+      <c r="G78" t="s">
         <v>140</v>
       </c>
-      <c r="E78" t="s">
-        <v>141</v>
-      </c>
-      <c r="F78" t="s">
-        <v>142</v>
-      </c>
-      <c r="G78" t="s">
-        <v>143</v>
-      </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B79" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="C79" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D79" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="E79" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="F79" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="G79" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B80" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="C80" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="D80" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E80" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="F80" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="G80" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="H80" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="I80" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B81" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="C81" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="D81" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E81" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F81" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="G81" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B82" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C82" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D82" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E82" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F82" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G82" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B83" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C83" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D83" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E83" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="F83" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="G83" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B84" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C84" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D84" t="s">
-        <v>145</v>
+        <v>14</v>
       </c>
       <c r="E84" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="F84" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="G84" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D85" t="s">
-        <v>146</v>
+        <v>76</v>
       </c>
       <c r="E85" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F85" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="G85" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C86" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="D86" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E86" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F86" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="G86" t="s">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B87" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C87" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D87" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E87" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="F87" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="G87" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B88" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C88" t="s">
-        <v>147</v>
+        <v>20</v>
       </c>
       <c r="D88" t="s">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="E88" t="s">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="F88" t="s">
-        <v>149</v>
+        <v>23</v>
       </c>
       <c r="G88" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H88" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="I88" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B89" t="s">
         <v>83</v>
       </c>
       <c r="C89" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D89" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="E89" t="s">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="F89" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="G89" t="s">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B90" t="s">
         <v>83</v>
       </c>
       <c r="C90" t="s">
-        <v>147</v>
+        <v>36</v>
       </c>
       <c r="D90" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E90" t="s">
-        <v>148</v>
+        <v>38</v>
       </c>
       <c r="F90" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="G90" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C91" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="D91" t="s">
+        <v>21</v>
+      </c>
+      <c r="E91" t="s">
+        <v>53</v>
+      </c>
+      <c r="F91" t="s">
+        <v>54</v>
+      </c>
+      <c r="G91" t="s">
         <v>151</v>
       </c>
-      <c r="E91" t="s">
-        <v>39</v>
-      </c>
-      <c r="F91" t="s">
-        <v>138</v>
-      </c>
-      <c r="G91" t="s">
-        <v>25</v>
-      </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B92" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C92" t="s">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="D92" t="s">
         <v>152</v>
       </c>
       <c r="E92" t="s">
-        <v>148</v>
+        <v>38</v>
       </c>
       <c r="F92" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G92" t="s">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B93" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C93" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D93" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E93" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="F93" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="G93" t="s">
-        <v>25</v>
+        <v>165</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C94" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D94" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E94" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F94" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="G94" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B95" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C95" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D95" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="E95" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F95" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="G95" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C96" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D96" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="E96" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="F96" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="G96" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C97" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D97" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E97" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F97" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="G97" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B98" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C98" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D98" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E98" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F98" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="G98" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="C99" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="D99" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="E99" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="F99" t="s">
-        <v>117</v>
+        <v>159</v>
       </c>
       <c r="G99" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="C100" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="D100" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="E100" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="F100" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="G100" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="B101" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="C101" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="D101" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="E101" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="F101" t="s">
-        <v>117</v>
+        <v>159</v>
       </c>
       <c r="G101" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
       </c>
       <c r="I101" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="B102" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="C102" t="s">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="E102" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="F102" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="G102" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <